--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD3DF82-4595-4864-947A-4B58CE47344E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFB1D01-8585-4E75-952F-3C66818A376E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -818,54 +818,54 @@
         <v>668.82</v>
       </c>
       <c r="G2" s="1">
-        <f>E2*F2</f>
+        <f t="shared" ref="G2:G34" si="0">E2*F2</f>
         <v>26.953446000000003</v>
       </c>
       <c r="H2" s="11">
-        <v>-5.7799999999999997E-2</v>
+        <v>8.1299999999999997E-2</v>
       </c>
       <c r="I2" s="11">
-        <v>0.29370000000000002</v>
+        <v>0.29920000000000002</v>
       </c>
       <c r="J2" s="9">
-        <f>IFERROR(H2/I2,"")</f>
-        <v>-0.1967994552264215</v>
+        <f t="shared" ref="J2:J34" si="1">IFERROR(H2/I2,"")</f>
+        <v>0.27172459893048123</v>
       </c>
       <c r="K2" s="9">
-        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-4.1798881774999651E-2</v>
+        <f t="shared" ref="K2:K34" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6909731162532133E-2</v>
       </c>
       <c r="L2" s="12">
-        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>630.16220400000009</v>
+        <f t="shared" ref="L2:L19" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
+        <v>723.195066</v>
       </c>
       <c r="M2" s="12">
-        <f>F2/(1+I2-H2)</f>
-        <v>494.87236403995558</v>
+        <f t="shared" ref="M2:M34" si="4">F2/(1+I2-H2)</f>
+        <v>549.15838738812715</v>
       </c>
       <c r="N2" s="12">
-        <f>L2-F2</f>
-        <v>-38.657795999999962</v>
+        <f t="shared" ref="N2:N34" si="5">L2-F2</f>
+        <v>54.375065999999947</v>
       </c>
       <c r="O2" s="12">
-        <f>0.5*(M2-F2)</f>
-        <v>-86.973817980022233</v>
+        <f t="shared" ref="O2:O34" si="6">0.5*(M2-F2)</f>
+        <v>-59.830806305936449</v>
       </c>
       <c r="P2" s="14">
-        <f>N2+O2</f>
-        <v>-125.63161398002219</v>
+        <f t="shared" ref="P2:P34" si="7">N2+O2</f>
+        <v>-5.4557403059365015</v>
       </c>
       <c r="Q2" s="12">
-        <f>MAX($P$2:$P$280)-P2</f>
-        <v>478.14268564059375</v>
+        <f t="shared" ref="Q2:Q34" si="8">MAX($P$2:$P$280)-P2</f>
+        <v>258.62331648914221</v>
       </c>
       <c r="R2" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.0914259070182067E-3</v>
+        <f t="shared" ref="R2:R34" si="9">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>3.8666273929790201E-3</v>
       </c>
       <c r="S2" s="9">
-        <f>Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.95220458439427857</v>
+        <f t="shared" ref="S2:S34" si="10">Q2/MAX($Q$2:$Q$28)</f>
+        <v>0.95148769032138802</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -888,54 +888,54 @@
         <v>135.82</v>
       </c>
       <c r="G3" s="1">
-        <f>E3*F3</f>
+        <f t="shared" si="0"/>
         <v>25.995947999999999</v>
       </c>
       <c r="H3" s="11">
-        <v>0.17030000000000001</v>
+        <v>0.1221</v>
       </c>
       <c r="I3" s="11">
-        <v>0.2268</v>
+        <v>0.29170000000000001</v>
       </c>
       <c r="J3" s="9">
-        <f>IFERROR(H3/I3,"")</f>
-        <v>0.75088183421516752</v>
+        <f t="shared" si="1"/>
+        <v>0.41858073363044224</v>
       </c>
       <c r="K3" s="9">
-        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.15948225557456175</v>
+        <f t="shared" si="2"/>
+        <v>4.1453350400169175E-2</v>
       </c>
       <c r="L3" s="12">
-        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
-        <v>158.95014600000002</v>
+        <f t="shared" si="3"/>
+        <v>152.40362200000001</v>
       </c>
       <c r="M3" s="12">
-        <f>F3/(1+I3-H3)</f>
-        <v>128.55655466161858</v>
+        <f t="shared" si="4"/>
+        <v>116.125170998632</v>
       </c>
       <c r="N3" s="12">
-        <f>L3-F3</f>
-        <v>23.130146000000025</v>
+        <f t="shared" si="5"/>
+        <v>16.58362200000002</v>
       </c>
       <c r="O3" s="12">
-        <f>0.5*(M3-F3)</f>
-        <v>-3.6317226691907081</v>
+        <f t="shared" si="6"/>
+        <v>-9.8474145006839962</v>
       </c>
       <c r="P3" s="14">
-        <f>N3+O3</f>
-        <v>19.498423330809317</v>
+        <f t="shared" si="7"/>
+        <v>6.7362074993160235</v>
       </c>
       <c r="Q3" s="12">
-        <f>MAX($P$2:$P$280)-P3</f>
-        <v>333.01264832976227</v>
+        <f t="shared" si="8"/>
+        <v>246.43136868388967</v>
       </c>
       <c r="R3" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.0028889443555326E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.0579249522521297E-3</v>
       </c>
       <c r="S3" s="9">
-        <f>Q3/MAX($Q$2:$Q$28)</f>
-        <v>0.6631831457926588</v>
+        <f t="shared" si="10"/>
+        <v>0.90663292465208434</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -958,54 +958,54 @@
         <v>133.19999999999999</v>
       </c>
       <c r="G4" s="1">
-        <f>E4*F4</f>
+        <f t="shared" si="0"/>
         <v>23.989319999999999</v>
       </c>
       <c r="H4" s="11">
-        <v>2.5100000000000001E-2</v>
+        <v>8.1299999999999997E-2</v>
       </c>
       <c r="I4" s="11">
-        <v>0.19259999999999999</v>
+        <v>0.25829999999999997</v>
       </c>
       <c r="J4" s="9">
-        <f>IFERROR(H4/I4,"")</f>
-        <v>0.13032191069574248</v>
+        <f t="shared" si="1"/>
+        <v>0.31475029036004648</v>
       </c>
       <c r="K4" s="9">
-        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7679498053468535E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.1170699046959412E-2</v>
       </c>
       <c r="L4" s="12">
-        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
-        <v>136.54331999999997</v>
+        <f t="shared" si="3"/>
+        <v>144.02915999999999</v>
       </c>
       <c r="M4" s="12">
-        <f>F4/(1+I4-H4)</f>
-        <v>114.08993576017127</v>
+        <f t="shared" si="4"/>
+        <v>113.16907391673746</v>
       </c>
       <c r="N4" s="12">
-        <f>L4-F4</f>
-        <v>3.3433199999999772</v>
+        <f t="shared" si="5"/>
+        <v>10.829160000000002</v>
       </c>
       <c r="O4" s="12">
-        <f>0.5*(M4-F4)</f>
-        <v>-9.5550321199143582</v>
+        <f t="shared" si="6"/>
+        <v>-10.015463041631264</v>
       </c>
       <c r="P4" s="14">
-        <f>N4+O4</f>
-        <v>-6.211712119914381</v>
+        <f t="shared" si="7"/>
+        <v>0.81369695836873746</v>
       </c>
       <c r="Q4" s="12">
-        <f>MAX($P$2:$P$280)-P4</f>
-        <v>358.722783780486</v>
+        <f t="shared" si="8"/>
+        <v>252.35387922483699</v>
       </c>
       <c r="R4" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7876679297067792E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.9626892325639301E-3</v>
       </c>
       <c r="S4" s="9">
-        <f>Q4/MAX($Q$2:$Q$28)</f>
-        <v>0.71438398934164682</v>
+        <f t="shared" si="10"/>
+        <v>0.92842212738913377</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1028,54 +1028,54 @@
         <v>47.42</v>
       </c>
       <c r="G5" s="1">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>4.7420000000000006E-44</v>
       </c>
       <c r="H5" s="11">
-        <v>-8.5000000000000006E-3</v>
+        <v>-6.9999999999999999E-4</v>
       </c>
       <c r="I5" s="11">
-        <v>0.42249999999999999</v>
+        <v>0.38319999999999999</v>
       </c>
       <c r="J5" s="9">
-        <f>IFERROR(H5/I5,"")</f>
-        <v>-2.0118343195266276E-2</v>
+        <f t="shared" si="1"/>
+        <v>-1.826722338204593E-3</v>
       </c>
       <c r="K5" s="9">
-        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-4.2730008970822833E-3</v>
+        <f t="shared" si="2"/>
+        <v>-1.8090598798621858E-4</v>
       </c>
       <c r="L5" s="12">
-        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
-        <v>47.016929999999995</v>
+        <f t="shared" si="3"/>
+        <v>47.386806</v>
       </c>
       <c r="M5" s="12">
-        <f>F5/(1+I5-H5)</f>
-        <v>33.137665967854652</v>
+        <f t="shared" si="4"/>
+        <v>34.265481609942917</v>
       </c>
       <c r="N5" s="12">
-        <f>L5-F5</f>
-        <v>-0.4030700000000067</v>
+        <f t="shared" si="5"/>
+        <v>-3.3194000000001722E-2</v>
       </c>
       <c r="O5" s="12">
-        <f>0.5*(M5-F5)</f>
-        <v>-7.141167016072675</v>
+        <f t="shared" si="6"/>
+        <v>-6.5772591950285424</v>
       </c>
       <c r="P5" s="14">
-        <f>N5+O5</f>
-        <v>-7.5442370160726817</v>
+        <f t="shared" si="7"/>
+        <v>-6.6104531950285441</v>
       </c>
       <c r="Q5" s="12">
-        <f>MAX($P$2:$P$280)-P5</f>
-        <v>360.05530867664424</v>
+        <f t="shared" si="8"/>
+        <v>259.77802937823424</v>
       </c>
       <c r="R5" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7773510788534784E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.8494402409374271E-3</v>
       </c>
       <c r="S5" s="9">
-        <f>Q5/MAX($Q$2:$Q$28)</f>
-        <v>0.7170376664824808</v>
+        <f t="shared" si="10"/>
+        <v>0.95573593489090902</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1098,54 +1098,54 @@
         <v>41.8</v>
       </c>
       <c r="G6" s="1">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>4.1799999999999994E-44</v>
       </c>
       <c r="H6" s="11">
-        <v>-0.18790000000000001</v>
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="I6" s="11">
-        <v>0.40749999999999997</v>
+        <v>0.4546</v>
       </c>
       <c r="J6" s="9">
-        <f>IFERROR(H6/I6,"")</f>
-        <v>-0.46110429447852769</v>
+        <f t="shared" si="1"/>
+        <v>0.16168059832820061</v>
       </c>
       <c r="K6" s="9">
-        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-9.7935453473069381E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.6011731923918807E-2</v>
       </c>
       <c r="L6" s="12">
-        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
-        <v>33.945779999999999</v>
+        <f t="shared" si="3"/>
+        <v>44.872299999999996</v>
       </c>
       <c r="M6" s="12">
-        <f>F6/(1+I6-H6)</f>
-        <v>26.200325937069074</v>
+        <f t="shared" si="4"/>
+        <v>30.26573021504597</v>
       </c>
       <c r="N6" s="12">
-        <f>L6-F6</f>
-        <v>-7.854219999999998</v>
+        <f t="shared" si="5"/>
+        <v>3.0722999999999985</v>
       </c>
       <c r="O6" s="12">
-        <f>0.5*(M6-F6)</f>
-        <v>-7.7998370314654615</v>
+        <f t="shared" si="6"/>
+        <v>-5.7671348924770136</v>
       </c>
       <c r="P6" s="14">
-        <f>N6+O6</f>
-        <v>-15.654057031465459</v>
+        <f t="shared" si="7"/>
+        <v>-2.6948348924770151</v>
       </c>
       <c r="Q6" s="12">
-        <f>MAX($P$2:$P$280)-P6</f>
-        <v>368.16512869203706</v>
+        <f t="shared" si="8"/>
+        <v>255.86241107568273</v>
       </c>
       <c r="R6" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7161725053990119E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.9083505693386332E-3</v>
       </c>
       <c r="S6" s="9">
-        <f>Q6/MAX($Q$2:$Q$28)</f>
-        <v>0.7331880919290682</v>
+        <f t="shared" si="10"/>
+        <v>0.94133018576723593</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -1168,54 +1168,54 @@
         <v>56</v>
       </c>
       <c r="G7" s="1">
-        <f>E7*F7</f>
+        <f t="shared" si="0"/>
         <v>5.5999999999999999E-34</v>
       </c>
       <c r="H7" s="11">
-        <v>-0.37809999999999999</v>
+        <v>-0.1119</v>
       </c>
       <c r="I7" s="11">
-        <v>0.42720000000000002</v>
+        <v>0.49480000000000002</v>
       </c>
       <c r="J7" s="9">
-        <f>IFERROR(H7/I7,"")</f>
-        <v>-0.88506554307116103</v>
+        <f t="shared" si="1"/>
+        <v>-0.2261519805982215</v>
       </c>
       <c r="K7" s="9">
-        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.18798197360553748</v>
+        <f t="shared" si="2"/>
+        <v>-2.2396533194734065E-2</v>
       </c>
       <c r="L7" s="12">
-        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
-        <v>34.8264</v>
+        <f t="shared" si="3"/>
+        <v>49.733599999999996</v>
       </c>
       <c r="M7" s="12">
-        <f>F7/(1+I7-H7)</f>
-        <v>31.01977510663048</v>
+        <f t="shared" si="4"/>
+        <v>34.854048671189396</v>
       </c>
       <c r="N7" s="12">
-        <f>L7-F7</f>
-        <v>-21.1736</v>
+        <f t="shared" si="5"/>
+        <v>-6.2664000000000044</v>
       </c>
       <c r="O7" s="12">
-        <f>0.5*(M7-F7)</f>
-        <v>-12.49011244668476</v>
+        <f t="shared" si="6"/>
+        <v>-10.572975664405302</v>
       </c>
       <c r="P7" s="14">
-        <f>N7+O7</f>
-        <v>-33.663712446684762</v>
+        <f t="shared" si="7"/>
+        <v>-16.839375664405306</v>
       </c>
       <c r="Q7" s="12">
-        <f>MAX($P$2:$P$280)-P7</f>
-        <v>386.17478410725636</v>
+        <f t="shared" si="8"/>
+        <v>270.00695184761099</v>
       </c>
       <c r="R7" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.5895010268776626E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.7036083447376912E-3</v>
       </c>
       <c r="S7" s="9">
-        <f>Q7/MAX($Q$2:$Q$28)</f>
-        <v>0.76905369641229437</v>
+        <f t="shared" si="10"/>
+        <v>0.99336863540293907</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -1238,54 +1238,54 @@
         <v>273.45999999999998</v>
       </c>
       <c r="G8" s="1">
-        <f>E8*F8</f>
+        <f t="shared" si="0"/>
         <v>39.952506</v>
       </c>
       <c r="H8" s="11">
-        <v>0.1293</v>
+        <v>0.109</v>
       </c>
       <c r="I8" s="11">
-        <v>0.22309999999999999</v>
+        <v>0.28029999999999999</v>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR(H8/I8,"")</f>
-        <v>0.57956073509636941</v>
+        <f t="shared" si="1"/>
+        <v>0.38886906885479844</v>
       </c>
       <c r="K8" s="9">
-        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.12309480541932255</v>
+        <f t="shared" si="2"/>
+        <v>3.8510911936184528E-2</v>
       </c>
       <c r="L8" s="12">
-        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
-        <v>308.818378</v>
+        <f t="shared" si="3"/>
+        <v>303.26713999999998</v>
       </c>
       <c r="M8" s="12">
-        <f>F8/(1+I8-H8)</f>
-        <v>250.00914243920275</v>
+        <f t="shared" si="4"/>
+        <v>233.46708785110559</v>
       </c>
       <c r="N8" s="12">
-        <f>L8-F8</f>
-        <v>35.358378000000016</v>
+        <f t="shared" si="5"/>
+        <v>29.807140000000004</v>
       </c>
       <c r="O8" s="12">
-        <f>0.5*(M8-F8)</f>
-        <v>-11.725428780398616</v>
+        <f t="shared" si="6"/>
+        <v>-19.996456074447195</v>
       </c>
       <c r="P8" s="14">
-        <f>N8+O8</f>
-        <v>23.6329492196014</v>
+        <f t="shared" si="7"/>
+        <v>9.8106839255528087</v>
       </c>
       <c r="Q8" s="12">
-        <f>MAX($P$2:$P$280)-P8</f>
-        <v>328.87812244097017</v>
+        <f t="shared" si="8"/>
+        <v>243.3568922576529</v>
       </c>
       <c r="R8" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.040640078391011E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.1091911994884248E-3</v>
       </c>
       <c r="S8" s="9">
-        <f>Q8/MAX($Q$2:$Q$28)</f>
-        <v>0.65494938080192144</v>
+        <f t="shared" si="10"/>
+        <v>0.89532177717528516</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1308,54 +1308,54 @@
         <v>15.3</v>
       </c>
       <c r="G9" s="1">
-        <f>E9*F9</f>
+        <f t="shared" si="0"/>
         <v>29.980350000000001</v>
       </c>
       <c r="H9" s="11">
-        <v>0.1077</v>
+        <v>9.98E-2</v>
       </c>
       <c r="I9" s="11">
-        <v>0.33939999999999998</v>
+        <v>0.41930000000000001</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(H9/I9,"")</f>
-        <v>0.31732469063052449</v>
+        <f t="shared" si="1"/>
+        <v>0.23801574051991414</v>
       </c>
       <c r="K9" s="9">
-        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.7397631831314572E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.3571438195334509E-2</v>
       </c>
       <c r="L9" s="12">
-        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
-        <v>16.94781</v>
+        <f t="shared" si="3"/>
+        <v>16.826940000000004</v>
       </c>
       <c r="M9" s="12">
-        <f>F9/(1+I9-H9)</f>
-        <v>12.421855971421612</v>
+        <f t="shared" si="4"/>
+        <v>11.595301250473664</v>
       </c>
       <c r="N9" s="12">
-        <f>L9-F9</f>
-        <v>1.6478099999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.5269400000000033</v>
       </c>
       <c r="O9" s="12">
-        <f>0.5*(M9-F9)</f>
-        <v>-1.4390720142891942</v>
+        <f t="shared" si="6"/>
+        <v>-1.8523493747631683</v>
       </c>
       <c r="P9" s="14">
-        <f>N9+O9</f>
-        <v>0.2087379857108056</v>
+        <f t="shared" si="7"/>
+        <v>-0.325409374763165</v>
       </c>
       <c r="Q9" s="12">
-        <f>MAX($P$2:$P$280)-P9</f>
-        <v>352.30233367486079</v>
+        <f t="shared" si="8"/>
+        <v>253.49298555796886</v>
       </c>
       <c r="R9" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.8384711210085204E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.9448823319464974E-3</v>
       </c>
       <c r="S9" s="9">
-        <f>Q9/MAX($Q$2:$Q$28)</f>
-        <v>0.70159788551102908</v>
+        <f t="shared" si="10"/>
+        <v>0.93261295468442762</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1378,54 +1378,54 @@
         <v>455.4</v>
       </c>
       <c r="G10" s="1">
-        <f>E10*F10</f>
+        <f t="shared" si="0"/>
         <v>14.982659999999999</v>
       </c>
       <c r="H10" s="11">
-        <v>0.1308</v>
+        <v>0.1205</v>
       </c>
       <c r="I10" s="11">
-        <v>0.2319</v>
+        <v>0.31109999999999999</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(H10/I10,"")</f>
-        <v>0.56403622250970242</v>
+        <f t="shared" si="1"/>
+        <v>0.38733526197364193</v>
       </c>
       <c r="K10" s="9">
-        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.11979750327243395</v>
+        <f t="shared" si="2"/>
+        <v>3.8359014275871031E-2</v>
       </c>
       <c r="L10" s="12">
-        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
-        <v>514.96632</v>
+        <f t="shared" si="3"/>
+        <v>510.27569999999997</v>
       </c>
       <c r="M10" s="12">
-        <f>F10/(1+I10-H10)</f>
-        <v>413.58641358641358</v>
+        <f t="shared" si="4"/>
+        <v>382.49622039307911</v>
       </c>
       <c r="N10" s="12">
-        <f>L10-F10</f>
-        <v>59.566320000000019</v>
+        <f t="shared" si="5"/>
+        <v>54.875699999999995</v>
       </c>
       <c r="O10" s="12">
-        <f>0.5*(M10-F10)</f>
-        <v>-20.906793206793196</v>
+        <f t="shared" si="6"/>
+        <v>-36.451889803460432</v>
       </c>
       <c r="P10" s="14">
-        <f>N10+O10</f>
-        <v>38.659526793206823</v>
+        <f t="shared" si="7"/>
+        <v>18.423810196539563</v>
       </c>
       <c r="Q10" s="12">
-        <f>MAX($P$2:$P$280)-P10</f>
-        <v>313.85154486736474</v>
+        <f t="shared" si="8"/>
+        <v>234.74376598666615</v>
       </c>
       <c r="R10" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.186219779235451E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.2599640326840531E-3</v>
       </c>
       <c r="S10" s="9">
-        <f>Q10/MAX($Q$2:$Q$28)</f>
-        <v>0.6250244724366002</v>
+        <f t="shared" si="10"/>
+        <v>0.86363366902912075</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1448,54 +1448,54 @@
         <v>77.53</v>
       </c>
       <c r="G11" s="1">
-        <f>E11*F11</f>
+        <f t="shared" si="0"/>
         <v>14.986549</v>
       </c>
       <c r="H11" s="11">
-        <v>-2.6599999999999999E-2</v>
+        <v>8.0100000000000005E-2</v>
       </c>
       <c r="I11" s="11">
-        <v>0.2873</v>
+        <v>0.30659999999999998</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR(H11/I11,"")</f>
-        <v>-9.2586146884789416E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.26125244618395305</v>
       </c>
       <c r="K11" s="9">
-        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-1.9664675408717771E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.5872641343607998E-2</v>
       </c>
       <c r="L11" s="12">
-        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
-        <v>75.467702000000003</v>
+        <f t="shared" si="3"/>
+        <v>83.740153000000007</v>
       </c>
       <c r="M11" s="12">
-        <f>F11/(1+I11-H11)</f>
-        <v>59.007534820001517</v>
+        <f t="shared" si="4"/>
+        <v>63.212392988177747</v>
       </c>
       <c r="N11" s="12">
-        <f>L11-F11</f>
-        <v>-2.0622979999999984</v>
+        <f t="shared" si="5"/>
+        <v>6.2101530000000054</v>
       </c>
       <c r="O11" s="12">
-        <f>0.5*(M11-F11)</f>
-        <v>-9.261232589999242</v>
+        <f t="shared" si="6"/>
+        <v>-7.158803505911127</v>
       </c>
       <c r="P11" s="14">
-        <f>N11+O11</f>
-        <v>-11.32353058999924</v>
+        <f t="shared" si="7"/>
+        <v>-0.94865050591112166</v>
       </c>
       <c r="Q11" s="12">
-        <f>MAX($P$2:$P$280)-P11</f>
-        <v>363.83460225057081</v>
+        <f t="shared" si="8"/>
+        <v>254.11622668911684</v>
       </c>
       <c r="R11" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7485016373217457E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.9352071807023546E-3</v>
       </c>
       <c r="S11" s="9">
-        <f>Q11/MAX($Q$2:$Q$28)</f>
-        <v>0.72456399863172904</v>
+        <f t="shared" si="10"/>
+        <v>0.9349058889505234</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1518,54 +1518,54 @@
         <v>10.4</v>
       </c>
       <c r="G12" s="1">
-        <f>E12*F12</f>
+        <f t="shared" si="0"/>
         <v>10.4</v>
       </c>
       <c r="H12" s="11">
-        <v>-1.7699</v>
+        <v>-1.4254</v>
       </c>
       <c r="I12" s="11">
-        <v>1.4341999999999999</v>
+        <v>1.3364</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR(H12/I12,"")</f>
-        <v>-1.2340677729744807</v>
+        <f t="shared" si="1"/>
+        <v>-1.0665968272972164</v>
       </c>
       <c r="K12" s="9">
-        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.26210770190166738</v>
+        <f t="shared" si="2"/>
+        <v>-0.10562839726086398</v>
       </c>
       <c r="L12" s="12">
-        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
-        <v>-8.0069600000000012</v>
+        <f t="shared" si="3"/>
+        <v>-4.4241600000000005</v>
       </c>
       <c r="M12" s="12">
-        <f>F12/(1+I12-H12)</f>
-        <v>2.4737756000095148</v>
+        <f t="shared" si="4"/>
+        <v>2.7646339518315699</v>
       </c>
       <c r="N12" s="12">
-        <f>L12-F12</f>
-        <v>-18.406960000000002</v>
+        <f t="shared" si="5"/>
+        <v>-14.824160000000001</v>
       </c>
       <c r="O12" s="12">
-        <f>0.5*(M12-F12)</f>
-        <v>-3.9631121999952428</v>
+        <f t="shared" si="6"/>
+        <v>-3.8176830240842152</v>
       </c>
       <c r="P12" s="14">
-        <f>N12+O12</f>
-        <v>-22.370072199995246</v>
+        <f t="shared" si="7"/>
+        <v>-18.641843024084217</v>
       </c>
       <c r="Q12" s="12">
-        <f>MAX($P$2:$P$280)-P12</f>
-        <v>374.88114386056685</v>
+        <f t="shared" si="8"/>
+        <v>271.80941920728992</v>
       </c>
       <c r="R12" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.6675121338509884E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.679048367479018E-3</v>
       </c>
       <c r="S12" s="9">
-        <f>Q12/MAX($Q$2:$Q$28)</f>
-        <v>0.74656280333716563</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1588,54 +1588,54 @@
         <v>187.36</v>
       </c>
       <c r="G13" s="1">
-        <f>E13*F13</f>
+        <f t="shared" si="0"/>
         <v>1.8736000000000003E-20</v>
       </c>
       <c r="H13" s="11">
-        <v>0.2681</v>
+        <v>0.24759999999999999</v>
       </c>
       <c r="I13" s="11">
-        <v>0.52139999999999997</v>
+        <v>0.52890000000000004</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR(H13/I13,"")</f>
-        <v>0.51419255849635603</v>
+        <f t="shared" si="1"/>
+        <v>0.46814142560030247</v>
       </c>
       <c r="K13" s="9">
-        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.10921104399118407</v>
+        <f t="shared" si="2"/>
+        <v>4.6361499689513468E-2</v>
       </c>
       <c r="L13" s="12">
-        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
-        <v>237.59121600000003</v>
+        <f t="shared" si="3"/>
+        <v>233.75033600000003</v>
       </c>
       <c r="M13" s="12">
-        <f>F13/(1+I13-H13)</f>
-        <v>149.49333758876568</v>
+        <f t="shared" si="4"/>
+        <v>146.22648872239131</v>
       </c>
       <c r="N13" s="12">
-        <f>L13-F13</f>
-        <v>50.231216000000018</v>
+        <f t="shared" si="5"/>
+        <v>46.390336000000019</v>
       </c>
       <c r="O13" s="12">
-        <f>0.5*(M13-F13)</f>
-        <v>-18.933331205617165</v>
+        <f t="shared" si="6"/>
+        <v>-20.566755638804352</v>
       </c>
       <c r="P13" s="14">
-        <f>N13+O13</f>
-        <v>31.297884794382853</v>
+        <f t="shared" si="7"/>
+        <v>25.823580361195667</v>
       </c>
       <c r="Q13" s="12">
-        <f>MAX($P$2:$P$280)-P13</f>
-        <v>321.21318686618872</v>
+        <f t="shared" si="8"/>
+        <v>227.34399582201004</v>
       </c>
       <c r="R13" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.1131972188196025E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.3986206734173451E-3</v>
       </c>
       <c r="S13" s="9">
-        <f>Q13/MAX($Q$2:$Q$28)</f>
-        <v>0.63968492729759696</v>
+        <f t="shared" si="10"/>
+        <v>0.83640955668512273</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -1658,54 +1658,54 @@
         <v>113.58</v>
       </c>
       <c r="G14" s="1">
-        <f>E14*F14</f>
+        <f t="shared" si="0"/>
         <v>1.1358E-20</v>
       </c>
       <c r="H14" s="11">
-        <v>8.5599999999999996E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="I14" s="11">
-        <v>0.1895</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR(H14/I14,"")</f>
-        <v>0.45171503957783637</v>
+        <f t="shared" si="1"/>
+        <v>0.38337368845843423</v>
       </c>
       <c r="K14" s="9">
-        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.5941238829041028E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.7966687343769748E-2</v>
       </c>
       <c r="L14" s="12">
-        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
-        <v>123.30244799999998</v>
+        <f t="shared" si="3"/>
+        <v>124.37009999999999</v>
       </c>
       <c r="M14" s="12">
-        <f>F14/(1+I14-H14)</f>
-        <v>102.88975450674879</v>
+        <f t="shared" si="4"/>
+        <v>98.525329632199856</v>
       </c>
       <c r="N14" s="12">
-        <f>L14-F14</f>
-        <v>9.7224479999999858</v>
+        <f t="shared" si="5"/>
+        <v>10.790099999999995</v>
       </c>
       <c r="O14" s="12">
-        <f>0.5*(M14-F14)</f>
-        <v>-5.3451227466256057</v>
+        <f t="shared" si="6"/>
+        <v>-7.5273351839000711</v>
       </c>
       <c r="P14" s="14">
-        <f>N14+O14</f>
-        <v>4.3773252533743801</v>
+        <f t="shared" si="7"/>
+        <v>3.2627648160999243</v>
       </c>
       <c r="Q14" s="12">
-        <f>MAX($P$2:$P$280)-P14</f>
-        <v>348.13374640719724</v>
+        <f t="shared" si="8"/>
+        <v>249.90481136710579</v>
       </c>
       <c r="R14" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.8724592496998051E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.0015235982432422E-3</v>
       </c>
       <c r="S14" s="9">
-        <f>Q14/MAX($Q$2:$Q$28)</f>
-        <v>0.69329628846495295</v>
+        <f t="shared" si="10"/>
+        <v>0.91941188828530251</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -1728,54 +1728,54 @@
         <v>20.82</v>
       </c>
       <c r="G15" s="1">
-        <f>E15*F15</f>
+        <f t="shared" si="0"/>
         <v>2.0820000000000001E-21</v>
       </c>
       <c r="H15" s="11">
-        <v>-0.20630000000000001</v>
+        <v>1.38E-2</v>
       </c>
       <c r="I15" s="11">
-        <v>0.70250000000000001</v>
+        <v>0.81420000000000003</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR(H15/I15,"")</f>
-        <v>-0.29366548042704627</v>
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
       </c>
       <c r="K15" s="9">
-        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-6.2372574576723745E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.6785272299350835E-3</v>
       </c>
       <c r="L15" s="12">
-        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
-        <v>16.524833999999998</v>
+        <f t="shared" si="3"/>
+        <v>21.107316000000001</v>
       </c>
       <c r="M15" s="12">
-        <f>F15/(1+I15-H15)</f>
-        <v>10.907376362112322</v>
+        <f t="shared" si="4"/>
+        <v>11.564096867362808</v>
       </c>
       <c r="N15" s="12">
-        <f>L15-F15</f>
-        <v>-4.2951660000000018</v>
+        <f t="shared" si="5"/>
+        <v>0.28731600000000057</v>
       </c>
       <c r="O15" s="12">
-        <f>0.5*(M15-F15)</f>
-        <v>-4.9563118189438393</v>
+        <f t="shared" si="6"/>
+        <v>-4.6279515663185959</v>
       </c>
       <c r="P15" s="14">
-        <f>N15+O15</f>
-        <v>-9.2514778189438402</v>
+        <f t="shared" si="7"/>
+        <v>-4.3406355663185954</v>
       </c>
       <c r="Q15" s="12">
-        <f>MAX($P$2:$P$280)-P15</f>
-        <v>361.76254947951543</v>
+        <f t="shared" si="8"/>
+        <v>257.50821174952432</v>
       </c>
       <c r="R15" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7642441193505142E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.8833713037962846E-3</v>
       </c>
       <c r="S15" s="9">
-        <f>Q15/MAX($Q$2:$Q$28)</f>
-        <v>0.72043757736260006</v>
+        <f t="shared" si="10"/>
+        <v>0.94738516604952872</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -1798,54 +1798,54 @@
         <v>13.04</v>
       </c>
       <c r="G16" s="1">
-        <f>E16*F16</f>
+        <f t="shared" si="0"/>
         <v>1.304E-21</v>
       </c>
       <c r="H16" s="11">
-        <v>-3.5999999999999999E-3</v>
+        <v>-5.2200000000000003E-2</v>
       </c>
       <c r="I16" s="11">
-        <v>0.39429999999999998</v>
+        <v>0.43780000000000002</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR(H16/I16,"")</f>
-        <v>-9.1301039817397924E-3</v>
+        <f t="shared" si="1"/>
+        <v>-0.11923252626770214</v>
       </c>
       <c r="K16" s="9">
-        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-1.9391727303671891E-3</v>
+        <f t="shared" si="2"/>
+        <v>-1.1807967480023001E-2</v>
       </c>
       <c r="L16" s="12">
-        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
-        <v>12.993056000000001</v>
+        <f t="shared" si="3"/>
+        <v>12.359312000000001</v>
       </c>
       <c r="M16" s="12">
-        <f>F16/(1+I16-H16)</f>
-        <v>9.3282781314829393</v>
+        <f t="shared" si="4"/>
+        <v>8.7516778523489922</v>
       </c>
       <c r="N16" s="12">
-        <f>L16-F16</f>
-        <v>-4.6943999999998098E-2</v>
+        <f t="shared" si="5"/>
+        <v>-0.68068799999999818</v>
       </c>
       <c r="O16" s="12">
-        <f>0.5*(M16-F16)</f>
-        <v>-1.8558609342585299</v>
+        <f t="shared" si="6"/>
+        <v>-2.1441610738255035</v>
       </c>
       <c r="P16" s="14">
-        <f>N16+O16</f>
-        <v>-1.902804934258528</v>
+        <f t="shared" si="7"/>
+        <v>-2.8248490738255017</v>
       </c>
       <c r="Q16" s="12">
-        <f>MAX($P$2:$P$280)-P16</f>
-        <v>354.41387659483013</v>
+        <f t="shared" si="8"/>
+        <v>255.99242525703121</v>
       </c>
       <c r="R16" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.8215599502138321E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.9063655848251841E-3</v>
       </c>
       <c r="S16" s="9">
-        <f>Q16/MAX($Q$2:$Q$28)</f>
-        <v>0.70580295004285676</v>
+        <f t="shared" si="10"/>
+        <v>0.94180851422887524</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1868,54 +1868,54 @@
         <v>11.05</v>
       </c>
       <c r="G17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="0"/>
         <v>1.1050000000000002E-21</v>
       </c>
       <c r="H17" s="11">
-        <v>-0.31009999999999999</v>
+        <v>-0.1159</v>
       </c>
       <c r="I17" s="11">
-        <v>0.63170000000000004</v>
+        <v>0.64090000000000003</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR(H17/I17,"")</f>
-        <v>-0.49089757796422345</v>
+        <f t="shared" si="1"/>
+        <v>-0.1808394445311281</v>
       </c>
       <c r="K17" s="9">
-        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.10426334667112155</v>
+        <f t="shared" si="2"/>
+        <v>-1.7909091981618185E-2</v>
       </c>
       <c r="L17" s="12">
-        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
-        <v>7.6233950000000004</v>
+        <f t="shared" si="3"/>
+        <v>9.769305000000001</v>
       </c>
       <c r="M17" s="12">
-        <f>F17/(1+I17-H17)</f>
-        <v>5.690596353898445</v>
+        <f t="shared" si="4"/>
+        <v>6.2898451730418943</v>
       </c>
       <c r="N17" s="12">
-        <f>L17-F17</f>
-        <v>-3.4266050000000003</v>
+        <f t="shared" si="5"/>
+        <v>-1.2806949999999997</v>
       </c>
       <c r="O17" s="12">
-        <f>0.5*(M17-F17)</f>
-        <v>-2.6797018230507779</v>
+        <f t="shared" si="6"/>
+        <v>-2.3800774134790532</v>
       </c>
       <c r="P17" s="14">
-        <f>N17+O17</f>
-        <v>-6.1063068230507778</v>
+        <f t="shared" si="7"/>
+        <v>-3.6607724134790529</v>
       </c>
       <c r="Q17" s="12">
-        <f>MAX($P$2:$P$280)-P17</f>
-        <v>358.61737848362236</v>
+        <f t="shared" si="8"/>
+        <v>256.82834859668475</v>
       </c>
       <c r="R17" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7884872847724219E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.8936511699896839E-3</v>
       </c>
       <c r="S17" s="9">
-        <f>Q17/MAX($Q$2:$Q$28)</f>
-        <v>0.71417407834665059</v>
+        <f t="shared" si="10"/>
+        <v>0.94488391662696514</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -1938,54 +1938,54 @@
         <v>10.47</v>
       </c>
       <c r="G18" s="1">
-        <f>E18*F18</f>
+        <f t="shared" si="0"/>
         <v>1.0470000000000001E-21</v>
       </c>
       <c r="H18" s="11">
-        <v>-1.0165999999999999</v>
+        <v>-0.39269999999999999</v>
       </c>
       <c r="I18" s="11">
-        <v>0.75790000000000002</v>
+        <v>0.75180000000000002</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR(H18/I18,"")</f>
-        <v>-1.3413379073756431</v>
+        <f t="shared" si="1"/>
+        <v>-0.52234636871508378</v>
       </c>
       <c r="K18" s="9">
-        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.28489115758076899</v>
+        <f t="shared" si="2"/>
+        <v>-5.1729583597412782E-2</v>
       </c>
       <c r="L18" s="12">
-        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
-        <v>-0.17380199999999946</v>
+        <f t="shared" si="3"/>
+        <v>6.3584309999999995</v>
       </c>
       <c r="M18" s="12">
-        <f>F18/(1+I18-H18)</f>
-        <v>3.7736529104343131</v>
+        <f t="shared" si="4"/>
+        <v>4.8822569363488002</v>
       </c>
       <c r="N18" s="12">
-        <f>L18-F18</f>
-        <v>-10.643802000000001</v>
+        <f t="shared" si="5"/>
+        <v>-4.1115690000000011</v>
       </c>
       <c r="O18" s="12">
-        <f>0.5*(M18-F18)</f>
-        <v>-3.3481735447828438</v>
+        <f t="shared" si="6"/>
+        <v>-2.7938715318256002</v>
       </c>
       <c r="P18" s="14">
-        <f>N18+O18</f>
-        <v>-13.991975544782845</v>
+        <f t="shared" si="7"/>
+        <v>-6.9054405318256009</v>
       </c>
       <c r="Q18" s="12">
-        <f>MAX($P$2:$P$280)-P18</f>
-        <v>366.50304720535445</v>
+        <f t="shared" si="8"/>
+        <v>260.07301671503132</v>
       </c>
       <c r="R18" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7284902748426331E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.8450740204845073E-3</v>
       </c>
       <c r="S18" s="9">
-        <f>Q18/MAX($Q$2:$Q$28)</f>
-        <v>0.7298781142617623</v>
+        <f t="shared" si="10"/>
+        <v>0.95682120757077926</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D19" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45603</v>
+        <v>45604</v>
       </c>
       <c r="E19" s="2">
         <v>1E-35</v>
@@ -2009,53 +2009,53 @@
         <v>2742.9</v>
       </c>
       <c r="G19" s="1">
-        <f>E19*F19</f>
+        <f t="shared" si="0"/>
         <v>2.7429E-32</v>
       </c>
       <c r="H19" s="11">
-        <v>0.1343</v>
+        <v>0.1152</v>
       </c>
       <c r="I19" s="11">
-        <v>0.14599999999999999</v>
+        <v>0.16320000000000001</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR(H19/I19,"")</f>
-        <v>0.91986301369863022</v>
+        <f t="shared" si="1"/>
+        <v>0.70588235294117641</v>
       </c>
       <c r="K19" s="9">
-        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.19537272252378618</v>
+        <f t="shared" si="2"/>
+        <v>6.99057222820023E-2</v>
       </c>
       <c r="L19" s="12">
-        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
-        <v>3111.2714700000001</v>
+        <f t="shared" si="3"/>
+        <v>3058.8820799999999</v>
       </c>
       <c r="M19" s="12">
-        <f>F19/(1+I19-H19)</f>
-        <v>2711.1792033211432</v>
+        <f t="shared" si="4"/>
+        <v>2617.270992366412</v>
       </c>
       <c r="N19" s="12">
-        <f>L19-F19</f>
-        <v>368.37147000000004</v>
+        <f t="shared" si="5"/>
+        <v>315.98207999999977</v>
       </c>
       <c r="O19" s="12">
-        <f>0.5*(M19-F19)</f>
-        <v>-15.860398339428457</v>
+        <f t="shared" si="6"/>
+        <v>-62.814503816794058</v>
       </c>
       <c r="P19" s="14">
-        <f>N19+O19</f>
-        <v>352.51107166057159</v>
+        <f t="shared" si="7"/>
+        <v>253.16757618320571</v>
       </c>
       <c r="Q19" s="12">
-        <f>MAX($P$2:$P$280)-P19</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R19" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S19" s="9">
-        <f>Q19/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2079,53 +2079,53 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G20" s="1">
-        <f>E20*F20</f>
+        <f t="shared" si="0"/>
         <v>2.0399999999999999E-34</v>
       </c>
       <c r="H20" s="11">
-        <v>-1.1999999999999999E-3</v>
+        <v>1.5100000000000001E-2</v>
       </c>
       <c r="I20" s="11">
-        <v>0.115</v>
+        <v>0.1336</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR(H20/I20,"")</f>
-        <v>-1.0434782608695651E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.11302395209580839</v>
       </c>
       <c r="K20" s="9">
-        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.2162777031413988E-3</v>
+        <f t="shared" si="2"/>
+        <v>1.1193113092433878E-2</v>
       </c>
       <c r="L20" s="12">
         <v>21.2</v>
       </c>
       <c r="M20" s="12">
-        <f>F20/(1+I20-H20)</f>
-        <v>18.276294570865435</v>
+        <f t="shared" si="4"/>
+        <v>18.238712561466247</v>
       </c>
       <c r="N20" s="12">
-        <f>L20-F20</f>
+        <f t="shared" si="5"/>
         <v>0.80000000000000071</v>
       </c>
       <c r="O20" s="12">
-        <f>0.5*(M20-F20)</f>
-        <v>-1.0618527145672818</v>
+        <f t="shared" si="6"/>
+        <v>-1.0806437192668756</v>
       </c>
       <c r="P20" s="14">
-        <f>N20+O20</f>
-        <v>-0.2618527145672811</v>
+        <f t="shared" si="7"/>
+        <v>-0.28064371926687492</v>
       </c>
       <c r="Q20" s="12">
-        <f>MAX($P$2:$P$280)-P20</f>
-        <v>352.77292437513887</v>
+        <f t="shared" si="8"/>
+        <v>253.44821990247257</v>
       </c>
       <c r="R20" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.8346846679667501E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.9455791024486271E-3</v>
       </c>
       <c r="S20" s="9">
-        <f>Q20/MAX($Q$2:$Q$28)</f>
-        <v>0.70253505057835153</v>
+        <f t="shared" si="10"/>
+        <v>0.93244825967265488</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -2148,54 +2148,54 @@
         <v>153.7552</v>
       </c>
       <c r="G21" s="1">
-        <f>E21*F21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H21" s="11">
-        <v>9.1600000000000001E-2</v>
+        <v>6.3700000000000007E-2</v>
       </c>
       <c r="I21" s="11">
-        <v>0.10589999999999999</v>
+        <v>9.2799999999999994E-2</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR(H21/I21,"")</f>
-        <v>0.86496694995278567</v>
+        <f t="shared" si="1"/>
+        <v>0.68642241379310354</v>
       </c>
       <c r="K21" s="9">
-        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.18371316749206404</v>
+        <f t="shared" si="2"/>
+        <v>6.7978544054580009E-2</v>
       </c>
       <c r="L21" s="12">
-        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
-        <v>167.83917631999998</v>
+        <f t="shared" ref="L21:L34" si="11">F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <v>163.54940624000002</v>
       </c>
       <c r="M21" s="12">
-        <f>F21/(1+I21-H21)</f>
-        <v>151.58749876762298</v>
+        <f t="shared" si="4"/>
+        <v>149.40744339714314</v>
       </c>
       <c r="N21" s="12">
-        <f>L21-F21</f>
-        <v>14.083976319999977</v>
+        <f t="shared" si="5"/>
+        <v>9.7942062400000225</v>
       </c>
       <c r="O21" s="12">
-        <f>0.5*(M21-F21)</f>
-        <v>-1.0838506161885135</v>
+        <f t="shared" si="6"/>
+        <v>-2.1738783014284309</v>
       </c>
       <c r="P21" s="14">
-        <f>N21+O21</f>
-        <v>13.000125703811463</v>
+        <f t="shared" si="7"/>
+        <v>7.6203279385715916</v>
       </c>
       <c r="Q21" s="12">
-        <f>MAX($P$2:$P$280)-P21</f>
-        <v>339.51094595676011</v>
+        <f t="shared" si="8"/>
+        <v>245.54724824463412</v>
       </c>
       <c r="R21" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.9454131358915285E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.0725359666980215E-3</v>
       </c>
       <c r="S21" s="9">
-        <f>Q21/MAX($Q$2:$Q$28)</f>
-        <v>0.67612428026362914</v>
+        <f t="shared" si="10"/>
+        <v>0.90338020279338627</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -2218,54 +2218,54 @@
         <v>188.53</v>
       </c>
       <c r="G22" s="1">
-        <f>E22*F22</f>
+        <f t="shared" si="0"/>
         <v>62.950166999999993</v>
       </c>
       <c r="H22" s="11">
-        <v>0.1356</v>
+        <v>0.2445</v>
       </c>
       <c r="I22" s="11">
-        <v>0.37040000000000001</v>
+        <v>0.3826</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR(H22/I22,"")</f>
-        <v>0.36609071274298055</v>
+        <f t="shared" si="1"/>
+        <v>0.63904861474124408</v>
       </c>
       <c r="K22" s="9">
-        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.775520721469352E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.3286969564632894E-2</v>
       </c>
       <c r="L22" s="12">
-        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
-        <v>214.09466799999998</v>
+        <f t="shared" si="11"/>
+        <v>234.625585</v>
       </c>
       <c r="M22" s="12">
-        <f>F22/(1+I22-H22)</f>
-        <v>152.68059604794297</v>
+        <f t="shared" si="4"/>
+        <v>165.65328178543186</v>
       </c>
       <c r="N22" s="12">
-        <f>L22-F22</f>
-        <v>25.564667999999983</v>
+        <f t="shared" si="5"/>
+        <v>46.095585</v>
       </c>
       <c r="O22" s="12">
-        <f>0.5*(M22-F22)</f>
-        <v>-17.924701976028516</v>
+        <f t="shared" si="6"/>
+        <v>-11.438359107284072</v>
       </c>
       <c r="P22" s="14">
-        <f>N22+O22</f>
-        <v>7.6399660239714677</v>
+        <f t="shared" si="7"/>
+        <v>34.657225892715928</v>
       </c>
       <c r="Q22" s="12">
-        <f>MAX($P$2:$P$280)-P22</f>
-        <v>344.87110563660013</v>
+        <f t="shared" si="8"/>
+        <v>218.51035029048978</v>
       </c>
       <c r="R22" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.8996340477816852E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.576442253973737E-3</v>
       </c>
       <c r="S22" s="9">
-        <f>Q22/MAX($Q$2:$Q$28)</f>
-        <v>0.68679885246458405</v>
+        <f t="shared" si="10"/>
+        <v>0.80391014751349477</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -2288,54 +2288,54 @@
         <v>423.77</v>
       </c>
       <c r="G23" s="1">
-        <f>E23*F23</f>
+        <f t="shared" si="0"/>
         <v>56.658049000000005</v>
       </c>
       <c r="H23" s="11">
-        <v>8.9599999999999999E-2</v>
+        <v>0.20669999999999999</v>
       </c>
       <c r="I23" s="11">
-        <v>0.27800000000000002</v>
+        <v>0.30690000000000001</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR(H23/I23,"")</f>
-        <v>0.32230215827338127</v>
+        <f t="shared" si="1"/>
+        <v>0.67350928641251218</v>
       </c>
       <c r="K23" s="9">
-        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.8454812509499322E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.6699716934595379E-2</v>
       </c>
       <c r="L23" s="12">
-        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
-        <v>461.73979199999997</v>
+        <f t="shared" si="11"/>
+        <v>511.36325900000003</v>
       </c>
       <c r="M23" s="12">
-        <f>F23/(1+I23-H23)</f>
-        <v>356.58869067653984</v>
+        <f t="shared" si="4"/>
+        <v>385.17542265042715</v>
       </c>
       <c r="N23" s="12">
-        <f>L23-F23</f>
-        <v>37.969791999999984</v>
+        <f t="shared" si="5"/>
+        <v>87.593259000000046</v>
       </c>
       <c r="O23" s="12">
-        <f>0.5*(M23-F23)</f>
-        <v>-33.590654661730071</v>
+        <f t="shared" si="6"/>
+        <v>-19.297288674786415</v>
       </c>
       <c r="P23" s="14">
-        <f>N23+O23</f>
-        <v>4.3791373382699135</v>
+        <f t="shared" si="7"/>
+        <v>68.295970325213631</v>
       </c>
       <c r="Q23" s="12">
-        <f>MAX($P$2:$P$280)-P23</f>
-        <v>348.13193432230167</v>
+        <f t="shared" si="8"/>
+        <v>184.87160585799208</v>
       </c>
       <c r="R23" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.8724742013302254E-3</v>
+        <f t="shared" si="9"/>
+        <v>5.4091594831936684E-3</v>
       </c>
       <c r="S23" s="9">
-        <f>Q23/MAX($Q$2:$Q$28)</f>
-        <v>0.69329267976069653</v>
+        <f t="shared" si="10"/>
+        <v>0.68015157972507023</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -2358,54 +2358,54 @@
         <v>227.38</v>
       </c>
       <c r="G24" s="1">
-        <f>E24*F24</f>
+        <f t="shared" si="0"/>
         <v>42.792915999999998</v>
       </c>
       <c r="H24" s="11">
-        <v>9.3700000000000006E-2</v>
+        <v>0.23910000000000001</v>
       </c>
       <c r="I24" s="11">
-        <v>0.27310000000000001</v>
+        <v>0.31859999999999999</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR(H24/I24,"")</f>
-        <v>0.34309776638593925</v>
+        <f t="shared" si="1"/>
+        <v>0.75047080979284375</v>
       </c>
       <c r="K24" s="9">
-        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.2871659923715817E-2</v>
+        <f t="shared" si="2"/>
+        <v>7.4321455681014545E-2</v>
       </c>
       <c r="L24" s="12">
-        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
-        <v>248.68550600000003</v>
+        <f t="shared" si="11"/>
+        <v>281.74655799999999</v>
       </c>
       <c r="M24" s="12">
-        <f>F24/(1+I24-H24)</f>
-        <v>192.79294556554183</v>
+        <f t="shared" si="4"/>
+        <v>210.63455303381195</v>
       </c>
       <c r="N24" s="12">
-        <f>L24-F24</f>
-        <v>21.305506000000037</v>
+        <f t="shared" si="5"/>
+        <v>54.366557999999998</v>
       </c>
       <c r="O24" s="12">
-        <f>0.5*(M24-F24)</f>
-        <v>-17.293527217229084</v>
+        <f t="shared" si="6"/>
+        <v>-8.3727234830940205</v>
       </c>
       <c r="P24" s="14">
-        <f>N24+O24</f>
-        <v>4.011978782770953</v>
+        <f t="shared" si="7"/>
+        <v>45.993834516905977</v>
       </c>
       <c r="Q24" s="12">
-        <f>MAX($P$2:$P$280)-P24</f>
-        <v>348.49909287780065</v>
+        <f t="shared" si="8"/>
+        <v>207.17374166629975</v>
       </c>
       <c r="R24" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.8694479280915795E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.8268665322013958E-3</v>
       </c>
       <c r="S24" s="9">
-        <f>Q24/MAX($Q$2:$Q$28)</f>
-        <v>0.69402386329700283</v>
+        <f t="shared" si="10"/>
+        <v>0.76220221606191985</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -2428,54 +2428,54 @@
         <v>188.12</v>
       </c>
       <c r="G25" s="1">
-        <f>E25*F25</f>
+        <f t="shared" si="0"/>
         <v>36.269536000000002</v>
       </c>
       <c r="H25" s="11">
-        <v>-3.8800000000000001E-2</v>
+        <v>0.13730000000000001</v>
       </c>
       <c r="I25" s="11">
-        <v>0.39800000000000002</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR(H25/I25,"")</f>
-        <v>-9.7487437185929643E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.32925659472422064</v>
       </c>
       <c r="K25" s="9">
-        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.0705676531442466E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.2607303432937967E-2</v>
       </c>
       <c r="L25" s="12">
-        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
-        <v>180.82094400000003</v>
+        <f t="shared" si="11"/>
+        <v>213.94887600000001</v>
       </c>
       <c r="M25" s="12">
-        <f>F25/(1+I25-H25)</f>
-        <v>130.92984409799556</v>
+        <f t="shared" si="4"/>
+        <v>147.00320387590841</v>
       </c>
       <c r="N25" s="12">
-        <f>L25-F25</f>
-        <v>-7.2990559999999789</v>
+        <f t="shared" si="5"/>
+        <v>25.828876000000008</v>
       </c>
       <c r="O25" s="12">
-        <f>0.5*(M25-F25)</f>
-        <v>-28.595077951002224</v>
+        <f t="shared" si="6"/>
+        <v>-20.558398062045796</v>
       </c>
       <c r="P25" s="14">
-        <f>N25+O25</f>
-        <v>-35.894133951002203</v>
+        <f t="shared" si="7"/>
+        <v>5.2704779379542117</v>
       </c>
       <c r="Q25" s="12">
-        <f>MAX($P$2:$P$280)-P25</f>
-        <v>388.40520561157382</v>
+        <f t="shared" si="8"/>
+        <v>247.8970982452515</v>
       </c>
       <c r="R25" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.5746307864886187E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.0339318494590536E-3</v>
       </c>
       <c r="S25" s="9">
-        <f>Q25/MAX($Q$2:$Q$28)</f>
-        <v>0.77349550352411345</v>
+        <f t="shared" si="10"/>
+        <v>0.91202541460197828</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -2498,54 +2498,54 @@
         <v>167.24</v>
       </c>
       <c r="G26" s="1">
-        <f>E26*F26</f>
+        <f t="shared" si="0"/>
         <v>19.98518</v>
       </c>
       <c r="H26" s="11">
-        <v>5.4199999999999998E-2</v>
+        <v>0.1852</v>
       </c>
       <c r="I26" s="11">
-        <v>0.32690000000000002</v>
+        <v>0.32479999999999998</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR(H26/I26,"")</f>
-        <v>0.16579993881921076</v>
+        <f t="shared" si="1"/>
+        <v>0.57019704433497542</v>
       </c>
       <c r="K26" s="9">
-        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.5214792810442389E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.6468384655340743E-2</v>
       </c>
       <c r="L26" s="12">
-        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
-        <v>176.30440800000002</v>
+        <f t="shared" si="11"/>
+        <v>198.21284800000001</v>
       </c>
       <c r="M26" s="12">
-        <f>F26/(1+I26-H26)</f>
-        <v>131.40567297870669</v>
+        <f t="shared" si="4"/>
+        <v>146.75324675324677</v>
       </c>
       <c r="N26" s="12">
-        <f>L26-F26</f>
-        <v>9.0644080000000145</v>
+        <f t="shared" si="5"/>
+        <v>30.972847999999999</v>
       </c>
       <c r="O26" s="12">
-        <f>0.5*(M26-F26)</f>
-        <v>-17.91716351064666</v>
+        <f t="shared" si="6"/>
+        <v>-10.243376623376619</v>
       </c>
       <c r="P26" s="14">
-        <f>N26+O26</f>
-        <v>-8.8527555106466451</v>
+        <f t="shared" si="7"/>
+        <v>20.72947137662338</v>
       </c>
       <c r="Q26" s="12">
-        <f>MAX($P$2:$P$280)-P26</f>
-        <v>361.36382717121825</v>
+        <f t="shared" si="8"/>
+        <v>232.43810480658232</v>
       </c>
       <c r="R26" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7672941362949116E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.3022205882814503E-3</v>
       </c>
       <c r="S26" s="9">
-        <f>Q26/MAX($Q$2:$Q$28)</f>
-        <v>0.71964353570670359</v>
+        <f t="shared" si="10"/>
+        <v>0.85515103002857351</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -2568,54 +2568,54 @@
         <v>700.32</v>
       </c>
       <c r="G27" s="1">
-        <f>E27*F27</f>
+        <f t="shared" si="0"/>
         <v>19.959120000000002</v>
       </c>
       <c r="H27" s="11">
-        <v>-4.9299999999999997E-2</v>
+        <v>0.1714</v>
       </c>
       <c r="I27" s="11">
-        <v>0.44040000000000001</v>
+        <v>0.4395</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR(H27/I27,"")</f>
-        <v>-0.11194368755676656</v>
+        <f t="shared" si="1"/>
+        <v>0.38998862343572238</v>
       </c>
       <c r="K27" s="9">
-        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.3776086962534363E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.8621784904303812E-2</v>
       </c>
       <c r="L27" s="12">
-        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
-        <v>665.7942240000001</v>
+        <f t="shared" si="11"/>
+        <v>820.35484800000006</v>
       </c>
       <c r="M27" s="12">
-        <f>F27/(1+I27-H27)</f>
-        <v>470.10807545143325</v>
+        <f t="shared" si="4"/>
+        <v>552.25928554530401</v>
       </c>
       <c r="N27" s="12">
-        <f>L27-F27</f>
-        <v>-34.525775999999951</v>
+        <f t="shared" si="5"/>
+        <v>120.03484800000001</v>
       </c>
       <c r="O27" s="12">
-        <f>0.5*(M27-F27)</f>
-        <v>-115.1059622742834</v>
+        <f t="shared" si="6"/>
+        <v>-74.03035722734802</v>
       </c>
       <c r="P27" s="14">
-        <f>N27+O27</f>
-        <v>-149.63173827428335</v>
+        <f t="shared" si="7"/>
+        <v>46.004490772651991</v>
       </c>
       <c r="Q27" s="12">
-        <f>MAX($P$2:$P$280)-P27</f>
-        <v>502.14280993485494</v>
+        <f t="shared" si="8"/>
+        <v>207.16308541055372</v>
       </c>
       <c r="R27" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.9914653365836984E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.8271148212443828E-3</v>
       </c>
       <c r="S27" s="9">
-        <f>Q27/MAX($Q$2:$Q$28)</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>0.762163011181614</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -2638,54 +2638,54 @@
         <v>147.01</v>
       </c>
       <c r="G28" s="1">
-        <f>E28*F28</f>
+        <f t="shared" si="0"/>
         <v>1.4700999999999999E-17</v>
       </c>
       <c r="H28" s="11">
-        <v>0.51919999999999999</v>
+        <v>0.63670000000000004</v>
       </c>
       <c r="I28" s="11">
-        <v>0.55179999999999996</v>
+        <v>0.53810000000000002</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR(H28/I28,"")</f>
-        <v>0.94092062341428062</v>
+        <f t="shared" si="1"/>
+        <v>1.1832373164839249</v>
       </c>
       <c r="K28" s="9">
-        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.19984521731781843</v>
+        <f t="shared" si="2"/>
+        <v>0.11717966725642148</v>
       </c>
       <c r="L28" s="12">
-        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
-        <v>223.337592</v>
+        <f t="shared" si="11"/>
+        <v>240.61126700000003</v>
       </c>
       <c r="M28" s="12">
-        <f>F28/(1+I28-H28)</f>
-        <v>142.36877784233971</v>
+        <f t="shared" si="4"/>
+        <v>163.09074772575991</v>
       </c>
       <c r="N28" s="12">
-        <f>L28-F28</f>
-        <v>76.32759200000001</v>
+        <f t="shared" si="5"/>
+        <v>93.601267000000036</v>
       </c>
       <c r="O28" s="12">
-        <f>0.5*(M28-F28)</f>
-        <v>-2.3206110788301402</v>
+        <f t="shared" si="6"/>
+        <v>8.0403738628799601</v>
       </c>
       <c r="P28" s="14">
-        <f>N28+O28</f>
-        <v>74.00698092116987</v>
+        <f t="shared" si="7"/>
+        <v>101.64164086288</v>
       </c>
       <c r="Q28" s="12">
-        <f>MAX($P$2:$P$280)-P28</f>
-        <v>278.5040907394017</v>
+        <f t="shared" si="8"/>
+        <v>151.52593532032571</v>
       </c>
       <c r="R28" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.5906115322941784E-3</v>
+        <f t="shared" si="9"/>
+        <v>6.5995302908772729E-3</v>
       </c>
       <c r="S28" s="9">
-        <f>Q28/MAX($Q$2:$Q$28)</f>
-        <v>0.55463124280427956</v>
+        <f t="shared" si="10"/>
+        <v>0.55747124497097555</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -2708,54 +2708,54 @@
         <v>169.34</v>
       </c>
       <c r="G29" s="1">
-        <f>E29*F29</f>
+        <f t="shared" si="0"/>
         <v>1.6934000000000002E-20</v>
       </c>
       <c r="H29" s="11">
-        <v>3.2800000000000003E-2</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="I29" s="11">
-        <v>0.43290000000000001</v>
+        <v>0.47220000000000001</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR(H29/I29,"")</f>
-        <v>7.5768075768075774E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.45806861499364676</v>
       </c>
       <c r="K29" s="9">
-        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.6092630122910137E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.5363957963283685E-2</v>
       </c>
       <c r="L29" s="12">
-        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
-        <v>174.894352</v>
+        <f t="shared" si="11"/>
+        <v>205.968242</v>
       </c>
       <c r="M29" s="12">
-        <f>F29/(1+I29-H29)</f>
-        <v>120.94850367830868</v>
+        <f t="shared" si="4"/>
+        <v>134.83557608089816</v>
       </c>
       <c r="N29" s="12">
-        <f>L29-F29</f>
-        <v>5.5543519999999944</v>
+        <f t="shared" si="5"/>
+        <v>36.628242</v>
       </c>
       <c r="O29" s="12">
-        <f>0.5*(M29-F29)</f>
-        <v>-24.19574816084566</v>
+        <f t="shared" si="6"/>
+        <v>-17.25221195955092</v>
       </c>
       <c r="P29" s="14">
-        <f>N29+O29</f>
-        <v>-18.641396160845666</v>
+        <f t="shared" si="7"/>
+        <v>19.376030040449081</v>
       </c>
       <c r="Q29" s="12">
-        <f>MAX($P$2:$P$280)-P29</f>
-        <v>371.15246782141725</v>
+        <f t="shared" si="8"/>
+        <v>233.79154614275663</v>
       </c>
       <c r="R29" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.6943105238388374E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.2773146270626275E-3</v>
       </c>
       <c r="S29" s="9">
-        <f>Q29/MAX($Q$2:$Q$28)</f>
-        <v>0.73913727425384901</v>
+        <f t="shared" si="10"/>
+        <v>0.86013040616690428</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -2778,54 +2778,54 @@
         <v>64.349999999999994</v>
       </c>
       <c r="G30" s="1">
-        <f>E30*F30</f>
+        <f t="shared" si="0"/>
         <v>6.4349999999999995E-21</v>
       </c>
       <c r="H30" s="11">
-        <v>0.43880000000000002</v>
+        <v>0.4667</v>
       </c>
       <c r="I30" s="11">
-        <v>0.6825</v>
+        <v>0.70420000000000005</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR(H30/I30,"")</f>
-        <v>0.64293040293040293</v>
+        <f t="shared" si="1"/>
+        <v>0.66273785856290823</v>
       </c>
       <c r="K30" s="9">
-        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.13655409701577689</v>
+        <f t="shared" si="2"/>
+        <v>6.563298897249574E-2</v>
       </c>
       <c r="L30" s="12">
-        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
-        <v>92.58677999999999</v>
+        <f t="shared" si="11"/>
+        <v>94.38214499999998</v>
       </c>
       <c r="M30" s="12">
-        <f>F30/(1+I30-H30)</f>
-        <v>51.740773498432091</v>
+        <f t="shared" si="4"/>
+        <v>51.999999999999986</v>
       </c>
       <c r="N30" s="12">
-        <f>L30-F30</f>
-        <v>28.236779999999996</v>
+        <f t="shared" si="5"/>
+        <v>30.032144999999986</v>
       </c>
       <c r="O30" s="12">
-        <f>0.5*(M30-F30)</f>
-        <v>-6.3046132507839516</v>
+        <f t="shared" si="6"/>
+        <v>-6.1750000000000043</v>
       </c>
       <c r="P30" s="14">
-        <f>N30+O30</f>
-        <v>21.932166749216044</v>
+        <f t="shared" si="7"/>
+        <v>23.857144999999981</v>
       </c>
       <c r="Q30" s="12">
-        <f>MAX($P$2:$P$280)-P30</f>
-        <v>330.57890491135555</v>
+        <f t="shared" si="8"/>
+        <v>229.31043118320574</v>
       </c>
       <c r="R30" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.0249964082497919E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.3609006133744433E-3</v>
       </c>
       <c r="S30" s="9">
-        <f>Q30/MAX($Q$2:$Q$28)</f>
-        <v>0.65833643013676313</v>
+        <f t="shared" si="10"/>
+        <v>0.84364416749048277</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -2848,54 +2848,54 @@
         <v>51.15</v>
       </c>
       <c r="G31" s="1">
-        <f>E31*F31</f>
+        <f t="shared" si="0"/>
         <v>54.996479999999998</v>
       </c>
       <c r="H31" s="11">
-        <v>0.1426</v>
+        <v>0.11169999999999999</v>
       </c>
       <c r="I31" s="11">
-        <v>0.20569999999999999</v>
+        <v>0.2477</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR(H31/I31,"")</f>
-        <v>0.69324258629071467</v>
+        <f t="shared" si="1"/>
+        <v>0.45094872830036331</v>
       </c>
       <c r="K31" s="9">
-        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.14724006665781803</v>
+        <f t="shared" si="2"/>
+        <v>4.4658853465648692E-2</v>
       </c>
       <c r="L31" s="12">
-        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
-        <v>58.443989999999999</v>
+        <f t="shared" si="11"/>
+        <v>56.863454999999995</v>
       </c>
       <c r="M31" s="12">
-        <f>F31/(1+I31-H31)</f>
-        <v>48.114006208258864</v>
+        <f t="shared" si="4"/>
+        <v>45.026408450704217</v>
       </c>
       <c r="N31" s="12">
-        <f>L31-F31</f>
-        <v>7.2939900000000009</v>
+        <f t="shared" si="5"/>
+        <v>5.7134549999999962</v>
       </c>
       <c r="O31" s="12">
-        <f>0.5*(M31-F31)</f>
-        <v>-1.5179968958705672</v>
+        <f t="shared" si="6"/>
+        <v>-3.0617957746478908</v>
       </c>
       <c r="P31" s="14">
-        <f>N31+O31</f>
-        <v>5.7759931041294337</v>
+        <f t="shared" si="7"/>
+        <v>2.6516592253521054</v>
       </c>
       <c r="Q31" s="12">
-        <f>MAX($P$2:$P$280)-P31</f>
-        <v>346.73507855644215</v>
+        <f t="shared" si="8"/>
+        <v>250.51591695785362</v>
       </c>
       <c r="R31" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.8840462411916547E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.9917623284920385E-3</v>
       </c>
       <c r="S31" s="9">
-        <f>Q31/MAX($Q$2:$Q$28)</f>
-        <v>0.6905108899227802</v>
+        <f t="shared" si="10"/>
+        <v>0.92166017531130062</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -2918,54 +2918,54 @@
         <v>144.28</v>
       </c>
       <c r="G32" s="1">
-        <f>E32*F32</f>
+        <f t="shared" si="0"/>
         <v>35.189892</v>
       </c>
       <c r="H32" s="11">
-        <v>2.6599999999999999E-2</v>
+        <v>3.8300000000000001E-2</v>
       </c>
       <c r="I32" s="11">
-        <v>0.18690000000000001</v>
+        <v>0.2152</v>
       </c>
       <c r="J32" s="9">
-        <f>IFERROR(H32/I32,"")</f>
-        <v>0.14232209737827714</v>
+        <f t="shared" si="1"/>
+        <v>0.17797397769516729</v>
       </c>
       <c r="K32" s="9">
-        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.0228257062196982E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.7625315899090652E-2</v>
       </c>
       <c r="L32" s="12">
-        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
-        <v>148.11784799999998</v>
+        <f t="shared" si="11"/>
+        <v>149.805924</v>
       </c>
       <c r="M32" s="12">
-        <f>F32/(1+I32-H32)</f>
-        <v>124.34715159872445</v>
+        <f t="shared" si="4"/>
+        <v>122.59325346248619</v>
       </c>
       <c r="N32" s="12">
-        <f>L32-F32</f>
-        <v>3.8378479999999797</v>
+        <f t="shared" si="5"/>
+        <v>5.5259240000000034</v>
       </c>
       <c r="O32" s="12">
-        <f>0.5*(M32-F32)</f>
-        <v>-9.9664242006377748</v>
+        <f t="shared" si="6"/>
+        <v>-10.843373268756906</v>
       </c>
       <c r="P32" s="14">
-        <f>N32+O32</f>
-        <v>-6.1285762006377951</v>
+        <f t="shared" si="7"/>
+        <v>-5.3174492687569028</v>
       </c>
       <c r="Q32" s="12">
-        <f>MAX($P$2:$P$280)-P32</f>
-        <v>358.63964786120937</v>
+        <f t="shared" si="8"/>
+        <v>258.4850254519626</v>
       </c>
       <c r="R32" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7883141363862587E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.868696061798915E-3</v>
       </c>
       <c r="S32" s="9">
-        <f>Q32/MAX($Q$2:$Q$28)</f>
-        <v>0.71421842704018235</v>
+        <f t="shared" si="10"/>
+        <v>0.95097891090681541</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -2988,54 +2988,54 @@
         <v>165.59</v>
       </c>
       <c r="G33" s="1">
-        <f>E33*F33</f>
+        <f t="shared" si="0"/>
         <v>29.922113</v>
       </c>
       <c r="H33" s="11">
-        <v>5.7000000000000002E-3</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="I33" s="11">
-        <v>0.1714</v>
+        <v>0.22189999999999999</v>
       </c>
       <c r="J33" s="9">
-        <f>IFERROR(H33/I33,"")</f>
-        <v>3.3255542590431737E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.29067147363677337</v>
       </c>
       <c r="K33" s="9">
-        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.0632537651166222E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.8786099024416232E-2</v>
       </c>
       <c r="L33" s="12">
-        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
-        <v>166.533863</v>
+        <f t="shared" si="11"/>
+        <v>176.270555</v>
       </c>
       <c r="M33" s="12">
-        <f>F33/(1+I33-H33)</f>
-        <v>142.05198593120014</v>
+        <f t="shared" si="4"/>
+        <v>143.07067565232418</v>
       </c>
       <c r="N33" s="12">
-        <f>L33-F33</f>
-        <v>0.94386299999999324</v>
+        <f t="shared" si="5"/>
+        <v>10.680554999999998</v>
       </c>
       <c r="O33" s="12">
-        <f>0.5*(M33-F33)</f>
-        <v>-11.769007034399934</v>
+        <f t="shared" si="6"/>
+        <v>-11.25966217383791</v>
       </c>
       <c r="P33" s="14">
-        <f>N33+O33</f>
-        <v>-10.825144034399941</v>
+        <f t="shared" si="7"/>
+        <v>-0.57910717383791166</v>
       </c>
       <c r="Q33" s="12">
-        <f>MAX($P$2:$P$280)-P33</f>
-        <v>363.33621569497154</v>
+        <f t="shared" si="8"/>
+        <v>253.74668335704362</v>
       </c>
       <c r="R33" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.752271743919745E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.9409382095958794E-3</v>
       </c>
       <c r="S33" s="9">
-        <f>Q33/MAX($Q$2:$Q$28)</f>
-        <v>0.72357147908203379</v>
+        <f t="shared" si="10"/>
+        <v>0.93354632115794667</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -3058,54 +3058,54 @@
         <v>86.6</v>
       </c>
       <c r="G34" s="1">
-        <f>E34*F34</f>
+        <f t="shared" si="0"/>
         <v>8.6599999999999988E-34</v>
       </c>
       <c r="H34" s="11">
-        <v>0.23649999999999999</v>
+        <v>0.18629999999999999</v>
       </c>
       <c r="I34" s="11">
-        <v>0.20849999999999999</v>
+        <v>0.22650000000000001</v>
       </c>
       <c r="J34" s="9">
-        <f>IFERROR(H34/I34,"")</f>
-        <v>1.1342925659472423</v>
+        <f t="shared" si="1"/>
+        <v>0.82251655629139064</v>
       </c>
       <c r="K34" s="9">
-        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.24091611843000879</v>
+        <f t="shared" si="2"/>
+        <v>8.1456369771644402E-2</v>
       </c>
       <c r="L34" s="12">
-        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
-        <v>107.08089999999999</v>
+        <f t="shared" si="11"/>
+        <v>102.73357999999999</v>
       </c>
       <c r="M34" s="12">
-        <f>F34/(1+I34-H34)</f>
-        <v>89.094650205761312</v>
+        <f t="shared" si="4"/>
+        <v>83.253220534512593</v>
       </c>
       <c r="N34" s="12">
-        <f>L34-F34</f>
-        <v>20.480899999999991</v>
+        <f t="shared" si="5"/>
+        <v>16.133579999999995</v>
       </c>
       <c r="O34" s="12">
-        <f>0.5*(M34-F34)</f>
-        <v>1.2473251028806587</v>
+        <f t="shared" si="6"/>
+        <v>-1.6733897327437006</v>
       </c>
       <c r="P34" s="14">
-        <f>N34+O34</f>
-        <v>21.72822510288065</v>
+        <f t="shared" si="7"/>
+        <v>14.460190267256294</v>
       </c>
       <c r="Q34" s="12">
-        <f>MAX($P$2:$P$280)-P34</f>
-        <v>330.78284655769096</v>
+        <f t="shared" si="8"/>
+        <v>238.70738591594943</v>
       </c>
       <c r="R34" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.0231313697386439E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.1892294038698369E-3</v>
       </c>
       <c r="S34" s="9">
-        <f>Q34/MAX($Q$2:$Q$28)</f>
-        <v>0.65874257285612592</v>
+        <f t="shared" si="10"/>
+        <v>0.87821601845925767</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFB1D01-8585-4E75-952F-3C66818A376E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99021514-03EF-4366-BDE1-AFA979FC89F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="133">
   <si>
     <t>Name</t>
   </si>
@@ -310,6 +311,135 @@
   </si>
   <si>
     <t>ING</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>MMM</t>
+  </si>
+  <si>
+    <t>Excelon</t>
+  </si>
+  <si>
+    <t>EXC</t>
+  </si>
+  <si>
+    <t>PG&amp;E</t>
+  </si>
+  <si>
+    <t>PCG</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Agios</t>
+  </si>
+  <si>
+    <t>AGIO</t>
+  </si>
+  <si>
+    <t>Albertson Companies</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>HCA Healthcare</t>
+  </si>
+  <si>
+    <t>HCA</t>
+  </si>
+  <si>
+    <t>Nombre Ticker</t>
+  </si>
+  <si>
+    <t>Annual Return</t>
+  </si>
+  <si>
+    <t>Annual Volatility</t>
+  </si>
+  <si>
+    <t>Monthly Return</t>
+  </si>
+  <si>
+    <t>Monthly Volatility</t>
+  </si>
+  <si>
+    <t>3M Company</t>
+  </si>
+  <si>
+    <t>Agios Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>HCA Healthcare, Inc.</t>
+  </si>
+  <si>
+    <t>Maxeon Solar Technologies, Ltd.</t>
+  </si>
+  <si>
+    <t>NextEra Energy, Inc.</t>
+  </si>
+  <si>
+    <t>First Solar, Inc.</t>
+  </si>
+  <si>
+    <t>Duke Energy Corporation (Holdin</t>
+  </si>
+  <si>
+    <t>JinkoSolar Holding Company Limi</t>
+  </si>
+  <si>
+    <t>SolarWinds Corporation</t>
+  </si>
+  <si>
+    <t>Canadian Solar Inc.</t>
+  </si>
+  <si>
+    <t>SolarEdge Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>Exelon Corporation</t>
+  </si>
+  <si>
+    <t>Pacific Gas &amp; Electric Co.</t>
+  </si>
+  <si>
+    <t>APA Corporation</t>
+  </si>
+  <si>
+    <t>Altria Group, Inc.</t>
+  </si>
+  <si>
+    <t>Kimberly-Clark Corporation</t>
+  </si>
+  <si>
+    <t>Pepsico, Inc.</t>
+  </si>
+  <si>
+    <t>Walmart Inc.</t>
+  </si>
+  <si>
+    <t>Albertsons Companies, Inc.</t>
+  </si>
+  <si>
+    <t>Tic</t>
+  </si>
+  <si>
+    <t>ker Vo</t>
+  </si>
+  <si>
+    <t>lume % Optimal</t>
+  </si>
+  <si>
+    <t>Weight</t>
   </si>
 </sst>
 </file>
@@ -395,7 +525,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -433,6 +563,7 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -715,7 +846,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S34"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -798,2320 +930,2859 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="D2" s="8">
-        <v>45562</v>
+        <v>45623</v>
       </c>
       <c r="E2" s="2">
-        <v>4.0300000000000002E-2</v>
+        <v>1.9595</v>
       </c>
       <c r="F2" s="1">
-        <v>668.82</v>
+        <v>15.3</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G34" si="0">E2*F2</f>
-        <v>26.953446000000003</v>
+        <f>E2*F2</f>
+        <v>29.980350000000001</v>
       </c>
       <c r="H2" s="11">
-        <v>8.1299999999999997E-2</v>
+        <v>0.35</v>
       </c>
       <c r="I2" s="11">
-        <v>0.29920000000000002</v>
+        <v>0.39532299999999998</v>
       </c>
       <c r="J2" s="9">
-        <f t="shared" ref="J2:J34" si="1">IFERROR(H2/I2,"")</f>
-        <v>0.27172459893048123</v>
+        <f>IFERROR(H2/I2,"")</f>
+        <v>0.88535197800279775</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K34" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6909731162532133E-2</v>
+        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.4858722504833506</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L19" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>723.195066</v>
+        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
+        <v>20.655000000000001</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M34" si="4">F2/(1+I2-H2)</f>
-        <v>549.15838738812715</v>
+        <f>F2/(1+I2-H2)</f>
+        <v>14.636624277854791</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N34" si="5">L2-F2</f>
-        <v>54.375065999999947</v>
+        <f>L2-F2</f>
+        <v>5.3550000000000004</v>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O34" si="6">0.5*(M2-F2)</f>
-        <v>-59.830806305936449</v>
+        <f>0.5*(M2-F2)</f>
+        <v>-0.33168786107260484</v>
       </c>
       <c r="P2" s="14">
-        <f t="shared" ref="P2:P34" si="7">N2+O2</f>
-        <v>-5.4557403059365015</v>
+        <f>N2+O2</f>
+        <v>5.0233121389273956</v>
       </c>
       <c r="Q2" s="12">
-        <f t="shared" ref="Q2:Q34" si="8">MAX($P$2:$P$280)-P2</f>
-        <v>258.62331648914221</v>
+        <f>MAX($P$2:$P$280)-P2</f>
+        <v>98.605197889725929</v>
       </c>
       <c r="R2" s="9">
-        <f t="shared" ref="R2:R34" si="9">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.8666273929790201E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0141453203291975E-2</v>
       </c>
       <c r="S2" s="9">
-        <f t="shared" ref="S2:S34" si="10">Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.95148769032138802</v>
+        <f>Q2/MAX($Q$2:$Q$28)</f>
+        <v>0.44581150370259182</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="D3" s="8">
-        <v>45580</v>
+        <v>45553</v>
       </c>
       <c r="E3" s="2">
-        <v>0.19139999999999999</v>
+        <v>1.0751999999999999</v>
       </c>
       <c r="F3" s="1">
-        <v>135.82</v>
+        <v>51.15</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" si="0"/>
-        <v>25.995947999999999</v>
+        <f>E3*F3</f>
+        <v>54.996479999999998</v>
       </c>
       <c r="H3" s="11">
-        <v>0.1221</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C3,Sheet1!$G:$G,0),2)</f>
+        <v>0.1346</v>
       </c>
       <c r="I3" s="11">
-        <v>0.29170000000000001</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C3,Sheet1!$G:$G,0),3)</f>
+        <v>0.20530000000000001</v>
       </c>
       <c r="J3" s="9">
-        <f t="shared" si="1"/>
-        <v>0.41858073363044224</v>
+        <f>IFERROR(H3/I3,"")</f>
+        <v>0.65562591329761322</v>
       </c>
       <c r="K3" s="9">
-        <f t="shared" si="2"/>
-        <v>4.1453350400169175E-2</v>
+        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1003266220337604</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" si="3"/>
-        <v>152.40362200000001</v>
+        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
+        <v>58.034790000000001</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" si="4"/>
-        <v>116.125170998632</v>
+        <f>F3/(1+I3-H3)</f>
+        <v>47.772485289997199</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" si="5"/>
-        <v>16.58362200000002</v>
+        <f>L3-F3</f>
+        <v>6.8847900000000024</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" si="6"/>
-        <v>-9.8474145006839962</v>
+        <f>0.5*(M3-F3)</f>
+        <v>-1.6887573550013997</v>
       </c>
       <c r="P3" s="14">
-        <f t="shared" si="7"/>
-        <v>6.7362074993160235</v>
+        <f>N3+O3</f>
+        <v>5.1960326449986027</v>
       </c>
       <c r="Q3" s="12">
-        <f t="shared" si="8"/>
-        <v>246.43136868388967</v>
+        <f>MAX($P$2:$P$280)-P3</f>
+        <v>98.432477383654714</v>
       </c>
       <c r="R3" s="9">
-        <f t="shared" si="9"/>
-        <v>4.0579249522521297E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0159248518173087E-2</v>
       </c>
       <c r="S3" s="9">
-        <f t="shared" si="10"/>
-        <v>0.90663292465208434</v>
+        <f>Q3/MAX($Q$2:$Q$28)</f>
+        <v>0.44503060380907916</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
+        <v>40</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D4" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E4" s="2">
-        <v>0.18010000000000001</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>133.19999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="0"/>
-        <v>23.989319999999999</v>
+        <f>E4*F4</f>
+        <v>10.92</v>
       </c>
       <c r="H4" s="11">
-        <v>8.1299999999999997E-2</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C4,Sheet1!$G:$G,0),2)</f>
+        <v>-1.7947</v>
       </c>
       <c r="I4" s="11">
-        <v>0.25829999999999997</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C4,Sheet1!$G:$G,0),3)</f>
+        <v>1.4319</v>
       </c>
       <c r="J4" s="9">
-        <f t="shared" si="1"/>
-        <v>0.31475029036004648</v>
+        <f>IFERROR(H4/I4,"")</f>
+        <v>-1.253369648718486</v>
       </c>
       <c r="K4" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1170699046959412E-2</v>
+        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-2.1035104985364117</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" si="3"/>
-        <v>144.02915999999999</v>
+        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
+        <v>-8.6781240000000022</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" si="4"/>
-        <v>113.16907391673746</v>
+        <f>F4/(1+I4-H4)</f>
+        <v>2.5836369658827429</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" si="5"/>
-        <v>10.829160000000002</v>
+        <f>L4-F4</f>
+        <v>-19.598124000000002</v>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.015463041631264</v>
+        <f>0.5*(M4-F4)</f>
+        <v>-4.1681815170586285</v>
       </c>
       <c r="P4" s="14">
-        <f t="shared" si="7"/>
-        <v>0.81369695836873746</v>
+        <f>N4+O4</f>
+        <v>-23.76630551705863</v>
       </c>
       <c r="Q4" s="12">
-        <f t="shared" si="8"/>
-        <v>252.35387922483699</v>
+        <f>MAX($P$2:$P$280)-P4</f>
+        <v>127.39481554571195</v>
       </c>
       <c r="R4" s="9">
-        <f t="shared" si="9"/>
-        <v>3.9626892325639301E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.8496129981143452E-3</v>
       </c>
       <c r="S4" s="9">
-        <f t="shared" si="10"/>
-        <v>0.92842212738913377</v>
+        <f>Q4/MAX($Q$2:$Q$28)</f>
+        <v>0.5759744465587221</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>59</v>
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8">
-        <v>45574</v>
+        <v>45511</v>
       </c>
       <c r="E5" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F5" s="1">
-        <v>47.42</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="0"/>
-        <v>4.7420000000000006E-44</v>
+        <f>E5*F5</f>
+        <v>34.982874000000002</v>
       </c>
       <c r="H5" s="11">
-        <v>-6.9999999999999999E-4</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C5,Sheet1!$G:$G,0),2)</f>
+        <v>-3.8800000000000001E-2</v>
       </c>
       <c r="I5" s="11">
-        <v>0.38319999999999999</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C5,Sheet1!$G:$G,0),3)</f>
+        <v>0.28689999999999999</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" si="1"/>
-        <v>-1.826722338204593E-3</v>
+        <f>IFERROR(H5/I5,"")</f>
+        <v>-0.13523875914952946</v>
       </c>
       <c r="K5" s="9">
-        <f t="shared" si="2"/>
-        <v>-1.8090598798621858E-4</v>
+        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-0.22696907490215393</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" si="3"/>
-        <v>47.386806</v>
+        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <v>74.425716000000008</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="4"/>
-        <v>34.265481609942917</v>
+        <f>F5/(1+I5-H5)</f>
+        <v>58.406879384476134</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" si="5"/>
-        <v>-3.3194000000001722E-2</v>
+        <f>L5-F5</f>
+        <v>-3.0042839999999984</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="6"/>
-        <v>-6.5772591950285424</v>
+        <f>0.5*(M5-F5)</f>
+        <v>-9.5115603077619362</v>
       </c>
       <c r="P5" s="14">
-        <f t="shared" si="7"/>
-        <v>-6.6104531950285441</v>
+        <f>N5+O5</f>
+        <v>-12.515844307761935</v>
       </c>
       <c r="Q5" s="12">
-        <f t="shared" si="8"/>
-        <v>259.77802937823424</v>
+        <f>MAX($P$2:$P$280)-P5</f>
+        <v>116.14435433641526</v>
       </c>
       <c r="R5" s="9">
-        <f t="shared" si="9"/>
-        <v>3.8494402409374271E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.6099751099693832E-3</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="10"/>
-        <v>0.95573593489090902</v>
+        <f>Q5/MAX($Q$2:$Q$28)</f>
+        <v>0.52510912569933532</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D6" s="8">
-        <v>45507</v>
+        <v>45544</v>
       </c>
       <c r="E6" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>0.35149999999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>41.8</v>
+        <v>142.78</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="0"/>
-        <v>4.1799999999999994E-44</v>
+        <f>E6*F6</f>
+        <v>50.187169999999995</v>
       </c>
       <c r="H6" s="11">
-        <v>7.3499999999999996E-2</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C6,Sheet1!$G:$G,0),2)</f>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="I6" s="11">
-        <v>0.4546</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C6,Sheet1!$G:$G,0),3)</f>
+        <v>0.1867</v>
       </c>
       <c r="J6" s="9">
-        <f t="shared" si="1"/>
-        <v>0.16168059832820061</v>
+        <f>IFERROR(H6/I6,"")</f>
+        <v>0.1098018211033744</v>
       </c>
       <c r="K6" s="9">
-        <f t="shared" si="2"/>
-        <v>1.6011731923918807E-2</v>
+        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.1842786632702656</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" si="3"/>
-        <v>44.872299999999996</v>
+        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <v>145.70698999999999</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="4"/>
-        <v>30.26573021504597</v>
+        <f>F6/(1+I6-H6)</f>
+        <v>122.43182987480705</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" si="5"/>
-        <v>3.0722999999999985</v>
+        <f>L6-F6</f>
+        <v>2.9269899999999893</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.7671348924770136</v>
+        <f>0.5*(M6-F6)</f>
+        <v>-10.174085062596475</v>
       </c>
       <c r="P6" s="14">
-        <f t="shared" si="7"/>
-        <v>-2.6948348924770151</v>
+        <f>N6+O6</f>
+        <v>-7.2470950625964861</v>
       </c>
       <c r="Q6" s="12">
-        <f t="shared" si="8"/>
-        <v>255.86241107568273</v>
+        <f>MAX($P$2:$P$280)-P6</f>
+        <v>110.87560509124981</v>
       </c>
       <c r="R6" s="9">
-        <f t="shared" si="9"/>
-        <v>3.9083505693386332E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.0191165060791081E-3</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="10"/>
-        <v>0.94133018576723593</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q6/MAX($Q$2:$Q$28)</f>
+        <v>0.50128818041564005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>75</v>
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="D7" s="8">
-        <v>45562</v>
+        <v>45484</v>
       </c>
       <c r="E7" s="2">
-        <v>1E-35</v>
+        <v>0.33389999999999997</v>
       </c>
       <c r="F7" s="1">
-        <v>56</v>
+        <v>188.53</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>5.5999999999999999E-34</v>
+        <f>E7*F7</f>
+        <v>62.950166999999993</v>
       </c>
       <c r="H7" s="11">
-        <v>-0.1119</v>
+        <f>227.4/F7-1</f>
+        <v>0.20617408370020684</v>
       </c>
       <c r="I7" s="11">
-        <v>0.49480000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.2261519805982215</v>
+        <f>IFERROR(H7/I7,"")</f>
+        <v>0.55722725324380229</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="2"/>
-        <v>-2.2396533194734065E-2</v>
+        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.93518570396801892</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="3"/>
-        <v>49.733599999999996</v>
+        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
+        <v>227.4</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="4"/>
-        <v>34.854048671189396</v>
+        <f>F7/(1+I7-H7)</f>
+        <v>161.9915808365931</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" si="5"/>
-        <v>-6.2664000000000044</v>
+        <f>L7-F7</f>
+        <v>38.870000000000005</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.572975664405302</v>
+        <f>0.5*(M7-F7)</f>
+        <v>-13.26920958170345</v>
       </c>
       <c r="P7" s="14">
-        <f t="shared" si="7"/>
-        <v>-16.839375664405306</v>
+        <f>N7+O7</f>
+        <v>25.600790418296555</v>
       </c>
       <c r="Q7" s="12">
-        <f t="shared" si="8"/>
-        <v>270.00695184761099</v>
+        <f>MAX($P$2:$P$280)-P7</f>
+        <v>78.027719610356769</v>
       </c>
       <c r="R7" s="9">
-        <f t="shared" si="9"/>
-        <v>3.7036083447376912E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2815958290126271E-2</v>
       </c>
       <c r="S7" s="9">
-        <f t="shared" si="10"/>
-        <v>0.99336863540293907</v>
+        <f>Q7/MAX($Q$2:$Q$28)</f>
+        <v>0.35277709242954441</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="8">
+        <v>45460</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.33529999999999999</v>
+      </c>
+      <c r="F8" s="1">
+        <v>163.15</v>
+      </c>
+      <c r="G8" s="1">
+        <f>E8*F8</f>
+        <v>54.704194999999999</v>
+      </c>
+      <c r="H8" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C8,Sheet1!$G:$G,0),2)</f>
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I8" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C8,Sheet1!$G:$G,0),3)</f>
+        <v>0.1711</v>
+      </c>
+      <c r="J8" s="9">
+        <f>IFERROR(H8/I8,"")</f>
+        <v>1.7533606078316772E-3</v>
+      </c>
+      <c r="K8" s="9">
+        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.9426374334699649E-3</v>
+      </c>
+      <c r="L8" s="12">
+        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <v>163.19894500000001</v>
+      </c>
+      <c r="M8" s="12">
+        <f>F8/(1+I8-H8)</f>
+        <v>139.34916296549369</v>
+      </c>
+      <c r="N8" s="12">
+        <f>L8-F8</f>
+        <v>4.8945000000003347E-2</v>
+      </c>
+      <c r="O8" s="12">
+        <f>0.5*(M8-F8)</f>
+        <v>-11.900418517253158</v>
+      </c>
+      <c r="P8" s="14">
+        <f>N8+O8</f>
+        <v>-11.851473517253154</v>
+      </c>
+      <c r="Q8" s="12">
+        <f>MAX($P$2:$P$280)-P8</f>
+        <v>115.47998354590648</v>
+      </c>
+      <c r="R8" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.6595093737822752E-3</v>
+      </c>
+      <c r="S8" s="9">
+        <f>Q8/MAX($Q$2:$Q$28)</f>
+        <v>0.52210538809247986</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="8">
+        <v>45544</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.1928</v>
+      </c>
+      <c r="F9" s="1">
+        <v>188.12</v>
+      </c>
+      <c r="G9" s="1">
+        <f>E9*F9</f>
+        <v>36.269536000000002</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0.37780000000000002</v>
+      </c>
+      <c r="J9" s="9">
+        <f>IFERROR(H9/I9,"")</f>
+        <v>0.39703546850185278</v>
+      </c>
+      <c r="K9" s="9">
+        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.66633836006711356</v>
+      </c>
+      <c r="L9" s="12">
+        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <v>216.33799999999999</v>
+      </c>
+      <c r="M9" s="12">
+        <f>F9/(1+I9-H9)</f>
+        <v>153.21713634142367</v>
+      </c>
+      <c r="N9" s="12">
+        <f>L9-F9</f>
+        <v>28.217999999999989</v>
+      </c>
+      <c r="O9" s="12">
+        <f>0.5*(M9-F9)</f>
+        <v>-17.451431829288168</v>
+      </c>
+      <c r="P9" s="14">
+        <f>N9+O9</f>
+        <v>10.766568170711821</v>
+      </c>
+      <c r="Q9" s="12">
+        <f>MAX($P$2:$P$280)-P9</f>
+        <v>92.861941857941503</v>
+      </c>
+      <c r="R9" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0768674227486882E-2</v>
+      </c>
+      <c r="S9" s="9">
+        <f>Q9/MAX($Q$2:$Q$28)</f>
+        <v>0.41984522948505815</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="8">
+        <v>45580</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.19139999999999999</v>
+      </c>
+      <c r="F10" s="1">
+        <v>135.82</v>
+      </c>
+      <c r="G10" s="1">
+        <f>E10*F10</f>
+        <v>25.995947999999999</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0.1202</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0.33710000000000001</v>
+      </c>
+      <c r="J10" s="9">
+        <f>IFERROR(H10/I10,"")</f>
+        <v>0.35657075051913378</v>
+      </c>
+      <c r="K10" s="9">
+        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.59842706256282674</v>
+      </c>
+      <c r="L10" s="12">
+        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <v>152.14556400000001</v>
+      </c>
+      <c r="M10" s="12">
+        <f>F10/(1+I10-H10)</f>
+        <v>111.61147177253677</v>
+      </c>
+      <c r="N10" s="12">
+        <f>L10-F10</f>
+        <v>16.325564000000014</v>
+      </c>
+      <c r="O10" s="12">
+        <f>0.5*(M10-F10)</f>
+        <v>-12.10426411373161</v>
+      </c>
+      <c r="P10" s="14">
+        <f>N10+O10</f>
+        <v>4.2212998862684046</v>
+      </c>
+      <c r="Q10" s="12">
+        <f>MAX($P$2:$P$280)-P10</f>
+        <v>99.407210142384912</v>
+      </c>
+      <c r="R10" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0059632481061084E-2</v>
+      </c>
+      <c r="S10" s="9">
+        <f>Q10/MAX($Q$2:$Q$28)</f>
+        <v>0.44943754265386154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="8">
+        <v>45482</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.18820000000000001</v>
+      </c>
+      <c r="F11" s="1">
+        <v>227.38</v>
+      </c>
+      <c r="G11" s="1">
+        <f>E11*F11</f>
+        <v>42.792915999999998</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0.2271</v>
+      </c>
+      <c r="J11" s="9">
+        <f>IFERROR(H11/I11,"")</f>
+        <v>0.66050198150594452</v>
+      </c>
+      <c r="K11" s="9">
+        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1085100503450265</v>
+      </c>
+      <c r="L11" s="12">
+        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <v>261.48699999999997</v>
+      </c>
+      <c r="M11" s="12">
+        <f>F11/(1+I11-H11)</f>
+        <v>211.10389007520189</v>
+      </c>
+      <c r="N11" s="12">
+        <f>L11-F11</f>
+        <v>34.106999999999971</v>
+      </c>
+      <c r="O11" s="12">
+        <f>0.5*(M11-F11)</f>
+        <v>-8.1380549623990532</v>
+      </c>
+      <c r="P11" s="14">
+        <f>N11+O11</f>
+        <v>25.968945037600918</v>
+      </c>
+      <c r="Q11" s="12">
+        <f>MAX($P$2:$P$280)-P11</f>
+        <v>77.659564991052406</v>
+      </c>
+      <c r="R11" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2876713900151458E-2</v>
+      </c>
+      <c r="S11" s="9">
+        <f>Q11/MAX($Q$2:$Q$28)</f>
+        <v>0.35111260041553638</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="8">
+        <v>45580</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.18010000000000001</v>
+      </c>
+      <c r="F12" s="1">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="G12" s="1">
+        <f>E12*F12</f>
+        <v>23.989319999999999</v>
+      </c>
+      <c r="H12" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0.1623</v>
+      </c>
+      <c r="J12" s="9">
+        <f>IFERROR(H12/I12,"")</f>
+        <v>0.43130006161429457</v>
+      </c>
+      <c r="K12" s="9">
+        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.7238440858630063</v>
+      </c>
+      <c r="L12" s="12">
+        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <v>142.524</v>
+      </c>
+      <c r="M12" s="12">
+        <f>F12/(1+I12-H12)</f>
+        <v>121.94452073606151</v>
+      </c>
+      <c r="N12" s="12">
+        <f>L12-F12</f>
+        <v>9.3240000000000123</v>
+      </c>
+      <c r="O12" s="12">
+        <f>0.5*(M12-F12)</f>
+        <v>-5.6277396319692414</v>
+      </c>
+      <c r="P12" s="14">
+        <f>N12+O12</f>
+        <v>3.6962603680307708</v>
+      </c>
+      <c r="Q12" s="12">
+        <f>MAX($P$2:$P$280)-P12</f>
+        <v>99.932249660622546</v>
+      </c>
+      <c r="R12" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0006779627158154E-2</v>
+      </c>
+      <c r="S12" s="9">
+        <f>Q12/MAX($Q$2:$Q$28)</f>
+        <v>0.45181133898649067</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C13" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" s="8">
-        <v>45511</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.14610000000000001</v>
-      </c>
-      <c r="F8" s="1">
-        <v>273.45999999999998</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>39.952506</v>
-      </c>
-      <c r="H8" s="11">
-        <v>0.109</v>
-      </c>
-      <c r="I8" s="11">
-        <v>0.28029999999999999</v>
-      </c>
-      <c r="J8" s="9">
-        <f t="shared" si="1"/>
-        <v>0.38886906885479844</v>
-      </c>
-      <c r="K8" s="9">
-        <f t="shared" si="2"/>
-        <v>3.8510911936184528E-2</v>
-      </c>
-      <c r="L8" s="12">
-        <f t="shared" si="3"/>
-        <v>303.26713999999998</v>
-      </c>
-      <c r="M8" s="12">
-        <f t="shared" si="4"/>
-        <v>233.46708785110559</v>
-      </c>
-      <c r="N8" s="12">
-        <f t="shared" si="5"/>
-        <v>29.807140000000004</v>
-      </c>
-      <c r="O8" s="12">
-        <f t="shared" si="6"/>
-        <v>-19.996456074447195</v>
-      </c>
-      <c r="P8" s="14">
-        <f t="shared" si="7"/>
-        <v>9.8106839255528087</v>
-      </c>
-      <c r="Q8" s="12">
-        <f t="shared" si="8"/>
-        <v>243.3568922576529</v>
-      </c>
-      <c r="R8" s="9">
-        <f t="shared" si="9"/>
-        <v>4.1091911994884248E-3</v>
-      </c>
-      <c r="S8" s="9">
-        <f t="shared" si="10"/>
-        <v>0.89532177717528516</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="8">
-        <v>45623</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1.9595</v>
-      </c>
-      <c r="F9" s="1">
-        <v>15.3</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>29.980350000000001</v>
-      </c>
-      <c r="H9" s="11">
-        <v>9.98E-2</v>
-      </c>
-      <c r="I9" s="11">
-        <v>0.41930000000000001</v>
-      </c>
-      <c r="J9" s="9">
-        <f t="shared" si="1"/>
-        <v>0.23801574051991414</v>
-      </c>
-      <c r="K9" s="9">
-        <f t="shared" si="2"/>
-        <v>2.3571438195334509E-2</v>
-      </c>
-      <c r="L9" s="12">
-        <f t="shared" si="3"/>
-        <v>16.826940000000004</v>
-      </c>
-      <c r="M9" s="12">
-        <f t="shared" si="4"/>
-        <v>11.595301250473664</v>
-      </c>
-      <c r="N9" s="12">
-        <f t="shared" si="5"/>
-        <v>1.5269400000000033</v>
-      </c>
-      <c r="O9" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.8523493747631683</v>
-      </c>
-      <c r="P9" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.325409374763165</v>
-      </c>
-      <c r="Q9" s="12">
-        <f t="shared" si="8"/>
-        <v>253.49298555796886</v>
-      </c>
-      <c r="R9" s="9">
-        <f t="shared" si="9"/>
-        <v>3.9448823319464974E-3</v>
-      </c>
-      <c r="S9" s="9">
-        <f t="shared" si="10"/>
-        <v>0.93261295468442762</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="8">
-        <v>45511</v>
-      </c>
-      <c r="E10" s="2">
-        <v>3.2899999999999999E-2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>455.4</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>14.982659999999999</v>
-      </c>
-      <c r="H10" s="11">
-        <v>0.1205</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0.31109999999999999</v>
-      </c>
-      <c r="J10" s="9">
-        <f t="shared" si="1"/>
-        <v>0.38733526197364193</v>
-      </c>
-      <c r="K10" s="9">
-        <f t="shared" si="2"/>
-        <v>3.8359014275871031E-2</v>
-      </c>
-      <c r="L10" s="12">
-        <f t="shared" si="3"/>
-        <v>510.27569999999997</v>
-      </c>
-      <c r="M10" s="12">
-        <f t="shared" si="4"/>
-        <v>382.49622039307911</v>
-      </c>
-      <c r="N10" s="12">
-        <f t="shared" si="5"/>
-        <v>54.875699999999995</v>
-      </c>
-      <c r="O10" s="12">
-        <f t="shared" si="6"/>
-        <v>-36.451889803460432</v>
-      </c>
-      <c r="P10" s="14">
-        <f t="shared" si="7"/>
-        <v>18.423810196539563</v>
-      </c>
-      <c r="Q10" s="12">
-        <f t="shared" si="8"/>
-        <v>234.74376598666615</v>
-      </c>
-      <c r="R10" s="9">
-        <f t="shared" si="9"/>
-        <v>4.2599640326840531E-3</v>
-      </c>
-      <c r="S10" s="9">
-        <f t="shared" si="10"/>
-        <v>0.86363366902912075</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="8">
-        <v>45511</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.1933</v>
-      </c>
-      <c r="F11" s="1">
-        <v>77.53</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>14.986549</v>
-      </c>
-      <c r="H11" s="11">
-        <v>8.0100000000000005E-2</v>
-      </c>
-      <c r="I11" s="11">
-        <v>0.30659999999999998</v>
-      </c>
-      <c r="J11" s="9">
-        <f t="shared" si="1"/>
-        <v>0.26125244618395305</v>
-      </c>
-      <c r="K11" s="9">
-        <f t="shared" si="2"/>
-        <v>2.5872641343607998E-2</v>
-      </c>
-      <c r="L11" s="12">
-        <f t="shared" si="3"/>
-        <v>83.740153000000007</v>
-      </c>
-      <c r="M11" s="12">
-        <f t="shared" si="4"/>
-        <v>63.212392988177747</v>
-      </c>
-      <c r="N11" s="12">
-        <f t="shared" si="5"/>
-        <v>6.2101530000000054</v>
-      </c>
-      <c r="O11" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.158803505911127</v>
-      </c>
-      <c r="P11" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.94865050591112166</v>
-      </c>
-      <c r="Q11" s="12">
-        <f t="shared" si="8"/>
-        <v>254.11622668911684</v>
-      </c>
-      <c r="R11" s="9">
-        <f t="shared" si="9"/>
-        <v>3.9352071807023546E-3</v>
-      </c>
-      <c r="S11" s="9">
-        <f t="shared" si="10"/>
-        <v>0.9349058889505234</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="8">
-        <v>45511</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>10.4</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>10.4</v>
-      </c>
-      <c r="H12" s="11">
-        <v>-1.4254</v>
-      </c>
-      <c r="I12" s="11">
-        <v>1.3364</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" si="1"/>
-        <v>-1.0665968272972164</v>
-      </c>
-      <c r="K12" s="9">
-        <f t="shared" si="2"/>
-        <v>-0.10562839726086398</v>
-      </c>
-      <c r="L12" s="12">
-        <f t="shared" si="3"/>
-        <v>-4.4241600000000005</v>
-      </c>
-      <c r="M12" s="12">
-        <f t="shared" si="4"/>
-        <v>2.7646339518315699</v>
-      </c>
-      <c r="N12" s="12">
-        <f t="shared" si="5"/>
-        <v>-14.824160000000001</v>
-      </c>
-      <c r="O12" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.8176830240842152</v>
-      </c>
-      <c r="P12" s="14">
-        <f t="shared" si="7"/>
-        <v>-18.641843024084217</v>
-      </c>
-      <c r="Q12" s="12">
-        <f t="shared" si="8"/>
-        <v>271.80941920728992</v>
-      </c>
-      <c r="R12" s="9">
-        <f t="shared" si="9"/>
-        <v>3.679048367479018E-3</v>
-      </c>
-      <c r="S12" s="9">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
       </c>
       <c r="D13" s="8">
         <v>45511</v>
       </c>
       <c r="E13" s="2">
-        <v>1E-22</v>
+        <v>0.14610000000000001</v>
       </c>
       <c r="F13" s="1">
-        <v>187.36</v>
+        <v>273.45999999999998</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>1.8736000000000003E-20</v>
+        <f>E13*F13</f>
+        <v>39.952506</v>
       </c>
       <c r="H13" s="11">
-        <v>0.24759999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="I13" s="11">
-        <v>0.52890000000000004</v>
+        <v>0.26</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="1"/>
-        <v>0.46814142560030247</v>
+        <f>IFERROR(H13/I13,"")</f>
+        <v>0.96153846153846145</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="2"/>
-        <v>4.6361499689513468E-2</v>
+        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.6137348232907405</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="3"/>
-        <v>233.75033600000003</v>
+        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <v>341.82499999999999</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="4"/>
-        <v>146.22648872239131</v>
+        <f>F13/(1+I13-H13)</f>
+        <v>270.75247524752473</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" si="5"/>
-        <v>46.390336000000019</v>
+        <f>L13-F13</f>
+        <v>68.365000000000009</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="6"/>
-        <v>-20.566755638804352</v>
+        <f>0.5*(M13-F13)</f>
+        <v>-1.3537623762376256</v>
       </c>
       <c r="P13" s="14">
-        <f t="shared" si="7"/>
-        <v>25.823580361195667</v>
+        <f>N13+O13</f>
+        <v>67.011237623762383</v>
       </c>
       <c r="Q13" s="12">
-        <f t="shared" si="8"/>
-        <v>227.34399582201004</v>
+        <f>MAX($P$2:$P$280)-P13</f>
+        <v>36.61727240489094</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="9"/>
-        <v>4.3986206734173451E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.7309516365463384E-2</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="10"/>
-        <v>0.83640955668512273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q13/MAX($Q$2:$Q$28)</f>
+        <v>0.1655531515749106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
       </c>
       <c r="D14" s="8">
-        <v>45511</v>
+        <v>45574</v>
       </c>
       <c r="E14" s="2">
-        <v>1E-22</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>113.58</v>
+        <v>423.77</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1358E-20</v>
+        <f>E14*F14</f>
+        <v>56.658049000000005</v>
       </c>
       <c r="H14" s="11">
-        <v>9.5000000000000001E-2</v>
+        <v>0.15</v>
       </c>
       <c r="I14" s="11">
-        <v>0.24779999999999999</v>
+        <v>0.1963</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="1"/>
-        <v>0.38337368845843423</v>
+        <f>IFERROR(H14/I14,"")</f>
+        <v>0.76413652572592972</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="2"/>
-        <v>3.7966687343769748E-2</v>
+        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.2824382701648269</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="3"/>
-        <v>124.37009999999999</v>
+        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <v>487.33549999999991</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="4"/>
-        <v>98.525329632199856</v>
+        <f>F14/(1+I14-H14)</f>
+        <v>405.01768135334032</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" si="5"/>
-        <v>10.790099999999995</v>
+        <f>L14-F14</f>
+        <v>63.565499999999929</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.5273351839000711</v>
+        <f>0.5*(M14-F14)</f>
+        <v>-9.3761593233298299</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="7"/>
-        <v>3.2627648160999243</v>
+        <f>N14+O14</f>
+        <v>54.189340676670099</v>
       </c>
       <c r="Q14" s="12">
-        <f t="shared" si="8"/>
-        <v>249.90481136710579</v>
+        <f>MAX($P$2:$P$280)-P14</f>
+        <v>49.439169351983224</v>
       </c>
       <c r="R14" s="9">
-        <f t="shared" si="9"/>
-        <v>4.0015235982432422E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.0226877051280505E-2</v>
       </c>
       <c r="S14" s="9">
-        <f t="shared" si="10"/>
-        <v>0.91941188828530251</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q14/MAX($Q$2:$Q$28)</f>
+        <v>0.22352321076687609</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
       </c>
       <c r="D15" s="8">
-        <v>45511</v>
+        <v>45483</v>
       </c>
       <c r="E15" s="2">
-        <v>1E-22</v>
+        <v>0.1195</v>
       </c>
       <c r="F15" s="1">
-        <v>20.82</v>
+        <v>167.24</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0820000000000001E-21</v>
+        <f>E15*F15</f>
+        <v>19.98518</v>
       </c>
       <c r="H15" s="11">
-        <v>1.38E-2</v>
+        <f>190.41/F15-1</f>
+        <v>0.13854341066730447</v>
       </c>
       <c r="I15" s="11">
-        <v>0.81420000000000003</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="1"/>
-        <v>1.6949152542372881E-2</v>
+        <f>IFERROR(H15/I15,"")</f>
+        <v>0.51714598979956872</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="2"/>
-        <v>1.6785272299350835E-3</v>
+        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.86791795216331102</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="3"/>
-        <v>21.107316000000001</v>
+        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <v>190.41</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="4"/>
-        <v>11.564096867362808</v>
+        <f>F15/(1+I15-H15)</f>
+        <v>148.08431772538498</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" si="5"/>
-        <v>0.28731600000000057</v>
+        <f>L15-F15</f>
+        <v>23.169999999999987</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="6"/>
-        <v>-4.6279515663185959</v>
+        <f>0.5*(M15-F15)</f>
+        <v>-9.5778411373075159</v>
       </c>
       <c r="P15" s="14">
-        <f t="shared" si="7"/>
-        <v>-4.3406355663185954</v>
+        <f>N15+O15</f>
+        <v>13.592158862692472</v>
       </c>
       <c r="Q15" s="12">
-        <f t="shared" si="8"/>
-        <v>257.50821174952432</v>
+        <f>MAX($P$2:$P$280)-P15</f>
+        <v>90.036351165960852</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="9"/>
-        <v>3.8833713037962846E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1106625124742505E-2</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="10"/>
-        <v>0.94738516604952872</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q15/MAX($Q$2:$Q$28)</f>
+        <v>0.40707023524338853</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>54</v>
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D16" s="8">
-        <v>45511</v>
+        <v>45562</v>
       </c>
       <c r="E16" s="2">
-        <v>1E-22</v>
+        <v>4.0300000000000002E-2</v>
       </c>
       <c r="F16" s="1">
-        <v>13.04</v>
+        <v>668.82</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>1.304E-21</v>
+        <f>E16*F16</f>
+        <v>26.953446000000003</v>
       </c>
       <c r="H16" s="11">
-        <v>-5.2200000000000003E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I16" s="11">
-        <v>0.43780000000000002</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.11923252626770214</v>
+        <f>IFERROR(H16/I16,"")</f>
+        <v>0.17857142857142858</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="2"/>
-        <v>-1.1807967480023001E-2</v>
+        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.29969361003970896</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" si="3"/>
-        <v>12.359312000000001</v>
+        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <v>702.26100000000008</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="4"/>
-        <v>8.7516778523489922</v>
+        <f>F16/(1+I16-H16)</f>
+        <v>543.7560975609756</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" si="5"/>
-        <v>-0.68068799999999818</v>
+        <f>L16-F16</f>
+        <v>33.441000000000031</v>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.1441610738255035</v>
+        <f>0.5*(M16-F16)</f>
+        <v>-62.531951219512223</v>
       </c>
       <c r="P16" s="14">
-        <f t="shared" si="7"/>
-        <v>-2.8248490738255017</v>
+        <f>N16+O16</f>
+        <v>-29.090951219512192</v>
       </c>
       <c r="Q16" s="12">
-        <f t="shared" si="8"/>
-        <v>255.99242525703121</v>
+        <f>MAX($P$2:$P$280)-P16</f>
+        <v>132.71946124816552</v>
       </c>
       <c r="R16" s="9">
-        <f t="shared" si="9"/>
-        <v>3.9063655848251841E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.5346900190481469E-3</v>
       </c>
       <c r="S16" s="9">
-        <f t="shared" si="10"/>
-        <v>0.94180851422887524</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q16/MAX($Q$2:$Q$28)</f>
+        <v>0.60004810959166965</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D17" s="8">
         <v>45511</v>
       </c>
       <c r="E17" s="2">
-        <v>1E-22</v>
+        <v>3.2899999999999999E-2</v>
       </c>
       <c r="F17" s="1">
-        <v>11.05</v>
+        <v>455.4</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1050000000000002E-21</v>
+        <f>E17*F17</f>
+        <v>14.982659999999999</v>
       </c>
       <c r="H17" s="11">
-        <v>-0.1159</v>
+        <v>0.25</v>
       </c>
       <c r="I17" s="11">
-        <v>0.64090000000000003</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.1808394445311281</v>
+        <f>IFERROR(H17/I17,"")</f>
+        <v>0.84175084175084181</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="2"/>
-        <v>-1.7909091981618185E-2</v>
+        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.4126971517023319</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="3"/>
-        <v>9.769305000000001</v>
+        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <v>569.25</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="4"/>
-        <v>6.2898451730418943</v>
+        <f>F17/(1+I17-H17)</f>
+        <v>434.95702005730658</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" si="5"/>
-        <v>-1.2806949999999997</v>
+        <f>L17-F17</f>
+        <v>113.85000000000002</v>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.3800774134790532</v>
+        <f>0.5*(M17-F17)</f>
+        <v>-10.221489971346699</v>
       </c>
       <c r="P17" s="14">
-        <f t="shared" si="7"/>
-        <v>-3.6607724134790529</v>
+        <f>N17+O17</f>
+        <v>103.62851002865332</v>
       </c>
       <c r="Q17" s="12">
-        <f t="shared" si="8"/>
-        <v>256.82834859668475</v>
+        <f>MAX($P$2:$P$280)-P17</f>
+        <v>0</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="9"/>
-        <v>3.8936511699896839E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>0</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="10"/>
-        <v>0.94488391662696514</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q17/MAX($Q$2:$Q$28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>53</v>
+        <v>36</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D18" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E18" s="2">
-        <v>1E-22</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="F18" s="1">
-        <v>10.47</v>
+        <v>700.32</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0470000000000001E-21</v>
+        <f>E18*F18</f>
+        <v>19.959120000000002</v>
       </c>
       <c r="H18" s="11">
-        <v>-0.39269999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="I18" s="11">
-        <v>0.75180000000000002</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.52234636871508378</v>
+        <f>IFERROR(H18/I18,"")</f>
+        <v>0.22055580061755625</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="2"/>
-        <v>-5.1729583597412782E-2</v>
+        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.37015531897273274</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="3"/>
-        <v>6.3584309999999995</v>
+        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <v>770.35200000000009</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="4"/>
-        <v>4.8822569363488002</v>
+        <f>F18/(1+I18-H18)</f>
+        <v>517.45234224915032</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" si="5"/>
-        <v>-4.1115690000000011</v>
+        <f>L18-F18</f>
+        <v>70.032000000000039</v>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.7938715318256002</v>
+        <f>0.5*(M18-F18)</f>
+        <v>-91.433828875424865</v>
       </c>
       <c r="P18" s="14">
-        <f t="shared" si="7"/>
-        <v>-6.9054405318256009</v>
+        <f>N18+O18</f>
+        <v>-21.401828875424826</v>
       </c>
       <c r="Q18" s="12">
-        <f t="shared" si="8"/>
-        <v>260.07301671503132</v>
+        <f>MAX($P$2:$P$280)-P18</f>
+        <v>125.03033890407815</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="9"/>
-        <v>3.8450740204845073E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.9980587812945834E-3</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="10"/>
-        <v>0.95682120757077926</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q18/MAX($Q$2:$Q$28)</f>
+        <v>0.565284230326356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>83</v>
+        <v>36</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
       </c>
       <c r="D19" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45604</v>
+        <v>45482</v>
       </c>
       <c r="E19" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F19" s="1">
-        <v>2742.9</v>
+        <v>147.01</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>2.7429E-32</v>
+        <f>E19*F19</f>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H19" s="11">
-        <v>0.1152</v>
+        <v>0.15</v>
       </c>
       <c r="I19" s="11">
-        <v>0.16320000000000001</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.70588235294117641</v>
+        <f>IFERROR(H19/I19,"")</f>
+        <v>0.28636884306987398</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="2"/>
-        <v>6.99057222820023E-2</v>
+        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.48060830934203036</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" si="3"/>
-        <v>3058.8820799999999</v>
+        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <v>169.06149999999997</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="4"/>
-        <v>2617.270992366412</v>
+        <f>F19/(1+I19-H19)</f>
+        <v>107.00975396709855</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" si="5"/>
-        <v>315.98207999999977</v>
+        <f>L19-F19</f>
+        <v>22.051499999999976</v>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="6"/>
-        <v>-62.814503816794058</v>
+        <f>0.5*(M19-F19)</f>
+        <v>-20.000123016450722</v>
       </c>
       <c r="P19" s="14">
-        <f t="shared" si="7"/>
-        <v>253.16757618320571</v>
+        <f>N19+O19</f>
+        <v>2.0513769835492539</v>
       </c>
       <c r="Q19" s="12">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>MAX($P$2:$P$280)-P19</f>
+        <v>101.57713304510406</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8447354244184312E-3</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>Q19/MAX($Q$2:$Q$28)</f>
+        <v>0.45924814709341422</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>78</v>
+        <v>40</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D20" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E20" s="2">
-        <v>1E-35</v>
+        <v>1E-22</v>
       </c>
       <c r="F20" s="1">
-        <v>20.399999999999999</v>
+        <v>187.36</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0399999999999999E-34</v>
+        <f>E20*F20</f>
+        <v>1.8736000000000003E-20</v>
       </c>
       <c r="H20" s="11">
-        <v>1.5100000000000001E-2</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C20,Sheet1!$G:$G,0),2)</f>
+        <v>0.2823</v>
       </c>
       <c r="I20" s="11">
-        <v>0.1336</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C20,Sheet1!$G:$G,0),3)</f>
+        <v>0.5212</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="1"/>
-        <v>0.11302395209580839</v>
+        <f>IFERROR(H20/I20,"")</f>
+        <v>0.54163468917881807</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="2"/>
-        <v>1.1193113092433878E-2</v>
+        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.90901694980731973</v>
       </c>
       <c r="L20" s="12">
-        <v>21.2</v>
+        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <v>240.25172799999999</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="4"/>
-        <v>18.238712561466247</v>
+        <f>F20/(1+I20-H20)</f>
+        <v>151.230930664299</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="5"/>
-        <v>0.80000000000000071</v>
+        <f>L20-F20</f>
+        <v>52.891727999999972</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.0806437192668756</v>
+        <f>0.5*(M20-F20)</f>
+        <v>-18.064534667850509</v>
       </c>
       <c r="P20" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.28064371926687492</v>
+        <f>N20+O20</f>
+        <v>34.827193332149463</v>
       </c>
       <c r="Q20" s="12">
-        <f t="shared" si="8"/>
-        <v>253.44821990247257</v>
+        <f>MAX($P$2:$P$280)-P20</f>
+        <v>68.801316696503861</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="9"/>
-        <v>3.9455791024486271E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.453460555720462E-2</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="10"/>
-        <v>0.93244825967265488</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q20/MAX($Q$2:$Q$28)</f>
+        <v>0.31106289637478135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>80</v>
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="D21" s="8">
-        <v>45574</v>
+        <v>45481</v>
       </c>
       <c r="E21" s="2">
-        <v>0</v>
+        <v>1E-22</v>
       </c>
       <c r="F21" s="1">
-        <v>153.7552</v>
+        <v>169.34</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E21*F21</f>
+        <v>1.6934000000000002E-20</v>
       </c>
       <c r="H21" s="11">
-        <v>6.3700000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I21" s="11">
-        <v>9.2799999999999994E-2</v>
+        <v>0.4259</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="1"/>
-        <v>0.68642241379310354</v>
+        <f>IFERROR(H21/I21,"")</f>
+        <v>0.23479690068091102</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="2"/>
-        <v>6.7978544054580009E-2</v>
+        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.39405593243070447</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ref="L21:L34" si="11">F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
-        <v>163.54940624000002</v>
+        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <v>186.27400000000003</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="4"/>
-        <v>149.40744339714314</v>
+        <f>F21/(1+I21-H21)</f>
+        <v>127.71702239987934</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" si="5"/>
-        <v>9.7942062400000225</v>
+        <f>L21-F21</f>
+        <v>16.934000000000026</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.1738783014284309</v>
+        <f>0.5*(M21-F21)</f>
+        <v>-20.811488800060332</v>
       </c>
       <c r="P21" s="14">
-        <f t="shared" si="7"/>
-        <v>7.6203279385715916</v>
+        <f>N21+O21</f>
+        <v>-3.8774888000603056</v>
       </c>
       <c r="Q21" s="12">
-        <f t="shared" si="8"/>
-        <v>245.54724824463412</v>
+        <f>MAX($P$2:$P$280)-P21</f>
+        <v>107.50599882871363</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="9"/>
-        <v>4.0725359666980215E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.3018065121488955E-3</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="10"/>
-        <v>0.90338020279338627</v>
+        <f>Q21/MAX($Q$2:$Q$28)</f>
+        <v>0.48605359575949542</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
+        <v>40</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="D22" s="8">
-        <v>45484</v>
+        <v>45511</v>
       </c>
       <c r="E22" s="2">
-        <v>0.33389999999999997</v>
+        <v>1E-22</v>
       </c>
       <c r="F22" s="1">
-        <v>188.53</v>
+        <v>113.58</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
-        <v>62.950166999999993</v>
+        <f>E22*F22</f>
+        <v>1.1358E-20</v>
       </c>
       <c r="H22" s="11">
-        <v>0.2445</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C22,Sheet1!$G:$G,0),2)</f>
+        <v>7.2800000000000004E-2</v>
       </c>
       <c r="I22" s="11">
-        <v>0.3826</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C22,Sheet1!$G:$G,0),3)</f>
+        <v>0.18940000000000001</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="1"/>
-        <v>0.63904861474124408</v>
+        <f>IFERROR(H22/I22,"")</f>
+        <v>0.38437170010559663</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="2"/>
-        <v>6.3286969564632894E-2</v>
+        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.64508495744978112</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" si="11"/>
-        <v>234.625585</v>
+        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <v>121.848624</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="4"/>
-        <v>165.65328178543186</v>
+        <f>F22/(1+I22-H22)</f>
+        <v>101.71950564212788</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="5"/>
-        <v>46.095585</v>
+        <f>L22-F22</f>
+        <v>8.2686240000000026</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="6"/>
-        <v>-11.438359107284072</v>
+        <f>0.5*(M22-F22)</f>
+        <v>-5.9302471789360567</v>
       </c>
       <c r="P22" s="14">
-        <f t="shared" si="7"/>
-        <v>34.657225892715928</v>
+        <f>N22+O22</f>
+        <v>2.338376821063946</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" si="8"/>
-        <v>218.51035029048978</v>
+        <f>MAX($P$2:$P$280)-P22</f>
+        <v>101.29013320758938</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="9"/>
-        <v>4.576442253973737E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8726299229022329E-3</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="10"/>
-        <v>0.80391014751349477</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q22/MAX($Q$2:$Q$28)</f>
+        <v>0.45795057017188207</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D23" s="8">
-        <v>45574</v>
+        <v>45481</v>
       </c>
       <c r="E23" s="2">
-        <v>0.13370000000000001</v>
+        <v>1E-22</v>
       </c>
       <c r="F23" s="1">
-        <v>423.77</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="0"/>
-        <v>56.658049000000005</v>
+        <f>E23*F23</f>
+        <v>6.4349999999999995E-21</v>
       </c>
       <c r="H23" s="11">
-        <v>0.20669999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="I23" s="11">
-        <v>0.30690000000000001</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="1"/>
-        <v>0.67350928641251218</v>
+        <f>IFERROR(H23/I23,"")</f>
+        <v>0.22288261515601782</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="2"/>
-        <v>6.6699716934595379E-2</v>
+        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.37406037508670953</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="11"/>
-        <v>511.36325900000003</v>
+        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <v>74.002499999999984</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="4"/>
-        <v>385.17542265042715</v>
+        <f>F23/(1+I23-H23)</f>
+        <v>42.252133946158892</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="5"/>
-        <v>87.593259000000046</v>
+        <f>L23-F23</f>
+        <v>9.6524999999999892</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="6"/>
-        <v>-19.297288674786415</v>
+        <f>0.5*(M23-F23)</f>
+        <v>-11.048933026920551</v>
       </c>
       <c r="P23" s="14">
-        <f t="shared" si="7"/>
-        <v>68.295970325213631</v>
+        <f>N23+O23</f>
+        <v>-1.3964330269205618</v>
       </c>
       <c r="Q23" s="12">
-        <f t="shared" si="8"/>
-        <v>184.87160585799208</v>
+        <f>MAX($P$2:$P$280)-P23</f>
+        <v>105.02494305557389</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="9"/>
-        <v>5.4091594831936684E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.5215476524548141E-3</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="10"/>
-        <v>0.68015157972507023</v>
+        <f>Q23/MAX($Q$2:$Q$28)</f>
+        <v>0.47483630469710741</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="D24" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E24" s="2">
-        <v>0.18820000000000001</v>
+        <v>1E-22</v>
       </c>
       <c r="F24" s="1">
-        <v>227.38</v>
+        <v>20.82</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="0"/>
-        <v>42.792915999999998</v>
+        <f>E24*F24</f>
+        <v>2.0820000000000001E-21</v>
       </c>
       <c r="H24" s="11">
-        <v>0.23910000000000001</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C24,Sheet1!$G:$G,0),2)</f>
+        <v>-0.1696</v>
       </c>
       <c r="I24" s="11">
-        <v>0.31859999999999999</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C24,Sheet1!$G:$G,0),3)</f>
+        <v>0.70540000000000003</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="1"/>
-        <v>0.75047080979284375</v>
+        <f>IFERROR(H24/I24,"")</f>
+        <v>-0.24043096115679047</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="2"/>
-        <v>7.4321455681014545E-2</v>
+        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-0.40351148720061519</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="11"/>
-        <v>281.74655799999999</v>
+        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <v>17.288928000000002</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="4"/>
-        <v>210.63455303381195</v>
+        <f>F24/(1+I24-H24)</f>
+        <v>11.104000000000001</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="5"/>
-        <v>54.366557999999998</v>
+        <f>L24-F24</f>
+        <v>-3.5310719999999982</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="6"/>
-        <v>-8.3727234830940205</v>
+        <f>0.5*(M24-F24)</f>
+        <v>-4.8579999999999997</v>
       </c>
       <c r="P24" s="14">
-        <f t="shared" si="7"/>
-        <v>45.993834516905977</v>
+        <f>N24+O24</f>
+        <v>-8.3890719999999988</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" si="8"/>
-        <v>207.17374166629975</v>
+        <f>MAX($P$2:$P$280)-P24</f>
+        <v>112.01758202865332</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="9"/>
-        <v>4.8268665322013958E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9271700200081704E-3</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="10"/>
-        <v>0.76220221606191985</v>
+        <f>Q24/MAX($Q$2:$Q$28)</f>
+        <v>0.50645125971118488</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D25" s="8">
-        <v>45544</v>
+        <v>45511</v>
       </c>
       <c r="E25" s="2">
-        <v>0.1928</v>
+        <v>1E-22</v>
       </c>
       <c r="F25" s="1">
-        <v>188.12</v>
+        <v>13.04</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="0"/>
-        <v>36.269536000000002</v>
+        <f>E25*F25</f>
+        <v>1.304E-21</v>
       </c>
       <c r="H25" s="11">
-        <v>0.13730000000000001</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C25,Sheet1!$G:$G,0),2)</f>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="I25" s="11">
-        <v>0.41699999999999998</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C25,Sheet1!$G:$G,0),3)</f>
+        <v>0.39489999999999997</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="1"/>
-        <v>0.32925659472422064</v>
+        <f>IFERROR(H25/I25,"")</f>
+        <v>7.6728285641934679E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="2"/>
-        <v>3.2607303432937967E-2</v>
+        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.12877187073066049</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="11"/>
-        <v>213.94887600000001</v>
+        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <v>13.435111999999998</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="4"/>
-        <v>147.00320387590841</v>
+        <f>F25/(1+I25-H25)</f>
+        <v>9.5559138208998959</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="5"/>
-        <v>25.828876000000008</v>
+        <f>L25-F25</f>
+        <v>0.39511199999999924</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="6"/>
-        <v>-20.558398062045796</v>
+        <f>0.5*(M25-F25)</f>
+        <v>-1.7420430895500516</v>
       </c>
       <c r="P25" s="14">
-        <f t="shared" si="7"/>
-        <v>5.2704779379542117</v>
+        <f>N25+O25</f>
+        <v>-1.3469310895500524</v>
       </c>
       <c r="Q25" s="12">
-        <f t="shared" si="8"/>
-        <v>247.8970982452515</v>
+        <f>MAX($P$2:$P$280)-P25</f>
+        <v>104.97544111820338</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="9"/>
-        <v>4.0339318494590536E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.5260376079200296E-3</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="10"/>
-        <v>0.91202541460197828</v>
+        <f>Q25/MAX($Q$2:$Q$28)</f>
+        <v>0.47461249770105007</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D26" s="8">
-        <v>45483</v>
+        <v>45511</v>
       </c>
       <c r="E26" s="2">
-        <v>0.1195</v>
+        <v>1E-22</v>
       </c>
       <c r="F26" s="1">
-        <v>167.24</v>
+        <v>11.05</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="0"/>
-        <v>19.98518</v>
+        <f>E26*F26</f>
+        <v>1.1050000000000002E-21</v>
       </c>
       <c r="H26" s="11">
-        <v>0.1852</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C26,Sheet1!$G:$G,0),2)</f>
+        <v>-0.32750000000000001</v>
       </c>
       <c r="I26" s="11">
-        <v>0.32479999999999998</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C26,Sheet1!$G:$G,0),3)</f>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="1"/>
-        <v>0.57019704433497542</v>
+        <f>IFERROR(H26/I26,"")</f>
+        <v>-0.51918199112238428</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="2"/>
-        <v>5.6468384655340743E-2</v>
+        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-0.87133494104760023</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="11"/>
-        <v>198.21284800000001</v>
+        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <v>7.4311250000000006</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="4"/>
-        <v>146.75324675324677</v>
+        <f>F26/(1+I26-H26)</f>
+        <v>5.6426492365827512</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="5"/>
-        <v>30.972847999999999</v>
+        <f>L26-F26</f>
+        <v>-3.6188750000000001</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.243376623376619</v>
+        <f>0.5*(M26-F26)</f>
+        <v>-2.7036753817086248</v>
       </c>
       <c r="P26" s="14">
-        <f t="shared" si="7"/>
-        <v>20.72947137662338</v>
+        <f>N26+O26</f>
+        <v>-6.3225503817086253</v>
       </c>
       <c r="Q26" s="12">
-        <f t="shared" si="8"/>
-        <v>232.43810480658232</v>
+        <f>MAX($P$2:$P$280)-P26</f>
+        <v>109.95106041036195</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="9"/>
-        <v>4.3022205882814503E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.0949554853566334E-3</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="10"/>
-        <v>0.85515103002857351</v>
+        <f>Q26/MAX($Q$2:$Q$28)</f>
+        <v>0.49710815072909353</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>62</v>
+        <v>40</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D27" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E27" s="2">
-        <v>2.8500000000000001E-2</v>
+        <v>1E-22</v>
       </c>
       <c r="F27" s="1">
-        <v>700.32</v>
+        <v>10.47</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="0"/>
-        <v>19.959120000000002</v>
+        <f>E27*F27</f>
+        <v>1.0470000000000001E-21</v>
       </c>
       <c r="H27" s="11">
-        <v>0.1714</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C27,Sheet1!$G:$G,0),2)</f>
+        <v>-1.03</v>
       </c>
       <c r="I27" s="11">
-        <v>0.4395</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C27,Sheet1!$G:$G,0),3)</f>
+        <v>0.75839999999999996</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="1"/>
-        <v>0.38998862343572238</v>
+        <f>IFERROR(H27/I27,"")</f>
+        <v>-1.3581223628691985</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="2"/>
-        <v>3.8621784904303812E-2</v>
+        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-2.2793153253020062</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="11"/>
-        <v>820.35484800000006</v>
+        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <v>-0.31410000000000032</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="4"/>
-        <v>552.25928554530401</v>
+        <f>F27/(1+I27-H27)</f>
+        <v>3.7548414861569359</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="5"/>
-        <v>120.03484800000001</v>
+        <f>L27-F27</f>
+        <v>-10.7841</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="6"/>
-        <v>-74.03035722734802</v>
+        <f>0.5*(M27-F27)</f>
+        <v>-3.3575792569215324</v>
       </c>
       <c r="P27" s="14">
-        <f t="shared" si="7"/>
-        <v>46.004490772651991</v>
+        <f>N27+O27</f>
+        <v>-14.141679256921533</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" si="8"/>
-        <v>207.16308541055372</v>
+        <f>MAX($P$2:$P$280)-P27</f>
+        <v>117.77018928557486</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="9"/>
-        <v>4.8271148212443828E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.4911131251997202E-3</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="10"/>
-        <v>0.762163011181614</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q27/MAX($Q$2:$Q$28)</f>
+        <v>0.53245981246807605</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" t="s">
-        <v>24</v>
+        <v>77</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="D28" s="8">
-        <v>45482</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45610</v>
       </c>
       <c r="E28" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>1E-35</v>
       </c>
       <c r="F28" s="1">
-        <v>147.01</v>
+        <v>2742.9</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="0"/>
-        <v>1.4700999999999999E-17</v>
+        <f>E28*F28</f>
+        <v>2.7429E-32</v>
       </c>
       <c r="H28" s="11">
-        <v>0.63670000000000004</v>
+        <v>0.1</v>
       </c>
       <c r="I28" s="11">
-        <v>0.53810000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="1"/>
-        <v>1.1832373164839249</v>
+        <f>IFERROR(H28/I28,"")</f>
+        <v>0.2</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="2"/>
-        <v>0.11717966725642148</v>
+        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.33565684324447403</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="11"/>
-        <v>240.61126700000003</v>
+        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <v>3017.1900000000005</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="4"/>
-        <v>163.09074772575991</v>
+        <f>F28/(1+I28-H28)</f>
+        <v>1959.214285714286</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="5"/>
-        <v>93.601267000000036</v>
+        <f>L28-F28</f>
+        <v>274.29000000000042</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="6"/>
-        <v>8.0403738628799601</v>
+        <f>0.5*(M28-F28)</f>
+        <v>-391.84285714285704</v>
       </c>
       <c r="P28" s="14">
-        <f t="shared" si="7"/>
-        <v>101.64164086288</v>
+        <f>N28+O28</f>
+        <v>-117.55285714285662</v>
       </c>
       <c r="Q28" s="12">
-        <f t="shared" si="8"/>
-        <v>151.52593532032571</v>
+        <f>MAX($P$2:$P$280)-P28</f>
+        <v>221.18136717150995</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="9"/>
-        <v>6.5995302908772729E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>4.5211765022890611E-3</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="10"/>
-        <v>0.55747124497097555</v>
+        <f>Q28/MAX($Q$2:$Q$28)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D29" s="8">
-        <v>45481</v>
+        <v>45505</v>
       </c>
       <c r="E29" s="2">
-        <v>1E-22</v>
+        <v>1E-35</v>
       </c>
       <c r="F29" s="1">
-        <v>169.34</v>
+        <v>86.6</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="0"/>
-        <v>1.6934000000000002E-20</v>
+        <f>E29*F29</f>
+        <v>8.6599999999999988E-34</v>
       </c>
       <c r="H29" s="11">
-        <v>0.21629999999999999</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C29,Sheet1!$G:$G,0),2)</f>
+        <v>0.2447</v>
       </c>
       <c r="I29" s="11">
-        <v>0.47220000000000001</v>
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C29,Sheet1!$G:$G,0),3)</f>
+        <v>0.20810000000000001</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="1"/>
-        <v>0.45806861499364676</v>
+        <f>IFERROR(H29/I29,"")</f>
+        <v>1.1758769822200865</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="2"/>
-        <v>4.5363957963283685E-2</v>
+        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.9734557794791638</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="11"/>
-        <v>205.968242</v>
+        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <v>107.79101999999999</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="4"/>
-        <v>134.83557608089816</v>
+        <f>F29/(1+I29-H29)</f>
+        <v>89.889973012248291</v>
       </c>
       <c r="N29" s="12">
-        <f t="shared" si="5"/>
-        <v>36.628242</v>
+        <f>L29-F29</f>
+        <v>21.191019999999995</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="6"/>
-        <v>-17.25221195955092</v>
+        <f>0.5*(M29-F29)</f>
+        <v>1.6449865061241482</v>
       </c>
       <c r="P29" s="14">
-        <f t="shared" si="7"/>
-        <v>19.376030040449081</v>
+        <f>N29+O29</f>
+        <v>22.836006506124143</v>
       </c>
       <c r="Q29" s="12">
-        <f t="shared" si="8"/>
-        <v>233.79154614275663</v>
+        <f>MAX($P$2:$P$280)-P29</f>
+        <v>80.792503522529188</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="9"/>
-        <v>4.2773146270626275E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.237738597518701E-2</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="10"/>
-        <v>0.86013040616690428</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q29/MAX($Q$2:$Q$28)</f>
+        <v>0.36527716848716518</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D30" s="8">
-        <v>45481</v>
+        <v>45562</v>
       </c>
       <c r="E30" s="2">
-        <v>1E-22</v>
+        <v>1E-35</v>
       </c>
       <c r="F30" s="1">
-        <v>64.349999999999994</v>
+        <v>56</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="0"/>
-        <v>6.4349999999999995E-21</v>
+        <f>E30*F30</f>
+        <v>5.5999999999999999E-34</v>
       </c>
       <c r="H30" s="11">
-        <v>0.4667</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I30" s="11">
-        <v>0.70420000000000005</v>
+        <v>0.19</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="1"/>
-        <v>0.66273785856290823</v>
+        <f>IFERROR(H30/I30,"")</f>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="2"/>
-        <v>6.563298897249574E-2</v>
+        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.61831523755561013</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" si="11"/>
-        <v>94.38214499999998</v>
+        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
+        <v>59.92</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="4"/>
-        <v>51.999999999999986</v>
+        <f>F30/(1+I30-H30)</f>
+        <v>50.000000000000007</v>
       </c>
       <c r="N30" s="12">
-        <f t="shared" si="5"/>
-        <v>30.032144999999986</v>
+        <f>L30-F30</f>
+        <v>3.9200000000000017</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="6"/>
-        <v>-6.1750000000000043</v>
+        <f>0.5*(M30-F30)</f>
+        <v>-2.9999999999999964</v>
       </c>
       <c r="P30" s="14">
-        <f t="shared" si="7"/>
-        <v>23.857144999999981</v>
+        <f>N30+O30</f>
+        <v>0.92000000000000526</v>
       </c>
       <c r="Q30" s="12">
-        <f t="shared" si="8"/>
-        <v>229.31043118320574</v>
+        <f>MAX($P$2:$P$280)-P30</f>
+        <v>102.70851002865332</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="9"/>
-        <v>4.3609006133744433E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.7362915665023565E-3</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" si="10"/>
-        <v>0.84364416749048277</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q30/MAX($Q$2:$Q$28)</f>
+        <v>0.46436330212666782</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="8">
+        <v>45580</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1E-35</v>
+      </c>
+      <c r="F31" s="1">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="G31" s="1">
+        <f>E31*F31</f>
+        <v>2.0399999999999999E-34</v>
+      </c>
+      <c r="H31" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="I31" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="J31" s="9">
+        <f>IFERROR(H31/I31,"")</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="K31" s="9">
+        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.118856144148247</v>
+      </c>
+      <c r="L31" s="12">
+        <v>21.2</v>
+      </c>
+      <c r="M31" s="12">
+        <f>F31/(1+I31-H31)</f>
+        <v>19.428571428571431</v>
+      </c>
+      <c r="N31" s="12">
+        <f>L31-F31</f>
+        <v>0.80000000000000071</v>
+      </c>
+      <c r="O31" s="12">
+        <f>0.5*(M31-F31)</f>
+        <v>-0.48571428571428399</v>
+      </c>
+      <c r="P31" s="14">
+        <f>N31+O31</f>
+        <v>0.31428571428571672</v>
+      </c>
+      <c r="Q31" s="12">
+        <f>MAX($P$2:$P$280)-P31</f>
+        <v>103.31422431436761</v>
+      </c>
+      <c r="R31" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.6792092921993977E-3</v>
+      </c>
+      <c r="S31" s="9">
+        <f>Q31/MAX($Q$2:$Q$28)</f>
+        <v>0.46710184332234006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="8">
+        <v>45574</v>
+      </c>
+      <c r="E32" s="2">
+        <v>9.9999999999999998E-46</v>
+      </c>
+      <c r="F32" s="1">
+        <v>47.42</v>
+      </c>
+      <c r="G32" s="1">
+        <f>E32*F32</f>
+        <v>4.7420000000000006E-44</v>
+      </c>
+      <c r="H32" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I32" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="J32" s="9">
+        <f>IFERROR(H32/I32,"")</f>
+        <v>0.17500000000000002</v>
+      </c>
+      <c r="K32" s="9">
+        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.29369973783891479</v>
+      </c>
+      <c r="L32" s="12">
+        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
+        <v>50.739400000000003</v>
+      </c>
+      <c r="M32" s="12">
+        <f>F32/(1+I32-H32)</f>
+        <v>35.654135338345867</v>
+      </c>
+      <c r="N32" s="12">
+        <f>L32-F32</f>
+        <v>3.3194000000000017</v>
+      </c>
+      <c r="O32" s="12">
+        <f>0.5*(M32-F32)</f>
+        <v>-5.8829323308270673</v>
+      </c>
+      <c r="P32" s="14">
+        <f>N32+O32</f>
+        <v>-2.5635323308270657</v>
+      </c>
+      <c r="Q32" s="12">
+        <f>MAX($P$2:$P$280)-P32</f>
+        <v>106.19204235948038</v>
+      </c>
+      <c r="R32" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.4169014719088714E-3</v>
+      </c>
+      <c r="S32" s="9">
+        <f>Q32/MAX($Q$2:$Q$28)</f>
+        <v>0.48011296664576736</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="8">
+        <v>45507</v>
+      </c>
+      <c r="E33" s="2">
+        <v>9.9999999999999998E-46</v>
+      </c>
+      <c r="F33" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="G33" s="1">
+        <f>E33*F33</f>
+        <v>4.1799999999999994E-44</v>
+      </c>
+      <c r="H33" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I33" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="J33" s="9">
+        <f>IFERROR(H33/I33,"")</f>
+        <v>0.17500000000000002</v>
+      </c>
+      <c r="K33" s="9">
+        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.29369973783891479</v>
+      </c>
+      <c r="L33" s="12">
+        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
+        <v>44.725999999999999</v>
+      </c>
+      <c r="M33" s="12">
+        <f>F33/(1+I33-H33)</f>
+        <v>31.428571428571431</v>
+      </c>
+      <c r="N33" s="12">
+        <f>L33-F33</f>
+        <v>2.9260000000000019</v>
+      </c>
+      <c r="O33" s="12">
+        <f>0.5*(M33-F33)</f>
+        <v>-5.1857142857142833</v>
+      </c>
+      <c r="P33" s="14">
+        <f>N33+O33</f>
+        <v>-2.2597142857142813</v>
+      </c>
+      <c r="Q33" s="12">
+        <f>MAX($P$2:$P$280)-P33</f>
+        <v>105.8882243143676</v>
+      </c>
+      <c r="R33" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.4439207614922058E-3</v>
+      </c>
+      <c r="S33" s="9">
+        <f>Q33/MAX($Q$2:$Q$28)</f>
+        <v>0.47873935163923209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="8">
+        <v>45574</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1">
+        <v>153.7552</v>
+      </c>
+      <c r="G34" s="1">
+        <f>E34*F34</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I34" s="11">
+        <v>0.19</v>
+      </c>
+      <c r="J34" s="9">
+        <f>IFERROR(H34/I34,"")</f>
+        <v>0.36842105263157898</v>
+      </c>
+      <c r="K34" s="9">
+        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.61831523755561013</v>
+      </c>
+      <c r="L34" s="12">
+        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <v>164.51806400000001</v>
+      </c>
+      <c r="M34" s="12">
+        <f>F34/(1+I34-H34)</f>
+        <v>137.28142857142859</v>
+      </c>
+      <c r="N34" s="12">
+        <f>L34-F34</f>
+        <v>10.762864000000008</v>
+      </c>
+      <c r="O34" s="12">
+        <f>0.5*(M34-F34)</f>
+        <v>-8.2368857142857053</v>
+      </c>
+      <c r="P34" s="14">
+        <f>N34+O34</f>
+        <v>2.5259782857143023</v>
+      </c>
+      <c r="Q34" s="12">
+        <f>MAX($P$2:$P$280)-P34</f>
+        <v>101.10253174293902</v>
+      </c>
+      <c r="R34" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8909491459875324E-3</v>
+      </c>
+      <c r="S34" s="9">
+        <f>Q34/MAX($Q$2:$Q$28)</f>
+        <v>0.45710239083810988</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1">
+        <v>133.53</v>
+      </c>
+      <c r="G35" s="1">
+        <f>E35*F35</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C35,Sheet1!$G:$G,0),2)</f>
+        <v>1.4E-3</v>
+      </c>
+      <c r="I35" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C35,Sheet1!$G:$G,0),3)</f>
+        <v>0.29289999999999999</v>
+      </c>
+      <c r="J35" s="9">
+        <f>IFERROR(H35/I35,"")</f>
+        <v>4.7797883236599522E-3</v>
+      </c>
+      <c r="K35" s="9">
+        <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>8.0218433004824799E-3</v>
+      </c>
+      <c r="L35" s="12">
+        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
+        <v>133.71694200000002</v>
+      </c>
+      <c r="M35" s="12">
+        <f>F35/(1+I35-H35)</f>
+        <v>103.39140534262486</v>
+      </c>
+      <c r="N35" s="12">
+        <f>L35-F35</f>
+        <v>0.18694200000001615</v>
+      </c>
+      <c r="O35" s="12">
+        <f>0.5*(M35-F35)</f>
+        <v>-15.069297328687568</v>
+      </c>
+      <c r="P35" s="14">
+        <f>N35+O35</f>
+        <v>-14.882355328687552</v>
+      </c>
+      <c r="Q35" s="12">
+        <f>MAX($P$2:$P$280)-P35</f>
+        <v>118.51086535734088</v>
+      </c>
+      <c r="R35" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q35)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.4380448744909731E-3</v>
+      </c>
+      <c r="S35" s="9">
+        <f>Q35/MAX($Q$2:$Q$28)</f>
+        <v>0.53580853971955233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1">
+        <v>39.56</v>
+      </c>
+      <c r="G36" s="1">
+        <f>E36*F36</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C36,Sheet1!$G:$G,0),2)</f>
+        <v>1.2E-2</v>
+      </c>
+      <c r="I36" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C36,Sheet1!$G:$G,0),3)</f>
+        <v>0.22159999999999999</v>
+      </c>
+      <c r="J36" s="9">
+        <f>IFERROR(H36/I36,"")</f>
+        <v>5.4151624548736468E-2</v>
+      </c>
+      <c r="K36" s="9">
+        <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.088181676294424E-2</v>
+      </c>
+      <c r="L36" s="12">
+        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
+        <v>40.03472</v>
+      </c>
+      <c r="M36" s="12">
+        <f>F36/(1+I36-H36)</f>
+        <v>32.705026455026456</v>
+      </c>
+      <c r="N36" s="12">
+        <f>L36-F36</f>
+        <v>0.47471999999999781</v>
+      </c>
+      <c r="O36" s="12">
+        <f>0.5*(M36-F36)</f>
+        <v>-3.4274867724867732</v>
+      </c>
+      <c r="P36" s="14">
+        <f>N36+O36</f>
+        <v>-2.9527667724867754</v>
+      </c>
+      <c r="Q36" s="12">
+        <f>MAX($P$2:$P$280)-P36</f>
+        <v>106.58127680114009</v>
+      </c>
+      <c r="R36" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.3825109814156676E-3</v>
+      </c>
+      <c r="S36" s="9">
+        <f>Q36/MAX($Q$2:$Q$28)</f>
+        <v>0.48187276425728087</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1">
+        <v>26.63</v>
+      </c>
+      <c r="G37" s="1">
+        <f>E37*F37</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C37,Sheet1!$G:$G,0),2)</f>
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="I37" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C37,Sheet1!$G:$G,0),3)</f>
+        <v>0.26369999999999999</v>
+      </c>
+      <c r="J37" s="9">
+        <f>IFERROR(H37/I37,"")</f>
+        <v>0.6788016685627607</v>
+      </c>
+      <c r="K37" s="9">
+        <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1392221262942899</v>
+      </c>
+      <c r="L37" s="12">
+        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
+        <v>31.396769999999997</v>
+      </c>
+      <c r="M37" s="12">
+        <f>F37/(1+I37-H37)</f>
+        <v>24.550566977044344</v>
+      </c>
+      <c r="N37" s="12">
+        <f>L37-F37</f>
+        <v>4.7667699999999975</v>
+      </c>
+      <c r="O37" s="12">
+        <f>0.5*(M37-F37)</f>
+        <v>-1.0397165114778275</v>
+      </c>
+      <c r="P37" s="14">
+        <f>N37+O37</f>
+        <v>3.72705348852217</v>
+      </c>
+      <c r="Q37" s="12">
+        <f>MAX($P$2:$P$280)-P37</f>
+        <v>99.90145654013115</v>
+      </c>
+      <c r="R37" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0009864066379178E-2</v>
+      </c>
+      <c r="S37" s="9">
+        <f>Q37/MAX($Q$2:$Q$28)</f>
+        <v>0.45167211785369282</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>22.65</v>
+      </c>
+      <c r="G38" s="1">
+        <f>E38*F38</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C38,Sheet1!$G:$G,0),2)</f>
+        <v>-5.4899999999999997E-2</v>
+      </c>
+      <c r="I38" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C38,Sheet1!$G:$G,0),3)</f>
+        <v>0.45929999999999999</v>
+      </c>
+      <c r="J38" s="9">
+        <f>IFERROR(H38/I38,"")</f>
+        <v>-0.11952971913781842</v>
+      </c>
+      <c r="K38" s="9">
+        <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-0.20060484099849363</v>
+      </c>
+      <c r="L38" s="12">
+        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
+        <v>21.406514999999999</v>
+      </c>
+      <c r="M38" s="12">
+        <f>F38/(1+I38-H38)</f>
+        <v>14.958393871351207</v>
+      </c>
+      <c r="N38" s="12">
+        <f>L38-F38</f>
+        <v>-1.2434849999999997</v>
+      </c>
+      <c r="O38" s="12">
+        <f>0.5*(M38-F38)</f>
+        <v>-3.8458030643243957</v>
+      </c>
+      <c r="P38" s="14">
+        <f>N38+O38</f>
+        <v>-5.0892880643243954</v>
+      </c>
+      <c r="Q38" s="12">
+        <f>MAX($P$2:$P$280)-P38</f>
+        <v>108.71779809297772</v>
+      </c>
+      <c r="R38" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.1981259512336627E-3</v>
+      </c>
+      <c r="S38" s="9">
+        <f>Q38/MAX($Q$2:$Q$28)</f>
+        <v>0.49153235411857737</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="8">
+        <v>45630</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>59.17</v>
+      </c>
+      <c r="G39" s="1">
+        <f>E39*F39</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C39,Sheet1!$G:$G,0),2)</f>
+        <v>0.18379999999999999</v>
+      </c>
+      <c r="I39" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C39,Sheet1!$G:$G,0),3)</f>
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="J39" s="9">
+        <f>IFERROR(H39/I39,"")</f>
+        <v>0.33681509987172442</v>
+      </c>
+      <c r="K39" s="9">
+        <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.56527146590007638</v>
+      </c>
+      <c r="L39" s="12">
+        <f>F39/(1-(F39*(1+H39)-F39)/(F39*(1+H39)))</f>
+        <v>70.045445999999998</v>
+      </c>
+      <c r="M39" s="12">
+        <f>F39/(1+I39-H39)</f>
+        <v>43.446655407886041</v>
+      </c>
+      <c r="N39" s="12">
+        <f>L39-F39</f>
+        <v>10.875445999999997</v>
+      </c>
+      <c r="O39" s="12">
+        <f>0.5*(M39-F39)</f>
+        <v>-7.8616722960569803</v>
+      </c>
+      <c r="P39" s="14">
+        <f>N39+O39</f>
+        <v>3.0137737039430164</v>
+      </c>
+      <c r="Q39" s="12">
+        <f>MAX($P$2:$P$280)-P39</f>
+        <v>100.61473632471031</v>
+      </c>
+      <c r="R39" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q39)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.9389019593783563E-3</v>
+      </c>
+      <c r="S39" s="9">
+        <f>Q39/MAX($Q$2:$Q$28)</f>
+        <v>0.45489698165528991</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="8">
-        <v>45553</v>
-      </c>
-      <c r="E31" s="2">
-        <v>1.0751999999999999</v>
-      </c>
-      <c r="F31" s="1">
-        <v>51.15</v>
-      </c>
-      <c r="G31" s="1">
-        <f t="shared" si="0"/>
-        <v>54.996479999999998</v>
-      </c>
-      <c r="H31" s="11">
-        <v>0.11169999999999999</v>
-      </c>
-      <c r="I31" s="11">
-        <v>0.2477</v>
-      </c>
-      <c r="J31" s="9">
-        <f t="shared" si="1"/>
-        <v>0.45094872830036331</v>
-      </c>
-      <c r="K31" s="9">
-        <f t="shared" si="2"/>
-        <v>4.4658853465648692E-2</v>
-      </c>
-      <c r="L31" s="12">
-        <f t="shared" si="11"/>
-        <v>56.863454999999995</v>
-      </c>
-      <c r="M31" s="12">
-        <f t="shared" si="4"/>
-        <v>45.026408450704217</v>
-      </c>
-      <c r="N31" s="12">
-        <f t="shared" si="5"/>
-        <v>5.7134549999999962</v>
-      </c>
-      <c r="O31" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.0617957746478908</v>
-      </c>
-      <c r="P31" s="14">
-        <f t="shared" si="7"/>
-        <v>2.6516592253521054</v>
-      </c>
-      <c r="Q31" s="12">
-        <f t="shared" si="8"/>
-        <v>250.51591695785362</v>
-      </c>
-      <c r="R31" s="9">
-        <f t="shared" si="9"/>
-        <v>3.9917623284920385E-3</v>
-      </c>
-      <c r="S31" s="9">
-        <f t="shared" si="10"/>
-        <v>0.92166017531130062</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="8">
-        <v>45544</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0.24390000000000001</v>
-      </c>
-      <c r="F32" s="1">
-        <v>144.28</v>
-      </c>
-      <c r="G32" s="1">
-        <f t="shared" si="0"/>
-        <v>35.189892</v>
-      </c>
-      <c r="H32" s="11">
-        <v>3.8300000000000001E-2</v>
-      </c>
-      <c r="I32" s="11">
-        <v>0.2152</v>
-      </c>
-      <c r="J32" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17797397769516729</v>
-      </c>
-      <c r="K32" s="9">
-        <f t="shared" si="2"/>
-        <v>1.7625315899090652E-2</v>
-      </c>
-      <c r="L32" s="12">
-        <f t="shared" si="11"/>
-        <v>149.805924</v>
-      </c>
-      <c r="M32" s="12">
-        <f t="shared" si="4"/>
-        <v>122.59325346248619</v>
-      </c>
-      <c r="N32" s="12">
-        <f t="shared" si="5"/>
-        <v>5.5259240000000034</v>
-      </c>
-      <c r="O32" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.843373268756906</v>
-      </c>
-      <c r="P32" s="14">
-        <f t="shared" si="7"/>
-        <v>-5.3174492687569028</v>
-      </c>
-      <c r="Q32" s="12">
-        <f t="shared" si="8"/>
-        <v>258.4850254519626</v>
-      </c>
-      <c r="R32" s="9">
-        <f t="shared" si="9"/>
-        <v>3.868696061798915E-3</v>
-      </c>
-      <c r="S32" s="9">
-        <f t="shared" si="10"/>
-        <v>0.95097891090681541</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="8">
-        <v>45460</v>
-      </c>
-      <c r="E33" s="2">
-        <v>0.1807</v>
-      </c>
-      <c r="F33" s="1">
-        <v>165.59</v>
-      </c>
-      <c r="G33" s="1">
-        <f t="shared" si="0"/>
-        <v>29.922113</v>
-      </c>
-      <c r="H33" s="11">
-        <v>6.4500000000000002E-2</v>
-      </c>
-      <c r="I33" s="11">
-        <v>0.22189999999999999</v>
-      </c>
-      <c r="J33" s="9">
-        <f t="shared" si="1"/>
-        <v>0.29067147363677337</v>
-      </c>
-      <c r="K33" s="9">
-        <f t="shared" si="2"/>
-        <v>2.8786099024416232E-2</v>
-      </c>
-      <c r="L33" s="12">
-        <f t="shared" si="11"/>
-        <v>176.270555</v>
-      </c>
-      <c r="M33" s="12">
-        <f t="shared" si="4"/>
-        <v>143.07067565232418</v>
-      </c>
-      <c r="N33" s="12">
-        <f t="shared" si="5"/>
-        <v>10.680554999999998</v>
-      </c>
-      <c r="O33" s="12">
-        <f t="shared" si="6"/>
-        <v>-11.25966217383791</v>
-      </c>
-      <c r="P33" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.57910717383791166</v>
-      </c>
-      <c r="Q33" s="12">
-        <f t="shared" si="8"/>
-        <v>253.74668335704362</v>
-      </c>
-      <c r="R33" s="9">
-        <f t="shared" si="9"/>
-        <v>3.9409382095958794E-3</v>
-      </c>
-      <c r="S33" s="9">
-        <f t="shared" si="10"/>
-        <v>0.93354632115794667</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="8">
-        <v>45505</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1E-35</v>
-      </c>
-      <c r="F34" s="1">
-        <v>86.6</v>
-      </c>
-      <c r="G34" s="1">
-        <f t="shared" si="0"/>
-        <v>8.6599999999999988E-34</v>
-      </c>
-      <c r="H34" s="11">
-        <v>0.18629999999999999</v>
-      </c>
-      <c r="I34" s="11">
-        <v>0.22650000000000001</v>
-      </c>
-      <c r="J34" s="9">
-        <f t="shared" si="1"/>
-        <v>0.82251655629139064</v>
-      </c>
-      <c r="K34" s="9">
-        <f t="shared" si="2"/>
-        <v>8.1456369771644402E-2</v>
-      </c>
-      <c r="L34" s="12">
-        <f t="shared" si="11"/>
-        <v>102.73357999999999</v>
-      </c>
-      <c r="M34" s="12">
-        <f t="shared" si="4"/>
-        <v>83.253220534512593</v>
-      </c>
-      <c r="N34" s="12">
-        <f t="shared" si="5"/>
-        <v>16.133579999999995</v>
-      </c>
-      <c r="O34" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.6733897327437006</v>
-      </c>
-      <c r="P34" s="14">
-        <f t="shared" si="7"/>
-        <v>14.460190267256294</v>
-      </c>
-      <c r="Q34" s="12">
-        <f t="shared" si="8"/>
-        <v>238.70738591594943</v>
-      </c>
-      <c r="R34" s="9">
-        <f t="shared" si="9"/>
-        <v>4.1892294038698369E-3</v>
-      </c>
-      <c r="S34" s="9">
-        <f t="shared" si="10"/>
-        <v>0.87821601845925767</v>
+      <c r="B40" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="8">
+        <v>45630</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="G40" s="1">
+        <f>E40*F40</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C40,Sheet1!$G:$G,0),2)</f>
+        <v>-2.3E-2</v>
+      </c>
+      <c r="I40" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C40,Sheet1!$G:$G,0),3)</f>
+        <v>0.25559999999999999</v>
+      </c>
+      <c r="J40" s="9">
+        <f>IFERROR(H40/I40,"")</f>
+        <v>-8.9984350547730824E-2</v>
+      </c>
+      <c r="K40" s="9">
+        <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-0.15101931523127743</v>
+      </c>
+      <c r="L40" s="12">
+        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
+        <v>18.865869999999994</v>
+      </c>
+      <c r="M40" s="12">
+        <f>F40/(1+I40-H40)</f>
+        <v>15.102455811043328</v>
+      </c>
+      <c r="N40" s="12">
+        <f>L40-F40</f>
+        <v>-0.4441300000000048</v>
+      </c>
+      <c r="O40" s="12">
+        <f>0.5*(M40-F40)</f>
+        <v>-2.1037720944783356</v>
+      </c>
+      <c r="P40" s="14">
+        <f>N40+O40</f>
+        <v>-2.5479020944783404</v>
+      </c>
+      <c r="Q40" s="12">
+        <f>MAX($P$2:$P$280)-P40</f>
+        <v>106.17641212313167</v>
+      </c>
+      <c r="R40" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q40)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.4182877345705615E-3</v>
+      </c>
+      <c r="S40" s="9">
+        <f>Q40/MAX($Q$2:$Q$28)</f>
+        <v>0.48004229958846234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="8">
+        <v>45630</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>323.75</v>
+      </c>
+      <c r="G41" s="1">
+        <f>E41*F41</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C41,Sheet1!$G:$G,0),2)</f>
+        <v>9.2100000000000001E-2</v>
+      </c>
+      <c r="I41" s="11">
+        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C41,Sheet1!$G:$G,0),3)</f>
+        <v>0.31609999999999999</v>
+      </c>
+      <c r="J41" s="9">
+        <f>IFERROR(H41/I41,"")</f>
+        <v>0.29136349256564381</v>
+      </c>
+      <c r="K41" s="9">
+        <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.48899075075634391</v>
+      </c>
+      <c r="L41" s="12">
+        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
+        <v>353.56737500000003</v>
+      </c>
+      <c r="M41" s="12">
+        <f>F41/(1+I41-H41)</f>
+        <v>264.50163398692808</v>
+      </c>
+      <c r="N41" s="12">
+        <f>L41-F41</f>
+        <v>29.817375000000027</v>
+      </c>
+      <c r="O41" s="12">
+        <f>0.5*(M41-F41)</f>
+        <v>-29.624183006535958</v>
+      </c>
+      <c r="P41" s="14">
+        <f>N41+O41</f>
+        <v>0.1931919934640689</v>
+      </c>
+      <c r="Q41" s="12">
+        <f>MAX($P$2:$P$280)-P41</f>
+        <v>103.43531803518925</v>
+      </c>
+      <c r="R41" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q41)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.667877655287864E-3</v>
+      </c>
+      <c r="S41" s="9">
+        <f>Q41/MAX($Q$2:$Q$28)</f>
+        <v>0.46764932940749365</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S34" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="R2:R34">
-    <cfRule type="iconSet" priority="3">
+  <autoFilter ref="A1:S41" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Energy"/>
+        <filter val="Health"/>
+        <filter val="Industrials"/>
+        <filter val="US Consumer"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="R2:R41">
+    <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -3125,7 +3796,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{2048185B-3E19-4351-A3A9-6DB74B32B9C2}">
+          <x14:cfRule type="iconSet" priority="2" id="{3E3ADDBA-BC7C-4D57-B9DE-7F1FC69F757B}">
             <x14:iconSet iconSet="5Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -3149,7 +3820,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>S2:S34</xm:sqref>
+          <xm:sqref>S2:S41</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3158,10 +3829,768 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A09BB01-2590-4471-B7D1-AC4B730D30F2}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E05E8D-08B7-4DF5-A194-73864790DB1A}">
+  <dimension ref="B1:E20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="19">
+        <v>0.26719999999999999</v>
+      </c>
+      <c r="E2" s="19">
+        <v>0.16900000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="19">
+        <v>5.3100000000000001E-2</v>
+      </c>
+      <c r="E3" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0.17</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3.6200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0.24390000000000001</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0.16639999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.26579999999999998</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0.28539999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19">
+        <v>0.1351</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="19">
+        <v>0</v>
+      </c>
+      <c r="E9" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="19">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0</v>
+      </c>
+      <c r="E11" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0</v>
+      </c>
+      <c r="E13" s="19">
+        <v>9.6100000000000005E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="19">
+        <v>0</v>
+      </c>
+      <c r="E14" s="19">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="19">
+        <v>0</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="19">
+        <v>0</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="19">
+        <v>0</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="19">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19">
+        <v>7.4399999999999994E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="19">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19">
+        <v>3.5400000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A09BB01-2590-4471-B7D1-AC4B730D30F2}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2">
+        <v>1.4E-3</v>
+      </c>
+      <c r="C2">
+        <v>0.29289999999999999</v>
+      </c>
+      <c r="D2">
+        <v>1E-4</v>
+      </c>
+      <c r="E2">
+        <v>8.4500000000000006E-2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3">
+        <v>0.18379999999999999</v>
+      </c>
+      <c r="C3">
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="D3">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="E3">
+        <v>0.1575</v>
+      </c>
+      <c r="F3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4">
+        <v>9.2100000000000001E-2</v>
+      </c>
+      <c r="C4">
+        <v>0.31609999999999999</v>
+      </c>
+      <c r="D4">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="E4">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5">
+        <v>-1.7947</v>
+      </c>
+      <c r="C5">
+        <v>1.4319</v>
+      </c>
+      <c r="D5">
+        <v>-0.14960000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.41339999999999999</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6">
+        <v>-3.8800000000000001E-2</v>
+      </c>
+      <c r="C6">
+        <v>0.28689999999999999</v>
+      </c>
+      <c r="D6">
+        <v>-3.2000000000000002E-3</v>
+      </c>
+      <c r="E6">
+        <v>8.2799999999999999E-2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7">
+        <v>0.2823</v>
+      </c>
+      <c r="C7">
+        <v>0.5212</v>
+      </c>
+      <c r="D7">
+        <v>2.35E-2</v>
+      </c>
+      <c r="E7">
+        <v>0.15049999999999999</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8">
+        <v>7.2800000000000004E-2</v>
+      </c>
+      <c r="C8">
+        <v>0.18940000000000001</v>
+      </c>
+      <c r="D8">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="E8">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9">
+        <v>-0.1696</v>
+      </c>
+      <c r="C9">
+        <v>0.70540000000000003</v>
+      </c>
+      <c r="D9">
+        <v>-1.41E-2</v>
+      </c>
+      <c r="E9">
+        <v>0.2036</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C10">
+        <v>0.39489999999999997</v>
+      </c>
+      <c r="D10">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E10">
+        <v>0.114</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11">
+        <v>-0.32750000000000001</v>
+      </c>
+      <c r="C11">
+        <v>0.63080000000000003</v>
+      </c>
+      <c r="D11">
+        <v>-2.7300000000000001E-2</v>
+      </c>
+      <c r="E11">
+        <v>0.18210000000000001</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12">
+        <v>-1.03</v>
+      </c>
+      <c r="C12">
+        <v>0.75839999999999996</v>
+      </c>
+      <c r="D12">
+        <v>-8.5800000000000001E-2</v>
+      </c>
+      <c r="E12">
+        <v>0.21890000000000001</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13">
+        <v>1.2E-2</v>
+      </c>
+      <c r="C13">
+        <v>0.22159999999999999</v>
+      </c>
+      <c r="D13">
+        <v>1E-3</v>
+      </c>
+      <c r="E13">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="C14">
+        <v>0.26369999999999999</v>
+      </c>
+      <c r="D14">
+        <v>1.49E-2</v>
+      </c>
+      <c r="E14">
+        <v>7.6100000000000001E-2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15">
+        <v>-5.4899999999999997E-2</v>
+      </c>
+      <c r="C15">
+        <v>0.45929999999999999</v>
+      </c>
+      <c r="D15">
+        <v>-4.5999999999999999E-3</v>
+      </c>
+      <c r="E15">
+        <v>0.1326</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16">
+        <v>0.1346</v>
+      </c>
+      <c r="C16">
+        <v>0.20530000000000001</v>
+      </c>
+      <c r="D16">
+        <v>1.12E-2</v>
+      </c>
+      <c r="E16">
+        <v>5.9299999999999999E-2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="C17">
+        <v>0.1867</v>
+      </c>
+      <c r="D17">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="E17">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C18">
+        <v>0.1711</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>4.9399999999999999E-2</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19">
+        <v>0.2447</v>
+      </c>
+      <c r="C19">
+        <v>0.20810000000000001</v>
+      </c>
+      <c r="D19">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="E19">
+        <v>6.0100000000000001E-2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20">
+        <v>-2.3E-2</v>
+      </c>
+      <c r="C20">
+        <v>0.25559999999999999</v>
+      </c>
+      <c r="D20">
+        <v>-1.9E-3</v>
+      </c>
+      <c r="E20">
+        <v>7.3800000000000004E-2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99021514-03EF-4366-BDE1-AFA979FC89F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A985094E-E737-4ECB-8249-EFF9EF46A1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -846,7 +846,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -930,290 +929,284 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>88</v>
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="D2" s="8">
-        <v>45623</v>
+        <v>45484</v>
       </c>
       <c r="E2" s="2">
-        <v>1.9595</v>
+        <v>0.33389999999999997</v>
       </c>
       <c r="F2" s="1">
-        <v>15.3</v>
+        <v>188.53</v>
       </c>
       <c r="G2" s="1">
         <f>E2*F2</f>
-        <v>29.980350000000001</v>
+        <v>62.950166999999993</v>
       </c>
       <c r="H2" s="11">
-        <v>0.35</v>
+        <v>0.20617408370020684</v>
       </c>
       <c r="I2" s="11">
-        <v>0.39532299999999998</v>
+        <v>0.37</v>
       </c>
       <c r="J2" s="9">
         <f>IFERROR(H2/I2,"")</f>
-        <v>0.88535197800279775</v>
+        <v>0.55722725324380229</v>
       </c>
       <c r="K2" s="9">
         <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.4858722504833506</v>
+        <v>5.2419145625509082E-2</v>
       </c>
       <c r="L2" s="12">
-        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>20.655000000000001</v>
+        <f>IF((1+H2)*F2&lt;0,0,(1+H2)*F2)</f>
+        <v>227.4</v>
       </c>
       <c r="M2" s="12">
         <f>F2/(1+I2-H2)</f>
-        <v>14.636624277854791</v>
+        <v>161.9915808365931</v>
       </c>
       <c r="N2" s="12">
         <f>L2-F2</f>
-        <v>5.3550000000000004</v>
+        <v>38.870000000000005</v>
       </c>
       <c r="O2" s="12">
         <f>0.5*(M2-F2)</f>
-        <v>-0.33168786107260484</v>
+        <v>-13.26920958170345</v>
       </c>
       <c r="P2" s="14">
         <f>N2+O2</f>
-        <v>5.0233121389273956</v>
+        <v>25.600790418296555</v>
       </c>
       <c r="Q2" s="12">
         <f>MAX($P$2:$P$280)-P2</f>
-        <v>98.605197889725929</v>
+        <v>78.027719610356769</v>
       </c>
       <c r="R2" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0141453203291975E-2</v>
+        <v>1.2815958290126271E-2</v>
       </c>
       <c r="S2" s="9">
         <f>Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.44581150370259182</v>
+        <v>0.58791468015724246</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D3" s="8">
-        <v>45553</v>
+        <v>45574</v>
       </c>
       <c r="E3" s="2">
-        <v>1.0751999999999999</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F3" s="1">
-        <v>51.15</v>
+        <v>423.77</v>
       </c>
       <c r="G3" s="1">
         <f>E3*F3</f>
-        <v>54.996479999999998</v>
+        <v>56.658049000000005</v>
       </c>
       <c r="H3" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C3,Sheet1!$G:$G,0),2)</f>
-        <v>0.1346</v>
+        <v>0.15</v>
       </c>
       <c r="I3" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C3,Sheet1!$G:$G,0),3)</f>
-        <v>0.20530000000000001</v>
+        <v>0.1963</v>
       </c>
       <c r="J3" s="9">
         <f>IFERROR(H3/I3,"")</f>
-        <v>0.65562591329761322</v>
+        <v>0.76413652572592972</v>
       </c>
       <c r="K3" s="9">
         <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1003266220337604</v>
+        <v>7.1883389742017412E-2</v>
       </c>
       <c r="L3" s="12">
-        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
-        <v>58.034790000000001</v>
+        <f t="shared" ref="L3:L41" si="0">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
+        <v>487.33549999999997</v>
       </c>
       <c r="M3" s="12">
         <f>F3/(1+I3-H3)</f>
-        <v>47.772485289997199</v>
+        <v>405.01768135334032</v>
       </c>
       <c r="N3" s="12">
         <f>L3-F3</f>
-        <v>6.8847900000000024</v>
+        <v>63.565499999999986</v>
       </c>
       <c r="O3" s="12">
         <f>0.5*(M3-F3)</f>
-        <v>-1.6887573550013997</v>
+        <v>-9.3761593233298299</v>
       </c>
       <c r="P3" s="14">
         <f>N3+O3</f>
-        <v>5.1960326449986027</v>
+        <v>54.189340676670156</v>
       </c>
       <c r="Q3" s="12">
         <f>MAX($P$2:$P$280)-P3</f>
-        <v>98.432477383654714</v>
+        <v>49.439169351983168</v>
       </c>
       <c r="R3" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0159248518173087E-2</v>
+        <v>2.0226877051280529E-2</v>
       </c>
       <c r="S3" s="9">
         <f>Q3/MAX($Q$2:$Q$28)</f>
-        <v>0.44503060380907916</v>
+        <v>0.3725088158664186</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>50</v>
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
       </c>
       <c r="D4" s="8">
-        <v>45511</v>
+        <v>45553</v>
       </c>
       <c r="E4" s="2">
-        <v>1</v>
+        <v>1.0751999999999999</v>
       </c>
       <c r="F4" s="1">
-        <v>10.92</v>
+        <v>51.15</v>
       </c>
       <c r="G4" s="1">
         <f>E4*F4</f>
-        <v>10.92</v>
+        <v>54.996479999999998</v>
       </c>
       <c r="H4" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C4,Sheet1!$G:$G,0),2)</f>
-        <v>-1.7947</v>
+        <v>0.1346</v>
       </c>
       <c r="I4" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C4,Sheet1!$G:$G,0),3)</f>
-        <v>1.4319</v>
+        <v>0.20530000000000001</v>
       </c>
       <c r="J4" s="9">
         <f>IFERROR(H4/I4,"")</f>
-        <v>-1.253369648718486</v>
+        <v>0.65562591329761322</v>
       </c>
       <c r="K4" s="9">
         <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.1035104985364117</v>
+        <v>6.1675644945471314E-2</v>
       </c>
       <c r="L4" s="12">
-        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
-        <v>-8.6781240000000022</v>
+        <f t="shared" si="0"/>
+        <v>58.034790000000001</v>
       </c>
       <c r="M4" s="12">
         <f>F4/(1+I4-H4)</f>
-        <v>2.5836369658827429</v>
+        <v>47.772485289997199</v>
       </c>
       <c r="N4" s="12">
         <f>L4-F4</f>
-        <v>-19.598124000000002</v>
+        <v>6.8847900000000024</v>
       </c>
       <c r="O4" s="12">
         <f>0.5*(M4-F4)</f>
-        <v>-4.1681815170586285</v>
+        <v>-1.6887573550013997</v>
       </c>
       <c r="P4" s="14">
         <f>N4+O4</f>
-        <v>-23.76630551705863</v>
+        <v>5.1960326449986027</v>
       </c>
       <c r="Q4" s="12">
         <f>MAX($P$2:$P$280)-P4</f>
-        <v>127.39481554571195</v>
+        <v>98.432477383654714</v>
       </c>
       <c r="R4" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.8496129981143452E-3</v>
+        <v>1.0159248518173085E-2</v>
       </c>
       <c r="S4" s="9">
         <f>Q4/MAX($Q$2:$Q$28)</f>
-        <v>0.5759744465587221</v>
+        <v>0.74165820489280565</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D5" s="8">
-        <v>45511</v>
+        <v>45460</v>
       </c>
       <c r="E5" s="2">
-        <v>0.45179999999999998</v>
+        <v>0.33529999999999999</v>
       </c>
       <c r="F5" s="1">
-        <v>77.430000000000007</v>
+        <v>163.15</v>
       </c>
       <c r="G5" s="1">
         <f>E5*F5</f>
-        <v>34.982874000000002</v>
+        <v>54.704194999999999</v>
       </c>
       <c r="H5" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C5,Sheet1!$G:$G,0),2)</f>
-        <v>-3.8800000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I5" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C5,Sheet1!$G:$G,0),3)</f>
-        <v>0.28689999999999999</v>
+        <v>0.1711</v>
       </c>
       <c r="J5" s="9">
         <f>IFERROR(H5/I5,"")</f>
-        <v>-0.13523875914952946</v>
+        <v>0.29222676797194624</v>
       </c>
       <c r="K5" s="9">
         <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.22696907490215393</v>
+        <v>2.7490180024075623E-2</v>
       </c>
       <c r="L5" s="12">
-        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
-        <v>74.425716000000008</v>
+        <f t="shared" si="0"/>
+        <v>171.3075</v>
       </c>
       <c r="M5" s="12">
         <f>F5/(1+I5-H5)</f>
-        <v>58.406879384476134</v>
+        <v>145.52671483364554</v>
       </c>
       <c r="N5" s="12">
         <f>L5-F5</f>
-        <v>-3.0042839999999984</v>
+        <v>8.1574999999999989</v>
       </c>
       <c r="O5" s="12">
         <f>0.5*(M5-F5)</f>
-        <v>-9.5115603077619362</v>
+        <v>-8.8116425831772318</v>
       </c>
       <c r="P5" s="14">
         <f>N5+O5</f>
-        <v>-12.515844307761935</v>
+        <v>-0.65414258317723295</v>
       </c>
       <c r="Q5" s="12">
         <f>MAX($P$2:$P$280)-P5</f>
-        <v>116.14435433641526</v>
+        <v>104.28265261183056</v>
       </c>
       <c r="R5" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.6099751099693832E-3</v>
+        <v>9.5893226241787512E-3</v>
       </c>
       <c r="S5" s="9">
         <f>Q5/MAX($Q$2:$Q$28)</f>
-        <v>0.52510912569933532</v>
+        <v>0.78573746179422488</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1240,11 +1233,9 @@
         <v>50.187169999999995</v>
       </c>
       <c r="H6" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C6,Sheet1!$G:$G,0),2)</f>
         <v>2.0500000000000001E-2</v>
       </c>
       <c r="I6" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C6,Sheet1!$G:$G,0),3)</f>
         <v>0.1867</v>
       </c>
       <c r="J6" s="9">
@@ -1253,10 +1244,10 @@
       </c>
       <c r="K6" s="9">
         <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.1842786632702656</v>
+        <v>1.0329210599190836E-2</v>
       </c>
       <c r="L6" s="12">
-        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <f t="shared" si="0"/>
         <v>145.70698999999999</v>
       </c>
       <c r="M6" s="12">
@@ -1281,157 +1272,154 @@
       </c>
       <c r="R6" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.0191165060791081E-3</v>
+        <v>9.0191165060791098E-3</v>
       </c>
       <c r="S6" s="9">
         <f>Q6/MAX($Q$2:$Q$28)</f>
-        <v>0.50128818041564005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.83541331503696381</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D7" s="8">
-        <v>45484</v>
+        <v>45482</v>
       </c>
       <c r="E7" s="2">
-        <v>0.33389999999999997</v>
+        <v>0.18820000000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>188.53</v>
+        <v>227.38</v>
       </c>
       <c r="G7" s="1">
         <f>E7*F7</f>
-        <v>62.950166999999993</v>
+        <v>42.792915999999998</v>
       </c>
       <c r="H7" s="11">
-        <f>227.4/F7-1</f>
-        <v>0.20617408370020684</v>
+        <v>0.15</v>
       </c>
       <c r="I7" s="11">
-        <v>0.37</v>
+        <v>0.2271</v>
       </c>
       <c r="J7" s="9">
         <f>IFERROR(H7/I7,"")</f>
-        <v>0.55722725324380229</v>
+        <v>0.66050198150594452</v>
       </c>
       <c r="K7" s="9">
         <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.93518570396801892</v>
+        <v>6.2134343489026939E-2</v>
       </c>
       <c r="L7" s="12">
-        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
-        <v>227.4</v>
+        <f t="shared" si="0"/>
+        <v>261.48699999999997</v>
       </c>
       <c r="M7" s="12">
         <f>F7/(1+I7-H7)</f>
-        <v>161.9915808365931</v>
+        <v>211.10389007520189</v>
       </c>
       <c r="N7" s="12">
         <f>L7-F7</f>
-        <v>38.870000000000005</v>
+        <v>34.106999999999971</v>
       </c>
       <c r="O7" s="12">
         <f>0.5*(M7-F7)</f>
-        <v>-13.26920958170345</v>
+        <v>-8.1380549623990532</v>
       </c>
       <c r="P7" s="14">
         <f>N7+O7</f>
-        <v>25.600790418296555</v>
+        <v>25.968945037600918</v>
       </c>
       <c r="Q7" s="12">
         <f>MAX($P$2:$P$280)-P7</f>
-        <v>78.027719610356769</v>
+        <v>77.659564991052406</v>
       </c>
       <c r="R7" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2815958290126271E-2</v>
+        <v>1.2876713900151458E-2</v>
       </c>
       <c r="S7" s="9">
         <f>Q7/MAX($Q$2:$Q$28)</f>
-        <v>0.35277709242954441</v>
+        <v>0.58514074922170345</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D8" s="8">
-        <v>45460</v>
+        <v>45511</v>
       </c>
       <c r="E8" s="2">
-        <v>0.33529999999999999</v>
+        <v>0.14610000000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>163.15</v>
+        <v>273.45999999999998</v>
       </c>
       <c r="G8" s="1">
         <f>E8*F8</f>
-        <v>54.704194999999999</v>
+        <v>39.952506</v>
       </c>
       <c r="H8" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C8,Sheet1!$G:$G,0),2)</f>
-        <v>2.9999999999999997E-4</v>
+        <v>0.25</v>
       </c>
       <c r="I8" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C8,Sheet1!$G:$G,0),3)</f>
-        <v>0.1711</v>
+        <v>0.26</v>
       </c>
       <c r="J8" s="9">
         <f>IFERROR(H8/I8,"")</f>
-        <v>1.7533606078316772E-3</v>
+        <v>0.96153846153846145</v>
       </c>
       <c r="K8" s="9">
         <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.9426374334699649E-3</v>
+        <v>9.0453265425371895E-2</v>
       </c>
       <c r="L8" s="12">
-        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
-        <v>163.19894500000001</v>
+        <f t="shared" si="0"/>
+        <v>341.82499999999999</v>
       </c>
       <c r="M8" s="12">
         <f>F8/(1+I8-H8)</f>
-        <v>139.34916296549369</v>
+        <v>270.75247524752473</v>
       </c>
       <c r="N8" s="12">
         <f>L8-F8</f>
-        <v>4.8945000000003347E-2</v>
+        <v>68.365000000000009</v>
       </c>
       <c r="O8" s="12">
         <f>0.5*(M8-F8)</f>
-        <v>-11.900418517253158</v>
+        <v>-1.3537623762376256</v>
       </c>
       <c r="P8" s="14">
         <f>N8+O8</f>
-        <v>-11.851473517253154</v>
+        <v>67.011237623762383</v>
       </c>
       <c r="Q8" s="12">
         <f>MAX($P$2:$P$280)-P8</f>
-        <v>115.47998354590648</v>
+        <v>36.61727240489094</v>
       </c>
       <c r="R8" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.6595093737822752E-3</v>
+        <v>2.7309516365463388E-2</v>
       </c>
       <c r="S8" s="9">
         <f>Q8/MAX($Q$2:$Q$28)</f>
-        <v>0.52210538809247986</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.27589979691389888</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1466,10 +1454,10 @@
       </c>
       <c r="K9" s="9">
         <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.66633836006711356</v>
+        <v>3.7349680800312375E-2</v>
       </c>
       <c r="L9" s="12">
-        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <f t="shared" si="0"/>
         <v>216.33799999999999</v>
       </c>
       <c r="M9" s="12">
@@ -1498,1064 +1486,1057 @@
       </c>
       <c r="S9" s="9">
         <f>Q9/MAX($Q$2:$Q$28)</f>
-        <v>0.41984522948505815</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.69968594646646121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D10" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E10" s="2">
-        <v>0.19139999999999999</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F10" s="1">
-        <v>135.82</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G10" s="1">
         <f>E10*F10</f>
-        <v>25.995947999999999</v>
+        <v>34.982874000000002</v>
       </c>
       <c r="H10" s="11">
-        <v>0.1202</v>
+        <v>0.04</v>
       </c>
       <c r="I10" s="11">
-        <v>0.33710000000000001</v>
+        <v>0.28689999999999999</v>
       </c>
       <c r="J10" s="9">
         <f>IFERROR(H10/I10,"")</f>
-        <v>0.35657075051913378</v>
+        <v>0.13942140118508192</v>
       </c>
       <c r="K10" s="9">
         <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.59842706256282674</v>
+        <v>1.3115565847666336E-2</v>
       </c>
       <c r="L10" s="12">
-        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
-        <v>152.14556400000001</v>
+        <f t="shared" si="0"/>
+        <v>80.527200000000008</v>
       </c>
       <c r="M10" s="12">
         <f>F10/(1+I10-H10)</f>
-        <v>111.61147177253677</v>
+        <v>62.098003047557953</v>
       </c>
       <c r="N10" s="12">
         <f>L10-F10</f>
-        <v>16.325564000000014</v>
+        <v>3.0972000000000008</v>
       </c>
       <c r="O10" s="12">
         <f>0.5*(M10-F10)</f>
-        <v>-12.10426411373161</v>
+        <v>-7.6659984762210271</v>
       </c>
       <c r="P10" s="14">
         <f>N10+O10</f>
-        <v>4.2212998862684046</v>
+        <v>-4.5687984762210263</v>
       </c>
       <c r="Q10" s="12">
         <f>MAX($P$2:$P$280)-P10</f>
-        <v>99.407210142384912</v>
+        <v>108.19730850487434</v>
       </c>
       <c r="R10" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0059632481061084E-2</v>
+        <v>9.2423740832236097E-3</v>
       </c>
       <c r="S10" s="9">
         <f>Q10/MAX($Q$2:$Q$28)</f>
-        <v>0.44943754265386154</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.81523318047954985</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="D11" s="8">
-        <v>45482</v>
+        <v>45623</v>
       </c>
       <c r="E11" s="2">
-        <v>0.18820000000000001</v>
+        <v>1.9595</v>
       </c>
       <c r="F11" s="1">
-        <v>227.38</v>
+        <v>15.3</v>
       </c>
       <c r="G11" s="1">
         <f>E11*F11</f>
-        <v>42.792915999999998</v>
+        <v>29.980350000000001</v>
       </c>
       <c r="H11" s="11">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="I11" s="11">
-        <v>0.2271</v>
+        <v>0.39532299999999998</v>
       </c>
       <c r="J11" s="9">
         <f>IFERROR(H11/I11,"")</f>
-        <v>0.66050198150594452</v>
+        <v>0.88535197800279775</v>
       </c>
       <c r="K11" s="9">
         <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1085100503450265</v>
+        <v>8.32862965596117E-2</v>
       </c>
       <c r="L11" s="12">
-        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
-        <v>261.48699999999997</v>
+        <f t="shared" si="0"/>
+        <v>20.655000000000001</v>
       </c>
       <c r="M11" s="12">
         <f>F11/(1+I11-H11)</f>
-        <v>211.10389007520189</v>
+        <v>14.636624277854791</v>
       </c>
       <c r="N11" s="12">
         <f>L11-F11</f>
-        <v>34.106999999999971</v>
+        <v>5.3550000000000004</v>
       </c>
       <c r="O11" s="12">
         <f>0.5*(M11-F11)</f>
-        <v>-8.1380549623990532</v>
+        <v>-0.33168786107260484</v>
       </c>
       <c r="P11" s="14">
         <f>N11+O11</f>
-        <v>25.968945037600918</v>
+        <v>5.0233121389273956</v>
       </c>
       <c r="Q11" s="12">
         <f>MAX($P$2:$P$280)-P11</f>
-        <v>77.659564991052406</v>
+        <v>98.605197889725929</v>
       </c>
       <c r="R11" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2876713900151458E-2</v>
+        <v>1.0141453203291973E-2</v>
       </c>
       <c r="S11" s="9">
         <f>Q11/MAX($Q$2:$Q$28)</f>
-        <v>0.35111260041553638</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.7429596003659853</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D12" s="8">
-        <v>45580</v>
+        <v>45562</v>
       </c>
       <c r="E12" s="2">
-        <v>0.18010000000000001</v>
+        <v>4.0300000000000002E-2</v>
       </c>
       <c r="F12" s="1">
-        <v>133.19999999999999</v>
+        <v>668.82</v>
       </c>
       <c r="G12" s="1">
         <f>E12*F12</f>
-        <v>23.989319999999999</v>
+        <v>26.953446000000003</v>
       </c>
       <c r="H12" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I12" s="11">
-        <v>0.1623</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J12" s="9">
         <f>IFERROR(H12/I12,"")</f>
-        <v>0.43130006161429457</v>
+        <v>0.17857142857142858</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.7238440858630063</v>
+        <v>1.6798463578997641E-2</v>
       </c>
       <c r="L12" s="12">
-        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
-        <v>142.524</v>
+        <f t="shared" si="0"/>
+        <v>702.26100000000008</v>
       </c>
       <c r="M12" s="12">
         <f>F12/(1+I12-H12)</f>
-        <v>121.94452073606151</v>
+        <v>543.7560975609756</v>
       </c>
       <c r="N12" s="12">
         <f>L12-F12</f>
-        <v>9.3240000000000123</v>
+        <v>33.441000000000031</v>
       </c>
       <c r="O12" s="12">
         <f>0.5*(M12-F12)</f>
-        <v>-5.6277396319692414</v>
+        <v>-62.531951219512223</v>
       </c>
       <c r="P12" s="14">
         <f>N12+O12</f>
-        <v>3.6962603680307708</v>
+        <v>-29.090951219512192</v>
       </c>
       <c r="Q12" s="12">
         <f>MAX($P$2:$P$280)-P12</f>
-        <v>99.932249660622546</v>
+        <v>132.71946124816552</v>
       </c>
       <c r="R12" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0006779627158154E-2</v>
+        <v>7.5346900190481469E-3</v>
       </c>
       <c r="S12" s="9">
         <f>Q12/MAX($Q$2:$Q$28)</f>
-        <v>0.45181133898649067</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>7</v>
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D13" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E13" s="2">
-        <v>0.14610000000000001</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F13" s="1">
-        <v>273.45999999999998</v>
+        <v>135.82</v>
       </c>
       <c r="G13" s="1">
         <f>E13*F13</f>
-        <v>39.952506</v>
+        <v>25.995947999999999</v>
       </c>
       <c r="H13" s="11">
-        <v>0.25</v>
+        <v>0.1202</v>
       </c>
       <c r="I13" s="11">
-        <v>0.26</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J13" s="9">
         <f>IFERROR(H13/I13,"")</f>
-        <v>0.96153846153846145</v>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K13" s="9">
         <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.6137348232907405</v>
+        <v>3.3543108289216528E-2</v>
       </c>
       <c r="L13" s="12">
-        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
-        <v>341.82499999999999</v>
+        <f t="shared" si="0"/>
+        <v>152.14556400000001</v>
       </c>
       <c r="M13" s="12">
         <f>F13/(1+I13-H13)</f>
-        <v>270.75247524752473</v>
+        <v>111.61147177253677</v>
       </c>
       <c r="N13" s="12">
         <f>L13-F13</f>
-        <v>68.365000000000009</v>
+        <v>16.325564000000014</v>
       </c>
       <c r="O13" s="12">
         <f>0.5*(M13-F13)</f>
-        <v>-1.3537623762376256</v>
+        <v>-12.10426411373161</v>
       </c>
       <c r="P13" s="14">
         <f>N13+O13</f>
-        <v>67.011237623762383</v>
+        <v>4.2212998862684046</v>
       </c>
       <c r="Q13" s="12">
         <f>MAX($P$2:$P$280)-P13</f>
-        <v>36.61727240489094</v>
+        <v>99.407210142384912</v>
       </c>
       <c r="R13" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7309516365463384E-2</v>
+        <v>1.0059632481061082E-2</v>
       </c>
       <c r="S13" s="9">
         <f>Q13/MAX($Q$2:$Q$28)</f>
-        <v>0.1655531515749106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.74900251408124929</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="D14" s="8">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="E14" s="2">
-        <v>0.13370000000000001</v>
+        <v>0.18010000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>423.77</v>
+        <v>133.19999999999999</v>
       </c>
       <c r="G14" s="1">
         <f>E14*F14</f>
-        <v>56.658049000000005</v>
+        <v>23.989319999999999</v>
       </c>
       <c r="H14" s="11">
-        <v>0.15</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I14" s="11">
-        <v>0.1963</v>
+        <v>0.1623</v>
       </c>
       <c r="J14" s="9">
         <f>IFERROR(H14/I14,"")</f>
-        <v>0.76413652572592972</v>
+        <v>0.43130006161429457</v>
       </c>
       <c r="K14" s="9">
         <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.2824382701648269</v>
+        <v>4.0572998909224126E-2</v>
       </c>
       <c r="L14" s="12">
-        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
-        <v>487.33549999999991</v>
+        <f t="shared" si="0"/>
+        <v>142.524</v>
       </c>
       <c r="M14" s="12">
         <f>F14/(1+I14-H14)</f>
-        <v>405.01768135334032</v>
+        <v>121.94452073606151</v>
       </c>
       <c r="N14" s="12">
         <f>L14-F14</f>
-        <v>63.565499999999929</v>
+        <v>9.3240000000000123</v>
       </c>
       <c r="O14" s="12">
         <f>0.5*(M14-F14)</f>
-        <v>-9.3761593233298299</v>
+        <v>-5.6277396319692414</v>
       </c>
       <c r="P14" s="14">
         <f>N14+O14</f>
-        <v>54.189340676670099</v>
+        <v>3.6962603680307708</v>
       </c>
       <c r="Q14" s="12">
         <f>MAX($P$2:$P$280)-P14</f>
-        <v>49.439169351983224</v>
+        <v>99.932249660622546</v>
       </c>
       <c r="R14" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.0226877051280505E-2</v>
+        <v>1.0006779627158154E-2</v>
       </c>
       <c r="S14" s="9">
         <f>Q14/MAX($Q$2:$Q$28)</f>
-        <v>0.22352321076687609</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.75295852409892028</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="D15" s="8">
-        <v>45483</v>
+        <v>45627</v>
       </c>
       <c r="E15" s="2">
-        <v>0.1195</v>
+        <v>0.9385</v>
       </c>
       <c r="F15" s="1">
-        <v>167.24</v>
+        <v>21.31</v>
       </c>
       <c r="G15" s="1">
         <f>E15*F15</f>
-        <v>19.98518</v>
+        <v>19.999434999999998</v>
       </c>
       <c r="H15" s="11">
-        <f>190.41/F15-1</f>
-        <v>0.13854341066730447</v>
+        <v>-5.4899999999999997E-2</v>
       </c>
       <c r="I15" s="11">
-        <v>0.26790000000000003</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="J15" s="9">
         <f>IFERROR(H15/I15,"")</f>
-        <v>0.51714598979956872</v>
+        <v>-0.11952971913781842</v>
       </c>
       <c r="K15" s="9">
         <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.86791795216331102</v>
+        <v>-1.1244327547848975E-2</v>
       </c>
       <c r="L15" s="12">
-        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
-        <v>190.41</v>
+        <f t="shared" si="0"/>
+        <v>20.140080999999999</v>
       </c>
       <c r="M15" s="12">
         <f>F15/(1+I15-H15)</f>
-        <v>148.08431772538498</v>
+        <v>14.073438119138819</v>
       </c>
       <c r="N15" s="12">
         <f>L15-F15</f>
-        <v>23.169999999999987</v>
+        <v>-1.1699190000000002</v>
       </c>
       <c r="O15" s="12">
         <f>0.5*(M15-F15)</f>
-        <v>-9.5778411373075159</v>
+        <v>-3.6182809404305898</v>
       </c>
       <c r="P15" s="14">
         <f>N15+O15</f>
-        <v>13.592158862692472</v>
+        <v>-4.7881999404305899</v>
       </c>
       <c r="Q15" s="12">
         <f>MAX($P$2:$P$280)-P15</f>
-        <v>90.036351165960852</v>
+        <v>108.41670996908391</v>
       </c>
       <c r="R15" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1106625124742505E-2</v>
+        <v>9.223670412846505E-3</v>
       </c>
       <c r="S15" s="9">
         <f>Q15/MAX($Q$2:$Q$28)</f>
-        <v>0.40707023524338853</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.81688630250209426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D16" s="8">
-        <v>45562</v>
+        <v>45483</v>
       </c>
       <c r="E16" s="2">
-        <v>4.0300000000000002E-2</v>
+        <v>0.1195</v>
       </c>
       <c r="F16" s="1">
-        <v>668.82</v>
+        <v>167.24</v>
       </c>
       <c r="G16" s="1">
         <f>E16*F16</f>
-        <v>26.953446000000003</v>
+        <v>19.98518</v>
       </c>
       <c r="H16" s="11">
-        <v>0.05</v>
+        <v>0.13854341066730447</v>
       </c>
       <c r="I16" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J16" s="9">
         <f>IFERROR(H16/I16,"")</f>
-        <v>0.17857142857142858</v>
+        <v>0.51714598979956872</v>
       </c>
       <c r="K16" s="9">
         <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.29969361003970896</v>
+        <v>4.8648645218167343E-2</v>
       </c>
       <c r="L16" s="12">
-        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
-        <v>702.26100000000008</v>
+        <f t="shared" si="0"/>
+        <v>190.41</v>
       </c>
       <c r="M16" s="12">
         <f>F16/(1+I16-H16)</f>
-        <v>543.7560975609756</v>
+        <v>148.08431772538498</v>
       </c>
       <c r="N16" s="12">
         <f>L16-F16</f>
-        <v>33.441000000000031</v>
+        <v>23.169999999999987</v>
       </c>
       <c r="O16" s="12">
         <f>0.5*(M16-F16)</f>
-        <v>-62.531951219512223</v>
+        <v>-9.5778411373075159</v>
       </c>
       <c r="P16" s="14">
         <f>N16+O16</f>
-        <v>-29.090951219512192</v>
+        <v>13.592158862692472</v>
       </c>
       <c r="Q16" s="12">
         <f>MAX($P$2:$P$280)-P16</f>
-        <v>132.71946124816552</v>
+        <v>90.036351165960852</v>
       </c>
       <c r="R16" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.5346900190481469E-3</v>
+        <v>1.1106625124742505E-2</v>
       </c>
       <c r="S16" s="9">
         <f>Q16/MAX($Q$2:$Q$28)</f>
-        <v>0.60004810959166965</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.67839599648167925</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D17" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E17" s="2">
-        <v>3.2899999999999999E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="F17" s="1">
-        <v>455.4</v>
+        <v>700.32</v>
       </c>
       <c r="G17" s="1">
         <f>E17*F17</f>
-        <v>14.982659999999999</v>
+        <v>19.959120000000002</v>
       </c>
       <c r="H17" s="11">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I17" s="11">
-        <v>0.29699999999999999</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J17" s="9">
         <f>IFERROR(H17/I17,"")</f>
-        <v>0.84175084175084181</v>
+        <v>0.22055580061755625</v>
       </c>
       <c r="K17" s="9">
         <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.4126971517023319</v>
+        <v>2.0747992069339829E-2</v>
       </c>
       <c r="L17" s="12">
-        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
-        <v>569.25</v>
+        <f t="shared" si="0"/>
+        <v>770.35200000000009</v>
       </c>
       <c r="M17" s="12">
         <f>F17/(1+I17-H17)</f>
-        <v>434.95702005730658</v>
+        <v>517.45234224915032</v>
       </c>
       <c r="N17" s="12">
         <f>L17-F17</f>
-        <v>113.85000000000002</v>
+        <v>70.032000000000039</v>
       </c>
       <c r="O17" s="12">
         <f>0.5*(M17-F17)</f>
-        <v>-10.221489971346699</v>
+        <v>-91.433828875424865</v>
       </c>
       <c r="P17" s="14">
         <f>N17+O17</f>
-        <v>103.62851002865332</v>
+        <v>-21.401828875424826</v>
       </c>
       <c r="Q17" s="12">
         <f>MAX($P$2:$P$280)-P17</f>
-        <v>0</v>
+        <v>125.03033890407815</v>
       </c>
       <c r="R17" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>0</v>
+        <v>7.9980587812945834E-3</v>
       </c>
       <c r="S17" s="9">
         <f>Q17/MAX($Q$2:$Q$28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.94206484661876488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D18" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E18" s="2">
-        <v>2.8500000000000001E-2</v>
+        <v>3.2899999999999999E-2</v>
       </c>
       <c r="F18" s="1">
-        <v>700.32</v>
+        <v>455.4</v>
       </c>
       <c r="G18" s="1">
         <f>E18*F18</f>
-        <v>19.959120000000002</v>
+        <v>14.982659999999999</v>
       </c>
       <c r="H18" s="11">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="I18" s="11">
-        <v>0.45340000000000003</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="J18" s="9">
         <f>IFERROR(H18/I18,"")</f>
-        <v>0.22055580061755625</v>
+        <v>0.84175084175084181</v>
       </c>
       <c r="K18" s="9">
         <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.37015531897273274</v>
+        <v>7.9184676803355877E-2</v>
       </c>
       <c r="L18" s="12">
-        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
-        <v>770.35200000000009</v>
+        <f t="shared" si="0"/>
+        <v>569.25</v>
       </c>
       <c r="M18" s="12">
         <f>F18/(1+I18-H18)</f>
-        <v>517.45234224915032</v>
+        <v>434.95702005730658</v>
       </c>
       <c r="N18" s="12">
         <f>L18-F18</f>
-        <v>70.032000000000039</v>
+        <v>113.85000000000002</v>
       </c>
       <c r="O18" s="12">
         <f>0.5*(M18-F18)</f>
-        <v>-91.433828875424865</v>
+        <v>-10.221489971346699</v>
       </c>
       <c r="P18" s="14">
         <f>N18+O18</f>
-        <v>-21.401828875424826</v>
+        <v>103.62851002865332</v>
       </c>
       <c r="Q18" s="12">
         <f>MAX($P$2:$P$280)-P18</f>
-        <v>125.03033890407815</v>
+        <v>0</v>
       </c>
       <c r="R18" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.9980587812945834E-3</v>
+        <v>0</v>
       </c>
       <c r="S18" s="9">
         <f>Q18/MAX($Q$2:$Q$28)</f>
-        <v>0.565284230326356</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D19" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E19" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>147.01</v>
+        <v>10.92</v>
       </c>
       <c r="G19" s="1">
         <f>E19*F19</f>
-        <v>1.4700999999999999E-17</v>
+        <v>10.92</v>
       </c>
       <c r="H19" s="11">
-        <v>0.15</v>
+        <v>-1.7947</v>
       </c>
       <c r="I19" s="11">
-        <v>0.52380000000000004</v>
+        <v>1.4319</v>
       </c>
       <c r="J19" s="9">
         <f>IFERROR(H19/I19,"")</f>
-        <v>0.28636884306987398</v>
+        <v>-1.253369648718486</v>
       </c>
       <c r="K19" s="9">
         <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.48060830934203036</v>
+        <v>-0.1179062326121039</v>
       </c>
       <c r="L19" s="12">
-        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
-        <v>169.06149999999997</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="M19" s="12">
         <f>F19/(1+I19-H19)</f>
-        <v>107.00975396709855</v>
+        <v>2.5836369658827429</v>
       </c>
       <c r="N19" s="12">
         <f>L19-F19</f>
-        <v>22.051499999999976</v>
+        <v>-10.92</v>
       </c>
       <c r="O19" s="12">
         <f>0.5*(M19-F19)</f>
-        <v>-20.000123016450722</v>
+        <v>-4.1681815170586285</v>
       </c>
       <c r="P19" s="14">
         <f>N19+O19</f>
-        <v>2.0513769835492539</v>
+        <v>-15.088181517058629</v>
       </c>
       <c r="Q19" s="12">
         <f>MAX($P$2:$P$280)-P19</f>
-        <v>101.57713304510406</v>
+        <v>118.71669154571195</v>
       </c>
       <c r="R19" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8447354244184312E-3</v>
+        <v>8.4234153342704066E-3</v>
       </c>
       <c r="S19" s="9">
         <f>Q19/MAX($Q$2:$Q$28)</f>
-        <v>0.45924814709341422</v>
+        <v>0.8944934708838933</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>47</v>
+        <v>36</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D20" s="8">
-        <v>45511</v>
+        <v>45482</v>
       </c>
       <c r="E20" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F20" s="1">
-        <v>187.36</v>
+        <v>147.01</v>
       </c>
       <c r="G20" s="1">
         <f>E20*F20</f>
-        <v>1.8736000000000003E-20</v>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H20" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C20,Sheet1!$G:$G,0),2)</f>
-        <v>0.2823</v>
+        <v>0.15</v>
       </c>
       <c r="I20" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C20,Sheet1!$G:$G,0),3)</f>
-        <v>0.5212</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J20" s="9">
         <f>IFERROR(H20/I20,"")</f>
-        <v>0.54163468917881807</v>
+        <v>0.28636884306987398</v>
       </c>
       <c r="K20" s="9">
         <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.90901694980731973</v>
+        <v>2.6939116850626225E-2</v>
       </c>
       <c r="L20" s="12">
-        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
-        <v>240.25172799999999</v>
+        <f t="shared" si="0"/>
+        <v>169.06149999999997</v>
       </c>
       <c r="M20" s="12">
         <f>F20/(1+I20-H20)</f>
-        <v>151.230930664299</v>
+        <v>107.00975396709855</v>
       </c>
       <c r="N20" s="12">
         <f>L20-F20</f>
-        <v>52.891727999999972</v>
+        <v>22.051499999999976</v>
       </c>
       <c r="O20" s="12">
         <f>0.5*(M20-F20)</f>
-        <v>-18.064534667850509</v>
+        <v>-20.000123016450722</v>
       </c>
       <c r="P20" s="14">
         <f>N20+O20</f>
-        <v>34.827193332149463</v>
+        <v>2.0513769835492539</v>
       </c>
       <c r="Q20" s="12">
         <f>MAX($P$2:$P$280)-P20</f>
-        <v>68.801316696503861</v>
+        <v>101.57713304510406</v>
       </c>
       <c r="R20" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.453460555720462E-2</v>
+        <v>9.8447354244184312E-3</v>
       </c>
       <c r="S20" s="9">
         <f>Q20/MAX($Q$2:$Q$28)</f>
-        <v>0.31106289637478135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.76535221051847124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D21" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E21" s="2">
         <v>1E-22</v>
       </c>
       <c r="F21" s="1">
-        <v>169.34</v>
+        <v>187.36</v>
       </c>
       <c r="G21" s="1">
         <f>E21*F21</f>
-        <v>1.6934000000000002E-20</v>
+        <v>1.8736000000000003E-20</v>
       </c>
       <c r="H21" s="11">
-        <v>0.1</v>
+        <v>0.2823</v>
       </c>
       <c r="I21" s="11">
-        <v>0.4259</v>
+        <v>0.5212</v>
       </c>
       <c r="J21" s="9">
         <f>IFERROR(H21/I21,"")</f>
-        <v>0.23479690068091102</v>
+        <v>0.54163468917881807</v>
       </c>
       <c r="K21" s="9">
         <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.39405593243070447</v>
+        <v>5.0952331356035663E-2</v>
       </c>
       <c r="L21" s="12">
-        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
-        <v>186.27400000000003</v>
+        <f t="shared" si="0"/>
+        <v>240.25172800000001</v>
       </c>
       <c r="M21" s="12">
         <f>F21/(1+I21-H21)</f>
-        <v>127.71702239987934</v>
+        <v>151.230930664299</v>
       </c>
       <c r="N21" s="12">
         <f>L21-F21</f>
-        <v>16.934000000000026</v>
+        <v>52.891728000000001</v>
       </c>
       <c r="O21" s="12">
         <f>0.5*(M21-F21)</f>
-        <v>-20.811488800060332</v>
+        <v>-18.064534667850509</v>
       </c>
       <c r="P21" s="14">
         <f>N21+O21</f>
-        <v>-3.8774888000603056</v>
+        <v>34.827193332149491</v>
       </c>
       <c r="Q21" s="12">
         <f>MAX($P$2:$P$280)-P21</f>
-        <v>107.50599882871363</v>
+        <v>68.801316696503832</v>
       </c>
       <c r="R21" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.3018065121488955E-3</v>
+        <v>1.4534605557204625E-2</v>
       </c>
       <c r="S21" s="9">
         <f>Q21/MAX($Q$2:$Q$28)</f>
-        <v>0.48605359575949542</v>
+        <v>0.51839659421051798</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
       </c>
       <c r="D22" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E22" s="2">
         <v>1E-22</v>
       </c>
       <c r="F22" s="1">
-        <v>113.58</v>
+        <v>169.34</v>
       </c>
       <c r="G22" s="1">
         <f>E22*F22</f>
-        <v>1.1358E-20</v>
+        <v>1.6934000000000002E-20</v>
       </c>
       <c r="H22" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C22,Sheet1!$G:$G,0),2)</f>
-        <v>7.2800000000000004E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I22" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C22,Sheet1!$G:$G,0),3)</f>
-        <v>0.18940000000000001</v>
+        <v>0.4259</v>
       </c>
       <c r="J22" s="9">
         <f>IFERROR(H22/I22,"")</f>
-        <v>0.38437170010559663</v>
+        <v>0.23479690068091102</v>
       </c>
       <c r="K22" s="9">
         <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.64508495744978112</v>
+        <v>2.2087672233478937E-2</v>
       </c>
       <c r="L22" s="12">
-        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
-        <v>121.848624</v>
+        <f t="shared" si="0"/>
+        <v>186.27400000000003</v>
       </c>
       <c r="M22" s="12">
         <f>F22/(1+I22-H22)</f>
-        <v>101.71950564212788</v>
+        <v>127.71702239987934</v>
       </c>
       <c r="N22" s="12">
         <f>L22-F22</f>
-        <v>8.2686240000000026</v>
+        <v>16.934000000000026</v>
       </c>
       <c r="O22" s="12">
         <f>0.5*(M22-F22)</f>
-        <v>-5.9302471789360567</v>
+        <v>-20.811488800060332</v>
       </c>
       <c r="P22" s="14">
         <f>N22+O22</f>
-        <v>2.338376821063946</v>
+        <v>-3.8774888000603056</v>
       </c>
       <c r="Q22" s="12">
         <f>MAX($P$2:$P$280)-P22</f>
-        <v>101.29013320758938</v>
+        <v>107.50599882871363</v>
       </c>
       <c r="R22" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8726299229022329E-3</v>
+        <v>9.3018065121488955E-3</v>
       </c>
       <c r="S22" s="9">
         <f>Q22/MAX($Q$2:$Q$28)</f>
-        <v>0.45795057017188207</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.81002437636251035</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>87</v>
+        <v>40</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="D23" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E23" s="2">
         <v>1E-22</v>
       </c>
       <c r="F23" s="1">
-        <v>64.349999999999994</v>
+        <v>113.58</v>
       </c>
       <c r="G23" s="1">
         <f>E23*F23</f>
-        <v>6.4349999999999995E-21</v>
+        <v>1.1358E-20</v>
       </c>
       <c r="H23" s="11">
-        <v>0.15</v>
+        <v>7.2800000000000004E-2</v>
       </c>
       <c r="I23" s="11">
-        <v>0.67300000000000004</v>
+        <v>0.18940000000000001</v>
       </c>
       <c r="J23" s="9">
         <f>IFERROR(H23/I23,"")</f>
-        <v>0.22288261515601782</v>
+        <v>0.38437170010559663</v>
       </c>
       <c r="K23" s="9">
         <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.37406037508670953</v>
+        <v>3.6158382428119099E-2</v>
       </c>
       <c r="L23" s="12">
-        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
-        <v>74.002499999999984</v>
+        <f t="shared" si="0"/>
+        <v>121.848624</v>
       </c>
       <c r="M23" s="12">
         <f>F23/(1+I23-H23)</f>
-        <v>42.252133946158892</v>
+        <v>101.71950564212788</v>
       </c>
       <c r="N23" s="12">
         <f>L23-F23</f>
-        <v>9.6524999999999892</v>
+        <v>8.2686240000000026</v>
       </c>
       <c r="O23" s="12">
         <f>0.5*(M23-F23)</f>
-        <v>-11.048933026920551</v>
+        <v>-5.9302471789360567</v>
       </c>
       <c r="P23" s="14">
         <f>N23+O23</f>
-        <v>-1.3964330269205618</v>
+        <v>2.338376821063946</v>
       </c>
       <c r="Q23" s="12">
         <f>MAX($P$2:$P$280)-P23</f>
-        <v>105.02494305557389</v>
+        <v>101.29013320758938</v>
       </c>
       <c r="R23" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.5215476524548141E-3</v>
+        <v>9.8726299229022329E-3</v>
       </c>
       <c r="S23" s="9">
         <f>Q23/MAX($Q$2:$Q$28)</f>
-        <v>0.47483630469710741</v>
+        <v>0.76318975570728098</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
       </c>
       <c r="D24" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="2">
         <v>1E-22</v>
       </c>
       <c r="F24" s="1">
-        <v>20.82</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G24" s="1">
         <f>E24*F24</f>
-        <v>2.0820000000000001E-21</v>
+        <v>6.4349999999999995E-21</v>
       </c>
       <c r="H24" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C24,Sheet1!$G:$G,0),2)</f>
-        <v>-0.1696</v>
+        <v>0.15</v>
       </c>
       <c r="I24" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C24,Sheet1!$G:$G,0),3)</f>
-        <v>0.70540000000000003</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="J24" s="9">
         <f>IFERROR(H24/I24,"")</f>
-        <v>-0.24043096115679047</v>
+        <v>0.22288261515601782</v>
       </c>
       <c r="K24" s="9">
         <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.40351148720061519</v>
+        <v>2.0966878761304632E-2</v>
       </c>
       <c r="L24" s="12">
-        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
-        <v>17.288928000000002</v>
+        <f t="shared" si="0"/>
+        <v>74.002499999999984</v>
       </c>
       <c r="M24" s="12">
         <f>F24/(1+I24-H24)</f>
-        <v>11.104000000000001</v>
+        <v>42.252133946158892</v>
       </c>
       <c r="N24" s="12">
         <f>L24-F24</f>
-        <v>-3.5310719999999982</v>
+        <v>9.6524999999999892</v>
       </c>
       <c r="O24" s="12">
         <f>0.5*(M24-F24)</f>
-        <v>-4.8579999999999997</v>
+        <v>-11.048933026920551</v>
       </c>
       <c r="P24" s="14">
         <f>N24+O24</f>
-        <v>-8.3890719999999988</v>
+        <v>-1.3964330269205618</v>
       </c>
       <c r="Q24" s="12">
         <f>MAX($P$2:$P$280)-P24</f>
-        <v>112.01758202865332</v>
+        <v>105.02494305557389</v>
       </c>
       <c r="R24" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9271700200081704E-3</v>
+        <v>9.5215476524548141E-3</v>
       </c>
       <c r="S24" s="9">
         <f>Q24/MAX($Q$2:$Q$28)</f>
-        <v>0.50645125971118488</v>
+        <v>0.79133039019193252</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -2563,10 +2544,10 @@
         <v>40</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="D25" s="8">
         <v>45511</v>
@@ -2575,59 +2556,57 @@
         <v>1E-22</v>
       </c>
       <c r="F25" s="1">
-        <v>13.04</v>
+        <v>20.82</v>
       </c>
       <c r="G25" s="1">
         <f>E25*F25</f>
-        <v>1.304E-21</v>
+        <v>2.0820000000000001E-21</v>
       </c>
       <c r="H25" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C25,Sheet1!$G:$G,0),2)</f>
-        <v>3.0300000000000001E-2</v>
+        <v>-0.1696</v>
       </c>
       <c r="I25" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C25,Sheet1!$G:$G,0),3)</f>
-        <v>0.39489999999999997</v>
+        <v>0.70540000000000003</v>
       </c>
       <c r="J25" s="9">
         <f>IFERROR(H25/I25,"")</f>
-        <v>7.6728285641934679E-2</v>
+        <v>-0.24043096115679047</v>
       </c>
       <c r="K25" s="9">
         <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.12877187073066049</v>
+        <v>-2.2617676167832147E-2</v>
       </c>
       <c r="L25" s="12">
-        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
-        <v>13.435111999999998</v>
+        <f t="shared" si="0"/>
+        <v>17.288928000000002</v>
       </c>
       <c r="M25" s="12">
         <f>F25/(1+I25-H25)</f>
-        <v>9.5559138208998959</v>
+        <v>11.104000000000001</v>
       </c>
       <c r="N25" s="12">
         <f>L25-F25</f>
-        <v>0.39511199999999924</v>
+        <v>-3.5310719999999982</v>
       </c>
       <c r="O25" s="12">
         <f>0.5*(M25-F25)</f>
-        <v>-1.7420430895500516</v>
+        <v>-4.8579999999999997</v>
       </c>
       <c r="P25" s="14">
         <f>N25+O25</f>
-        <v>-1.3469310895500524</v>
+        <v>-8.3890719999999988</v>
       </c>
       <c r="Q25" s="12">
         <f>MAX($P$2:$P$280)-P25</f>
-        <v>104.97544111820338</v>
+        <v>112.01758202865332</v>
       </c>
       <c r="R25" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.5260376079200296E-3</v>
+        <v>8.9271700200081704E-3</v>
       </c>
       <c r="S25" s="9">
         <f>Q25/MAX($Q$2:$Q$28)</f>
-        <v>0.47461249770105007</v>
+        <v>0.84401775726920125</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -2635,10 +2614,10 @@
         <v>40</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D26" s="8">
         <v>45511</v>
@@ -2647,59 +2626,57 @@
         <v>1E-22</v>
       </c>
       <c r="F26" s="1">
-        <v>11.05</v>
+        <v>13.04</v>
       </c>
       <c r="G26" s="1">
         <f>E26*F26</f>
-        <v>1.1050000000000002E-21</v>
+        <v>1.304E-21</v>
       </c>
       <c r="H26" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C26,Sheet1!$G:$G,0),2)</f>
-        <v>-0.32750000000000001</v>
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="I26" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C26,Sheet1!$G:$G,0),3)</f>
-        <v>0.63080000000000003</v>
+        <v>0.39489999999999997</v>
       </c>
       <c r="J26" s="9">
         <f>IFERROR(H26/I26,"")</f>
-        <v>-0.51918199112238428</v>
+        <v>7.6728285641934679E-2</v>
       </c>
       <c r="K26" s="9">
         <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.87133494104760023</v>
+        <v>7.2179369462758167E-3</v>
       </c>
       <c r="L26" s="12">
-        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
-        <v>7.4311250000000006</v>
+        <f t="shared" si="0"/>
+        <v>13.435111999999998</v>
       </c>
       <c r="M26" s="12">
         <f>F26/(1+I26-H26)</f>
-        <v>5.6426492365827512</v>
+        <v>9.5559138208998959</v>
       </c>
       <c r="N26" s="12">
         <f>L26-F26</f>
-        <v>-3.6188750000000001</v>
+        <v>0.39511199999999924</v>
       </c>
       <c r="O26" s="12">
         <f>0.5*(M26-F26)</f>
-        <v>-2.7036753817086248</v>
+        <v>-1.7420430895500516</v>
       </c>
       <c r="P26" s="14">
         <f>N26+O26</f>
-        <v>-6.3225503817086253</v>
+        <v>-1.3469310895500524</v>
       </c>
       <c r="Q26" s="12">
         <f>MAX($P$2:$P$280)-P26</f>
-        <v>109.95106041036195</v>
+        <v>104.97544111820338</v>
       </c>
       <c r="R26" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.0949554853566334E-3</v>
+        <v>9.5260376079200296E-3</v>
       </c>
       <c r="S26" s="9">
         <f>Q26/MAX($Q$2:$Q$28)</f>
-        <v>0.49710815072909353</v>
+        <v>0.79095740843850337</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -2707,10 +2684,10 @@
         <v>40</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D27" s="8">
         <v>45511</v>
@@ -2719,435 +2696,432 @@
         <v>1E-22</v>
       </c>
       <c r="F27" s="1">
-        <v>10.47</v>
+        <v>11.05</v>
       </c>
       <c r="G27" s="1">
         <f>E27*F27</f>
-        <v>1.0470000000000001E-21</v>
+        <v>1.1050000000000002E-21</v>
       </c>
       <c r="H27" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C27,Sheet1!$G:$G,0),2)</f>
-        <v>-1.03</v>
+        <v>-0.32750000000000001</v>
       </c>
       <c r="I27" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C27,Sheet1!$G:$G,0),3)</f>
-        <v>0.75839999999999996</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J27" s="9">
         <f>IFERROR(H27/I27,"")</f>
-        <v>-1.3581223628691985</v>
+        <v>-0.51918199112238428</v>
       </c>
       <c r="K27" s="9">
         <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.2793153253020062</v>
+        <v>-4.8840174704948752E-2</v>
       </c>
       <c r="L27" s="12">
-        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
-        <v>-0.31410000000000032</v>
+        <f t="shared" si="0"/>
+        <v>7.4311250000000006</v>
       </c>
       <c r="M27" s="12">
         <f>F27/(1+I27-H27)</f>
-        <v>3.7548414861569359</v>
+        <v>5.6426492365827512</v>
       </c>
       <c r="N27" s="12">
         <f>L27-F27</f>
-        <v>-10.7841</v>
+        <v>-3.6188750000000001</v>
       </c>
       <c r="O27" s="12">
         <f>0.5*(M27-F27)</f>
-        <v>-3.3575792569215324</v>
+        <v>-2.7036753817086248</v>
       </c>
       <c r="P27" s="14">
         <f>N27+O27</f>
-        <v>-14.141679256921533</v>
+        <v>-6.3225503817086253</v>
       </c>
       <c r="Q27" s="12">
         <f>MAX($P$2:$P$280)-P27</f>
-        <v>117.77018928557486</v>
+        <v>109.95106041036195</v>
       </c>
       <c r="R27" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.4911131251997202E-3</v>
+        <v>9.0949554853566334E-3</v>
       </c>
       <c r="S27" s="9">
         <f>Q27/MAX($Q$2:$Q$28)</f>
-        <v>0.53245981246807605</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.82844715745771402</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>83</v>
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
       </c>
       <c r="D28" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45610</v>
+        <v>45511</v>
       </c>
       <c r="E28" s="2">
-        <v>1E-35</v>
+        <v>1E-22</v>
       </c>
       <c r="F28" s="1">
-        <v>2742.9</v>
+        <v>10.47</v>
       </c>
       <c r="G28" s="1">
         <f>E28*F28</f>
-        <v>2.7429E-32</v>
+        <v>1.0470000000000001E-21</v>
       </c>
       <c r="H28" s="11">
-        <v>0.1</v>
+        <v>-1.03</v>
       </c>
       <c r="I28" s="11">
-        <v>0.5</v>
+        <v>0.75839999999999996</v>
       </c>
       <c r="J28" s="9">
         <f>IFERROR(H28/I28,"")</f>
-        <v>0.2</v>
+        <v>-1.3581223628691985</v>
       </c>
       <c r="K28" s="9">
         <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.33565684324447403</v>
+        <v>-0.12776046667149052</v>
       </c>
       <c r="L28" s="12">
-        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
-        <v>3017.1900000000005</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="M28" s="12">
         <f>F28/(1+I28-H28)</f>
-        <v>1959.214285714286</v>
+        <v>3.7548414861569359</v>
       </c>
       <c r="N28" s="12">
         <f>L28-F28</f>
-        <v>274.29000000000042</v>
+        <v>-10.47</v>
       </c>
       <c r="O28" s="12">
         <f>0.5*(M28-F28)</f>
-        <v>-391.84285714285704</v>
+        <v>-3.3575792569215324</v>
       </c>
       <c r="P28" s="14">
         <f>N28+O28</f>
-        <v>-117.55285714285662</v>
+        <v>-13.827579256921533</v>
       </c>
       <c r="Q28" s="12">
         <f>MAX($P$2:$P$280)-P28</f>
-        <v>221.18136717150995</v>
+        <v>117.45608928557486</v>
       </c>
       <c r="R28" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>4.5211765022890611E-3</v>
+        <v>8.5138199822800773E-3</v>
       </c>
       <c r="S28" s="9">
         <f>Q28/MAX($Q$2:$Q$28)</f>
-        <v>1</v>
+        <v>0.88499522361644889</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
+        <v>77</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="D29" s="8">
-        <v>45505</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45616</v>
       </c>
       <c r="E29" s="2">
         <v>1E-35</v>
       </c>
       <c r="F29" s="1">
-        <v>86.6</v>
+        <v>2742.9</v>
       </c>
       <c r="G29" s="1">
         <f>E29*F29</f>
-        <v>8.6599999999999988E-34</v>
+        <v>2.7429E-32</v>
       </c>
       <c r="H29" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C29,Sheet1!$G:$G,0),2)</f>
-        <v>0.2447</v>
+        <v>0.1</v>
       </c>
       <c r="I29" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C29,Sheet1!$G:$G,0),3)</f>
-        <v>0.20810000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="9">
         <f>IFERROR(H29/I29,"")</f>
-        <v>1.1758769822200865</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="9">
         <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9734557794791638</v>
+        <v>1.8814279208477357E-2</v>
       </c>
       <c r="L29" s="12">
-        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
-        <v>107.79101999999999</v>
+        <f t="shared" si="0"/>
+        <v>3017.1900000000005</v>
       </c>
       <c r="M29" s="12">
         <f>F29/(1+I29-H29)</f>
-        <v>89.889973012248291</v>
+        <v>1959.214285714286</v>
       </c>
       <c r="N29" s="12">
         <f>L29-F29</f>
-        <v>21.191019999999995</v>
+        <v>274.29000000000042</v>
       </c>
       <c r="O29" s="12">
         <f>0.5*(M29-F29)</f>
-        <v>1.6449865061241482</v>
+        <v>-391.84285714285704</v>
       </c>
       <c r="P29" s="14">
         <f>N29+O29</f>
-        <v>22.836006506124143</v>
+        <v>-117.55285714285662</v>
       </c>
       <c r="Q29" s="12">
         <f>MAX($P$2:$P$280)-P29</f>
-        <v>80.792503522529188</v>
+        <v>221.18136717150995</v>
       </c>
       <c r="R29" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.237738597518701E-2</v>
+        <v>4.5211765022890619E-3</v>
       </c>
       <c r="S29" s="9">
         <f>Q29/MAX($Q$2:$Q$28)</f>
-        <v>0.36527716848716518</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>1.6665330396265994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D30" s="8">
-        <v>45562</v>
+        <v>45505</v>
       </c>
       <c r="E30" s="2">
         <v>1E-35</v>
       </c>
       <c r="F30" s="1">
-        <v>56</v>
+        <v>86.6</v>
       </c>
       <c r="G30" s="1">
         <f>E30*F30</f>
-        <v>5.5999999999999999E-34</v>
+        <v>8.6599999999999988E-34</v>
       </c>
       <c r="H30" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.2447</v>
       </c>
       <c r="I30" s="11">
-        <v>0.19</v>
+        <v>0.20810000000000001</v>
       </c>
       <c r="J30" s="9">
         <f>IFERROR(H30/I30,"")</f>
-        <v>0.36842105263157898</v>
+        <v>1.1758769822200865</v>
       </c>
       <c r="K30" s="9">
         <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.61831523755561013</v>
+        <v>0.11061638929155236</v>
       </c>
       <c r="L30" s="12">
-        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
-        <v>59.92</v>
+        <f t="shared" si="0"/>
+        <v>107.79101999999999</v>
       </c>
       <c r="M30" s="12">
         <f>F30/(1+I30-H30)</f>
-        <v>50.000000000000007</v>
+        <v>89.889973012248291</v>
       </c>
       <c r="N30" s="12">
         <f>L30-F30</f>
-        <v>3.9200000000000017</v>
+        <v>21.191019999999995</v>
       </c>
       <c r="O30" s="12">
         <f>0.5*(M30-F30)</f>
-        <v>-2.9999999999999964</v>
+        <v>1.6449865061241482</v>
       </c>
       <c r="P30" s="14">
         <f>N30+O30</f>
-        <v>0.92000000000000526</v>
+        <v>22.836006506124143</v>
       </c>
       <c r="Q30" s="12">
         <f>MAX($P$2:$P$280)-P30</f>
-        <v>102.70851002865332</v>
+        <v>80.792503522529188</v>
       </c>
       <c r="R30" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.7362915665023565E-3</v>
+        <v>1.237738597518701E-2</v>
       </c>
       <c r="S30" s="9">
         <f>Q30/MAX($Q$2:$Q$28)</f>
-        <v>0.46436330212666782</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.60874646990511294</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D31" s="8">
-        <v>45580</v>
+        <v>45562</v>
       </c>
       <c r="E31" s="2">
         <v>1E-35</v>
       </c>
       <c r="F31" s="1">
-        <v>20.399999999999999</v>
+        <v>56</v>
       </c>
       <c r="G31" s="1">
         <f>E31*F31</f>
-        <v>2.0399999999999999E-34</v>
+        <v>5.5999999999999999E-34</v>
       </c>
       <c r="H31" s="11">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I31" s="11">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J31" s="9">
         <f>IFERROR(H31/I31,"")</f>
-        <v>0.66666666666666674</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K31" s="9">
         <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.118856144148247</v>
+        <v>3.4657882752458291E-2</v>
       </c>
       <c r="L31" s="12">
-        <v>21.2</v>
+        <f t="shared" si="0"/>
+        <v>59.92</v>
       </c>
       <c r="M31" s="12">
         <f>F31/(1+I31-H31)</f>
-        <v>19.428571428571431</v>
+        <v>50.000000000000007</v>
       </c>
       <c r="N31" s="12">
         <f>L31-F31</f>
-        <v>0.80000000000000071</v>
+        <v>3.9200000000000017</v>
       </c>
       <c r="O31" s="12">
         <f>0.5*(M31-F31)</f>
-        <v>-0.48571428571428399</v>
+        <v>-2.9999999999999964</v>
       </c>
       <c r="P31" s="14">
         <f>N31+O31</f>
-        <v>0.31428571428571672</v>
+        <v>0.92000000000000526</v>
       </c>
       <c r="Q31" s="12">
         <f>MAX($P$2:$P$280)-P31</f>
-        <v>103.31422431436761</v>
+        <v>102.70851002865332</v>
       </c>
       <c r="R31" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.6792092921993977E-3</v>
+        <v>9.7362915665023565E-3</v>
       </c>
       <c r="S31" s="9">
         <f>Q31/MAX($Q$2:$Q$28)</f>
-        <v>0.46710184332234006</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.77387678538420068</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>59</v>
+        <v>77</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D32" s="8">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="E32" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>1E-35</v>
       </c>
       <c r="F32" s="1">
-        <v>47.42</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="G32" s="1">
         <f>E32*F32</f>
-        <v>4.7420000000000006E-44</v>
+        <v>2.0399999999999999E-34</v>
       </c>
       <c r="H32" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I32" s="11">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="J32" s="9">
         <f>IFERROR(H32/I32,"")</f>
-        <v>0.17500000000000002</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="K32" s="9">
         <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.29369973783891479</v>
+        <v>6.271426402825786E-2</v>
       </c>
       <c r="L32" s="12">
-        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
-        <v>50.739400000000003</v>
+        <f t="shared" si="0"/>
+        <v>22.44</v>
       </c>
       <c r="M32" s="12">
         <f>F32/(1+I32-H32)</f>
-        <v>35.654135338345867</v>
+        <v>19.428571428571431</v>
       </c>
       <c r="N32" s="12">
         <f>L32-F32</f>
-        <v>3.3194000000000017</v>
+        <v>2.0400000000000027</v>
       </c>
       <c r="O32" s="12">
         <f>0.5*(M32-F32)</f>
-        <v>-5.8829323308270673</v>
+        <v>-0.48571428571428399</v>
       </c>
       <c r="P32" s="14">
         <f>N32+O32</f>
-        <v>-2.5635323308270657</v>
+        <v>1.5542857142857187</v>
       </c>
       <c r="Q32" s="12">
         <f>MAX($P$2:$P$280)-P32</f>
-        <v>106.19204235948038</v>
+        <v>102.0742243143676</v>
       </c>
       <c r="R32" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.4169014719088714E-3</v>
+        <v>9.7967925469627445E-3</v>
       </c>
       <c r="S32" s="9">
         <f>Q32/MAX($Q$2:$Q$28)</f>
-        <v>0.48011296664576736</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.76909763914354723</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D33" s="8">
-        <v>45507</v>
+        <v>45574</v>
       </c>
       <c r="E33" s="2">
         <v>9.9999999999999998E-46</v>
       </c>
       <c r="F33" s="1">
-        <v>41.8</v>
+        <v>47.42</v>
       </c>
       <c r="G33" s="1">
         <f>E33*F33</f>
-        <v>4.1799999999999994E-44</v>
+        <v>4.7420000000000006E-44</v>
       </c>
       <c r="H33" s="11">
         <v>7.0000000000000007E-2</v>
@@ -3161,192 +3135,190 @@
       </c>
       <c r="K33" s="9">
         <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.29369973783891479</v>
+        <v>1.646249430741769E-2</v>
       </c>
       <c r="L33" s="12">
-        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
-        <v>44.725999999999999</v>
+        <f t="shared" si="0"/>
+        <v>50.739400000000003</v>
       </c>
       <c r="M33" s="12">
         <f>F33/(1+I33-H33)</f>
-        <v>31.428571428571431</v>
+        <v>35.654135338345867</v>
       </c>
       <c r="N33" s="12">
         <f>L33-F33</f>
-        <v>2.9260000000000019</v>
+        <v>3.3194000000000017</v>
       </c>
       <c r="O33" s="12">
         <f>0.5*(M33-F33)</f>
-        <v>-5.1857142857142833</v>
+        <v>-5.8829323308270673</v>
       </c>
       <c r="P33" s="14">
         <f>N33+O33</f>
-        <v>-2.2597142857142813</v>
+        <v>-2.5635323308270657</v>
       </c>
       <c r="Q33" s="12">
         <f>MAX($P$2:$P$280)-P33</f>
-        <v>105.8882243143676</v>
+        <v>106.19204235948038</v>
       </c>
       <c r="R33" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.4439207614922058E-3</v>
+        <v>9.4169014719088714E-3</v>
       </c>
       <c r="S33" s="9">
         <f>Q33/MAX($Q$2:$Q$28)</f>
-        <v>0.47873935163923209</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.80012412166831481</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>80</v>
+        <v>39</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="D34" s="8">
-        <v>45574</v>
+        <v>45507</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-46</v>
       </c>
       <c r="F34" s="1">
-        <v>153.7552</v>
+        <v>41.8</v>
       </c>
       <c r="G34" s="1">
         <f>E34*F34</f>
-        <v>0</v>
+        <v>4.1799999999999994E-44</v>
       </c>
       <c r="H34" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I34" s="11">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="J34" s="9">
         <f>IFERROR(H34/I34,"")</f>
-        <v>0.36842105263157898</v>
+        <v>0.17500000000000002</v>
       </c>
       <c r="K34" s="9">
         <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.61831523755561013</v>
+        <v>1.646249430741769E-2</v>
       </c>
       <c r="L34" s="12">
-        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
-        <v>164.51806400000001</v>
+        <f t="shared" si="0"/>
+        <v>44.725999999999999</v>
       </c>
       <c r="M34" s="12">
         <f>F34/(1+I34-H34)</f>
-        <v>137.28142857142859</v>
+        <v>31.428571428571431</v>
       </c>
       <c r="N34" s="12">
         <f>L34-F34</f>
-        <v>10.762864000000008</v>
+        <v>2.9260000000000019</v>
       </c>
       <c r="O34" s="12">
         <f>0.5*(M34-F34)</f>
-        <v>-8.2368857142857053</v>
+        <v>-5.1857142857142833</v>
       </c>
       <c r="P34" s="14">
         <f>N34+O34</f>
-        <v>2.5259782857143023</v>
+        <v>-2.2597142857142813</v>
       </c>
       <c r="Q34" s="12">
         <f>MAX($P$2:$P$280)-P34</f>
-        <v>101.10253174293902</v>
+        <v>105.8882243143676</v>
       </c>
       <c r="R34" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8909491459875324E-3</v>
+        <v>9.4439207614922058E-3</v>
       </c>
       <c r="S34" s="9">
         <f>Q34/MAX($Q$2:$Q$28)</f>
-        <v>0.45710239083810988</v>
+        <v>0.79783494687619694</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" t="s">
-        <v>91</v>
+        <v>77</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D35" s="8">
-        <v>45627</v>
+        <v>45574</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>133.53</v>
+        <v>153.7552</v>
       </c>
       <c r="G35" s="1">
         <f>E35*F35</f>
         <v>0</v>
       </c>
       <c r="H35" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C35,Sheet1!$G:$G,0),2)</f>
-        <v>1.4E-3</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I35" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C35,Sheet1!$G:$G,0),3)</f>
-        <v>0.29289999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="J35" s="9">
         <f>IFERROR(H35/I35,"")</f>
-        <v>4.7797883236599522E-3</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K35" s="9">
         <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.0218433004824799E-3</v>
+        <v>3.4657882752458291E-2</v>
       </c>
       <c r="L35" s="12">
-        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
-        <v>133.71694200000002</v>
+        <f t="shared" si="0"/>
+        <v>164.51806400000001</v>
       </c>
       <c r="M35" s="12">
         <f>F35/(1+I35-H35)</f>
-        <v>103.39140534262486</v>
+        <v>137.28142857142859</v>
       </c>
       <c r="N35" s="12">
         <f>L35-F35</f>
-        <v>0.18694200000001615</v>
+        <v>10.762864000000008</v>
       </c>
       <c r="O35" s="12">
         <f>0.5*(M35-F35)</f>
-        <v>-15.069297328687568</v>
+        <v>-8.2368857142857053</v>
       </c>
       <c r="P35" s="14">
         <f>N35+O35</f>
-        <v>-14.882355328687552</v>
+        <v>2.5259782857143023</v>
       </c>
       <c r="Q35" s="12">
         <f>MAX($P$2:$P$280)-P35</f>
-        <v>118.51086535734088</v>
+        <v>101.10253174293902</v>
       </c>
       <c r="R35" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q35)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.4380448744909731E-3</v>
+        <v>9.8909491459875307E-3</v>
       </c>
       <c r="S35" s="9">
         <f>Q35/MAX($Q$2:$Q$28)</f>
-        <v>0.53580853971955233</v>
+        <v>0.76177623682402107</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="B36" t="s">
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D36" s="8">
         <v>45627</v>
@@ -3355,59 +3327,57 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>39.56</v>
+        <v>133.53</v>
       </c>
       <c r="G36" s="1">
         <f>E36*F36</f>
         <v>0</v>
       </c>
       <c r="H36" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C36,Sheet1!$G:$G,0),2)</f>
-        <v>1.2E-2</v>
+        <v>1.4E-3</v>
       </c>
       <c r="I36" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C36,Sheet1!$G:$G,0),3)</f>
-        <v>0.22159999999999999</v>
+        <v>0.29289999999999999</v>
       </c>
       <c r="J36" s="9">
         <f>IFERROR(H36/I36,"")</f>
-        <v>5.4151624548736468E-2</v>
+        <v>4.7797883236599522E-3</v>
       </c>
       <c r="K36" s="9">
         <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.088181676294424E-2</v>
+        <v>4.4964136039379139E-4</v>
       </c>
       <c r="L36" s="12">
-        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
-        <v>40.03472</v>
+        <f t="shared" si="0"/>
+        <v>133.71694200000002</v>
       </c>
       <c r="M36" s="12">
         <f>F36/(1+I36-H36)</f>
-        <v>32.705026455026456</v>
+        <v>103.39140534262486</v>
       </c>
       <c r="N36" s="12">
         <f>L36-F36</f>
-        <v>0.47471999999999781</v>
+        <v>0.18694200000001615</v>
       </c>
       <c r="O36" s="12">
         <f>0.5*(M36-F36)</f>
-        <v>-3.4274867724867732</v>
+        <v>-15.069297328687568</v>
       </c>
       <c r="P36" s="14">
         <f>N36+O36</f>
-        <v>-2.9527667724867754</v>
+        <v>-14.882355328687552</v>
       </c>
       <c r="Q36" s="12">
         <f>MAX($P$2:$P$280)-P36</f>
-        <v>106.58127680114009</v>
+        <v>118.51086535734088</v>
       </c>
       <c r="R36" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.3825109814156676E-3</v>
+        <v>8.4380448744909731E-3</v>
       </c>
       <c r="S36" s="9">
         <f>Q36/MAX($Q$2:$Q$28)</f>
-        <v>0.48187276425728087</v>
+        <v>0.89294263435671506</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -3415,10 +3385,10 @@
         <v>40</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D37" s="8">
         <v>45627</v>
@@ -3427,59 +3397,57 @@
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>26.63</v>
+        <v>39.56</v>
       </c>
       <c r="G37" s="1">
         <f>E37*F37</f>
         <v>0</v>
       </c>
       <c r="H37" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C37,Sheet1!$G:$G,0),2)</f>
-        <v>0.17899999999999999</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I37" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C37,Sheet1!$G:$G,0),3)</f>
-        <v>0.26369999999999999</v>
+        <v>0.22159999999999999</v>
       </c>
       <c r="J37" s="9">
         <f>IFERROR(H37/I37,"")</f>
-        <v>0.6788016685627607</v>
+        <v>5.4151624548736468E-2</v>
       </c>
       <c r="K37" s="9">
         <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1392221262942899</v>
+        <v>5.0941189192628229E-3</v>
       </c>
       <c r="L37" s="12">
-        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
-        <v>31.396769999999997</v>
+        <f t="shared" si="0"/>
+        <v>40.03472</v>
       </c>
       <c r="M37" s="12">
         <f>F37/(1+I37-H37)</f>
-        <v>24.550566977044344</v>
+        <v>32.705026455026456</v>
       </c>
       <c r="N37" s="12">
         <f>L37-F37</f>
-        <v>4.7667699999999975</v>
+        <v>0.47471999999999781</v>
       </c>
       <c r="O37" s="12">
         <f>0.5*(M37-F37)</f>
-        <v>-1.0397165114778275</v>
+        <v>-3.4274867724867732</v>
       </c>
       <c r="P37" s="14">
         <f>N37+O37</f>
-        <v>3.72705348852217</v>
+        <v>-2.9527667724867754</v>
       </c>
       <c r="Q37" s="12">
         <f>MAX($P$2:$P$280)-P37</f>
-        <v>99.90145654013115</v>
+        <v>106.58127680114009</v>
       </c>
       <c r="R37" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0009864066379178E-2</v>
+        <v>9.3825109814156676E-3</v>
       </c>
       <c r="S37" s="9">
         <f>Q37/MAX($Q$2:$Q$28)</f>
-        <v>0.45167211785369282</v>
+        <v>0.80305688253095808</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -3487,10 +3455,10 @@
         <v>40</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38" s="8">
         <v>45627</v>
@@ -3499,59 +3467,57 @@
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>22.65</v>
+        <v>26.63</v>
       </c>
       <c r="G38" s="1">
         <f>E38*F38</f>
         <v>0</v>
       </c>
       <c r="H38" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C38,Sheet1!$G:$G,0),2)</f>
-        <v>-5.4899999999999997E-2</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="I38" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C38,Sheet1!$G:$G,0),3)</f>
-        <v>0.45929999999999999</v>
+        <v>0.26369999999999999</v>
       </c>
       <c r="J38" s="9">
         <f>IFERROR(H38/I38,"")</f>
-        <v>-0.11952971913781842</v>
+        <v>0.6788016685627607</v>
       </c>
       <c r="K38" s="9">
         <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.20060484099849363</v>
+        <v>6.3855820597600435E-2</v>
       </c>
       <c r="L38" s="12">
-        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
-        <v>21.406514999999999</v>
+        <f t="shared" si="0"/>
+        <v>31.39677</v>
       </c>
       <c r="M38" s="12">
         <f>F38/(1+I38-H38)</f>
-        <v>14.958393871351207</v>
+        <v>24.550566977044344</v>
       </c>
       <c r="N38" s="12">
         <f>L38-F38</f>
-        <v>-1.2434849999999997</v>
+        <v>4.7667700000000011</v>
       </c>
       <c r="O38" s="12">
         <f>0.5*(M38-F38)</f>
-        <v>-3.8458030643243957</v>
+        <v>-1.0397165114778275</v>
       </c>
       <c r="P38" s="14">
         <f>N38+O38</f>
-        <v>-5.0892880643243954</v>
+        <v>3.7270534885221736</v>
       </c>
       <c r="Q38" s="12">
         <f>MAX($P$2:$P$280)-P38</f>
-        <v>108.71779809297772</v>
+        <v>99.90145654013115</v>
       </c>
       <c r="R38" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.1981259512336627E-3</v>
+        <v>1.0009864066379178E-2</v>
       </c>
       <c r="S38" s="9">
         <f>Q38/MAX($Q$2:$Q$28)</f>
-        <v>0.49153235411857737</v>
+        <v>0.75272650748129832</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -3578,11 +3544,9 @@
         <v>0</v>
       </c>
       <c r="H39" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C39,Sheet1!$G:$G,0),2)</f>
         <v>0.18379999999999999</v>
       </c>
       <c r="I39" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C39,Sheet1!$G:$G,0),3)</f>
         <v>0.54569999999999996</v>
       </c>
       <c r="J39" s="9">
@@ -3591,10 +3555,10 @@
       </c>
       <c r="K39" s="9">
         <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.56527146590007638</v>
+        <v>3.1684666653089048E-2</v>
       </c>
       <c r="L39" s="12">
-        <f>F39/(1-(F39*(1+H39)-F39)/(F39*(1+H39)))</f>
+        <f t="shared" si="0"/>
         <v>70.045445999999998</v>
       </c>
       <c r="M39" s="12">
@@ -3619,11 +3583,11 @@
       </c>
       <c r="R39" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q39)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.9389019593783563E-3</v>
+        <v>9.938901959378358E-3</v>
       </c>
       <c r="S39" s="9">
         <f>Q39/MAX($Q$2:$Q$28)</f>
-        <v>0.45489698165528991</v>
+        <v>0.75810084955495571</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -3650,11 +3614,9 @@
         <v>0</v>
       </c>
       <c r="H40" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C40,Sheet1!$G:$G,0),2)</f>
         <v>-2.3E-2</v>
       </c>
       <c r="I40" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C40,Sheet1!$G:$G,0),3)</f>
         <v>0.25559999999999999</v>
       </c>
       <c r="J40" s="9">
@@ -3663,11 +3625,11 @@
       </c>
       <c r="K40" s="9">
         <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.15101931523127743</v>
+        <v>-8.4649534779925508E-3</v>
       </c>
       <c r="L40" s="12">
-        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
-        <v>18.865869999999994</v>
+        <f t="shared" si="0"/>
+        <v>18.865869999999997</v>
       </c>
       <c r="M40" s="12">
         <f>F40/(1+I40-H40)</f>
@@ -3675,7 +3637,7 @@
       </c>
       <c r="N40" s="12">
         <f>L40-F40</f>
-        <v>-0.4441300000000048</v>
+        <v>-0.44413000000000125</v>
       </c>
       <c r="O40" s="12">
         <f>0.5*(M40-F40)</f>
@@ -3683,11 +3645,11 @@
       </c>
       <c r="P40" s="14">
         <f>N40+O40</f>
-        <v>-2.5479020944783404</v>
+        <v>-2.5479020944783368</v>
       </c>
       <c r="Q40" s="12">
         <f>MAX($P$2:$P$280)-P40</f>
-        <v>106.17641212313167</v>
+        <v>106.17641212313166</v>
       </c>
       <c r="R40" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q40)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
@@ -3695,7 +3657,7 @@
       </c>
       <c r="S40" s="9">
         <f>Q40/MAX($Q$2:$Q$28)</f>
-        <v>0.48004229958846234</v>
+        <v>0.80000635268250275</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -3722,11 +3684,9 @@
         <v>0</v>
       </c>
       <c r="H41" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C41,Sheet1!$G:$G,0),2)</f>
         <v>9.2100000000000001E-2</v>
       </c>
       <c r="I41" s="11">
-        <f>INDEX(Sheet1!$A:$G,MATCH(Positions!$C41,Sheet1!$G:$G,0),3)</f>
         <v>0.31609999999999999</v>
       </c>
       <c r="J41" s="9">
@@ -3735,10 +3695,10 @@
       </c>
       <c r="K41" s="9">
         <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.48899075075634391</v>
+        <v>2.7408970501435696E-2</v>
       </c>
       <c r="L41" s="12">
-        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
+        <f t="shared" si="0"/>
         <v>353.56737500000003</v>
       </c>
       <c r="M41" s="12">
@@ -3767,19 +3727,14 @@
       </c>
       <c r="S41" s="9">
         <f>Q41/MAX($Q$2:$Q$28)</f>
-        <v>0.46764932940749365</v>
+        <v>0.77935305841681124</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S41" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Energy"/>
-        <filter val="Health"/>
-        <filter val="Industrials"/>
-        <filter val="US Consumer"/>
-      </filters>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S41">
+      <sortCondition descending="1" ref="G1:G41"/>
+    </sortState>
   </autoFilter>
   <conditionalFormatting sqref="R2:R41">
     <cfRule type="iconSet" priority="1">

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A985094E-E737-4ECB-8249-EFF9EF46A1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E758EEE-48A9-4F22-BCA9-12577431D4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="161">
   <si>
     <t>Name</t>
   </si>
@@ -202,9 +202,6 @@
     <t>SEDG</t>
   </si>
   <si>
-    <t>SolarEdge</t>
-  </si>
-  <si>
     <t>SolarWinds</t>
   </si>
   <si>
@@ -403,9 +400,6 @@
     <t>Canadian Solar Inc.</t>
   </si>
   <si>
-    <t>SolarEdge Technologies, Inc.</t>
-  </si>
-  <si>
     <t>Exelon Corporation</t>
   </si>
   <si>
@@ -440,6 +434,96 @@
   </si>
   <si>
     <t>Weight</t>
+  </si>
+  <si>
+    <t>Taiwan Semiconductor Manufactur</t>
+  </si>
+  <si>
+    <t>QUALCOMM Incorporated</t>
+  </si>
+  <si>
+    <t>Apple Inc.</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation</t>
+  </si>
+  <si>
+    <t>Alphabet Inc.</t>
+  </si>
+  <si>
+    <t>ASML Holding N.V. - New York Re</t>
+  </si>
+  <si>
+    <t>NVIDIA Corporation</t>
+  </si>
+  <si>
+    <t>Applied Materials, Inc.</t>
+  </si>
+  <si>
+    <t>Palantir Technologies Inc.</t>
+  </si>
+  <si>
+    <t>YPF Sociedad Anonima</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>Yum! Brands, Inc.</t>
+  </si>
+  <si>
+    <t>Ingredion Incorporated</t>
+  </si>
+  <si>
+    <t>Yum China Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>Darling Ingredients Inc.</t>
+  </si>
+  <si>
+    <t>Aptiv PLC</t>
+  </si>
+  <si>
+    <t>ING Group, N.V.</t>
+  </si>
+  <si>
+    <t>Visa Inc.</t>
+  </si>
+  <si>
+    <t>Mastercard Incorporated</t>
+  </si>
+  <si>
+    <t>ETF</t>
+  </si>
+  <si>
+    <t>ETF1</t>
+  </si>
+  <si>
+    <t>BOTZ.UK</t>
+  </si>
+  <si>
+    <t>ETF2</t>
+  </si>
+  <si>
+    <t>BATT.NL</t>
+  </si>
+  <si>
+    <t>ETF3</t>
+  </si>
+  <si>
+    <t>VBTC.DE</t>
+  </si>
+  <si>
+    <t>ETF5</t>
+  </si>
+  <si>
+    <t>BONDS</t>
+  </si>
+  <si>
+    <t>Emerging Markets</t>
+  </si>
+  <si>
+    <t>VWO.US</t>
   </si>
 </sst>
 </file>
@@ -467,7 +551,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -510,6 +594,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -525,7 +615,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -564,6 +654,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -846,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -878,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>1</v>
@@ -893,180 +984,184 @@
         <v>4</v>
       </c>
       <c r="H1" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="N1" s="15" t="s">
+      <c r="O1" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="P1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="S1" s="15" t="s">
         <v>72</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
+        <v>37</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="D2" s="8">
-        <v>45484</v>
+        <v>45623</v>
       </c>
       <c r="E2" s="2">
-        <v>0.33389999999999997</v>
+        <v>1.9595</v>
       </c>
       <c r="F2" s="1">
-        <v>188.53</v>
+        <v>15.3</v>
       </c>
       <c r="G2" s="1">
-        <f>E2*F2</f>
-        <v>62.950166999999993</v>
+        <f t="shared" ref="G2:G46" si="0">E2*F2</f>
+        <v>29.980350000000001</v>
       </c>
       <c r="H2" s="11">
-        <v>0.20617408370020684</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),1)</f>
+        <v>8.0299999999999996E-2</v>
       </c>
       <c r="I2" s="11">
-        <v>0.37</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),2)</f>
+        <v>0.36080000000000001</v>
       </c>
       <c r="J2" s="9">
-        <f>IFERROR(H2/I2,"")</f>
-        <v>0.55722725324380229</v>
+        <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
+        <v>0.22256097560975607</v>
       </c>
       <c r="K2" s="9">
-        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.2419145625509082E-2</v>
+        <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.3972581982225623E-2</v>
       </c>
       <c r="L2" s="12">
         <f>IF((1+H2)*F2&lt;0,0,(1+H2)*F2)</f>
-        <v>227.4</v>
+        <v>16.528590000000001</v>
       </c>
       <c r="M2" s="12">
-        <f>F2/(1+I2-H2)</f>
-        <v>161.9915808365931</v>
+        <f t="shared" ref="M2:M41" si="3">F2/(1+I2-H2)</f>
+        <v>11.948457633736822</v>
       </c>
       <c r="N2" s="12">
-        <f>L2-F2</f>
-        <v>38.870000000000005</v>
+        <f t="shared" ref="N2:N41" si="4">L2-F2</f>
+        <v>1.2285900000000005</v>
       </c>
       <c r="O2" s="12">
-        <f>0.5*(M2-F2)</f>
-        <v>-13.26920958170345</v>
+        <f t="shared" ref="O2:O41" si="5">0.5*(M2-F2)</f>
+        <v>-1.6757711831315891</v>
       </c>
       <c r="P2" s="14">
-        <f>N2+O2</f>
-        <v>25.600790418296555</v>
+        <f t="shared" ref="P2:P41" si="6">N2+O2</f>
+        <v>-0.44718118313158861</v>
       </c>
       <c r="Q2" s="12">
-        <f>MAX($P$2:$P$280)-P2</f>
-        <v>78.027719610356769</v>
+        <f t="shared" ref="Q2:Q46" si="7">MAX($P$2:$P$280)-P2</f>
+        <v>124.01376058792488</v>
       </c>
       <c r="R2" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2815958290126271E-2</v>
+        <f t="shared" ref="R2:R46" si="8">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.0636212889537134E-3</v>
       </c>
       <c r="S2" s="9">
-        <f>Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.58791468015724246</v>
+        <f t="shared" ref="S2:S41" si="9">Q2/MAX($Q$2:$Q$28)</f>
+        <v>0.89536605345572151</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>40</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="D3" s="8">
-        <v>45574</v>
+        <v>45627</v>
       </c>
       <c r="E3" s="2">
-        <v>0.13370000000000001</v>
+        <v>1.8976999999999999</v>
       </c>
       <c r="F3" s="1">
-        <v>423.77</v>
+        <v>21.73</v>
       </c>
       <c r="G3" s="1">
-        <f>E3*F3</f>
-        <v>56.658049000000005</v>
+        <f t="shared" si="0"/>
+        <v>41.237020999999999</v>
       </c>
       <c r="H3" s="11">
-        <v>0.15</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C3,Sheet1!$G:$G,0),1)</f>
+        <v>-4.8300000000000003E-2</v>
       </c>
       <c r="I3" s="11">
-        <v>0.1963</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C3,Sheet1!$G:$G,0),2)</f>
+        <v>0.61990000000000001</v>
       </c>
       <c r="J3" s="9">
-        <f>IFERROR(H3/I3,"")</f>
-        <v>0.76413652572592972</v>
+        <f t="shared" si="1"/>
+        <v>-7.7915792869817715E-2</v>
       </c>
       <c r="K3" s="9">
-        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.1883389742017412E-2</v>
+        <f t="shared" si="2"/>
+        <v>-4.8916248708963496E-3</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ref="L3:L41" si="0">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
-        <v>487.33549999999997</v>
+        <f t="shared" ref="L3:L41" si="10">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
+        <v>20.680441000000002</v>
       </c>
       <c r="M3" s="12">
-        <f>F3/(1+I3-H3)</f>
-        <v>405.01768135334032</v>
+        <f t="shared" si="3"/>
+        <v>13.026016065219999</v>
       </c>
       <c r="N3" s="12">
-        <f>L3-F3</f>
-        <v>63.565499999999986</v>
+        <f t="shared" si="4"/>
+        <v>-1.0495589999999986</v>
       </c>
       <c r="O3" s="12">
-        <f>0.5*(M3-F3)</f>
-        <v>-9.3761593233298299</v>
+        <f t="shared" si="5"/>
+        <v>-4.3519919673900009</v>
       </c>
       <c r="P3" s="14">
-        <f>N3+O3</f>
-        <v>54.189340676670156</v>
+        <f t="shared" si="6"/>
+        <v>-5.4015509673899995</v>
       </c>
       <c r="Q3" s="12">
-        <f>MAX($P$2:$P$280)-P3</f>
-        <v>49.439169351983168</v>
+        <f t="shared" si="7"/>
+        <v>128.96813037218328</v>
       </c>
       <c r="R3" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.0226877051280529E-2</v>
+        <f t="shared" si="8"/>
+        <v>7.7538535847123261E-3</v>
       </c>
       <c r="S3" s="9">
-        <f>Q3/MAX($Q$2:$Q$28)</f>
-        <v>0.3725088158664186</v>
+        <f t="shared" si="9"/>
+        <v>0.93113607204125293</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1083,340 +1178,350 @@
         <v>45553</v>
       </c>
       <c r="E4" s="2">
-        <v>1.0751999999999999</v>
+        <v>1.7345999999999999</v>
       </c>
       <c r="F4" s="1">
-        <v>51.15</v>
+        <v>51.88</v>
       </c>
       <c r="G4" s="1">
-        <f>E4*F4</f>
-        <v>54.996479999999998</v>
+        <f t="shared" si="0"/>
+        <v>89.991048000000006</v>
       </c>
       <c r="H4" s="11">
-        <v>0.1346</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C4,Sheet1!$G:$G,0),1)</f>
+        <v>5.6500000000000002E-2</v>
       </c>
       <c r="I4" s="11">
-        <v>0.20530000000000001</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C4,Sheet1!$G:$G,0),2)</f>
+        <v>0.22939999999999999</v>
       </c>
       <c r="J4" s="9">
-        <f>IFERROR(H4/I4,"")</f>
-        <v>0.65562591329761322</v>
+        <f t="shared" si="1"/>
+        <v>0.24629468177855277</v>
       </c>
       <c r="K4" s="9">
-        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.1675644945471314E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.5462605802785426E-2</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" si="0"/>
-        <v>58.034790000000001</v>
+        <f t="shared" si="10"/>
+        <v>54.811220000000006</v>
       </c>
       <c r="M4" s="12">
-        <f>F4/(1+I4-H4)</f>
-        <v>47.772485289997199</v>
+        <f t="shared" si="3"/>
+        <v>44.232244863159693</v>
       </c>
       <c r="N4" s="12">
-        <f>L4-F4</f>
-        <v>6.8847900000000024</v>
+        <f t="shared" si="4"/>
+        <v>2.9312200000000033</v>
       </c>
       <c r="O4" s="12">
-        <f>0.5*(M4-F4)</f>
-        <v>-1.6887573550013997</v>
+        <f t="shared" si="5"/>
+        <v>-3.8238775684201549</v>
       </c>
       <c r="P4" s="14">
-        <f>N4+O4</f>
-        <v>5.1960326449986027</v>
+        <f t="shared" si="6"/>
+        <v>-0.89265756842015165</v>
       </c>
       <c r="Q4" s="12">
-        <f>MAX($P$2:$P$280)-P4</f>
-        <v>98.432477383654714</v>
+        <f t="shared" si="7"/>
+        <v>124.45923697321344</v>
       </c>
       <c r="R4" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0159248518173085E-2</v>
+        <f t="shared" si="8"/>
+        <v>8.0347592056604338E-3</v>
       </c>
       <c r="S4" s="9">
-        <f>Q4/MAX($Q$2:$Q$28)</f>
-        <v>0.74165820489280565</v>
+        <f t="shared" si="9"/>
+        <v>0.8985823451890953</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D5" s="8">
-        <v>45460</v>
+        <v>45511</v>
       </c>
       <c r="E5" s="2">
-        <v>0.33529999999999999</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F5" s="1">
-        <v>163.15</v>
+        <v>10.92</v>
       </c>
       <c r="G5" s="1">
-        <f>E5*F5</f>
-        <v>54.704194999999999</v>
+        <f t="shared" si="0"/>
+        <v>1.092E-18</v>
       </c>
       <c r="H5" s="11">
-        <v>0.05</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),1)</f>
+        <v>-1.4657</v>
       </c>
       <c r="I5" s="11">
-        <v>0.1711</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),2)</f>
+        <v>1.325</v>
       </c>
       <c r="J5" s="9">
-        <f>IFERROR(H5/I5,"")</f>
-        <v>0.29222676797194624</v>
+        <f t="shared" si="1"/>
+        <v>-1.1061886792452831</v>
       </c>
       <c r="K5" s="9">
-        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7490180024075623E-2</v>
+        <f t="shared" si="2"/>
+        <v>-6.9447538887797117E-2</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" si="0"/>
-        <v>171.3075</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="M5" s="12">
-        <f>F5/(1+I5-H5)</f>
-        <v>145.52671483364554</v>
+        <f t="shared" si="3"/>
+        <v>2.8807344289972825</v>
       </c>
       <c r="N5" s="12">
-        <f>L5-F5</f>
-        <v>8.1574999999999989</v>
+        <f t="shared" si="4"/>
+        <v>-10.92</v>
       </c>
       <c r="O5" s="12">
-        <f>0.5*(M5-F5)</f>
-        <v>-8.8116425831772318</v>
+        <f t="shared" si="5"/>
+        <v>-4.0196327855013587</v>
       </c>
       <c r="P5" s="14">
-        <f>N5+O5</f>
-        <v>-0.65414258317723295</v>
+        <f t="shared" si="6"/>
+        <v>-14.93963278550136</v>
       </c>
       <c r="Q5" s="12">
-        <f>MAX($P$2:$P$280)-P5</f>
-        <v>104.28265261183056</v>
+        <f t="shared" si="7"/>
+        <v>138.50621219029466</v>
       </c>
       <c r="R5" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.5893226241787512E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.2198927700520242E-3</v>
       </c>
       <c r="S5" s="9">
-        <f>Q5/MAX($Q$2:$Q$28)</f>
-        <v>0.78573746179422488</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6" s="8">
-        <v>45544</v>
+        <v>45511</v>
       </c>
       <c r="E6" s="2">
-        <v>0.35149999999999998</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>142.78</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G6" s="1">
-        <f>E6*F6</f>
-        <v>50.187169999999995</v>
+        <f t="shared" si="0"/>
+        <v>34.982874000000002</v>
       </c>
       <c r="H6" s="11">
-        <v>2.0500000000000001E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1)</f>
+        <v>0.13569999999999999</v>
       </c>
       <c r="I6" s="11">
-        <v>0.1867</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),2)</f>
+        <v>0.25069999999999998</v>
       </c>
       <c r="J6" s="9">
-        <f>IFERROR(H6/I6,"")</f>
-        <v>0.1098018211033744</v>
+        <f t="shared" si="1"/>
+        <v>0.54128440366972475</v>
       </c>
       <c r="K6" s="9">
-        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.0329210599190836E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.3982330843286453E-2</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" si="0"/>
-        <v>145.70698999999999</v>
+        <f t="shared" si="10"/>
+        <v>87.937251000000003</v>
       </c>
       <c r="M6" s="12">
-        <f>F6/(1+I6-H6)</f>
-        <v>122.43182987480705</v>
+        <f t="shared" si="3"/>
+        <v>69.443946188340817</v>
       </c>
       <c r="N6" s="12">
-        <f>L6-F6</f>
-        <v>2.9269899999999893</v>
+        <f t="shared" si="4"/>
+        <v>10.507250999999997</v>
       </c>
       <c r="O6" s="12">
-        <f>0.5*(M6-F6)</f>
-        <v>-10.174085062596475</v>
+        <f t="shared" si="5"/>
+        <v>-3.9930269058295949</v>
       </c>
       <c r="P6" s="14">
-        <f>N6+O6</f>
-        <v>-7.2470950625964861</v>
+        <f t="shared" si="6"/>
+        <v>6.5142240941704017</v>
       </c>
       <c r="Q6" s="12">
-        <f>MAX($P$2:$P$280)-P6</f>
-        <v>110.87560509124981</v>
+        <f t="shared" si="7"/>
+        <v>117.05235531062289</v>
       </c>
       <c r="R6" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.0191165060791098E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.5431856313039675E-3</v>
       </c>
       <c r="S6" s="9">
-        <f>Q6/MAX($Q$2:$Q$28)</f>
-        <v>0.83541331503696381</v>
+        <f t="shared" si="9"/>
+        <v>0.8451054538247269</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>40</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="D7" s="8">
-        <v>45482</v>
+        <v>45627</v>
       </c>
       <c r="E7" s="2">
-        <v>0.18820000000000001</v>
+        <v>0.71050000000000002</v>
       </c>
       <c r="F7" s="1">
-        <v>227.38</v>
+        <v>42.26</v>
       </c>
       <c r="G7" s="1">
-        <f>E7*F7</f>
-        <v>42.792915999999998</v>
+        <f t="shared" si="0"/>
+        <v>30.025729999999999</v>
       </c>
       <c r="H7" s="11">
-        <v>0.15</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1)</f>
+        <v>0.10249999999999999</v>
       </c>
       <c r="I7" s="11">
-        <v>0.2271</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),2)</f>
+        <v>0.54600000000000004</v>
       </c>
       <c r="J7" s="9">
-        <f>IFERROR(H7/I7,"")</f>
-        <v>0.66050198150594452</v>
+        <f t="shared" si="1"/>
+        <v>0.1877289377289377</v>
       </c>
       <c r="K7" s="9">
-        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.2134343489026939E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.1785794727342702E-2</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="0"/>
-        <v>261.48699999999997</v>
+        <f t="shared" si="10"/>
+        <v>46.591650000000001</v>
       </c>
       <c r="M7" s="12">
-        <f>F7/(1+I7-H7)</f>
-        <v>211.10389007520189</v>
+        <f t="shared" si="3"/>
+        <v>29.276065119501212</v>
       </c>
       <c r="N7" s="12">
-        <f>L7-F7</f>
-        <v>34.106999999999971</v>
+        <f t="shared" si="4"/>
+        <v>4.3316500000000033</v>
       </c>
       <c r="O7" s="12">
-        <f>0.5*(M7-F7)</f>
-        <v>-8.1380549623990532</v>
+        <f t="shared" si="5"/>
+        <v>-6.4919674402493932</v>
       </c>
       <c r="P7" s="14">
-        <f>N7+O7</f>
-        <v>25.968945037600918</v>
+        <f t="shared" si="6"/>
+        <v>-2.1603174402493899</v>
       </c>
       <c r="Q7" s="12">
-        <f>MAX($P$2:$P$280)-P7</f>
-        <v>77.659564991052406</v>
+        <f t="shared" si="7"/>
+        <v>125.72689684504267</v>
       </c>
       <c r="R7" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2876713900151458E-2</v>
+        <f t="shared" si="8"/>
+        <v>7.9537475678930613E-3</v>
       </c>
       <c r="S7" s="9">
-        <f>Q7/MAX($Q$2:$Q$28)</f>
-        <v>0.58514074922170345</v>
+        <f t="shared" si="9"/>
+        <v>0.90773471353260027</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D8" s="8">
-        <v>45511</v>
+        <v>45460</v>
       </c>
       <c r="E8" s="2">
-        <v>0.14610000000000001</v>
+        <v>0.43659999999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>273.45999999999998</v>
+        <v>160.25</v>
       </c>
       <c r="G8" s="1">
-        <f>E8*F8</f>
-        <v>39.952506</v>
+        <f t="shared" si="0"/>
+        <v>69.965149999999994</v>
       </c>
       <c r="H8" s="11">
-        <v>0.25</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),1)</f>
+        <v>7.5399999999999995E-2</v>
       </c>
       <c r="I8" s="11">
-        <v>0.26</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),2)</f>
+        <v>0.1905</v>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR(H8/I8,"")</f>
-        <v>0.96153846153846145</v>
+        <f t="shared" si="1"/>
+        <v>0.39580052493438317</v>
       </c>
       <c r="K8" s="9">
-        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.0453265425371895E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.484871962886552E-2</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="0"/>
-        <v>341.82499999999999</v>
+        <f t="shared" si="10"/>
+        <v>172.33284999999998</v>
       </c>
       <c r="M8" s="12">
-        <f>F8/(1+I8-H8)</f>
-        <v>270.75247524752473</v>
+        <f t="shared" si="3"/>
+        <v>143.70908438705047</v>
       </c>
       <c r="N8" s="12">
-        <f>L8-F8</f>
-        <v>68.365000000000009</v>
+        <f t="shared" si="4"/>
+        <v>12.082849999999979</v>
       </c>
       <c r="O8" s="12">
-        <f>0.5*(M8-F8)</f>
-        <v>-1.3537623762376256</v>
+        <f t="shared" si="5"/>
+        <v>-8.2704578064747665</v>
       </c>
       <c r="P8" s="14">
-        <f>N8+O8</f>
-        <v>67.011237623762383</v>
+        <f t="shared" si="6"/>
+        <v>3.8123921935252127</v>
       </c>
       <c r="Q8" s="12">
-        <f>MAX($P$2:$P$280)-P8</f>
-        <v>36.61727240489094</v>
+        <f t="shared" si="7"/>
+        <v>119.75418721126807</v>
       </c>
       <c r="R8" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7309516365463388E-2</v>
+        <f t="shared" si="8"/>
+        <v>8.3504387052105236E-3</v>
       </c>
       <c r="S8" s="9">
-        <f>Q8/MAX($Q$2:$Q$28)</f>
-        <v>0.27589979691389888</v>
+        <f t="shared" si="9"/>
+        <v>0.86461239043009097</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1424,349 +1529,359 @@
         <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" s="8">
-        <v>45544</v>
+        <v>45484</v>
       </c>
       <c r="E9" s="2">
-        <v>0.1928</v>
+        <v>0.4108</v>
       </c>
       <c r="F9" s="1">
-        <v>188.12</v>
+        <v>189.76</v>
       </c>
       <c r="G9" s="1">
-        <f>E9*F9</f>
-        <v>36.269536000000002</v>
+        <f t="shared" si="0"/>
+        <v>77.953407999999996</v>
       </c>
       <c r="H9" s="11">
-        <v>0.15</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C9,Sheet1!$G:$G,0),1)</f>
+        <v>0.2722</v>
       </c>
       <c r="I9" s="11">
-        <v>0.37780000000000002</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C9,Sheet1!$G:$G,0),2)</f>
+        <v>0.3296</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(H9/I9,"")</f>
-        <v>0.39703546850185278</v>
+        <f t="shared" si="1"/>
+        <v>0.82584951456310673</v>
       </c>
       <c r="K9" s="9">
-        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.7349680800312375E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.1847589253236605E-2</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="0"/>
-        <v>216.33799999999999</v>
+        <f t="shared" si="10"/>
+        <v>241.41267199999999</v>
       </c>
       <c r="M9" s="12">
-        <f>F9/(1+I9-H9)</f>
-        <v>153.21713634142367</v>
+        <f t="shared" si="3"/>
+        <v>179.4590505012294</v>
       </c>
       <c r="N9" s="12">
-        <f>L9-F9</f>
-        <v>28.217999999999989</v>
+        <f t="shared" si="4"/>
+        <v>51.652671999999995</v>
       </c>
       <c r="O9" s="12">
-        <f>0.5*(M9-F9)</f>
-        <v>-17.451431829288168</v>
+        <f t="shared" si="5"/>
+        <v>-5.150474749385296</v>
       </c>
       <c r="P9" s="14">
-        <f>N9+O9</f>
-        <v>10.766568170711821</v>
+        <f t="shared" si="6"/>
+        <v>46.502197250614699</v>
       </c>
       <c r="Q9" s="12">
-        <f>MAX($P$2:$P$280)-P9</f>
-        <v>92.861941857941503</v>
+        <f t="shared" si="7"/>
+        <v>77.064382154178588</v>
       </c>
       <c r="R9" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0768674227486882E-2</v>
+        <f t="shared" si="8"/>
+        <v>1.2976163203376542E-2</v>
       </c>
       <c r="S9" s="9">
-        <f>Q9/MAX($Q$2:$Q$28)</f>
-        <v>0.69968594646646121</v>
+        <f t="shared" si="9"/>
+        <v>0.55639657554348021</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D10" s="8">
-        <v>45511</v>
+        <v>45544</v>
       </c>
       <c r="E10" s="2">
-        <v>0.45179999999999998</v>
+        <v>0.35149999999999998</v>
       </c>
       <c r="F10" s="1">
-        <v>77.430000000000007</v>
+        <v>142.78</v>
       </c>
       <c r="G10" s="1">
-        <f>E10*F10</f>
-        <v>34.982874000000002</v>
+        <f t="shared" si="0"/>
+        <v>50.187169999999995</v>
       </c>
       <c r="H10" s="11">
-        <v>0.04</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C10,Sheet1!$G:$G,0),1)</f>
+        <v>3.5799999999999998E-2</v>
       </c>
       <c r="I10" s="11">
-        <v>0.28689999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C10,Sheet1!$G:$G,0),2)</f>
+        <v>0.20300000000000001</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(H10/I10,"")</f>
-        <v>0.13942140118508192</v>
+        <f t="shared" si="1"/>
+        <v>0.17635467980295563</v>
       </c>
       <c r="K10" s="9">
-        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.3115565847666336E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.1071708392474941E-2</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="0"/>
-        <v>80.527200000000008</v>
+        <f t="shared" si="10"/>
+        <v>147.891524</v>
       </c>
       <c r="M10" s="12">
-        <f>F10/(1+I10-H10)</f>
-        <v>62.098003047557953</v>
+        <f t="shared" si="3"/>
+        <v>122.32693625771076</v>
       </c>
       <c r="N10" s="12">
-        <f>L10-F10</f>
-        <v>3.0972000000000008</v>
+        <f t="shared" si="4"/>
+        <v>5.1115240000000028</v>
       </c>
       <c r="O10" s="12">
-        <f>0.5*(M10-F10)</f>
-        <v>-7.6659984762210271</v>
+        <f t="shared" si="5"/>
+        <v>-10.226531871144623</v>
       </c>
       <c r="P10" s="14">
-        <f>N10+O10</f>
-        <v>-4.5687984762210263</v>
+        <f t="shared" si="6"/>
+        <v>-5.1150078711446199</v>
       </c>
       <c r="Q10" s="12">
-        <f>MAX($P$2:$P$280)-P10</f>
-        <v>108.19730850487434</v>
+        <f t="shared" si="7"/>
+        <v>128.68158727593791</v>
       </c>
       <c r="R10" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.2423740832236097E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.7711195608401486E-3</v>
       </c>
       <c r="S10" s="9">
-        <f>Q10/MAX($Q$2:$Q$28)</f>
-        <v>0.81523318047954985</v>
+        <f t="shared" si="9"/>
+        <v>0.92906726161236275</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="D11" s="8">
-        <v>45623</v>
+        <v>45580</v>
       </c>
       <c r="E11" s="2">
-        <v>1.9595</v>
+        <v>0.25669999999999998</v>
       </c>
       <c r="F11" s="1">
-        <v>15.3</v>
+        <v>132.38999999999999</v>
       </c>
       <c r="G11" s="1">
-        <f>E11*F11</f>
-        <v>29.980350000000001</v>
+        <f t="shared" si="0"/>
+        <v>33.984512999999993</v>
       </c>
       <c r="H11" s="11">
-        <v>0.35</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),1)</f>
+        <v>0.1193</v>
       </c>
       <c r="I11" s="11">
-        <v>0.39532299999999998</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),2)</f>
+        <v>0.2243</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR(H11/I11,"")</f>
-        <v>0.88535197800279775</v>
+        <f t="shared" si="1"/>
+        <v>0.53187695051270623</v>
       </c>
       <c r="K11" s="9">
-        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.32862965596117E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.3391722314004703E-2</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="0"/>
-        <v>20.655000000000001</v>
+        <f t="shared" si="10"/>
+        <v>148.18412699999999</v>
       </c>
       <c r="M11" s="12">
-        <f>F11/(1+I11-H11)</f>
-        <v>14.636624277854791</v>
+        <f t="shared" si="3"/>
+        <v>119.80995475113122</v>
       </c>
       <c r="N11" s="12">
-        <f>L11-F11</f>
-        <v>5.3550000000000004</v>
+        <f t="shared" si="4"/>
+        <v>15.794127000000003</v>
       </c>
       <c r="O11" s="12">
-        <f>0.5*(M11-F11)</f>
-        <v>-0.33168786107260484</v>
+        <f t="shared" si="5"/>
+        <v>-6.2900226244343855</v>
       </c>
       <c r="P11" s="14">
-        <f>N11+O11</f>
-        <v>5.0233121389273956</v>
+        <f t="shared" si="6"/>
+        <v>9.5041043755656176</v>
       </c>
       <c r="Q11" s="12">
-        <f>MAX($P$2:$P$280)-P11</f>
-        <v>98.605197889725929</v>
+        <f t="shared" si="7"/>
+        <v>114.06247502922767</v>
       </c>
       <c r="R11" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0141453203291973E-2</v>
+        <f t="shared" si="8"/>
+        <v>8.7671252069864113E-3</v>
       </c>
       <c r="S11" s="9">
-        <f>Q11/MAX($Q$2:$Q$28)</f>
-        <v>0.7429596003659853</v>
+        <f t="shared" si="9"/>
+        <v>0.82351883879776044</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D12" s="8">
-        <v>45562</v>
+        <v>45511</v>
       </c>
       <c r="E12" s="2">
-        <v>4.0300000000000002E-2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F12" s="1">
-        <v>668.82</v>
+        <v>283.43</v>
       </c>
       <c r="G12" s="1">
-        <f>E12*F12</f>
-        <v>26.953446000000003</v>
+        <f t="shared" si="0"/>
+        <v>2.8342999999999998E-17</v>
       </c>
       <c r="H12" s="11">
-        <v>0.05</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),1)</f>
+        <v>0.17119999999999999</v>
       </c>
       <c r="I12" s="11">
-        <v>0.28000000000000003</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),2)</f>
+        <v>0.24590000000000001</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR(H12/I12,"")</f>
-        <v>0.17857142857142858</v>
+        <f t="shared" si="1"/>
+        <v>0.69621797478649849</v>
       </c>
       <c r="K12" s="9">
-        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.6798463578997641E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.3709202404201772E-2</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="0"/>
-        <v>702.26100000000008</v>
+        <f t="shared" si="10"/>
+        <v>331.953216</v>
       </c>
       <c r="M12" s="12">
-        <f>F12/(1+I12-H12)</f>
-        <v>543.7560975609756</v>
+        <f t="shared" si="3"/>
+        <v>263.72941285940266</v>
       </c>
       <c r="N12" s="12">
-        <f>L12-F12</f>
-        <v>33.441000000000031</v>
+        <f t="shared" si="4"/>
+        <v>48.523215999999991</v>
       </c>
       <c r="O12" s="12">
-        <f>0.5*(M12-F12)</f>
-        <v>-62.531951219512223</v>
+        <f t="shared" si="5"/>
+        <v>-9.8502935702986747</v>
       </c>
       <c r="P12" s="14">
-        <f>N12+O12</f>
-        <v>-29.090951219512192</v>
+        <f t="shared" si="6"/>
+        <v>38.672922429701316</v>
       </c>
       <c r="Q12" s="12">
-        <f>MAX($P$2:$P$280)-P12</f>
-        <v>132.71946124816552</v>
+        <f t="shared" si="7"/>
+        <v>84.893656975091972</v>
       </c>
       <c r="R12" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.5346900190481469E-3</v>
+        <f t="shared" si="8"/>
+        <v>1.1779443077748468E-2</v>
       </c>
       <c r="S12" s="9">
-        <f>Q12/MAX($Q$2:$Q$28)</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>0.6129231002177431</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D13" s="8">
-        <v>45580</v>
+        <v>45544</v>
       </c>
       <c r="E13" s="2">
-        <v>0.19139999999999999</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F13" s="1">
-        <v>135.82</v>
+        <v>188.12</v>
       </c>
       <c r="G13" s="1">
-        <f>E13*F13</f>
-        <v>25.995947999999999</v>
+        <f t="shared" si="0"/>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="H13" s="11">
-        <v>0.1202</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),1)</f>
+        <v>0.16470000000000001</v>
       </c>
       <c r="I13" s="11">
-        <v>0.33710000000000001</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),2)</f>
+        <v>0.372</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR(H13/I13,"")</f>
-        <v>0.35657075051913378</v>
+        <f t="shared" si="1"/>
+        <v>0.44274193548387103</v>
       </c>
       <c r="K13" s="9">
-        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.3543108289216528E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.7795744395750475E-2</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="0"/>
-        <v>152.14556400000001</v>
+        <f t="shared" si="10"/>
+        <v>219.10336400000003</v>
       </c>
       <c r="M13" s="12">
-        <f>F13/(1+I13-H13)</f>
-        <v>111.61147177253677</v>
+        <f t="shared" si="3"/>
+        <v>155.8187691543113</v>
       </c>
       <c r="N13" s="12">
-        <f>L13-F13</f>
-        <v>16.325564000000014</v>
+        <f t="shared" si="4"/>
+        <v>30.983364000000023</v>
       </c>
       <c r="O13" s="12">
-        <f>0.5*(M13-F13)</f>
-        <v>-12.10426411373161</v>
+        <f t="shared" si="5"/>
+        <v>-16.150615422844353</v>
       </c>
       <c r="P13" s="14">
-        <f>N13+O13</f>
-        <v>4.2212998862684046</v>
+        <f t="shared" si="6"/>
+        <v>14.83274857715567</v>
       </c>
       <c r="Q13" s="12">
-        <f>MAX($P$2:$P$280)-P13</f>
-        <v>99.407210142384912</v>
+        <f t="shared" si="7"/>
+        <v>108.73383082763762</v>
       </c>
       <c r="R13" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0059632481061082E-2</v>
+        <f t="shared" si="8"/>
+        <v>9.1967696933733262E-3</v>
       </c>
       <c r="S13" s="9">
-        <f>Q13/MAX($Q$2:$Q$28)</f>
-        <v>0.74900251408124929</v>
+        <f t="shared" si="9"/>
+        <v>0.78504659905252072</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -1774,139 +1889,143 @@
         <v>39</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D14" s="8">
         <v>45580</v>
       </c>
       <c r="E14" s="2">
-        <v>0.18010000000000001</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F14" s="1">
-        <v>133.19999999999999</v>
+        <v>135.82</v>
       </c>
       <c r="G14" s="1">
-        <f>E14*F14</f>
-        <v>23.989319999999999</v>
+        <f t="shared" si="0"/>
+        <v>25.995947999999999</v>
       </c>
       <c r="H14" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1)</f>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="I14" s="11">
-        <v>0.1623</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),2)</f>
+        <v>0.25819999999999999</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR(H14/I14,"")</f>
-        <v>0.43130006161429457</v>
+        <f t="shared" si="1"/>
+        <v>0.2594887683965918</v>
       </c>
       <c r="K14" s="9">
-        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.0572998909224126E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.6290942650456285E-2</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="0"/>
-        <v>142.524</v>
+        <f t="shared" si="10"/>
+        <v>144.91994</v>
       </c>
       <c r="M14" s="12">
-        <f>F14/(1+I14-H14)</f>
-        <v>121.94452073606151</v>
+        <f t="shared" si="3"/>
+        <v>114.01947615849562</v>
       </c>
       <c r="N14" s="12">
-        <f>L14-F14</f>
-        <v>9.3240000000000123</v>
+        <f t="shared" si="4"/>
+        <v>9.0999400000000037</v>
       </c>
       <c r="O14" s="12">
-        <f>0.5*(M14-F14)</f>
-        <v>-5.6277396319692414</v>
+        <f t="shared" si="5"/>
+        <v>-10.900261920752186</v>
       </c>
       <c r="P14" s="14">
-        <f>N14+O14</f>
-        <v>3.6962603680307708</v>
+        <f t="shared" si="6"/>
+        <v>-1.8003219207521823</v>
       </c>
       <c r="Q14" s="12">
-        <f>MAX($P$2:$P$280)-P14</f>
-        <v>99.932249660622546</v>
+        <f t="shared" si="7"/>
+        <v>125.36690132554547</v>
       </c>
       <c r="R14" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0006779627158154E-2</v>
+        <f t="shared" si="8"/>
+        <v>7.9765870371419495E-3</v>
       </c>
       <c r="S14" s="9">
-        <f>Q14/MAX($Q$2:$Q$28)</f>
-        <v>0.75295852409892028</v>
+        <f t="shared" si="9"/>
+        <v>0.90513558448413134</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>97</v>
+        <v>36</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="D15" s="8">
-        <v>45627</v>
+        <v>45482</v>
       </c>
       <c r="E15" s="2">
-        <v>0.9385</v>
+        <v>0.18820000000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>21.31</v>
+        <v>227.38</v>
       </c>
       <c r="G15" s="1">
-        <f>E15*F15</f>
-        <v>19.999434999999998</v>
+        <f t="shared" si="0"/>
+        <v>42.792915999999998</v>
       </c>
       <c r="H15" s="11">
-        <v>-5.4899999999999997E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1)</f>
+        <v>0.25430000000000003</v>
       </c>
       <c r="I15" s="11">
-        <v>0.45929999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),2)</f>
+        <v>0.2868</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR(H15/I15,"")</f>
-        <v>-0.11952971913781842</v>
+        <f t="shared" si="1"/>
+        <v>0.8866806136680615</v>
       </c>
       <c r="K15" s="9">
-        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-1.1244327547848975E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.566662139480677E-2</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="0"/>
-        <v>20.140080999999999</v>
+        <f t="shared" si="10"/>
+        <v>285.20273399999996</v>
       </c>
       <c r="M15" s="12">
-        <f>F15/(1+I15-H15)</f>
-        <v>14.073438119138819</v>
+        <f t="shared" si="3"/>
+        <v>220.22276029055689</v>
       </c>
       <c r="N15" s="12">
-        <f>L15-F15</f>
-        <v>-1.1699190000000002</v>
+        <f t="shared" si="4"/>
+        <v>57.822733999999969</v>
       </c>
       <c r="O15" s="12">
-        <f>0.5*(M15-F15)</f>
-        <v>-3.6182809404305898</v>
+        <f t="shared" si="5"/>
+        <v>-3.578619854721552</v>
       </c>
       <c r="P15" s="14">
-        <f>N15+O15</f>
-        <v>-4.7881999404305899</v>
+        <f t="shared" si="6"/>
+        <v>54.244114145278417</v>
       </c>
       <c r="Q15" s="12">
-        <f>MAX($P$2:$P$280)-P15</f>
-        <v>108.41670996908391</v>
+        <f t="shared" si="7"/>
+        <v>69.322465259514871</v>
       </c>
       <c r="R15" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.223670412846505E-3</v>
+        <f t="shared" si="8"/>
+        <v>1.4425338110184196E-2</v>
       </c>
       <c r="S15" s="9">
-        <f>Q15/MAX($Q$2:$Q$28)</f>
-        <v>0.81688630250209426</v>
+        <f t="shared" si="9"/>
+        <v>0.50050076572935409</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -1914,209 +2033,215 @@
         <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D16" s="8">
-        <v>45483</v>
+        <v>45574</v>
       </c>
       <c r="E16" s="2">
-        <v>0.1195</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F16" s="1">
-        <v>167.24</v>
+        <v>423.77</v>
       </c>
       <c r="G16" s="1">
-        <f>E16*F16</f>
-        <v>19.98518</v>
+        <f t="shared" si="0"/>
+        <v>56.658049000000005</v>
       </c>
       <c r="H16" s="11">
-        <v>0.13854341066730447</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),1)</f>
+        <v>0.24590000000000001</v>
       </c>
       <c r="I16" s="11">
-        <v>0.26790000000000003</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),2)</f>
+        <v>0.2702</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR(H16/I16,"")</f>
-        <v>0.51714598979956872</v>
+        <f t="shared" si="1"/>
+        <v>0.91006661732050342</v>
       </c>
       <c r="K16" s="9">
-        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.8648645218167343E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.7134816132788716E-2</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" si="0"/>
-        <v>190.41</v>
+        <f t="shared" si="10"/>
+        <v>527.97504300000003</v>
       </c>
       <c r="M16" s="12">
-        <f>F16/(1+I16-H16)</f>
-        <v>148.08431772538498</v>
+        <f t="shared" si="3"/>
+        <v>413.71668456506882</v>
       </c>
       <c r="N16" s="12">
-        <f>L16-F16</f>
-        <v>23.169999999999987</v>
+        <f t="shared" si="4"/>
+        <v>104.20504300000005</v>
       </c>
       <c r="O16" s="12">
-        <f>0.5*(M16-F16)</f>
-        <v>-9.5778411373075159</v>
+        <f t="shared" si="5"/>
+        <v>-5.0266577174655822</v>
       </c>
       <c r="P16" s="14">
-        <f>N16+O16</f>
-        <v>13.592158862692472</v>
+        <f t="shared" si="6"/>
+        <v>99.178385282534464</v>
       </c>
       <c r="Q16" s="12">
-        <f>MAX($P$2:$P$280)-P16</f>
-        <v>90.036351165960852</v>
+        <f t="shared" si="7"/>
+        <v>24.388194122258824</v>
       </c>
       <c r="R16" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1106625124742505E-2</v>
+        <f t="shared" si="8"/>
+        <v>4.1003445970085643E-2</v>
       </c>
       <c r="S16" s="9">
-        <f>Q16/MAX($Q$2:$Q$28)</f>
-        <v>0.67839599648167925</v>
+        <f t="shared" si="9"/>
+        <v>0.17608014641792177</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D17" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E17" s="2">
-        <v>2.8500000000000001E-2</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F17" s="1">
-        <v>700.32</v>
+        <v>501.56</v>
       </c>
       <c r="G17" s="1">
-        <f>E17*F17</f>
-        <v>19.959120000000002</v>
+        <f t="shared" si="0"/>
+        <v>64.901863999999989</v>
       </c>
       <c r="H17" s="11">
-        <v>0.1</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),1)</f>
+        <v>0.2</v>
       </c>
       <c r="I17" s="11">
-        <v>0.45340000000000003</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),2)</f>
+        <v>0.27160000000000001</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR(H17/I17,"")</f>
-        <v>0.22055580061755625</v>
+        <f t="shared" si="1"/>
+        <v>0.7363770250368189</v>
       </c>
       <c r="K17" s="9">
-        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0747992069339829E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.6230424376803171E-2</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="0"/>
-        <v>770.35200000000009</v>
+        <f t="shared" si="10"/>
+        <v>601.87199999999996</v>
       </c>
       <c r="M17" s="12">
-        <f>F17/(1+I17-H17)</f>
-        <v>517.45234224915032</v>
+        <f t="shared" si="3"/>
+        <v>468.04777902202312</v>
       </c>
       <c r="N17" s="12">
-        <f>L17-F17</f>
-        <v>70.032000000000039</v>
+        <f t="shared" si="4"/>
+        <v>100.31199999999995</v>
       </c>
       <c r="O17" s="12">
-        <f>0.5*(M17-F17)</f>
-        <v>-91.433828875424865</v>
+        <f t="shared" si="5"/>
+        <v>-16.75611048898844</v>
       </c>
       <c r="P17" s="14">
-        <f>N17+O17</f>
-        <v>-21.401828875424826</v>
+        <f t="shared" si="6"/>
+        <v>83.555889511011515</v>
       </c>
       <c r="Q17" s="12">
-        <f>MAX($P$2:$P$280)-P17</f>
-        <v>125.03033890407815</v>
+        <f t="shared" si="7"/>
+        <v>40.010689893781773</v>
       </c>
       <c r="R17" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.9980587812945834E-3</v>
+        <f t="shared" si="8"/>
+        <v>2.499332060143792E-2</v>
       </c>
       <c r="S17" s="9">
-        <f>Q17/MAX($Q$2:$Q$28)</f>
-        <v>0.94206484661876488</v>
+        <f t="shared" si="9"/>
+        <v>0.28887289068890865</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D18" s="8">
-        <v>45511</v>
+        <v>45483</v>
       </c>
       <c r="E18" s="2">
-        <v>3.2899999999999999E-2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F18" s="1">
-        <v>455.4</v>
+        <v>167.24</v>
       </c>
       <c r="G18" s="1">
-        <f>E18*F18</f>
-        <v>14.982659999999999</v>
+        <f t="shared" si="0"/>
+        <v>1.6724000000000001E-17</v>
       </c>
       <c r="H18" s="11">
-        <v>0.25</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),1)</f>
+        <v>0.18140000000000001</v>
       </c>
       <c r="I18" s="11">
-        <v>0.29699999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),2)</f>
+        <v>0.2843</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR(H18/I18,"")</f>
-        <v>0.84175084175084181</v>
+        <f t="shared" si="1"/>
+        <v>0.63805838902567713</v>
       </c>
       <c r="K18" s="9">
-        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.9184676803355877E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.0057890318293862E-2</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="0"/>
-        <v>569.25</v>
+        <f t="shared" si="10"/>
+        <v>197.577336</v>
       </c>
       <c r="M18" s="12">
-        <f>F18/(1+I18-H18)</f>
-        <v>434.95702005730658</v>
+        <f t="shared" si="3"/>
+        <v>151.63659443285883</v>
       </c>
       <c r="N18" s="12">
-        <f>L18-F18</f>
-        <v>113.85000000000002</v>
+        <f t="shared" si="4"/>
+        <v>30.337335999999993</v>
       </c>
       <c r="O18" s="12">
-        <f>0.5*(M18-F18)</f>
-        <v>-10.221489971346699</v>
+        <f t="shared" si="5"/>
+        <v>-7.8017027835705903</v>
       </c>
       <c r="P18" s="14">
-        <f>N18+O18</f>
-        <v>103.62851002865332</v>
+        <f t="shared" si="6"/>
+        <v>22.535633216429403</v>
       </c>
       <c r="Q18" s="12">
-        <f>MAX($P$2:$P$280)-P18</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>101.03094618836388</v>
       </c>
       <c r="R18" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>9.8979573856072013E-3</v>
       </c>
       <c r="S18" s="9">
-        <f>Q18/MAX($Q$2:$Q$28)</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>0.72943259793688353</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -2124,209 +2249,215 @@
         <v>40</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
       </c>
       <c r="D19" s="8">
         <v>45511</v>
       </c>
       <c r="E19" s="2">
-        <v>1</v>
+        <v>0.25169999999999998</v>
       </c>
       <c r="F19" s="1">
-        <v>10.92</v>
+        <v>178.56</v>
       </c>
       <c r="G19" s="1">
-        <f>E19*F19</f>
-        <v>10.92</v>
+        <f t="shared" si="0"/>
+        <v>44.943551999999997</v>
       </c>
       <c r="H19" s="11">
-        <v>-1.7947</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),1)</f>
+        <v>9.6799999999999997E-2</v>
       </c>
       <c r="I19" s="11">
-        <v>1.4319</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),2)</f>
+        <v>0.4829</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR(H19/I19,"")</f>
-        <v>-1.253369648718486</v>
+        <f t="shared" si="1"/>
+        <v>0.20045558086560364</v>
       </c>
       <c r="K19" s="9">
-        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.1179062326121039</v>
+        <f t="shared" si="2"/>
+        <v>1.2584785044932769E-2</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>195.84460799999999</v>
       </c>
       <c r="M19" s="12">
-        <f>F19/(1+I19-H19)</f>
-        <v>2.5836369658827429</v>
+        <f t="shared" si="3"/>
+        <v>128.82187432364188</v>
       </c>
       <c r="N19" s="12">
-        <f>L19-F19</f>
-        <v>-10.92</v>
+        <f t="shared" si="4"/>
+        <v>17.284607999999992</v>
       </c>
       <c r="O19" s="12">
-        <f>0.5*(M19-F19)</f>
-        <v>-4.1681815170586285</v>
+        <f t="shared" si="5"/>
+        <v>-24.869062838179062</v>
       </c>
       <c r="P19" s="14">
-        <f>N19+O19</f>
-        <v>-15.088181517058629</v>
+        <f t="shared" si="6"/>
+        <v>-7.5844548381790702</v>
       </c>
       <c r="Q19" s="12">
-        <f>MAX($P$2:$P$280)-P19</f>
-        <v>118.71669154571195</v>
+        <f t="shared" si="7"/>
+        <v>131.15103424297234</v>
       </c>
       <c r="R19" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.4234153342704066E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.6247969051268421E-3</v>
       </c>
       <c r="S19" s="9">
-        <f>Q19/MAX($Q$2:$Q$28)</f>
-        <v>0.8944934708838933</v>
+        <f t="shared" si="9"/>
+        <v>0.94689640391568153</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>23</v>
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D20" s="8">
-        <v>45482</v>
+        <v>45562</v>
       </c>
       <c r="E20" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F20" s="1">
-        <v>147.01</v>
+        <v>668.82</v>
       </c>
       <c r="G20" s="1">
-        <f>E20*F20</f>
-        <v>1.4700999999999999E-17</v>
+        <f t="shared" si="0"/>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="H20" s="11">
-        <v>0.15</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),1)</f>
+        <v>0.1993</v>
       </c>
       <c r="I20" s="11">
-        <v>0.52380000000000004</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),2)</f>
+        <v>0.27200000000000002</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR(H20/I20,"")</f>
-        <v>0.28636884306987398</v>
+        <f t="shared" si="1"/>
+        <v>0.73272058823529407</v>
       </c>
       <c r="K20" s="9">
-        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6939116850626225E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.6000869923996872E-2</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="0"/>
-        <v>169.06149999999997</v>
+        <f t="shared" si="10"/>
+        <v>802.11582600000008</v>
       </c>
       <c r="M20" s="12">
-        <f>F20/(1+I20-H20)</f>
-        <v>107.00975396709855</v>
+        <f t="shared" si="3"/>
+        <v>623.49212268108522</v>
       </c>
       <c r="N20" s="12">
-        <f>L20-F20</f>
-        <v>22.051499999999976</v>
+        <f t="shared" si="4"/>
+        <v>133.29582600000003</v>
       </c>
       <c r="O20" s="12">
-        <f>0.5*(M20-F20)</f>
-        <v>-20.000123016450722</v>
+        <f t="shared" si="5"/>
+        <v>-22.663938659457415</v>
       </c>
       <c r="P20" s="14">
-        <f>N20+O20</f>
-        <v>2.0513769835492539</v>
+        <f t="shared" si="6"/>
+        <v>110.63188734054262</v>
       </c>
       <c r="Q20" s="12">
-        <f>MAX($P$2:$P$280)-P20</f>
-        <v>101.57713304510406</v>
+        <f t="shared" si="7"/>
+        <v>12.934692064250669</v>
       </c>
       <c r="R20" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8447354244184312E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.7311465555784914E-2</v>
       </c>
       <c r="S20" s="9">
-        <f>Q20/MAX($Q$2:$Q$28)</f>
-        <v>0.76535221051847124</v>
+        <f t="shared" si="9"/>
+        <v>9.3387089717532706E-2</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>47</v>
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D21" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E21" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F21" s="1">
-        <v>187.36</v>
+        <v>700.32</v>
       </c>
       <c r="G21" s="1">
-        <f>E21*F21</f>
-        <v>1.8736000000000003E-20</v>
+        <f t="shared" si="0"/>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="H21" s="11">
-        <v>0.2823</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),1)</f>
+        <v>0.23749999999999999</v>
       </c>
       <c r="I21" s="11">
-        <v>0.5212</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),2)</f>
+        <v>0.37659999999999999</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR(H21/I21,"")</f>
-        <v>0.54163468917881807</v>
+        <f t="shared" si="1"/>
+        <v>0.63064259160913438</v>
       </c>
       <c r="K21" s="9">
-        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.0952331356035663E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.9592319761360704E-2</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="0"/>
-        <v>240.25172800000001</v>
+        <f t="shared" si="10"/>
+        <v>866.64600000000007</v>
       </c>
       <c r="M21" s="12">
-        <f>F21/(1+I21-H21)</f>
-        <v>151.230930664299</v>
+        <f t="shared" si="3"/>
+        <v>614.80115880958658</v>
       </c>
       <c r="N21" s="12">
-        <f>L21-F21</f>
-        <v>52.891728000000001</v>
+        <f t="shared" si="4"/>
+        <v>166.32600000000002</v>
       </c>
       <c r="O21" s="12">
-        <f>0.5*(M21-F21)</f>
-        <v>-18.064534667850509</v>
+        <f t="shared" si="5"/>
+        <v>-42.759420595206734</v>
       </c>
       <c r="P21" s="14">
-        <f>N21+O21</f>
-        <v>34.827193332149491</v>
+        <f t="shared" si="6"/>
+        <v>123.56657940479329</v>
       </c>
       <c r="Q21" s="12">
-        <f>MAX($P$2:$P$280)-P21</f>
-        <v>68.801316696503832</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="R21" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.4534605557204625E-2</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="S21" s="9">
-        <f>Q21/MAX($Q$2:$Q$28)</f>
-        <v>0.51839659421051798</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -2334,279 +2465,287 @@
         <v>36</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D22" s="8">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="E22" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F22" s="1">
-        <v>169.34</v>
+        <v>147.01</v>
       </c>
       <c r="G22" s="1">
-        <f>E22*F22</f>
-        <v>1.6934000000000002E-20</v>
+        <f t="shared" si="0"/>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H22" s="11">
-        <v>0.1</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),1)</f>
+        <v>0.56320000000000003</v>
       </c>
       <c r="I22" s="11">
-        <v>0.4259</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),2)</f>
+        <v>0.50019999999999998</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR(H22/I22,"")</f>
-        <v>0.23479690068091102</v>
+        <f t="shared" si="1"/>
+        <v>1.1259496201519394</v>
       </c>
       <c r="K22" s="9">
-        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.2087672233478937E-2</v>
+        <f t="shared" si="2"/>
+        <v>7.0688148864940251E-2</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" si="0"/>
-        <v>186.27400000000003</v>
+        <f t="shared" si="10"/>
+        <v>229.80603200000002</v>
       </c>
       <c r="M22" s="12">
-        <f>F22/(1+I22-H22)</f>
-        <v>127.71702239987934</v>
+        <f t="shared" si="3"/>
+        <v>156.89434364994665</v>
       </c>
       <c r="N22" s="12">
-        <f>L22-F22</f>
-        <v>16.934000000000026</v>
+        <f t="shared" si="4"/>
+        <v>82.796032000000025</v>
       </c>
       <c r="O22" s="12">
-        <f>0.5*(M22-F22)</f>
-        <v>-20.811488800060332</v>
+        <f t="shared" si="5"/>
+        <v>4.9421718249733289</v>
       </c>
       <c r="P22" s="14">
-        <f>N22+O22</f>
-        <v>-3.8774888000603056</v>
+        <f t="shared" si="6"/>
+        <v>87.738203824973354</v>
       </c>
       <c r="Q22" s="12">
-        <f>MAX($P$2:$P$280)-P22</f>
-        <v>107.50599882871363</v>
+        <f t="shared" si="7"/>
+        <v>35.828375579819934</v>
       </c>
       <c r="R22" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.3018065121488955E-3</v>
+        <f t="shared" si="8"/>
+        <v>2.7910838373683973E-2</v>
       </c>
       <c r="S22" s="9">
-        <f>Q22/MAX($Q$2:$Q$28)</f>
-        <v>0.81002437636251035</v>
+        <f t="shared" si="9"/>
+        <v>0.25867702981145047</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
       </c>
       <c r="D23" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E23" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F23" s="1">
-        <v>113.58</v>
+        <v>169.34</v>
       </c>
       <c r="G23" s="1">
-        <f>E23*F23</f>
-        <v>1.1358E-20</v>
+        <f t="shared" si="0"/>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="H23" s="11">
-        <v>7.2800000000000004E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),1)</f>
+        <v>0.25890000000000002</v>
       </c>
       <c r="I23" s="11">
-        <v>0.18940000000000001</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),2)</f>
+        <v>0.41639999999999999</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR(H23/I23,"")</f>
-        <v>0.38437170010559663</v>
+        <f t="shared" si="1"/>
+        <v>0.62175792507204619</v>
       </c>
       <c r="K23" s="9">
-        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.6158382428119099E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.90345322551095E-2</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="0"/>
-        <v>121.848624</v>
+        <f t="shared" si="10"/>
+        <v>213.18212600000004</v>
       </c>
       <c r="M23" s="12">
-        <f>F23/(1+I23-H23)</f>
-        <v>101.71950564212788</v>
+        <f t="shared" si="3"/>
+        <v>146.2980561555076</v>
       </c>
       <c r="N23" s="12">
-        <f>L23-F23</f>
-        <v>8.2686240000000026</v>
+        <f t="shared" si="4"/>
+        <v>43.842126000000036</v>
       </c>
       <c r="O23" s="12">
-        <f>0.5*(M23-F23)</f>
-        <v>-5.9302471789360567</v>
+        <f t="shared" si="5"/>
+        <v>-11.520971922246204</v>
       </c>
       <c r="P23" s="14">
-        <f>N23+O23</f>
-        <v>2.338376821063946</v>
+        <f t="shared" si="6"/>
+        <v>32.321154077753832</v>
       </c>
       <c r="Q23" s="12">
-        <f>MAX($P$2:$P$280)-P23</f>
-        <v>101.29013320758938</v>
+        <f t="shared" si="7"/>
+        <v>91.245425327039456</v>
       </c>
       <c r="R23" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8726299229022329E-3</v>
+        <f t="shared" si="8"/>
+        <v>1.0959453544282646E-2</v>
       </c>
       <c r="S23" s="9">
-        <f>Q23/MAX($Q$2:$Q$28)</f>
-        <v>0.76318975570728098</v>
+        <f t="shared" si="9"/>
+        <v>0.658782186619014</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>87</v>
+        <v>40</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="D24" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E24" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F24" s="1">
-        <v>64.349999999999994</v>
+        <v>113.58</v>
       </c>
       <c r="G24" s="1">
-        <f>E24*F24</f>
-        <v>6.4349999999999995E-21</v>
+        <f t="shared" si="0"/>
+        <v>1.1357999999999999E-17</v>
       </c>
       <c r="H24" s="11">
-        <v>0.15</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),1)</f>
+        <v>9.0899999999999995E-2</v>
       </c>
       <c r="I24" s="11">
-        <v>0.67300000000000004</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),2)</f>
+        <v>0.2077</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR(H24/I24,"")</f>
-        <v>0.22288261515601782</v>
+        <f t="shared" si="1"/>
+        <v>0.43765045739046698</v>
       </c>
       <c r="K24" s="9">
-        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0966878761304632E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.7476096735706362E-2</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="0"/>
-        <v>74.002499999999984</v>
+        <f t="shared" si="10"/>
+        <v>123.904422</v>
       </c>
       <c r="M24" s="12">
-        <f>F24/(1+I24-H24)</f>
-        <v>42.252133946158892</v>
+        <f t="shared" si="3"/>
+        <v>101.70128939828079</v>
       </c>
       <c r="N24" s="12">
-        <f>L24-F24</f>
-        <v>9.6524999999999892</v>
+        <f t="shared" si="4"/>
+        <v>10.324421999999998</v>
       </c>
       <c r="O24" s="12">
-        <f>0.5*(M24-F24)</f>
-        <v>-11.048933026920551</v>
+        <f t="shared" si="5"/>
+        <v>-5.9393553008596029</v>
       </c>
       <c r="P24" s="14">
-        <f>N24+O24</f>
-        <v>-1.3964330269205618</v>
+        <f t="shared" si="6"/>
+        <v>4.3850666991403955</v>
       </c>
       <c r="Q24" s="12">
-        <f>MAX($P$2:$P$280)-P24</f>
-        <v>105.02494305557389</v>
+        <f t="shared" si="7"/>
+        <v>119.18151270565289</v>
       </c>
       <c r="R24" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.5215476524548141E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.3905630772596242E-3</v>
       </c>
       <c r="S24" s="9">
-        <f>Q24/MAX($Q$2:$Q$28)</f>
-        <v>0.79133039019193252</v>
+        <f t="shared" si="9"/>
+        <v>0.86047774190740678</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
       </c>
       <c r="D25" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E25" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>20.82</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G25" s="1">
-        <f>E25*F25</f>
-        <v>2.0820000000000001E-21</v>
+        <f t="shared" si="0"/>
+        <v>6.4349999999999993E-18</v>
       </c>
       <c r="H25" s="11">
-        <v>-0.1696</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),1)</f>
+        <v>0.49509999999999998</v>
       </c>
       <c r="I25" s="11">
-        <v>0.70540000000000003</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),2)</f>
+        <v>0.70050000000000001</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR(H25/I25,"")</f>
-        <v>-0.24043096115679047</v>
+        <f t="shared" si="1"/>
+        <v>0.70678087080656671</v>
       </c>
       <c r="K25" s="9">
-        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.2617676167832147E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.4372350695162349E-2</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="0"/>
-        <v>17.288928000000002</v>
+        <f t="shared" si="10"/>
+        <v>96.209684999999979</v>
       </c>
       <c r="M25" s="12">
-        <f>F25/(1+I25-H25)</f>
-        <v>11.104000000000001</v>
+        <f t="shared" si="3"/>
+        <v>53.384768541562963</v>
       </c>
       <c r="N25" s="12">
-        <f>L25-F25</f>
-        <v>-3.5310719999999982</v>
+        <f t="shared" si="4"/>
+        <v>31.859684999999985</v>
       </c>
       <c r="O25" s="12">
-        <f>0.5*(M25-F25)</f>
-        <v>-4.8579999999999997</v>
+        <f t="shared" si="5"/>
+        <v>-5.4826157292185158</v>
       </c>
       <c r="P25" s="14">
-        <f>N25+O25</f>
-        <v>-8.3890719999999988</v>
+        <f t="shared" si="6"/>
+        <v>26.377069270781469</v>
       </c>
       <c r="Q25" s="12">
-        <f>MAX($P$2:$P$280)-P25</f>
-        <v>112.01758202865332</v>
+        <f t="shared" si="7"/>
+        <v>97.189510134011812</v>
       </c>
       <c r="R25" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9271700200081704E-3</v>
+        <f t="shared" si="8"/>
+        <v>1.0289176255967633E-2</v>
       </c>
       <c r="S25" s="9">
-        <f>Q25/MAX($Q$2:$Q$28)</f>
-        <v>0.84401775726920125</v>
+        <f t="shared" si="9"/>
+        <v>0.70169784154144987</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -2614,69 +2753,71 @@
         <v>40</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="D26" s="8">
         <v>45511</v>
       </c>
       <c r="E26" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>13.04</v>
+        <v>20.82</v>
       </c>
       <c r="G26" s="1">
-        <f>E26*F26</f>
-        <v>1.304E-21</v>
+        <f t="shared" si="0"/>
+        <v>2.0820000000000002E-18</v>
       </c>
       <c r="H26" s="11">
-        <v>3.0300000000000001E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),1)</f>
+        <v>-1.9199999999999998E-2</v>
       </c>
       <c r="I26" s="11">
-        <v>0.39489999999999997</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),2)</f>
+        <v>0.71699999999999997</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR(H26/I26,"")</f>
-        <v>7.6728285641934679E-2</v>
+        <f t="shared" si="1"/>
+        <v>-2.6778242677824266E-2</v>
       </c>
       <c r="K26" s="9">
-        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.2179369462758167E-3</v>
+        <f t="shared" si="2"/>
+        <v>-1.6811626123166177E-3</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="0"/>
-        <v>13.435111999999998</v>
+        <f t="shared" si="10"/>
+        <v>20.420256000000002</v>
       </c>
       <c r="M26" s="12">
-        <f>F26/(1+I26-H26)</f>
-        <v>9.5559138208998959</v>
+        <f t="shared" si="3"/>
+        <v>11.991706024651537</v>
       </c>
       <c r="N26" s="12">
-        <f>L26-F26</f>
-        <v>0.39511199999999924</v>
+        <f t="shared" si="4"/>
+        <v>-0.39974399999999832</v>
       </c>
       <c r="O26" s="12">
-        <f>0.5*(M26-F26)</f>
-        <v>-1.7420430895500516</v>
+        <f t="shared" si="5"/>
+        <v>-4.4141469876742319</v>
       </c>
       <c r="P26" s="14">
-        <f>N26+O26</f>
-        <v>-1.3469310895500524</v>
+        <f t="shared" si="6"/>
+        <v>-4.8138909876742302</v>
       </c>
       <c r="Q26" s="12">
-        <f>MAX($P$2:$P$280)-P26</f>
-        <v>104.97544111820338</v>
+        <f t="shared" si="7"/>
+        <v>128.38047039246752</v>
       </c>
       <c r="R26" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.5260376079200296E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.7893467514407316E-3</v>
       </c>
       <c r="S26" s="9">
-        <f>Q26/MAX($Q$2:$Q$28)</f>
-        <v>0.79095740843850337</v>
+        <f t="shared" si="9"/>
+        <v>0.92689323000245416</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -2684,69 +2825,71 @@
         <v>40</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D27" s="8">
         <v>45511</v>
       </c>
       <c r="E27" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F27" s="1">
-        <v>11.05</v>
+        <v>13.04</v>
       </c>
       <c r="G27" s="1">
-        <f>E27*F27</f>
-        <v>1.1050000000000002E-21</v>
+        <f t="shared" si="0"/>
+        <v>1.304E-18</v>
       </c>
       <c r="H27" s="11">
-        <v>-0.32750000000000001</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),1)</f>
+        <v>1.61E-2</v>
       </c>
       <c r="I27" s="11">
-        <v>0.63080000000000003</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),2)</f>
+        <v>0.42009999999999997</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR(H27/I27,"")</f>
-        <v>-0.51918199112238428</v>
+        <f t="shared" si="1"/>
+        <v>3.8324208521780527E-2</v>
       </c>
       <c r="K27" s="9">
-        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-4.8840174704948752E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4060289276113997E-3</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="0"/>
-        <v>7.4311250000000006</v>
+        <f t="shared" si="10"/>
+        <v>13.249943999999999</v>
       </c>
       <c r="M27" s="12">
-        <f>F27/(1+I27-H27)</f>
-        <v>5.6426492365827512</v>
+        <f t="shared" si="3"/>
+        <v>9.2877492877492873</v>
       </c>
       <c r="N27" s="12">
-        <f>L27-F27</f>
-        <v>-3.6188750000000001</v>
+        <f t="shared" si="4"/>
+        <v>0.20994400000000013</v>
       </c>
       <c r="O27" s="12">
-        <f>0.5*(M27-F27)</f>
-        <v>-2.7036753817086248</v>
+        <f t="shared" si="5"/>
+        <v>-1.8761253561253559</v>
       </c>
       <c r="P27" s="14">
-        <f>N27+O27</f>
-        <v>-6.3225503817086253</v>
+        <f t="shared" si="6"/>
+        <v>-1.6661813561253558</v>
       </c>
       <c r="Q27" s="12">
-        <f>MAX($P$2:$P$280)-P27</f>
-        <v>109.95106041036195</v>
+        <f t="shared" si="7"/>
+        <v>125.23276076091864</v>
       </c>
       <c r="R27" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.0949554853566334E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.9851309986617314E-3</v>
       </c>
       <c r="S27" s="9">
-        <f>Q27/MAX($Q$2:$Q$28)</f>
-        <v>0.82844715745771402</v>
+        <f t="shared" si="9"/>
+        <v>0.90416710399141131</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -2754,140 +2897,142 @@
         <v>40</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D28" s="8">
         <v>45511</v>
       </c>
       <c r="E28" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F28" s="1">
-        <v>10.47</v>
+        <v>11.05</v>
       </c>
       <c r="G28" s="1">
-        <f>E28*F28</f>
-        <v>1.0470000000000001E-21</v>
+        <f t="shared" si="0"/>
+        <v>1.1050000000000001E-18</v>
       </c>
       <c r="H28" s="11">
-        <v>-1.03</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),1)</f>
+        <v>-0.1114</v>
       </c>
       <c r="I28" s="11">
-        <v>0.75839999999999996</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),2)</f>
+        <v>0.58130000000000004</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR(H28/I28,"")</f>
-        <v>-1.3581223628691985</v>
+        <f t="shared" si="1"/>
+        <v>-0.19163942886633406</v>
       </c>
       <c r="K28" s="9">
-        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.12776046667149052</v>
+        <f t="shared" si="2"/>
+        <v>-1.203129894414594E-2</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>9.8190300000000015</v>
       </c>
       <c r="M28" s="12">
-        <f>F28/(1+I28-H28)</f>
-        <v>3.7548414861569359</v>
+        <f t="shared" si="3"/>
+        <v>6.528032138004372</v>
       </c>
       <c r="N28" s="12">
-        <f>L28-F28</f>
-        <v>-10.47</v>
+        <f t="shared" si="4"/>
+        <v>-1.2309699999999992</v>
       </c>
       <c r="O28" s="12">
-        <f>0.5*(M28-F28)</f>
-        <v>-3.3575792569215324</v>
+        <f t="shared" si="5"/>
+        <v>-2.2609839309978144</v>
       </c>
       <c r="P28" s="14">
-        <f>N28+O28</f>
-        <v>-13.827579256921533</v>
+        <f t="shared" si="6"/>
+        <v>-3.4919539309978136</v>
       </c>
       <c r="Q28" s="12">
-        <f>MAX($P$2:$P$280)-P28</f>
-        <v>117.45608928557486</v>
+        <f t="shared" si="7"/>
+        <v>127.0585333357911</v>
       </c>
       <c r="R28" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.5138199822800773E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.8703883457964495E-3</v>
       </c>
       <c r="S28" s="9">
-        <f>Q28/MAX($Q$2:$Q$28)</f>
-        <v>0.88499522361644889</v>
+        <f t="shared" si="9"/>
+        <v>0.91734898620449223</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>83</v>
       </c>
       <c r="D29" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45616</v>
+        <v>45666</v>
       </c>
       <c r="E29" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F29" s="1">
         <v>2742.9</v>
       </c>
       <c r="G29" s="1">
-        <f>E29*F29</f>
-        <v>2.7429E-32</v>
+        <f t="shared" si="0"/>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="H29" s="11">
-        <v>0.1</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I29" s="11">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR(H29/I29,"")</f>
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.28846153846153844</v>
       </c>
       <c r="K29" s="9">
-        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8814279208477357E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.8109879702990009E-2</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="0"/>
-        <v>3017.1900000000005</v>
+        <f t="shared" si="10"/>
+        <v>2948.6174999999998</v>
       </c>
       <c r="M29" s="12">
-        <f>F29/(1+I29-H29)</f>
-        <v>1959.214285714286</v>
+        <f t="shared" si="3"/>
+        <v>2314.6835443037976</v>
       </c>
       <c r="N29" s="12">
-        <f>L29-F29</f>
-        <v>274.29000000000042</v>
+        <f t="shared" si="4"/>
+        <v>205.71749999999975</v>
       </c>
       <c r="O29" s="12">
-        <f>0.5*(M29-F29)</f>
-        <v>-391.84285714285704</v>
+        <f t="shared" si="5"/>
+        <v>-214.10822784810125</v>
       </c>
       <c r="P29" s="14">
-        <f>N29+O29</f>
-        <v>-117.55285714285662</v>
+        <f t="shared" si="6"/>
+        <v>-8.3907278481015055</v>
       </c>
       <c r="Q29" s="12">
-        <f>MAX($P$2:$P$280)-P29</f>
-        <v>221.18136717150995</v>
+        <f t="shared" si="7"/>
+        <v>131.95730725289479</v>
       </c>
       <c r="R29" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>4.5211765022890619E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.5782085950231648E-3</v>
       </c>
       <c r="S29" s="9">
-        <f>Q29/MAX($Q$2:$Q$28)</f>
-        <v>1.6665330396265994</v>
+        <f t="shared" si="9"/>
+        <v>0.95271760859070864</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -2895,209 +3040,213 @@
         <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" t="s">
         <v>56</v>
-      </c>
-      <c r="C30" t="s">
-        <v>57</v>
       </c>
       <c r="D30" s="8">
         <v>45505</v>
       </c>
       <c r="E30" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F30" s="1">
         <v>86.6</v>
       </c>
       <c r="G30" s="1">
-        <f>E30*F30</f>
-        <v>8.6599999999999988E-34</v>
+        <f t="shared" si="0"/>
+        <v>8.6599999999999986E-18</v>
       </c>
       <c r="H30" s="11">
-        <v>0.2447</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),1)</f>
+        <v>0.1913</v>
       </c>
       <c r="I30" s="11">
-        <v>0.20810000000000001</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),2)</f>
+        <v>0.2109</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR(H30/I30,"")</f>
-        <v>1.1758769822200865</v>
+        <f t="shared" si="1"/>
+        <v>0.90706495969653866</v>
       </c>
       <c r="K30" s="9">
-        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.11061638929155236</v>
+        <f t="shared" si="2"/>
+        <v>5.6946369316726225E-2</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" si="0"/>
-        <v>107.79101999999999</v>
+        <f t="shared" si="10"/>
+        <v>103.16658</v>
       </c>
       <c r="M30" s="12">
-        <f>F30/(1+I30-H30)</f>
-        <v>89.889973012248291</v>
+        <f t="shared" si="3"/>
+        <v>84.935268732836391</v>
       </c>
       <c r="N30" s="12">
-        <f>L30-F30</f>
-        <v>21.191019999999995</v>
+        <f t="shared" si="4"/>
+        <v>16.566580000000002</v>
       </c>
       <c r="O30" s="12">
-        <f>0.5*(M30-F30)</f>
-        <v>1.6449865061241482</v>
+        <f t="shared" si="5"/>
+        <v>-0.83236563358180149</v>
       </c>
       <c r="P30" s="14">
-        <f>N30+O30</f>
-        <v>22.836006506124143</v>
+        <f t="shared" si="6"/>
+        <v>15.7342143664182</v>
       </c>
       <c r="Q30" s="12">
-        <f>MAX($P$2:$P$280)-P30</f>
-        <v>80.792503522529188</v>
+        <f t="shared" si="7"/>
+        <v>107.83236503837509</v>
       </c>
       <c r="R30" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.237738597518701E-2</v>
+        <f t="shared" si="8"/>
+        <v>9.2736535978240175E-3</v>
       </c>
       <c r="S30" s="9">
-        <f>Q30/MAX($Q$2:$Q$28)</f>
-        <v>0.60874646990511294</v>
+        <f t="shared" si="9"/>
+        <v>0.77853811271817497</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" t="s">
         <v>75</v>
-      </c>
-      <c r="C31" t="s">
-        <v>76</v>
       </c>
       <c r="D31" s="8">
         <v>45562</v>
       </c>
       <c r="E31" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F31" s="1">
         <v>56</v>
       </c>
       <c r="G31" s="1">
-        <f>E31*F31</f>
-        <v>5.5999999999999999E-34</v>
+        <f t="shared" si="0"/>
+        <v>5.5999999999999995E-18</v>
       </c>
       <c r="H31" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),1)</f>
+        <v>-7.1999999999999998E-3</v>
       </c>
       <c r="I31" s="11">
-        <v>0.19</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),2)</f>
+        <v>0.41589999999999999</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR(H31/I31,"")</f>
-        <v>0.36842105263157898</v>
+        <f t="shared" si="1"/>
+        <v>-1.7311853811012263E-2</v>
       </c>
       <c r="K31" s="9">
-        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.4657882752458291E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.0868540451710281E-3</v>
       </c>
       <c r="L31" s="12">
-        <f t="shared" si="0"/>
-        <v>59.92</v>
+        <f t="shared" si="10"/>
+        <v>55.596800000000002</v>
       </c>
       <c r="M31" s="12">
-        <f>F31/(1+I31-H31)</f>
-        <v>50.000000000000007</v>
+        <f t="shared" si="3"/>
+        <v>39.350713231677325</v>
       </c>
       <c r="N31" s="12">
-        <f>L31-F31</f>
-        <v>3.9200000000000017</v>
+        <f t="shared" si="4"/>
+        <v>-0.40319999999999823</v>
       </c>
       <c r="O31" s="12">
-        <f>0.5*(M31-F31)</f>
-        <v>-2.9999999999999964</v>
+        <f t="shared" si="5"/>
+        <v>-8.3246433841613374</v>
       </c>
       <c r="P31" s="14">
-        <f>N31+O31</f>
-        <v>0.92000000000000526</v>
+        <f t="shared" si="6"/>
+        <v>-8.7278433841613356</v>
       </c>
       <c r="Q31" s="12">
-        <f>MAX($P$2:$P$280)-P31</f>
-        <v>102.70851002865332</v>
+        <f t="shared" si="7"/>
+        <v>132.29442278895462</v>
       </c>
       <c r="R31" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.7362915665023565E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.5588976384535159E-3</v>
       </c>
       <c r="S31" s="9">
-        <f>Q31/MAX($Q$2:$Q$28)</f>
-        <v>0.77387678538420068</v>
+        <f t="shared" si="9"/>
+        <v>0.95515154661217927</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" t="s">
         <v>78</v>
-      </c>
-      <c r="C32" t="s">
-        <v>79</v>
       </c>
       <c r="D32" s="8">
         <v>45580</v>
       </c>
       <c r="E32" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F32" s="1">
         <v>20.399999999999999</v>
       </c>
       <c r="G32" s="1">
-        <f>E32*F32</f>
-        <v>2.0399999999999999E-34</v>
+        <f t="shared" si="0"/>
+        <v>2.0399999999999999E-18</v>
       </c>
       <c r="H32" s="11">
-        <v>0.1</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I32" s="11">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="J32" s="9">
-        <f>IFERROR(H32/I32,"")</f>
-        <v>0.66666666666666674</v>
+        <f t="shared" si="1"/>
+        <v>0.28846153846153844</v>
       </c>
       <c r="K32" s="9">
-        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.271426402825786E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.8109879702990009E-2</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" si="0"/>
-        <v>22.44</v>
+        <f t="shared" si="10"/>
+        <v>21.929999999999996</v>
       </c>
       <c r="M32" s="12">
-        <f>F32/(1+I32-H32)</f>
-        <v>19.428571428571431</v>
+        <f t="shared" si="3"/>
+        <v>17.215189873417721</v>
       </c>
       <c r="N32" s="12">
-        <f>L32-F32</f>
-        <v>2.0400000000000027</v>
+        <f t="shared" si="4"/>
+        <v>1.5299999999999976</v>
       </c>
       <c r="O32" s="12">
-        <f>0.5*(M32-F32)</f>
-        <v>-0.48571428571428399</v>
+        <f t="shared" si="5"/>
+        <v>-1.5924050632911388</v>
       </c>
       <c r="P32" s="14">
-        <f>N32+O32</f>
-        <v>1.5542857142857187</v>
+        <f t="shared" si="6"/>
+        <v>-6.2405063291141261E-2</v>
       </c>
       <c r="Q32" s="12">
-        <f>MAX($P$2:$P$280)-P32</f>
-        <v>102.0742243143676</v>
+        <f t="shared" si="7"/>
+        <v>123.62898446808443</v>
       </c>
       <c r="R32" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.7967925469627445E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.0887180648010256E-3</v>
       </c>
       <c r="S32" s="9">
-        <f>Q32/MAX($Q$2:$Q$28)</f>
-        <v>0.76909763914354723</v>
+        <f t="shared" si="9"/>
+        <v>0.89258801112999675</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -3105,69 +3254,71 @@
         <v>39</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D33" s="8">
         <v>45574</v>
       </c>
       <c r="E33" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F33" s="1">
         <v>47.42</v>
       </c>
       <c r="G33" s="1">
-        <f>E33*F33</f>
-        <v>4.7420000000000006E-44</v>
+        <f t="shared" si="0"/>
+        <v>4.7419999999999999E-18</v>
       </c>
       <c r="H33" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C33,Sheet1!$G:$G,0),1)</f>
+        <v>7.8399999999999997E-2</v>
       </c>
       <c r="I33" s="11">
-        <v>0.4</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C33,Sheet1!$G:$G,0),2)</f>
+        <v>0.36230000000000001</v>
       </c>
       <c r="J33" s="9">
-        <f>IFERROR(H33/I33,"")</f>
-        <v>0.17500000000000002</v>
+        <f t="shared" si="1"/>
+        <v>0.21639525255313274</v>
       </c>
       <c r="K33" s="9">
-        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.646249430741769E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.3585492239055969E-2</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" si="0"/>
-        <v>50.739400000000003</v>
+        <f t="shared" si="10"/>
+        <v>51.137728000000003</v>
       </c>
       <c r="M33" s="12">
-        <f>F33/(1+I33-H33)</f>
-        <v>35.654135338345867</v>
+        <f t="shared" si="3"/>
+        <v>36.934340680738373</v>
       </c>
       <c r="N33" s="12">
-        <f>L33-F33</f>
-        <v>3.3194000000000017</v>
+        <f t="shared" si="4"/>
+        <v>3.717728000000001</v>
       </c>
       <c r="O33" s="12">
-        <f>0.5*(M33-F33)</f>
-        <v>-5.8829323308270673</v>
+        <f t="shared" si="5"/>
+        <v>-5.2428296596308144</v>
       </c>
       <c r="P33" s="14">
-        <f>N33+O33</f>
-        <v>-2.5635323308270657</v>
+        <f t="shared" si="6"/>
+        <v>-1.5251016596308133</v>
       </c>
       <c r="Q33" s="12">
-        <f>MAX($P$2:$P$280)-P33</f>
-        <v>106.19204235948038</v>
+        <f t="shared" si="7"/>
+        <v>125.09168106442411</v>
       </c>
       <c r="R33" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.4169014719088714E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.9941367122965193E-3</v>
       </c>
       <c r="S33" s="9">
-        <f>Q33/MAX($Q$2:$Q$28)</f>
-        <v>0.80012412166831481</v>
+        <f t="shared" si="9"/>
+        <v>0.90314852371068932</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -3184,200 +3335,204 @@
         <v>45507</v>
       </c>
       <c r="E34" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F34" s="1">
         <v>41.8</v>
       </c>
       <c r="G34" s="1">
-        <f>E34*F34</f>
-        <v>4.1799999999999994E-44</v>
+        <f t="shared" si="0"/>
+        <v>4.1799999999999993E-18</v>
       </c>
       <c r="H34" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C34,Sheet1!$G:$G,0),1)</f>
+        <v>0.1303</v>
       </c>
       <c r="I34" s="11">
-        <v>0.4</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C34,Sheet1!$G:$G,0),2)</f>
+        <v>0.39119999999999999</v>
       </c>
       <c r="J34" s="9">
-        <f>IFERROR(H34/I34,"")</f>
-        <v>0.17500000000000002</v>
+        <f t="shared" si="1"/>
+        <v>0.33307770961145194</v>
       </c>
       <c r="K34" s="9">
-        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.646249430741769E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.0910923809744224E-2</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" si="0"/>
-        <v>44.725999999999999</v>
+        <f t="shared" si="10"/>
+        <v>47.246540000000003</v>
       </c>
       <c r="M34" s="12">
-        <f>F34/(1+I34-H34)</f>
-        <v>31.428571428571431</v>
+        <f t="shared" si="3"/>
+        <v>33.150923943215162</v>
       </c>
       <c r="N34" s="12">
-        <f>L34-F34</f>
-        <v>2.9260000000000019</v>
+        <f t="shared" si="4"/>
+        <v>5.4465400000000059</v>
       </c>
       <c r="O34" s="12">
-        <f>0.5*(M34-F34)</f>
-        <v>-5.1857142857142833</v>
+        <f t="shared" si="5"/>
+        <v>-4.3245380283924177</v>
       </c>
       <c r="P34" s="14">
-        <f>N34+O34</f>
-        <v>-2.2597142857142813</v>
+        <f t="shared" si="6"/>
+        <v>1.1220019716075882</v>
       </c>
       <c r="Q34" s="12">
-        <f>MAX($P$2:$P$280)-P34</f>
-        <v>105.8882243143676</v>
+        <f t="shared" si="7"/>
+        <v>122.4445774331857</v>
       </c>
       <c r="R34" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.4439207614922058E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.1669602767478183E-3</v>
       </c>
       <c r="S34" s="9">
-        <f>Q34/MAX($Q$2:$Q$28)</f>
-        <v>0.79783494687619694</v>
+        <f t="shared" si="9"/>
+        <v>0.88403671934193273</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
         <v>80</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
       </c>
       <c r="D35" s="8">
         <v>45574</v>
       </c>
       <c r="E35" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F35" s="1">
         <v>153.7552</v>
       </c>
       <c r="G35" s="1">
-        <f>E35*F35</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="H35" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I35" s="11">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="J35" s="9">
-        <f>IFERROR(H35/I35,"")</f>
-        <v>0.36842105263157898</v>
+        <f t="shared" si="1"/>
+        <v>0.28846153846153844</v>
       </c>
       <c r="K35" s="9">
-        <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.4657882752458291E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.8109879702990009E-2</v>
       </c>
       <c r="L35" s="12">
-        <f t="shared" si="0"/>
-        <v>164.51806400000001</v>
+        <f t="shared" si="10"/>
+        <v>165.28683999999998</v>
       </c>
       <c r="M35" s="12">
-        <f>F35/(1+I35-H35)</f>
-        <v>137.28142857142859</v>
+        <f t="shared" si="3"/>
+        <v>129.75122362869197</v>
       </c>
       <c r="N35" s="12">
-        <f>L35-F35</f>
-        <v>10.762864000000008</v>
+        <f t="shared" si="4"/>
+        <v>11.531639999999982</v>
       </c>
       <c r="O35" s="12">
-        <f>0.5*(M35-F35)</f>
-        <v>-8.2368857142857053</v>
+        <f t="shared" si="5"/>
+        <v>-12.001988185654014</v>
       </c>
       <c r="P35" s="14">
-        <f>N35+O35</f>
-        <v>2.5259782857143023</v>
+        <f t="shared" si="6"/>
+        <v>-0.47034818565403214</v>
       </c>
       <c r="Q35" s="12">
-        <f>MAX($P$2:$P$280)-P35</f>
-        <v>101.10253174293902</v>
+        <f t="shared" si="7"/>
+        <v>124.03692759044732</v>
       </c>
       <c r="R35" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q35)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8909491459875307E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.0621152057382527E-3</v>
       </c>
       <c r="S35" s="9">
-        <f>Q35/MAX($Q$2:$Q$28)</f>
-        <v>0.76177623682402107</v>
+        <f t="shared" si="9"/>
+        <v>0.89553331672973713</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" t="s">
         <v>90</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" s="20" t="s">
         <v>91</v>
-      </c>
-      <c r="C36" t="s">
-        <v>92</v>
       </c>
       <c r="D36" s="8">
         <v>45627</v>
       </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F36" s="1">
         <v>133.53</v>
       </c>
       <c r="G36" s="1">
-        <f>E36*F36</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1.3353E-17</v>
       </c>
       <c r="H36" s="11">
-        <v>1.4E-3</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),1)</f>
+        <v>5.7599999999999998E-2</v>
       </c>
       <c r="I36" s="11">
-        <v>0.29289999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),2)</f>
+        <v>0.2555</v>
       </c>
       <c r="J36" s="9">
-        <f>IFERROR(H36/I36,"")</f>
-        <v>4.7797883236599522E-3</v>
+        <f t="shared" si="1"/>
+        <v>0.22544031311154597</v>
       </c>
       <c r="K36" s="9">
-        <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.4964136039379139E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.4153349428935596E-2</v>
       </c>
       <c r="L36" s="12">
-        <f t="shared" si="0"/>
-        <v>133.71694200000002</v>
+        <f t="shared" si="10"/>
+        <v>141.22132800000003</v>
       </c>
       <c r="M36" s="12">
-        <f>F36/(1+I36-H36)</f>
-        <v>103.39140534262486</v>
+        <f t="shared" si="3"/>
+        <v>111.47007262709742</v>
       </c>
       <c r="N36" s="12">
-        <f>L36-F36</f>
-        <v>0.18694200000001615</v>
+        <f t="shared" si="4"/>
+        <v>7.691328000000027</v>
       </c>
       <c r="O36" s="12">
-        <f>0.5*(M36-F36)</f>
-        <v>-15.069297328687568</v>
+        <f t="shared" si="5"/>
+        <v>-11.029963686451289</v>
       </c>
       <c r="P36" s="14">
-        <f>N36+O36</f>
-        <v>-14.882355328687552</v>
+        <f t="shared" si="6"/>
+        <v>-3.3386356864512621</v>
       </c>
       <c r="Q36" s="12">
-        <f>MAX($P$2:$P$280)-P36</f>
-        <v>118.51086535734088</v>
+        <f t="shared" si="7"/>
+        <v>126.90521509124454</v>
       </c>
       <c r="R36" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.4380448744909731E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.8798968133894452E-3</v>
       </c>
       <c r="S36" s="9">
-        <f>Q36/MAX($Q$2:$Q$28)</f>
-        <v>0.89294263435671506</v>
+        <f t="shared" si="9"/>
+        <v>0.91624204491917349</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -3385,69 +3540,71 @@
         <v>40</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="C37" t="s">
-        <v>94</v>
       </c>
       <c r="D37" s="8">
         <v>45627</v>
       </c>
       <c r="E37" s="2">
-        <v>0</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="F37" s="1">
-        <v>39.56</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="G37" s="1">
-        <f>E37*F37</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>10.9251</v>
       </c>
       <c r="H37" s="11">
-        <v>1.2E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),1)</f>
+        <v>0.1114</v>
       </c>
       <c r="I37" s="11">
-        <v>0.22159999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),2)</f>
+        <v>0.245</v>
       </c>
       <c r="J37" s="9">
-        <f>IFERROR(H37/I37,"")</f>
-        <v>5.4151624548736468E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.45469387755102042</v>
       </c>
       <c r="K37" s="9">
-        <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.0941189192628229E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.8546098270334837E-2</v>
       </c>
       <c r="L37" s="12">
-        <f t="shared" si="0"/>
-        <v>40.03472</v>
+        <f t="shared" si="10"/>
+        <v>44.233719999999991</v>
       </c>
       <c r="M37" s="12">
-        <f>F37/(1+I37-H37)</f>
-        <v>32.705026455026456</v>
+        <f t="shared" si="3"/>
+        <v>35.109386026817212</v>
       </c>
       <c r="N37" s="12">
-        <f>L37-F37</f>
-        <v>0.47471999999999781</v>
+        <f t="shared" si="4"/>
+        <v>4.4337199999999939</v>
       </c>
       <c r="O37" s="12">
-        <f>0.5*(M37-F37)</f>
-        <v>-3.4274867724867732</v>
+        <f t="shared" si="5"/>
+        <v>-2.3453069865913925</v>
       </c>
       <c r="P37" s="14">
-        <f>N37+O37</f>
-        <v>-2.9527667724867754</v>
+        <f t="shared" si="6"/>
+        <v>2.0884130134086014</v>
       </c>
       <c r="Q37" s="12">
-        <f>MAX($P$2:$P$280)-P37</f>
-        <v>106.58127680114009</v>
+        <f t="shared" si="7"/>
+        <v>121.47816639138469</v>
       </c>
       <c r="R37" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.3825109814156676E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.2319319570411352E-3</v>
       </c>
       <c r="S37" s="9">
-        <f>Q37/MAX($Q$2:$Q$28)</f>
-        <v>0.80305688253095808</v>
+        <f t="shared" si="9"/>
+        <v>0.87705933524833513</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -3455,139 +3612,143 @@
         <v>40</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>95</v>
-      </c>
-      <c r="C38" t="s">
-        <v>96</v>
       </c>
       <c r="D38" s="8">
         <v>45627</v>
       </c>
       <c r="E38" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F38" s="1">
         <v>26.63</v>
       </c>
       <c r="G38" s="1">
-        <f>E38*F38</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>2.663E-18</v>
       </c>
       <c r="H38" s="11">
-        <v>0.17899999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),1)</f>
+        <v>-0.12609999999999999</v>
       </c>
       <c r="I38" s="11">
-        <v>0.26369999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),2)</f>
+        <v>0.63</v>
       </c>
       <c r="J38" s="9">
-        <f>IFERROR(H38/I38,"")</f>
-        <v>0.6788016685627607</v>
+        <f t="shared" si="1"/>
+        <v>-0.20015873015873015</v>
       </c>
       <c r="K38" s="9">
-        <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.3855820597600435E-2</v>
+        <f t="shared" si="2"/>
+        <v>-1.256614848554985E-2</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" si="0"/>
-        <v>31.39677</v>
+        <f t="shared" si="10"/>
+        <v>23.271957</v>
       </c>
       <c r="M38" s="12">
-        <f>F38/(1+I38-H38)</f>
-        <v>24.550566977044344</v>
+        <f t="shared" si="3"/>
+        <v>15.164284494049314</v>
       </c>
       <c r="N38" s="12">
-        <f>L38-F38</f>
-        <v>4.7667700000000011</v>
+        <f t="shared" si="4"/>
+        <v>-3.3580429999999986</v>
       </c>
       <c r="O38" s="12">
-        <f>0.5*(M38-F38)</f>
-        <v>-1.0397165114778275</v>
+        <f t="shared" si="5"/>
+        <v>-5.7328577529753426</v>
       </c>
       <c r="P38" s="14">
-        <f>N38+O38</f>
-        <v>3.7270534885221736</v>
+        <f t="shared" si="6"/>
+        <v>-9.0909007529753403</v>
       </c>
       <c r="Q38" s="12">
-        <f>MAX($P$2:$P$280)-P38</f>
-        <v>99.90145654013115</v>
+        <f t="shared" si="7"/>
+        <v>132.65748015776862</v>
       </c>
       <c r="R38" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0009864066379178E-2</v>
+        <f t="shared" si="8"/>
+        <v>7.538210425908189E-3</v>
       </c>
       <c r="S38" s="9">
-        <f>Q38/MAX($Q$2:$Q$28)</f>
-        <v>0.75272650748129832</v>
+        <f t="shared" si="9"/>
+        <v>0.95777278188439352</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="C39" s="20" t="s">
         <v>99</v>
-      </c>
-      <c r="C39" t="s">
-        <v>100</v>
       </c>
       <c r="D39" s="8">
         <v>45630</v>
       </c>
       <c r="E39" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F39" s="1">
         <v>59.17</v>
       </c>
       <c r="G39" s="1">
-        <f>E39*F39</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5.9170000000000002E-18</v>
       </c>
       <c r="H39" s="11">
-        <v>0.18379999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),1)</f>
+        <v>-7.0800000000000002E-2</v>
       </c>
       <c r="I39" s="11">
-        <v>0.54569999999999996</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),2)</f>
+        <v>0.5726</v>
       </c>
       <c r="J39" s="9">
-        <f>IFERROR(H39/I39,"")</f>
-        <v>0.33681509987172442</v>
+        <f t="shared" si="1"/>
+        <v>-0.12364652462451974</v>
       </c>
       <c r="K39" s="9">
-        <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.1684666653089048E-2</v>
+        <f t="shared" si="2"/>
+        <v>-7.7626421136951932E-3</v>
       </c>
       <c r="L39" s="12">
-        <f t="shared" si="0"/>
-        <v>70.045445999999998</v>
+        <f t="shared" si="10"/>
+        <v>54.980764000000001</v>
       </c>
       <c r="M39" s="12">
-        <f>F39/(1+I39-H39)</f>
-        <v>43.446655407886041</v>
+        <f t="shared" si="3"/>
+        <v>36.004624558841428</v>
       </c>
       <c r="N39" s="12">
-        <f>L39-F39</f>
-        <v>10.875445999999997</v>
+        <f t="shared" si="4"/>
+        <v>-4.1892360000000011</v>
       </c>
       <c r="O39" s="12">
-        <f>0.5*(M39-F39)</f>
-        <v>-7.8616722960569803</v>
+        <f t="shared" si="5"/>
+        <v>-11.582687720579287</v>
       </c>
       <c r="P39" s="14">
-        <f>N39+O39</f>
-        <v>3.0137737039430164</v>
+        <f t="shared" si="6"/>
+        <v>-15.771923720579288</v>
       </c>
       <c r="Q39" s="12">
-        <f>MAX($P$2:$P$280)-P39</f>
-        <v>100.61473632471031</v>
+        <f t="shared" si="7"/>
+        <v>139.33850312537257</v>
       </c>
       <c r="R39" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q39)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.938901959378358E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.1767672076987242E-3</v>
       </c>
       <c r="S39" s="9">
-        <f>Q39/MAX($Q$2:$Q$28)</f>
-        <v>0.75810084955495571</v>
+        <f t="shared" si="9"/>
+        <v>1.0060090513047488</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -3595,148 +3756,498 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>101</v>
-      </c>
-      <c r="C40" t="s">
-        <v>102</v>
       </c>
       <c r="D40" s="8">
         <v>45630</v>
       </c>
       <c r="E40" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F40" s="1">
         <v>19.309999999999999</v>
       </c>
       <c r="G40" s="1">
-        <f>E40*F40</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1.931E-18</v>
       </c>
       <c r="H40" s="11">
-        <v>-2.3E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),1)</f>
+        <v>0.1391</v>
       </c>
       <c r="I40" s="11">
-        <v>0.25559999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),2)</f>
+        <v>0.31609999999999999</v>
       </c>
       <c r="J40" s="9">
-        <f>IFERROR(H40/I40,"")</f>
-        <v>-8.9984350547730824E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.4400506168933882</v>
       </c>
       <c r="K40" s="9">
-        <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-8.4649534779925508E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.7626780948574785E-2</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="0"/>
-        <v>18.865869999999997</v>
+        <f t="shared" si="10"/>
+        <v>21.996020999999999</v>
       </c>
       <c r="M40" s="12">
-        <f>F40/(1+I40-H40)</f>
-        <v>15.102455811043328</v>
+        <f t="shared" si="3"/>
+        <v>16.40611724723874</v>
       </c>
       <c r="N40" s="12">
-        <f>L40-F40</f>
-        <v>-0.44413000000000125</v>
+        <f t="shared" si="4"/>
+        <v>2.6860210000000002</v>
       </c>
       <c r="O40" s="12">
-        <f>0.5*(M40-F40)</f>
-        <v>-2.1037720944783356</v>
+        <f t="shared" si="5"/>
+        <v>-1.4519413763806295</v>
       </c>
       <c r="P40" s="14">
-        <f>N40+O40</f>
-        <v>-2.5479020944783368</v>
+        <f t="shared" si="6"/>
+        <v>1.2340796236193707</v>
       </c>
       <c r="Q40" s="12">
-        <f>MAX($P$2:$P$280)-P40</f>
-        <v>106.17641212313166</v>
+        <f t="shared" si="7"/>
+        <v>122.33249978117392</v>
       </c>
       <c r="R40" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q40)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.4182877345705615E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.1744426198171478E-3</v>
       </c>
       <c r="S40" s="9">
-        <f>Q40/MAX($Q$2:$Q$28)</f>
-        <v>0.80000635268250275</v>
+        <f t="shared" si="9"/>
+        <v>0.8832275307124885</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>103</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
       </c>
       <c r="D41" s="8">
         <v>45630</v>
       </c>
       <c r="E41" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F41" s="1">
         <v>323.75</v>
       </c>
       <c r="G41" s="1">
-        <f>E41*F41</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>3.2375000000000002E-17</v>
       </c>
       <c r="H41" s="11">
-        <v>9.2100000000000001E-2</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),1)</f>
+        <v>0.1842</v>
       </c>
       <c r="I41" s="11">
-        <v>0.31609999999999999</v>
+        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),2)</f>
+        <v>0.33040000000000003</v>
       </c>
       <c r="J41" s="9">
-        <f>IFERROR(H41/I41,"")</f>
-        <v>0.29136349256564381</v>
+        <f t="shared" si="1"/>
+        <v>0.55750605326876512</v>
       </c>
       <c r="K41" s="9">
-        <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7408970501435696E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.5000740869071734E-2</v>
       </c>
       <c r="L41" s="12">
+        <f t="shared" si="10"/>
+        <v>383.38475</v>
+      </c>
+      <c r="M41" s="12">
+        <f t="shared" si="3"/>
+        <v>282.45506892339904</v>
+      </c>
+      <c r="N41" s="12">
+        <f t="shared" si="4"/>
+        <v>59.634749999999997</v>
+      </c>
+      <c r="O41" s="12">
+        <f t="shared" si="5"/>
+        <v>-20.64746553830048</v>
+      </c>
+      <c r="P41" s="14">
+        <f t="shared" si="6"/>
+        <v>38.987284461699517</v>
+      </c>
+      <c r="Q41" s="12">
+        <f t="shared" si="7"/>
+        <v>84.579294943093771</v>
+      </c>
+      <c r="R41" s="9">
+        <f t="shared" si="8"/>
+        <v>1.1823224592647823E-2</v>
+      </c>
+      <c r="S41" s="9">
+        <f t="shared" si="9"/>
+        <v>0.61065344005574052</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>20.928000000000001</v>
+      </c>
+      <c r="G42" s="1">
         <f t="shared" si="0"/>
-        <v>353.56737500000003</v>
-      </c>
-      <c r="M41" s="12">
-        <f>F41/(1+I41-H41)</f>
-        <v>264.50163398692808</v>
-      </c>
-      <c r="N41" s="12">
-        <f>L41-F41</f>
-        <v>29.817375000000027</v>
-      </c>
-      <c r="O41" s="12">
-        <f>0.5*(M41-F41)</f>
-        <v>-29.624183006535958</v>
-      </c>
-      <c r="P41" s="14">
-        <f>N41+O41</f>
-        <v>0.1931919934640689</v>
-      </c>
-      <c r="Q41" s="12">
-        <f>MAX($P$2:$P$280)-P41</f>
-        <v>103.43531803518925</v>
-      </c>
-      <c r="R41" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q41)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.667877655287864E-3</v>
-      </c>
-      <c r="S41" s="9">
-        <f>Q41/MAX($Q$2:$Q$28)</f>
-        <v>0.77935305841681124</v>
+        <v>41.856000000000002</v>
+      </c>
+      <c r="H42" s="11">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I42" s="11">
+        <v>0.26</v>
+      </c>
+      <c r="J42" s="9">
+        <f t="shared" ref="J42:J46" si="11">IFERROR(H42/I42,"")</f>
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="K42" s="9">
+        <f t="shared" si="2"/>
+        <v>1.0865927821794005E-2</v>
+      </c>
+      <c r="L42" s="12">
+        <f t="shared" ref="L42:L46" si="12">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
+        <v>21.869759999999999</v>
+      </c>
+      <c r="M42" s="12">
+        <f t="shared" ref="M42:M46" si="13">F42/(1+I42-H42)</f>
+        <v>17.224691358024693</v>
+      </c>
+      <c r="N42" s="12">
+        <f t="shared" ref="N42:N46" si="14">L42-F42</f>
+        <v>0.9417599999999986</v>
+      </c>
+      <c r="O42" s="12">
+        <f t="shared" ref="O42:O46" si="15">0.5*(M42-F42)</f>
+        <v>-1.8516543209876541</v>
+      </c>
+      <c r="P42" s="14">
+        <f t="shared" ref="P42:P46" si="16">N42+O42</f>
+        <v>-0.90989432098765555</v>
+      </c>
+      <c r="Q42" s="12">
+        <f t="shared" si="7"/>
+        <v>124.47647372578095</v>
+      </c>
+      <c r="R42" s="9">
+        <f t="shared" si="8"/>
+        <v>8.0336466005855763E-3</v>
+      </c>
+      <c r="S42" s="9">
+        <f t="shared" ref="S42:S46" si="17">Q42/MAX($Q$2:$Q$28)</f>
+        <v>0.89870679269433662</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="G43" s="1">
+        <f t="shared" si="0"/>
+        <v>32.799999999999997</v>
+      </c>
+      <c r="H43" s="11">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0.26</v>
+      </c>
+      <c r="J43" s="9">
+        <f t="shared" si="11"/>
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="K43" s="9">
+        <f t="shared" si="2"/>
+        <v>1.0865927821794005E-2</v>
+      </c>
+      <c r="L43" s="12">
+        <f t="shared" si="12"/>
+        <v>17.137999999999998</v>
+      </c>
+      <c r="M43" s="12">
+        <f t="shared" si="13"/>
+        <v>13.497942386831273</v>
+      </c>
+      <c r="N43" s="12">
+        <f t="shared" si="14"/>
+        <v>0.73799999999999955</v>
+      </c>
+      <c r="O43" s="12">
+        <f t="shared" si="15"/>
+        <v>-1.4510288065843628</v>
+      </c>
+      <c r="P43" s="14">
+        <f t="shared" si="16"/>
+        <v>-0.71302880658436329</v>
+      </c>
+      <c r="Q43" s="12">
+        <f t="shared" si="7"/>
+        <v>124.27960821137765</v>
+      </c>
+      <c r="R43" s="9">
+        <f t="shared" si="8"/>
+        <v>8.0463723244055992E-3</v>
+      </c>
+      <c r="S43" s="9">
+        <f t="shared" si="17"/>
+        <v>0.89728544479022365</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>150</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C44" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>48.68</v>
+      </c>
+      <c r="G44" s="1">
+        <f t="shared" si="0"/>
+        <v>48.68</v>
+      </c>
+      <c r="H44" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0.26</v>
+      </c>
+      <c r="J44" s="9">
+        <f t="shared" si="11"/>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="K44" s="9">
+        <f t="shared" si="2"/>
+        <v>2.4146506270653345E-2</v>
+      </c>
+      <c r="L44" s="12">
+        <f t="shared" si="12"/>
+        <v>53.548000000000002</v>
+      </c>
+      <c r="M44" s="12">
+        <f t="shared" si="13"/>
+        <v>41.96551724137931</v>
+      </c>
+      <c r="N44" s="12">
+        <f t="shared" si="14"/>
+        <v>4.8680000000000021</v>
+      </c>
+      <c r="O44" s="12">
+        <f t="shared" si="15"/>
+        <v>-3.3572413793103451</v>
+      </c>
+      <c r="P44" s="14">
+        <f t="shared" si="16"/>
+        <v>1.5107586206896571</v>
+      </c>
+      <c r="Q44" s="12">
+        <f t="shared" si="7"/>
+        <v>122.05582078410363</v>
+      </c>
+      <c r="R44" s="9">
+        <f t="shared" si="8"/>
+        <v>8.1929726380590498E-3</v>
+      </c>
+      <c r="S44" s="9">
+        <f t="shared" si="17"/>
+        <v>0.8812299380219154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>150</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>51.28</v>
+      </c>
+      <c r="G45" s="1">
+        <f t="shared" si="0"/>
+        <v>51.28</v>
+      </c>
+      <c r="H45" s="11">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I45" s="11">
+        <v>0.26</v>
+      </c>
+      <c r="J45" s="9">
+        <f t="shared" si="11"/>
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="K45" s="9">
+        <f t="shared" si="2"/>
+        <v>1.0865927821794005E-2</v>
+      </c>
+      <c r="L45" s="12">
+        <f t="shared" si="12"/>
+        <v>53.587599999999995</v>
+      </c>
+      <c r="M45" s="12">
+        <f t="shared" si="13"/>
+        <v>42.205761316872426</v>
+      </c>
+      <c r="N45" s="12">
+        <f t="shared" si="14"/>
+        <v>2.3075999999999937</v>
+      </c>
+      <c r="O45" s="12">
+        <f t="shared" si="15"/>
+        <v>-4.5371193415637876</v>
+      </c>
+      <c r="P45" s="14">
+        <f t="shared" si="16"/>
+        <v>-2.2295193415637939</v>
+      </c>
+      <c r="Q45" s="12">
+        <f t="shared" si="7"/>
+        <v>125.79609874635707</v>
+      </c>
+      <c r="R45" s="9">
+        <f t="shared" si="8"/>
+        <v>7.9493721185766031E-3</v>
+      </c>
+      <c r="S45" s="9">
+        <f t="shared" si="17"/>
+        <v>0.90823434383957402</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44.14</v>
+      </c>
+      <c r="G46" s="1">
+        <f t="shared" si="0"/>
+        <v>44.14</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0.26</v>
+      </c>
+      <c r="J46" s="9">
+        <f t="shared" si="11"/>
+        <v>0.57692307692307687</v>
+      </c>
+      <c r="K46" s="9">
+        <f t="shared" si="2"/>
+        <v>3.6219759405980018E-2</v>
+      </c>
+      <c r="L46" s="12">
+        <f t="shared" si="12"/>
+        <v>50.760999999999996</v>
+      </c>
+      <c r="M46" s="12">
+        <f t="shared" si="13"/>
+        <v>39.765765765765764</v>
+      </c>
+      <c r="N46" s="12">
+        <f t="shared" si="14"/>
+        <v>6.6209999999999951</v>
+      </c>
+      <c r="O46" s="12">
+        <f t="shared" si="15"/>
+        <v>-2.1871171171171184</v>
+      </c>
+      <c r="P46" s="14">
+        <f t="shared" si="16"/>
+        <v>4.4338828828828767</v>
+      </c>
+      <c r="Q46" s="12">
+        <f t="shared" si="7"/>
+        <v>119.13269652191042</v>
+      </c>
+      <c r="R46" s="9">
+        <f t="shared" si="8"/>
+        <v>8.3940012204465116E-3</v>
+      </c>
+      <c r="S46" s="9">
+        <f t="shared" si="17"/>
+        <v>0.86012529429534301</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S41" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S41">
-      <sortCondition descending="1" ref="G1:G41"/>
-    </sortState>
-  </autoFilter>
-  <conditionalFormatting sqref="R2:R41">
+  <autoFilter ref="A1:S46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="R2:R46">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
@@ -3775,7 +4286,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>S2:S41</xm:sqref>
+          <xm:sqref>S2:S46</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3796,16 +4307,16 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" t="s">
         <v>129</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
@@ -3925,7 +4436,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="19">
         <v>0</v>
@@ -3967,7 +4478,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="19">
         <v>0</v>
@@ -3981,7 +4492,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" s="19">
         <v>0</v>
@@ -3995,7 +4506,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" s="19">
         <v>0</v>
@@ -4009,7 +4520,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16" s="19">
         <v>0</v>
@@ -4023,7 +4534,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" s="19">
         <v>0</v>
@@ -4037,7 +4548,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D18" s="19">
         <v>0</v>
@@ -4051,7 +4562,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D19" s="19">
         <v>0</v>
@@ -4065,7 +4576,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" s="19">
         <v>0</v>
@@ -4081,283 +4592,292 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A09BB01-2590-4471-B7D1-AC4B730D30F2}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" t="s">
         <v>105</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>107</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>108</v>
-      </c>
-      <c r="E1" t="s">
-        <v>109</v>
       </c>
       <c r="F1" t="s">
         <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B2">
-        <v>1.4E-3</v>
+        <v>0.2722</v>
       </c>
       <c r="C2">
-        <v>0.29289999999999999</v>
+        <v>0.3296</v>
       </c>
       <c r="D2">
-        <v>1E-4</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="E2">
-        <v>8.4500000000000006E-2</v>
+        <v>9.5100000000000004E-2</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="B3">
-        <v>0.18379999999999999</v>
+        <v>0.16470000000000001</v>
       </c>
       <c r="C3">
-        <v>0.54569999999999996</v>
+        <v>0.372</v>
       </c>
       <c r="D3">
-        <v>1.5299999999999999E-2</v>
+        <v>1.37E-2</v>
       </c>
       <c r="E3">
-        <v>0.1575</v>
+        <v>0.1074</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B4">
-        <v>9.2100000000000001E-2</v>
+        <v>0.25430000000000003</v>
       </c>
       <c r="C4">
-        <v>0.31609999999999999</v>
+        <v>0.2868</v>
       </c>
       <c r="D4">
-        <v>7.7000000000000002E-3</v>
+        <v>2.12E-2</v>
       </c>
       <c r="E4">
-        <v>9.1200000000000003E-2</v>
+        <v>8.2799999999999999E-2</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B5">
-        <v>-1.7947</v>
+        <v>0.24590000000000001</v>
       </c>
       <c r="C5">
-        <v>1.4319</v>
+        <v>0.2702</v>
       </c>
       <c r="D5">
-        <v>-0.14960000000000001</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="E5">
-        <v>0.41339999999999999</v>
+        <v>7.8E-2</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B6">
-        <v>-3.8800000000000001E-2</v>
+        <v>0.18140000000000001</v>
       </c>
       <c r="C6">
-        <v>0.28689999999999999</v>
+        <v>0.2843</v>
       </c>
       <c r="D6">
-        <v>-3.2000000000000002E-3</v>
+        <v>1.5100000000000001E-2</v>
       </c>
       <c r="E6">
-        <v>8.2799999999999999E-2</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B7">
-        <v>0.2823</v>
+        <v>0.23749999999999999</v>
       </c>
       <c r="C7">
-        <v>0.5212</v>
+        <v>0.37659999999999999</v>
       </c>
       <c r="D7">
-        <v>2.35E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="E7">
-        <v>0.15049999999999999</v>
+        <v>0.1087</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="B8">
-        <v>7.2800000000000004E-2</v>
+        <v>0.56320000000000003</v>
       </c>
       <c r="C8">
-        <v>0.18940000000000001</v>
+        <v>0.50019999999999998</v>
       </c>
       <c r="D8">
-        <v>6.1000000000000004E-3</v>
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="E8">
-        <v>5.4699999999999999E-2</v>
+        <v>0.1444</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B9">
-        <v>-0.1696</v>
+        <v>0.25890000000000002</v>
       </c>
       <c r="C9">
-        <v>0.70540000000000003</v>
+        <v>0.41639999999999999</v>
       </c>
       <c r="D9">
-        <v>-1.41E-2</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="E9">
-        <v>0.2036</v>
+        <v>0.1202</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B10">
-        <v>3.0300000000000001E-2</v>
+        <v>0.49509999999999998</v>
       </c>
       <c r="C10">
-        <v>0.39489999999999997</v>
+        <v>0.70050000000000001</v>
       </c>
       <c r="D10">
-        <v>2.5000000000000001E-3</v>
+        <v>4.1300000000000003E-2</v>
       </c>
       <c r="E10">
-        <v>0.114</v>
+        <v>0.20219999999999999</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B11">
-        <v>-0.32750000000000001</v>
+        <v>-7.0800000000000002E-2</v>
       </c>
       <c r="C11">
-        <v>0.63080000000000003</v>
+        <v>0.5726</v>
       </c>
       <c r="D11">
-        <v>-2.7300000000000001E-2</v>
+        <v>-5.8999999999999999E-3</v>
       </c>
       <c r="E11">
-        <v>0.18210000000000001</v>
+        <v>0.1653</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B12">
-        <v>-1.03</v>
+        <v>0.1842</v>
       </c>
       <c r="C12">
-        <v>0.75839999999999996</v>
+        <v>0.33040000000000003</v>
       </c>
       <c r="D12">
-        <v>-8.5800000000000001E-2</v>
+        <v>1.54E-2</v>
       </c>
       <c r="E12">
-        <v>0.21890000000000001</v>
+        <v>9.5399999999999999E-2</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4365,183 +4885,597 @@
         <v>121</v>
       </c>
       <c r="B13">
-        <v>1.2E-2</v>
+        <v>-4.8300000000000003E-2</v>
       </c>
       <c r="C13">
-        <v>0.22159999999999999</v>
+        <v>0.61990000000000001</v>
       </c>
       <c r="D13">
-        <v>1E-3</v>
+        <v>-4.0000000000000001E-3</v>
       </c>
       <c r="E13">
-        <v>6.4000000000000001E-2</v>
+        <v>0.1789</v>
       </c>
       <c r="F13" t="s">
         <v>40</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B14">
-        <v>0.17899999999999999</v>
+        <v>-1.4657</v>
       </c>
       <c r="C14">
-        <v>0.26369999999999999</v>
+        <v>1.325</v>
       </c>
       <c r="D14">
-        <v>1.49E-2</v>
+        <v>-0.1221</v>
       </c>
       <c r="E14">
-        <v>7.6100000000000001E-2</v>
+        <v>0.38250000000000001</v>
       </c>
       <c r="F14" t="s">
         <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B15">
-        <v>-5.4899999999999997E-2</v>
+        <v>0.13569999999999999</v>
       </c>
       <c r="C15">
-        <v>0.45929999999999999</v>
+        <v>0.25069999999999998</v>
       </c>
       <c r="D15">
-        <v>-4.5999999999999999E-3</v>
+        <v>1.1299999999999999E-2</v>
       </c>
       <c r="E15">
-        <v>0.1326</v>
+        <v>7.2400000000000006E-2</v>
       </c>
       <c r="F15" t="s">
         <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B16">
-        <v>0.1346</v>
+        <v>0.10249999999999999</v>
       </c>
       <c r="C16">
-        <v>0.20530000000000001</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="D16">
-        <v>1.12E-2</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="E16">
-        <v>5.9299999999999999E-2</v>
+        <v>0.15759999999999999</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B17">
-        <v>2.0500000000000001E-2</v>
+        <v>9.6799999999999997E-2</v>
       </c>
       <c r="C17">
-        <v>0.1867</v>
+        <v>0.4829</v>
       </c>
       <c r="D17">
-        <v>1.6999999999999999E-3</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="E17">
-        <v>5.3900000000000003E-2</v>
+        <v>0.1394</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B18">
-        <v>2.9999999999999997E-4</v>
+        <v>9.0899999999999995E-2</v>
       </c>
       <c r="C18">
-        <v>0.1711</v>
+        <v>0.2077</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>7.6E-3</v>
       </c>
       <c r="E18">
-        <v>4.9399999999999999E-2</v>
+        <v>0.06</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B19">
-        <v>0.2447</v>
+        <v>-1.9199999999999998E-2</v>
       </c>
       <c r="C19">
-        <v>0.20810000000000001</v>
+        <v>0.71699999999999997</v>
       </c>
       <c r="D19">
-        <v>2.0400000000000001E-2</v>
+        <v>-1.6000000000000001E-3</v>
       </c>
       <c r="E19">
-        <v>6.0100000000000001E-2</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B20">
-        <v>-2.3E-2</v>
+        <v>1.61E-2</v>
       </c>
       <c r="C20">
-        <v>0.25559999999999999</v>
+        <v>0.42009999999999997</v>
       </c>
       <c r="D20">
-        <v>-1.9E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="E20">
+        <v>0.12130000000000001</v>
+      </c>
+      <c r="F20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21">
+        <v>-0.1114</v>
+      </c>
+      <c r="C21">
+        <v>0.58130000000000004</v>
+      </c>
+      <c r="D21">
+        <v>-9.2999999999999992E-3</v>
+      </c>
+      <c r="E21">
+        <v>0.1678</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22">
+        <v>0.1114</v>
+      </c>
+      <c r="C22">
+        <v>0.245</v>
+      </c>
+      <c r="D22">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="E22">
+        <v>7.0699999999999999E-2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23">
+        <v>-0.12609999999999999</v>
+      </c>
+      <c r="C23">
+        <v>0.63</v>
+      </c>
+      <c r="D23">
+        <v>-1.0500000000000001E-2</v>
+      </c>
+      <c r="E23">
+        <v>0.18190000000000001</v>
+      </c>
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24">
+        <v>0.1193</v>
+      </c>
+      <c r="C24">
+        <v>0.2243</v>
+      </c>
+      <c r="D24">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="E24">
+        <v>6.4699999999999994E-2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C25">
+        <v>0.25819999999999999</v>
+      </c>
+      <c r="D25">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="E25">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <v>0.1993</v>
+      </c>
+      <c r="C26">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="D26">
+        <v>1.66E-2</v>
+      </c>
+      <c r="E26">
+        <v>7.85E-2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27">
+        <v>7.8399999999999997E-2</v>
+      </c>
+      <c r="C27">
+        <v>0.36230000000000001</v>
+      </c>
+      <c r="D27">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="E27">
+        <v>0.1046</v>
+      </c>
+      <c r="F27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28">
+        <v>0.1303</v>
+      </c>
+      <c r="C28">
+        <v>0.39119999999999999</v>
+      </c>
+      <c r="D28">
+        <v>1.09E-2</v>
+      </c>
+      <c r="E28">
+        <v>0.1129</v>
+      </c>
+      <c r="F28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29">
+        <v>-7.1999999999999998E-3</v>
+      </c>
+      <c r="C29">
+        <v>0.41589999999999999</v>
+      </c>
+      <c r="D29">
+        <v>-5.9999999999999995E-4</v>
+      </c>
+      <c r="E29">
+        <v>0.12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>73</v>
+      </c>
+      <c r="G29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="C30">
+        <v>0.2555</v>
+      </c>
+      <c r="D30">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="E30">
         <v>7.3800000000000004E-2</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31">
+        <v>8.0299999999999996E-2</v>
+      </c>
+      <c r="C31">
+        <v>0.36080000000000001</v>
+      </c>
+      <c r="D31">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="E31">
+        <v>0.1042</v>
+      </c>
+      <c r="F31" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32">
+        <v>0.17119999999999999</v>
+      </c>
+      <c r="C32">
+        <v>0.24590000000000001</v>
+      </c>
+      <c r="D32">
+        <v>1.43E-2</v>
+      </c>
+      <c r="E32">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33">
+        <v>0.2</v>
+      </c>
+      <c r="C33">
+        <v>0.27160000000000001</v>
+      </c>
+      <c r="D33">
+        <v>1.67E-2</v>
+      </c>
+      <c r="E33">
+        <v>7.8399999999999997E-2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34">
+        <v>5.6500000000000002E-2</v>
+      </c>
+      <c r="C34">
+        <v>0.22939999999999999</v>
+      </c>
+      <c r="D34">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="E34">
+        <v>6.6199999999999995E-2</v>
+      </c>
+      <c r="F34" t="s">
         <v>38</v>
       </c>
-      <c r="G20" t="s">
-        <v>102</v>
+      <c r="G34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35">
+        <v>7.5399999999999995E-2</v>
+      </c>
+      <c r="C35">
+        <v>0.1905</v>
+      </c>
+      <c r="D35">
+        <v>6.3E-3</v>
+      </c>
+      <c r="E35">
+        <v>5.5E-2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="C36">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="D36">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E36">
+        <v>5.8599999999999999E-2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37">
+        <v>0.1913</v>
+      </c>
+      <c r="C37">
+        <v>0.2109</v>
+      </c>
+      <c r="D37">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="E37">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38">
+        <v>0.1391</v>
+      </c>
+      <c r="C38">
+        <v>0.31609999999999999</v>
+      </c>
+      <c r="D38">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="E38">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E758EEE-48A9-4F22-BCA9-12577431D4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC1F8C8-C13E-4050-9F90-E93E9DF5B6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -496,21 +496,12 @@
     <t>ETF</t>
   </si>
   <si>
-    <t>ETF1</t>
-  </si>
-  <si>
     <t>BOTZ.UK</t>
   </si>
   <si>
-    <t>ETF2</t>
-  </si>
-  <si>
     <t>BATT.NL</t>
   </si>
   <si>
-    <t>ETF3</t>
-  </si>
-  <si>
     <t>VBTC.DE</t>
   </si>
   <si>
@@ -520,10 +511,19 @@
     <t>BONDS</t>
   </si>
   <si>
-    <t>Emerging Markets</t>
-  </si>
-  <si>
     <t>VWO.US</t>
+  </si>
+  <si>
+    <t>Robotics &amp; AI</t>
+  </si>
+  <si>
+    <t>Batterey Value-Chain</t>
+  </si>
+  <si>
+    <t>Emergin Markets</t>
+  </si>
+  <si>
+    <t>Bitcoin ETF</t>
   </si>
 </sst>
 </file>
@@ -944,11 +944,10 @@
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.7109375" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="10"/>
     <col min="11" max="11" width="7.5703125" style="10" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -1022,218 +1021,218 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>88</v>
+        <v>150</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
       </c>
       <c r="D2" s="8">
-        <v>45623</v>
+        <v>45481</v>
       </c>
       <c r="E2" s="2">
-        <v>1.9595</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1">
-        <v>15.3</v>
+        <v>20.928000000000001</v>
       </c>
       <c r="G2" s="1">
         <f t="shared" ref="G2:G46" si="0">E2*F2</f>
-        <v>29.980350000000001</v>
+        <v>41.856000000000002</v>
       </c>
       <c r="H2" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),1)</f>
-        <v>8.0299999999999996E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I2" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),2)</f>
-        <v>0.36080000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25</v>
       </c>
       <c r="J2" s="9">
         <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
-        <v>0.22256097560975607</v>
+        <v>0.1</v>
       </c>
       <c r="K2" s="9">
         <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.3972581982225623E-2</v>
+        <v>6.9530133741456208E-3</v>
       </c>
       <c r="L2" s="12">
         <f>IF((1+H2)*F2&lt;0,0,(1+H2)*F2)</f>
-        <v>16.528590000000001</v>
+        <v>21.4512</v>
       </c>
       <c r="M2" s="12">
         <f t="shared" ref="M2:M41" si="3">F2/(1+I2-H2)</f>
-        <v>11.948457633736822</v>
+        <v>17.08408163265306</v>
       </c>
       <c r="N2" s="12">
         <f t="shared" ref="N2:N41" si="4">L2-F2</f>
-        <v>1.2285900000000005</v>
+        <v>0.52319999999999922</v>
       </c>
       <c r="O2" s="12">
         <f t="shared" ref="O2:O41" si="5">0.5*(M2-F2)</f>
-        <v>-1.6757711831315891</v>
+        <v>-1.9219591836734704</v>
       </c>
       <c r="P2" s="14">
         <f t="shared" ref="P2:P41" si="6">N2+O2</f>
-        <v>-0.44718118313158861</v>
+        <v>-1.3987591836734712</v>
       </c>
       <c r="Q2" s="12">
         <f t="shared" ref="Q2:Q46" si="7">MAX($P$2:$P$280)-P2</f>
-        <v>124.01376058792488</v>
+        <v>124.96533858846676</v>
       </c>
       <c r="R2" s="9">
         <f t="shared" ref="R2:R46" si="8">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.0636212889537134E-3</v>
+        <v>8.0022189456324284E-3</v>
       </c>
       <c r="S2" s="9">
         <f t="shared" ref="S2:S41" si="9">Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.89536605345572151</v>
+        <v>0.90223634458197444</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="D3" s="8">
-        <v>45627</v>
+        <v>45481</v>
       </c>
       <c r="E3" s="2">
-        <v>1.8976999999999999</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>21.73</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>41.237020999999999</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H3" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C3,Sheet1!$G:$G,0),1)</f>
-        <v>-4.8300000000000003E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C3,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I3" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C3,Sheet1!$G:$G,0),2)</f>
-        <v>0.61990000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C3,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25</v>
       </c>
       <c r="J3" s="9">
         <f t="shared" si="1"/>
-        <v>-7.7915792869817715E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>-4.8916248708963496E-3</v>
+        <v>6.9530133741456208E-3</v>
       </c>
       <c r="L3" s="12">
         <f t="shared" ref="L3:L41" si="10">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
-        <v>20.680441000000002</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="M3" s="12">
         <f t="shared" si="3"/>
-        <v>13.026016065219999</v>
+        <v>13.387755102040813</v>
       </c>
       <c r="N3" s="12">
         <f t="shared" si="4"/>
-        <v>-1.0495589999999986</v>
+        <v>0.41000000000000014</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" si="5"/>
-        <v>-4.3519919673900009</v>
+        <v>-1.5061224489795926</v>
       </c>
       <c r="P3" s="14">
         <f t="shared" si="6"/>
-        <v>-5.4015509673899995</v>
+        <v>-1.0961224489795924</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" si="7"/>
-        <v>128.96813037218328</v>
+        <v>124.66270185377289</v>
       </c>
       <c r="R3" s="9">
         <f t="shared" si="8"/>
-        <v>7.7538535847123261E-3</v>
+        <v>8.0216454892256556E-3</v>
       </c>
       <c r="S3" s="9">
         <f t="shared" si="9"/>
-        <v>0.93113607204125293</v>
+        <v>0.90005133980920593</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="D4" s="8">
-        <v>45553</v>
+        <v>45623</v>
       </c>
       <c r="E4" s="2">
-        <v>1.7345999999999999</v>
+        <v>1.9595</v>
       </c>
       <c r="F4" s="1">
-        <v>51.88</v>
+        <v>15.3</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>89.991048000000006</v>
+        <v>29.980350000000001</v>
       </c>
       <c r="H4" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C4,Sheet1!$G:$G,0),1)</f>
-        <v>5.6500000000000002E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C4,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>8.0299999999999996E-2</v>
       </c>
       <c r="I4" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C4,Sheet1!$G:$G,0),2)</f>
-        <v>0.22939999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C4,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.36080000000000001</v>
       </c>
       <c r="J4" s="9">
         <f t="shared" si="1"/>
-        <v>0.24629468177855277</v>
+        <v>0.22256097560975607</v>
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>1.5462605802785426E-2</v>
+        <v>1.5474694399775312E-2</v>
       </c>
       <c r="L4" s="12">
         <f t="shared" si="10"/>
-        <v>54.811220000000006</v>
+        <v>16.528590000000001</v>
       </c>
       <c r="M4" s="12">
         <f t="shared" si="3"/>
-        <v>44.232244863159693</v>
+        <v>11.948457633736822</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" si="4"/>
-        <v>2.9312200000000033</v>
+        <v>1.2285900000000005</v>
       </c>
       <c r="O4" s="12">
         <f t="shared" si="5"/>
-        <v>-3.8238775684201549</v>
+        <v>-1.6757711831315891</v>
       </c>
       <c r="P4" s="14">
         <f t="shared" si="6"/>
-        <v>-0.89265756842015165</v>
+        <v>-0.44718118313158861</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="7"/>
-        <v>124.45923697321344</v>
+        <v>124.01376058792488</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" si="8"/>
-        <v>8.0347592056604338E-3</v>
+        <v>8.0636212889537134E-3</v>
       </c>
       <c r="S4" s="9">
         <f t="shared" si="9"/>
-        <v>0.8985823451890953</v>
+        <v>0.89536605345572151</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1241,575 +1240,575 @@
         <v>40</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>50</v>
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
       </c>
       <c r="D5" s="8">
-        <v>45511</v>
+        <v>45627</v>
       </c>
       <c r="E5" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>1.8976999999999999</v>
       </c>
       <c r="F5" s="1">
-        <v>10.92</v>
+        <v>21.73</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>1.092E-18</v>
+        <v>41.237020999999999</v>
       </c>
       <c r="H5" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),1)</f>
-        <v>-1.4657</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>-4.8300000000000003E-2</v>
       </c>
       <c r="I5" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),2)</f>
-        <v>1.325</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.61990000000000001</v>
       </c>
       <c r="J5" s="9">
         <f t="shared" si="1"/>
-        <v>-1.1061886792452831</v>
+        <v>-7.7915792869817715E-2</v>
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>-6.9447538887797117E-2</v>
+        <v>-5.4174954988100259E-3</v>
       </c>
       <c r="L5" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>20.680441000000002</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="3"/>
-        <v>2.8807344289972825</v>
+        <v>13.026016065219999</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="4"/>
-        <v>-10.92</v>
+        <v>-1.0495589999999986</v>
       </c>
       <c r="O5" s="12">
         <f t="shared" si="5"/>
-        <v>-4.0196327855013587</v>
+        <v>-4.3519919673900009</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="6"/>
-        <v>-14.93963278550136</v>
+        <v>-5.4015509673899995</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="7"/>
-        <v>138.50621219029466</v>
+        <v>128.96813037218328</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="8"/>
-        <v>7.2198927700520242E-3</v>
+        <v>7.7538535847123261E-3</v>
       </c>
       <c r="S5" s="9">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.93113607204125293</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8">
-        <v>45511</v>
+        <v>45553</v>
       </c>
       <c r="E6" s="2">
-        <v>0.45179999999999998</v>
+        <v>1.7345999999999999</v>
       </c>
       <c r="F6" s="1">
-        <v>77.430000000000007</v>
+        <v>51.88</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>34.982874000000002</v>
+        <v>89.991048000000006</v>
       </c>
       <c r="H6" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1)</f>
-        <v>0.13569999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>5.6500000000000002E-2</v>
       </c>
       <c r="I6" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),2)</f>
-        <v>0.25069999999999998</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.22939999999999999</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="1"/>
-        <v>0.54128440366972475</v>
+        <v>0.24629468177855277</v>
       </c>
       <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v>3.3982330843286453E-2</v>
+        <v>1.712490216387217E-2</v>
       </c>
       <c r="L6" s="12">
         <f t="shared" si="10"/>
-        <v>87.937251000000003</v>
+        <v>54.811220000000006</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="3"/>
-        <v>69.443946188340817</v>
+        <v>44.232244863159693</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="4"/>
-        <v>10.507250999999997</v>
+        <v>2.9312200000000033</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="5"/>
-        <v>-3.9930269058295949</v>
+        <v>-3.8238775684201549</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="6"/>
-        <v>6.5142240941704017</v>
+        <v>-0.89265756842015165</v>
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="7"/>
-        <v>117.05235531062289</v>
+        <v>124.45923697321344</v>
       </c>
       <c r="R6" s="9">
         <f t="shared" si="8"/>
-        <v>8.5431856313039675E-3</v>
+        <v>8.0347592056604321E-3</v>
       </c>
       <c r="S6" s="9">
         <f t="shared" si="9"/>
-        <v>0.8451054538247269</v>
+        <v>0.8985823451890953</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D7" s="8">
-        <v>45627</v>
+        <v>45688</v>
       </c>
       <c r="E7" s="2">
-        <v>0.71050000000000002</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>42.26</v>
+        <v>44.24</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>30.025729999999999</v>
+        <v>44.24</v>
       </c>
       <c r="H7" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1)</f>
-        <v>0.10249999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I7" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),2)</f>
-        <v>0.54600000000000004</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25</v>
       </c>
       <c r="J7" s="9">
         <f t="shared" si="1"/>
-        <v>0.1877289377289377</v>
+        <v>0.1</v>
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>1.1785794727342702E-2</v>
+        <v>6.9530133741456208E-3</v>
       </c>
       <c r="L7" s="12">
         <f t="shared" si="10"/>
-        <v>46.591650000000001</v>
+        <v>45.345999999999997</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" si="3"/>
-        <v>29.276065119501212</v>
+        <v>36.114285714285714</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="4"/>
-        <v>4.3316500000000033</v>
+        <v>1.1059999999999945</v>
       </c>
       <c r="O7" s="12">
         <f t="shared" si="5"/>
-        <v>-6.4919674402493932</v>
+        <v>-4.0628571428571441</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="6"/>
-        <v>-2.1603174402493899</v>
+        <v>-2.9568571428571495</v>
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="7"/>
-        <v>125.72689684504267</v>
+        <v>126.52343654765043</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" si="8"/>
-        <v>7.9537475678930613E-3</v>
+        <v>7.9036740329400269E-3</v>
       </c>
       <c r="S7" s="9">
         <f t="shared" si="9"/>
-        <v>0.90773471353260027</v>
+        <v>0.91348564477251748</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
+        <v>150</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="D8" s="8">
-        <v>45460</v>
+        <v>45481</v>
       </c>
       <c r="E8" s="2">
-        <v>0.43659999999999999</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>160.25</v>
+        <v>48.68</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>69.965149999999994</v>
+        <v>48.68</v>
       </c>
       <c r="H8" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),1)</f>
-        <v>7.5399999999999995E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I8" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),2)</f>
-        <v>0.1905</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25</v>
       </c>
       <c r="J8" s="9">
         <f t="shared" si="1"/>
-        <v>0.39580052493438317</v>
+        <v>0.1</v>
       </c>
       <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v>2.484871962886552E-2</v>
+        <v>6.9530133741456208E-3</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" si="10"/>
-        <v>172.33284999999998</v>
+        <v>49.896999999999998</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="3"/>
-        <v>143.70908438705047</v>
+        <v>39.738775510204079</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="4"/>
-        <v>12.082849999999979</v>
+        <v>1.2169999999999987</v>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="5"/>
-        <v>-8.2704578064747665</v>
+        <v>-4.4706122448979606</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="6"/>
-        <v>3.8123921935252127</v>
+        <v>-3.2536122448979619</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="7"/>
-        <v>119.75418721126807</v>
+        <v>126.82019164969125</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" si="8"/>
-        <v>8.3504387052105236E-3</v>
+        <v>7.885179694115646E-3</v>
       </c>
       <c r="S8" s="9">
         <f t="shared" si="9"/>
-        <v>0.86461239043009097</v>
+        <v>0.91562818478821795</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>150</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="D9" s="8">
-        <v>45484</v>
+        <v>45481</v>
       </c>
       <c r="E9" s="2">
-        <v>0.4108</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>189.76</v>
+        <v>51.28</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>77.953407999999996</v>
+        <v>51.28</v>
       </c>
       <c r="H9" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C9,Sheet1!$G:$G,0),1)</f>
-        <v>0.2722</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C9,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I9" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C9,Sheet1!$G:$G,0),2)</f>
-        <v>0.3296</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C9,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25</v>
       </c>
       <c r="J9" s="9">
         <f t="shared" si="1"/>
-        <v>0.82584951456310673</v>
+        <v>0.1</v>
       </c>
       <c r="K9" s="9">
         <f t="shared" si="2"/>
-        <v>5.1847589253236605E-2</v>
+        <v>6.9530133741456208E-3</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" si="10"/>
-        <v>241.41267199999999</v>
+        <v>52.561999999999998</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="3"/>
-        <v>179.4590505012294</v>
+        <v>41.861224489795916</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="4"/>
-        <v>51.652671999999995</v>
+        <v>1.2819999999999965</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="5"/>
-        <v>-5.150474749385296</v>
+        <v>-4.7093877551020427</v>
       </c>
       <c r="P9" s="14">
         <f t="shared" si="6"/>
-        <v>46.502197250614699</v>
+        <v>-3.4273877551020462</v>
       </c>
       <c r="Q9" s="12">
         <f t="shared" si="7"/>
-        <v>77.064382154178588</v>
+        <v>126.99396715989533</v>
       </c>
       <c r="R9" s="9">
         <f t="shared" si="8"/>
-        <v>1.2976163203376542E-2</v>
+        <v>7.8743898026346539E-3</v>
       </c>
       <c r="S9" s="9">
         <f t="shared" si="9"/>
-        <v>0.55639657554348021</v>
+        <v>0.91688282533795251</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="D10" s="8">
-        <v>45544</v>
+        <v>45627</v>
       </c>
       <c r="E10" s="2">
-        <v>0.35149999999999998</v>
+        <v>0.95840000000000003</v>
       </c>
       <c r="F10" s="1">
-        <v>142.78</v>
+        <v>41.76</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>50.187169999999995</v>
+        <v>40.022784000000001</v>
       </c>
       <c r="H10" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C10,Sheet1!$G:$G,0),1)</f>
-        <v>3.5799999999999998E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C10,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.10249999999999999</v>
       </c>
       <c r="I10" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C10,Sheet1!$G:$G,0),2)</f>
-        <v>0.20300000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C10,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.54600000000000004</v>
       </c>
       <c r="J10" s="9">
         <f t="shared" si="1"/>
-        <v>0.17635467980295563</v>
+        <v>0.1877289377289377</v>
       </c>
       <c r="K10" s="9">
         <f t="shared" si="2"/>
-        <v>1.1071708392474941E-2</v>
+        <v>1.3052818147434543E-2</v>
       </c>
       <c r="L10" s="12">
         <f t="shared" si="10"/>
-        <v>147.891524</v>
+        <v>46.040399999999998</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="3"/>
-        <v>122.32693625771076</v>
+        <v>28.929684793903704</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="4"/>
-        <v>5.1115240000000028</v>
+        <v>4.2804000000000002</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="5"/>
-        <v>-10.226531871144623</v>
+        <v>-6.4151576030481472</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="6"/>
-        <v>-5.1150078711446199</v>
+        <v>-2.134757603048147</v>
       </c>
       <c r="Q10" s="12">
         <f t="shared" si="7"/>
-        <v>128.68158727593791</v>
+        <v>125.70133700784143</v>
       </c>
       <c r="R10" s="9">
         <f t="shared" si="8"/>
-        <v>7.7711195608401486E-3</v>
+        <v>7.9553648656705903E-3</v>
       </c>
       <c r="S10" s="9">
         <f t="shared" si="9"/>
-        <v>0.92906726161236275</v>
+        <v>0.90755017424878737</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>59</v>
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D11" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E11" s="2">
-        <v>0.25669999999999998</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F11" s="1">
-        <v>132.38999999999999</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>33.984512999999993</v>
+        <v>34.982874000000002</v>
       </c>
       <c r="H11" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),1)</f>
-        <v>0.1193</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.13569999999999999</v>
       </c>
       <c r="I11" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),2)</f>
-        <v>0.2243</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25069999999999998</v>
       </c>
       <c r="J11" s="9">
         <f t="shared" si="1"/>
-        <v>0.53187695051270623</v>
+        <v>0.54128440366972475</v>
       </c>
       <c r="K11" s="9">
         <f t="shared" si="2"/>
-        <v>3.3391722314004703E-2</v>
+        <v>3.763557697932033E-2</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" si="10"/>
-        <v>148.18412699999999</v>
+        <v>87.937251000000003</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="3"/>
-        <v>119.80995475113122</v>
+        <v>69.443946188340817</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="4"/>
-        <v>15.794127000000003</v>
+        <v>10.507250999999997</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="5"/>
-        <v>-6.2900226244343855</v>
+        <v>-3.9930269058295949</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" si="6"/>
-        <v>9.5041043755656176</v>
+        <v>6.5142240941704017</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="7"/>
-        <v>114.06247502922767</v>
+        <v>117.05235531062289</v>
       </c>
       <c r="R11" s="9">
         <f t="shared" si="8"/>
-        <v>8.7671252069864113E-3</v>
+        <v>8.5431856313039675E-3</v>
       </c>
       <c r="S11" s="9">
         <f t="shared" si="9"/>
-        <v>0.82351883879776044</v>
+        <v>0.8451054538247269</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D12" s="8">
-        <v>45511</v>
+        <v>45460</v>
       </c>
       <c r="E12" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.43659999999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>283.43</v>
+        <v>160.25</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
-        <v>2.8342999999999998E-17</v>
+        <v>69.965149999999994</v>
       </c>
       <c r="H12" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),1)</f>
-        <v>0.17119999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>7.5399999999999995E-2</v>
       </c>
       <c r="I12" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),2)</f>
-        <v>0.24590000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.1905</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" si="1"/>
-        <v>0.69621797478649849</v>
+        <v>0.39580052493438317</v>
       </c>
       <c r="K12" s="9">
         <f t="shared" si="2"/>
-        <v>4.3709202404201772E-2</v>
+        <v>2.7520063433626233E-2</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="10"/>
-        <v>331.953216</v>
+        <v>172.33284999999998</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="3"/>
-        <v>263.72941285940266</v>
+        <v>143.70908438705047</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="4"/>
-        <v>48.523215999999991</v>
+        <v>12.082849999999979</v>
       </c>
       <c r="O12" s="12">
         <f t="shared" si="5"/>
-        <v>-9.8502935702986747</v>
+        <v>-8.2704578064747665</v>
       </c>
       <c r="P12" s="14">
         <f t="shared" si="6"/>
-        <v>38.672922429701316</v>
+        <v>3.8123921935252127</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="7"/>
-        <v>84.893656975091972</v>
+        <v>119.75418721126807</v>
       </c>
       <c r="R12" s="9">
         <f t="shared" si="8"/>
-        <v>1.1779443077748468E-2</v>
+        <v>8.3504387052105236E-3</v>
       </c>
       <c r="S12" s="9">
         <f t="shared" si="9"/>
-        <v>0.6129231002177431</v>
+        <v>0.86461239043009097</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1817,575 +1816,575 @@
         <v>36</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D13" s="8">
-        <v>45544</v>
+        <v>45484</v>
       </c>
       <c r="E13" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.4108</v>
       </c>
       <c r="F13" s="1">
-        <v>188.12</v>
+        <v>189.76</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="0"/>
-        <v>1.8812000000000001E-17</v>
+        <v>77.953407999999996</v>
       </c>
       <c r="H13" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),1)</f>
-        <v>0.16470000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.2722</v>
       </c>
       <c r="I13" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),2)</f>
-        <v>0.372</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.3296</v>
       </c>
       <c r="J13" s="9">
         <f t="shared" si="1"/>
-        <v>0.44274193548387103</v>
+        <v>0.82584951456310673</v>
       </c>
       <c r="K13" s="9">
         <f t="shared" si="2"/>
-        <v>2.7795744395750475E-2</v>
+        <v>5.7421427197889494E-2</v>
       </c>
       <c r="L13" s="12">
         <f t="shared" si="10"/>
-        <v>219.10336400000003</v>
+        <v>241.41267199999999</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="3"/>
-        <v>155.8187691543113</v>
+        <v>179.4590505012294</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="4"/>
-        <v>30.983364000000023</v>
+        <v>51.652671999999995</v>
       </c>
       <c r="O13" s="12">
         <f t="shared" si="5"/>
-        <v>-16.150615422844353</v>
+        <v>-5.150474749385296</v>
       </c>
       <c r="P13" s="14">
         <f t="shared" si="6"/>
-        <v>14.83274857715567</v>
+        <v>46.502197250614699</v>
       </c>
       <c r="Q13" s="12">
         <f t="shared" si="7"/>
-        <v>108.73383082763762</v>
+        <v>77.064382154178588</v>
       </c>
       <c r="R13" s="9">
         <f t="shared" si="8"/>
-        <v>9.1967696933733262E-3</v>
+        <v>1.2976163203376542E-2</v>
       </c>
       <c r="S13" s="9">
         <f t="shared" si="9"/>
-        <v>0.78504659905252072</v>
+        <v>0.55639657554348021</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D14" s="8">
-        <v>45580</v>
+        <v>45544</v>
       </c>
       <c r="E14" s="2">
-        <v>0.19139999999999999</v>
+        <v>0.35149999999999998</v>
       </c>
       <c r="F14" s="1">
-        <v>135.82</v>
+        <v>142.78</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="0"/>
-        <v>25.995947999999999</v>
+        <v>50.187169999999995</v>
       </c>
       <c r="H14" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1)</f>
-        <v>6.7000000000000004E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>3.5799999999999998E-2</v>
       </c>
       <c r="I14" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),2)</f>
-        <v>0.25819999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.20300000000000001</v>
       </c>
       <c r="J14" s="9">
         <f t="shared" si="1"/>
-        <v>0.2594887683965918</v>
+        <v>0.17635467980295563</v>
       </c>
       <c r="K14" s="9">
         <f t="shared" si="2"/>
-        <v>1.6290942650456285E-2</v>
+        <v>1.2261964472631191E-2</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="10"/>
-        <v>144.91994</v>
+        <v>147.891524</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" si="3"/>
-        <v>114.01947615849562</v>
+        <v>122.32693625771076</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="4"/>
-        <v>9.0999400000000037</v>
+        <v>5.1115240000000028</v>
       </c>
       <c r="O14" s="12">
         <f t="shared" si="5"/>
-        <v>-10.900261920752186</v>
+        <v>-10.226531871144623</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="6"/>
-        <v>-1.8003219207521823</v>
+        <v>-5.1150078711446199</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="7"/>
-        <v>125.36690132554547</v>
+        <v>128.68158727593791</v>
       </c>
       <c r="R14" s="9">
         <f t="shared" si="8"/>
-        <v>7.9765870371419495E-3</v>
+        <v>7.7711195608401486E-3</v>
       </c>
       <c r="S14" s="9">
         <f t="shared" si="9"/>
-        <v>0.90513558448413134</v>
+        <v>0.92906726161236275</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
+        <v>97</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>99</v>
       </c>
       <c r="D15" s="8">
-        <v>45482</v>
+        <v>45630</v>
       </c>
       <c r="E15" s="2">
-        <v>0.18820000000000001</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="F15" s="1">
-        <v>227.38</v>
+        <v>34.78</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="0"/>
-        <v>42.792915999999998</v>
+        <v>9.99925</v>
       </c>
       <c r="H15" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1)</f>
-        <v>0.25430000000000003</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>-7.0800000000000002E-2</v>
       </c>
       <c r="I15" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),2)</f>
-        <v>0.2868</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.5726</v>
       </c>
       <c r="J15" s="9">
         <f t="shared" si="1"/>
-        <v>0.8866806136680615</v>
+        <v>-0.12364652462451974</v>
       </c>
       <c r="K15" s="9">
         <f t="shared" si="2"/>
-        <v>5.566662139480677E-2</v>
+        <v>-8.5971593938091156E-3</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="10"/>
-        <v>285.20273399999996</v>
+        <v>32.317576000000003</v>
       </c>
       <c r="M15" s="12">
         <f t="shared" si="3"/>
-        <v>220.22276029055689</v>
+        <v>21.163441645369357</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="4"/>
-        <v>57.822733999999969</v>
+        <v>-2.4624239999999986</v>
       </c>
       <c r="O15" s="12">
         <f t="shared" si="5"/>
-        <v>-3.578619854721552</v>
+        <v>-6.8082791773153222</v>
       </c>
       <c r="P15" s="14">
         <f t="shared" si="6"/>
-        <v>54.244114145278417</v>
+        <v>-9.2707031773153208</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="7"/>
-        <v>69.322465259514871</v>
+        <v>132.8372825821086</v>
       </c>
       <c r="R15" s="9">
         <f t="shared" si="8"/>
-        <v>1.4425338110184196E-2</v>
+        <v>7.528007051648967E-3</v>
       </c>
       <c r="S15" s="9">
         <f t="shared" si="9"/>
-        <v>0.50050076572935409</v>
+        <v>0.9590709361079236</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
+        <v>40</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="D16" s="8">
-        <v>45574</v>
+        <v>45627</v>
       </c>
       <c r="E16" s="2">
-        <v>0.13370000000000001</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="F16" s="1">
-        <v>423.77</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="0"/>
-        <v>56.658049000000005</v>
+        <v>10.9251</v>
       </c>
       <c r="H16" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),1)</f>
-        <v>0.24590000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.1114</v>
       </c>
       <c r="I16" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),2)</f>
-        <v>0.2702</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.245</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>0.91006661732050342</v>
+        <v>0.45469387755102042</v>
       </c>
       <c r="K16" s="9">
         <f t="shared" si="2"/>
-        <v>5.7134816132788716E-2</v>
+        <v>3.1614926117543761E-2</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="10"/>
-        <v>527.97504300000003</v>
+        <v>44.233719999999991</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" si="3"/>
-        <v>413.71668456506882</v>
+        <v>35.109386026817212</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="4"/>
-        <v>104.20504300000005</v>
+        <v>4.4337199999999939</v>
       </c>
       <c r="O16" s="12">
         <f t="shared" si="5"/>
-        <v>-5.0266577174655822</v>
+        <v>-2.3453069865913925</v>
       </c>
       <c r="P16" s="14">
         <f t="shared" si="6"/>
-        <v>99.178385282534464</v>
+        <v>2.0884130134086014</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="7"/>
-        <v>24.388194122258824</v>
+        <v>121.47816639138469</v>
       </c>
       <c r="R16" s="9">
         <f t="shared" si="8"/>
-        <v>4.1003445970085643E-2</v>
+        <v>8.2319319570411352E-3</v>
       </c>
       <c r="S16" s="9">
         <f t="shared" si="9"/>
-        <v>0.17608014641792177</v>
+        <v>0.87705933524833513</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>8</v>
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D17" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E17" s="2">
-        <v>0.12939999999999999</v>
+        <v>0.25669999999999998</v>
       </c>
       <c r="F17" s="1">
-        <v>501.56</v>
+        <v>132.38999999999999</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="0"/>
-        <v>64.901863999999989</v>
+        <v>33.984512999999993</v>
       </c>
       <c r="H17" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),1)</f>
-        <v>0.2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.1193</v>
       </c>
       <c r="I17" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),2)</f>
-        <v>0.27160000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.2243</v>
       </c>
       <c r="J17" s="9">
         <f t="shared" si="1"/>
-        <v>0.7363770250368189</v>
+        <v>0.53187695051270623</v>
       </c>
       <c r="K17" s="9">
         <f t="shared" si="2"/>
-        <v>4.6230424376803171E-2</v>
+        <v>3.6981475503146351E-2</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="10"/>
-        <v>601.87199999999996</v>
+        <v>148.18412699999999</v>
       </c>
       <c r="M17" s="12">
         <f t="shared" si="3"/>
-        <v>468.04777902202312</v>
+        <v>119.80995475113122</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="4"/>
-        <v>100.31199999999995</v>
+        <v>15.794127000000003</v>
       </c>
       <c r="O17" s="12">
         <f t="shared" si="5"/>
-        <v>-16.75611048898844</v>
+        <v>-6.2900226244343855</v>
       </c>
       <c r="P17" s="14">
         <f t="shared" si="6"/>
-        <v>83.555889511011515</v>
+        <v>9.5041043755656176</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="7"/>
-        <v>40.010689893781773</v>
+        <v>114.06247502922767</v>
       </c>
       <c r="R17" s="9">
         <f t="shared" si="8"/>
-        <v>2.499332060143792E-2</v>
+        <v>8.7671252069864113E-3</v>
       </c>
       <c r="S17" s="9">
         <f t="shared" si="9"/>
-        <v>0.28887289068890865</v>
+        <v>0.82351883879776044</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D18" s="8">
-        <v>45483</v>
+        <v>45511</v>
       </c>
       <c r="E18" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.25169999999999998</v>
       </c>
       <c r="F18" s="1">
-        <v>167.24</v>
+        <v>178.56</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="0"/>
-        <v>1.6724000000000001E-17</v>
+        <v>44.943551999999997</v>
       </c>
       <c r="H18" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),1)</f>
-        <v>0.18140000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>9.6799999999999997E-2</v>
       </c>
       <c r="I18" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),2)</f>
-        <v>0.2843</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.4829</v>
       </c>
       <c r="J18" s="9">
         <f t="shared" si="1"/>
-        <v>0.63805838902567713</v>
+        <v>0.20045558086560364</v>
       </c>
       <c r="K18" s="9">
         <f t="shared" si="2"/>
-        <v>4.0057890318293862E-2</v>
+        <v>1.3937703346806711E-2</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="10"/>
-        <v>197.577336</v>
+        <v>195.84460799999999</v>
       </c>
       <c r="M18" s="12">
         <f t="shared" si="3"/>
-        <v>151.63659443285883</v>
+        <v>128.82187432364188</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="4"/>
-        <v>30.337335999999993</v>
+        <v>17.284607999999992</v>
       </c>
       <c r="O18" s="12">
         <f t="shared" si="5"/>
-        <v>-7.8017027835705903</v>
+        <v>-24.869062838179062</v>
       </c>
       <c r="P18" s="14">
         <f t="shared" si="6"/>
-        <v>22.535633216429403</v>
+        <v>-7.5844548381790702</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="7"/>
-        <v>101.03094618836388</v>
+        <v>131.15103424297234</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" si="8"/>
-        <v>9.8979573856072013E-3</v>
+        <v>7.6247969051268421E-3</v>
       </c>
       <c r="S18" s="9">
         <f t="shared" si="9"/>
-        <v>0.72943259793688353</v>
+        <v>0.94689640391568153</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D19" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E19" s="2">
-        <v>0.25169999999999998</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F19" s="1">
-        <v>178.56</v>
+        <v>135.82</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="0"/>
-        <v>44.943551999999997</v>
+        <v>25.995947999999999</v>
       </c>
       <c r="H19" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),1)</f>
-        <v>9.6799999999999997E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="I19" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),2)</f>
-        <v>0.4829</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25819999999999999</v>
       </c>
       <c r="J19" s="9">
         <f t="shared" si="1"/>
-        <v>0.20045558086560364</v>
+        <v>0.2594887683965918</v>
       </c>
       <c r="K19" s="9">
         <f t="shared" si="2"/>
-        <v>1.2584785044932769E-2</v>
+        <v>1.8042288771020782E-2</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="10"/>
-        <v>195.84460799999999</v>
+        <v>144.91994</v>
       </c>
       <c r="M19" s="12">
         <f t="shared" si="3"/>
-        <v>128.82187432364188</v>
+        <v>114.01947615849562</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="4"/>
-        <v>17.284607999999992</v>
+        <v>9.0999400000000037</v>
       </c>
       <c r="O19" s="12">
         <f t="shared" si="5"/>
-        <v>-24.869062838179062</v>
+        <v>-10.900261920752186</v>
       </c>
       <c r="P19" s="14">
         <f t="shared" si="6"/>
-        <v>-7.5844548381790702</v>
+        <v>-1.8003219207521823</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="7"/>
-        <v>131.15103424297234</v>
+        <v>125.36690132554547</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" si="8"/>
-        <v>7.6247969051268421E-3</v>
+        <v>7.9765870371419512E-3</v>
       </c>
       <c r="S19" s="9">
         <f t="shared" si="9"/>
-        <v>0.94689640391568153</v>
+        <v>0.90513558448413134</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D20" s="8">
-        <v>45562</v>
+        <v>45482</v>
       </c>
       <c r="E20" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.18820000000000001</v>
       </c>
       <c r="F20" s="1">
-        <v>668.82</v>
+        <v>227.38</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="0"/>
-        <v>6.6881999999999999E-17</v>
+        <v>42.792915999999998</v>
       </c>
       <c r="H20" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),1)</f>
-        <v>0.1993</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.25430000000000003</v>
       </c>
       <c r="I20" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),2)</f>
-        <v>0.27200000000000002</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.2868</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>0.73272058823529407</v>
+        <v>0.8866806136680615</v>
       </c>
       <c r="K20" s="9">
         <f t="shared" si="2"/>
-        <v>4.6000869923996872E-2</v>
+        <v>6.1651021654296777E-2</v>
       </c>
       <c r="L20" s="12">
         <f t="shared" si="10"/>
-        <v>802.11582600000008</v>
+        <v>285.20273399999996</v>
       </c>
       <c r="M20" s="12">
         <f t="shared" si="3"/>
-        <v>623.49212268108522</v>
+        <v>220.22276029055689</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="4"/>
-        <v>133.29582600000003</v>
+        <v>57.822733999999969</v>
       </c>
       <c r="O20" s="12">
         <f t="shared" si="5"/>
-        <v>-22.663938659457415</v>
+        <v>-3.578619854721552</v>
       </c>
       <c r="P20" s="14">
         <f t="shared" si="6"/>
-        <v>110.63188734054262</v>
+        <v>54.244114145278417</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="7"/>
-        <v>12.934692064250669</v>
+        <v>69.322465259514871</v>
       </c>
       <c r="R20" s="9">
         <f t="shared" si="8"/>
-        <v>7.7311465555784914E-2</v>
+        <v>1.4425338110184198E-2</v>
       </c>
       <c r="S20" s="9">
         <f t="shared" si="9"/>
-        <v>9.3387089717532706E-2</v>
+        <v>0.50050076572935409</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -2393,226 +2392,226 @@
         <v>36</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="D21" s="8">
-        <v>45481</v>
+        <v>45574</v>
       </c>
       <c r="E21" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F21" s="1">
-        <v>700.32</v>
+        <v>423.77</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="0"/>
-        <v>7.0031999999999998E-17</v>
+        <v>56.658049000000005</v>
       </c>
       <c r="H21" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),1)</f>
-        <v>0.23749999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.24590000000000001</v>
       </c>
       <c r="I21" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),2)</f>
-        <v>0.37659999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.2702</v>
       </c>
       <c r="J21" s="9">
         <f t="shared" si="1"/>
-        <v>0.63064259160913438</v>
+        <v>0.91006661732050342</v>
       </c>
       <c r="K21" s="9">
         <f t="shared" si="2"/>
-        <v>3.9592319761360704E-2</v>
+        <v>6.3277053615929252E-2</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="10"/>
-        <v>866.64600000000007</v>
+        <v>527.97504300000003</v>
       </c>
       <c r="M21" s="12">
         <f t="shared" si="3"/>
-        <v>614.80115880958658</v>
+        <v>413.71668456506882</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="4"/>
-        <v>166.32600000000002</v>
+        <v>104.20504300000005</v>
       </c>
       <c r="O21" s="12">
         <f t="shared" si="5"/>
-        <v>-42.759420595206734</v>
+        <v>-5.0266577174655822</v>
       </c>
       <c r="P21" s="14">
         <f t="shared" si="6"/>
-        <v>123.56657940479329</v>
+        <v>99.178385282534464</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24.388194122258824</v>
       </c>
       <c r="R21" s="9">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.1003445970085643E-2</v>
       </c>
       <c r="S21" s="9">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.17608014641792177</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D22" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E22" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F22" s="1">
-        <v>147.01</v>
+        <v>501.56</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="0"/>
-        <v>1.4700999999999999E-17</v>
+        <v>64.901863999999989</v>
       </c>
       <c r="H22" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),1)</f>
-        <v>0.56320000000000003</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.2</v>
       </c>
       <c r="I22" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),2)</f>
-        <v>0.50019999999999998</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.27160000000000001</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>1.1259496201519394</v>
+        <v>0.7363770250368189</v>
       </c>
       <c r="K22" s="9">
         <f t="shared" si="2"/>
-        <v>7.0688148864940251E-2</v>
+        <v>5.1200393034945661E-2</v>
       </c>
       <c r="L22" s="12">
         <f t="shared" si="10"/>
-        <v>229.80603200000002</v>
+        <v>601.87199999999996</v>
       </c>
       <c r="M22" s="12">
         <f t="shared" si="3"/>
-        <v>156.89434364994665</v>
+        <v>468.04777902202312</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="4"/>
-        <v>82.796032000000025</v>
+        <v>100.31199999999995</v>
       </c>
       <c r="O22" s="12">
         <f t="shared" si="5"/>
-        <v>4.9421718249733289</v>
+        <v>-16.75611048898844</v>
       </c>
       <c r="P22" s="14">
         <f t="shared" si="6"/>
-        <v>87.738203824973354</v>
+        <v>83.555889511011515</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="7"/>
-        <v>35.828375579819934</v>
+        <v>40.010689893781773</v>
       </c>
       <c r="R22" s="9">
         <f t="shared" si="8"/>
-        <v>2.7910838373683973E-2</v>
+        <v>2.499332060143792E-2</v>
       </c>
       <c r="S22" s="9">
         <f t="shared" si="9"/>
-        <v>0.25867702981145047</v>
+        <v>0.28887289068890865</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D23" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E23" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F23" s="1">
-        <v>169.34</v>
+        <v>10.92</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="0"/>
-        <v>1.6933999999999999E-17</v>
+        <v>1.092E-18</v>
       </c>
       <c r="H23" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),1)</f>
-        <v>0.25890000000000002</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>-1.4657</v>
       </c>
       <c r="I23" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),2)</f>
-        <v>0.41639999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),2),25%)</f>
+        <v>1.325</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>0.62175792507204619</v>
+        <v>-1.1061886792452831</v>
       </c>
       <c r="K23" s="9">
         <f t="shared" si="2"/>
-        <v>3.90345322551095E-2</v>
+        <v>-7.6913446811209332E-2</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="10"/>
-        <v>213.18212600000004</v>
+        <v>0</v>
       </c>
       <c r="M23" s="12">
         <f t="shared" si="3"/>
-        <v>146.2980561555076</v>
+        <v>2.8807344289972825</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="4"/>
-        <v>43.842126000000036</v>
+        <v>-10.92</v>
       </c>
       <c r="O23" s="12">
         <f t="shared" si="5"/>
-        <v>-11.520971922246204</v>
+        <v>-4.0196327855013587</v>
       </c>
       <c r="P23" s="14">
         <f t="shared" si="6"/>
-        <v>32.321154077753832</v>
+        <v>-14.93963278550136</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="7"/>
-        <v>91.245425327039456</v>
+        <v>138.50621219029466</v>
       </c>
       <c r="R23" s="9">
         <f t="shared" si="8"/>
-        <v>1.0959453544282646E-2</v>
+        <v>7.2198927700520242E-3</v>
       </c>
       <c r="S23" s="9">
         <f t="shared" si="9"/>
-        <v>0.658782186619014</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
       </c>
       <c r="D24" s="8">
         <v>45511</v>
@@ -2621,59 +2620,59 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F24" s="1">
-        <v>113.58</v>
+        <v>283.43</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>1.1357999999999999E-17</v>
+        <v>2.8342999999999998E-17</v>
       </c>
       <c r="H24" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),1)</f>
-        <v>9.0899999999999995E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.17119999999999999</v>
       </c>
       <c r="I24" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),2)</f>
-        <v>0.2077</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.24590000000000001</v>
       </c>
       <c r="J24" s="9">
         <f t="shared" si="1"/>
-        <v>0.43765045739046698</v>
+        <v>0.69621797478649849</v>
       </c>
       <c r="K24" s="9">
         <f t="shared" si="2"/>
-        <v>2.7476096735706362E-2</v>
+        <v>4.8408128900111022E-2</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="10"/>
-        <v>123.904422</v>
+        <v>331.953216</v>
       </c>
       <c r="M24" s="12">
         <f t="shared" si="3"/>
-        <v>101.70128939828079</v>
+        <v>263.72941285940266</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="4"/>
-        <v>10.324421999999998</v>
+        <v>48.523215999999991</v>
       </c>
       <c r="O24" s="12">
         <f t="shared" si="5"/>
-        <v>-5.9393553008596029</v>
+        <v>-9.8502935702986747</v>
       </c>
       <c r="P24" s="14">
         <f t="shared" si="6"/>
-        <v>4.3850666991403955</v>
+        <v>38.672922429701316</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="7"/>
-        <v>119.18151270565289</v>
+        <v>84.893656975091972</v>
       </c>
       <c r="R24" s="9">
         <f t="shared" si="8"/>
-        <v>8.3905630772596242E-3</v>
+        <v>1.1779443077748466E-2</v>
       </c>
       <c r="S24" s="9">
         <f t="shared" si="9"/>
-        <v>0.86047774190740678</v>
+        <v>0.6129231002177431</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -2681,1568 +2680,1584 @@
         <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="D25" s="8">
-        <v>45481</v>
+        <v>45544</v>
       </c>
       <c r="E25" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>64.349999999999994</v>
+        <v>188.12</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="0"/>
-        <v>6.4349999999999993E-18</v>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="H25" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),1)</f>
-        <v>0.49509999999999998</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.16470000000000001</v>
       </c>
       <c r="I25" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),2)</f>
-        <v>0.70050000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.372</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>0.70678087080656671</v>
+        <v>0.44274193548387103</v>
       </c>
       <c r="K25" s="9">
         <f t="shared" si="2"/>
-        <v>4.4372350695162349E-2</v>
+        <v>3.0783905987144727E-2</v>
       </c>
       <c r="L25" s="12">
         <f t="shared" si="10"/>
-        <v>96.209684999999979</v>
+        <v>219.10336400000003</v>
       </c>
       <c r="M25" s="12">
         <f t="shared" si="3"/>
-        <v>53.384768541562963</v>
+        <v>155.8187691543113</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="4"/>
-        <v>31.859684999999985</v>
+        <v>30.983364000000023</v>
       </c>
       <c r="O25" s="12">
         <f t="shared" si="5"/>
-        <v>-5.4826157292185158</v>
+        <v>-16.150615422844353</v>
       </c>
       <c r="P25" s="14">
         <f t="shared" si="6"/>
-        <v>26.377069270781469</v>
+        <v>14.83274857715567</v>
       </c>
       <c r="Q25" s="12">
         <f t="shared" si="7"/>
-        <v>97.189510134011812</v>
+        <v>108.73383082763762</v>
       </c>
       <c r="R25" s="9">
         <f t="shared" si="8"/>
-        <v>1.0289176255967633E-2</v>
+        <v>9.1967696933733262E-3</v>
       </c>
       <c r="S25" s="9">
         <f t="shared" si="9"/>
-        <v>0.70169784154144987</v>
+        <v>0.78504659905252072</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
       </c>
       <c r="D26" s="8">
-        <v>45511</v>
+        <v>45483</v>
       </c>
       <c r="E26" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>20.82</v>
+        <v>167.24</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="0"/>
-        <v>2.0820000000000002E-18</v>
+        <v>1.6724000000000001E-17</v>
       </c>
       <c r="H26" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),1)</f>
-        <v>-1.9199999999999998E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.18140000000000001</v>
       </c>
       <c r="I26" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),2)</f>
-        <v>0.71699999999999997</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.2843</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>-2.6778242677824266E-2</v>
+        <v>0.63805838902567713</v>
       </c>
       <c r="K26" s="9">
         <f t="shared" si="2"/>
-        <v>-1.6811626123166177E-3</v>
+        <v>4.4364285123813421E-2</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="10"/>
-        <v>20.420256000000002</v>
+        <v>197.577336</v>
       </c>
       <c r="M26" s="12">
         <f t="shared" si="3"/>
-        <v>11.991706024651537</v>
+        <v>151.63659443285883</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="4"/>
-        <v>-0.39974399999999832</v>
+        <v>30.337335999999993</v>
       </c>
       <c r="O26" s="12">
         <f t="shared" si="5"/>
-        <v>-4.4141469876742319</v>
+        <v>-7.8017027835705903</v>
       </c>
       <c r="P26" s="14">
         <f t="shared" si="6"/>
-        <v>-4.8138909876742302</v>
+        <v>22.535633216429403</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="7"/>
-        <v>128.38047039246752</v>
+        <v>101.03094618836388</v>
       </c>
       <c r="R26" s="9">
         <f t="shared" si="8"/>
-        <v>7.7893467514407316E-3</v>
+        <v>9.8979573856072013E-3</v>
       </c>
       <c r="S26" s="9">
         <f t="shared" si="9"/>
-        <v>0.92689323000245416</v>
+        <v>0.72943259793688353</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D27" s="8">
-        <v>45511</v>
+        <v>45562</v>
       </c>
       <c r="E27" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F27" s="1">
-        <v>13.04</v>
+        <v>668.82</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="0"/>
-        <v>1.304E-18</v>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="H27" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),1)</f>
-        <v>1.61E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.1993</v>
       </c>
       <c r="I27" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),2)</f>
-        <v>0.42009999999999997</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.27200000000000002</v>
       </c>
       <c r="J27" s="9">
         <f t="shared" si="1"/>
-        <v>3.8324208521780527E-2</v>
+        <v>0.73272058823529407</v>
       </c>
       <c r="K27" s="9">
         <f t="shared" si="2"/>
-        <v>2.4060289276113997E-3</v>
+        <v>5.0946160495118457E-2</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="10"/>
-        <v>13.249943999999999</v>
+        <v>802.11582600000008</v>
       </c>
       <c r="M27" s="12">
         <f t="shared" si="3"/>
-        <v>9.2877492877492873</v>
+        <v>623.49212268108522</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="4"/>
-        <v>0.20994400000000013</v>
+        <v>133.29582600000003</v>
       </c>
       <c r="O27" s="12">
         <f t="shared" si="5"/>
-        <v>-1.8761253561253559</v>
+        <v>-22.663938659457415</v>
       </c>
       <c r="P27" s="14">
         <f t="shared" si="6"/>
-        <v>-1.6661813561253558</v>
+        <v>110.63188734054262</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="7"/>
-        <v>125.23276076091864</v>
+        <v>12.934692064250669</v>
       </c>
       <c r="R27" s="9">
         <f t="shared" si="8"/>
-        <v>7.9851309986617314E-3</v>
+        <v>7.7311465555784914E-2</v>
       </c>
       <c r="S27" s="9">
         <f t="shared" si="9"/>
-        <v>0.90416710399141131</v>
+        <v>9.3387089717532706E-2</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D28" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E28" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F28" s="1">
-        <v>11.05</v>
+        <v>700.32</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="0"/>
-        <v>1.1050000000000001E-18</v>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="H28" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),1)</f>
-        <v>-0.1114</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.23749999999999999</v>
       </c>
       <c r="I28" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),2)</f>
-        <v>0.58130000000000004</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.37659999999999999</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>-0.19163942886633406</v>
+        <v>0.63064259160913438</v>
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
-        <v>-1.203129894414594E-2</v>
+        <v>4.3848663737641659E-2</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="10"/>
-        <v>9.8190300000000015</v>
+        <v>866.64600000000007</v>
       </c>
       <c r="M28" s="12">
         <f t="shared" si="3"/>
-        <v>6.528032138004372</v>
+        <v>614.80115880958658</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="4"/>
-        <v>-1.2309699999999992</v>
+        <v>166.32600000000002</v>
       </c>
       <c r="O28" s="12">
         <f t="shared" si="5"/>
-        <v>-2.2609839309978144</v>
+        <v>-42.759420595206734</v>
       </c>
       <c r="P28" s="14">
         <f t="shared" si="6"/>
-        <v>-3.4919539309978136</v>
+        <v>123.56657940479329</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="7"/>
-        <v>127.0585333357911</v>
+        <v>0</v>
       </c>
       <c r="R28" s="9">
         <f t="shared" si="8"/>
-        <v>7.8703883457964495E-3</v>
+        <v>0</v>
       </c>
       <c r="S28" s="9">
         <f t="shared" si="9"/>
-        <v>0.91734898620449223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>82</v>
+        <v>36</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
       </c>
       <c r="D29" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45666</v>
+        <v>45482</v>
       </c>
       <c r="E29" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F29" s="1">
-        <v>2742.9</v>
+        <v>147.01</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" si="0"/>
-        <v>2.7429000000000002E-16</v>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H29" s="11">
-        <v>7.4999999999999997E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C29,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.56320000000000003</v>
       </c>
       <c r="I29" s="11">
-        <v>0.26</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C29,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.50019999999999998</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>0.28846153846153844</v>
+        <v>1.1259496201519394</v>
       </c>
       <c r="K29" s="9">
         <f t="shared" si="2"/>
-        <v>1.8109879702990009E-2</v>
+        <v>7.8287427675306165E-2</v>
       </c>
       <c r="L29" s="12">
         <f t="shared" si="10"/>
-        <v>2948.6174999999998</v>
+        <v>229.80603200000002</v>
       </c>
       <c r="M29" s="12">
         <f t="shared" si="3"/>
-        <v>2314.6835443037976</v>
+        <v>156.89434364994665</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="4"/>
-        <v>205.71749999999975</v>
+        <v>82.796032000000025</v>
       </c>
       <c r="O29" s="12">
         <f t="shared" si="5"/>
-        <v>-214.10822784810125</v>
+        <v>4.9421718249733289</v>
       </c>
       <c r="P29" s="14">
         <f t="shared" si="6"/>
-        <v>-8.3907278481015055</v>
+        <v>87.738203824973354</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="7"/>
-        <v>131.95730725289479</v>
+        <v>35.828375579819934</v>
       </c>
       <c r="R29" s="9">
         <f t="shared" si="8"/>
-        <v>7.5782085950231648E-3</v>
+        <v>2.7910838373683976E-2</v>
       </c>
       <c r="S29" s="9">
         <f t="shared" si="9"/>
-        <v>0.95271760859070864</v>
+        <v>0.25867702981145047</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>55</v>
+        <v>36</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D30" s="8">
-        <v>45505</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F30" s="1">
-        <v>86.6</v>
+        <v>169.34</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" si="0"/>
-        <v>8.6599999999999986E-18</v>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="H30" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),1)</f>
-        <v>0.1913</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.25890000000000002</v>
       </c>
       <c r="I30" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),2)</f>
-        <v>0.2109</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.41639999999999999</v>
       </c>
       <c r="J30" s="9">
         <f t="shared" si="1"/>
-        <v>0.90706495969653866</v>
+        <v>0.62175792507204619</v>
       </c>
       <c r="K30" s="9">
         <f t="shared" si="2"/>
-        <v>5.6946369316726225E-2</v>
+        <v>4.3230911685069678E-2</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="10"/>
-        <v>103.16658</v>
+        <v>213.18212600000004</v>
       </c>
       <c r="M30" s="12">
         <f t="shared" si="3"/>
-        <v>84.935268732836391</v>
+        <v>146.2980561555076</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="4"/>
-        <v>16.566580000000002</v>
+        <v>43.842126000000036</v>
       </c>
       <c r="O30" s="12">
         <f t="shared" si="5"/>
-        <v>-0.83236563358180149</v>
+        <v>-11.520971922246204</v>
       </c>
       <c r="P30" s="14">
         <f t="shared" si="6"/>
-        <v>15.7342143664182</v>
+        <v>32.321154077753832</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="7"/>
-        <v>107.83236503837509</v>
+        <v>91.245425327039456</v>
       </c>
       <c r="R30" s="9">
         <f t="shared" si="8"/>
-        <v>9.2736535978240175E-3</v>
+        <v>1.0959453544282646E-2</v>
       </c>
       <c r="S30" s="9">
         <f t="shared" si="9"/>
-        <v>0.77853811271817497</v>
+        <v>0.658782186619014</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" t="s">
-        <v>75</v>
+        <v>40</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="D31" s="8">
-        <v>45562</v>
+        <v>45511</v>
       </c>
       <c r="E31" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F31" s="1">
-        <v>56</v>
+        <v>113.58</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="0"/>
-        <v>5.5999999999999995E-18</v>
+        <v>1.1357999999999999E-17</v>
       </c>
       <c r="H31" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),1)</f>
-        <v>-7.1999999999999998E-3</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>9.0899999999999995E-2</v>
       </c>
       <c r="I31" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),2)</f>
-        <v>0.41589999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.2077</v>
       </c>
       <c r="J31" s="9">
         <f t="shared" si="1"/>
-        <v>-1.7311853811012263E-2</v>
+        <v>0.43765045739046698</v>
       </c>
       <c r="K31" s="9">
         <f t="shared" si="2"/>
-        <v>-1.0868540451710281E-3</v>
+        <v>3.042989483436865E-2</v>
       </c>
       <c r="L31" s="12">
         <f t="shared" si="10"/>
-        <v>55.596800000000002</v>
+        <v>123.904422</v>
       </c>
       <c r="M31" s="12">
         <f t="shared" si="3"/>
-        <v>39.350713231677325</v>
+        <v>101.70128939828079</v>
       </c>
       <c r="N31" s="12">
         <f t="shared" si="4"/>
-        <v>-0.40319999999999823</v>
+        <v>10.324421999999998</v>
       </c>
       <c r="O31" s="12">
         <f t="shared" si="5"/>
-        <v>-8.3246433841613374</v>
+        <v>-5.9393553008596029</v>
       </c>
       <c r="P31" s="14">
         <f t="shared" si="6"/>
-        <v>-8.7278433841613356</v>
+        <v>4.3850666991403955</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="7"/>
-        <v>132.29442278895462</v>
+        <v>119.18151270565289</v>
       </c>
       <c r="R31" s="9">
         <f t="shared" si="8"/>
-        <v>7.5588976384535159E-3</v>
+        <v>8.3905630772596242E-3</v>
       </c>
       <c r="S31" s="9">
         <f t="shared" si="9"/>
-        <v>0.95515154661217927</v>
+        <v>0.86047774190740678</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>77</v>
+        <v>36</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D32" s="8">
-        <v>45580</v>
+        <v>45481</v>
       </c>
       <c r="E32" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F32" s="1">
-        <v>20.399999999999999</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" si="0"/>
-        <v>2.0399999999999999E-18</v>
+        <v>6.4349999999999993E-18</v>
       </c>
       <c r="H32" s="11">
-        <v>7.4999999999999997E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C32,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.49509999999999998</v>
       </c>
       <c r="I32" s="11">
-        <v>0.26</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C32,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.70050000000000001</v>
       </c>
       <c r="J32" s="9">
         <f t="shared" si="1"/>
-        <v>0.28846153846153844</v>
+        <v>0.70678087080656671</v>
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>1.8109879702990009E-2</v>
+        <v>4.9142568473083466E-2</v>
       </c>
       <c r="L32" s="12">
         <f t="shared" si="10"/>
-        <v>21.929999999999996</v>
+        <v>96.209684999999979</v>
       </c>
       <c r="M32" s="12">
         <f t="shared" si="3"/>
-        <v>17.215189873417721</v>
+        <v>53.384768541562963</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="4"/>
-        <v>1.5299999999999976</v>
+        <v>31.859684999999985</v>
       </c>
       <c r="O32" s="12">
         <f t="shared" si="5"/>
-        <v>-1.5924050632911388</v>
+        <v>-5.4826157292185158</v>
       </c>
       <c r="P32" s="14">
         <f t="shared" si="6"/>
-        <v>-6.2405063291141261E-2</v>
+        <v>26.377069270781469</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="7"/>
-        <v>123.62898446808443</v>
+        <v>97.189510134011812</v>
       </c>
       <c r="R32" s="9">
         <f t="shared" si="8"/>
-        <v>8.0887180648010256E-3</v>
+        <v>1.0289176255967633E-2</v>
       </c>
       <c r="S32" s="9">
         <f t="shared" si="9"/>
-        <v>0.89258801112999675</v>
+        <v>0.70169784154144987</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" t="s">
-        <v>57</v>
+        <v>40</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="D33" s="8">
-        <v>45574</v>
+        <v>45511</v>
       </c>
       <c r="E33" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F33" s="1">
-        <v>47.42</v>
+        <v>20.82</v>
       </c>
       <c r="G33" s="1">
         <f t="shared" si="0"/>
-        <v>4.7419999999999999E-18</v>
+        <v>2.0820000000000002E-18</v>
       </c>
       <c r="H33" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C33,Sheet1!$G:$G,0),1)</f>
-        <v>7.8399999999999997E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C33,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>-1.9199999999999998E-2</v>
       </c>
       <c r="I33" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C33,Sheet1!$G:$G,0),2)</f>
-        <v>0.36230000000000001</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C33,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.71699999999999997</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="1"/>
-        <v>0.21639525255313274</v>
+        <v>-2.6778242677824266E-2</v>
       </c>
       <c r="K33" s="9">
         <f t="shared" si="2"/>
-        <v>1.3585492239055969E-2</v>
+        <v>-1.8618947947502916E-3</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="10"/>
-        <v>51.137728000000003</v>
+        <v>20.420256000000002</v>
       </c>
       <c r="M33" s="12">
         <f t="shared" si="3"/>
-        <v>36.934340680738373</v>
+        <v>11.991706024651537</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="4"/>
-        <v>3.717728000000001</v>
+        <v>-0.39974399999999832</v>
       </c>
       <c r="O33" s="12">
         <f t="shared" si="5"/>
-        <v>-5.2428296596308144</v>
+        <v>-4.4141469876742319</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="6"/>
-        <v>-1.5251016596308133</v>
+        <v>-4.8138909876742302</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="7"/>
-        <v>125.09168106442411</v>
+        <v>128.38047039246752</v>
       </c>
       <c r="R33" s="9">
         <f t="shared" si="8"/>
-        <v>7.9941367122965193E-3</v>
+        <v>7.7893467514407334E-3</v>
       </c>
       <c r="S33" s="9">
         <f t="shared" si="9"/>
-        <v>0.90314852371068932</v>
+        <v>0.92689323000245416</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D34" s="8">
-        <v>45507</v>
+        <v>45511</v>
       </c>
       <c r="E34" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F34" s="1">
-        <v>41.8</v>
+        <v>13.04</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" si="0"/>
-        <v>4.1799999999999993E-18</v>
+        <v>1.304E-18</v>
       </c>
       <c r="H34" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C34,Sheet1!$G:$G,0),1)</f>
-        <v>0.1303</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C34,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>1.61E-2</v>
       </c>
       <c r="I34" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C34,Sheet1!$G:$G,0),2)</f>
-        <v>0.39119999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C34,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.42009999999999997</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>0.33307770961145194</v>
+        <v>3.8324208521780527E-2</v>
       </c>
       <c r="K34" s="9">
         <f t="shared" si="2"/>
-        <v>2.0910923809744224E-2</v>
+        <v>2.6646873440548556E-3</v>
       </c>
       <c r="L34" s="12">
         <f t="shared" si="10"/>
-        <v>47.246540000000003</v>
+        <v>13.249943999999999</v>
       </c>
       <c r="M34" s="12">
         <f t="shared" si="3"/>
-        <v>33.150923943215162</v>
+        <v>9.2877492877492873</v>
       </c>
       <c r="N34" s="12">
         <f t="shared" si="4"/>
-        <v>5.4465400000000059</v>
+        <v>0.20994400000000013</v>
       </c>
       <c r="O34" s="12">
         <f t="shared" si="5"/>
-        <v>-4.3245380283924177</v>
+        <v>-1.8761253561253559</v>
       </c>
       <c r="P34" s="14">
         <f t="shared" si="6"/>
-        <v>1.1220019716075882</v>
+        <v>-1.6661813561253558</v>
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="7"/>
-        <v>122.4445774331857</v>
+        <v>125.23276076091864</v>
       </c>
       <c r="R34" s="9">
         <f t="shared" si="8"/>
-        <v>8.1669602767478183E-3</v>
+        <v>7.9851309986617314E-3</v>
       </c>
       <c r="S34" s="9">
         <f t="shared" si="9"/>
-        <v>0.88403671934193273</v>
+        <v>0.90416710399141131</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D35" s="8">
-        <v>45574</v>
+        <v>45511</v>
       </c>
       <c r="E35" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F35" s="1">
-        <v>153.7552</v>
+        <v>11.05</v>
       </c>
       <c r="G35" s="1">
         <f t="shared" si="0"/>
-        <v>1.5375519999999999E-17</v>
+        <v>1.1050000000000001E-18</v>
       </c>
       <c r="H35" s="11">
-        <v>7.4999999999999997E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C35,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>-0.1114</v>
       </c>
       <c r="I35" s="11">
-        <v>0.26</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C35,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.58130000000000004</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="1"/>
-        <v>0.28846153846153844</v>
+        <v>-0.19163942886633406</v>
       </c>
       <c r="K35" s="9">
         <f t="shared" si="2"/>
-        <v>1.8109879702990009E-2</v>
+        <v>-1.332471511921249E-2</v>
       </c>
       <c r="L35" s="12">
         <f t="shared" si="10"/>
-        <v>165.28683999999998</v>
+        <v>9.8190300000000015</v>
       </c>
       <c r="M35" s="12">
         <f t="shared" si="3"/>
-        <v>129.75122362869197</v>
+        <v>6.528032138004372</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="4"/>
-        <v>11.531639999999982</v>
+        <v>-1.2309699999999992</v>
       </c>
       <c r="O35" s="12">
         <f t="shared" si="5"/>
-        <v>-12.001988185654014</v>
+        <v>-2.2609839309978144</v>
       </c>
       <c r="P35" s="14">
         <f t="shared" si="6"/>
-        <v>-0.47034818565403214</v>
+        <v>-3.4919539309978136</v>
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="7"/>
-        <v>124.03692759044732</v>
+        <v>127.0585333357911</v>
       </c>
       <c r="R35" s="9">
         <f t="shared" si="8"/>
-        <v>8.0621152057382527E-3</v>
+        <v>7.8703883457964512E-3</v>
       </c>
       <c r="S35" s="9">
         <f t="shared" si="9"/>
-        <v>0.89553331672973713</v>
+        <v>0.91734898620449223</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>91</v>
+        <v>76</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="D36" s="8">
-        <v>45627</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45671</v>
       </c>
       <c r="E36" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F36" s="1">
-        <v>133.53</v>
+        <v>2742.9</v>
       </c>
       <c r="G36" s="1">
         <f t="shared" si="0"/>
-        <v>1.3353E-17</v>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="H36" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),1)</f>
-        <v>5.7599999999999998E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I36" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),2)</f>
-        <v>0.2555</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="1"/>
-        <v>0.22544031311154597</v>
+        <v>0.1</v>
       </c>
       <c r="K36" s="9">
         <f t="shared" si="2"/>
-        <v>1.4153349428935596E-2</v>
+        <v>6.9530133741456208E-3</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="10"/>
-        <v>141.22132800000003</v>
+        <v>2811.4724999999999</v>
       </c>
       <c r="M36" s="12">
         <f t="shared" si="3"/>
-        <v>111.47007262709742</v>
+        <v>2239.1020408163263</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="4"/>
-        <v>7.691328000000027</v>
+        <v>68.572499999999764</v>
       </c>
       <c r="O36" s="12">
         <f t="shared" si="5"/>
-        <v>-11.029963686451289</v>
+        <v>-251.89897959183691</v>
       </c>
       <c r="P36" s="14">
         <f t="shared" si="6"/>
-        <v>-3.3386356864512621</v>
+        <v>-183.32647959183714</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="7"/>
-        <v>126.90521509124454</v>
+        <v>306.89305899663043</v>
       </c>
       <c r="R36" s="9">
         <f t="shared" si="8"/>
-        <v>7.8798968133894452E-3</v>
+        <v>3.2584640502116391E-3</v>
       </c>
       <c r="S36" s="9">
         <f t="shared" si="9"/>
-        <v>0.91624204491917349</v>
+        <v>2.2157349778289213</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>93</v>
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" t="s">
+        <v>56</v>
       </c>
       <c r="D37" s="8">
-        <v>45627</v>
+        <v>45505</v>
       </c>
       <c r="E37" s="2">
-        <v>0.27450000000000002</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F37" s="1">
-        <v>39.799999999999997</v>
+        <v>86.6</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" si="0"/>
-        <v>10.9251</v>
+        <v>8.6599999999999986E-18</v>
       </c>
       <c r="H37" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),1)</f>
-        <v>0.1114</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.1913</v>
       </c>
       <c r="I37" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),2)</f>
-        <v>0.245</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.2109</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="1"/>
-        <v>0.45469387755102042</v>
+        <v>0.90706495969653866</v>
       </c>
       <c r="K37" s="9">
         <f t="shared" si="2"/>
-        <v>2.8546098270334837E-2</v>
+        <v>6.3068347959888915E-2</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="10"/>
-        <v>44.233719999999991</v>
+        <v>103.16658</v>
       </c>
       <c r="M37" s="12">
         <f t="shared" si="3"/>
-        <v>35.109386026817212</v>
+        <v>84.935268732836391</v>
       </c>
       <c r="N37" s="12">
         <f t="shared" si="4"/>
-        <v>4.4337199999999939</v>
+        <v>16.566580000000002</v>
       </c>
       <c r="O37" s="12">
         <f t="shared" si="5"/>
-        <v>-2.3453069865913925</v>
+        <v>-0.83236563358180149</v>
       </c>
       <c r="P37" s="14">
         <f t="shared" si="6"/>
-        <v>2.0884130134086014</v>
+        <v>15.7342143664182</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="7"/>
-        <v>121.47816639138469</v>
+        <v>107.83236503837509</v>
       </c>
       <c r="R37" s="9">
         <f t="shared" si="8"/>
-        <v>8.2319319570411352E-3</v>
+        <v>9.2736535978240175E-3</v>
       </c>
       <c r="S37" s="9">
         <f t="shared" si="9"/>
-        <v>0.87705933524833513</v>
+        <v>0.77853811271817497</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>95</v>
+        <v>73</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
       </c>
       <c r="D38" s="8">
-        <v>45627</v>
+        <v>45562</v>
       </c>
       <c r="E38" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F38" s="1">
-        <v>26.63</v>
+        <v>56</v>
       </c>
       <c r="G38" s="1">
         <f t="shared" si="0"/>
-        <v>2.663E-18</v>
+        <v>5.5999999999999995E-18</v>
       </c>
       <c r="H38" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),1)</f>
-        <v>-0.12609999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>-7.1999999999999998E-3</v>
       </c>
       <c r="I38" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),2)</f>
-        <v>0.63</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.41589999999999999</v>
       </c>
       <c r="J38" s="9">
         <f t="shared" si="1"/>
-        <v>-0.20015873015873015</v>
+        <v>-1.7311853811012263E-2</v>
       </c>
       <c r="K38" s="9">
         <f t="shared" si="2"/>
-        <v>-1.256614848554985E-2</v>
+        <v>-1.2036955107922209E-3</v>
       </c>
       <c r="L38" s="12">
         <f t="shared" si="10"/>
-        <v>23.271957</v>
+        <v>55.596800000000002</v>
       </c>
       <c r="M38" s="12">
         <f t="shared" si="3"/>
-        <v>15.164284494049314</v>
+        <v>39.350713231677325</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3580429999999986</v>
+        <v>-0.40319999999999823</v>
       </c>
       <c r="O38" s="12">
         <f t="shared" si="5"/>
-        <v>-5.7328577529753426</v>
+        <v>-8.3246433841613374</v>
       </c>
       <c r="P38" s="14">
         <f t="shared" si="6"/>
-        <v>-9.0909007529753403</v>
+        <v>-8.7278433841613356</v>
       </c>
       <c r="Q38" s="12">
         <f t="shared" si="7"/>
-        <v>132.65748015776862</v>
+        <v>132.29442278895462</v>
       </c>
       <c r="R38" s="9">
         <f t="shared" si="8"/>
-        <v>7.538210425908189E-3</v>
+        <v>7.5588976384535151E-3</v>
       </c>
       <c r="S38" s="9">
         <f t="shared" si="9"/>
-        <v>0.95777278188439352</v>
+        <v>0.95515154661217927</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>97</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>99</v>
+        <v>76</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
       </c>
       <c r="D39" s="8">
-        <v>45630</v>
+        <v>45580</v>
       </c>
       <c r="E39" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F39" s="1">
-        <v>59.17</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="0"/>
-        <v>5.9170000000000002E-18</v>
+        <v>2.0399999999999999E-18</v>
       </c>
       <c r="H39" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),1)</f>
-        <v>-7.0800000000000002E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I39" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),2)</f>
-        <v>0.5726</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25</v>
       </c>
       <c r="J39" s="9">
         <f t="shared" si="1"/>
-        <v>-0.12364652462451974</v>
+        <v>0.1</v>
       </c>
       <c r="K39" s="9">
         <f t="shared" si="2"/>
-        <v>-7.7626421136951932E-3</v>
+        <v>6.9530133741456208E-3</v>
       </c>
       <c r="L39" s="12">
         <f t="shared" si="10"/>
-        <v>54.980764000000001</v>
+        <v>20.909999999999997</v>
       </c>
       <c r="M39" s="12">
         <f t="shared" si="3"/>
-        <v>36.004624558841428</v>
+        <v>16.653061224489793</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="4"/>
-        <v>-4.1892360000000011</v>
+        <v>0.50999999999999801</v>
       </c>
       <c r="O39" s="12">
         <f t="shared" si="5"/>
-        <v>-11.582687720579287</v>
+        <v>-1.8734693877551027</v>
       </c>
       <c r="P39" s="14">
         <f t="shared" si="6"/>
-        <v>-15.771923720579288</v>
+        <v>-1.3634693877551047</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="7"/>
-        <v>139.33850312537257</v>
+        <v>124.93004879254839</v>
       </c>
       <c r="R39" s="9">
         <f t="shared" si="8"/>
-        <v>7.1767672076987242E-3</v>
+        <v>8.0044793839834493E-3</v>
       </c>
       <c r="S39" s="9">
         <f t="shared" si="9"/>
-        <v>1.0060090513047488</v>
+        <v>0.90198155603956676</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>101</v>
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
       </c>
       <c r="D40" s="8">
-        <v>45630</v>
+        <v>45574</v>
       </c>
       <c r="E40" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F40" s="1">
-        <v>19.309999999999999</v>
+        <v>47.42</v>
       </c>
       <c r="G40" s="1">
         <f t="shared" si="0"/>
-        <v>1.931E-18</v>
+        <v>4.7419999999999999E-18</v>
       </c>
       <c r="H40" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),1)</f>
-        <v>0.1391</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>7.8399999999999997E-2</v>
       </c>
       <c r="I40" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),2)</f>
-        <v>0.31609999999999999</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.36230000000000001</v>
       </c>
       <c r="J40" s="9">
         <f t="shared" si="1"/>
-        <v>0.4400506168933882</v>
+        <v>0.21639525255313274</v>
       </c>
       <c r="K40" s="9">
         <f t="shared" si="2"/>
-        <v>2.7626780948574785E-2</v>
+        <v>1.5045990851035512E-2</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="10"/>
-        <v>21.996020999999999</v>
+        <v>51.137728000000003</v>
       </c>
       <c r="M40" s="12">
         <f t="shared" si="3"/>
-        <v>16.40611724723874</v>
+        <v>36.934340680738373</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="4"/>
-        <v>2.6860210000000002</v>
+        <v>3.717728000000001</v>
       </c>
       <c r="O40" s="12">
         <f t="shared" si="5"/>
-        <v>-1.4519413763806295</v>
+        <v>-5.2428296596308144</v>
       </c>
       <c r="P40" s="14">
         <f t="shared" si="6"/>
-        <v>1.2340796236193707</v>
+        <v>-1.5251016596308133</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="7"/>
-        <v>122.33249978117392</v>
+        <v>125.09168106442411</v>
       </c>
       <c r="R40" s="9">
         <f t="shared" si="8"/>
-        <v>8.1744426198171478E-3</v>
+        <v>7.9941367122965176E-3</v>
       </c>
       <c r="S40" s="9">
         <f t="shared" si="9"/>
-        <v>0.8832275307124885</v>
+        <v>0.90314852371068932</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>103</v>
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
       </c>
       <c r="D41" s="8">
-        <v>45630</v>
+        <v>45507</v>
       </c>
       <c r="E41" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F41" s="1">
-        <v>323.75</v>
+        <v>41.8</v>
       </c>
       <c r="G41" s="1">
         <f t="shared" si="0"/>
-        <v>3.2375000000000002E-17</v>
+        <v>4.1799999999999993E-18</v>
       </c>
       <c r="H41" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),1)</f>
-        <v>0.1842</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.1303</v>
       </c>
       <c r="I41" s="11">
-        <f>INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),2)</f>
-        <v>0.33040000000000003</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.39119999999999999</v>
       </c>
       <c r="J41" s="9">
         <f t="shared" si="1"/>
-        <v>0.55750605326876512</v>
+        <v>0.33307770961145194</v>
       </c>
       <c r="K41" s="9">
         <f t="shared" si="2"/>
-        <v>3.5000740869071734E-2</v>
+        <v>2.3158937695582166E-2</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="10"/>
-        <v>383.38475</v>
+        <v>47.246540000000003</v>
       </c>
       <c r="M41" s="12">
         <f t="shared" si="3"/>
-        <v>282.45506892339904</v>
+        <v>33.150923943215162</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="4"/>
-        <v>59.634749999999997</v>
+        <v>5.4465400000000059</v>
       </c>
       <c r="O41" s="12">
         <f t="shared" si="5"/>
-        <v>-20.64746553830048</v>
+        <v>-4.3245380283924177</v>
       </c>
       <c r="P41" s="14">
         <f t="shared" si="6"/>
-        <v>38.987284461699517</v>
+        <v>1.1220019716075882</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="7"/>
-        <v>84.579294943093771</v>
+        <v>122.4445774331857</v>
       </c>
       <c r="R41" s="9">
         <f t="shared" si="8"/>
-        <v>1.1823224592647823E-2</v>
+        <v>8.16696027674782E-3</v>
       </c>
       <c r="S41" s="9">
         <f t="shared" si="9"/>
-        <v>0.61065344005574052</v>
+        <v>0.88403671934193273</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="D42" s="8">
-        <v>45481</v>
+        <v>45574</v>
       </c>
       <c r="E42" s="2">
-        <v>2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F42" s="1">
-        <v>20.928000000000001</v>
+        <v>153.7552</v>
       </c>
       <c r="G42" s="1">
         <f t="shared" si="0"/>
-        <v>41.856000000000002</v>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="H42" s="11">
-        <v>4.4999999999999998E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C42,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I42" s="11">
-        <v>0.26</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C42,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.25</v>
       </c>
       <c r="J42" s="9">
         <f t="shared" ref="J42:J46" si="11">IFERROR(H42/I42,"")</f>
-        <v>0.17307692307692307</v>
+        <v>0.1</v>
       </c>
       <c r="K42" s="9">
         <f t="shared" si="2"/>
-        <v>1.0865927821794005E-2</v>
+        <v>6.9530133741456208E-3</v>
       </c>
       <c r="L42" s="12">
         <f t="shared" ref="L42:L46" si="12">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
-        <v>21.869759999999999</v>
+        <v>157.59907999999999</v>
       </c>
       <c r="M42" s="12">
         <f t="shared" ref="M42:M46" si="13">F42/(1+I42-H42)</f>
-        <v>17.224691358024693</v>
+        <v>125.51444897959183</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" ref="N42:N46" si="14">L42-F42</f>
-        <v>0.9417599999999986</v>
+        <v>3.8438799999999844</v>
       </c>
       <c r="O42" s="12">
         <f t="shared" ref="O42:O46" si="15">0.5*(M42-F42)</f>
-        <v>-1.8516543209876541</v>
+        <v>-14.120375510204084</v>
       </c>
       <c r="P42" s="14">
         <f t="shared" ref="P42:P46" si="16">N42+O42</f>
-        <v>-0.90989432098765555</v>
+        <v>-10.2764955102041</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="7"/>
-        <v>124.47647372578095</v>
+        <v>133.84307491499737</v>
       </c>
       <c r="R42" s="9">
         <f t="shared" si="8"/>
-        <v>8.0336466005855763E-3</v>
+        <v>7.4714362370641267E-3</v>
       </c>
       <c r="S42" s="9">
         <f t="shared" ref="S42:S46" si="17">Q42/MAX($Q$2:$Q$28)</f>
-        <v>0.89870679269433662</v>
+        <v>0.966332648900321</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>150</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C43" t="s">
-        <v>154</v>
+        <v>89</v>
+      </c>
+      <c r="B43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>91</v>
       </c>
       <c r="D43" s="8">
-        <v>45481</v>
+        <v>45627</v>
       </c>
       <c r="E43" s="2">
-        <v>2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F43" s="1">
-        <v>16.399999999999999</v>
+        <v>133.53</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>1.3353E-17</v>
       </c>
       <c r="H43" s="11">
-        <v>4.4999999999999998E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C43,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>5.7599999999999998E-2</v>
       </c>
       <c r="I43" s="11">
-        <v>0.26</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C43,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.2555</v>
       </c>
       <c r="J43" s="9">
         <f t="shared" si="11"/>
-        <v>0.17307692307692307</v>
+        <v>0.22544031311154597</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="2"/>
-        <v>1.0865927821794005E-2</v>
+        <v>1.5674895121361554E-2</v>
       </c>
       <c r="L43" s="12">
         <f t="shared" si="12"/>
-        <v>17.137999999999998</v>
+        <v>141.22132800000003</v>
       </c>
       <c r="M43" s="12">
         <f t="shared" si="13"/>
-        <v>13.497942386831273</v>
+        <v>111.47007262709742</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="14"/>
-        <v>0.73799999999999955</v>
+        <v>7.691328000000027</v>
       </c>
       <c r="O43" s="12">
         <f t="shared" si="15"/>
-        <v>-1.4510288065843628</v>
+        <v>-11.029963686451289</v>
       </c>
       <c r="P43" s="14">
         <f t="shared" si="16"/>
-        <v>-0.71302880658436329</v>
+        <v>-3.3386356864512621</v>
       </c>
       <c r="Q43" s="12">
         <f t="shared" si="7"/>
-        <v>124.27960821137765</v>
+        <v>126.90521509124454</v>
       </c>
       <c r="R43" s="9">
         <f t="shared" si="8"/>
-        <v>8.0463723244055992E-3</v>
+        <v>7.8798968133894452E-3</v>
       </c>
       <c r="S43" s="9">
         <f t="shared" si="17"/>
-        <v>0.89728544479022365</v>
+        <v>0.91624204491917349</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" t="s">
-        <v>156</v>
+        <v>94</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="D44" s="8">
-        <v>45481</v>
+        <v>45627</v>
       </c>
       <c r="E44" s="2">
-        <v>1</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F44" s="1">
-        <v>48.68</v>
+        <v>26.63</v>
       </c>
       <c r="G44" s="1">
         <f t="shared" si="0"/>
-        <v>48.68</v>
+        <v>2.663E-18</v>
       </c>
       <c r="H44" s="11">
-        <v>0.1</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C44,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>-0.12609999999999999</v>
       </c>
       <c r="I44" s="11">
-        <v>0.26</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C44,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.63</v>
       </c>
       <c r="J44" s="9">
         <f t="shared" si="11"/>
-        <v>0.38461538461538464</v>
+        <v>-0.20015873015873015</v>
       </c>
       <c r="K44" s="9">
         <f t="shared" si="2"/>
-        <v>2.4146506270653345E-2</v>
+        <v>-1.3917063277456551E-2</v>
       </c>
       <c r="L44" s="12">
         <f t="shared" si="12"/>
-        <v>53.548000000000002</v>
+        <v>23.271957</v>
       </c>
       <c r="M44" s="12">
         <f t="shared" si="13"/>
-        <v>41.96551724137931</v>
+        <v>15.164284494049314</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="14"/>
-        <v>4.8680000000000021</v>
+        <v>-3.3580429999999986</v>
       </c>
       <c r="O44" s="12">
         <f t="shared" si="15"/>
-        <v>-3.3572413793103451</v>
+        <v>-5.7328577529753426</v>
       </c>
       <c r="P44" s="14">
         <f t="shared" si="16"/>
-        <v>1.5107586206896571</v>
+        <v>-9.0909007529753403</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="7"/>
-        <v>122.05582078410363</v>
+        <v>132.65748015776862</v>
       </c>
       <c r="R44" s="9">
         <f t="shared" si="8"/>
-        <v>8.1929726380590498E-3</v>
+        <v>7.5382104259081881E-3</v>
       </c>
       <c r="S44" s="9">
         <f t="shared" si="17"/>
-        <v>0.8812299380219154</v>
+        <v>0.95777278188439352</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>150</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" t="s">
-        <v>158</v>
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>101</v>
       </c>
       <c r="D45" s="8">
-        <v>45481</v>
+        <v>45630</v>
       </c>
       <c r="E45" s="2">
-        <v>1</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F45" s="1">
-        <v>51.28</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="G45" s="1">
         <f t="shared" si="0"/>
-        <v>51.28</v>
+        <v>1.931E-18</v>
       </c>
       <c r="H45" s="11">
-        <v>4.4999999999999998E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C45,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.1391</v>
       </c>
       <c r="I45" s="11">
-        <v>0.26</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C45,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.31609999999999999</v>
       </c>
       <c r="J45" s="9">
         <f t="shared" si="11"/>
-        <v>0.17307692307692307</v>
+        <v>0.4400506168933882</v>
       </c>
       <c r="K45" s="9">
         <f t="shared" si="2"/>
-        <v>1.0865927821794005E-2</v>
+        <v>3.0596778245607588E-2</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="12"/>
-        <v>53.587599999999995</v>
+        <v>21.996020999999999</v>
       </c>
       <c r="M45" s="12">
         <f t="shared" si="13"/>
-        <v>42.205761316872426</v>
+        <v>16.40611724723874</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="14"/>
-        <v>2.3075999999999937</v>
+        <v>2.6860210000000002</v>
       </c>
       <c r="O45" s="12">
         <f t="shared" si="15"/>
-        <v>-4.5371193415637876</v>
+        <v>-1.4519413763806295</v>
       </c>
       <c r="P45" s="14">
         <f t="shared" si="16"/>
-        <v>-2.2295193415637939</v>
+        <v>1.2340796236193707</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="7"/>
-        <v>125.79609874635707</v>
+        <v>122.33249978117392</v>
       </c>
       <c r="R45" s="9">
         <f t="shared" si="8"/>
-        <v>7.9493721185766031E-3</v>
+        <v>8.1744426198171478E-3</v>
       </c>
       <c r="S45" s="9">
         <f t="shared" si="17"/>
-        <v>0.90823434383957402</v>
+        <v>0.8832275307124885</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" t="s">
-        <v>160</v>
+        <v>102</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="D46" s="8">
-        <v>45481</v>
+        <v>45630</v>
       </c>
       <c r="E46" s="2">
-        <v>1</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F46" s="1">
-        <v>44.14</v>
+        <v>323.75</v>
       </c>
       <c r="G46" s="1">
         <f t="shared" si="0"/>
-        <v>44.14</v>
+        <v>3.2375000000000002E-17</v>
       </c>
       <c r="H46" s="11">
-        <v>0.15</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C46,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>0.1842</v>
       </c>
       <c r="I46" s="11">
-        <v>0.26</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C46,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.33040000000000003</v>
       </c>
       <c r="J46" s="9">
         <f t="shared" si="11"/>
-        <v>0.57692307692307687</v>
+        <v>0.55750605326876512</v>
       </c>
       <c r="K46" s="9">
         <f t="shared" si="2"/>
-        <v>3.6219759405980018E-2</v>
+        <v>3.8763470445448645E-2</v>
       </c>
       <c r="L46" s="12">
         <f t="shared" si="12"/>
-        <v>50.760999999999996</v>
+        <v>383.38475</v>
       </c>
       <c r="M46" s="12">
         <f t="shared" si="13"/>
-        <v>39.765765765765764</v>
+        <v>282.45506892339904</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="14"/>
-        <v>6.6209999999999951</v>
+        <v>59.634749999999997</v>
       </c>
       <c r="O46" s="12">
         <f t="shared" si="15"/>
-        <v>-2.1871171171171184</v>
+        <v>-20.64746553830048</v>
       </c>
       <c r="P46" s="14">
         <f t="shared" si="16"/>
-        <v>4.4338828828828767</v>
+        <v>38.987284461699517</v>
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="7"/>
-        <v>119.13269652191042</v>
+        <v>84.579294943093771</v>
       </c>
       <c r="R46" s="9">
         <f t="shared" si="8"/>
-        <v>8.3940012204465116E-3</v>
+        <v>1.1823224592647823E-2</v>
       </c>
       <c r="S46" s="9">
         <f t="shared" si="17"/>
-        <v>0.86012529429534301</v>
+        <v>0.61065344005574052</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC1F8C8-C13E-4050-9F90-E93E9DF5B6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935F7F83-726D-42F1-96DE-37A6FEAC9D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -937,6 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1019,7 +1020,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -1056,7 +1057,7 @@
       </c>
       <c r="K2" s="9">
         <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.9530133741456208E-3</v>
+        <v>0.2304893482747446</v>
       </c>
       <c r="L2" s="12">
         <f>IF((1+H2)*F2&lt;0,0,(1+H2)*F2)</f>
@@ -1091,7 +1092,7 @@
         <v>0.90223634458197444</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>150</v>
       </c>
@@ -1128,7 +1129,7 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>6.9530133741456208E-3</v>
+        <v>0.2304893482747446</v>
       </c>
       <c r="L3" s="12">
         <f t="shared" ref="L3:L41" si="10">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
@@ -1163,7 +1164,7 @@
         <v>0.90005133980920593</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>1.5474694399775312E-2</v>
+        <v>0.51297934219684005</v>
       </c>
       <c r="L4" s="12">
         <f t="shared" si="10"/>
@@ -1235,7 +1236,7 @@
         <v>0.89536605345572151</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1272,7 +1273,7 @@
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>-5.4174954988100259E-3</v>
+        <v>-0.17958760318874276</v>
       </c>
       <c r="L5" s="12">
         <f t="shared" si="10"/>
@@ -1307,7 +1308,7 @@
         <v>0.93113607204125293</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1344,7 +1345,7 @@
       </c>
       <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v>1.712490216387217E-2</v>
+        <v>0.56768300686674245</v>
       </c>
       <c r="L6" s="12">
         <f t="shared" si="10"/>
@@ -1372,14 +1373,14 @@
       </c>
       <c r="R6" s="9">
         <f t="shared" si="8"/>
-        <v>8.0347592056604321E-3</v>
+        <v>8.0347592056604338E-3</v>
       </c>
       <c r="S6" s="9">
         <f t="shared" si="9"/>
         <v>0.8985823451890953</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>150</v>
       </c>
@@ -1416,7 +1417,7 @@
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>6.9530133741456208E-3</v>
+        <v>0.2304893482747446</v>
       </c>
       <c r="L7" s="12">
         <f t="shared" si="10"/>
@@ -1451,7 +1452,7 @@
         <v>0.91348564477251748</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>150</v>
       </c>
@@ -1488,7 +1489,7 @@
       </c>
       <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v>6.9530133741456208E-3</v>
+        <v>0.2304893482747446</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" si="10"/>
@@ -1523,7 +1524,7 @@
         <v>0.91562818478821795</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -1560,7 +1561,7 @@
       </c>
       <c r="K9" s="9">
         <f t="shared" si="2"/>
-        <v>6.9530133741456208E-3</v>
+        <v>0.2304893482747446</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" si="10"/>
@@ -1595,7 +1596,7 @@
         <v>0.91688282533795251</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1632,7 +1633,7 @@
       </c>
       <c r="K10" s="9">
         <f t="shared" si="2"/>
-        <v>1.3052818147434543E-2</v>
+        <v>0.43269520509452963</v>
       </c>
       <c r="L10" s="12">
         <f t="shared" si="10"/>
@@ -1667,7 +1668,7 @@
         <v>0.90755017424878737</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1704,7 +1705,7 @@
       </c>
       <c r="K11" s="9">
         <f t="shared" si="2"/>
-        <v>3.763557697932033E-2</v>
+        <v>1.2476028943311863</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" si="10"/>
@@ -1732,14 +1733,14 @@
       </c>
       <c r="R11" s="9">
         <f t="shared" si="8"/>
-        <v>8.5431856313039675E-3</v>
+        <v>8.5431856313039657E-3</v>
       </c>
       <c r="S11" s="9">
         <f t="shared" si="9"/>
         <v>0.8451054538247269</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1776,7 +1777,7 @@
       </c>
       <c r="K12" s="9">
         <f t="shared" si="2"/>
-        <v>2.7520063433626233E-2</v>
+        <v>0.91227805038927778</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="10"/>
@@ -1811,7 +1812,7 @@
         <v>0.86461239043009097</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1848,7 +1849,7 @@
       </c>
       <c r="K13" s="9">
         <f t="shared" si="2"/>
-        <v>5.7421427197889494E-2</v>
+        <v>1.9034951638466466</v>
       </c>
       <c r="L13" s="12">
         <f t="shared" si="10"/>
@@ -1876,14 +1877,14 @@
       </c>
       <c r="R13" s="9">
         <f t="shared" si="8"/>
-        <v>1.2976163203376542E-2</v>
+        <v>1.297616320337654E-2</v>
       </c>
       <c r="S13" s="9">
         <f t="shared" si="9"/>
         <v>0.55639657554348021</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1920,7 +1921,7 @@
       </c>
       <c r="K14" s="9">
         <f t="shared" si="2"/>
-        <v>1.2261964472631191E-2</v>
+        <v>0.40647875212984508</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="10"/>
@@ -1948,7 +1949,7 @@
       </c>
       <c r="R14" s="9">
         <f t="shared" si="8"/>
-        <v>7.7711195608401486E-3</v>
+        <v>7.7711195608401494E-3</v>
       </c>
       <c r="S14" s="9">
         <f t="shared" si="9"/>
@@ -1992,7 +1993,7 @@
       </c>
       <c r="K15" s="9">
         <f t="shared" si="2"/>
-        <v>-8.5971593938091156E-3</v>
+        <v>-0.28499206877142713</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="10"/>
@@ -2027,7 +2028,7 @@
         <v>0.9590709361079236</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -2064,7 +2065,7 @@
       </c>
       <c r="K16" s="9">
         <f t="shared" si="2"/>
-        <v>3.1614926117543761E-2</v>
+        <v>1.0480209550125121</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="10"/>
@@ -2099,7 +2100,7 @@
         <v>0.87705933524833513</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -2136,7 +2137,7 @@
       </c>
       <c r="K17" s="9">
         <f t="shared" si="2"/>
-        <v>3.6981475503146351E-2</v>
+        <v>1.2259197168603224</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="10"/>
@@ -2171,7 +2172,7 @@
         <v>0.82351883879776044</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -2208,7 +2209,7 @@
       </c>
       <c r="K18" s="9">
         <f t="shared" si="2"/>
-        <v>1.3937703346806711E-2</v>
+        <v>0.46202876191748343</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="10"/>
@@ -2243,7 +2244,7 @@
         <v>0.94689640391568153</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -2257,14 +2258,14 @@
         <v>45580</v>
       </c>
       <c r="E19" s="2">
-        <v>0.19139999999999999</v>
+        <v>0.34860000000000002</v>
       </c>
       <c r="F19" s="1">
-        <v>135.82</v>
+        <v>131.91</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="0"/>
-        <v>25.995947999999999</v>
+        <v>45.983826000000001</v>
       </c>
       <c r="H19" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),1),2.5%)</f>
@@ -2280,42 +2281,42 @@
       </c>
       <c r="K19" s="9">
         <f t="shared" si="2"/>
-        <v>1.8042288771020782E-2</v>
+        <v>0.59809397112346585</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="10"/>
-        <v>144.91994</v>
+        <v>140.74796999999998</v>
       </c>
       <c r="M19" s="12">
         <f t="shared" si="3"/>
-        <v>114.01947615849562</v>
+        <v>110.73707186030893</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="4"/>
-        <v>9.0999400000000037</v>
+        <v>8.8379699999999843</v>
       </c>
       <c r="O19" s="12">
         <f t="shared" si="5"/>
-        <v>-10.900261920752186</v>
+        <v>-10.586464069845533</v>
       </c>
       <c r="P19" s="14">
         <f t="shared" si="6"/>
-        <v>-1.8003219207521823</v>
+        <v>-1.7484940698455489</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="7"/>
-        <v>125.36690132554547</v>
+        <v>125.31507347463884</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" si="8"/>
-        <v>7.9765870371419512E-3</v>
+        <v>7.9798859967342983E-3</v>
       </c>
       <c r="S19" s="9">
         <f t="shared" si="9"/>
-        <v>0.90513558448413134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.90476139295808311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2352,7 +2353,7 @@
       </c>
       <c r="K20" s="9">
         <f t="shared" si="2"/>
-        <v>6.1651021654296777E-2</v>
+        <v>2.0437043677220208</v>
       </c>
       <c r="L20" s="12">
         <f t="shared" si="10"/>
@@ -2380,14 +2381,14 @@
       </c>
       <c r="R20" s="9">
         <f t="shared" si="8"/>
-        <v>1.4425338110184198E-2</v>
+        <v>1.44253381101842E-2</v>
       </c>
       <c r="S20" s="9">
         <f t="shared" si="9"/>
         <v>0.50050076572935409</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -2424,7 +2425,7 @@
       </c>
       <c r="K21" s="9">
         <f t="shared" si="2"/>
-        <v>6.3277053615929252E-2</v>
+        <v>2.0976066151280421</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="10"/>
@@ -2459,7 +2460,7 @@
         <v>0.17608014641792177</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -2496,7 +2497,7 @@
       </c>
       <c r="K22" s="9">
         <f t="shared" si="2"/>
-        <v>5.1200393034945661E-2</v>
+        <v>1.6972706058523168</v>
       </c>
       <c r="L22" s="12">
         <f t="shared" si="10"/>
@@ -2531,7 +2532,7 @@
         <v>0.28887289068890865</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -2568,7 +2569,7 @@
       </c>
       <c r="K23" s="9">
         <f t="shared" si="2"/>
-        <v>-7.6913446811209332E-2</v>
+        <v>-2.5496470774814579</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="10"/>
@@ -2596,14 +2597,14 @@
       </c>
       <c r="R23" s="9">
         <f t="shared" si="8"/>
-        <v>7.2198927700520242E-3</v>
+        <v>7.2198927700520251E-3</v>
       </c>
       <c r="S23" s="9">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -2640,7 +2641,7 @@
       </c>
       <c r="K24" s="9">
         <f t="shared" si="2"/>
-        <v>4.8408128900111022E-2</v>
+        <v>1.6047082726570261</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="10"/>
@@ -2675,7 +2676,7 @@
         <v>0.6129231002177431</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2712,7 +2713,7 @@
       </c>
       <c r="K25" s="9">
         <f t="shared" si="2"/>
-        <v>3.0783905987144727E-2</v>
+        <v>1.0204730016357646</v>
       </c>
       <c r="L25" s="12">
         <f t="shared" si="10"/>
@@ -2747,7 +2748,7 @@
         <v>0.78504659905252072</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2784,7 +2785,7 @@
       </c>
       <c r="K26" s="9">
         <f t="shared" si="2"/>
-        <v>4.4364285123813421E-2</v>
+        <v>1.4706566224776176</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="10"/>
@@ -2819,7 +2820,7 @@
         <v>0.72943259793688353</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -2856,7 +2857,7 @@
       </c>
       <c r="K27" s="9">
         <f t="shared" si="2"/>
-        <v>5.0946160495118457E-2</v>
+        <v>1.6888429084984042</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="10"/>
@@ -2891,7 +2892,7 @@
         <v>9.3387089717532706E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2928,7 +2929,7 @@
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
-        <v>4.3848663737641659E-2</v>
+        <v>1.4535639993428531</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="10"/>
@@ -2963,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -3000,7 +3001,7 @@
       </c>
       <c r="K29" s="9">
         <f t="shared" si="2"/>
-        <v>7.8287427675306165E-2</v>
+        <v>2.5951939413901677</v>
       </c>
       <c r="L29" s="12">
         <f t="shared" si="10"/>
@@ -3028,14 +3029,14 @@
       </c>
       <c r="R29" s="9">
         <f t="shared" si="8"/>
-        <v>2.7910838373683976E-2</v>
+        <v>2.7910838373683973E-2</v>
       </c>
       <c r="S29" s="9">
         <f t="shared" si="9"/>
         <v>0.25867702981145047</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -3072,7 +3073,7 @@
       </c>
       <c r="K30" s="9">
         <f t="shared" si="2"/>
-        <v>4.3230911685069678E-2</v>
+        <v>1.4330857893451341</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="10"/>
@@ -3107,7 +3108,7 @@
         <v>0.658782186619014</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -3144,7 +3145,7 @@
       </c>
       <c r="K31" s="9">
         <f t="shared" si="2"/>
-        <v>3.042989483436865E-2</v>
+        <v>1.0087376869607261</v>
       </c>
       <c r="L31" s="12">
         <f t="shared" si="10"/>
@@ -3172,14 +3173,14 @@
       </c>
       <c r="R31" s="9">
         <f t="shared" si="8"/>
-        <v>8.3905630772596242E-3</v>
+        <v>8.390563077259626E-3</v>
       </c>
       <c r="S31" s="9">
         <f t="shared" si="9"/>
         <v>0.86047774190740678</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -3216,7 +3217,7 @@
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>4.9142568473083466E-2</v>
+        <v>1.6290546228526201</v>
       </c>
       <c r="L32" s="12">
         <f t="shared" si="10"/>
@@ -3251,7 +3252,7 @@
         <v>0.70169784154144987</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -3288,7 +3289,7 @@
       </c>
       <c r="K33" s="9">
         <f t="shared" si="2"/>
-        <v>-1.8618947947502916E-3</v>
+        <v>-6.1720997027546666E-2</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="10"/>
@@ -3316,14 +3317,14 @@
       </c>
       <c r="R33" s="9">
         <f t="shared" si="8"/>
-        <v>7.7893467514407334E-3</v>
+        <v>7.7893467514407325E-3</v>
       </c>
       <c r="S33" s="9">
         <f t="shared" si="9"/>
         <v>0.92689323000245416</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -3360,7 +3361,7 @@
       </c>
       <c r="K34" s="9">
         <f t="shared" si="2"/>
-        <v>2.6646873440548556E-3</v>
+        <v>8.8333218453306064E-2</v>
       </c>
       <c r="L34" s="12">
         <f t="shared" si="10"/>
@@ -3395,7 +3396,7 @@
         <v>0.90416710399141131</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -3432,7 +3433,7 @@
       </c>
       <c r="K35" s="9">
         <f t="shared" si="2"/>
-        <v>-1.332471511921249E-2</v>
+        <v>-0.44170847063145613</v>
       </c>
       <c r="L35" s="12">
         <f t="shared" si="10"/>
@@ -3460,14 +3461,14 @@
       </c>
       <c r="R35" s="9">
         <f t="shared" si="8"/>
-        <v>7.8703883457964512E-3</v>
+        <v>7.8703883457964495E-3</v>
       </c>
       <c r="S35" s="9">
         <f t="shared" si="9"/>
         <v>0.91734898620449223</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>76</v>
       </c>
@@ -3479,7 +3480,7 @@
       </c>
       <c r="D36" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="E36" s="2">
         <v>9.9999999999999998E-20</v>
@@ -3505,7 +3506,7 @@
       </c>
       <c r="K36" s="9">
         <f t="shared" si="2"/>
-        <v>6.9530133741456208E-3</v>
+        <v>0.2304893482747446</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="10"/>
@@ -3540,7 +3541,7 @@
         <v>2.2157349778289213</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -3577,7 +3578,7 @@
       </c>
       <c r="K37" s="9">
         <f t="shared" si="2"/>
-        <v>6.3068347959888915E-2</v>
+        <v>2.0906881140331266</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="10"/>
@@ -3605,14 +3606,14 @@
       </c>
       <c r="R37" s="9">
         <f t="shared" si="8"/>
-        <v>9.2736535978240175E-3</v>
+        <v>9.2736535978240192E-3</v>
       </c>
       <c r="S37" s="9">
         <f t="shared" si="9"/>
         <v>0.77853811271817497</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -3649,7 +3650,7 @@
       </c>
       <c r="K38" s="9">
         <f t="shared" si="2"/>
-        <v>-1.2036955107922209E-3</v>
+        <v>-3.9901979023278702E-2</v>
       </c>
       <c r="L38" s="12">
         <f t="shared" si="10"/>
@@ -3677,14 +3678,14 @@
       </c>
       <c r="R38" s="9">
         <f t="shared" si="8"/>
-        <v>7.5588976384535151E-3</v>
+        <v>7.5588976384535159E-3</v>
       </c>
       <c r="S38" s="9">
         <f t="shared" si="9"/>
         <v>0.95515154661217927</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -3721,7 +3722,7 @@
       </c>
       <c r="K39" s="9">
         <f t="shared" si="2"/>
-        <v>6.9530133741456208E-3</v>
+        <v>0.2304893482747446</v>
       </c>
       <c r="L39" s="12">
         <f t="shared" si="10"/>
@@ -3756,7 +3757,7 @@
         <v>0.90198155603956676</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -3793,7 +3794,7 @@
       </c>
       <c r="K40" s="9">
         <f t="shared" si="2"/>
-        <v>1.5045990851035512E-2</v>
+        <v>0.49876800730720328</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="10"/>
@@ -3828,7 +3829,7 @@
         <v>0.90314852371068932</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3865,7 +3866,7 @@
       </c>
       <c r="K41" s="9">
         <f t="shared" si="2"/>
-        <v>2.3158937695582166E-2</v>
+        <v>0.76770864213188195</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="10"/>
@@ -3900,7 +3901,7 @@
         <v>0.88403671934193273</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -3937,7 +3938,7 @@
       </c>
       <c r="K42" s="9">
         <f t="shared" si="2"/>
-        <v>6.9530133741456208E-3</v>
+        <v>0.2304893482747446</v>
       </c>
       <c r="L42" s="12">
         <f t="shared" ref="L42:L46" si="12">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
@@ -3965,14 +3966,14 @@
       </c>
       <c r="R42" s="9">
         <f t="shared" si="8"/>
-        <v>7.4714362370641267E-3</v>
+        <v>7.4714362370641276E-3</v>
       </c>
       <c r="S42" s="9">
         <f t="shared" ref="S42:S46" si="17">Q42/MAX($Q$2:$Q$28)</f>
         <v>0.966332648900321</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -4009,7 +4010,7 @@
       </c>
       <c r="K43" s="9">
         <f t="shared" si="2"/>
-        <v>1.5674895121361554E-2</v>
+        <v>0.51961590843934591</v>
       </c>
       <c r="L43" s="12">
         <f t="shared" si="12"/>
@@ -4044,7 +4045,7 @@
         <v>0.91624204491917349</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -4081,7 +4082,7 @@
       </c>
       <c r="K44" s="9">
         <f t="shared" si="2"/>
-        <v>-1.3917063277456551E-2</v>
+        <v>-0.46134455265786178</v>
       </c>
       <c r="L44" s="12">
         <f t="shared" si="12"/>
@@ -4116,7 +4117,7 @@
         <v>0.95777278188439352</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -4153,7 +4154,7 @@
       </c>
       <c r="K45" s="9">
         <f t="shared" si="2"/>
-        <v>3.0596778245607588E-2</v>
+        <v>1.0142697989565637</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="12"/>
@@ -4225,7 +4226,7 @@
       </c>
       <c r="K46" s="9">
         <f t="shared" si="2"/>
-        <v>3.8763470445448645E-2</v>
+        <v>1.2849920687714271</v>
       </c>
       <c r="L46" s="12">
         <f t="shared" si="12"/>
@@ -4253,7 +4254,7 @@
       </c>
       <c r="R46" s="9">
         <f t="shared" si="8"/>
-        <v>1.1823224592647823E-2</v>
+        <v>1.1823224592647825E-2</v>
       </c>
       <c r="S46" s="9">
         <f t="shared" si="17"/>
@@ -4261,7 +4262,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:S46" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Health"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="R2:R46">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Symbols">

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4ACB836-CB89-491C-B52F-4E100A740AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647E1721-014B-47FC-8D34-DA7024ED2BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId4"/>
+    <pivotCache cacheId="40" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -555,7 +555,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -692,7 +692,7 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -710,132 +710,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="3">
     <dxf>
-      <alignment vertical="center"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
       <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -975,8 +858,8 @@
     <cacheField name="Normalized Risk %" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1.0857253751650462"/>
     </cacheField>
-    <cacheField name="TargetReturn%_Metric" numFmtId="0" formula="'Target Value' /Value-1" databaseField="0"/>
-    <cacheField name="TargetP&amp;L_metric" numFmtId="0" formula="'Target Value' -Value" databaseField="0"/>
+    <cacheField name="TargetReturn%_Metric" numFmtId="0" formula="'Target Value'/Value-1" databaseField="0"/>
+    <cacheField name="TargetP&amp;L_metric" numFmtId="0" formula="'Target Value'-Value" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -2114,7 +1997,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EC9E47C-0324-45D9-96E2-71F0F41D16E2}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EC9E47C-0324-45D9-96E2-71F0F41D16E2}" name="PivotTable1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B3:F17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -2301,7 +2184,7 @@
     <dataField name="Target P&amp;L" fld="21" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="39">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2311,7 +2194,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2321,7 +2204,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="0">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2837,7 +2720,7 @@
       </c>
       <c r="S3" s="9">
         <f t="shared" si="9"/>
-        <v>6.1854037698548638E-3</v>
+        <v>6.1854037698548647E-3</v>
       </c>
       <c r="T3" s="9">
         <f t="shared" si="10"/>
@@ -2989,7 +2872,7 @@
       </c>
       <c r="S5" s="9">
         <f t="shared" si="9"/>
-        <v>6.2159385679079878E-3</v>
+        <v>6.215938567907987E-3</v>
       </c>
       <c r="T5" s="9">
         <f t="shared" si="10"/>
@@ -3390,14 +3273,14 @@
         <v>45627</v>
       </c>
       <c r="E11" s="2">
-        <v>0.95840000000000003</v>
+        <v>1.2354000000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>41.76</v>
+        <v>40.49</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>40.022784000000001</v>
+        <v>50.021346000000001</v>
       </c>
       <c r="H11" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),1),2.5%)</f>
@@ -3417,39 +3300,39 @@
       </c>
       <c r="L11" s="12">
         <f t="shared" si="11"/>
-        <v>43.509743999999998</v>
+        <v>42.186531000000002</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="3"/>
-        <v>41.6997386496</v>
+        <v>52.117240397400003</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="4"/>
-        <v>27.966782748459686</v>
+        <v>27.116260380391111</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="5"/>
-        <v>1.7497439999999997</v>
+        <v>1.6965310000000002</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="6"/>
-        <v>-6.8966086257701562</v>
+        <v>-6.6868698098044455</v>
       </c>
       <c r="Q11" s="14">
         <f t="shared" si="7"/>
-        <v>-5.1468646257701565</v>
+        <v>-4.9903388098044452</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="8"/>
-        <v>165.41903869201519</v>
+        <v>165.2625128760495</v>
       </c>
       <c r="S11" s="9">
         <f t="shared" si="9"/>
-        <v>6.045253363259148E-3</v>
+        <v>6.0509790308587519E-3</v>
       </c>
       <c r="T11" s="9">
         <f t="shared" si="10"/>
-        <v>0.94407817833040264</v>
+        <v>0.94318485547973796</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -3521,7 +3404,7 @@
       </c>
       <c r="S12" s="9">
         <f t="shared" si="9"/>
-        <v>6.2686224886143423E-3</v>
+        <v>6.2686224886143432E-3</v>
       </c>
       <c r="T12" s="9">
         <f t="shared" si="10"/>
@@ -3673,7 +3556,7 @@
       </c>
       <c r="S14" s="9">
         <f t="shared" si="9"/>
-        <v>6.312135149064345E-3</v>
+        <v>6.3121351490643459E-3</v>
       </c>
       <c r="T14" s="9">
         <f t="shared" si="10"/>
@@ -4053,7 +3936,7 @@
       </c>
       <c r="S19" s="9">
         <f t="shared" si="9"/>
-        <v>6.1835484904055682E-3</v>
+        <v>6.1835484904055674E-3</v>
       </c>
       <c r="T19" s="9">
         <f t="shared" si="10"/>
@@ -4281,7 +4164,7 @@
       </c>
       <c r="S22" s="9">
         <f t="shared" si="9"/>
-        <v>1.2378499914152326E-2</v>
+        <v>1.2378499914152324E-2</v>
       </c>
       <c r="T22" s="9">
         <f t="shared" si="10"/>
@@ -4290,165 +4173,165 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>58</v>
+        <v>36</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D23" s="8">
-        <v>45580</v>
+        <v>45678</v>
       </c>
       <c r="E23" s="2">
-        <v>2.9999999999999997E-4</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="F23" s="1">
-        <v>130.51</v>
+        <v>185.82</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="0"/>
-        <v>3.9152999999999993E-2</v>
+        <v>9.9971160000000001</v>
       </c>
       <c r="H23" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1169</v>
+        <v>0.1925</v>
       </c>
       <c r="I23" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.23899999999999999</v>
+        <v>0.28539999999999999</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>0.48912133891213394</v>
+        <v>0.6744919411352488</v>
       </c>
       <c r="K23" s="9">
         <f t="shared" si="2"/>
-        <v>3.5170970200438814E-2</v>
+        <v>4.8500308767689022E-2</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="11"/>
-        <v>145.76661899999999</v>
+        <v>221.59034999999997</v>
       </c>
       <c r="M23" s="12">
         <f t="shared" si="3"/>
-        <v>4.3729985699999994E-2</v>
+        <v>11.921560829999999</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="4"/>
-        <v>116.3087068888691</v>
+        <v>170.02470491353276</v>
       </c>
       <c r="O23" s="12">
         <f t="shared" si="5"/>
-        <v>15.256619000000001</v>
+        <v>35.770349999999979</v>
       </c>
       <c r="P23" s="12">
         <f t="shared" si="6"/>
-        <v>-7.1006465555654472</v>
+        <v>-7.8976475432336173</v>
       </c>
       <c r="Q23" s="14">
         <f t="shared" si="7"/>
-        <v>8.1559724444345534</v>
+        <v>27.872702456766362</v>
       </c>
       <c r="R23" s="12">
         <f t="shared" si="8"/>
-        <v>152.11620162181049</v>
+        <v>132.39947160947867</v>
       </c>
       <c r="S23" s="9">
         <f t="shared" si="9"/>
-        <v>6.5739217081306582E-3</v>
+        <v>7.552900233239364E-3</v>
       </c>
       <c r="T23" s="9">
         <f t="shared" si="10"/>
-        <v>0.86815633591631525</v>
+        <v>0.75562917640760074</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
       </c>
       <c r="D24" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E24" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F24" s="1">
-        <v>10.92</v>
+        <v>130.51</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>1.092E-18</v>
+        <v>3.9152999999999993E-2</v>
       </c>
       <c r="H24" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-1.4844999999999999</v>
+        <v>0.1169</v>
       </c>
       <c r="I24" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),2),25%)</f>
-        <v>1.3212999999999999</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="J24" s="9">
         <f t="shared" si="1"/>
-        <v>-1.1235147203511693</v>
+        <v>0.48912133891213394</v>
       </c>
       <c r="K24" s="9">
         <f t="shared" si="2"/>
-        <v>-8.0787934619887522E-2</v>
+        <v>3.5170970200438814E-2</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>145.76661899999999</v>
       </c>
       <c r="M24" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.3729985699999994E-2</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="4"/>
-        <v>2.8693047453886176</v>
+        <v>116.3087068888691</v>
       </c>
       <c r="O24" s="12">
         <f t="shared" si="5"/>
-        <v>-10.92</v>
+        <v>15.256619000000001</v>
       </c>
       <c r="P24" s="12">
         <f t="shared" si="6"/>
-        <v>-4.025347627305691</v>
+        <v>-7.1006465555654472</v>
       </c>
       <c r="Q24" s="14">
         <f t="shared" si="7"/>
-        <v>-14.94534762730569</v>
+        <v>8.1559724444345534</v>
       </c>
       <c r="R24" s="12">
         <f t="shared" si="8"/>
-        <v>175.21752169355074</v>
+        <v>152.11620162181049</v>
       </c>
       <c r="S24" s="9">
         <f t="shared" si="9"/>
-        <v>5.7071917827314364E-3</v>
+        <v>6.5739217081306573E-3</v>
       </c>
       <c r="T24" s="9">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.86815633591631525</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" t="s">
-        <v>25</v>
+        <v>40</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D25" s="8">
         <v>45511</v>
@@ -4457,139 +4340,139 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>283.43</v>
+        <v>10.92</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="0"/>
-        <v>2.8342999999999998E-17</v>
+        <v>1.092E-18</v>
       </c>
       <c r="H25" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.17100000000000001</v>
+        <v>-1.4844999999999999</v>
       </c>
       <c r="I25" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24360000000000001</v>
+        <v>1.3212999999999999</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>0.70197044334975367</v>
+        <v>-1.1235147203511693</v>
       </c>
       <c r="K25" s="9">
         <f t="shared" si="2"/>
-        <v>5.0476189813256446E-2</v>
+        <v>-8.0787934619887522E-2</v>
       </c>
       <c r="L25" s="12">
         <f t="shared" si="11"/>
-        <v>331.89653000000004</v>
+        <v>0</v>
       </c>
       <c r="M25" s="12">
         <f t="shared" si="3"/>
-        <v>3.3189653000000001E-17</v>
+        <v>0</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="4"/>
-        <v>264.24575797128472</v>
+        <v>2.8693047453886176</v>
       </c>
       <c r="O25" s="12">
         <f t="shared" si="5"/>
-        <v>48.466530000000034</v>
+        <v>-10.92</v>
       </c>
       <c r="P25" s="12">
         <f t="shared" si="6"/>
-        <v>-9.5921210143576445</v>
+        <v>-4.025347627305691</v>
       </c>
       <c r="Q25" s="14">
         <f t="shared" si="7"/>
-        <v>38.87440898564239</v>
+        <v>-14.94534762730569</v>
       </c>
       <c r="R25" s="12">
         <f t="shared" si="8"/>
-        <v>121.39776508060265</v>
+        <v>175.21752169355074</v>
       </c>
       <c r="S25" s="9">
         <f t="shared" si="9"/>
-        <v>8.2373839364838792E-3</v>
+        <v>5.7071917827314364E-3</v>
       </c>
       <c r="T25" s="9">
         <f t="shared" si="10"/>
-        <v>0.6928403273099768</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D26" s="8">
-        <v>45544</v>
+        <v>45511</v>
       </c>
       <c r="E26" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>188.12</v>
+        <v>283.43</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="0"/>
-        <v>1.8812000000000001E-17</v>
+        <v>2.8342999999999998E-17</v>
       </c>
       <c r="H26" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1164</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="I26" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.3664</v>
+        <v>0.24360000000000001</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>0.31768558951965065</v>
+        <v>0.70197044334975367</v>
       </c>
       <c r="K26" s="9">
         <f t="shared" si="2"/>
-        <v>2.2843637177955244E-2</v>
+        <v>5.0476189813256446E-2</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="11"/>
-        <v>210.01716800000003</v>
+        <v>331.89653000000004</v>
       </c>
       <c r="M26" s="12">
         <f t="shared" si="3"/>
-        <v>2.1001716800000003E-17</v>
+        <v>3.3189653000000001E-17</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="4"/>
-        <v>150.49600000000001</v>
+        <v>264.24575797128472</v>
       </c>
       <c r="O26" s="12">
         <f t="shared" si="5"/>
-        <v>21.897168000000022</v>
+        <v>48.466530000000034</v>
       </c>
       <c r="P26" s="12">
         <f t="shared" si="6"/>
-        <v>-18.811999999999998</v>
+        <v>-9.5921210143576445</v>
       </c>
       <c r="Q26" s="14">
         <f t="shared" si="7"/>
-        <v>3.0851680000000243</v>
+        <v>38.87440898564239</v>
       </c>
       <c r="R26" s="12">
         <f t="shared" si="8"/>
-        <v>157.18700606624503</v>
+        <v>121.39776508060265</v>
       </c>
       <c r="S26" s="9">
         <f t="shared" si="9"/>
-        <v>6.3618490168236876E-3</v>
+        <v>8.2373839364838809E-3</v>
       </c>
       <c r="T26" s="9">
         <f t="shared" si="10"/>
-        <v>0.89709638937343017</v>
+        <v>0.6928403273099768</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -4597,75 +4480,75 @@
         <v>36</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D27" s="8">
-        <v>45678</v>
+        <v>45544</v>
       </c>
       <c r="E27" s="2">
-        <v>5.3800000000000001E-2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F27" s="1">
-        <v>185.82</v>
+        <v>188.12</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="0"/>
-        <v>9.9971160000000001</v>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="H27" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1925</v>
+        <v>0.1164</v>
       </c>
       <c r="I27" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.28539999999999999</v>
+        <v>0.3664</v>
       </c>
       <c r="J27" s="9">
         <f t="shared" si="1"/>
-        <v>0.6744919411352488</v>
+        <v>0.31768558951965065</v>
       </c>
       <c r="K27" s="9">
         <f t="shared" si="2"/>
-        <v>4.8500308767689022E-2</v>
+        <v>2.2843637177955244E-2</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="11"/>
-        <v>221.59034999999997</v>
+        <v>210.01716800000003</v>
       </c>
       <c r="M27" s="12">
         <f t="shared" si="3"/>
-        <v>11.921560829999999</v>
+        <v>2.1001716800000003E-17</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="4"/>
-        <v>170.02470491353276</v>
+        <v>150.49600000000001</v>
       </c>
       <c r="O27" s="12">
         <f t="shared" si="5"/>
-        <v>35.770349999999979</v>
+        <v>21.897168000000022</v>
       </c>
       <c r="P27" s="12">
         <f t="shared" si="6"/>
-        <v>-7.8976475432336173</v>
+        <v>-18.811999999999998</v>
       </c>
       <c r="Q27" s="14">
         <f t="shared" si="7"/>
-        <v>27.872702456766362</v>
+        <v>3.0851680000000243</v>
       </c>
       <c r="R27" s="12">
         <f t="shared" si="8"/>
-        <v>132.39947160947867</v>
+        <v>157.18700606624503</v>
       </c>
       <c r="S27" s="9">
         <f t="shared" si="9"/>
-        <v>7.552900233239364E-3</v>
+        <v>6.3618490168236876E-3</v>
       </c>
       <c r="T27" s="9">
         <f t="shared" si="10"/>
-        <v>0.75562917640760074</v>
+        <v>0.89709638937343017</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -4737,7 +4620,7 @@
       </c>
       <c r="S28" s="9">
         <f t="shared" si="9"/>
-        <v>1.1411253449000455E-2</v>
+        <v>1.1411253449000453E-2</v>
       </c>
       <c r="T28" s="9">
         <f t="shared" si="10"/>
@@ -4965,7 +4848,7 @@
       </c>
       <c r="S31" s="9">
         <f t="shared" si="9"/>
-        <v>7.2710755755275806E-3</v>
+        <v>7.2710755755275814E-3</v>
       </c>
       <c r="T31" s="9">
         <f t="shared" si="10"/>
@@ -5193,7 +5076,7 @@
       </c>
       <c r="S34" s="9">
         <f t="shared" si="9"/>
-        <v>6.086545580471424E-3</v>
+        <v>6.0865455804714232E-3</v>
       </c>
       <c r="T34" s="9">
         <f t="shared" si="10"/>
@@ -5364,7 +5247,7 @@
       </c>
       <c r="D37" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45677</v>
+        <v>45683</v>
       </c>
       <c r="E37" s="2">
         <v>9.9999999999999998E-20</v>
@@ -5498,7 +5381,7 @@
       </c>
       <c r="S38" s="9">
         <f t="shared" si="9"/>
-        <v>6.6588407642211127E-3</v>
+        <v>6.6588407642211135E-3</v>
       </c>
       <c r="T38" s="9">
         <f t="shared" si="10"/>
@@ -5574,7 +5457,7 @@
       </c>
       <c r="S39" s="9">
         <f t="shared" si="9"/>
-        <v>5.9505695061192881E-3</v>
+        <v>5.950569506119289E-3</v>
       </c>
       <c r="T39" s="9">
         <f t="shared" si="10"/>
@@ -5598,11 +5481,11 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F40" s="1">
-        <v>20.399999999999999</v>
+        <v>17</v>
       </c>
       <c r="G40" s="1">
         <f t="shared" si="0"/>
-        <v>2.0399999999999999E-18</v>
+        <v>1.7E-18</v>
       </c>
       <c r="H40" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),1),2.5%)</f>
@@ -5622,39 +5505,39 @@
       </c>
       <c r="L40" s="12">
         <f t="shared" si="11"/>
-        <v>21.034439999999996</v>
+        <v>17.528699999999997</v>
       </c>
       <c r="M40" s="12">
         <f t="shared" si="3"/>
-        <v>2.1034439999999996E-18</v>
+        <v>1.7528699999999997E-18</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="4"/>
-        <v>18.589393110989608</v>
+        <v>15.491160925824675</v>
       </c>
       <c r="O40" s="12">
         <f t="shared" si="5"/>
-        <v>0.63443999999999789</v>
+        <v>0.52869999999999706</v>
       </c>
       <c r="P40" s="12">
         <f t="shared" si="6"/>
-        <v>-0.90530344450519529</v>
+        <v>-0.75441953708766274</v>
       </c>
       <c r="Q40" s="14">
         <f t="shared" si="7"/>
-        <v>-0.27086344450519739</v>
+        <v>-0.22571953708766568</v>
       </c>
       <c r="R40" s="12">
         <f t="shared" si="8"/>
-        <v>160.54303751075025</v>
+        <v>160.4978936033327</v>
       </c>
       <c r="S40" s="9">
         <f t="shared" si="9"/>
-        <v>6.2288593482793565E-3</v>
+        <v>6.2306113653521206E-3</v>
       </c>
       <c r="T40" s="9">
         <f t="shared" si="10"/>
-        <v>0.91624990445609866</v>
+        <v>0.91599225951864482</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5726,7 +5609,7 @@
       </c>
       <c r="S41" s="9">
         <f t="shared" si="9"/>
-        <v>6.1959646326745959E-3</v>
+        <v>6.195964632674595E-3</v>
       </c>
       <c r="T41" s="9">
         <f t="shared" si="10"/>
@@ -5954,7 +5837,7 @@
       </c>
       <c r="S44" s="9">
         <f t="shared" si="9"/>
-        <v>6.0111673310153466E-3</v>
+        <v>6.0111673310153475E-3</v>
       </c>
       <c r="T44" s="9">
         <f t="shared" si="18"/>
@@ -6030,7 +5913,7 @@
       </c>
       <c r="S45" s="9">
         <f t="shared" si="9"/>
-        <v>5.9159350261975968E-3</v>
+        <v>5.9159350261975977E-3</v>
       </c>
       <c r="T45" s="9">
         <f t="shared" si="18"/>

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647E1721-014B-47FC-8D34-DA7024ED2BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B37DBF6-F8A0-47DD-8016-20B57B5E55F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,11 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$T$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$X$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId4"/>
+    <pivotCache cacheId="63" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,8 +43,455 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="42">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="15"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="16"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="18"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="20"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="26"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="27"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="28"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="29"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="30"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="31"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="32"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="33"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="34"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="35"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="36"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="37"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="38"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="39"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="40"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="41"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="42">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+    <bk>
+      <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
+    <bk>
+      <rc t="2" v="5"/>
+    </bk>
+    <bk>
+      <rc t="2" v="6"/>
+    </bk>
+    <bk>
+      <rc t="2" v="7"/>
+    </bk>
+    <bk>
+      <rc t="2" v="8"/>
+    </bk>
+    <bk>
+      <rc t="2" v="9"/>
+    </bk>
+    <bk>
+      <rc t="2" v="10"/>
+    </bk>
+    <bk>
+      <rc t="2" v="11"/>
+    </bk>
+    <bk>
+      <rc t="2" v="12"/>
+    </bk>
+    <bk>
+      <rc t="2" v="13"/>
+    </bk>
+    <bk>
+      <rc t="2" v="14"/>
+    </bk>
+    <bk>
+      <rc t="2" v="15"/>
+    </bk>
+    <bk>
+      <rc t="2" v="16"/>
+    </bk>
+    <bk>
+      <rc t="2" v="17"/>
+    </bk>
+    <bk>
+      <rc t="2" v="18"/>
+    </bk>
+    <bk>
+      <rc t="2" v="19"/>
+    </bk>
+    <bk>
+      <rc t="2" v="20"/>
+    </bk>
+    <bk>
+      <rc t="2" v="21"/>
+    </bk>
+    <bk>
+      <rc t="2" v="22"/>
+    </bk>
+    <bk>
+      <rc t="2" v="23"/>
+    </bk>
+    <bk>
+      <rc t="2" v="24"/>
+    </bk>
+    <bk>
+      <rc t="2" v="25"/>
+    </bk>
+    <bk>
+      <rc t="2" v="26"/>
+    </bk>
+    <bk>
+      <rc t="2" v="27"/>
+    </bk>
+    <bk>
+      <rc t="2" v="28"/>
+    </bk>
+    <bk>
+      <rc t="2" v="29"/>
+    </bk>
+    <bk>
+      <rc t="2" v="30"/>
+    </bk>
+    <bk>
+      <rc t="2" v="31"/>
+    </bk>
+    <bk>
+      <rc t="2" v="32"/>
+    </bk>
+    <bk>
+      <rc t="2" v="33"/>
+    </bk>
+    <bk>
+      <rc t="2" v="34"/>
+    </bk>
+    <bk>
+      <rc t="2" v="35"/>
+    </bk>
+    <bk>
+      <rc t="2" v="36"/>
+    </bk>
+    <bk>
+      <rc t="2" v="37"/>
+    </bk>
+    <bk>
+      <rc t="2" v="38"/>
+    </bk>
+    <bk>
+      <rc t="2" v="39"/>
+    </bk>
+    <bk>
+      <rc t="2" v="40"/>
+    </bk>
+    <bk>
+      <rc t="2" v="41"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="174">
   <si>
     <t>Name</t>
   </si>
@@ -545,6 +992,27 @@
   </si>
   <si>
     <t>Target Value</t>
+  </si>
+  <si>
+    <t>Actual Return %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual P&amp;L </t>
+  </si>
+  <si>
+    <t>Close Price</t>
+  </si>
+  <si>
+    <t>Actual Value</t>
+  </si>
+  <si>
+    <t>Actual P&amp;L</t>
+  </si>
+  <si>
+    <t>W/Avg Volatility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volatility </t>
   </si>
 </sst>
 </file>
@@ -573,7 +1041,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -619,6 +1087,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,24 +1175,133 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="40">
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
       <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -734,45 +1317,44 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45697.788801273149" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="51" xr:uid="{AB591AA1-F226-44DB-A2BB-AD1766B5125E}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" invalid="1" refreshedBy="samuel walton" refreshedDate="45707.909361574071" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{1E74FF3F-FD41-47C6-9554-6AF9D4A04843}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:T1048576" sheet="Positions"/>
+    <worksheetSource ref="A1:X46" sheet="Positions"/>
   </cacheSource>
-  <cacheFields count="22">
+  <cacheFields count="29">
     <cacheField name="Chapter" numFmtId="0">
-      <sharedItems containsBlank="1" count="11">
+      <sharedItems count="10">
         <s v="Energy"/>
         <s v="ETF"/>
+        <s v="US Consumer"/>
         <s v="Banking"/>
-        <s v="US Consumer"/>
         <s v="Tech"/>
         <s v="Asia Consumer"/>
         <s v="Health"/>
         <s v="Forex"/>
         <s v="Automotive"/>
         <s v="Industrials"/>
-        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Name" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Ticker" numFmtId="0">
-      <sharedItems containsBlank="1" count="46">
+      <sharedItems count="45">
         <s v="APA"/>
         <s v="BOTZ.UK"/>
         <s v="BATT.NL"/>
+        <s v="ACI"/>
         <s v="ING"/>
         <s v="MO"/>
+        <s v="YPF"/>
         <s v="VWO.US"/>
         <s v="VBTC.DE"/>
         <s v="BONDS"/>
-        <s v="ACI"/>
-        <s v="YPF"/>
+        <s v="NEE"/>
         <s v="EXC"/>
         <s v="KMB"/>
         <s v="PEP"/>
-        <s v="NEE"/>
         <s v="TSM"/>
         <s v="INGR"/>
         <s v="AGIO"/>
@@ -780,11 +1362,11 @@
         <s v="AAPL"/>
         <s v="MSFT"/>
         <s v="MA"/>
+        <s v="GOOGL"/>
         <s v="YUM"/>
         <s v="MAXN"/>
         <s v="V"/>
         <s v="QCOM"/>
-        <s v="GOOGL"/>
         <s v="MC.PA"/>
         <s v="ASML"/>
         <s v="NVDA"/>
@@ -804,73 +1386,95 @@
         <s v="MMM"/>
         <s v="PCG"/>
         <s v="HCA"/>
-        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Date" numFmtId="165">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-06-17T00:00:00" maxDate="2025-02-01T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-06-17T00:00:00" maxDate="2025-02-01T00:00:00"/>
     </cacheField>
     <cacheField name="Volume" numFmtId="164">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="2.2953000000000001"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="2.2953000000000001"/>
     </cacheField>
     <cacheField name="Price" numFmtId="44">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
     </cacheField>
     <cacheField name="Value" numFmtId="44">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1.092E-18" maxValue="89.991048000000006"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.092E-18" maxValue="89.991048000000006"/>
     </cacheField>
-    <cacheField name="Expected Return QoQ%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-1.8341000000000001" maxValue="0.72509999999999997"/>
+    <cacheField name="Expected Return QoQ%" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.4844999999999999" maxValue="0.56589999999999996"/>
     </cacheField>
-    <cacheField name="Volatility" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.105" maxValue="1.4081999999999999"/>
+    <cacheField name="Volatility" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="8.8400000000000006E-2" maxValue="1.3212999999999999"/>
     </cacheField>
-    <cacheField name="Ranking" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-1.3024428348245989" maxValue="1.3437731653076352"/>
+    <cacheField name="Ranking" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.1235147203511693" maxValue="1.1293562935629355"/>
     </cacheField>
-    <cacheField name="Mix %" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-0.14647433487221048" maxValue="0.15112239504474517"/>
+    <cacheField name="Mix %" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.0108145040936092" maxValue="1.0160701067325602"/>
     </cacheField>
-    <cacheField name="Target Price" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="3155.9807400000004"/>
+    <cacheField name="W/Avg Volatility" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.1845000000000003E-19" maxValue="30.189947772600004"/>
     </cacheField>
-    <cacheField name="Target Value" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="99.971055223199997"/>
+    <cacheField name="Target Price" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="2980.43514"/>
     </cacheField>
-    <cacheField name="Tolerance" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5740753836362349" maxValue="2757.2376357056696"/>
+    <cacheField name="Target Value" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="96.802542054400007"/>
     </cacheField>
-    <cacheField name="Unit Profit" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-17.287199999999999" maxValue="413.08074000000033"/>
+    <cacheField name="Close Price" numFmtId="44">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0.78559999999999997" maxValue="717.5"/>
     </cacheField>
-    <cacheField name="Unit Half Loss" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-109.43402722397911" maxValue="7.1688178528347635"/>
+    <cacheField name="Actual Value" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.8559999999999989E-20" maxValue="92.523564000000007"/>
     </cacheField>
-    <cacheField name="Balance Risk" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-123.30036322397916" maxValue="420.2495578528351"/>
+    <cacheField name="Actual P&amp;L" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-9.4742760000000033" maxValue="8.6620360000000005"/>
     </cacheField>
-    <cacheField name="Normalized Risk" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="543.54992107681426"/>
+    <cacheField name="Tolerance" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.8693047453886176" maxValue="2588.3740681324903"/>
     </cacheField>
-    <cacheField name="Risk Mix" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="2.8080220881230035E-3"/>
+    <cacheField name="Unit Profit" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-10.92" maxValue="237.53513999999996"/>
     </cacheField>
-    <cacheField name="Normalized Risk %" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1.0857253751650462"/>
+    <cacheField name="Unit Half Loss" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-77.262965933754913" maxValue="4.9505448820578408"/>
+    </cacheField>
+    <cacheField name="Balance Risk" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-14.94534762730569" maxValue="160.27217406624504"/>
+    </cacheField>
+    <cacheField name="Normalized Risk" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="175.21752169355074"/>
+    </cacheField>
+    <cacheField name="Risk Mix" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1.5480196656953615E-2"/>
+    </cacheField>
+    <cacheField name="Normalized Risk %" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="TargetReturn%_Metric" numFmtId="0" formula="'Target Value'/Value-1" databaseField="0"/>
     <cacheField name="TargetP&amp;L_metric" numFmtId="0" formula="'Target Value'-Value" databaseField="0"/>
+    <cacheField name="ActualP&amp;L_Metric" numFmtId="0" formula="'Actual Value' -Value" databaseField="0"/>
+    <cacheField name="ActualReturn_Metric" numFmtId="0" formula="'ActualP&amp;L_Metric' /Value" databaseField="0"/>
+    <cacheField name="AvgVolatility_Metric" numFmtId="0" formula="'W/Avg Volatility' /Value" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xxpvi="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotVersionInfo" uri="{9F748A41-CAEA-4470-BF7A-CE61E8FFA7F9}">
+      <xxpvi:cacheVersionInfo>
+        <xxpvi:lastRefreshFeature>RichData</xxpvi:lastRefreshFeature>
+      </xxpvi:cacheVersionInfo>
+    </ext>
+    <ext xmlns:xprd="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotRichData" uri="{2C874A73-7782-4A18-856F-96AC7E287872}">
+      <xprd:richInfo pivotCacheGuid="{1E74FF3F-FD41-47C6-9554-6AF9D4A04843}" pivotIgnoreInvalidCache="1" r:id="rId1"/>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="51">
+<file path=xl/pivotCache/richPivotRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="45">
   <r>
     <x v="0"/>
     <s v="APA"/>
@@ -879,19 +1483,23 @@
     <n v="2.2953000000000001"/>
     <n v="21.78"/>
     <n v="49.991634000000005"/>
-    <n v="-5.62E-2"/>
-    <n v="0.4531"/>
-    <n v="-0.12403442948576474"/>
-    <n v="-1.3949065613024133E-2"/>
-    <n v="20.555963999999999"/>
-    <n v="47.182104169200002"/>
-    <n v="14.430530709600477"/>
-    <n v="-1.2240360000000017"/>
-    <n v="-3.674734645199762"/>
-    <n v="-4.8987706451997637"/>
-    <n v="425.14832849803486"/>
-    <n v="2.352120267137831E-3"/>
-    <n v="0.84922159043803613"/>
+    <n v="-8.7400000000000005E-2"/>
+    <n v="0.60389999999999999"/>
+    <n v="-0.14472594800463653"/>
+    <n v="-0.13020842959321346"/>
+    <n v="30.189947772600004"/>
+    <n v="19.876428000000001"/>
+    <n v="45.622365188400003"/>
+    <n v="23.59"/>
+    <n v="54.146127"/>
+    <n v="4.1544929999999951"/>
+    <n v="12.877668065984748"/>
+    <n v="-1.9035720000000005"/>
+    <n v="-4.4511659670076265"/>
+    <n v="-6.3547379670076269"/>
+    <n v="166.62691203325267"/>
+    <n v="6.0014315082574203E-3"/>
+    <n v="0.95097174313809352"/>
   </r>
   <r>
     <x v="1"/>
@@ -899,21 +1507,25 @@
     <x v="1"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="2"/>
-    <n v="20.928000000000001"/>
-    <n v="41.856000000000002"/>
-    <n v="2.5000000000000001E-2"/>
-    <n v="0.25"/>
-    <n v="0.1"/>
-    <n v="1.1246123895482624E-2"/>
-    <n v="21.4512"/>
-    <n v="42.9024"/>
-    <n v="17.08408163265306"/>
-    <n v="0.52319999999999922"/>
-    <n v="-1.9219591836734704"/>
-    <n v="-1.3987591836734712"/>
-    <n v="421.64831703650856"/>
-    <n v="2.371644708624355E-3"/>
-    <n v="0.8422304179444049"/>
+    <n v="22.56"/>
+    <n v="45.12"/>
+    <n v="3.5000000000000003E-2"/>
+    <n v="0.16500000000000001"/>
+    <n v="0.21212121212121213"/>
+    <n v="0.19084324749302797"/>
+    <n v="7.4447999999999999"/>
+    <n v="23.349599999999995"/>
+    <n v="46.69919999999999"/>
+    <n v="22.65"/>
+    <n v="45.3"/>
+    <n v="0.17999999999999972"/>
+    <n v="19.9646017699115"/>
+    <n v="0.78959999999999653"/>
+    <n v="-1.2976991150442494"/>
+    <n v="-0.50809911504425287"/>
+    <n v="160.78027318128929"/>
+    <n v="6.2196684967218627E-3"/>
+    <n v="0.91760385392556976"/>
   </r>
   <r>
     <x v="1"/>
@@ -923,261 +1535,309 @@
     <n v="2"/>
     <n v="16.399000000000001"/>
     <n v="32.798000000000002"/>
-    <n v="2.5000000000000001E-2"/>
-    <n v="0.25"/>
-    <n v="0.1"/>
-    <n v="1.1246123895482624E-2"/>
-    <n v="16.808975"/>
-    <n v="33.61795"/>
-    <n v="13.386938775510204"/>
-    <n v="0.40997499999999931"/>
-    <n v="-1.5060306122448983"/>
-    <n v="-1.096055612244899"/>
-    <n v="421.34561346508002"/>
-    <n v="2.373348548181521E-3"/>
-    <n v="0.84162577624378254"/>
+    <n v="3.5000000000000003E-2"/>
+    <n v="0.16500000000000001"/>
+    <n v="0.21212121212121213"/>
+    <n v="0.19084324749302797"/>
+    <n v="5.4116700000000009"/>
+    <n v="16.972964999999999"/>
+    <n v="33.945929999999997"/>
+    <n v="16.874600000000001"/>
+    <n v="33.749200000000002"/>
+    <n v="0.95120000000000005"/>
+    <n v="14.512389380530973"/>
+    <n v="0.57396499999999762"/>
+    <n v="-0.9433053097345141"/>
+    <n v="-0.36934030973451648"/>
+    <n v="160.64151437597957"/>
+    <n v="6.2250409172532562E-3"/>
+    <n v="0.91681193081212453"/>
   </r>
   <r>
     <x v="2"/>
+    <s v="Albertson Companies"/>
+    <x v="3"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="2"/>
+    <n v="20.5"/>
+    <n v="41"/>
+    <n v="0.14929999999999999"/>
+    <n v="0.31569999999999998"/>
+    <n v="0.47291732657586316"/>
+    <n v="0.42547879816887618"/>
+    <n v="12.9437"/>
+    <n v="23.560649999999999"/>
+    <n v="47.121299999999998"/>
+    <n v="20.52"/>
+    <n v="41.04"/>
+    <n v="3.9999999999999147E-2"/>
+    <n v="17.575445816186555"/>
+    <n v="3.060649999999999"/>
+    <n v="-1.4622770919067225"/>
+    <n v="1.5983729080932765"/>
+    <n v="158.67380115815178"/>
+    <n v="6.302237626508298E-3"/>
+    <n v="0.90558181410456573"/>
+  </r>
+  <r>
+    <x v="3"/>
     <s v="ING Group NV"/>
-    <x v="3"/>
+    <x v="4"/>
     <d v="2024-11-27T00:00:00"/>
     <n v="1.9595"/>
     <n v="15.3"/>
     <n v="29.980350000000001"/>
-    <n v="0.12470000000000001"/>
-    <n v="0.33310000000000001"/>
-    <n v="0.37436205343740619"/>
-    <n v="4.2101220347243569E-2"/>
-    <n v="17.207910000000002"/>
-    <n v="33.718899645"/>
-    <n v="12.661370407149953"/>
-    <n v="1.9079100000000011"/>
-    <n v="-1.319314796425024"/>
-    <n v="0.58859520357497708"/>
-    <n v="419.66096264926011"/>
-    <n v="2.3828759141358825E-3"/>
-    <n v="0.83826073456480554"/>
+    <n v="7.0499999999999993E-2"/>
+    <n v="0.35260000000000002"/>
+    <n v="0.19994327850255245"/>
+    <n v="0.17988688732377014"/>
+    <n v="10.571071410000002"/>
+    <n v="16.37865"/>
+    <n v="32.093964675000002"/>
+    <n v="17.03"/>
+    <n v="33.370285000000003"/>
+    <n v="3.3899350000000013"/>
+    <n v="11.933546525232041"/>
+    <n v="1.0786499999999997"/>
+    <n v="-1.68322673738398"/>
+    <n v="-0.60457673738398032"/>
+    <n v="160.87675080362902"/>
+    <n v="6.2159385679079878E-3"/>
+    <n v="0.91815447021900465"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="2"/>
     <s v="Altaria"/>
-    <x v="4"/>
+    <x v="5"/>
     <d v="2024-09-18T00:00:00"/>
     <n v="1.7345999999999999"/>
     <n v="51.88"/>
     <n v="89.991048000000006"/>
-    <n v="0.1109"/>
-    <n v="0.2039"/>
-    <n v="0.54389406571848942"/>
-    <n v="6.1167000490879003E-2"/>
-    <n v="57.633492000000004"/>
-    <n v="99.971055223199997"/>
-    <n v="47.465690759377864"/>
-    <n v="5.7534920000000014"/>
-    <n v="-2.2071546203110692"/>
-    <n v="3.5463373796889321"/>
-    <n v="416.70322047314619"/>
-    <n v="2.3997894685444205E-3"/>
-    <n v="0.83235272941333582"/>
+    <n v="5.8799999999999998E-2"/>
+    <n v="0.22600000000000001"/>
+    <n v="0.26017699115044246"/>
+    <n v="0.23407853188082897"/>
+    <n v="20.337976848"/>
+    <n v="54.930543999999998"/>
+    <n v="95.282521622399997"/>
+    <n v="53.34"/>
+    <n v="92.523564000000007"/>
+    <n v="2.5325160000000011"/>
+    <n v="44.44825222755312"/>
+    <n v="3.050543999999995"/>
+    <n v="-3.7158738862234415"/>
+    <n v="-0.66532988622344647"/>
+    <n v="160.93750395246849"/>
+    <n v="6.21359208040993E-3"/>
+    <n v="0.91850120009083625"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="YPF"/>
+    <x v="6"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="1.2354000000000001"/>
+    <n v="40.49"/>
+    <n v="50.021346000000001"/>
+    <n v="4.19E-2"/>
+    <n v="0.53510000000000002"/>
+    <n v="7.8303120911979066E-2"/>
+    <n v="7.0448503165926199E-2"/>
+    <n v="26.766422244600001"/>
+    <n v="42.186531000000002"/>
+    <n v="52.117240397400003"/>
+    <n v="37.11"/>
+    <n v="45.845694000000002"/>
+    <n v="-4.1756519999999995"/>
+    <n v="27.116260380391111"/>
+    <n v="1.6965310000000002"/>
+    <n v="-6.6868698098044455"/>
+    <n v="-4.9903388098044452"/>
+    <n v="165.2625128760495"/>
+    <n v="6.0509790308587519E-3"/>
+    <n v="0.94318485547973796"/>
   </r>
   <r>
     <x v="1"/>
     <s v="Emergin Markets"/>
-    <x v="5"/>
+    <x v="7"/>
     <d v="2025-01-31T00:00:00"/>
     <n v="1"/>
     <n v="44.24"/>
     <n v="44.24"/>
-    <n v="2.5000000000000001E-2"/>
-    <n v="0.25"/>
-    <n v="0.1"/>
-    <n v="1.1246123895482624E-2"/>
-    <n v="45.345999999999997"/>
-    <n v="45.345999999999997"/>
-    <n v="36.114285714285714"/>
-    <n v="1.1059999999999945"/>
-    <n v="-4.0628571428571441"/>
-    <n v="-2.9568571428571495"/>
-    <n v="423.20641499569223"/>
-    <n v="2.36291314253868E-3"/>
-    <n v="0.84534267392252604"/>
+    <n v="6.2E-2"/>
+    <n v="0.26100000000000001"/>
+    <n v="0.23754789272030649"/>
+    <n v="0.21371936747166675"/>
+    <n v="11.546640000000002"/>
+    <n v="46.982880000000002"/>
+    <n v="46.982880000000002"/>
+    <n v="45.97"/>
+    <n v="45.97"/>
+    <n v="1.7299999999999969"/>
+    <n v="36.897414512093412"/>
+    <n v="2.7428799999999995"/>
+    <n v="-3.6712927439532947"/>
+    <n v="-0.92841274395329521"/>
+    <n v="161.20058681019833"/>
+    <n v="6.2034513632225506E-3"/>
+    <n v="0.92000266441464951"/>
   </r>
   <r>
     <x v="1"/>
     <s v="Bitcoin ETF"/>
-    <x v="6"/>
+    <x v="8"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="1"/>
     <n v="48.68"/>
     <n v="48.68"/>
-    <n v="2.5000000000000001E-2"/>
-    <n v="0.25"/>
-    <n v="0.1"/>
-    <n v="1.1246123895482624E-2"/>
-    <n v="49.896999999999998"/>
-    <n v="49.896999999999998"/>
-    <n v="39.738775510204079"/>
-    <n v="1.2169999999999987"/>
-    <n v="-4.4706122448979606"/>
-    <n v="-3.2536122448979619"/>
-    <n v="423.50317009773306"/>
-    <n v="2.3612574134196612E-3"/>
-    <n v="0.84593543372618341"/>
+    <n v="3.7999999999999999E-2"/>
+    <n v="0.16900000000000001"/>
+    <n v="0.22485207100591714"/>
+    <n v="0.20229706877113868"/>
+    <n v="8.2269199999999998"/>
+    <n v="50.52984"/>
+    <n v="50.52984"/>
+    <n v="49.3"/>
+    <n v="49.3"/>
+    <n v="0.61999999999999744"/>
+    <n v="43.041556145004421"/>
+    <n v="1.8498400000000004"/>
+    <n v="-2.8192219274977894"/>
+    <n v="-0.96938192749778906"/>
+    <n v="161.24155599374282"/>
+    <n v="6.2018751545588301E-3"/>
+    <n v="0.92023648340231989"/>
   </r>
   <r>
     <x v="1"/>
     <s v="ETF5"/>
-    <x v="7"/>
+    <x v="9"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="1"/>
     <n v="51.28"/>
     <n v="51.28"/>
-    <n v="2.5000000000000001E-2"/>
-    <n v="0.25"/>
-    <n v="0.1"/>
-    <n v="1.1246123895482624E-2"/>
-    <n v="52.561999999999998"/>
-    <n v="52.561999999999998"/>
-    <n v="41.861224489795916"/>
-    <n v="1.2819999999999965"/>
-    <n v="-4.7093877551020427"/>
-    <n v="-3.4273877551020462"/>
-    <n v="423.67694560793711"/>
-    <n v="2.3602889191081493E-3"/>
-    <n v="0.84628254532291958"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="Albertson Companies"/>
-    <x v="8"/>
-    <d v="2024-12-04T00:00:00"/>
-    <n v="1"/>
-    <n v="20.36"/>
-    <n v="20.36"/>
-    <n v="6.1999999999999998E-3"/>
-    <n v="0.25559999999999999"/>
-    <n v="2.4256651017214397E-2"/>
-    <n v="2.7279330262907769E-3"/>
-    <n v="20.486231999999998"/>
-    <n v="20.486231999999998"/>
-    <n v="16.295821994557386"/>
-    <n v="0.12623199999999812"/>
-    <n v="-2.0320890027213068"/>
-    <n v="-1.9058570027213086"/>
-    <n v="422.15541485555639"/>
-    <n v="2.3687958624009535E-3"/>
-    <n v="0.84324333129142626"/>
+    <n v="3.7999999999999999E-2"/>
+    <n v="0.16900000000000001"/>
+    <n v="0.22485207100591714"/>
+    <n v="0.20229706877113868"/>
+    <n v="8.6663200000000007"/>
+    <n v="53.228640000000006"/>
+    <n v="53.228640000000006"/>
+    <n v="51.28"/>
+    <n v="51.28"/>
+    <n v="0"/>
+    <n v="45.340406719717066"/>
+    <n v="1.9486400000000046"/>
+    <n v="-2.9697966401414675"/>
+    <n v="-1.0211566401414629"/>
+    <n v="161.29333070638651"/>
+    <n v="6.1998843698030494E-3"/>
+    <n v="0.92053197161687317"/>
   </r>
   <r>
     <x v="0"/>
-    <s v="YPF"/>
-    <x v="9"/>
-    <d v="2024-12-01T00:00:00"/>
-    <n v="0.95840000000000003"/>
-    <n v="41.76"/>
-    <n v="40.022784000000001"/>
-    <n v="0.72509999999999997"/>
-    <n v="0.53959999999999997"/>
-    <n v="1.3437731653076352"/>
-    <n v="0.15112239504474517"/>
-    <n v="72.040175999999988"/>
-    <n v="69.043304678399991"/>
-    <n v="51.270718232044189"/>
-    <n v="30.28017599999999"/>
-    <n v="4.7553591160220954"/>
-    <n v="35.035535116022089"/>
-    <n v="385.21402273681304"/>
-    <n v="2.5959594951797033E-3"/>
-    <n v="0.76945396022908807"/>
+    <s v="NextEra Energy"/>
+    <x v="10"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.74609999999999999"/>
+    <n v="73.7"/>
+    <n v="54.987569999999998"/>
+    <n v="0.1212"/>
+    <n v="0.24540000000000001"/>
+    <n v="0.49388753056234719"/>
+    <n v="0.44434547250734346"/>
+    <n v="13.493949678"/>
+    <n v="82.632440000000003"/>
+    <n v="61.652063484000003"/>
+    <n v="69.06"/>
+    <n v="51.525666000000001"/>
+    <n v="-3.461903999999997"/>
+    <n v="65.557729941291583"/>
+    <n v="8.9324399999999997"/>
+    <n v="-4.0711350293542097"/>
+    <n v="4.86130497064579"/>
+    <n v="155.41086909559925"/>
+    <n v="6.4345563847587857E-3"/>
+    <n v="0.886959635049555"/>
   </r>
   <r>
     <x v="0"/>
     <s v="Excelon"/>
-    <x v="10"/>
+    <x v="11"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="0.52039999999999997"/>
     <n v="40.340000000000003"/>
     <n v="20.992936"/>
-    <n v="3.9699999999999999E-2"/>
-    <n v="0.2208"/>
-    <n v="0.17980072463768115"/>
-    <n v="2.0220612257729174E-2"/>
-    <n v="41.941498000000003"/>
-    <n v="21.8263555592"/>
-    <n v="34.154601642536619"/>
-    <n v="1.6014979999999994"/>
-    <n v="-3.0926991787316922"/>
-    <n v="-1.4912011787316928"/>
-    <n v="421.74075903156677"/>
-    <n v="2.3711248642324162E-3"/>
-    <n v="0.84241506817775746"/>
+    <n v="8.6900000000000005E-2"/>
+    <n v="0.24529999999999999"/>
+    <n v="0.35426008968609868"/>
+    <n v="0.31872411672922735"/>
+    <n v="5.1495672008"/>
+    <n v="43.845546000000006"/>
+    <n v="22.817222138400002"/>
+    <n v="42.65"/>
+    <n v="22.195059999999998"/>
+    <n v="1.2021239999999977"/>
+    <n v="34.82389502762431"/>
+    <n v="3.5055460000000025"/>
+    <n v="-2.7580524861878466"/>
+    <n v="0.7474935138121559"/>
+    <n v="159.5246805524329"/>
+    <n v="6.2686224886143432E-3"/>
+    <n v="0.91043794599170247"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="2"/>
     <s v="Kimberly Clark"/>
-    <x v="11"/>
+    <x v="12"/>
     <d v="2024-09-09T00:00:00"/>
     <n v="0.51380000000000003"/>
     <n v="138.53"/>
     <n v="71.176714000000004"/>
-    <n v="6.4000000000000003E-3"/>
-    <n v="0.1852"/>
-    <n v="3.4557235421166309E-2"/>
-    <n v="3.8863495103179696E-3"/>
-    <n v="139.41659200000001"/>
-    <n v="71.632244969600009"/>
-    <n v="117.51781472684085"/>
-    <n v="0.88659200000000737"/>
-    <n v="-10.506092636579574"/>
-    <n v="-9.6195006365795663"/>
-    <n v="429.86905848941467"/>
-    <n v="2.3262897858107286E-3"/>
-    <n v="0.85865111317771359"/>
+    <n v="5.0200000000000002E-2"/>
+    <n v="0.2001"/>
+    <n v="0.25087456271864067"/>
+    <n v="0.22570923380948818"/>
+    <n v="14.242460471400001"/>
+    <n v="145.484206"/>
+    <n v="74.749785042799999"/>
+    <n v="137.93"/>
+    <n v="70.868434000000008"/>
+    <n v="-0.30827999999999633"/>
+    <n v="120.47134533437691"/>
+    <n v="6.9542059999999992"/>
+    <n v="-9.0293273328115475"/>
+    <n v="-2.0751213328115483"/>
+    <n v="162.34729539905658"/>
+    <n v="6.1596344893948326E-3"/>
+    <n v="0.92654715025016887"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="2"/>
     <s v="Pepsi"/>
-    <x v="12"/>
+    <x v="13"/>
     <d v="2024-06-17T00:00:00"/>
     <n v="0.51239999999999997"/>
     <n v="157.99"/>
     <n v="80.954076000000001"/>
-    <n v="-3.0200000000000001E-2"/>
-    <n v="0.1744"/>
-    <n v="-0.17316513761467892"/>
-    <n v="-1.9474365919929775E-2"/>
-    <n v="153.21870200000001"/>
-    <n v="78.509262904799996"/>
-    <n v="131.15557031379714"/>
-    <n v="-4.7712980000000016"/>
-    <n v="-13.417214843101434"/>
-    <n v="-18.188512843101435"/>
-    <n v="438.43807069593652"/>
-    <n v="2.2808238308609729E-3"/>
-    <n v="0.87576746925093063"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="NextEra Energy"/>
-    <x v="13"/>
-    <d v="2024-08-07T00:00:00"/>
-    <n v="0.45179999999999998"/>
-    <n v="77.430000000000007"/>
-    <n v="34.982874000000002"/>
-    <n v="-7.0400000000000004E-2"/>
-    <n v="0.28639999999999999"/>
-    <n v="-0.24581005586592181"/>
-    <n v="-2.7644103430236617E-2"/>
-    <n v="71.97892800000001"/>
-    <n v="32.520079670400001"/>
-    <n v="57.068101415094347"/>
-    <n v="-5.4510719999999964"/>
-    <n v="-10.18094929245283"/>
-    <n v="-15.632021292452826"/>
-    <n v="435.8815791452879"/>
-    <n v="2.2942011037972321E-3"/>
-    <n v="0.87066095071361682"/>
+    <n v="6.59E-2"/>
+    <n v="0.1875"/>
+    <n v="0.35146666666666665"/>
+    <n v="0.31621090310330507"/>
+    <n v="15.178889250000001"/>
+    <n v="168.40154100000001"/>
+    <n v="86.288949608400003"/>
+    <n v="139.5"/>
+    <n v="71.479799999999997"/>
+    <n v="-9.4742760000000033"/>
+    <n v="140.86126961483598"/>
+    <n v="10.411541"/>
+    <n v="-8.5643651925820166"/>
+    <n v="1.8471758074179832"/>
+    <n v="158.42499825882706"/>
+    <n v="6.312135149064345E-3"/>
+    <n v="0.90416184824201995"/>
   </r>
   <r>
     <x v="4"/>
@@ -1187,19 +1847,23 @@
     <n v="0.4108"/>
     <n v="189.76"/>
     <n v="77.953407999999996"/>
-    <n v="0.17019999999999999"/>
-    <n v="0.38159999999999999"/>
-    <n v="0.44601677148846958"/>
-    <n v="5.0159598716224905E-2"/>
-    <n v="222.05715199999997"/>
-    <n v="91.221078041599995"/>
-    <n v="156.64520389631829"/>
-    <n v="32.297151999999983"/>
-    <n v="-16.557398051840849"/>
-    <n v="15.739753948159134"/>
-    <n v="404.50980390467595"/>
-    <n v="2.4721279690804558E-3"/>
-    <n v="0.80799672959620927"/>
+    <n v="0.24179999999999999"/>
+    <n v="0.32229999999999998"/>
+    <n v="0.75023270245113249"/>
+    <n v="0.67497655646729637"/>
+    <n v="25.124383398399996"/>
+    <n v="235.643968"/>
+    <n v="96.802542054400007"/>
+    <n v="200.95"/>
+    <n v="82.550259999999994"/>
+    <n v="4.5968519999999984"/>
+    <n v="175.62239703840814"/>
+    <n v="45.88396800000001"/>
+    <n v="-7.0688014807959263"/>
+    <n v="38.815166519204084"/>
+    <n v="121.45700754704096"/>
+    <n v="8.2333660296438193E-3"/>
+    <n v="0.69317843542762225"/>
   </r>
   <r>
     <x v="5"/>
@@ -1209,19 +1873,23 @@
     <n v="0.34860000000000002"/>
     <n v="131.91"/>
     <n v="45.983826000000001"/>
-    <n v="0.1167"/>
-    <n v="0.22509999999999999"/>
-    <n v="0.51843625055530873"/>
-    <n v="5.8303983056544738E-2"/>
-    <n v="147.30389700000001"/>
-    <n v="51.350138494200003"/>
-    <n v="119.00938289426199"/>
-    <n v="15.39389700000001"/>
-    <n v="-6.4503085528690036"/>
-    <n v="8.9435884471310061"/>
-    <n v="411.3059694057041"/>
-    <n v="2.4312800551980797E-3"/>
-    <n v="0.821571875230799"/>
+    <n v="6.9500000000000006E-2"/>
+    <n v="0.25430000000000003"/>
+    <n v="0.2732992528509634"/>
+    <n v="0.24588449419990988"/>
+    <n v="11.693686951800002"/>
+    <n v="141.07774500000002"/>
+    <n v="49.179701907000009"/>
+    <n v="126.91"/>
+    <n v="44.240825999999998"/>
+    <n v="-1.7430000000000021"/>
+    <n v="111.3352464550979"/>
+    <n v="9.1677450000000249"/>
+    <n v="-10.287376772451047"/>
+    <n v="-1.1196317724510223"/>
+    <n v="161.39180583869606"/>
+    <n v="6.1961014365218489E-3"/>
+    <n v="0.92109398808279364"/>
   </r>
   <r>
     <x v="6"/>
@@ -1231,19 +1899,23 @@
     <n v="0.28749999999999998"/>
     <n v="34.78"/>
     <n v="9.99925"/>
-    <n v="-1.2800000000000001E-2"/>
-    <n v="0.56640000000000001"/>
-    <n v="-2.2598870056497175E-2"/>
-    <n v="-2.5414969255327961E-3"/>
-    <n v="34.334815999999996"/>
-    <n v="9.8712595999999984"/>
-    <n v="22.023809523809526"/>
-    <n v="-0.44518400000000469"/>
-    <n v="-6.3780952380952378"/>
-    <n v="-6.8232792380952425"/>
-    <n v="427.07283709093036"/>
-    <n v="2.3415209611822832E-3"/>
-    <n v="0.85306574114619993"/>
+    <n v="-0.1268"/>
+    <n v="0.58609999999999995"/>
+    <n v="-0.2163453335608258"/>
+    <n v="-0.19464364560163458"/>
+    <n v="5.8605604249999992"/>
+    <n v="30.369896000000001"/>
+    <n v="8.7313450999999986"/>
+    <n v="34.020000000000003"/>
+    <n v="9.7807499999999994"/>
+    <n v="-0.21850000000000058"/>
+    <n v="20.304746336622102"/>
+    <n v="-4.4101040000000005"/>
+    <n v="-7.2376268316889494"/>
+    <n v="-11.64773083168895"/>
+    <n v="171.919904897934"/>
+    <n v="5.8166621287609683E-3"/>
+    <n v="0.981179868521459"/>
   </r>
   <r>
     <x v="0"/>
@@ -1253,41 +1925,49 @@
     <n v="0.25169999999999998"/>
     <n v="178.56"/>
     <n v="44.943551999999997"/>
-    <n v="0.2082"/>
-    <n v="0.51629999999999998"/>
-    <n v="0.4032539221382917"/>
-    <n v="4.5350435697065317E-2"/>
-    <n v="215.73619199999999"/>
-    <n v="54.300799526399992"/>
-    <n v="136.50332543383533"/>
-    <n v="37.176191999999986"/>
-    <n v="-21.028337283082337"/>
-    <n v="16.147854716917649"/>
-    <n v="404.10170313591743"/>
-    <n v="2.4746245616877674E-3"/>
-    <n v="0.80718156001732733"/>
+    <n v="0.123"/>
+    <n v="0.47839999999999999"/>
+    <n v="0.25710702341137126"/>
+    <n v="0.23131651384800542"/>
+    <n v="21.500995276799998"/>
+    <n v="200.52288000000001"/>
+    <n v="50.471608895999999"/>
+    <n v="162.5"/>
+    <n v="40.901249999999997"/>
+    <n v="-4.0423019999999994"/>
+    <n v="131.73970783532536"/>
+    <n v="21.962880000000013"/>
+    <n v="-23.41014608233732"/>
+    <n v="-1.4472660823373076"/>
+    <n v="161.71944014858235"/>
+    <n v="6.1835484904055682E-3"/>
+    <n v="0.92296385992391761"/>
   </r>
   <r>
     <x v="4"/>
     <s v="Apple2"/>
     <x v="18"/>
     <d v="2024-07-09T00:00:00"/>
-    <n v="0.18820000000000001"/>
+    <n v="1E-4"/>
     <n v="227.38"/>
-    <n v="42.792915999999998"/>
-    <n v="7.7799999999999994E-2"/>
-    <n v="0.27179999999999999"/>
-    <n v="0.28623988226637231"/>
-    <n v="3.2190891797959822E-2"/>
-    <n v="245.07016400000001"/>
-    <n v="46.122204864800004"/>
-    <n v="190.43551088777221"/>
-    <n v="17.69016400000001"/>
-    <n v="-18.472244556113893"/>
-    <n v="-0.78208055611388261"/>
-    <n v="421.03163840894899"/>
-    <n v="2.3751184205038239E-3"/>
-    <n v="0.84099862007579895"/>
+    <n v="2.2738000000000001E-2"/>
+    <n v="0.2092"/>
+    <n v="0.28439999999999999"/>
+    <n v="0.73558368495077353"/>
+    <n v="0.66179698784050023"/>
+    <n v="6.4666871999999997E-3"/>
+    <n v="274.94789600000001"/>
+    <n v="2.7494789600000003E-2"/>
+    <n v="244.87"/>
+    <n v="2.4487000000000002E-2"/>
+    <n v="1.7490000000000006E-3"/>
+    <n v="211.47693452380955"/>
+    <n v="47.567896000000019"/>
+    <n v="-7.9515327380952243"/>
+    <n v="39.616363261904795"/>
+    <n v="120.65581080434025"/>
+    <n v="8.2880384569429116E-3"/>
+    <n v="0.68860585196132951"/>
   </r>
   <r>
     <x v="4"/>
@@ -1297,151 +1977,179 @@
     <n v="0.16059999999999999"/>
     <n v="421.18"/>
     <n v="67.641508000000002"/>
-    <n v="7.3899999999999993E-2"/>
-    <n v="0.27660000000000001"/>
-    <n v="0.26717281272595805"/>
-    <n v="3.0046585534207009E-2"/>
-    <n v="452.30520200000007"/>
-    <n v="72.640215441200013"/>
-    <n v="350.19539369751396"/>
-    <n v="31.125202000000058"/>
-    <n v="-35.492303151243021"/>
-    <n v="-4.3671011512429629"/>
-    <n v="424.61665900407809"/>
-    <n v="2.3550653955628151E-3"/>
-    <n v="0.84815959587524326"/>
+    <n v="0.2412"/>
+    <n v="0.27010000000000001"/>
+    <n v="0.89300259163272855"/>
+    <n v="0.80342514028957801"/>
+    <n v="18.269971310800003"/>
+    <n v="522.76861600000007"/>
+    <n v="83.956639729600013"/>
+    <n v="414.77"/>
+    <n v="66.612061999999995"/>
+    <n v="-1.0294460000000072"/>
+    <n v="409.34979103897371"/>
+    <n v="101.58861600000006"/>
+    <n v="-5.9151044805131505"/>
+    <n v="95.673511519486908"/>
+    <n v="64.598662546758135"/>
+    <n v="1.5480196656953615E-2"/>
+    <n v="0.36867695606229905"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Master Card"/>
     <x v="20"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="0.12939999999999999"/>
     <n v="501.56"/>
     <n v="64.901863999999989"/>
-    <n v="0.1414"/>
-    <n v="0.2291"/>
-    <n v="0.61719773024879965"/>
-    <n v="6.9410821423886646E-2"/>
-    <n v="572.48058400000002"/>
-    <n v="74.078987569600002"/>
-    <n v="461.11979406086232"/>
-    <n v="70.920584000000019"/>
-    <n v="-20.220102969568842"/>
-    <n v="50.700481030431177"/>
-    <n v="369.54907682240389"/>
-    <n v="2.7060005361089702E-3"/>
-    <n v="0.7381636801271827"/>
+    <n v="0.1928"/>
+    <n v="0.26650000000000001"/>
+    <n v="0.72345215759849901"/>
+    <n v="0.65088237890626699"/>
+    <n v="17.296346755999998"/>
+    <n v="598.2607680000001"/>
+    <n v="77.414943379200011"/>
+    <n v="568.5"/>
+    <n v="73.56389999999999"/>
+    <n v="8.6620360000000005"/>
+    <n v="467.13234609294966"/>
+    <n v="96.700768000000096"/>
+    <n v="-17.213826953525171"/>
+    <n v="79.486941046474925"/>
+    <n v="80.785233019770118"/>
+    <n v="1.2378499914152326E-2"/>
+    <n v="0.46105681805647636"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Google"/>
+    <x v="21"/>
+    <d v="2025-01-21T00:00:00"/>
+    <n v="5.3800000000000001E-2"/>
+    <n v="185.82"/>
+    <n v="9.9971160000000001"/>
+    <n v="0.1925"/>
+    <n v="0.28539999999999999"/>
+    <n v="0.6744919411352488"/>
+    <n v="0.60683338156945643"/>
+    <n v="2.8531769063999999"/>
+    <n v="221.59034999999997"/>
+    <n v="11.921560829999999"/>
+    <n v="185.27"/>
+    <n v="9.9675260000000012"/>
+    <n v="-2.9589999999998895E-2"/>
+    <n v="170.02470491353276"/>
+    <n v="35.770349999999979"/>
+    <n v="-7.8976475432336173"/>
+    <n v="27.872702456766362"/>
+    <n v="132.39947160947867"/>
+    <n v="7.552900233239364E-3"/>
+    <n v="0.75562917640760074"/>
   </r>
   <r>
     <x v="5"/>
     <s v="Yum! Brands"/>
-    <x v="21"/>
+    <x v="22"/>
     <d v="2024-10-15T00:00:00"/>
     <n v="2.9999999999999997E-4"/>
     <n v="130.51"/>
     <n v="3.9152999999999993E-2"/>
-    <n v="3.49E-2"/>
-    <n v="0.19839999999999999"/>
-    <n v="0.17590725806451613"/>
-    <n v="1.9782748183081834E-2"/>
-    <n v="135.06479899999999"/>
-    <n v="4.0519439699999993E-2"/>
-    <n v="112.17017619252256"/>
-    <n v="4.5547990000000027"/>
-    <n v="-9.1699119037387149"/>
-    <n v="-4.6151129037387122"/>
-    <n v="424.86467075657379"/>
-    <n v="2.3536906427622218E-3"/>
-    <n v="0.84865499223642815"/>
+    <n v="0.1169"/>
+    <n v="0.23899999999999999"/>
+    <n v="0.48912133891213394"/>
+    <n v="0.44005737947032519"/>
+    <n v="9.3575669999999972E-3"/>
+    <n v="145.76661899999999"/>
+    <n v="4.3729985699999994E-2"/>
+    <n v="148.29"/>
+    <n v="4.4486999999999992E-2"/>
+    <n v="5.3339999999999985E-3"/>
+    <n v="116.3087068888691"/>
+    <n v="15.256619000000001"/>
+    <n v="-7.1006465555654472"/>
+    <n v="8.1559724444345534"/>
+    <n v="152.11620162181049"/>
+    <n v="6.5739217081306582E-3"/>
+    <n v="0.86815633591631525"/>
   </r>
   <r>
     <x v="0"/>
     <s v="Maxeon Solar"/>
-    <x v="22"/>
+    <x v="23"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="10.92"/>
     <n v="1.092E-18"/>
-    <n v="-1.8341000000000001"/>
-    <n v="1.4081999999999999"/>
-    <n v="-1.3024428348245989"/>
-    <n v="-0.14647433487221048"/>
+    <n v="-1.4844999999999999"/>
+    <n v="1.3212999999999999"/>
+    <n v="-1.1235147203511693"/>
+    <n v="-1.0108145040936092"/>
+    <n v="1.4428596E-18"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="2.5740753836362349"/>
+    <n v="5.64"/>
+    <n v="5.6399999999999995E-19"/>
+    <n v="-5.280000000000001E-19"/>
+    <n v="2.8693047453886176"/>
     <n v="-10.92"/>
-    <n v="-4.1729623081818827"/>
-    <n v="-15.092962308181882"/>
-    <n v="435.34252016101698"/>
-    <n v="2.2970418778072428E-3"/>
-    <n v="0.86958419585589519"/>
+    <n v="-4.025347627305691"/>
+    <n v="-14.94534762730569"/>
+    <n v="175.21752169355074"/>
+    <n v="5.7071917827314364E-3"/>
+    <n v="1"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Visa"/>
-    <x v="23"/>
+    <x v="24"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="283.43"/>
     <n v="2.8342999999999998E-17"/>
-    <n v="0.15409999999999999"/>
-    <n v="0.21940000000000001"/>
-    <n v="0.70237010027347302"/>
-    <n v="7.8989411681580315E-2"/>
-    <n v="327.10656299999999"/>
-    <n v="3.2710656299999999E-17"/>
-    <n v="266.05650990331361"/>
-    <n v="43.676562999999987"/>
-    <n v="-8.6867450483431981"/>
-    <n v="34.989817951656789"/>
-    <n v="385.25973990117831"/>
-    <n v="2.5956514435079739E-3"/>
-    <n v="0.76954527895347236"/>
+    <n v="0.17100000000000001"/>
+    <n v="0.24360000000000001"/>
+    <n v="0.70197044334975367"/>
+    <n v="0.6315555041069415"/>
+    <n v="6.9043547999999996E-18"/>
+    <n v="331.89653000000004"/>
+    <n v="3.3189653000000001E-17"/>
+    <n v="355.23"/>
+    <n v="3.5522999999999998E-17"/>
+    <n v="7.1800000000000003E-18"/>
+    <n v="264.24575797128472"/>
+    <n v="48.466530000000034"/>
+    <n v="-9.5921210143576445"/>
+    <n v="38.87440898564239"/>
+    <n v="121.39776508060265"/>
+    <n v="8.2373839364838809E-3"/>
+    <n v="0.6928403273099768"/>
   </r>
   <r>
     <x v="4"/>
     <s v="QualComm2"/>
-    <x v="24"/>
+    <x v="25"/>
     <d v="2024-09-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="188.12"/>
     <n v="1.8812000000000001E-17"/>
-    <n v="-1.1599999999999999E-2"/>
-    <n v="0.39100000000000001"/>
-    <n v="-2.9667519181585673E-2"/>
-    <n v="-3.3364459638771972E-3"/>
-    <n v="185.93780799999999"/>
-    <n v="1.8593780799999998E-17"/>
-    <n v="134.12234421788108"/>
-    <n v="-2.1821920000000148"/>
-    <n v="-26.998827891059463"/>
-    <n v="-29.181019891059478"/>
-    <n v="449.43057774389456"/>
-    <n v="2.2250377466969864E-3"/>
-    <n v="0.89772468674993211"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="Google"/>
-    <x v="25"/>
-    <d v="2025-01-21T00:00:00"/>
-    <n v="5.3800000000000001E-2"/>
-    <n v="185.82"/>
-    <n v="9.9971160000000001"/>
-    <n v="8.0799999999999997E-2"/>
-    <n v="0.32900000000000001"/>
-    <n v="0.24559270516717324"/>
-    <n v="2.7619659901367659E-2"/>
-    <n v="200.83425599999998"/>
-    <n v="10.8048829728"/>
-    <n v="148.87037333760614"/>
-    <n v="15.014255999999989"/>
-    <n v="-18.474813331196927"/>
-    <n v="-3.460557331196938"/>
-    <n v="423.71011518403202"/>
-    <n v="2.3601041470668344E-3"/>
-    <n v="0.84634880059967199"/>
+    <n v="0.1164"/>
+    <n v="0.3664"/>
+    <n v="0.31768558951965065"/>
+    <n v="0.28581841947528813"/>
+    <n v="6.8927168000000004E-18"/>
+    <n v="210.01716800000003"/>
+    <n v="2.1001716800000003E-17"/>
+    <n v="175.22"/>
+    <n v="1.7522E-17"/>
+    <n v="-1.2900000000000016E-18"/>
+    <n v="150.49600000000001"/>
+    <n v="21.897168000000022"/>
+    <n v="-18.811999999999998"/>
+    <n v="3.0851680000000243"/>
+    <n v="157.18700606624503"/>
+    <n v="6.3618490168236884E-3"/>
+    <n v="0.89709638937343017"/>
   </r>
   <r>
     <x v="5"/>
@@ -1451,19 +2159,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="668.82"/>
     <n v="6.6881999999999999E-17"/>
-    <n v="-4.3E-3"/>
-    <n v="0.2974"/>
-    <n v="-1.4458641560188298E-2"/>
-    <n v="-1.6260367434625179E-3"/>
-    <n v="665.94407400000011"/>
-    <n v="6.6594407400000007E-17"/>
-    <n v="513.8050241991242"/>
-    <n v="-2.8759259999999358"/>
-    <n v="-77.507487900437923"/>
-    <n v="-80.383413900437859"/>
-    <n v="500.63297175327295"/>
-    <n v="1.9974713141603269E-3"/>
-    <n v="1"/>
+    <n v="0.16070000000000001"/>
+    <n v="0.27700000000000002"/>
+    <n v="0.58014440433212999"/>
+    <n v="0.52194988436321643"/>
+    <n v="1.8526314000000002E-17"/>
+    <n v="776.29937400000006"/>
+    <n v="7.7629937400000001E-17"/>
+    <s v="#VALUE!"/>
+    <n v="6.6881999999999999E-17"/>
+    <n v="0"/>
+    <n v="599.14001612469769"/>
+    <n v="107.47937400000001"/>
+    <n v="-34.839991937651178"/>
+    <n v="72.63938206234883"/>
+    <n v="87.632792003896213"/>
+    <n v="1.1411253449000453E-2"/>
+    <n v="0.50013715042244966"/>
   </r>
   <r>
     <x v="4"/>
@@ -1473,19 +2185,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="700.32"/>
     <n v="7.0031999999999998E-17"/>
-    <n v="-1.9800000000000002E-2"/>
-    <n v="0.43480000000000002"/>
-    <n v="-4.5538178472861089E-2"/>
-    <n v="-5.1212799708039549E-3"/>
-    <n v="686.453664"/>
-    <n v="6.8645366400000003E-17"/>
-    <n v="481.45194555204182"/>
-    <n v="-13.866336000000047"/>
-    <n v="-109.43402722397911"/>
-    <n v="-123.30036322397916"/>
-    <n v="543.54992107681426"/>
-    <n v="1.8397574191877776E-3"/>
-    <n v="1.0857253751650462"/>
+    <n v="0.2051"/>
+    <n v="0.36940000000000001"/>
+    <n v="0.55522468868435304"/>
+    <n v="0.49952987547647199"/>
+    <n v="2.5869820800000001E-17"/>
+    <n v="843.95563200000015"/>
+    <n v="8.4395563200000012E-17"/>
+    <n v="717.5"/>
+    <n v="7.1749999999999995E-17"/>
+    <n v="1.7179999999999966E-18"/>
+    <n v="601.49446019067261"/>
+    <n v="143.6356320000001"/>
+    <n v="-49.412769904663719"/>
+    <n v="94.222862095336382"/>
+    <n v="66.049311970908661"/>
+    <n v="1.5140203132478486E-2"/>
+    <n v="0.376956090535435"/>
   </r>
   <r>
     <x v="4"/>
@@ -1495,19 +2211,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="147.01"/>
     <n v="1.4700999999999999E-17"/>
-    <n v="0.47439999999999999"/>
-    <n v="0.55710000000000004"/>
-    <n v="0.85155268353975944"/>
-    <n v="9.5766669826188408E-2"/>
-    <n v="216.75154399999997"/>
-    <n v="2.1675154399999996E-17"/>
-    <n v="135.78091807518237"/>
-    <n v="69.741543999999976"/>
-    <n v="-5.6145409624088103"/>
-    <n v="64.127003037591166"/>
-    <n v="356.12255481524392"/>
-    <n v="2.8080220881230035E-3"/>
-    <n v="0.71134458756893837"/>
+    <n v="0.55089999999999995"/>
+    <n v="0.48780000000000001"/>
+    <n v="1.1293562935629355"/>
+    <n v="1.0160701067325602"/>
+    <n v="7.1711477999999992E-18"/>
+    <n v="227.99780899999999"/>
+    <n v="2.2799780899999998E-17"/>
+    <n v="139.22999999999999"/>
+    <n v="1.3922999999999999E-17"/>
+    <n v="-7.7800000000000002E-19"/>
+    <n v="156.91108976411567"/>
+    <n v="80.987808999999999"/>
+    <n v="4.9505448820578408"/>
+    <n v="85.938353882057839"/>
+    <n v="74.333820184187203"/>
+    <n v="1.3452826688069595E-2"/>
+    <n v="0.42423736773422943"/>
   </r>
   <r>
     <x v="4"/>
@@ -1517,19 +2237,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="169.34"/>
     <n v="1.6933999999999999E-17"/>
-    <n v="4.6899999999999997E-2"/>
-    <n v="0.42930000000000001"/>
-    <n v="0.10924761239226646"/>
-    <n v="1.2286121842490914E-2"/>
-    <n v="177.28204599999998"/>
-    <n v="1.7728204599999998E-17"/>
-    <n v="122.49710648148148"/>
-    <n v="7.9420459999999764"/>
-    <n v="-23.421446759259261"/>
-    <n v="-15.479400759259285"/>
-    <n v="435.7289586120944"/>
-    <n v="2.2950046817756843E-3"/>
-    <n v="0.87035609557661098"/>
+    <n v="0.21429999999999999"/>
+    <n v="0.40479999999999999"/>
+    <n v="0.52939723320158105"/>
+    <n v="0.47629318250492114"/>
+    <n v="6.8548831999999995E-18"/>
+    <n v="205.62956199999999"/>
+    <n v="2.0562956199999998E-17"/>
+    <n v="174.06"/>
+    <n v="1.7406000000000001E-17"/>
+    <n v="4.720000000000018E-19"/>
+    <n v="142.2427551448971"/>
+    <n v="36.289561999999989"/>
+    <n v="-13.54862242755145"/>
+    <n v="22.740939572448539"/>
+    <n v="137.53123449379649"/>
+    <n v="7.2710755755275806E-3"/>
+    <n v="0.78491713137190566"/>
   </r>
   <r>
     <x v="0"/>
@@ -1539,19 +2263,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="113.58"/>
     <n v="1.1357999999999999E-17"/>
-    <n v="7.3599999999999999E-2"/>
-    <n v="0.18840000000000001"/>
-    <n v="0.39065817409766451"/>
-    <n v="4.3933902266853557E-2"/>
-    <n v="121.93948799999998"/>
-    <n v="1.2193948799999998E-17"/>
-    <n v="101.88374596340148"/>
-    <n v="8.3594879999999847"/>
-    <n v="-5.8481270182992589"/>
-    <n v="2.5113609817007259"/>
-    <n v="417.73819687113439"/>
-    <n v="2.393843817706917E-3"/>
-    <n v="0.83442006507915023"/>
+    <n v="7.6100000000000001E-2"/>
+    <n v="0.20619999999999999"/>
+    <n v="0.36905916585838994"/>
+    <n v="0.33203869158184923"/>
+    <n v="2.3420195999999997E-18"/>
+    <n v="122.223438"/>
+    <n v="1.2222343799999999E-17"/>
+    <n v="111.79"/>
+    <n v="1.1179E-17"/>
+    <n v="-1.7899999999999882E-19"/>
+    <n v="100.50438014335016"/>
+    <n v="8.6434380000000033"/>
+    <n v="-6.5378099283249185"/>
+    <n v="2.1056280716750848"/>
+    <n v="158.16654599456996"/>
+    <n v="6.3224495022754764E-3"/>
+    <n v="0.9026868116032235"/>
   </r>
   <r>
     <x v="4"/>
@@ -1561,19 +2289,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="64.349999999999994"/>
     <n v="6.4349999999999993E-18"/>
-    <n v="0.58009999999999995"/>
-    <n v="0.68779999999999997"/>
-    <n v="0.84341378307647563"/>
-    <n v="9.4851358996357507E-2"/>
-    <n v="101.67943499999998"/>
-    <n v="1.0167943499999998E-17"/>
-    <n v="58.093346573982124"/>
-    <n v="37.329434999999989"/>
-    <n v="-3.1283267130089349"/>
-    <n v="34.201108286991058"/>
-    <n v="386.04844956584407"/>
-    <n v="2.5903484423383002E-3"/>
-    <n v="0.77112070388384324"/>
+    <n v="0.56589999999999996"/>
+    <n v="0.70699999999999996"/>
+    <n v="0.80042432814710041"/>
+    <n v="0.7201334398783692"/>
+    <n v="4.5495449999999992E-18"/>
+    <n v="100.765665"/>
+    <n v="1.0076566499999999E-17"/>
+    <n v="112.06"/>
+    <n v="1.1206E-17"/>
+    <n v="4.771000000000001E-18"/>
+    <n v="56.392954167031817"/>
+    <n v="36.415665000000004"/>
+    <n v="-3.9785229164840885"/>
+    <n v="32.437142083515916"/>
+    <n v="127.83503198272913"/>
+    <n v="7.822581842316139E-3"/>
+    <n v="0.7295790440770421"/>
   </r>
   <r>
     <x v="0"/>
@@ -1583,19 +2315,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="20.82"/>
     <n v="2.0820000000000002E-18"/>
-    <n v="-0.2054"/>
-    <n v="0.70030000000000003"/>
-    <n v="-0.29330287019848633"/>
-    <n v="-3.2985204171528351E-2"/>
-    <n v="16.543572000000001"/>
-    <n v="1.6543572000000001E-18"/>
-    <n v="10.925119378705988"/>
-    <n v="-4.2764279999999992"/>
-    <n v="-4.9474403106470062"/>
-    <n v="-9.2238683106470063"/>
-    <n v="429.47342616348209"/>
-    <n v="2.3284327715758202E-3"/>
-    <n v="0.85786084895570869"/>
+    <n v="1.1900000000000001E-2"/>
+    <n v="0.70799999999999996"/>
+    <n v="1.6807909604519777E-2"/>
+    <n v="1.5121901390337388E-2"/>
+    <n v="1.474056E-18"/>
+    <n v="21.067758000000001"/>
+    <n v="2.1067757999999999E-18"/>
+    <n v="23.2"/>
+    <n v="2.32E-18"/>
+    <n v="2.3799999999999981E-19"/>
+    <n v="12.275219621484583"/>
+    <n v="0.24775800000000103"/>
+    <n v="-4.2723901892577087"/>
+    <n v="-4.0246321892577077"/>
+    <n v="164.29680625550276"/>
+    <n v="6.0865455804714232E-3"/>
+    <n v="0.93767338259042421"/>
   </r>
   <r>
     <x v="0"/>
@@ -1605,19 +2341,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="13.04"/>
     <n v="1.304E-18"/>
-    <n v="0.1043"/>
-    <n v="0.40300000000000002"/>
-    <n v="0.25880893300248137"/>
-    <n v="2.9105973258035669E-2"/>
-    <n v="14.400072"/>
-    <n v="1.4400072E-18"/>
-    <n v="10.04081004081004"/>
-    <n v="1.3600720000000006"/>
-    <n v="-1.4995949795949794"/>
-    <n v="-0.13952297959497884"/>
-    <n v="420.38908083243007"/>
-    <n v="2.3787487487064553E-3"/>
-    <n v="0.83971512974900597"/>
+    <n v="4.82E-2"/>
+    <n v="0.4264"/>
+    <n v="0.11303939962476547"/>
+    <n v="0.10170037170410422"/>
+    <n v="5.5602559999999997E-19"/>
+    <n v="13.668528"/>
+    <n v="1.3668528E-18"/>
+    <n v="18.309999999999999"/>
+    <n v="1.8309999999999997E-18"/>
+    <n v="5.2699999999999978E-19"/>
+    <n v="9.4616166013640974"/>
+    <n v="0.62852800000000109"/>
+    <n v="-1.7891916993179509"/>
+    <n v="-1.1606636993179498"/>
+    <n v="161.43283776556299"/>
+    <n v="6.1945265525978448E-3"/>
+    <n v="0.92132816515863825"/>
   </r>
   <r>
     <x v="0"/>
@@ -1627,63 +2367,75 @@
     <n v="9.9999999999999998E-20"/>
     <n v="11.05"/>
     <n v="1.1050000000000001E-18"/>
-    <n v="-0.36459999999999998"/>
-    <n v="0.628"/>
-    <n v="-0.58057324840764324"/>
-    <n v="-6.5291986819951658E-2"/>
-    <n v="7.0211699999999997"/>
-    <n v="7.0211699999999999E-19"/>
-    <n v="5.545518418147144"/>
-    <n v="-4.028830000000001"/>
-    <n v="-2.7522407909264284"/>
-    <n v="-6.7810707909264298"/>
-    <n v="427.03062864376153"/>
-    <n v="2.3417524011707888E-3"/>
-    <n v="0.85298143098376489"/>
+    <n v="-0.1055"/>
+    <n v="0.57940000000000003"/>
+    <n v="-0.18208491542975491"/>
+    <n v="-0.16381990387765097"/>
+    <n v="6.4023700000000011E-19"/>
+    <n v="9.8842250000000007"/>
+    <n v="9.8842250000000007E-19"/>
+    <n v="11.05"/>
+    <n v="1.1050000000000001E-18"/>
+    <n v="0"/>
+    <n v="6.5582527152946763"/>
+    <n v="-1.165775"/>
+    <n v="-2.2458736423526622"/>
+    <n v="-3.4116486423526622"/>
+    <n v="163.68382270859772"/>
+    <n v="6.1093392337266909E-3"/>
+    <n v="0.93417496792857824"/>
   </r>
   <r>
     <x v="7"/>
     <s v="Gold"/>
     <x v="35"/>
-    <d v="2025-01-20T00:00:00"/>
+    <d v="2025-01-30T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="2742.9"/>
     <n v="2.7429000000000002E-16"/>
-    <n v="0.15060000000000001"/>
-    <n v="0.1454"/>
-    <n v="1.0357634112792298"/>
-    <n v="0.11648323649653942"/>
-    <n v="3155.9807400000004"/>
-    <n v="3.1559807400000002E-16"/>
-    <n v="2757.2376357056696"/>
-    <n v="413.08074000000033"/>
-    <n v="7.1688178528347635"/>
-    <n v="420.2495578528351"/>
+    <n v="8.6599999999999996E-2"/>
+    <n v="0.14630000000000001"/>
+    <n v="0.59193438140806554"/>
+    <n v="0.53255720406754736"/>
+    <n v="4.0128627000000008E-17"/>
+    <n v="2980.43514"/>
+    <n v="2.98043514E-16"/>
+    <n v="0.78559999999999997"/>
+    <n v="7.8559999999999989E-20"/>
+    <n v="-2.7421144000000001E-16"/>
+    <n v="2588.3740681324903"/>
+    <n v="237.53513999999996"/>
+    <n v="-77.262965933754913"/>
+    <n v="160.27217406624504"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="2"/>
     <s v="Walmart"/>
     <x v="36"/>
     <d v="2024-08-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="86.6"/>
     <n v="8.6599999999999986E-18"/>
-    <n v="0.25409999999999999"/>
-    <n v="0.20669999999999999"/>
-    <n v="1.2293178519593615"/>
-    <n v="0.13825060870063546"/>
-    <n v="108.60505999999999"/>
-    <n v="1.0860505999999999E-17"/>
-    <n v="90.909090909090892"/>
-    <n v="22.00506"/>
-    <n v="2.154545454545449"/>
-    <n v="24.159605454545449"/>
-    <n v="396.08995239828965"/>
-    <n v="2.5246790380444857E-3"/>
-    <n v="0.79117831774271297"/>
+    <n v="0.1467"/>
+    <n v="0.21079999999999999"/>
+    <n v="0.6959203036053131"/>
+    <n v="0.62611225632861045"/>
+    <n v="1.8255279999999995E-18"/>
+    <n v="99.304220000000001"/>
+    <n v="9.9304219999999992E-18"/>
+    <n v="104"/>
+    <n v="1.04E-17"/>
+    <n v="1.7400000000000015E-18"/>
+    <n v="81.383328634526833"/>
+    <n v="12.704220000000007"/>
+    <n v="-2.6083356827365805"/>
+    <n v="10.095884317263426"/>
+    <n v="150.17628974898162"/>
+    <n v="6.6588407642211127E-3"/>
+    <n v="0.8570848868164832"/>
   </r>
   <r>
     <x v="8"/>
@@ -1693,19 +2445,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="56"/>
     <n v="5.5999999999999995E-18"/>
-    <n v="-0.30869999999999997"/>
-    <n v="0.41749999999999998"/>
-    <n v="-0.73940119760479039"/>
-    <n v="-8.3153974767317021E-2"/>
-    <n v="38.712800000000001"/>
-    <n v="3.8712800000000001E-18"/>
-    <n v="32.441200324412002"/>
-    <n v="-17.287199999999999"/>
-    <n v="-11.779399837793999"/>
-    <n v="-29.066599837793998"/>
-    <n v="449.3161576906291"/>
-    <n v="2.2256043609465239E-3"/>
-    <n v="0.8974961359757696"/>
+    <n v="4.1000000000000003E-3"/>
+    <n v="0.4047"/>
+    <n v="1.0130961205831481E-2"/>
+    <n v="9.1147203875204513E-3"/>
+    <n v="2.2663199999999999E-18"/>
+    <n v="56.229599999999998"/>
+    <n v="5.6229599999999995E-18"/>
+    <n v="66.66"/>
+    <n v="6.6659999999999998E-18"/>
+    <n v="1.0660000000000003E-18"/>
+    <n v="39.98286448664858"/>
+    <n v="0.22959999999999781"/>
+    <n v="-8.0085677566757099"/>
+    <n v="-7.7789677566757121"/>
+    <n v="168.05114182292075"/>
+    <n v="5.9505695061192881E-3"/>
+    <n v="0.95910009569040855"/>
   </r>
   <r>
     <x v="7"/>
@@ -1713,21 +2469,25 @@
     <x v="38"/>
     <d v="2024-10-15T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
-    <n v="20.399999999999999"/>
-    <n v="2.0399999999999999E-18"/>
-    <n v="6.9999999999999999E-4"/>
-    <n v="0.1174"/>
-    <n v="5.9625212947189091E-3"/>
-    <n v="6.7055253209862312E-4"/>
-    <n v="20.414279999999998"/>
-    <n v="2.0414279999999996E-18"/>
-    <n v="18.268111399659709"/>
-    <n v="1.4279999999999404E-2"/>
-    <n v="-1.0659443001701447"/>
-    <n v="-1.0516643001701453"/>
-    <n v="421.30122215300526"/>
-    <n v="2.3735986211709274E-3"/>
-    <n v="0.84153710587131525"/>
+    <n v="17"/>
+    <n v="1.7E-18"/>
+    <n v="3.1099999999999999E-2"/>
+    <n v="0.1285"/>
+    <n v="0.24202334630350195"/>
+    <n v="0.21774588649482446"/>
+    <n v="2.1845000000000003E-19"/>
+    <n v="17.528699999999997"/>
+    <n v="1.7528699999999997E-18"/>
+    <n v="20.431999999999999"/>
+    <n v="2.0431999999999997E-18"/>
+    <n v="3.4319999999999965E-19"/>
+    <n v="15.491160925824675"/>
+    <n v="0.52869999999999706"/>
+    <n v="-0.75441953708766274"/>
+    <n v="-0.22571953708766568"/>
+    <n v="160.4978936033327"/>
+    <n v="6.2306113653521197E-3"/>
+    <n v="0.91599225951864482"/>
   </r>
   <r>
     <x v="5"/>
@@ -1737,19 +2497,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="47.42"/>
     <n v="4.7419999999999999E-18"/>
-    <n v="3.3999999999999998E-3"/>
-    <n v="0.42030000000000001"/>
-    <n v="8.0894599095883892E-3"/>
-    <n v="9.0975068390770691E-4"/>
-    <n v="47.581228000000003"/>
-    <n v="4.7581228000000004E-18"/>
-    <n v="33.467428894064504"/>
-    <n v="0.16122800000000126"/>
-    <n v="-6.9762855529677488"/>
-    <n v="-6.8150575529677475"/>
-    <n v="427.06461540580284"/>
-    <n v="2.3415660392509595E-3"/>
-    <n v="0.85304931856600363"/>
+    <n v="8.5199999999999998E-2"/>
+    <n v="0.36359999999999998"/>
+    <n v="0.23432343234323433"/>
+    <n v="0.21081835401987956"/>
+    <n v="1.7241911999999999E-18"/>
+    <n v="51.460183999999998"/>
+    <n v="5.1460184E-18"/>
+    <n v="47.29"/>
+    <n v="4.729E-18"/>
+    <n v="-1.2999999999999854E-20"/>
+    <n v="37.093241551939926"/>
+    <n v="4.0401839999999964"/>
+    <n v="-5.163379224030038"/>
+    <n v="-1.1231952240300416"/>
+    <n v="161.39536929027508"/>
+    <n v="6.1959646326745959E-3"/>
+    <n v="0.92111432538436366"/>
   </r>
   <r>
     <x v="5"/>
@@ -1759,19 +2523,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="41.8"/>
     <n v="4.1799999999999993E-18"/>
-    <n v="-0.18279999999999999"/>
-    <n v="0.40949999999999998"/>
-    <n v="-0.44639804639804642"/>
-    <n v="-5.0202477364938304E-2"/>
-    <n v="34.15896"/>
-    <n v="3.4158960000000001E-18"/>
-    <n v="26.251334547509888"/>
-    <n v="-7.6410399999999967"/>
-    <n v="-7.7743327262450546"/>
-    <n v="-15.415372726245051"/>
-    <n v="435.66493057908013"/>
-    <n v="2.2953419699648834E-3"/>
-    <n v="0.87022820141736279"/>
+    <n v="8.3500000000000005E-2"/>
+    <n v="0.39029999999999998"/>
+    <n v="0.21393799641301564"/>
+    <n v="0.19247778941731217"/>
+    <n v="1.6314539999999997E-18"/>
+    <n v="45.290299999999995"/>
+    <n v="4.5290299999999995E-18"/>
+    <n v="38.39"/>
+    <n v="3.8390000000000001E-18"/>
+    <n v="-3.4099999999999919E-19"/>
+    <n v="31.986531986531986"/>
+    <n v="3.4902999999999977"/>
+    <n v="-4.9067340067340055"/>
+    <n v="-1.4164340067340078"/>
+    <n v="161.68860807297904"/>
+    <n v="6.1847276188353641E-3"/>
+    <n v="0.92278789535538974"/>
   </r>
   <r>
     <x v="7"/>
@@ -1781,19 +2549,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="153.7552"/>
     <n v="1.5375519999999999E-17"/>
-    <n v="8.4900000000000003E-2"/>
-    <n v="0.105"/>
-    <n v="0.80857142857142861"/>
-    <n v="9.0932944640616645E-2"/>
-    <n v="166.80901648"/>
-    <n v="1.6680901648000001E-17"/>
-    <n v="150.72561513577099"/>
-    <n v="13.053816479999995"/>
-    <n v="-1.5147924321145041"/>
-    <n v="11.539024047885491"/>
-    <n v="408.71053380494959"/>
-    <n v="2.4467194194638339E-3"/>
-    <n v="0.81638756707054139"/>
+    <n v="2.2700000000000001E-2"/>
+    <n v="8.8400000000000006E-2"/>
+    <n v="0.25678733031674206"/>
+    <n v="0.23102888929707052"/>
+    <n v="1.359195968E-18"/>
+    <n v="157.24544304"/>
+    <n v="1.5724544303999999E-17"/>
+    <n v="151.47"/>
+    <n v="1.5146999999999998E-17"/>
+    <n v="-2.28520000000001E-19"/>
+    <n v="144.27625035188137"/>
+    <n v="3.4902430399999957"/>
+    <n v="-4.7394748240593145"/>
+    <n v="-1.2492317840593188"/>
+    <n v="161.52140585030435"/>
+    <n v="6.1911298674974706E-3"/>
+    <n v="0.92183364020408631"/>
   </r>
   <r>
     <x v="9"/>
@@ -1803,19 +2575,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="133.53"/>
     <n v="1.3353E-17"/>
-    <n v="4.6300000000000001E-2"/>
-    <n v="0.28910000000000002"/>
-    <n v="0.16015219647180906"/>
-    <n v="1.8010914436556398E-2"/>
-    <n v="139.71243899999999"/>
-    <n v="1.39712439E-17"/>
-    <n v="107.4428709365948"/>
-    <n v="6.182438999999988"/>
-    <n v="-13.0435645317026"/>
-    <n v="-6.8611255317026121"/>
-    <n v="427.11068338453771"/>
-    <n v="2.3413134789224571E-3"/>
-    <n v="0.85314133803202785"/>
+    <n v="4.0899999999999999E-2"/>
+    <n v="0.25"/>
+    <n v="0.1636"/>
+    <n v="0.14718921779505134"/>
+    <n v="3.3382499999999999E-18"/>
+    <n v="138.991377"/>
+    <n v="1.38991377E-17"/>
+    <n v="150.19999999999999"/>
+    <n v="1.5019999999999999E-17"/>
+    <n v="1.6669999999999989E-18"/>
+    <n v="110.4375155074022"/>
+    <n v="5.4613769999999988"/>
+    <n v="-11.546242246298903"/>
+    <n v="-6.0848652462989037"/>
+    <n v="166.35703931254395"/>
+    <n v="6.0111673310153475E-3"/>
+    <n v="0.94943152776408135"/>
   </r>
   <r>
     <x v="0"/>
@@ -1825,19 +2601,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="26.63"/>
     <n v="2.663E-18"/>
-    <n v="7.4700000000000003E-2"/>
-    <n v="0.27450000000000002"/>
-    <n v="0.27213114754098361"/>
-    <n v="3.0604206010657629E-2"/>
-    <n v="28.619260999999998"/>
-    <n v="2.8619260999999998E-18"/>
-    <n v="22.195365894315717"/>
-    <n v="1.9892609999999991"/>
-    <n v="-2.2173170528421409"/>
-    <n v="-0.22805605284214181"/>
-    <n v="420.47761390567723"/>
-    <n v="2.3782478946056873E-3"/>
-    <n v="0.83989197202317167"/>
+    <n v="-0.1193"/>
+    <n v="0.60340000000000005"/>
+    <n v="-0.19771295989393436"/>
+    <n v="-0.17788029287733836"/>
+    <n v="1.6068542000000001E-18"/>
+    <n v="23.453040999999999"/>
+    <n v="2.3453040999999998E-18"/>
+    <n v="15.66"/>
+    <n v="1.566E-18"/>
+    <n v="-1.097E-18"/>
+    <n v="15.458292215707898"/>
+    <n v="-3.1769590000000001"/>
+    <n v="-5.5858538921460505"/>
+    <n v="-8.7628128921460515"/>
+    <n v="169.0349869583911"/>
+    <n v="5.9159350261975968E-3"/>
+    <n v="0.96471508856304522"/>
   </r>
   <r>
     <x v="6"/>
@@ -1847,172 +2627,43 @@
     <n v="9.9999999999999998E-20"/>
     <n v="323.75"/>
     <n v="3.2375000000000002E-17"/>
-    <n v="8.5699999999999998E-2"/>
-    <n v="0.31409999999999999"/>
-    <n v="0.2728430436166826"/>
-    <n v="3.0684266725337819E-2"/>
-    <n v="351.49537500000002"/>
-    <n v="3.5149537499999999E-17"/>
-    <n v="263.55421686746985"/>
-    <n v="27.745375000000024"/>
-    <n v="-30.097891566265076"/>
-    <n v="-2.3525165662650522"/>
-    <n v="422.60207441910018"/>
-    <n v="2.3662922179797123E-3"/>
-    <n v="0.84413552095680033"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <m/>
-    <x v="45"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="10"/>
-    <m/>
-    <x v="45"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="10"/>
-    <m/>
-    <x v="45"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="10"/>
-    <m/>
-    <x v="45"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="10"/>
-    <m/>
-    <x v="45"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <x v="10"/>
-    <m/>
-    <x v="45"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <n v="0.16109999999999999"/>
+    <n v="0.32779999999999998"/>
+    <n v="0.49145820622330688"/>
+    <n v="0.44215983467584091"/>
+    <n v="1.0612525E-17"/>
+    <n v="375.90612500000003"/>
+    <n v="3.7590612500000005E-17"/>
+    <n v="320.56"/>
+    <n v="3.2055999999999996E-17"/>
+    <n v="-3.1900000000000578E-19"/>
+    <n v="277.49207165509563"/>
+    <n v="52.156125000000031"/>
+    <n v="-23.128964172452186"/>
+    <n v="29.027160827547846"/>
+    <n v="131.2450132386972"/>
+    <n v="7.619337110974918E-3"/>
+    <n v="0.74904046108037126"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EC9E47C-0324-45D9-96E2-71F0F41D16E2}" name="PivotTable1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B3:F17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18AC1D4E-8AFF-4F3A-87D7-1A82850D7D48}" name="PivotTable4" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:H14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="29">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="12">
+      <items count="11">
         <item sd="0" x="5"/>
         <item sd="0" x="8"/>
-        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
         <item sd="0" x="0"/>
-        <item x="7"/>
+        <item sd="0" x="7"/>
         <item sd="0" x="6"/>
         <item sd="0" x="9"/>
         <item sd="0" x="4"/>
-        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
         <item sd="0" x="1"/>
-        <item h="1" sd="0" x="10"/>
         <item t="default" sd="0"/>
       </items>
       <autoSortScope>
@@ -2027,53 +2678,52 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="47">
+      <items count="46">
         <item x="18"/>
-        <item x="8"/>
+        <item x="3"/>
         <item x="16"/>
         <item x="29"/>
         <item x="0"/>
         <item x="37"/>
         <item x="27"/>
         <item x="2"/>
-        <item x="7"/>
+        <item x="9"/>
         <item x="1"/>
         <item x="34"/>
         <item x="40"/>
         <item x="30"/>
-        <item x="10"/>
+        <item x="11"/>
         <item x="17"/>
         <item x="35"/>
-        <item x="25"/>
+        <item x="21"/>
         <item x="44"/>
-        <item x="3"/>
+        <item x="4"/>
         <item x="15"/>
         <item x="32"/>
-        <item x="11"/>
+        <item x="12"/>
         <item x="20"/>
-        <item x="22"/>
+        <item x="23"/>
         <item x="26"/>
         <item x="42"/>
-        <item x="4"/>
+        <item x="5"/>
         <item x="19"/>
-        <item x="13"/>
+        <item x="10"/>
         <item x="28"/>
         <item x="43"/>
-        <item x="12"/>
+        <item x="13"/>
         <item x="31"/>
-        <item x="24"/>
+        <item x="25"/>
         <item x="33"/>
         <item x="14"/>
         <item x="41"/>
         <item x="38"/>
-        <item x="23"/>
+        <item x="24"/>
+        <item x="8"/>
+        <item x="36"/>
         <item x="6"/>
-        <item x="36"/>
-        <item x="9"/>
-        <item x="21"/>
+        <item x="22"/>
         <item x="39"/>
-        <item x="45"/>
-        <item x="5"/>
+        <item x="7"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -2094,8 +2744,12 @@
     <pivotField showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
     <pivotField numFmtId="44" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
     <pivotField numFmtId="44" showAll="0"/>
     <pivotField numFmtId="44" showAll="0"/>
     <pivotField numFmtId="44" showAll="0"/>
@@ -2105,12 +2759,15 @@
     <pivotField numFmtId="9" showAll="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="14">
+  <rowItems count="11">
     <i>
       <x v="8"/>
     </i>
@@ -2118,10 +2775,10 @@
       <x v="9"/>
     </i>
     <i>
-      <x v="7"/>
+      <x v="3"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="7"/>
     </i>
     <i>
       <x v="2"/>
@@ -2134,15 +2791,6 @@
     </i>
     <i>
       <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="15"/>
-    </i>
-    <i r="1">
-      <x v="36"/>
-    </i>
-    <i r="1">
-      <x v="37"/>
     </i>
     <i>
       <x v="6"/>
@@ -2157,7 +2805,7 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="4">
+  <colItems count="7">
     <i>
       <x/>
     </i>
@@ -2170,8 +2818,17 @@
     <i i="3">
       <x v="3"/>
     </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+    <i i="6">
+      <x v="6"/>
+    </i>
   </colItems>
-  <dataFields count="4">
+  <dataFields count="7">
     <dataField name="Initial Volume $" fld="6" baseField="0" baseItem="0" numFmtId="44"/>
     <dataField name="$%" fld="6" baseField="0" baseItem="7" numFmtId="9">
       <extLst>
@@ -2180,11 +2837,14 @@
         </ext>
       </extLst>
     </dataField>
-    <dataField name="Target Return %" fld="20" baseField="0" baseItem="0" numFmtId="10"/>
-    <dataField name="Target P&amp;L" fld="21" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Volatility " fld="28" baseField="0" baseItem="8" numFmtId="10"/>
+    <dataField name="Target Return %" fld="24" baseField="0" baseItem="0" numFmtId="10"/>
+    <dataField name="Target P&amp;L" fld="25" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Actual Return %" fld="27" baseField="0" baseItem="8" numFmtId="10"/>
+    <dataField name="Actual P&amp;L " fld="26" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
-  <formats count="3">
-    <format dxfId="2">
+  <formats count="8">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2194,7 +2854,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2204,11 +2864,68 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="34">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="36">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
             <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="5">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="5">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="5">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
           </reference>
         </references>
       </pivotArea>
@@ -2222,8 +2939,1106 @@
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
       <xpdl:pivotTableDefinition16/>
     </ext>
+    <ext xmlns:xxpvi="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotVersionInfo" uri="{9F748A41-CAEA-4470-BF7A-CE61E8FFA7F9}">
+      <xxpvi:pivotVersionInfo>
+        <xxpvi:lastUpdateFeature>RichData</xxpvi:lastUpdateFeature>
+      </xxpvi:pivotVersionInfo>
+    </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="42">
+  <a r="1">
+    <v t="i">0</v>
+  </a>
+  <a r="1">
+    <v>200.95</v>
+  </a>
+  <a r="1">
+    <v>162.5</v>
+  </a>
+  <a r="1">
+    <v>148.29</v>
+  </a>
+  <a r="1">
+    <v>45.97</v>
+  </a>
+  <a r="1">
+    <v>151.47</v>
+  </a>
+  <a r="1">
+    <v>137.93</v>
+  </a>
+  <a r="1">
+    <v>175.22</v>
+  </a>
+  <a r="1">
+    <v>5.64</v>
+  </a>
+  <a r="1">
+    <v>0.78559999999999997</v>
+  </a>
+  <a r="1">
+    <v>37.11</v>
+  </a>
+  <a r="1">
+    <v>23.2</v>
+  </a>
+  <a r="1">
+    <v>23.59</v>
+  </a>
+  <a r="1">
+    <v>174.06</v>
+  </a>
+  <a r="1">
+    <v>66.66</v>
+  </a>
+  <a r="1">
+    <v>53.34</v>
+  </a>
+  <a r="1">
+    <v>11.05</v>
+  </a>
+  <a r="1">
+    <v>139.22999999999999</v>
+  </a>
+  <a r="1">
+    <v>414.77</v>
+  </a>
+  <a r="1">
+    <v>69.06</v>
+  </a>
+  <a r="1">
+    <v>355.23</v>
+  </a>
+  <a r="1">
+    <v>42.65</v>
+  </a>
+  <a r="1">
+    <v>568.5</v>
+  </a>
+  <a r="1">
+    <v>20.431999999999999</v>
+  </a>
+  <a r="1">
+    <v>38.39</v>
+  </a>
+  <a r="1">
+    <v>18.309999999999999</v>
+  </a>
+  <a r="1">
+    <v>112.06</v>
+  </a>
+  <a r="1">
+    <v>34.020000000000003</v>
+  </a>
+  <a r="1">
+    <v>49.3</v>
+  </a>
+  <a r="1">
+    <v>150.19999999999999</v>
+  </a>
+  <a r="1">
+    <v>47.29</v>
+  </a>
+  <a r="1">
+    <v>104</v>
+  </a>
+  <a r="1">
+    <v>717.5</v>
+  </a>
+  <a r="1">
+    <v>185.27</v>
+  </a>
+  <a r="1">
+    <v>244.87</v>
+  </a>
+  <a r="1">
+    <v>320.56</v>
+  </a>
+  <a r="1">
+    <v>126.91</v>
+  </a>
+  <a r="1">
+    <v>139.5</v>
+  </a>
+  <a r="1">
+    <v>16.874600000000001</v>
+  </a>
+  <a r="1">
+    <v>111.79</v>
+  </a>
+  <a r="1">
+    <v>15.66</v>
+  </a>
+  <a r="46">
+    <v t="r">0</v>
+    <v t="e">#NULL!</v>
+    <v t="r">1</v>
+    <v t="e">#NULL!</v>
+    <v t="r">2</v>
+    <v t="r">3</v>
+    <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">6</v>
+    <v t="e">#NULL!</v>
+    <v t="r">7</v>
+    <v t="r">8</v>
+    <v t="r">9</v>
+    <v t="r">10</v>
+    <v t="r">11</v>
+    <v t="r">12</v>
+    <v t="r">13</v>
+    <v t="r">14</v>
+    <v t="r">15</v>
+    <v t="r">16</v>
+    <v t="r">17</v>
+    <v t="r">18</v>
+    <v t="r">19</v>
+    <v t="r">20</v>
+    <v t="r">21</v>
+    <v t="r">22</v>
+    <v t="r">82</v>
+    <v t="r">24</v>
+    <v t="r">25</v>
+    <v t="r">26</v>
+    <v t="r">27</v>
+    <v t="r">28</v>
+    <v t="r">29</v>
+    <v t="r">30</v>
+    <v t="r">31</v>
+    <v t="r">32</v>
+    <v t="r">33</v>
+    <v t="r">34</v>
+    <v t="r">35</v>
+    <v t="r">36</v>
+    <v t="r">37</v>
+    <v t="r">38</v>
+    <v t="r">39</v>
+    <v t="r">40</v>
+    <v t="r">41</v>
+    <v t="i">2</v>
+  </a>
+</arrayData>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="85">
+  <rv s="0">
+    <fb>23.59</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>16.874600000000001</fb>
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <fb>17.03</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>53.34</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>37.11</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>45.97</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>49.3</fb>
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <fb>69.06</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>42.65</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>137.93</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>139.5</fb>
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <fb>200.95</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>126.91</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>34.020000000000003</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>162.5</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>244.87</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>414.77</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>568.5</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>185.27</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>148.29</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>5.64</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>355.23</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>175.22</fb>
+    <v>0</v>
+  </rv>
+  <rv s="1">
+    <v>2</v>
+    <v>18</v>
+  </rv>
+  <rv s="0">
+    <fb>717.5</fb>
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <fb>139.22999999999999</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>174.06</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>111.79</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>112.06</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>23.2</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18.309999999999999</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>11.05</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>0.78559999999999997</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>104</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>66.66</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>20.431999999999999</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>47.29</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>38.39</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>151.47</fb>
+    <v>3</v>
+  </rv>
+  <rv s="0">
+    <fb>150.19999999999999</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>15.66</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>320.56</fb>
+    <v>0</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>TSM</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345373213,0</v>
+    <v>0</v>
+    <v>a24kjc</v>
+    <v>XNYS:TSM</v>
+    <v>1</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>FSLR</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195344434400,0</v>
+    <v>0</v>
+    <v>a1tdvh</v>
+    <v>XNAS:FSLR</v>
+    <v>2</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>YUM</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343637206,0</v>
+    <v>0</v>
+    <v>a26em7</v>
+    <v>XNYS:YUM</v>
+    <v>3</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>VWO.US</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195344265467,0</v>
+    <v>0</v>
+    <v>a25nhw</v>
+    <v>ARCX:VWO</v>
+    <v>4</v>
+  </rv>
+  <rv s="2">
+    <v>5</v>
+    <v>USDJPY=X</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195344297942,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>5</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>KMB</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195344463565,0</v>
+    <v>0</v>
+    <v>a1wjz2</v>
+    <v>XNYS:KMB</v>
+    <v>6</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>QCOM</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345514549,0</v>
+    <v>0</v>
+    <v>a21k2w</v>
+    <v>XNAS:QCOM</v>
+    <v>7</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>MAXN</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195344407151,0</v>
+    <v>0</v>
+    <v>bvhkk2</v>
+    <v>XNAS:MAXN</v>
+    <v>8</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>GC=F</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195344336785,0</v>
+    <v>0</v>
+    <v>a2losm</v>
+    <v>OTCM:JETMF</v>
+    <v>9</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>YPF</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195435611501,0</v>
+    <v>0</v>
+    <v>a26e7w</v>
+    <v>XNYS:YPF</v>
+    <v>10</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>JKS</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195344370947,0</v>
+    <v>0</v>
+    <v>a1w7f2</v>
+    <v>XNYS:JKS</v>
+    <v>11</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>APA</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195344530952,0</v>
+    <v>0</v>
+    <v>a1nkur</v>
+    <v>XNAS:APA</v>
+    <v>12</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>AMAT</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343841890,0</v>
+    <v>0</v>
+    <v>a1nda2</v>
+    <v>XNAS:AMAT</v>
+    <v>13</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>APTV</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343547070,0</v>
+    <v>0</v>
+    <v>awagjc</v>
+    <v>XNYS:APTV</v>
+    <v>14</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>MO</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345407070,0</v>
+    <v>0</v>
+    <v>a1xtpr</v>
+    <v>XNYS:MO</v>
+    <v>15</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>CSIQ</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343580784,0</v>
+    <v>0</v>
+    <v>a1qepr</v>
+    <v>XNAS:CSIQ</v>
+    <v>16</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>NVDA</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343604968,0</v>
+    <v>0</v>
+    <v>a1yv52</v>
+    <v>XNAS:NVDA</v>
+    <v>17</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>MSFT</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343657119,0</v>
+    <v>0</v>
+    <v>a1xzim</v>
+    <v>XNAS:MSFT</v>
+    <v>18</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>NEE</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343682753,0</v>
+    <v>0</v>
+    <v>a1ye2w</v>
+    <v>XNYS:NEE</v>
+    <v>19</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>V</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343744492,0</v>
+    <v>0</v>
+    <v>a256cw</v>
+    <v>XNYS:V</v>
+    <v>20</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>EXC</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343720482,0</v>
+    <v>0</v>
+    <v>a1shjc</v>
+    <v>XNAS:EXC</v>
+    <v>21</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>MA</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345356613,0</v>
+    <v>0</v>
+    <v>a1x8w7</v>
+    <v>XNYS:MA</v>
+    <v>22</v>
+  </rv>
+  <rv s="2">
+    <v>6</v>
+    <v>USDMXN=X</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343813914,0</v>
+    <v>0</v>
+    <v>avyqcw</v>
+    <v>USDMXN</v>
+    <v>23</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>DAR</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345450404,0</v>
+    <v>0</v>
+    <v>a1qqk2</v>
+    <v>XNYS:DAR</v>
+    <v>24</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>SWI</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343680192,0</v>
+    <v>0</v>
+    <v>bn8mkr</v>
+    <v>XNYS:SWI</v>
+    <v>25</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>PLTR</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345479208,0</v>
+    <v>0</v>
+    <v>bvsk7w</v>
+    <v>XNAS:PLTR</v>
+    <v>26</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>AGIO</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345541479,0</v>
+    <v>0</v>
+    <v>a1n2qh</v>
+    <v>XNAS:AGIO</v>
+    <v>27</v>
+  </rv>
+  <rv s="2">
+    <v>7</v>
+    <v>VBTC.DE</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345591773,0</v>
+    <v>0</v>
+    <v>bwxxim</v>
+    <v>XFRA:VBTC</v>
+    <v>28</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>MMM</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345619194,0</v>
+    <v>0</v>
+    <v>a1xroc</v>
+    <v>XNYS:MMM</v>
+    <v>29</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>YUMC</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195345649314,0</v>
+    <v>0</v>
+    <v>a26erw</v>
+    <v>XNYS:YUMC</v>
+    <v>30</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>WMT</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343638409,0</v>
+    <v>0</v>
+    <v>a25ya2</v>
+    <v>XNYS:WMT</v>
+    <v>31</v>
+  </rv>
+  <rv s="2">
+    <v>7</v>
+    <v>ASML</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343716563,0</v>
+    <v>0</v>
+    <v>alnz5r</v>
+    <v>XAMS:ASML</v>
+    <v>32</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>GOOGL</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343767202,0</v>
+    <v>0</v>
+    <v>a1u3rw</v>
+    <v>XNAS:GOOGL</v>
+    <v>33</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>AAPL</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343793213,0</v>
+    <v>0</v>
+    <v>a1mou2</v>
+    <v>XNAS:AAPL</v>
+    <v>34</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>HCA</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343924290,0</v>
+    <v>0</v>
+    <v>a1uhnm</v>
+    <v>XNYS:HCA</v>
+    <v>35</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>INGR</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343830973,0</v>
+    <v>0</v>
+    <v>a1vkp2</v>
+    <v>XNYS:INGR</v>
+    <v>36</v>
+  </rv>
+  <rv s="2">
+    <v>7</v>
+    <v>PEP</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343863163,0</v>
+    <v>0</v>
+    <v>afiar7</v>
+    <v>XFRA:PEP</v>
+    <v>37</v>
+  </rv>
+  <rv s="2">
+    <v>7</v>
+    <v>BATT.NL</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343888223,0</v>
+    <v>0</v>
+    <v>aytcmw</v>
+    <v>XAMS:BATT</v>
+    <v>38</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>DUK</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343286502,0</v>
+    <v>0</v>
+    <v>a1rdzr</v>
+    <v>XNYS:DUK</v>
+    <v>39</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+    <v>PCG</v>
+    <v>Daily</v>
+    <v>45707</v>
+    <v>45707</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638755200000000000,638756195343315233,0</v>
+    <v>0</v>
+    <v>a1zkar</v>
+    <v>XNYS:PCG</v>
+    <v>40</v>
+  </rv>
+  <rv s="3">
+    <v>2</v>
+    <v>1</v>
+  </rv>
+  <rv s="4">
+    <v>41</v>
+  </rv>
+  <rv s="5">
+    <v>{1E74FF3F-FD41-47C6-9554-6AF9D4A04843}</v>
+    <v>0</v>
+    <v>8</v>
+    <v>83</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+  <s t="_formattednumber">
+    <k n="_Format" t="spb"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+  <s t="_stockhistorycache">
+    <k n="_Format" t="spb"/>
+    <k n="Symbol" t="s"/>
+    <k n="Interval" t="s"/>
+    <k n="StartDate" t="i"/>
+    <k n="EndDate" t="i"/>
+    <k n="f1904" t="b"/>
+    <k n="fdcompat" t="b"/>
+    <k n="etag" t="s"/>
+    <k n="Date" t="a"/>
+    <k n="EntityId" t="s"/>
+    <k n="Instrument" t="s"/>
+    <k n="Close" t="a"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="propagated" t="b"/>
+  </s>
+  <s t="_array">
+    <k n="array" t="a"/>
+  </s>
+  <s t="_datasourcecontainer">
+    <k n="%XLUID" t="s"/>
+    <k n="_CRID" t="i"/>
+    <k n="_Display" t="spb"/>
+    <k n="Close Price" t="r"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
+<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
+  <spbArrays count="1">
+    <a count="4">
+      <v t="s">Close Price</v>
+      <v t="s">_CRID</v>
+      <v t="s">%XLUID</v>
+      <v t="s">_Display</v>
+    </a>
+  </spbArrays>
+  <spbData count="9">
+    <spb s="0">
+      <v>1</v>
+    </spb>
+    <spb s="0">
+      <v>2</v>
+    </spb>
+    <spb s="0">
+      <v>3</v>
+    </spb>
+    <spb s="0">
+      <v>4</v>
+    </spb>
+    <spb s="1">
+      <v>5</v>
+      <v>1</v>
+    </spb>
+    <spb s="1">
+      <v>5</v>
+      <v>4</v>
+    </spb>
+    <spb s="1">
+      <v>5</v>
+      <v>3</v>
+    </spb>
+    <spb s="1">
+      <v>5</v>
+      <v>2</v>
+    </spb>
+    <spb s="2">
+      <v>0</v>
+    </spb>
+  </spbData>
+</supportingPropertyBags>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="3">
+  <s>
+    <k n="_Self" t="i"/>
+  </s>
+  <s>
+    <k n="Date" t="i"/>
+    <k n="Close" t="i"/>
+  </s>
+  <s>
+    <k n="^Order" t="spba"/>
+  </s>
+</spbStructures>
+</file>
+
+<file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
+<richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <dxfs count="2">
+    <x:dxf>
+      <x:numFmt numFmtId="0" formatCode="General"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </x:dxf>
+  </dxfs>
+  <richProperties>
+    <rPr n="NumberFormat" t="s"/>
+  </richProperties>
+  <richStyles>
+    <rSty dxfid="0">
+      <rpv i="0">_([$$-en-US]* #,##0.00_);_([$$-en-US]* (#,##0.00);_([$$-en-US]* "-"??_);_(@_)</rpv>
+    </rSty>
+    <rSty dxfid="0">
+      <rpv i="0">_([$€-x-euro2] * #,##0.00_);_([$€-x-euro2] * (#,##0.00);_([$€-x-euro2] * "-"??_);_(@_)</rpv>
+    </rSty>
+    <rSty dxfid="0">
+      <rpv i="0">_-[$$-es-MX]* #,##0.00_-;-[$$-es-MX]* #,##0.00_-;_-[$$-es-MX]* "-"??_-;_-@_-</rpv>
+    </rSty>
+    <rSty dxfid="0">
+      <rpv i="0">_-[$¥-ja-JP]* #,##0.00_-;-[$¥-ja-JP]* #,##0.00_-;_-[$¥-ja-JP]* "-"??_-;_-@_-</rpv>
+    </rSty>
+    <rSty dxfid="1"/>
+  </richStyles>
+</richStyleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2489,7 +4304,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T46"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -2501,19 +4317,19 @@
     <col min="7" max="7" width="11.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="13.7109375" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="10"/>
-    <col min="11" max="11" width="7.5703125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.5703125" style="10" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="11.42578125" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>35</v>
       </c>
@@ -2548,34 +4364,46 @@
         <v>63</v>
       </c>
       <c r="L1" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="O1" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="R1" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="U1" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="V1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="W1" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="X1" s="15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -2612,46 +4440,62 @@
       </c>
       <c r="K2" s="9">
         <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-1.0406726510486033E-2</v>
-      </c>
-      <c r="L2" s="12">
+        <v>-0.13020842959321346</v>
+      </c>
+      <c r="L2" s="9">
+        <f>I2*G2</f>
+        <v>30.189947772600004</v>
+      </c>
+      <c r="M2" s="12">
         <f>IF((1+H2)*F2&lt;0,0,(1+H2)*F2)</f>
         <v>19.876428000000001</v>
       </c>
-      <c r="M2" s="12">
-        <f t="shared" ref="M2:M46" si="3">L2*E2</f>
+      <c r="N2" s="12">
+        <f t="shared" ref="N2:N46" si="3">M2*E2</f>
         <v>45.622365188400003</v>
       </c>
-      <c r="N2" s="12">
-        <f t="shared" ref="N2:N41" si="4">F2/(1+I2-H2)</f>
+      <c r="O2" s="12" cm="1" vm="1">
+        <f t="array" aca="1" ref="O2" ca="1">_xlfn.STOCKHISTORY(C2,TODAY(),TODAY(),0,0,1)</f>
+        <v>23.59</v>
+      </c>
+      <c r="P2" s="12">
+        <f ca="1">IFERROR(O2*E2,G2)</f>
+        <v>54.146127</v>
+      </c>
+      <c r="Q2" s="12">
+        <f ca="1">P2-G2</f>
+        <v>4.1544929999999951</v>
+      </c>
+      <c r="R2" s="12">
+        <f t="shared" ref="R2:R41" si="4">F2/(1+I2-H2)</f>
         <v>12.877668065984748</v>
       </c>
-      <c r="O2" s="12">
-        <f t="shared" ref="O2:O41" si="5">L2-F2</f>
+      <c r="S2" s="12">
+        <f t="shared" ref="S2:S41" si="5">M2-F2</f>
         <v>-1.9035720000000005</v>
       </c>
-      <c r="P2" s="12">
-        <f t="shared" ref="P2:P41" si="6">0.5*(N2-F2)</f>
+      <c r="T2" s="12">
+        <f t="shared" ref="T2:T41" si="6">0.5*(R2-F2)</f>
         <v>-4.4511659670076265</v>
       </c>
-      <c r="Q2" s="14">
-        <f t="shared" ref="Q2:Q41" si="7">O2+P2</f>
+      <c r="U2" s="14">
+        <f t="shared" ref="U2:U41" si="7">S2+T2</f>
         <v>-6.3547379670076269</v>
       </c>
-      <c r="R2" s="12">
-        <f t="shared" ref="R2:R46" si="8">MAX($Q$2:$Q$280)-Q2</f>
+      <c r="V2" s="12">
+        <f t="shared" ref="V2:V46" si="8">MAX($U$2:$U$280)-U2</f>
         <v>166.62691203325267</v>
       </c>
-      <c r="S2" s="9">
-        <f t="shared" ref="S2:S46" si="9">IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+      <c r="W2" s="9">
+        <f t="shared" ref="W2:W46" si="9">IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V2)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
         <v>6.0014315082574203E-3</v>
       </c>
-      <c r="T2" s="9">
-        <f t="shared" ref="T2:T41" si="10">R2/MAX($R$2:$R$28)</f>
+      <c r="X2" s="9">
+        <f t="shared" ref="X2:X41" si="10">V2/MAX($V$2:$V$28)</f>
         <v>0.95097174313809352</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>145</v>
       </c>
@@ -2668,66 +4512,80 @@
         <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>20.928000000000001</v>
+        <f>45.12/2</f>
+        <v>22.56</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>41.856000000000002</v>
+        <v>45.12</v>
       </c>
       <c r="H3" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C3,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="I3" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C3,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="J3" s="9">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.21212121212121213</v>
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>7.1906431804147786E-3</v>
-      </c>
-      <c r="L3" s="12">
-        <f t="shared" ref="L3:L41" si="11">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
-        <v>21.4512</v>
+        <v>0.19084324749302797</v>
+      </c>
+      <c r="L3" s="9">
+        <f t="shared" ref="L3:L47" si="11">I3*G3</f>
+        <v>7.4447999999999999</v>
       </c>
       <c r="M3" s="12">
+        <f t="shared" ref="M3:M41" si="12">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
+        <v>23.349599999999995</v>
+      </c>
+      <c r="N3" s="12">
         <f t="shared" si="3"/>
-        <v>42.9024</v>
-      </c>
-      <c r="N3" s="12">
+        <v>46.69919999999999</v>
+      </c>
+      <c r="O3" s="12">
+        <v>22.65</v>
+      </c>
+      <c r="P3" s="12">
+        <f>IFERROR(O3*E3,G3)</f>
+        <v>45.3</v>
+      </c>
+      <c r="Q3" s="12">
+        <f>P3-G3</f>
+        <v>0.17999999999999972</v>
+      </c>
+      <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>17.08408163265306</v>
-      </c>
-      <c r="O3" s="12">
+        <v>19.9646017699115</v>
+      </c>
+      <c r="S3" s="12">
         <f t="shared" si="5"/>
-        <v>0.52319999999999922</v>
-      </c>
-      <c r="P3" s="12">
+        <v>0.78959999999999653</v>
+      </c>
+      <c r="T3" s="12">
         <f t="shared" si="6"/>
-        <v>-1.9219591836734704</v>
-      </c>
-      <c r="Q3" s="14">
+        <v>-1.2976991150442494</v>
+      </c>
+      <c r="U3" s="14">
         <f t="shared" si="7"/>
-        <v>-1.3987591836734712</v>
-      </c>
-      <c r="R3" s="12">
+        <v>-0.50809911504425287</v>
+      </c>
+      <c r="V3" s="12">
         <f t="shared" si="8"/>
-        <v>161.67093324991851</v>
-      </c>
-      <c r="S3" s="9">
+        <v>160.78027318128929</v>
+      </c>
+      <c r="W3" s="9">
         <f t="shared" si="9"/>
-        <v>6.1854037698548647E-3</v>
-      </c>
-      <c r="T3" s="9">
+        <v>6.2196684967218627E-3</v>
+      </c>
+      <c r="X3" s="9">
         <f t="shared" si="10"/>
-        <v>0.92268702175045747</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.91760385392556976</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -2751,895 +4609,1076 @@
         <v>32.798000000000002</v>
       </c>
       <c r="H4" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C4,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="I4" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C4,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="J4" s="9">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.21212121212121213</v>
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>7.1906431804147786E-3</v>
-      </c>
-      <c r="L4" s="12">
+        <v>0.19084324749302797</v>
+      </c>
+      <c r="L4" s="9">
         <f t="shared" si="11"/>
-        <v>16.808975</v>
+        <v>5.4116700000000009</v>
       </c>
       <c r="M4" s="12">
+        <f t="shared" si="12"/>
+        <v>16.972964999999999</v>
+      </c>
+      <c r="N4" s="12">
         <f t="shared" si="3"/>
-        <v>33.61795</v>
-      </c>
-      <c r="N4" s="12">
+        <v>33.945929999999997</v>
+      </c>
+      <c r="O4" s="26" cm="1" vm="2">
+        <f t="array" aca="1" ref="O4" ca="1">_xlfn.STOCKHISTORY(C4,TODAY(),TODAY(),0,0,1)</f>
+        <v>16.874600000000001</v>
+      </c>
+      <c r="P4" s="12">
+        <f ca="1">IFERROR(O4*E4,G4)</f>
+        <v>33.749200000000002</v>
+      </c>
+      <c r="Q4" s="12">
+        <f ca="1">P4-G4</f>
+        <v>0.95120000000000005</v>
+      </c>
+      <c r="R4" s="12">
         <f t="shared" si="4"/>
-        <v>13.386938775510204</v>
-      </c>
-      <c r="O4" s="12">
+        <v>14.512389380530973</v>
+      </c>
+      <c r="S4" s="12">
         <f t="shared" si="5"/>
-        <v>0.40997499999999931</v>
-      </c>
-      <c r="P4" s="12">
+        <v>0.57396499999999762</v>
+      </c>
+      <c r="T4" s="12">
         <f t="shared" si="6"/>
-        <v>-1.5060306122448983</v>
-      </c>
-      <c r="Q4" s="14">
+        <v>-0.9433053097345141</v>
+      </c>
+      <c r="U4" s="14">
         <f t="shared" si="7"/>
-        <v>-1.096055612244899</v>
-      </c>
-      <c r="R4" s="12">
+        <v>-0.36934030973451648</v>
+      </c>
+      <c r="V4" s="12">
         <f t="shared" si="8"/>
-        <v>161.36822967848994</v>
-      </c>
-      <c r="S4" s="9">
+        <v>160.64151437597957</v>
+      </c>
+      <c r="W4" s="9">
         <f t="shared" si="9"/>
-        <v>6.1970066969960569E-3</v>
-      </c>
-      <c r="T4" s="9">
+        <v>6.2250409172532562E-3</v>
+      </c>
+      <c r="X4" s="9">
         <f t="shared" si="10"/>
-        <v>0.92095943441499695</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.91681193081212453</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>86</v>
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D5" s="8">
-        <v>45623</v>
+        <v>45630</v>
       </c>
       <c r="E5" s="2">
-        <v>1.9595</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
-        <v>15.3</v>
+        <v>20.5</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>29.980350000000001</v>
+        <v>41</v>
       </c>
       <c r="H5" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>7.0499999999999993E-2</v>
+        <v>0.14929999999999999</v>
       </c>
       <c r="I5" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.35260000000000002</v>
+        <v>0.31569999999999998</v>
       </c>
       <c r="J5" s="9">
         <f t="shared" si="1"/>
-        <v>0.19994327850255245</v>
+        <v>0.47291732657586316</v>
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>1.4377207720341513E-2</v>
-      </c>
-      <c r="L5" s="12">
+        <v>0.42547879816887618</v>
+      </c>
+      <c r="L5" s="9">
         <f t="shared" si="11"/>
+        <v>12.9437</v>
+      </c>
+      <c r="M5" s="12">
+        <f t="shared" si="12"/>
+        <v>23.560649999999999</v>
+      </c>
+      <c r="N5" s="12">
+        <f t="shared" si="3"/>
+        <v>47.121299999999998</v>
+      </c>
+      <c r="O5" s="26">
+        <v>20.52</v>
+      </c>
+      <c r="P5" s="12">
+        <f>IFERROR(O5*E5,G5)</f>
+        <v>41.04</v>
+      </c>
+      <c r="Q5" s="12">
+        <f>P5-G5</f>
+        <v>3.9999999999999147E-2</v>
+      </c>
+      <c r="R5" s="12">
+        <f t="shared" si="4"/>
+        <v>17.575445816186555</v>
+      </c>
+      <c r="S5" s="12">
+        <f t="shared" si="5"/>
+        <v>3.060649999999999</v>
+      </c>
+      <c r="T5" s="12">
+        <f t="shared" si="6"/>
+        <v>-1.4622770919067225</v>
+      </c>
+      <c r="U5" s="14">
+        <f t="shared" si="7"/>
+        <v>1.5983729080932765</v>
+      </c>
+      <c r="V5" s="12">
+        <f t="shared" si="8"/>
+        <v>158.67380115815178</v>
+      </c>
+      <c r="W5" s="9">
+        <f t="shared" si="9"/>
+        <v>6.302237626508298E-3</v>
+      </c>
+      <c r="X5" s="9">
+        <f t="shared" si="10"/>
+        <v>0.90558181410456573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="8">
+        <v>45623</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.9595</v>
+      </c>
+      <c r="F6" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>29.980350000000001</v>
+      </c>
+      <c r="H6" s="21">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>7.0499999999999993E-2</v>
+      </c>
+      <c r="I6" s="11">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.35260000000000002</v>
+      </c>
+      <c r="J6" s="9">
+        <f t="shared" si="1"/>
+        <v>0.19994327850255245</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" si="2"/>
+        <v>0.17988688732377014</v>
+      </c>
+      <c r="L6" s="9">
+        <f t="shared" si="11"/>
+        <v>10.571071410000002</v>
+      </c>
+      <c r="M6" s="12">
+        <f t="shared" si="12"/>
         <v>16.37865</v>
       </c>
-      <c r="M5" s="12">
+      <c r="N6" s="12">
         <f t="shared" si="3"/>
         <v>32.093964675000002</v>
       </c>
-      <c r="N5" s="12">
+      <c r="O6" s="12" vm="3">
+        <v>17.03</v>
+      </c>
+      <c r="P6" s="12">
+        <f>IFERROR(O6*E6,G6)</f>
+        <v>33.370285000000003</v>
+      </c>
+      <c r="Q6" s="12">
+        <f>P6-G6</f>
+        <v>3.3899350000000013</v>
+      </c>
+      <c r="R6" s="12">
         <f t="shared" si="4"/>
         <v>11.933546525232041</v>
       </c>
-      <c r="O5" s="12">
+      <c r="S6" s="12">
         <f t="shared" si="5"/>
         <v>1.0786499999999997</v>
       </c>
-      <c r="P5" s="12">
+      <c r="T6" s="12">
         <f t="shared" si="6"/>
         <v>-1.68322673738398</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="U6" s="14">
         <f t="shared" si="7"/>
         <v>-0.60457673738398032</v>
       </c>
-      <c r="R5" s="12">
+      <c r="V6" s="12">
         <f t="shared" si="8"/>
         <v>160.87675080362902</v>
       </c>
-      <c r="S5" s="9">
+      <c r="W6" s="9">
         <f t="shared" si="9"/>
-        <v>6.215938567907987E-3</v>
-      </c>
-      <c r="T5" s="9">
+        <v>6.2159385679079878E-3</v>
+      </c>
+      <c r="X6" s="9">
         <f t="shared" si="10"/>
         <v>0.91815447021900465</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D7" s="8">
         <v>45553</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E7" s="2">
         <v>1.7345999999999999</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F7" s="1">
         <v>51.88</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>89.991048000000006</v>
       </c>
-      <c r="H6" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1),2.5%)</f>
+      <c r="H7" s="21">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1),2.5%)</f>
         <v>5.8799999999999998E-2</v>
       </c>
-      <c r="I6" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),2),25%)</f>
+      <c r="I7" s="11">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),2),25%)</f>
         <v>0.22600000000000001</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J7" s="9">
         <f t="shared" si="1"/>
         <v>0.26017699115044246</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>1.8708399071167652E-2</v>
-      </c>
-      <c r="L6" s="12">
+        <v>0.23407853188082897</v>
+      </c>
+      <c r="L7" s="9">
         <f t="shared" si="11"/>
+        <v>20.337976848</v>
+      </c>
+      <c r="M7" s="12">
+        <f t="shared" si="12"/>
         <v>54.930543999999998</v>
       </c>
-      <c r="M6" s="12">
+      <c r="N7" s="12">
         <f t="shared" si="3"/>
         <v>95.282521622399997</v>
       </c>
-      <c r="N6" s="12">
+      <c r="O7" s="12" cm="1" vm="4">
+        <f t="array" aca="1" ref="O7" ca="1">_xlfn.STOCKHISTORY(C7,TODAY(),TODAY(),0,0,1)</f>
+        <v>53.34</v>
+      </c>
+      <c r="P7" s="12">
+        <f ca="1">IFERROR(O7*E7,G7)</f>
+        <v>92.523564000000007</v>
+      </c>
+      <c r="Q7" s="12">
+        <f ca="1">P7-G7</f>
+        <v>2.5325160000000011</v>
+      </c>
+      <c r="R7" s="12">
         <f t="shared" si="4"/>
         <v>44.44825222755312</v>
       </c>
-      <c r="O6" s="12">
+      <c r="S7" s="12">
         <f t="shared" si="5"/>
         <v>3.050543999999995</v>
       </c>
-      <c r="P6" s="12">
+      <c r="T7" s="12">
         <f t="shared" si="6"/>
         <v>-3.7158738862234415</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="U7" s="14">
         <f t="shared" si="7"/>
         <v>-0.66532988622344647</v>
       </c>
-      <c r="R6" s="12">
+      <c r="V7" s="12">
         <f t="shared" si="8"/>
         <v>160.93750395246849</v>
       </c>
-      <c r="S6" s="9">
+      <c r="W7" s="9">
         <f t="shared" si="9"/>
         <v>6.21359208040993E-3</v>
       </c>
-      <c r="T6" s="9">
+      <c r="X7" s="9">
         <f t="shared" si="10"/>
         <v>0.91850120009083625</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.2354000000000001</v>
+      </c>
+      <c r="F8" s="1">
+        <v>40.49</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
+        <v>50.021346000000001</v>
+      </c>
+      <c r="H8" s="21">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>4.19E-2</v>
+      </c>
+      <c r="I8" s="11">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.53510000000000002</v>
+      </c>
+      <c r="J8" s="9">
+        <f t="shared" si="1"/>
+        <v>7.8303120911979066E-2</v>
+      </c>
+      <c r="K8" s="9">
+        <f t="shared" si="2"/>
+        <v>7.0448503165926199E-2</v>
+      </c>
+      <c r="L8" s="9">
+        <f t="shared" si="11"/>
+        <v>26.766422244600001</v>
+      </c>
+      <c r="M8" s="12">
+        <f t="shared" si="12"/>
+        <v>42.186531000000002</v>
+      </c>
+      <c r="N8" s="12">
+        <f t="shared" si="3"/>
+        <v>52.117240397400003</v>
+      </c>
+      <c r="O8" s="12" cm="1" vm="5">
+        <f t="array" aca="1" ref="O8" ca="1">_xlfn.STOCKHISTORY(C8,TODAY(),TODAY(),0,0,1)</f>
+        <v>37.11</v>
+      </c>
+      <c r="P8" s="12">
+        <f ca="1">IFERROR(O8*E8,G8)</f>
+        <v>45.845694000000002</v>
+      </c>
+      <c r="Q8" s="12">
+        <f ca="1">P8-G8</f>
+        <v>-4.1756519999999995</v>
+      </c>
+      <c r="R8" s="12">
+        <f t="shared" si="4"/>
+        <v>27.116260380391111</v>
+      </c>
+      <c r="S8" s="12">
+        <f t="shared" si="5"/>
+        <v>1.6965310000000002</v>
+      </c>
+      <c r="T8" s="12">
+        <f t="shared" si="6"/>
+        <v>-6.6868698098044455</v>
+      </c>
+      <c r="U8" s="14">
+        <f t="shared" si="7"/>
+        <v>-4.9903388098044452</v>
+      </c>
+      <c r="V8" s="12">
+        <f t="shared" si="8"/>
+        <v>165.2625128760495</v>
+      </c>
+      <c r="W8" s="9">
+        <f t="shared" si="9"/>
+        <v>6.0509790308587519E-3</v>
+      </c>
+      <c r="X8" s="9">
+        <f t="shared" si="10"/>
+        <v>0.94318485547973796</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B9" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D9" s="8">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F9" s="1">
         <v>44.24</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G9" s="1">
         <f t="shared" si="0"/>
         <v>44.24</v>
       </c>
-      <c r="H7" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I7" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
-      </c>
-      <c r="J7" s="9">
+      <c r="H9" s="21">
+        <v>6.2E-2</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="J9" s="9">
         <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="9">
+        <v>0.23754789272030649</v>
+      </c>
+      <c r="K9" s="9">
         <f t="shared" si="2"/>
-        <v>7.1906431804147786E-3</v>
-      </c>
-      <c r="L7" s="12">
+        <v>0.21371936747166675</v>
+      </c>
+      <c r="L9" s="9">
         <f t="shared" si="11"/>
-        <v>45.345999999999997</v>
-      </c>
-      <c r="M7" s="12">
+        <v>11.546640000000002</v>
+      </c>
+      <c r="M9" s="12">
+        <f t="shared" si="12"/>
+        <v>46.982880000000002</v>
+      </c>
+      <c r="N9" s="12">
         <f t="shared" si="3"/>
-        <v>45.345999999999997</v>
-      </c>
-      <c r="N7" s="12">
+        <v>46.982880000000002</v>
+      </c>
+      <c r="O9" s="12" cm="1" vm="6">
+        <f t="array" aca="1" ref="O9" ca="1">_xlfn.STOCKHISTORY(C9,TODAY(),TODAY(),0,0,1)</f>
+        <v>45.97</v>
+      </c>
+      <c r="P9" s="12">
+        <f ca="1">IFERROR(O9*E9,G9)</f>
+        <v>45.97</v>
+      </c>
+      <c r="Q9" s="12">
+        <f ca="1">P9-G9</f>
+        <v>1.7299999999999969</v>
+      </c>
+      <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>36.114285714285714</v>
-      </c>
-      <c r="O7" s="12">
+        <v>36.897414512093412</v>
+      </c>
+      <c r="S9" s="12">
         <f t="shared" si="5"/>
-        <v>1.1059999999999945</v>
-      </c>
-      <c r="P7" s="12">
+        <v>2.7428799999999995</v>
+      </c>
+      <c r="T9" s="12">
         <f t="shared" si="6"/>
-        <v>-4.0628571428571441</v>
-      </c>
-      <c r="Q7" s="14">
+        <v>-3.6712927439532947</v>
+      </c>
+      <c r="U9" s="14">
         <f t="shared" si="7"/>
-        <v>-2.9568571428571495</v>
-      </c>
-      <c r="R7" s="12">
+        <v>-0.92841274395329521</v>
+      </c>
+      <c r="V9" s="12">
         <f t="shared" si="8"/>
-        <v>163.2290312091022</v>
-      </c>
-      <c r="S7" s="9">
+        <v>161.20058681019833</v>
+      </c>
+      <c r="W9" s="9">
         <f t="shared" si="9"/>
-        <v>6.1263611784778916E-3</v>
-      </c>
-      <c r="T7" s="9">
+        <v>6.2034513632225506E-3</v>
+      </c>
+      <c r="X9" s="9">
         <f t="shared" si="10"/>
-        <v>0.93157938561980136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>0.92000266441464951</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B10" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D10" s="8">
         <v>45481</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F10" s="1">
         <v>48.68</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G10" s="1">
         <f t="shared" si="0"/>
         <v>48.68</v>
       </c>
-      <c r="H8" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I8" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
-      </c>
-      <c r="J8" s="9">
+      <c r="H10" s="21">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="J10" s="9">
         <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="9">
+        <v>0.22485207100591714</v>
+      </c>
+      <c r="K10" s="9">
         <f t="shared" si="2"/>
-        <v>7.1906431804147786E-3</v>
-      </c>
-      <c r="L8" s="12">
+        <v>0.20229706877113868</v>
+      </c>
+      <c r="L10" s="9">
         <f t="shared" si="11"/>
-        <v>49.896999999999998</v>
-      </c>
-      <c r="M8" s="12">
+        <v>8.2269199999999998</v>
+      </c>
+      <c r="M10" s="12">
+        <f t="shared" si="12"/>
+        <v>50.52984</v>
+      </c>
+      <c r="N10" s="12">
         <f t="shared" si="3"/>
-        <v>49.896999999999998</v>
-      </c>
-      <c r="N8" s="12">
+        <v>50.52984</v>
+      </c>
+      <c r="O10" s="12" cm="1" vm="7">
+        <f t="array" aca="1" ref="O10" ca="1">_xlfn.STOCKHISTORY(C10,TODAY(),TODAY(),0,0,1)</f>
+        <v>49.3</v>
+      </c>
+      <c r="P10" s="12">
+        <f ca="1">IFERROR(O10*E10,G10)</f>
+        <v>49.3</v>
+      </c>
+      <c r="Q10" s="12">
+        <f ca="1">P10-G10</f>
+        <v>0.61999999999999744</v>
+      </c>
+      <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>39.738775510204079</v>
-      </c>
-      <c r="O8" s="12">
+        <v>43.041556145004421</v>
+      </c>
+      <c r="S10" s="12">
         <f t="shared" si="5"/>
-        <v>1.2169999999999987</v>
-      </c>
-      <c r="P8" s="12">
+        <v>1.8498400000000004</v>
+      </c>
+      <c r="T10" s="12">
         <f t="shared" si="6"/>
-        <v>-4.4706122448979606</v>
-      </c>
-      <c r="Q8" s="14">
+        <v>-2.8192219274977894</v>
+      </c>
+      <c r="U10" s="14">
         <f t="shared" si="7"/>
-        <v>-3.2536122448979619</v>
-      </c>
-      <c r="R8" s="12">
+        <v>-0.96938192749778906</v>
+      </c>
+      <c r="V10" s="12">
         <f t="shared" si="8"/>
-        <v>163.52578631114301</v>
-      </c>
-      <c r="S8" s="9">
+        <v>161.24155599374282</v>
+      </c>
+      <c r="W10" s="9">
         <f t="shared" si="9"/>
-        <v>6.1152434888604341E-3</v>
-      </c>
-      <c r="T8" s="9">
+        <v>6.2018751545588301E-3</v>
+      </c>
+      <c r="X10" s="9">
         <f t="shared" si="10"/>
-        <v>0.93327302389965228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>0.92023648340231989</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C11" t="s">
         <v>150</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D11" s="8">
         <v>45481</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F11" s="1">
         <v>51.28</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G11" s="1">
         <f t="shared" si="0"/>
         <v>51.28</v>
       </c>
-      <c r="H9" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C9,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="I9" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C9,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
-      </c>
-      <c r="J9" s="9">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="K9" s="9">
-        <f t="shared" si="2"/>
-        <v>7.1906431804147786E-3</v>
-      </c>
-      <c r="L9" s="12">
-        <f t="shared" si="11"/>
-        <v>52.561999999999998</v>
-      </c>
-      <c r="M9" s="12">
-        <f t="shared" si="3"/>
-        <v>52.561999999999998</v>
-      </c>
-      <c r="N9" s="12">
-        <f t="shared" si="4"/>
-        <v>41.861224489795916</v>
-      </c>
-      <c r="O9" s="12">
-        <f t="shared" si="5"/>
-        <v>1.2819999999999965</v>
-      </c>
-      <c r="P9" s="12">
-        <f t="shared" si="6"/>
-        <v>-4.7093877551020427</v>
-      </c>
-      <c r="Q9" s="14">
-        <f t="shared" si="7"/>
-        <v>-3.4273877551020462</v>
-      </c>
-      <c r="R9" s="12">
-        <f t="shared" si="8"/>
-        <v>163.69956182134709</v>
-      </c>
-      <c r="S9" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1087518431561004E-3</v>
-      </c>
-      <c r="T9" s="9">
-        <f t="shared" si="10"/>
-        <v>0.93426479406352891</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="8">
-        <v>45630</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>20.36</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>20.36</v>
-      </c>
-      <c r="H10" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C10,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.14929999999999999</v>
-      </c>
-      <c r="I10" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C10,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.31569999999999998</v>
-      </c>
-      <c r="J10" s="9">
-        <f t="shared" si="1"/>
-        <v>0.47291732657586316</v>
-      </c>
-      <c r="K10" s="9">
-        <f t="shared" si="2"/>
-        <v>3.4005797492427187E-2</v>
-      </c>
-      <c r="L10" s="12">
-        <f t="shared" si="11"/>
-        <v>23.399747999999999</v>
-      </c>
-      <c r="M10" s="12">
-        <f t="shared" si="3"/>
-        <v>23.399747999999999</v>
-      </c>
-      <c r="N10" s="12">
-        <f t="shared" si="4"/>
-        <v>17.455418381344305</v>
-      </c>
-      <c r="O10" s="12">
-        <f t="shared" si="5"/>
-        <v>3.0397479999999995</v>
-      </c>
-      <c r="P10" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.452290809327847</v>
-      </c>
-      <c r="Q10" s="14">
-        <f t="shared" si="7"/>
-        <v>1.5874571906721524</v>
-      </c>
-      <c r="R10" s="12">
-        <f t="shared" si="8"/>
-        <v>158.68471687557289</v>
-      </c>
-      <c r="S10" s="9">
-        <f t="shared" si="9"/>
-        <v>6.3018041036939634E-3</v>
-      </c>
-      <c r="T10" s="9">
-        <f t="shared" si="10"/>
-        <v>0.90564411219733409</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D11" s="8">
-        <v>45627</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1.2354000000000001</v>
-      </c>
-      <c r="F11" s="1">
-        <v>40.49</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>50.021346000000001</v>
-      </c>
       <c r="H11" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>4.19E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="I11" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C11,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.53510000000000002</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="J11" s="9">
         <f t="shared" si="1"/>
-        <v>7.8303120911979066E-2</v>
+        <v>0.22485207100591714</v>
       </c>
       <c r="K11" s="9">
         <f t="shared" si="2"/>
-        <v>5.6304980239091605E-3</v>
-      </c>
-      <c r="L11" s="12">
+        <v>0.20229706877113868</v>
+      </c>
+      <c r="L11" s="9">
         <f t="shared" si="11"/>
-        <v>42.186531000000002</v>
+        <v>8.6663200000000007</v>
       </c>
       <c r="M11" s="12">
+        <f t="shared" si="12"/>
+        <v>53.228640000000006</v>
+      </c>
+      <c r="N11" s="12">
         <f t="shared" si="3"/>
-        <v>52.117240397400003</v>
-      </c>
-      <c r="N11" s="12">
+        <v>53.228640000000006</v>
+      </c>
+      <c r="O11" s="12">
+        <v>51.28</v>
+      </c>
+      <c r="P11" s="12">
+        <f>IFERROR(O11*E11,G11)</f>
+        <v>51.28</v>
+      </c>
+      <c r="Q11" s="12">
+        <f>P11-G11</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
         <f t="shared" si="4"/>
-        <v>27.116260380391111</v>
-      </c>
-      <c r="O11" s="12">
+        <v>45.340406719717066</v>
+      </c>
+      <c r="S11" s="12">
         <f t="shared" si="5"/>
-        <v>1.6965310000000002</v>
-      </c>
-      <c r="P11" s="12">
+        <v>1.9486400000000046</v>
+      </c>
+      <c r="T11" s="12">
         <f t="shared" si="6"/>
-        <v>-6.6868698098044455</v>
-      </c>
-      <c r="Q11" s="14">
+        <v>-2.9697966401414675</v>
+      </c>
+      <c r="U11" s="14">
         <f t="shared" si="7"/>
-        <v>-4.9903388098044452</v>
-      </c>
-      <c r="R11" s="12">
+        <v>-1.0211566401414629</v>
+      </c>
+      <c r="V11" s="12">
         <f t="shared" si="8"/>
-        <v>165.2625128760495</v>
-      </c>
-      <c r="S11" s="9">
+        <v>161.29333070638651</v>
+      </c>
+      <c r="W11" s="9">
         <f t="shared" si="9"/>
-        <v>6.0509790308587519E-3</v>
-      </c>
-      <c r="T11" s="9">
+        <v>6.1998843698030494E-3</v>
+      </c>
+      <c r="X11" s="9">
         <f t="shared" si="10"/>
-        <v>0.94318485547973796</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.92053197161687317</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>92</v>
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
       </c>
       <c r="D12" s="8">
-        <v>45627</v>
+        <v>45511</v>
       </c>
       <c r="E12" s="2">
-        <v>0.52039999999999997</v>
+        <v>0.74609999999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>40.340000000000003</v>
+        <v>73.7</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
-        <v>20.992936</v>
+        <v>54.987569999999998</v>
       </c>
       <c r="H12" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>8.6900000000000005E-2</v>
+        <v>0.1212</v>
       </c>
       <c r="I12" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24529999999999999</v>
+        <v>0.24540000000000001</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" si="1"/>
-        <v>0.35426008968609868</v>
+        <v>0.49388753056234719</v>
       </c>
       <c r="K12" s="9">
         <f t="shared" si="2"/>
-        <v>2.547357897994473E-2</v>
-      </c>
-      <c r="L12" s="12">
+        <v>0.44434547250734346</v>
+      </c>
+      <c r="L12" s="9">
         <f t="shared" si="11"/>
+        <v>13.493949678</v>
+      </c>
+      <c r="M12" s="12">
+        <f t="shared" si="12"/>
+        <v>82.632440000000003</v>
+      </c>
+      <c r="N12" s="12">
+        <f t="shared" si="3"/>
+        <v>61.652063484000003</v>
+      </c>
+      <c r="O12" s="12" cm="1" vm="8">
+        <f t="array" aca="1" ref="O12" ca="1">_xlfn.STOCKHISTORY(C12,TODAY(),TODAY(),0,0,1)</f>
+        <v>69.06</v>
+      </c>
+      <c r="P12" s="12">
+        <f ca="1">IFERROR(O12*E12,G12)</f>
+        <v>51.525666000000001</v>
+      </c>
+      <c r="Q12" s="12">
+        <f ca="1">P12-G12</f>
+        <v>-3.461903999999997</v>
+      </c>
+      <c r="R12" s="12">
+        <f t="shared" si="4"/>
+        <v>65.557729941291583</v>
+      </c>
+      <c r="S12" s="12">
+        <f t="shared" si="5"/>
+        <v>8.9324399999999997</v>
+      </c>
+      <c r="T12" s="12">
+        <f t="shared" si="6"/>
+        <v>-4.0711350293542097</v>
+      </c>
+      <c r="U12" s="14">
+        <f t="shared" si="7"/>
+        <v>4.86130497064579</v>
+      </c>
+      <c r="V12" s="12">
+        <f t="shared" si="8"/>
+        <v>155.41086909559925</v>
+      </c>
+      <c r="W12" s="9">
+        <f t="shared" si="9"/>
+        <v>6.4345563847587857E-3</v>
+      </c>
+      <c r="X12" s="9">
+        <f t="shared" si="10"/>
+        <v>0.886959635049555</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.52039999999999997</v>
+      </c>
+      <c r="F13" s="1">
+        <v>40.340000000000003</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="0"/>
+        <v>20.992936</v>
+      </c>
+      <c r="H13" s="21">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),1),2.5%)</f>
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="I13" s="11">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),2),25%)</f>
+        <v>0.24529999999999999</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="1"/>
+        <v>0.35426008968609868</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="2"/>
+        <v>0.31872411672922735</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="11"/>
+        <v>5.1495672008</v>
+      </c>
+      <c r="M13" s="12">
+        <f t="shared" si="12"/>
         <v>43.845546000000006</v>
       </c>
-      <c r="M12" s="12">
+      <c r="N13" s="12">
         <f t="shared" si="3"/>
         <v>22.817222138400002</v>
       </c>
-      <c r="N12" s="12">
+      <c r="O13" s="12" cm="1" vm="9">
+        <f t="array" aca="1" ref="O13" ca="1">_xlfn.STOCKHISTORY(C13,TODAY(),TODAY(),0,0,1)</f>
+        <v>42.65</v>
+      </c>
+      <c r="P13" s="12">
+        <f ca="1">IFERROR(O13*E13,G13)</f>
+        <v>22.195059999999998</v>
+      </c>
+      <c r="Q13" s="12">
+        <f ca="1">P13-G13</f>
+        <v>1.2021239999999977</v>
+      </c>
+      <c r="R13" s="12">
         <f t="shared" si="4"/>
         <v>34.82389502762431</v>
       </c>
-      <c r="O12" s="12">
+      <c r="S13" s="12">
         <f t="shared" si="5"/>
         <v>3.5055460000000025</v>
       </c>
-      <c r="P12" s="12">
+      <c r="T13" s="12">
         <f t="shared" si="6"/>
         <v>-2.7580524861878466</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="U13" s="14">
         <f t="shared" si="7"/>
         <v>0.7474935138121559</v>
       </c>
-      <c r="R12" s="12">
+      <c r="V13" s="12">
         <f t="shared" si="8"/>
         <v>159.5246805524329</v>
       </c>
-      <c r="S12" s="9">
+      <c r="W13" s="9">
         <f t="shared" si="9"/>
         <v>6.2686224886143432E-3</v>
       </c>
-      <c r="T12" s="9">
+      <c r="X13" s="9">
         <f t="shared" si="10"/>
         <v>0.91043794599170247</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D14" s="8">
         <v>45544</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E14" s="2">
         <v>0.51380000000000003</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14" s="1">
         <v>138.53</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G14" s="1">
         <f t="shared" si="0"/>
         <v>71.176714000000004</v>
       </c>
-      <c r="H13" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),1),2.5%)</f>
+      <c r="H14" s="21">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1),2.5%)</f>
         <v>5.0200000000000002E-2</v>
       </c>
-      <c r="I13" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),2),25%)</f>
+      <c r="I14" s="11">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),2),25%)</f>
         <v>0.2001</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J14" s="9">
         <f t="shared" si="1"/>
         <v>0.25087456271864067</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K14" s="9">
         <f t="shared" si="2"/>
-        <v>1.8039494635523332E-2</v>
-      </c>
-      <c r="L13" s="12">
+        <v>0.22570923380948818</v>
+      </c>
+      <c r="L14" s="9">
         <f t="shared" si="11"/>
+        <v>14.242460471400001</v>
+      </c>
+      <c r="M14" s="12">
+        <f t="shared" si="12"/>
         <v>145.484206</v>
       </c>
-      <c r="M13" s="12">
+      <c r="N14" s="12">
         <f t="shared" si="3"/>
         <v>74.749785042799999</v>
       </c>
-      <c r="N13" s="12">
+      <c r="O14" s="12" cm="1" vm="10">
+        <f t="array" aca="1" ref="O14" ca="1">_xlfn.STOCKHISTORY(C14,TODAY(),TODAY(),0,0,1)</f>
+        <v>137.93</v>
+      </c>
+      <c r="P14" s="12">
+        <f ca="1">IFERROR(O14*E14,G14)</f>
+        <v>70.868434000000008</v>
+      </c>
+      <c r="Q14" s="12">
+        <f ca="1">P14-G14</f>
+        <v>-0.30827999999999633</v>
+      </c>
+      <c r="R14" s="12">
         <f t="shared" si="4"/>
         <v>120.47134533437691</v>
       </c>
-      <c r="O13" s="12">
+      <c r="S14" s="12">
         <f t="shared" si="5"/>
         <v>6.9542059999999992</v>
       </c>
-      <c r="P13" s="12">
+      <c r="T14" s="12">
         <f t="shared" si="6"/>
         <v>-9.0293273328115475</v>
       </c>
-      <c r="Q13" s="14">
+      <c r="U14" s="14">
         <f t="shared" si="7"/>
         <v>-2.0751213328115483</v>
       </c>
-      <c r="R13" s="12">
+      <c r="V14" s="12">
         <f t="shared" si="8"/>
         <v>162.34729539905658</v>
       </c>
-      <c r="S13" s="9">
+      <c r="W14" s="9">
         <f t="shared" si="9"/>
-        <v>6.1596344893948335E-3</v>
-      </c>
-      <c r="T13" s="9">
+        <v>6.1596344893948326E-3</v>
+      </c>
+      <c r="X14" s="9">
         <f t="shared" si="10"/>
         <v>0.92654715025016887</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D15" s="8">
         <v>45460</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E15" s="2">
         <v>0.51239999999999997</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F15" s="1">
         <v>157.99</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" s="1">
         <f t="shared" si="0"/>
         <v>80.954076000000001</v>
       </c>
-      <c r="H14" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1),2.5%)</f>
+      <c r="H15" s="21">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1),2.5%)</f>
         <v>6.59E-2</v>
       </c>
-      <c r="I14" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),2),25%)</f>
+      <c r="I15" s="11">
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),2),25%)</f>
         <v>0.1875</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J15" s="9">
         <f t="shared" si="1"/>
         <v>0.35146666666666665</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K15" s="9">
         <f t="shared" si="2"/>
-        <v>2.5272713898097803E-2</v>
-      </c>
-      <c r="L14" s="12">
+        <v>0.31621090310330507</v>
+      </c>
+      <c r="L15" s="9">
         <f t="shared" si="11"/>
+        <v>15.178889250000001</v>
+      </c>
+      <c r="M15" s="12">
+        <f t="shared" si="12"/>
         <v>168.40154100000001</v>
       </c>
-      <c r="M14" s="12">
+      <c r="N15" s="12">
         <f t="shared" si="3"/>
         <v>86.288949608400003</v>
       </c>
-      <c r="N14" s="12">
+      <c r="O15" s="12" cm="1" vm="11">
+        <f t="array" aca="1" ref="O15" ca="1">_xlfn.STOCKHISTORY(C15,TODAY(),TODAY(),0,0,1)</f>
+        <v>139.5</v>
+      </c>
+      <c r="P15" s="12">
+        <f ca="1">IFERROR(O15*E15,G15)</f>
+        <v>71.479799999999997</v>
+      </c>
+      <c r="Q15" s="12">
+        <f ca="1">P15-G15</f>
+        <v>-9.4742760000000033</v>
+      </c>
+      <c r="R15" s="12">
         <f t="shared" si="4"/>
         <v>140.86126961483598</v>
       </c>
-      <c r="O14" s="12">
+      <c r="S15" s="12">
         <f t="shared" si="5"/>
         <v>10.411541</v>
       </c>
-      <c r="P14" s="12">
+      <c r="T15" s="12">
         <f t="shared" si="6"/>
         <v>-8.5643651925820166</v>
       </c>
-      <c r="Q14" s="14">
+      <c r="U15" s="14">
         <f t="shared" si="7"/>
         <v>1.8471758074179832</v>
       </c>
-      <c r="R14" s="12">
+      <c r="V15" s="12">
         <f t="shared" si="8"/>
         <v>158.42499825882706</v>
       </c>
-      <c r="S14" s="9">
+      <c r="W15" s="9">
         <f t="shared" si="9"/>
-        <v>6.3121351490643459E-3</v>
-      </c>
-      <c r="T14" s="9">
+        <v>6.312135149064345E-3</v>
+      </c>
+      <c r="X15" s="9">
         <f t="shared" si="10"/>
         <v>0.90416184824201995</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="8">
-        <v>45511</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.45179999999999998</v>
-      </c>
-      <c r="F15" s="1">
-        <v>77.430000000000007</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>34.982874000000002</v>
-      </c>
-      <c r="H15" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1212</v>
-      </c>
-      <c r="I15" s="11">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24540000000000001</v>
-      </c>
-      <c r="J15" s="9">
-        <f t="shared" si="1"/>
-        <v>0.49388753056234719</v>
-      </c>
-      <c r="K15" s="9">
-        <f t="shared" si="2"/>
-        <v>3.5513690035300367E-2</v>
-      </c>
-      <c r="L15" s="12">
-        <f t="shared" si="11"/>
-        <v>86.814516000000012</v>
-      </c>
-      <c r="M15" s="12">
-        <f t="shared" si="3"/>
-        <v>39.222798328800003</v>
-      </c>
-      <c r="N15" s="12">
-        <f t="shared" si="4"/>
-        <v>68.875644903042158</v>
-      </c>
-      <c r="O15" s="12">
-        <f t="shared" si="5"/>
-        <v>9.384516000000005</v>
-      </c>
-      <c r="P15" s="12">
-        <f t="shared" si="6"/>
-        <v>-4.2771775484789245</v>
-      </c>
-      <c r="Q15" s="14">
-        <f t="shared" si="7"/>
-        <v>5.1073384515210805</v>
-      </c>
-      <c r="R15" s="12">
-        <f t="shared" si="8"/>
-        <v>155.16483561472396</v>
-      </c>
-      <c r="S15" s="9">
-        <f t="shared" si="9"/>
-        <v>6.4447591881127714E-3</v>
-      </c>
-      <c r="T15" s="9">
-        <f t="shared" si="10"/>
-        <v>0.88555547478922669</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -3676,46 +5715,62 @@
       </c>
       <c r="K16" s="9">
         <f t="shared" si="2"/>
-        <v>5.3946556656043851E-2</v>
-      </c>
-      <c r="L16" s="12">
+        <v>0.67497655646729637</v>
+      </c>
+      <c r="L16" s="9">
         <f t="shared" si="11"/>
+        <v>25.124383398399996</v>
+      </c>
+      <c r="M16" s="12">
+        <f t="shared" si="12"/>
         <v>235.643968</v>
       </c>
-      <c r="M16" s="12">
+      <c r="N16" s="12">
         <f t="shared" si="3"/>
         <v>96.802542054400007</v>
       </c>
-      <c r="N16" s="12">
+      <c r="O16" s="12" cm="1" vm="12">
+        <f t="array" aca="1" ref="O16" ca="1">_xlfn.STOCKHISTORY(C16,TODAY(),TODAY(),0,0,1)</f>
+        <v>200.95</v>
+      </c>
+      <c r="P16" s="12">
+        <f ca="1">IFERROR(O16*E16,G16)</f>
+        <v>82.550259999999994</v>
+      </c>
+      <c r="Q16" s="12">
+        <f ca="1">P16-G16</f>
+        <v>4.5968519999999984</v>
+      </c>
+      <c r="R16" s="12">
         <f t="shared" si="4"/>
         <v>175.62239703840814</v>
       </c>
-      <c r="O16" s="12">
+      <c r="S16" s="12">
         <f t="shared" si="5"/>
         <v>45.88396800000001</v>
       </c>
-      <c r="P16" s="12">
+      <c r="T16" s="12">
         <f t="shared" si="6"/>
         <v>-7.0688014807959263</v>
       </c>
-      <c r="Q16" s="14">
+      <c r="U16" s="14">
         <f t="shared" si="7"/>
         <v>38.815166519204084</v>
       </c>
-      <c r="R16" s="12">
+      <c r="V16" s="12">
         <f t="shared" si="8"/>
         <v>121.45700754704096</v>
       </c>
-      <c r="S16" s="9">
+      <c r="W16" s="9">
         <f t="shared" si="9"/>
         <v>8.2333660296438193E-3</v>
       </c>
-      <c r="T16" s="9">
+      <c r="X16" s="9">
         <f t="shared" si="10"/>
         <v>0.69317843542762225</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -3752,46 +5807,62 @@
       </c>
       <c r="K17" s="9">
         <f t="shared" si="2"/>
-        <v>1.965197408725234E-2</v>
-      </c>
-      <c r="L17" s="12">
+        <v>0.24588449419990988</v>
+      </c>
+      <c r="L17" s="9">
         <f t="shared" si="11"/>
+        <v>11.693686951800002</v>
+      </c>
+      <c r="M17" s="12">
+        <f t="shared" si="12"/>
         <v>141.07774500000002</v>
       </c>
-      <c r="M17" s="12">
+      <c r="N17" s="12">
         <f t="shared" si="3"/>
         <v>49.179701907000009</v>
       </c>
-      <c r="N17" s="12">
+      <c r="O17" s="12" cm="1" vm="13">
+        <f t="array" aca="1" ref="O17" ca="1">_xlfn.STOCKHISTORY(C17,TODAY(),TODAY(),0,0,1)</f>
+        <v>126.91</v>
+      </c>
+      <c r="P17" s="12">
+        <f ca="1">IFERROR(O17*E17,G17)</f>
+        <v>44.240825999999998</v>
+      </c>
+      <c r="Q17" s="12">
+        <f ca="1">P17-G17</f>
+        <v>-1.7430000000000021</v>
+      </c>
+      <c r="R17" s="12">
         <f t="shared" si="4"/>
         <v>111.3352464550979</v>
       </c>
-      <c r="O17" s="12">
+      <c r="S17" s="12">
         <f t="shared" si="5"/>
         <v>9.1677450000000249</v>
       </c>
-      <c r="P17" s="12">
+      <c r="T17" s="12">
         <f t="shared" si="6"/>
         <v>-10.287376772451047</v>
       </c>
-      <c r="Q17" s="14">
+      <c r="U17" s="14">
         <f t="shared" si="7"/>
         <v>-1.1196317724510223</v>
       </c>
-      <c r="R17" s="12">
+      <c r="V17" s="12">
         <f t="shared" si="8"/>
         <v>161.39180583869606</v>
       </c>
-      <c r="S17" s="9">
+      <c r="W17" s="9">
         <f t="shared" si="9"/>
         <v>6.1961014365218489E-3</v>
       </c>
-      <c r="T17" s="9">
+      <c r="X17" s="9">
         <f t="shared" si="10"/>
         <v>0.92109398808279364</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -3828,46 +5899,62 @@
       </c>
       <c r="K18" s="9">
         <f t="shared" si="2"/>
-        <v>-1.5556620973837124E-2</v>
-      </c>
-      <c r="L18" s="12">
+        <v>-0.19464364560163458</v>
+      </c>
+      <c r="L18" s="9">
         <f t="shared" si="11"/>
+        <v>5.8605604249999992</v>
+      </c>
+      <c r="M18" s="12">
+        <f t="shared" si="12"/>
         <v>30.369896000000001</v>
       </c>
-      <c r="M18" s="12">
+      <c r="N18" s="12">
         <f t="shared" si="3"/>
         <v>8.7313450999999986</v>
       </c>
-      <c r="N18" s="12">
+      <c r="O18" s="12" cm="1" vm="14">
+        <f t="array" aca="1" ref="O18" ca="1">_xlfn.STOCKHISTORY(C18,TODAY(),TODAY(),0,0,1)</f>
+        <v>34.020000000000003</v>
+      </c>
+      <c r="P18" s="12">
+        <f ca="1">IFERROR(O18*E18,G18)</f>
+        <v>9.7807499999999994</v>
+      </c>
+      <c r="Q18" s="12">
+        <f ca="1">P18-G18</f>
+        <v>-0.21850000000000058</v>
+      </c>
+      <c r="R18" s="12">
         <f t="shared" si="4"/>
         <v>20.304746336622102</v>
       </c>
-      <c r="O18" s="12">
+      <c r="S18" s="12">
         <f t="shared" si="5"/>
         <v>-4.4101040000000005</v>
       </c>
-      <c r="P18" s="12">
+      <c r="T18" s="12">
         <f t="shared" si="6"/>
         <v>-7.2376268316889494</v>
       </c>
-      <c r="Q18" s="14">
+      <c r="U18" s="14">
         <f t="shared" si="7"/>
         <v>-11.64773083168895</v>
       </c>
-      <c r="R18" s="12">
+      <c r="V18" s="12">
         <f t="shared" si="8"/>
         <v>171.919904897934</v>
       </c>
-      <c r="S18" s="9">
+      <c r="W18" s="9">
         <f t="shared" si="9"/>
         <v>5.8166621287609683E-3</v>
       </c>
-      <c r="T18" s="9">
+      <c r="X18" s="9">
         <f t="shared" si="10"/>
         <v>0.981179868521459</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -3904,46 +5991,62 @@
       </c>
       <c r="K19" s="9">
         <f t="shared" si="2"/>
-        <v>1.8487648645297193E-2</v>
-      </c>
-      <c r="L19" s="12">
+        <v>0.23131651384800542</v>
+      </c>
+      <c r="L19" s="9">
         <f t="shared" si="11"/>
+        <v>21.500995276799998</v>
+      </c>
+      <c r="M19" s="12">
+        <f t="shared" si="12"/>
         <v>200.52288000000001</v>
       </c>
-      <c r="M19" s="12">
+      <c r="N19" s="12">
         <f t="shared" si="3"/>
         <v>50.471608895999999</v>
       </c>
-      <c r="N19" s="12">
+      <c r="O19" s="12" cm="1" vm="15">
+        <f t="array" aca="1" ref="O19" ca="1">_xlfn.STOCKHISTORY(C19,TODAY(),TODAY(),0,0,1)</f>
+        <v>162.5</v>
+      </c>
+      <c r="P19" s="12">
+        <f ca="1">IFERROR(O19*E19,G19)</f>
+        <v>40.901249999999997</v>
+      </c>
+      <c r="Q19" s="12">
+        <f ca="1">P19-G19</f>
+        <v>-4.0423019999999994</v>
+      </c>
+      <c r="R19" s="12">
         <f t="shared" si="4"/>
         <v>131.73970783532536</v>
       </c>
-      <c r="O19" s="12">
+      <c r="S19" s="12">
         <f t="shared" si="5"/>
         <v>21.962880000000013</v>
       </c>
-      <c r="P19" s="12">
+      <c r="T19" s="12">
         <f t="shared" si="6"/>
         <v>-23.41014608233732</v>
       </c>
-      <c r="Q19" s="14">
+      <c r="U19" s="14">
         <f t="shared" si="7"/>
         <v>-1.4472660823373076</v>
       </c>
-      <c r="R19" s="12">
+      <c r="V19" s="12">
         <f t="shared" si="8"/>
         <v>161.71944014858235</v>
       </c>
-      <c r="S19" s="9">
+      <c r="W19" s="9">
         <f t="shared" si="9"/>
-        <v>6.1835484904055674E-3</v>
-      </c>
-      <c r="T19" s="9">
+        <v>6.1835484904055682E-3</v>
+      </c>
+      <c r="X19" s="9">
         <f t="shared" si="10"/>
         <v>0.92296385992391761</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -3957,14 +6060,14 @@
         <v>45482</v>
       </c>
       <c r="E20" s="2">
-        <v>0.18820000000000001</v>
+        <v>1E-4</v>
       </c>
       <c r="F20" s="1">
         <v>227.38</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="0"/>
-        <v>42.792915999999998</v>
+        <v>2.2738000000000001E-2</v>
       </c>
       <c r="H20" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),1),2.5%)</f>
@@ -3980,46 +6083,62 @@
       </c>
       <c r="K20" s="9">
         <f t="shared" si="2"/>
-        <v>5.2893198078156518E-2</v>
-      </c>
-      <c r="L20" s="12">
+        <v>0.66179698784050023</v>
+      </c>
+      <c r="L20" s="9">
         <f t="shared" si="11"/>
+        <v>6.4666871999999997E-3</v>
+      </c>
+      <c r="M20" s="12">
+        <f t="shared" si="12"/>
         <v>274.94789600000001</v>
       </c>
-      <c r="M20" s="12">
+      <c r="N20" s="12">
         <f t="shared" si="3"/>
-        <v>51.745194027200007</v>
-      </c>
-      <c r="N20" s="12">
+        <v>2.7494789600000003E-2</v>
+      </c>
+      <c r="O20" s="12" cm="1" vm="16">
+        <f t="array" aca="1" ref="O20" ca="1">_xlfn.STOCKHISTORY(C20,TODAY(),TODAY(),0,0,1)</f>
+        <v>244.87</v>
+      </c>
+      <c r="P20" s="12">
+        <f ca="1">IFERROR(O20*E20,G20)</f>
+        <v>2.4487000000000002E-2</v>
+      </c>
+      <c r="Q20" s="12">
+        <f ca="1">P20-G20</f>
+        <v>1.7490000000000006E-3</v>
+      </c>
+      <c r="R20" s="12">
         <f t="shared" si="4"/>
         <v>211.47693452380955</v>
       </c>
-      <c r="O20" s="12">
+      <c r="S20" s="12">
         <f t="shared" si="5"/>
         <v>47.567896000000019</v>
       </c>
-      <c r="P20" s="12">
+      <c r="T20" s="12">
         <f t="shared" si="6"/>
         <v>-7.9515327380952243</v>
       </c>
-      <c r="Q20" s="14">
+      <c r="U20" s="14">
         <f t="shared" si="7"/>
         <v>39.616363261904795</v>
       </c>
-      <c r="R20" s="12">
+      <c r="V20" s="12">
         <f t="shared" si="8"/>
         <v>120.65581080434025</v>
       </c>
-      <c r="S20" s="9">
+      <c r="W20" s="9">
         <f t="shared" si="9"/>
         <v>8.2880384569429116E-3</v>
       </c>
-      <c r="T20" s="9">
+      <c r="X20" s="9">
         <f t="shared" si="10"/>
         <v>0.68860585196132951</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -4056,46 +6175,62 @@
       </c>
       <c r="K21" s="9">
         <f t="shared" si="2"/>
-        <v>6.4212629956166029E-2</v>
-      </c>
-      <c r="L21" s="12">
+        <v>0.80342514028957801</v>
+      </c>
+      <c r="L21" s="9">
         <f t="shared" si="11"/>
+        <v>18.269971310800003</v>
+      </c>
+      <c r="M21" s="12">
+        <f t="shared" si="12"/>
         <v>522.76861600000007</v>
       </c>
-      <c r="M21" s="12">
+      <c r="N21" s="12">
         <f t="shared" si="3"/>
         <v>83.956639729600013</v>
       </c>
-      <c r="N21" s="12">
+      <c r="O21" s="12" cm="1" vm="17">
+        <f t="array" aca="1" ref="O21" ca="1">_xlfn.STOCKHISTORY(C21,TODAY(),TODAY(),0,0,1)</f>
+        <v>414.77</v>
+      </c>
+      <c r="P21" s="12">
+        <f ca="1">IFERROR(O21*E21,G21)</f>
+        <v>66.612061999999995</v>
+      </c>
+      <c r="Q21" s="12">
+        <f ca="1">P21-G21</f>
+        <v>-1.0294460000000072</v>
+      </c>
+      <c r="R21" s="12">
         <f t="shared" si="4"/>
         <v>409.34979103897371</v>
       </c>
-      <c r="O21" s="12">
+      <c r="S21" s="12">
         <f t="shared" si="5"/>
         <v>101.58861600000006</v>
       </c>
-      <c r="P21" s="12">
+      <c r="T21" s="12">
         <f t="shared" si="6"/>
         <v>-5.9151044805131505</v>
       </c>
-      <c r="Q21" s="14">
+      <c r="U21" s="14">
         <f t="shared" si="7"/>
         <v>95.673511519486908</v>
       </c>
-      <c r="R21" s="12">
+      <c r="V21" s="12">
         <f t="shared" si="8"/>
         <v>64.598662546758135</v>
       </c>
-      <c r="S21" s="9">
+      <c r="W21" s="9">
         <f t="shared" si="9"/>
-        <v>1.5480196656953616E-2</v>
-      </c>
-      <c r="T21" s="9">
+        <v>1.5480196656953615E-2</v>
+      </c>
+      <c r="X21" s="9">
         <f t="shared" si="10"/>
         <v>0.36867695606229905</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -4132,46 +6267,62 @@
       </c>
       <c r="K22" s="9">
         <f t="shared" si="2"/>
-        <v>5.2020863233920044E-2</v>
-      </c>
-      <c r="L22" s="12">
+        <v>0.65088237890626699</v>
+      </c>
+      <c r="L22" s="9">
         <f t="shared" si="11"/>
+        <v>17.296346755999998</v>
+      </c>
+      <c r="M22" s="12">
+        <f t="shared" si="12"/>
         <v>598.2607680000001</v>
       </c>
-      <c r="M22" s="12">
+      <c r="N22" s="12">
         <f t="shared" si="3"/>
         <v>77.414943379200011</v>
       </c>
-      <c r="N22" s="12">
+      <c r="O22" s="12" cm="1" vm="18">
+        <f t="array" aca="1" ref="O22" ca="1">_xlfn.STOCKHISTORY(C22,TODAY(),TODAY(),0,0,1)</f>
+        <v>568.5</v>
+      </c>
+      <c r="P22" s="12">
+        <f ca="1">IFERROR(O22*E22,G22)</f>
+        <v>73.56389999999999</v>
+      </c>
+      <c r="Q22" s="12">
+        <f ca="1">P22-G22</f>
+        <v>8.6620360000000005</v>
+      </c>
+      <c r="R22" s="12">
         <f t="shared" si="4"/>
         <v>467.13234609294966</v>
       </c>
-      <c r="O22" s="12">
+      <c r="S22" s="12">
         <f t="shared" si="5"/>
         <v>96.700768000000096</v>
       </c>
-      <c r="P22" s="12">
+      <c r="T22" s="12">
         <f t="shared" si="6"/>
         <v>-17.213826953525171</v>
       </c>
-      <c r="Q22" s="14">
+      <c r="U22" s="14">
         <f t="shared" si="7"/>
         <v>79.486941046474925</v>
       </c>
-      <c r="R22" s="12">
+      <c r="V22" s="12">
         <f t="shared" si="8"/>
         <v>80.785233019770118</v>
       </c>
-      <c r="S22" s="9">
+      <c r="W22" s="9">
         <f t="shared" si="9"/>
-        <v>1.2378499914152324E-2</v>
-      </c>
-      <c r="T22" s="9">
+        <v>1.2378499914152326E-2</v>
+      </c>
+      <c r="X22" s="9">
         <f t="shared" si="10"/>
         <v>0.46105681805647636</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -4208,46 +6359,62 @@
       </c>
       <c r="K23" s="9">
         <f t="shared" si="2"/>
-        <v>4.8500308767689022E-2</v>
-      </c>
-      <c r="L23" s="12">
+        <v>0.60683338156945643</v>
+      </c>
+      <c r="L23" s="9">
         <f t="shared" si="11"/>
+        <v>2.8531769063999999</v>
+      </c>
+      <c r="M23" s="12">
+        <f t="shared" si="12"/>
         <v>221.59034999999997</v>
       </c>
-      <c r="M23" s="12">
+      <c r="N23" s="12">
         <f t="shared" si="3"/>
         <v>11.921560829999999</v>
       </c>
-      <c r="N23" s="12">
+      <c r="O23" s="12" cm="1" vm="19">
+        <f t="array" aca="1" ref="O23" ca="1">_xlfn.STOCKHISTORY(C23,TODAY(),TODAY(),0,0,1)</f>
+        <v>185.27</v>
+      </c>
+      <c r="P23" s="12">
+        <f ca="1">IFERROR(O23*E23,G23)</f>
+        <v>9.9675260000000012</v>
+      </c>
+      <c r="Q23" s="12">
+        <f ca="1">P23-G23</f>
+        <v>-2.9589999999998895E-2</v>
+      </c>
+      <c r="R23" s="12">
         <f t="shared" si="4"/>
         <v>170.02470491353276</v>
       </c>
-      <c r="O23" s="12">
+      <c r="S23" s="12">
         <f t="shared" si="5"/>
         <v>35.770349999999979</v>
       </c>
-      <c r="P23" s="12">
+      <c r="T23" s="12">
         <f t="shared" si="6"/>
         <v>-7.8976475432336173</v>
       </c>
-      <c r="Q23" s="14">
+      <c r="U23" s="14">
         <f t="shared" si="7"/>
         <v>27.872702456766362</v>
       </c>
-      <c r="R23" s="12">
+      <c r="V23" s="12">
         <f t="shared" si="8"/>
         <v>132.39947160947867</v>
       </c>
-      <c r="S23" s="9">
+      <c r="W23" s="9">
         <f t="shared" si="9"/>
         <v>7.552900233239364E-3</v>
       </c>
-      <c r="T23" s="9">
+      <c r="X23" s="9">
         <f t="shared" si="10"/>
         <v>0.75562917640760074</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -4284,46 +6451,62 @@
       </c>
       <c r="K24" s="9">
         <f t="shared" si="2"/>
-        <v>3.5170970200438814E-2</v>
-      </c>
-      <c r="L24" s="12">
+        <v>0.44005737947032519</v>
+      </c>
+      <c r="L24" s="9">
         <f t="shared" si="11"/>
+        <v>9.3575669999999972E-3</v>
+      </c>
+      <c r="M24" s="12">
+        <f t="shared" si="12"/>
         <v>145.76661899999999</v>
       </c>
-      <c r="M24" s="12">
+      <c r="N24" s="12">
         <f t="shared" si="3"/>
         <v>4.3729985699999994E-2</v>
       </c>
-      <c r="N24" s="12">
+      <c r="O24" s="12" cm="1" vm="20">
+        <f t="array" aca="1" ref="O24" ca="1">_xlfn.STOCKHISTORY(C24,TODAY(),TODAY(),0,0,1)</f>
+        <v>148.29</v>
+      </c>
+      <c r="P24" s="12">
+        <f ca="1">IFERROR(O24*E24,G24)</f>
+        <v>4.4486999999999992E-2</v>
+      </c>
+      <c r="Q24" s="12">
+        <f ca="1">P24-G24</f>
+        <v>5.3339999999999985E-3</v>
+      </c>
+      <c r="R24" s="12">
         <f t="shared" si="4"/>
         <v>116.3087068888691</v>
       </c>
-      <c r="O24" s="12">
+      <c r="S24" s="12">
         <f t="shared" si="5"/>
         <v>15.256619000000001</v>
       </c>
-      <c r="P24" s="12">
+      <c r="T24" s="12">
         <f t="shared" si="6"/>
         <v>-7.1006465555654472</v>
       </c>
-      <c r="Q24" s="14">
+      <c r="U24" s="14">
         <f t="shared" si="7"/>
         <v>8.1559724444345534</v>
       </c>
-      <c r="R24" s="12">
+      <c r="V24" s="12">
         <f t="shared" si="8"/>
         <v>152.11620162181049</v>
       </c>
-      <c r="S24" s="9">
+      <c r="W24" s="9">
         <f t="shared" si="9"/>
-        <v>6.5739217081306573E-3</v>
-      </c>
-      <c r="T24" s="9">
+        <v>6.5739217081306582E-3</v>
+      </c>
+      <c r="X24" s="9">
         <f t="shared" si="10"/>
         <v>0.86815633591631525</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -4360,46 +6543,62 @@
       </c>
       <c r="K25" s="9">
         <f t="shared" si="2"/>
-        <v>-8.0787934619887522E-2</v>
-      </c>
-      <c r="L25" s="12">
+        <v>-1.0108145040936092</v>
+      </c>
+      <c r="L25" s="9">
         <f t="shared" si="11"/>
+        <v>1.4428596E-18</v>
+      </c>
+      <c r="M25" s="12">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M25" s="12">
+      <c r="N25" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N25" s="12">
+      <c r="O25" s="12" cm="1" vm="21">
+        <f t="array" aca="1" ref="O25" ca="1">_xlfn.STOCKHISTORY(C25,TODAY(),TODAY(),0,0,1)</f>
+        <v>5.64</v>
+      </c>
+      <c r="P25" s="12">
+        <f ca="1">IFERROR(O25*E25,G25)</f>
+        <v>5.6399999999999995E-19</v>
+      </c>
+      <c r="Q25" s="12">
+        <f ca="1">P25-G25</f>
+        <v>-5.280000000000001E-19</v>
+      </c>
+      <c r="R25" s="12">
         <f t="shared" si="4"/>
         <v>2.8693047453886176</v>
       </c>
-      <c r="O25" s="12">
+      <c r="S25" s="12">
         <f t="shared" si="5"/>
         <v>-10.92</v>
       </c>
-      <c r="P25" s="12">
+      <c r="T25" s="12">
         <f t="shared" si="6"/>
         <v>-4.025347627305691</v>
       </c>
-      <c r="Q25" s="14">
+      <c r="U25" s="14">
         <f t="shared" si="7"/>
         <v>-14.94534762730569</v>
       </c>
-      <c r="R25" s="12">
+      <c r="V25" s="12">
         <f t="shared" si="8"/>
         <v>175.21752169355074</v>
       </c>
-      <c r="S25" s="9">
+      <c r="W25" s="9">
         <f t="shared" si="9"/>
         <v>5.7071917827314364E-3</v>
       </c>
-      <c r="T25" s="9">
+      <c r="X25" s="9">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -4436,46 +6635,62 @@
       </c>
       <c r="K26" s="9">
         <f t="shared" si="2"/>
-        <v>5.0476189813256446E-2</v>
-      </c>
-      <c r="L26" s="12">
+        <v>0.6315555041069415</v>
+      </c>
+      <c r="L26" s="9">
         <f t="shared" si="11"/>
+        <v>6.9043547999999996E-18</v>
+      </c>
+      <c r="M26" s="12">
+        <f t="shared" si="12"/>
         <v>331.89653000000004</v>
       </c>
-      <c r="M26" s="12">
+      <c r="N26" s="12">
         <f t="shared" si="3"/>
         <v>3.3189653000000001E-17</v>
       </c>
-      <c r="N26" s="12">
+      <c r="O26" s="12" cm="1" vm="22">
+        <f t="array" aca="1" ref="O26" ca="1">_xlfn.STOCKHISTORY(C26,TODAY(),TODAY(),0,0,1)</f>
+        <v>355.23</v>
+      </c>
+      <c r="P26" s="12">
+        <f ca="1">IFERROR(O26*E26,G26)</f>
+        <v>3.5522999999999998E-17</v>
+      </c>
+      <c r="Q26" s="12">
+        <f ca="1">P26-G26</f>
+        <v>7.1800000000000003E-18</v>
+      </c>
+      <c r="R26" s="12">
         <f t="shared" si="4"/>
         <v>264.24575797128472</v>
       </c>
-      <c r="O26" s="12">
+      <c r="S26" s="12">
         <f t="shared" si="5"/>
         <v>48.466530000000034</v>
       </c>
-      <c r="P26" s="12">
+      <c r="T26" s="12">
         <f t="shared" si="6"/>
         <v>-9.5921210143576445</v>
       </c>
-      <c r="Q26" s="14">
+      <c r="U26" s="14">
         <f t="shared" si="7"/>
         <v>38.87440898564239</v>
       </c>
-      <c r="R26" s="12">
+      <c r="V26" s="12">
         <f t="shared" si="8"/>
         <v>121.39776508060265</v>
       </c>
-      <c r="S26" s="9">
+      <c r="W26" s="9">
         <f t="shared" si="9"/>
         <v>8.2373839364838809E-3</v>
       </c>
-      <c r="T26" s="9">
+      <c r="X26" s="9">
         <f t="shared" si="10"/>
         <v>0.6928403273099768</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -4512,46 +6727,62 @@
       </c>
       <c r="K27" s="9">
         <f t="shared" si="2"/>
-        <v>2.2843637177955244E-2</v>
-      </c>
-      <c r="L27" s="12">
+        <v>0.28581841947528813</v>
+      </c>
+      <c r="L27" s="9">
         <f t="shared" si="11"/>
+        <v>6.8927168000000004E-18</v>
+      </c>
+      <c r="M27" s="12">
+        <f t="shared" si="12"/>
         <v>210.01716800000003</v>
       </c>
-      <c r="M27" s="12">
+      <c r="N27" s="12">
         <f t="shared" si="3"/>
         <v>2.1001716800000003E-17</v>
       </c>
-      <c r="N27" s="12">
+      <c r="O27" s="12" cm="1" vm="23">
+        <f t="array" aca="1" ref="O27" ca="1">_xlfn.STOCKHISTORY(C27,TODAY(),TODAY(),0,0,1)</f>
+        <v>175.22</v>
+      </c>
+      <c r="P27" s="12">
+        <f ca="1">IFERROR(O27*E27,G27)</f>
+        <v>1.7522E-17</v>
+      </c>
+      <c r="Q27" s="12">
+        <f ca="1">P27-G27</f>
+        <v>-1.2900000000000016E-18</v>
+      </c>
+      <c r="R27" s="12">
         <f t="shared" si="4"/>
         <v>150.49600000000001</v>
       </c>
-      <c r="O27" s="12">
+      <c r="S27" s="12">
         <f t="shared" si="5"/>
         <v>21.897168000000022</v>
       </c>
-      <c r="P27" s="12">
+      <c r="T27" s="12">
         <f t="shared" si="6"/>
         <v>-18.811999999999998</v>
       </c>
-      <c r="Q27" s="14">
+      <c r="U27" s="14">
         <f t="shared" si="7"/>
         <v>3.0851680000000243</v>
       </c>
-      <c r="R27" s="12">
+      <c r="V27" s="12">
         <f t="shared" si="8"/>
         <v>157.18700606624503</v>
       </c>
-      <c r="S27" s="9">
+      <c r="W27" s="9">
         <f t="shared" si="9"/>
-        <v>6.3618490168236876E-3</v>
-      </c>
-      <c r="T27" s="9">
+        <v>6.3618490168236884E-3</v>
+      </c>
+      <c r="X27" s="9">
         <f t="shared" si="10"/>
         <v>0.89709638937343017</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -4588,46 +6819,62 @@
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
-        <v>4.1716114046666239E-2</v>
-      </c>
-      <c r="L28" s="12">
+        <v>0.52194988436321643</v>
+      </c>
+      <c r="L28" s="9">
         <f t="shared" si="11"/>
+        <v>1.8526314000000002E-17</v>
+      </c>
+      <c r="M28" s="12">
+        <f t="shared" si="12"/>
         <v>776.29937400000006</v>
       </c>
-      <c r="M28" s="12">
+      <c r="N28" s="12">
         <f t="shared" si="3"/>
         <v>7.7629937400000001E-17</v>
       </c>
-      <c r="N28" s="12">
+      <c r="O28" s="12" t="e" cm="1" vm="24">
+        <f t="array" aca="1" ref="O28" ca="1">_xlfn.STOCKHISTORY(C28,TODAY(),TODAY(),0,0,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P28" s="12">
+        <f ca="1">IFERROR(O28*E28,G28)</f>
+        <v>6.6881999999999999E-17</v>
+      </c>
+      <c r="Q28" s="12">
+        <f ca="1">P28-G28</f>
+        <v>0</v>
+      </c>
+      <c r="R28" s="12">
         <f t="shared" si="4"/>
         <v>599.14001612469769</v>
       </c>
-      <c r="O28" s="12">
+      <c r="S28" s="12">
         <f t="shared" si="5"/>
         <v>107.47937400000001</v>
       </c>
-      <c r="P28" s="12">
+      <c r="T28" s="12">
         <f t="shared" si="6"/>
         <v>-34.839991937651178</v>
       </c>
-      <c r="Q28" s="14">
+      <c r="U28" s="14">
         <f t="shared" si="7"/>
         <v>72.63938206234883</v>
       </c>
-      <c r="R28" s="12">
+      <c r="V28" s="12">
         <f t="shared" si="8"/>
         <v>87.632792003896213</v>
       </c>
-      <c r="S28" s="9">
+      <c r="W28" s="9">
         <f t="shared" si="9"/>
         <v>1.1411253449000453E-2</v>
       </c>
-      <c r="T28" s="9">
+      <c r="X28" s="9">
         <f t="shared" si="10"/>
         <v>0.50013715042244966</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -4664,46 +6911,62 @@
       </c>
       <c r="K29" s="9">
         <f t="shared" si="2"/>
-        <v>3.9924226212860611E-2</v>
-      </c>
-      <c r="L29" s="12">
+        <v>0.49952987547647199</v>
+      </c>
+      <c r="L29" s="9">
         <f t="shared" si="11"/>
+        <v>2.5869820800000001E-17</v>
+      </c>
+      <c r="M29" s="12">
+        <f t="shared" si="12"/>
         <v>843.95563200000015</v>
       </c>
-      <c r="M29" s="12">
+      <c r="N29" s="12">
         <f t="shared" si="3"/>
         <v>8.4395563200000012E-17</v>
       </c>
-      <c r="N29" s="12">
+      <c r="O29" s="12" cm="1" vm="25">
+        <f t="array" aca="1" ref="O29" ca="1">_xlfn.STOCKHISTORY(C29,TODAY(),TODAY(),0,0,1)</f>
+        <v>717.5</v>
+      </c>
+      <c r="P29" s="12">
+        <f ca="1">IFERROR(O29*E29,G29)</f>
+        <v>7.1749999999999995E-17</v>
+      </c>
+      <c r="Q29" s="12">
+        <f ca="1">P29-G29</f>
+        <v>1.7179999999999966E-18</v>
+      </c>
+      <c r="R29" s="12">
         <f t="shared" si="4"/>
         <v>601.49446019067261</v>
       </c>
-      <c r="O29" s="12">
+      <c r="S29" s="12">
         <f t="shared" si="5"/>
         <v>143.6356320000001</v>
       </c>
-      <c r="P29" s="12">
+      <c r="T29" s="12">
         <f t="shared" si="6"/>
         <v>-49.412769904663719</v>
       </c>
-      <c r="Q29" s="14">
+      <c r="U29" s="14">
         <f t="shared" si="7"/>
         <v>94.222862095336382</v>
       </c>
-      <c r="R29" s="12">
+      <c r="V29" s="12">
         <f t="shared" si="8"/>
         <v>66.049311970908661</v>
       </c>
-      <c r="S29" s="9">
+      <c r="W29" s="9">
         <f t="shared" si="9"/>
-        <v>1.5140203132478484E-2</v>
-      </c>
-      <c r="T29" s="9">
+        <v>1.5140203132478486E-2</v>
+      </c>
+      <c r="X29" s="9">
         <f t="shared" si="10"/>
         <v>0.376956090535435</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -4740,46 +7003,62 @@
       </c>
       <c r="K30" s="9">
         <f t="shared" si="2"/>
-        <v>8.1207981305668323E-2</v>
-      </c>
-      <c r="L30" s="12">
+        <v>1.0160701067325602</v>
+      </c>
+      <c r="L30" s="9">
         <f t="shared" si="11"/>
+        <v>7.1711477999999992E-18</v>
+      </c>
+      <c r="M30" s="12">
+        <f t="shared" si="12"/>
         <v>227.99780899999999</v>
       </c>
-      <c r="M30" s="12">
+      <c r="N30" s="12">
         <f t="shared" si="3"/>
         <v>2.2799780899999998E-17</v>
       </c>
-      <c r="N30" s="12">
+      <c r="O30" s="12" cm="1" vm="26">
+        <f t="array" aca="1" ref="O30" ca="1">_xlfn.STOCKHISTORY(C30,TODAY(),TODAY(),0,0,1)</f>
+        <v>139.22999999999999</v>
+      </c>
+      <c r="P30" s="12">
+        <f ca="1">IFERROR(O30*E30,G30)</f>
+        <v>1.3922999999999999E-17</v>
+      </c>
+      <c r="Q30" s="12">
+        <f ca="1">P30-G30</f>
+        <v>-7.7800000000000002E-19</v>
+      </c>
+      <c r="R30" s="12">
         <f t="shared" si="4"/>
         <v>156.91108976411567</v>
       </c>
-      <c r="O30" s="12">
+      <c r="S30" s="12">
         <f t="shared" si="5"/>
         <v>80.987808999999999</v>
       </c>
-      <c r="P30" s="12">
+      <c r="T30" s="12">
         <f t="shared" si="6"/>
         <v>4.9505448820578408</v>
       </c>
-      <c r="Q30" s="14">
+      <c r="U30" s="14">
         <f t="shared" si="7"/>
         <v>85.938353882057839</v>
       </c>
-      <c r="R30" s="12">
+      <c r="V30" s="12">
         <f t="shared" si="8"/>
         <v>74.333820184187203</v>
       </c>
-      <c r="S30" s="9">
+      <c r="W30" s="9">
         <f t="shared" si="9"/>
         <v>1.3452826688069595E-2</v>
       </c>
-      <c r="T30" s="9">
+      <c r="X30" s="9">
         <f t="shared" si="10"/>
         <v>0.42423736773422943</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -4816,46 +7095,62 @@
       </c>
       <c r="K31" s="9">
         <f t="shared" si="2"/>
-        <v>3.8067066046514005E-2</v>
-      </c>
-      <c r="L31" s="12">
+        <v>0.47629318250492114</v>
+      </c>
+      <c r="L31" s="9">
         <f t="shared" si="11"/>
+        <v>6.8548831999999995E-18</v>
+      </c>
+      <c r="M31" s="12">
+        <f t="shared" si="12"/>
         <v>205.62956199999999</v>
       </c>
-      <c r="M31" s="12">
+      <c r="N31" s="12">
         <f t="shared" si="3"/>
         <v>2.0562956199999998E-17</v>
       </c>
-      <c r="N31" s="12">
+      <c r="O31" s="12" cm="1" vm="27">
+        <f t="array" aca="1" ref="O31" ca="1">_xlfn.STOCKHISTORY(C31,TODAY(),TODAY(),0,0,1)</f>
+        <v>174.06</v>
+      </c>
+      <c r="P31" s="12">
+        <f ca="1">IFERROR(O31*E31,G31)</f>
+        <v>1.7406000000000001E-17</v>
+      </c>
+      <c r="Q31" s="12">
+        <f ca="1">P31-G31</f>
+        <v>4.720000000000018E-19</v>
+      </c>
+      <c r="R31" s="12">
         <f t="shared" si="4"/>
         <v>142.2427551448971</v>
       </c>
-      <c r="O31" s="12">
+      <c r="S31" s="12">
         <f t="shared" si="5"/>
         <v>36.289561999999989</v>
       </c>
-      <c r="P31" s="12">
+      <c r="T31" s="12">
         <f t="shared" si="6"/>
         <v>-13.54862242755145</v>
       </c>
-      <c r="Q31" s="14">
+      <c r="U31" s="14">
         <f t="shared" si="7"/>
         <v>22.740939572448539</v>
       </c>
-      <c r="R31" s="12">
+      <c r="V31" s="12">
         <f t="shared" si="8"/>
         <v>137.53123449379649</v>
       </c>
-      <c r="S31" s="9">
+      <c r="W31" s="9">
         <f t="shared" si="9"/>
-        <v>7.2710755755275814E-3</v>
-      </c>
-      <c r="T31" s="9">
+        <v>7.2710755755275806E-3</v>
+      </c>
+      <c r="X31" s="9">
         <f t="shared" si="10"/>
         <v>0.78491713137190566</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -4892,46 +7187,62 @@
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>2.6537727741491979E-2</v>
-      </c>
-      <c r="L32" s="12">
+        <v>0.33203869158184923</v>
+      </c>
+      <c r="L32" s="9">
         <f t="shared" si="11"/>
+        <v>2.3420195999999997E-18</v>
+      </c>
+      <c r="M32" s="12">
+        <f t="shared" si="12"/>
         <v>122.223438</v>
       </c>
-      <c r="M32" s="12">
+      <c r="N32" s="12">
         <f t="shared" si="3"/>
         <v>1.2222343799999999E-17</v>
       </c>
-      <c r="N32" s="12">
+      <c r="O32" s="12" cm="1" vm="28">
+        <f t="array" aca="1" ref="O32" ca="1">_xlfn.STOCKHISTORY(C32,TODAY(),TODAY(),0,0,1)</f>
+        <v>111.79</v>
+      </c>
+      <c r="P32" s="12">
+        <f ca="1">IFERROR(O32*E32,G32)</f>
+        <v>1.1179E-17</v>
+      </c>
+      <c r="Q32" s="12">
+        <f ca="1">P32-G32</f>
+        <v>-1.7899999999999882E-19</v>
+      </c>
+      <c r="R32" s="12">
         <f t="shared" si="4"/>
         <v>100.50438014335016</v>
       </c>
-      <c r="O32" s="12">
+      <c r="S32" s="12">
         <f t="shared" si="5"/>
         <v>8.6434380000000033</v>
       </c>
-      <c r="P32" s="12">
+      <c r="T32" s="12">
         <f t="shared" si="6"/>
         <v>-6.5378099283249185</v>
       </c>
-      <c r="Q32" s="14">
+      <c r="U32" s="14">
         <f t="shared" si="7"/>
         <v>2.1056280716750848</v>
       </c>
-      <c r="R32" s="12">
+      <c r="V32" s="12">
         <f t="shared" si="8"/>
         <v>158.16654599456996</v>
       </c>
-      <c r="S32" s="9">
+      <c r="W32" s="9">
         <f t="shared" si="9"/>
-        <v>6.3224495022754755E-3</v>
-      </c>
-      <c r="T32" s="9">
+        <v>6.3224495022754764E-3</v>
+      </c>
+      <c r="X32" s="9">
         <f t="shared" si="10"/>
         <v>0.9026868116032235</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -4968,46 +7279,62 @@
       </c>
       <c r="K33" s="9">
         <f t="shared" si="2"/>
-        <v>5.7555657366290279E-2</v>
-      </c>
-      <c r="L33" s="12">
+        <v>0.7201334398783692</v>
+      </c>
+      <c r="L33" s="9">
         <f t="shared" si="11"/>
+        <v>4.5495449999999992E-18</v>
+      </c>
+      <c r="M33" s="12">
+        <f t="shared" si="12"/>
         <v>100.765665</v>
       </c>
-      <c r="M33" s="12">
+      <c r="N33" s="12">
         <f t="shared" si="3"/>
         <v>1.0076566499999999E-17</v>
       </c>
-      <c r="N33" s="12">
+      <c r="O33" s="12" cm="1" vm="29">
+        <f t="array" aca="1" ref="O33" ca="1">_xlfn.STOCKHISTORY(C33,TODAY(),TODAY(),0,0,1)</f>
+        <v>112.06</v>
+      </c>
+      <c r="P33" s="12">
+        <f ca="1">IFERROR(O33*E33,G33)</f>
+        <v>1.1206E-17</v>
+      </c>
+      <c r="Q33" s="12">
+        <f ca="1">P33-G33</f>
+        <v>4.771000000000001E-18</v>
+      </c>
+      <c r="R33" s="12">
         <f t="shared" si="4"/>
         <v>56.392954167031817</v>
       </c>
-      <c r="O33" s="12">
+      <c r="S33" s="12">
         <f t="shared" si="5"/>
         <v>36.415665000000004</v>
       </c>
-      <c r="P33" s="12">
+      <c r="T33" s="12">
         <f t="shared" si="6"/>
         <v>-3.9785229164840885</v>
       </c>
-      <c r="Q33" s="14">
+      <c r="U33" s="14">
         <f t="shared" si="7"/>
         <v>32.437142083515916</v>
       </c>
-      <c r="R33" s="12">
+      <c r="V33" s="12">
         <f t="shared" si="8"/>
         <v>127.83503198272913</v>
       </c>
-      <c r="S33" s="9">
+      <c r="W33" s="9">
         <f t="shared" si="9"/>
-        <v>7.8225818423161408E-3</v>
-      </c>
-      <c r="T33" s="9">
+        <v>7.822581842316139E-3</v>
+      </c>
+      <c r="X33" s="9">
         <f t="shared" si="10"/>
         <v>0.7295790440770421</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -5044,46 +7371,62 @@
       </c>
       <c r="K34" s="9">
         <f t="shared" si="2"/>
-        <v>1.2085968057476818E-3</v>
-      </c>
-      <c r="L34" s="12">
+        <v>1.5121901390337388E-2</v>
+      </c>
+      <c r="L34" s="9">
         <f t="shared" si="11"/>
+        <v>1.474056E-18</v>
+      </c>
+      <c r="M34" s="12">
+        <f t="shared" si="12"/>
         <v>21.067758000000001</v>
       </c>
-      <c r="M34" s="12">
+      <c r="N34" s="12">
         <f t="shared" si="3"/>
         <v>2.1067757999999999E-18</v>
       </c>
-      <c r="N34" s="12">
+      <c r="O34" s="12" cm="1" vm="30">
+        <f t="array" aca="1" ref="O34" ca="1">_xlfn.STOCKHISTORY(C34,TODAY(),TODAY(),0,0,1)</f>
+        <v>23.2</v>
+      </c>
+      <c r="P34" s="12">
+        <f ca="1">IFERROR(O34*E34,G34)</f>
+        <v>2.32E-18</v>
+      </c>
+      <c r="Q34" s="12">
+        <f ca="1">P34-G34</f>
+        <v>2.3799999999999981E-19</v>
+      </c>
+      <c r="R34" s="12">
         <f t="shared" si="4"/>
         <v>12.275219621484583</v>
       </c>
-      <c r="O34" s="12">
+      <c r="S34" s="12">
         <f t="shared" si="5"/>
         <v>0.24775800000000103</v>
       </c>
-      <c r="P34" s="12">
+      <c r="T34" s="12">
         <f t="shared" si="6"/>
         <v>-4.2723901892577087</v>
       </c>
-      <c r="Q34" s="14">
+      <c r="U34" s="14">
         <f t="shared" si="7"/>
         <v>-4.0246321892577077</v>
       </c>
-      <c r="R34" s="12">
+      <c r="V34" s="12">
         <f t="shared" si="8"/>
         <v>164.29680625550276</v>
       </c>
-      <c r="S34" s="9">
+      <c r="W34" s="9">
         <f t="shared" si="9"/>
         <v>6.0865455804714232E-3</v>
       </c>
-      <c r="T34" s="9">
+      <c r="X34" s="9">
         <f t="shared" si="10"/>
         <v>0.93767338259042421</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -5120,46 +7463,62 @@
       </c>
       <c r="K35" s="9">
         <f t="shared" si="2"/>
-        <v>8.128259880300007E-3</v>
-      </c>
-      <c r="L35" s="12">
+        <v>0.10170037170410422</v>
+      </c>
+      <c r="L35" s="9">
         <f t="shared" si="11"/>
+        <v>5.5602559999999997E-19</v>
+      </c>
+      <c r="M35" s="12">
+        <f t="shared" si="12"/>
         <v>13.668528</v>
       </c>
-      <c r="M35" s="12">
+      <c r="N35" s="12">
         <f t="shared" si="3"/>
         <v>1.3668528E-18</v>
       </c>
-      <c r="N35" s="12">
+      <c r="O35" s="12" cm="1" vm="31">
+        <f t="array" aca="1" ref="O35" ca="1">_xlfn.STOCKHISTORY(C35,TODAY(),TODAY(),0,0,1)</f>
+        <v>18.309999999999999</v>
+      </c>
+      <c r="P35" s="12">
+        <f ca="1">IFERROR(O35*E35,G35)</f>
+        <v>1.8309999999999997E-18</v>
+      </c>
+      <c r="Q35" s="12">
+        <f ca="1">P35-G35</f>
+        <v>5.2699999999999978E-19</v>
+      </c>
+      <c r="R35" s="12">
         <f t="shared" si="4"/>
         <v>9.4616166013640974</v>
       </c>
-      <c r="O35" s="12">
+      <c r="S35" s="12">
         <f t="shared" si="5"/>
         <v>0.62852800000000109</v>
       </c>
-      <c r="P35" s="12">
+      <c r="T35" s="12">
         <f t="shared" si="6"/>
         <v>-1.7891916993179509</v>
       </c>
-      <c r="Q35" s="14">
+      <c r="U35" s="14">
         <f t="shared" si="7"/>
         <v>-1.1606636993179498</v>
       </c>
-      <c r="R35" s="12">
+      <c r="V35" s="12">
         <f t="shared" si="8"/>
         <v>161.43283776556299</v>
       </c>
-      <c r="S35" s="9">
+      <c r="W35" s="9">
         <f t="shared" si="9"/>
-        <v>6.1945265525978439E-3</v>
-      </c>
-      <c r="T35" s="9">
+        <v>6.1945265525978448E-3</v>
+      </c>
+      <c r="X35" s="9">
         <f t="shared" si="10"/>
         <v>0.92132816515863825</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -5196,46 +7555,62 @@
       </c>
       <c r="K36" s="9">
         <f t="shared" si="2"/>
-        <v>-1.3093076553913688E-2</v>
-      </c>
-      <c r="L36" s="12">
+        <v>-0.16381990387765097</v>
+      </c>
+      <c r="L36" s="9">
         <f t="shared" si="11"/>
+        <v>6.4023700000000011E-19</v>
+      </c>
+      <c r="M36" s="12">
+        <f t="shared" si="12"/>
         <v>9.8842250000000007</v>
       </c>
-      <c r="M36" s="12">
+      <c r="N36" s="12">
         <f t="shared" si="3"/>
         <v>9.8842250000000007E-19</v>
       </c>
-      <c r="N36" s="12">
+      <c r="O36" s="12" cm="1" vm="32">
+        <f t="array" aca="1" ref="O36" ca="1">_xlfn.STOCKHISTORY(C36,TODAY(),TODAY(),0,0,1)</f>
+        <v>11.05</v>
+      </c>
+      <c r="P36" s="12">
+        <f ca="1">IFERROR(O36*E36,G36)</f>
+        <v>1.1050000000000001E-18</v>
+      </c>
+      <c r="Q36" s="12">
+        <f ca="1">P36-G36</f>
+        <v>0</v>
+      </c>
+      <c r="R36" s="12">
         <f t="shared" si="4"/>
         <v>6.5582527152946763</v>
       </c>
-      <c r="O36" s="12">
+      <c r="S36" s="12">
         <f t="shared" si="5"/>
         <v>-1.165775</v>
       </c>
-      <c r="P36" s="12">
+      <c r="T36" s="12">
         <f t="shared" si="6"/>
         <v>-2.2458736423526622</v>
       </c>
-      <c r="Q36" s="14">
+      <c r="U36" s="14">
         <f t="shared" si="7"/>
         <v>-3.4116486423526622</v>
       </c>
-      <c r="R36" s="12">
+      <c r="V36" s="12">
         <f t="shared" si="8"/>
         <v>163.68382270859772</v>
       </c>
-      <c r="S36" s="9">
+      <c r="W36" s="9">
         <f t="shared" si="9"/>
-        <v>6.1093392337266917E-3</v>
-      </c>
-      <c r="T36" s="9">
+        <v>6.1093392337266909E-3</v>
+      </c>
+      <c r="X36" s="9">
         <f t="shared" si="10"/>
         <v>0.93417496792857824</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -5247,7 +7622,7 @@
       </c>
       <c r="D37" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45683</v>
+        <v>45687</v>
       </c>
       <c r="E37" s="2">
         <v>9.9999999999999998E-20</v>
@@ -5273,46 +7648,62 @@
       </c>
       <c r="K37" s="9">
         <f t="shared" si="2"/>
-        <v>4.2563889229249467E-2</v>
-      </c>
-      <c r="L37" s="12">
+        <v>0.53255720406754736</v>
+      </c>
+      <c r="L37" s="9">
         <f t="shared" si="11"/>
+        <v>4.0128627000000008E-17</v>
+      </c>
+      <c r="M37" s="12">
+        <f t="shared" si="12"/>
         <v>2980.43514</v>
       </c>
-      <c r="M37" s="12">
+      <c r="N37" s="12">
         <f t="shared" si="3"/>
         <v>2.98043514E-16</v>
       </c>
-      <c r="N37" s="12">
+      <c r="O37" s="12" cm="1" vm="33">
+        <f t="array" aca="1" ref="O37" ca="1">_xlfn.STOCKHISTORY(C37,TODAY(),TODAY(),0,0,1)</f>
+        <v>0.78559999999999997</v>
+      </c>
+      <c r="P37" s="12">
+        <f ca="1">IFERROR(O37*E37,G37)</f>
+        <v>7.8559999999999989E-20</v>
+      </c>
+      <c r="Q37" s="12">
+        <f ca="1">P37-G37</f>
+        <v>-2.7421144000000001E-16</v>
+      </c>
+      <c r="R37" s="12">
         <f t="shared" si="4"/>
         <v>2588.3740681324903</v>
       </c>
-      <c r="O37" s="12">
+      <c r="S37" s="12">
         <f t="shared" si="5"/>
         <v>237.53513999999996</v>
       </c>
-      <c r="P37" s="12">
+      <c r="T37" s="12">
         <f t="shared" si="6"/>
         <v>-77.262965933754913</v>
       </c>
-      <c r="Q37" s="14">
+      <c r="U37" s="14">
         <f t="shared" si="7"/>
         <v>160.27217406624504</v>
       </c>
-      <c r="R37" s="12">
+      <c r="V37" s="12">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S37" s="9">
+      <c r="W37" s="9">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T37" s="9">
+      <c r="X37" s="9">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -5349,46 +7740,62 @@
       </c>
       <c r="K38" s="9">
         <f t="shared" si="2"/>
-        <v>5.0041145852317261E-2</v>
-      </c>
-      <c r="L38" s="12">
+        <v>0.62611225632861045</v>
+      </c>
+      <c r="L38" s="9">
         <f t="shared" si="11"/>
+        <v>1.8255279999999995E-18</v>
+      </c>
+      <c r="M38" s="12">
+        <f t="shared" si="12"/>
         <v>99.304220000000001</v>
       </c>
-      <c r="M38" s="12">
+      <c r="N38" s="12">
         <f t="shared" si="3"/>
         <v>9.9304219999999992E-18</v>
       </c>
-      <c r="N38" s="12">
+      <c r="O38" s="12" cm="1" vm="34">
+        <f t="array" aca="1" ref="O38" ca="1">_xlfn.STOCKHISTORY(C38,TODAY(),TODAY(),0,0,1)</f>
+        <v>104</v>
+      </c>
+      <c r="P38" s="12">
+        <f ca="1">IFERROR(O38*E38,G38)</f>
+        <v>1.04E-17</v>
+      </c>
+      <c r="Q38" s="12">
+        <f ca="1">P38-G38</f>
+        <v>1.7400000000000015E-18</v>
+      </c>
+      <c r="R38" s="12">
         <f t="shared" si="4"/>
         <v>81.383328634526833</v>
       </c>
-      <c r="O38" s="12">
+      <c r="S38" s="12">
         <f t="shared" si="5"/>
         <v>12.704220000000007</v>
       </c>
-      <c r="P38" s="12">
+      <c r="T38" s="12">
         <f t="shared" si="6"/>
         <v>-2.6083356827365805</v>
       </c>
-      <c r="Q38" s="14">
+      <c r="U38" s="14">
         <f t="shared" si="7"/>
         <v>10.095884317263426</v>
       </c>
-      <c r="R38" s="12">
+      <c r="V38" s="12">
         <f t="shared" si="8"/>
         <v>150.17628974898162</v>
       </c>
-      <c r="S38" s="9">
+      <c r="W38" s="9">
         <f t="shared" si="9"/>
-        <v>6.6588407642211135E-3</v>
-      </c>
-      <c r="T38" s="9">
+        <v>6.6588407642211127E-3</v>
+      </c>
+      <c r="X38" s="9">
         <f t="shared" si="10"/>
         <v>0.8570848868164832</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -5425,46 +7832,62 @@
       </c>
       <c r="K39" s="9">
         <f t="shared" si="2"/>
-        <v>7.2848127105758817E-4</v>
-      </c>
-      <c r="L39" s="12">
+        <v>9.1147203875204513E-3</v>
+      </c>
+      <c r="L39" s="9">
         <f t="shared" si="11"/>
+        <v>2.2663199999999999E-18</v>
+      </c>
+      <c r="M39" s="12">
+        <f t="shared" si="12"/>
         <v>56.229599999999998</v>
       </c>
-      <c r="M39" s="12">
+      <c r="N39" s="12">
         <f t="shared" si="3"/>
         <v>5.6229599999999995E-18</v>
       </c>
-      <c r="N39" s="12">
+      <c r="O39" s="12" cm="1" vm="35">
+        <f t="array" aca="1" ref="O39" ca="1">_xlfn.STOCKHISTORY(C39,TODAY(),TODAY(),0,0,1)</f>
+        <v>66.66</v>
+      </c>
+      <c r="P39" s="12">
+        <f ca="1">IFERROR(O39*E39,G39)</f>
+        <v>6.6659999999999998E-18</v>
+      </c>
+      <c r="Q39" s="12">
+        <f ca="1">P39-G39</f>
+        <v>1.0660000000000003E-18</v>
+      </c>
+      <c r="R39" s="12">
         <f t="shared" si="4"/>
         <v>39.98286448664858</v>
       </c>
-      <c r="O39" s="12">
+      <c r="S39" s="12">
         <f t="shared" si="5"/>
         <v>0.22959999999999781</v>
       </c>
-      <c r="P39" s="12">
+      <c r="T39" s="12">
         <f t="shared" si="6"/>
         <v>-8.0085677566757099</v>
       </c>
-      <c r="Q39" s="14">
+      <c r="U39" s="14">
         <f t="shared" si="7"/>
         <v>-7.7789677566757121</v>
       </c>
-      <c r="R39" s="12">
+      <c r="V39" s="12">
         <f t="shared" si="8"/>
         <v>168.05114182292075</v>
       </c>
-      <c r="S39" s="9">
+      <c r="W39" s="9">
         <f t="shared" si="9"/>
-        <v>5.950569506119289E-3</v>
-      </c>
-      <c r="T39" s="9">
+        <v>5.9505695061192881E-3</v>
+      </c>
+      <c r="X39" s="9">
         <f t="shared" si="10"/>
         <v>0.95910009569040855</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -5501,46 +7924,62 @@
       </c>
       <c r="K40" s="9">
         <f t="shared" si="2"/>
-        <v>1.7403035245984404E-2</v>
-      </c>
-      <c r="L40" s="12">
+        <v>0.21774588649482446</v>
+      </c>
+      <c r="L40" s="9">
         <f t="shared" si="11"/>
+        <v>2.1845000000000003E-19</v>
+      </c>
+      <c r="M40" s="12">
+        <f t="shared" si="12"/>
         <v>17.528699999999997</v>
       </c>
-      <c r="M40" s="12">
+      <c r="N40" s="12">
         <f t="shared" si="3"/>
         <v>1.7528699999999997E-18</v>
       </c>
-      <c r="N40" s="12">
+      <c r="O40" s="12" cm="1" vm="36">
+        <f t="array" aca="1" ref="O40" ca="1">_xlfn.STOCKHISTORY(C40,TODAY(),TODAY(),0,0,1)</f>
+        <v>20.431999999999999</v>
+      </c>
+      <c r="P40" s="12">
+        <f ca="1">IFERROR(O40*E40,G40)</f>
+        <v>2.0431999999999997E-18</v>
+      </c>
+      <c r="Q40" s="12">
+        <f ca="1">P40-G40</f>
+        <v>3.4319999999999965E-19</v>
+      </c>
+      <c r="R40" s="12">
         <f t="shared" si="4"/>
         <v>15.491160925824675</v>
       </c>
-      <c r="O40" s="12">
+      <c r="S40" s="12">
         <f t="shared" si="5"/>
         <v>0.52869999999999706</v>
       </c>
-      <c r="P40" s="12">
+      <c r="T40" s="12">
         <f t="shared" si="6"/>
         <v>-0.75441953708766274</v>
       </c>
-      <c r="Q40" s="14">
+      <c r="U40" s="14">
         <f t="shared" si="7"/>
         <v>-0.22571953708766568</v>
       </c>
-      <c r="R40" s="12">
+      <c r="V40" s="12">
         <f t="shared" si="8"/>
         <v>160.4978936033327</v>
       </c>
-      <c r="S40" s="9">
+      <c r="W40" s="9">
         <f t="shared" si="9"/>
-        <v>6.2306113653521206E-3</v>
-      </c>
-      <c r="T40" s="9">
+        <v>6.2306113653521197E-3</v>
+      </c>
+      <c r="X40" s="9">
         <f t="shared" si="10"/>
         <v>0.91599225951864482</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5577,46 +8016,62 @@
       </c>
       <c r="K41" s="9">
         <f t="shared" si="2"/>
-        <v>1.6849361907902614E-2</v>
-      </c>
-      <c r="L41" s="12">
+        <v>0.21081835401987956</v>
+      </c>
+      <c r="L41" s="9">
         <f t="shared" si="11"/>
+        <v>1.7241911999999999E-18</v>
+      </c>
+      <c r="M41" s="12">
+        <f t="shared" si="12"/>
         <v>51.460183999999998</v>
       </c>
-      <c r="M41" s="12">
+      <c r="N41" s="12">
         <f t="shared" si="3"/>
         <v>5.1460184E-18</v>
       </c>
-      <c r="N41" s="12">
+      <c r="O41" s="12" cm="1" vm="37">
+        <f t="array" aca="1" ref="O41" ca="1">_xlfn.STOCKHISTORY(C41,TODAY(),TODAY(),0,0,1)</f>
+        <v>47.29</v>
+      </c>
+      <c r="P41" s="12">
+        <f ca="1">IFERROR(O41*E41,G41)</f>
+        <v>4.729E-18</v>
+      </c>
+      <c r="Q41" s="12">
+        <f ca="1">P41-G41</f>
+        <v>-1.2999999999999854E-20</v>
+      </c>
+      <c r="R41" s="12">
         <f t="shared" si="4"/>
         <v>37.093241551939926</v>
       </c>
-      <c r="O41" s="12">
+      <c r="S41" s="12">
         <f t="shared" si="5"/>
         <v>4.0401839999999964</v>
       </c>
-      <c r="P41" s="12">
+      <c r="T41" s="12">
         <f t="shared" si="6"/>
         <v>-5.163379224030038</v>
       </c>
-      <c r="Q41" s="14">
+      <c r="U41" s="14">
         <f t="shared" si="7"/>
         <v>-1.1231952240300416</v>
       </c>
-      <c r="R41" s="12">
+      <c r="V41" s="12">
         <f t="shared" si="8"/>
         <v>161.39536929027508</v>
       </c>
-      <c r="S41" s="9">
+      <c r="W41" s="9">
         <f t="shared" si="9"/>
-        <v>6.195964632674595E-3</v>
-      </c>
-      <c r="T41" s="9">
+        <v>6.1959646326745959E-3</v>
+      </c>
+      <c r="X41" s="9">
         <f t="shared" si="10"/>
         <v>0.92111432538436366</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -5648,51 +8103,67 @@
         <v>0.39029999999999998</v>
       </c>
       <c r="J42" s="9">
-        <f t="shared" ref="J42:J46" si="12">IFERROR(H42/I42,"")</f>
+        <f t="shared" ref="J42:J46" si="13">IFERROR(H42/I42,"")</f>
         <v>0.21393799641301564</v>
       </c>
       <c r="K42" s="9">
         <f t="shared" si="2"/>
-        <v>1.5383517949388522E-2</v>
-      </c>
-      <c r="L42" s="12">
-        <f t="shared" ref="L42:L46" si="13">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
+        <v>0.19247778941731217</v>
+      </c>
+      <c r="L42" s="9">
+        <f t="shared" si="11"/>
+        <v>1.6314539999999997E-18</v>
+      </c>
+      <c r="M42" s="12">
+        <f t="shared" ref="M42:M46" si="14">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
         <v>45.290299999999995</v>
       </c>
-      <c r="M42" s="12">
+      <c r="N42" s="12">
         <f t="shared" si="3"/>
         <v>4.5290299999999995E-18</v>
       </c>
-      <c r="N42" s="12">
-        <f t="shared" ref="N42:N46" si="14">F42/(1+I42-H42)</f>
+      <c r="O42" s="12" cm="1" vm="38">
+        <f t="array" aca="1" ref="O42" ca="1">_xlfn.STOCKHISTORY(C42,TODAY(),TODAY(),0,0,1)</f>
+        <v>38.39</v>
+      </c>
+      <c r="P42" s="12">
+        <f ca="1">IFERROR(O42*E42,G42)</f>
+        <v>3.8390000000000001E-18</v>
+      </c>
+      <c r="Q42" s="12">
+        <f ca="1">P42-G42</f>
+        <v>-3.4099999999999919E-19</v>
+      </c>
+      <c r="R42" s="12">
+        <f t="shared" ref="R42:R46" si="15">F42/(1+I42-H42)</f>
         <v>31.986531986531986</v>
       </c>
-      <c r="O42" s="12">
-        <f t="shared" ref="O42:O46" si="15">L42-F42</f>
+      <c r="S42" s="12">
+        <f t="shared" ref="S42:S46" si="16">M42-F42</f>
         <v>3.4902999999999977</v>
       </c>
-      <c r="P42" s="12">
-        <f t="shared" ref="P42:P46" si="16">0.5*(N42-F42)</f>
+      <c r="T42" s="12">
+        <f t="shared" ref="T42:T46" si="17">0.5*(R42-F42)</f>
         <v>-4.9067340067340055</v>
       </c>
-      <c r="Q42" s="14">
-        <f t="shared" ref="Q42:Q46" si="17">O42+P42</f>
+      <c r="U42" s="14">
+        <f t="shared" ref="U42:U46" si="18">S42+T42</f>
         <v>-1.4164340067340078</v>
       </c>
-      <c r="R42" s="12">
+      <c r="V42" s="12">
         <f t="shared" si="8"/>
         <v>161.68860807297904</v>
       </c>
-      <c r="S42" s="9">
+      <c r="W42" s="9">
         <f t="shared" si="9"/>
-        <v>6.1847276188353633E-3</v>
-      </c>
-      <c r="T42" s="9">
-        <f t="shared" ref="T42:T46" si="18">R42/MAX($R$2:$R$28)</f>
+        <v>6.1847276188353641E-3</v>
+      </c>
+      <c r="X42" s="9">
+        <f t="shared" ref="X42:X46" si="19">V42/MAX($V$2:$V$28)</f>
         <v>0.92278789535538974</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>75</v>
       </c>
@@ -5724,51 +8195,67 @@
         <v>8.8400000000000006E-2</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.25678733031674206</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="2"/>
-        <v>1.8464660655589982E-2</v>
-      </c>
-      <c r="L43" s="12">
-        <f t="shared" si="13"/>
+        <v>0.23102888929707052</v>
+      </c>
+      <c r="L43" s="9">
+        <f t="shared" si="11"/>
+        <v>1.359195968E-18</v>
+      </c>
+      <c r="M43" s="12">
+        <f t="shared" si="14"/>
         <v>157.24544304</v>
       </c>
-      <c r="M43" s="12">
+      <c r="N43" s="12">
         <f t="shared" si="3"/>
         <v>1.5724544303999999E-17</v>
       </c>
-      <c r="N43" s="12">
-        <f t="shared" si="14"/>
+      <c r="O43" s="12" cm="1" vm="39">
+        <f t="array" aca="1" ref="O43" ca="1">_xlfn.STOCKHISTORY(C43,TODAY(),TODAY(),0,0,1)</f>
+        <v>151.47</v>
+      </c>
+      <c r="P43" s="12">
+        <f ca="1">IFERROR(O43*E43,G43)</f>
+        <v>1.5146999999999998E-17</v>
+      </c>
+      <c r="Q43" s="12">
+        <f ca="1">P43-G43</f>
+        <v>-2.28520000000001E-19</v>
+      </c>
+      <c r="R43" s="12">
+        <f t="shared" si="15"/>
         <v>144.27625035188137</v>
       </c>
-      <c r="O43" s="12">
-        <f t="shared" si="15"/>
+      <c r="S43" s="12">
+        <f t="shared" si="16"/>
         <v>3.4902430399999957</v>
       </c>
-      <c r="P43" s="12">
-        <f t="shared" si="16"/>
+      <c r="T43" s="12">
+        <f t="shared" si="17"/>
         <v>-4.7394748240593145</v>
       </c>
-      <c r="Q43" s="14">
-        <f t="shared" si="17"/>
+      <c r="U43" s="14">
+        <f t="shared" si="18"/>
         <v>-1.2492317840593188</v>
       </c>
-      <c r="R43" s="12">
+      <c r="V43" s="12">
         <f t="shared" si="8"/>
         <v>161.52140585030435</v>
       </c>
-      <c r="S43" s="9">
+      <c r="W43" s="9">
         <f t="shared" si="9"/>
-        <v>6.1911298674974715E-3</v>
-      </c>
-      <c r="T43" s="9">
-        <f t="shared" si="18"/>
+        <v>6.1911298674974706E-3</v>
+      </c>
+      <c r="X43" s="9">
+        <f t="shared" si="19"/>
         <v>0.92183364020408631</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -5800,51 +8287,67 @@
         <v>0.25</v>
       </c>
       <c r="J44" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.1636</v>
       </c>
       <c r="K44" s="9">
         <f t="shared" si="2"/>
-        <v>1.1763892243158576E-2</v>
-      </c>
-      <c r="L44" s="12">
-        <f t="shared" si="13"/>
+        <v>0.14718921779505134</v>
+      </c>
+      <c r="L44" s="9">
+        <f t="shared" si="11"/>
+        <v>3.3382499999999999E-18</v>
+      </c>
+      <c r="M44" s="12">
+        <f t="shared" si="14"/>
         <v>138.991377</v>
       </c>
-      <c r="M44" s="12">
+      <c r="N44" s="12">
         <f t="shared" si="3"/>
         <v>1.38991377E-17</v>
       </c>
-      <c r="N44" s="12">
-        <f t="shared" si="14"/>
+      <c r="O44" s="12" cm="1" vm="40">
+        <f t="array" aca="1" ref="O44" ca="1">_xlfn.STOCKHISTORY(C44,TODAY(),TODAY(),0,0,1)</f>
+        <v>150.19999999999999</v>
+      </c>
+      <c r="P44" s="12">
+        <f ca="1">IFERROR(O44*E44,G44)</f>
+        <v>1.5019999999999999E-17</v>
+      </c>
+      <c r="Q44" s="12">
+        <f ca="1">P44-G44</f>
+        <v>1.6669999999999989E-18</v>
+      </c>
+      <c r="R44" s="12">
+        <f t="shared" si="15"/>
         <v>110.4375155074022</v>
       </c>
-      <c r="O44" s="12">
-        <f t="shared" si="15"/>
+      <c r="S44" s="12">
+        <f t="shared" si="16"/>
         <v>5.4613769999999988</v>
       </c>
-      <c r="P44" s="12">
-        <f t="shared" si="16"/>
+      <c r="T44" s="12">
+        <f t="shared" si="17"/>
         <v>-11.546242246298903</v>
       </c>
-      <c r="Q44" s="14">
-        <f t="shared" si="17"/>
+      <c r="U44" s="14">
+        <f t="shared" si="18"/>
         <v>-6.0848652462989037</v>
       </c>
-      <c r="R44" s="12">
+      <c r="V44" s="12">
         <f t="shared" si="8"/>
         <v>166.35703931254395</v>
       </c>
-      <c r="S44" s="9">
+      <c r="W44" s="9">
         <f t="shared" si="9"/>
         <v>6.0111673310153475E-3</v>
       </c>
-      <c r="T44" s="9">
-        <f t="shared" si="18"/>
+      <c r="X44" s="9">
+        <f t="shared" si="19"/>
         <v>0.94943152776408135</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -5876,51 +8379,67 @@
         <v>0.60340000000000005</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.19771295989393436</v>
       </c>
       <c r="K45" s="9">
         <f t="shared" si="2"/>
-        <v>-1.4216833467409396E-2</v>
-      </c>
-      <c r="L45" s="12">
-        <f t="shared" si="13"/>
+        <v>-0.17788029287733836</v>
+      </c>
+      <c r="L45" s="9">
+        <f t="shared" si="11"/>
+        <v>1.6068542000000001E-18</v>
+      </c>
+      <c r="M45" s="12">
+        <f t="shared" si="14"/>
         <v>23.453040999999999</v>
       </c>
-      <c r="M45" s="12">
+      <c r="N45" s="12">
         <f t="shared" si="3"/>
         <v>2.3453040999999998E-18</v>
       </c>
-      <c r="N45" s="12">
-        <f t="shared" si="14"/>
+      <c r="O45" s="12" cm="1" vm="41">
+        <f t="array" aca="1" ref="O45" ca="1">_xlfn.STOCKHISTORY(C45,TODAY(),TODAY(),0,0,1)</f>
+        <v>15.66</v>
+      </c>
+      <c r="P45" s="12">
+        <f ca="1">IFERROR(O45*E45,G45)</f>
+        <v>1.566E-18</v>
+      </c>
+      <c r="Q45" s="12">
+        <f ca="1">P45-G45</f>
+        <v>-1.097E-18</v>
+      </c>
+      <c r="R45" s="12">
+        <f t="shared" si="15"/>
         <v>15.458292215707898</v>
       </c>
-      <c r="O45" s="12">
-        <f t="shared" si="15"/>
+      <c r="S45" s="12">
+        <f t="shared" si="16"/>
         <v>-3.1769590000000001</v>
       </c>
-      <c r="P45" s="12">
-        <f t="shared" si="16"/>
+      <c r="T45" s="12">
+        <f t="shared" si="17"/>
         <v>-5.5858538921460505</v>
       </c>
-      <c r="Q45" s="14">
-        <f t="shared" si="17"/>
+      <c r="U45" s="14">
+        <f t="shared" si="18"/>
         <v>-8.7628128921460515</v>
       </c>
-      <c r="R45" s="12">
+      <c r="V45" s="12">
         <f t="shared" si="8"/>
         <v>169.0349869583911</v>
       </c>
-      <c r="S45" s="9">
+      <c r="W45" s="9">
         <f t="shared" si="9"/>
-        <v>5.9159350261975977E-3</v>
-      </c>
-      <c r="T45" s="9">
-        <f t="shared" si="18"/>
+        <v>5.9159350261975968E-3</v>
+      </c>
+      <c r="X45" s="9">
+        <f t="shared" si="19"/>
         <v>0.96471508856304522</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>96</v>
       </c>
@@ -5952,53 +8471,78 @@
         <v>0.32779999999999998</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.49145820622330688</v>
       </c>
       <c r="K46" s="9">
         <f t="shared" si="2"/>
-        <v>3.533900599038501E-2</v>
-      </c>
-      <c r="L46" s="12">
-        <f t="shared" si="13"/>
+        <v>0.44215983467584091</v>
+      </c>
+      <c r="L46" s="9">
+        <f t="shared" si="11"/>
+        <v>1.0612525E-17</v>
+      </c>
+      <c r="M46" s="12">
+        <f t="shared" si="14"/>
         <v>375.90612500000003</v>
       </c>
-      <c r="M46" s="12">
+      <c r="N46" s="12">
         <f t="shared" si="3"/>
         <v>3.7590612500000005E-17</v>
       </c>
-      <c r="N46" s="12">
-        <f t="shared" si="14"/>
+      <c r="O46" s="12" cm="1" vm="42">
+        <f t="array" aca="1" ref="O46" ca="1">_xlfn.STOCKHISTORY(C46,TODAY(),TODAY(),0,0,1)</f>
+        <v>320.56</v>
+      </c>
+      <c r="P46" s="12">
+        <f ca="1">IFERROR(O46*E46,G46)</f>
+        <v>3.2055999999999996E-17</v>
+      </c>
+      <c r="Q46" s="12">
+        <f ca="1">P46-G46</f>
+        <v>-3.1900000000000578E-19</v>
+      </c>
+      <c r="R46" s="12">
+        <f t="shared" si="15"/>
         <v>277.49207165509563</v>
       </c>
-      <c r="O46" s="12">
-        <f t="shared" si="15"/>
+      <c r="S46" s="12">
+        <f t="shared" si="16"/>
         <v>52.156125000000031</v>
       </c>
-      <c r="P46" s="12">
-        <f t="shared" si="16"/>
+      <c r="T46" s="12">
+        <f t="shared" si="17"/>
         <v>-23.128964172452186</v>
       </c>
-      <c r="Q46" s="14">
-        <f t="shared" si="17"/>
+      <c r="U46" s="14">
+        <f t="shared" si="18"/>
         <v>29.027160827547846</v>
       </c>
-      <c r="R46" s="12">
+      <c r="V46" s="12">
         <f t="shared" si="8"/>
         <v>131.2450132386972</v>
       </c>
-      <c r="S46" s="9">
+      <c r="W46" s="9">
         <f t="shared" si="9"/>
         <v>7.619337110974918E-3</v>
       </c>
-      <c r="T46" s="9">
-        <f t="shared" si="18"/>
+      <c r="X46" s="9">
+        <f t="shared" si="19"/>
         <v>0.74904046108037126</v>
       </c>
     </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="L47" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="S2:S46">
+  <autoFilter ref="A1:X46" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="ETF"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="W2:W46">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
@@ -6037,7 +8581,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>T2:T46</xm:sqref>
+          <xm:sqref>X2:X46</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -6047,269 +8591,328 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E05E8D-08B7-4DF5-A194-73864790DB1A}">
-  <dimension ref="B3:F17"/>
+  <dimension ref="A3:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
         <v>160</v>
       </c>
+      <c r="B3" s="10" t="s">
+        <v>161</v>
+      </c>
       <c r="C3" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="15" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
+      <c r="G3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="12">
-        <v>262.48183799999998</v>
-      </c>
-      <c r="D4" s="24">
-        <v>0.25694241418020713</v>
+      <c r="B4" s="12">
+        <v>283.12183800000003</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0.27415794541660166</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0.22147011693742963</v>
       </c>
       <c r="E4" s="19">
-        <v>3.0923880903333201E-2</v>
+        <v>7.17737579592852E-2</v>
       </c>
       <c r="F4" s="12">
-        <v>8.1169570975999932</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
+        <v>20.320718273599937</v>
+      </c>
+      <c r="G4" s="19">
+        <v>-2.5466209356835242E-2</v>
+      </c>
+      <c r="H4" s="12">
+        <v>-7.2100399999999922</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="12">
-        <v>218.85400000000001</v>
-      </c>
-      <c r="D5" s="24">
-        <v>0.21423529925523863</v>
+      <c r="B5" s="12">
+        <v>222.11800000000002</v>
+      </c>
+      <c r="C5" s="24">
+        <v>0.21508554391358795</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0.1859207718419939</v>
       </c>
       <c r="E5" s="19">
-        <v>2.4999999999999911E-2</v>
+        <v>4.172777532662808E-2</v>
       </c>
       <c r="F5" s="12">
-        <v>5.471350000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
+        <v>9.2684899999999857</v>
+      </c>
+      <c r="G5" s="19">
+        <v>1.5672750519993752E-2</v>
+      </c>
+      <c r="H5" s="12">
+        <v>3.4811999999999728</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="12">
+        <v>220.93703800000003</v>
+      </c>
+      <c r="C6" s="24">
+        <v>0.21394197223496991</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.43949571810951849</v>
+      </c>
+      <c r="E6" s="19">
+        <v>5.3152980643290659E-2</v>
+      </c>
+      <c r="F6" s="12">
+        <v>11.743462104199978</v>
+      </c>
+      <c r="G6" s="19">
+        <v>-2.8620103977314997E-2</v>
+      </c>
+      <c r="H6" s="12">
+        <v>-6.3232409999999959</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="12">
-        <v>198.38494800000001</v>
-      </c>
-      <c r="D6" s="24">
-        <v>0.19419822668315384</v>
-      </c>
-      <c r="E6" s="19">
-        <v>0.11292909843341525</v>
-      </c>
-      <c r="F6" s="12">
-        <v>22.403433320399984</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="12">
-        <v>190.93378000000001</v>
-      </c>
-      <c r="D7" s="24">
-        <v>0.18690430833447821</v>
+      <c r="B7" s="12">
+        <v>155.61477000000002</v>
+      </c>
+      <c r="C7" s="24">
+        <v>0.15068786611817991</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0.29723398558375913</v>
       </c>
       <c r="E7" s="19">
-        <v>0.17775201226100479</v>
+        <v>0.23836726683206222</v>
       </c>
       <c r="F7" s="12">
-        <v>33.938863603599998</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
+        <v>37.093467403599988</v>
+      </c>
+      <c r="G7" s="19">
+        <v>2.2745687957511699E-2</v>
+      </c>
+      <c r="H7" s="12">
+        <v>3.5395649999999534</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="12">
+      <c r="B8" s="12">
         <v>94.882213999999991</v>
       </c>
-      <c r="D8" s="24">
-        <v>9.2879817185381977E-2</v>
+      <c r="C8" s="24">
+        <v>9.1878157582525696E-2</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0.29370539525985345</v>
       </c>
       <c r="E8" s="19">
-        <v>0.13612322763252549</v>
+        <v>0.1541563317040644</v>
       </c>
       <c r="F8" s="12">
-        <v>12.915673214600005</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+        <v>14.62669405420003</v>
+      </c>
+      <c r="G8" s="19">
+        <v>0.12702033913331739</v>
+      </c>
+      <c r="H8" s="12">
+        <v>12.051970999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="12">
+      <c r="B9" s="12">
         <v>46.022978999999999</v>
       </c>
-      <c r="D9" s="24">
-        <v>4.5051708804420124E-2</v>
+      <c r="C9" s="24">
+        <v>4.4565850001974779E-2</v>
+      </c>
+      <c r="D9" s="19">
+        <v>0.25428698387386012</v>
       </c>
       <c r="E9" s="19">
-        <v>0.11663041051514722</v>
+        <v>6.9540324469218096E-2</v>
       </c>
       <c r="F9" s="12">
-        <v>5.3676789339000024</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
+        <v>3.2004528927000067</v>
+      </c>
+      <c r="G9" s="19">
+        <v>-3.7756486819334412E-2</v>
+      </c>
+      <c r="H9" s="12">
+        <v>-1.7376660000000044</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="12">
+      <c r="B10" s="12">
         <v>9.99925</v>
       </c>
-      <c r="D10" s="24">
-        <v>9.7882255571200196E-3</v>
+      <c r="C10" s="24">
+        <v>9.6826647321601317E-3</v>
+      </c>
+      <c r="D10" s="19">
+        <v>0.58609999999999995</v>
       </c>
       <c r="E10" s="19">
-        <v>-1.2800000000000145E-2</v>
+        <v>-0.12680000000000013</v>
       </c>
       <c r="F10" s="12">
-        <v>-0.12799040000000161</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
+        <v>-1.2679049000000013</v>
+      </c>
+      <c r="G10" s="19">
+        <v>-2.1851638872915528E-2</v>
+      </c>
+      <c r="H10" s="12">
+        <v>-0.21850000000000058</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="12">
-        <v>2.9170551999999998E-16</v>
-      </c>
-      <c r="D11" s="24">
-        <v>2.8554935880360874E-19</v>
+      <c r="B11" s="12">
+        <v>2.9136552000000001E-16</v>
+      </c>
+      <c r="C11" s="24">
+        <v>2.8214062501402581E-19</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0.14314072910205713</v>
       </c>
       <c r="E11" s="19">
-        <v>0.14608871182142869</v>
+        <v>8.2904141519559271E-2</v>
       </c>
       <c r="F11" s="12">
-        <v>4.2614883648000013E-17</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="12">
-        <v>2.7429000000000002E-16</v>
-      </c>
-      <c r="D12" s="24">
-        <v>0.94029759875644459</v>
+        <v>2.4155408304000005E-17</v>
+      </c>
+      <c r="G11" s="19">
+        <v>-0.9407316280938115</v>
+      </c>
+      <c r="H11" s="12">
+        <v>-2.7409676E-16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="12">
+        <v>1.3353E-17</v>
+      </c>
+      <c r="C12" s="24">
+        <v>1.2930231984252241E-20</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0.25</v>
       </c>
       <c r="E12" s="19">
-        <v>0.15060000000000007</v>
+        <v>4.0900000000000158E-2</v>
       </c>
       <c r="F12" s="12">
-        <v>4.1308074000000006E-17</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="12">
-        <v>1.5375519999999999E-17</v>
-      </c>
-      <c r="D13" s="24">
-        <v>5.270904712396255E-2</v>
+        <v>5.4613770000000075E-19</v>
+      </c>
+      <c r="G12" s="19">
+        <v>0.12484085973189538</v>
+      </c>
+      <c r="H12" s="12">
+        <v>1.6669999999999989E-18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="12">
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="C13" s="24">
+        <v>5.4226989524311053E-21</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0.4047</v>
       </c>
       <c r="E13" s="19">
-        <v>8.4900000000000198E-2</v>
+        <v>4.0999999999999925E-3</v>
       </c>
       <c r="F13" s="12">
-        <v>1.3053816480000015E-18</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="12">
-        <v>2.0399999999999999E-18</v>
-      </c>
-      <c r="D14" s="24">
-        <v>6.9933541195929374E-3</v>
+        <v>2.2960000000000069E-20</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0.19035714285714295</v>
+      </c>
+      <c r="H13" s="12">
+        <v>1.0660000000000003E-18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" s="12">
+        <v>1032.696089</v>
+      </c>
+      <c r="C14" s="24">
+        <v>1</v>
+      </c>
+      <c r="D14" s="19">
+        <v>0.28351543428262177</v>
       </c>
       <c r="E14" s="19">
-        <v>6.9999999999992291E-4</v>
+        <v>9.1978057087713339E-2</v>
       </c>
       <c r="F14" s="12">
-        <v>1.4279999999996661E-21</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="12">
-        <v>1.3353E-17</v>
-      </c>
-      <c r="D15" s="24">
-        <v>1.3071197926266831E-20</v>
-      </c>
-      <c r="E15" s="19">
-        <v>4.6300000000000008E-2</v>
-      </c>
-      <c r="F15" s="12">
-        <v>6.1824389999999998E-19</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="12">
-        <v>5.5999999999999995E-18</v>
-      </c>
-      <c r="D16" s="24">
-        <v>5.4818174482958324E-21</v>
-      </c>
-      <c r="E16" s="19">
-        <v>-0.30869999999999986</v>
-      </c>
-      <c r="F16" s="12">
-        <v>-1.7287199999999994E-18</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="C17" s="12">
-        <v>1021.5590090000001</v>
-      </c>
-      <c r="D17" s="24">
-        <v>1</v>
-      </c>
-      <c r="E17" s="19">
-        <v>8.6226997162236252E-2</v>
-      </c>
-      <c r="F17" s="12">
-        <v>88.085965770099961</v>
+        <v>94.985379828300211</v>
+      </c>
+      <c r="G14" s="19">
+        <v>3.4698388404566937E-3</v>
+      </c>
+      <c r="H14" s="12">
+        <v>3.5832889999999225</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B37DBF6-F8A0-47DD-8016-20B57B5E55F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C63D74-45BB-4E2C-BE9B-F70462B19001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="63" r:id="rId4"/>
+    <pivotCache cacheId="12" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,21 +44,11 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="42">
+  <futureMetadata name="XLRICHVALUE" count="41">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -346,145 +336,130 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="41"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
-  <cellMetadata count="1">
+  <valueMetadata count="41">
     <bk>
       <rc t="1" v="0"/>
     </bk>
-  </cellMetadata>
-  <valueMetadata count="42">
     <bk>
-      <rc t="2" v="0"/>
+      <rc t="1" v="1"/>
     </bk>
     <bk>
-      <rc t="2" v="1"/>
+      <rc t="1" v="2"/>
     </bk>
     <bk>
-      <rc t="2" v="2"/>
+      <rc t="1" v="3"/>
     </bk>
     <bk>
-      <rc t="2" v="3"/>
+      <rc t="1" v="4"/>
     </bk>
     <bk>
-      <rc t="2" v="4"/>
+      <rc t="1" v="5"/>
     </bk>
     <bk>
-      <rc t="2" v="5"/>
+      <rc t="1" v="6"/>
     </bk>
     <bk>
-      <rc t="2" v="6"/>
+      <rc t="1" v="7"/>
     </bk>
     <bk>
-      <rc t="2" v="7"/>
+      <rc t="1" v="8"/>
     </bk>
     <bk>
-      <rc t="2" v="8"/>
+      <rc t="1" v="9"/>
     </bk>
     <bk>
-      <rc t="2" v="9"/>
+      <rc t="1" v="10"/>
     </bk>
     <bk>
-      <rc t="2" v="10"/>
+      <rc t="1" v="11"/>
     </bk>
     <bk>
-      <rc t="2" v="11"/>
+      <rc t="1" v="12"/>
     </bk>
     <bk>
-      <rc t="2" v="12"/>
+      <rc t="1" v="13"/>
     </bk>
     <bk>
-      <rc t="2" v="13"/>
+      <rc t="1" v="14"/>
     </bk>
     <bk>
-      <rc t="2" v="14"/>
+      <rc t="1" v="15"/>
     </bk>
     <bk>
-      <rc t="2" v="15"/>
+      <rc t="1" v="16"/>
     </bk>
     <bk>
-      <rc t="2" v="16"/>
+      <rc t="1" v="17"/>
     </bk>
     <bk>
-      <rc t="2" v="17"/>
+      <rc t="1" v="18"/>
     </bk>
     <bk>
-      <rc t="2" v="18"/>
+      <rc t="1" v="19"/>
     </bk>
     <bk>
-      <rc t="2" v="19"/>
+      <rc t="1" v="20"/>
     </bk>
     <bk>
-      <rc t="2" v="20"/>
+      <rc t="1" v="21"/>
     </bk>
     <bk>
-      <rc t="2" v="21"/>
+      <rc t="1" v="22"/>
     </bk>
     <bk>
-      <rc t="2" v="22"/>
+      <rc t="1" v="23"/>
     </bk>
     <bk>
-      <rc t="2" v="23"/>
+      <rc t="1" v="24"/>
     </bk>
     <bk>
-      <rc t="2" v="24"/>
+      <rc t="1" v="25"/>
     </bk>
     <bk>
-      <rc t="2" v="25"/>
+      <rc t="1" v="26"/>
     </bk>
     <bk>
-      <rc t="2" v="26"/>
+      <rc t="1" v="27"/>
     </bk>
     <bk>
-      <rc t="2" v="27"/>
+      <rc t="1" v="28"/>
     </bk>
     <bk>
-      <rc t="2" v="28"/>
+      <rc t="1" v="29"/>
     </bk>
     <bk>
-      <rc t="2" v="29"/>
+      <rc t="1" v="30"/>
     </bk>
     <bk>
-      <rc t="2" v="30"/>
+      <rc t="1" v="31"/>
     </bk>
     <bk>
-      <rc t="2" v="31"/>
+      <rc t="1" v="32"/>
     </bk>
     <bk>
-      <rc t="2" v="32"/>
+      <rc t="1" v="33"/>
     </bk>
     <bk>
-      <rc t="2" v="33"/>
+      <rc t="1" v="34"/>
     </bk>
     <bk>
-      <rc t="2" v="34"/>
+      <rc t="1" v="35"/>
     </bk>
     <bk>
-      <rc t="2" v="35"/>
+      <rc t="1" v="36"/>
     </bk>
     <bk>
-      <rc t="2" v="36"/>
+      <rc t="1" v="37"/>
     </bk>
     <bk>
-      <rc t="2" v="37"/>
+      <rc t="1" v="38"/>
     </bk>
     <bk>
-      <rc t="2" v="38"/>
+      <rc t="1" v="39"/>
     </bk>
     <bk>
-      <rc t="2" v="39"/>
-    </bk>
-    <bk>
-      <rc t="2" v="40"/>
-    </bk>
-    <bk>
-      <rc t="2" v="41"/>
+      <rc t="1" v="40"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -1182,12 +1157,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="8">
     <dxf>
-      <alignment vertical="center"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
@@ -1199,109 +1177,10 @@
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1317,17 +1196,17 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" invalid="1" refreshedBy="samuel walton" refreshedDate="45707.909361574071" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{1E74FF3F-FD41-47C6-9554-6AF9D4A04843}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" invalid="1" refreshedBy="samuel walton" refreshedDate="45711.139992824072" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{1E74FF3F-FD41-47C6-9554-6AF9D4A04843}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:X46" sheet="Positions"/>
   </cacheSource>
   <cacheFields count="29">
     <cacheField name="Chapter" numFmtId="0">
       <sharedItems count="10">
+        <s v="Banking"/>
         <s v="Energy"/>
         <s v="ETF"/>
         <s v="US Consumer"/>
-        <s v="Banking"/>
         <s v="Tech"/>
         <s v="Asia Consumer"/>
         <s v="Health"/>
@@ -1340,12 +1219,12 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Ticker" numFmtId="0">
-      <sharedItems count="45">
+      <sharedItems count="46">
+        <s v="ING"/>
         <s v="APA"/>
         <s v="BOTZ.UK"/>
         <s v="BATT.NL"/>
         <s v="ACI"/>
-        <s v="ING"/>
         <s v="MO"/>
         <s v="YPF"/>
         <s v="VWO.US"/>
@@ -1359,15 +1238,15 @@
         <s v="INGR"/>
         <s v="AGIO"/>
         <s v="FSLR"/>
-        <s v="AAPL"/>
         <s v="MSFT"/>
         <s v="MA"/>
         <s v="GOOGL"/>
         <s v="YUM"/>
+        <s v="AAPL"/>
         <s v="MAXN"/>
         <s v="V"/>
         <s v="QCOM"/>
-        <s v="MC.PA"/>
+        <s v="LVMH"/>
         <s v="ASML"/>
         <s v="NVDA"/>
         <s v="AMAT"/>
@@ -1386,13 +1265,14 @@
         <s v="MMM"/>
         <s v="PCG"/>
         <s v="HCA"/>
+        <s v="MC.PA" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Date" numFmtId="165">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-06-17T00:00:00" maxDate="2025-02-01T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-06-17T00:00:00" maxDate="2025-02-04T00:00:00"/>
     </cacheField>
     <cacheField name="Volume" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="2.2953000000000001"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="3.1236000000000002"/>
     </cacheField>
     <cacheField name="Price" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
@@ -1410,10 +1290,10 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.1235147203511693" maxValue="1.1293562935629355"/>
     </cacheField>
     <cacheField name="Mix %" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.0108145040936092" maxValue="1.0160701067325602"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-7.8660767840531068E-2" maxValue="7.9069754590691835E-2"/>
     </cacheField>
     <cacheField name="W/Avg Volatility" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.1845000000000003E-19" maxValue="30.189947772600004"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.1845000000000003E-19" maxValue="32.116701999999997"/>
     </cacheField>
     <cacheField name="Target Price" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="2980.43514"/>
@@ -1422,13 +1302,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="96.802542054400007"/>
     </cacheField>
     <cacheField name="Close Price" numFmtId="44">
-      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0.78559999999999997" maxValue="717.5"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.74750000000000005" maxValue="737.21"/>
     </cacheField>
     <cacheField name="Actual Value" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.8559999999999989E-20" maxValue="92.523564000000007"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.4750000000000002E-20" maxValue="95.489729999999994"/>
     </cacheField>
     <cacheField name="Actual P&amp;L" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-9.4742760000000033" maxValue="8.6620360000000005"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-6.3082209999999961" maxValue="7.2399300000000011"/>
     </cacheField>
     <cacheField name="Tolerance" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.8693047453886176" maxValue="2588.3740681324903"/>
@@ -1440,22 +1320,22 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-77.262965933754913" maxValue="4.9505448820578408"/>
     </cacheField>
     <cacheField name="Balance Risk" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-14.94534762730569" maxValue="160.27217406624504"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-44.701744897959315" maxValue="160.27217406624504"/>
     </cacheField>
     <cacheField name="Normalized Risk" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="175.21752169355074"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="204.97391896420436"/>
     </cacheField>
     <cacheField name="Risk Mix" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1.5480196656953615E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1.5480196656953616E-2"/>
     </cacheField>
     <cacheField name="Normalized Risk %" numFmtId="9">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="TargetReturn%_Metric" numFmtId="0" formula="'Target Value'/Value-1" databaseField="0"/>
     <cacheField name="TargetP&amp;L_metric" numFmtId="0" formula="'Target Value'-Value" databaseField="0"/>
-    <cacheField name="ActualP&amp;L_Metric" numFmtId="0" formula="'Actual Value' -Value" databaseField="0"/>
-    <cacheField name="ActualReturn_Metric" numFmtId="0" formula="'ActualP&amp;L_Metric' /Value" databaseField="0"/>
-    <cacheField name="AvgVolatility_Metric" numFmtId="0" formula="'W/Avg Volatility' /Value" databaseField="0"/>
+    <cacheField name="ActualP&amp;L_Metric" numFmtId="0" formula="'Actual Value'-Value" databaseField="0"/>
+    <cacheField name="ActualReturn_Metric" numFmtId="0" formula="'ActualP&amp;L_Metric'/Value" databaseField="0"/>
+    <cacheField name="AvgVolatility_Metric" numFmtId="0" formula="'W/Avg Volatility'/Value" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -1477,86 +1357,112 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="45">
   <r>
     <x v="0"/>
+    <s v="ING Group NV"/>
+    <x v="0"/>
+    <d v="2024-11-27T00:00:00"/>
+    <n v="3.1236000000000002"/>
+    <n v="16"/>
+    <n v="49.977600000000002"/>
+    <n v="7.0499999999999993E-2"/>
+    <n v="0.35260000000000002"/>
+    <n v="0.19994327850255245"/>
+    <n v="1.3998652199810989E-2"/>
+    <n v="17.622101760000003"/>
+    <n v="17.128"/>
+    <n v="53.501020800000006"/>
+    <n v="17.100000000000001"/>
+    <n v="53.413560000000004"/>
+    <n v="3.4359600000000015"/>
+    <n v="12.479525778020435"/>
+    <n v="1.1280000000000001"/>
+    <n v="-1.7602371109897827"/>
+    <n v="-0.63223711098978264"/>
+    <n v="160.90441117723483"/>
+    <n v="6.2148700130943493E-3"/>
+    <n v="0.78499943793012217"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="APA"/>
-    <x v="0"/>
+    <x v="1"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="2.2953000000000001"/>
     <n v="21.78"/>
     <n v="49.991634000000005"/>
-    <n v="-8.7400000000000005E-2"/>
-    <n v="0.60389999999999999"/>
-    <n v="-0.14472594800463653"/>
-    <n v="-0.13020842959321346"/>
-    <n v="30.189947772600004"/>
-    <n v="19.876428000000001"/>
-    <n v="45.622365188400003"/>
-    <n v="23.59"/>
-    <n v="54.146127"/>
-    <n v="4.1544929999999951"/>
-    <n v="12.877668065984748"/>
-    <n v="-1.9035720000000005"/>
-    <n v="-4.4511659670076265"/>
-    <n v="-6.3547379670076269"/>
-    <n v="166.62691203325267"/>
-    <n v="6.0014315082574203E-3"/>
-    <n v="0.95097174313809352"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="Robotics &amp; AI"/>
-    <x v="1"/>
-    <d v="2024-07-08T00:00:00"/>
-    <n v="2"/>
-    <n v="22.56"/>
-    <n v="45.12"/>
     <n v="3.5000000000000003E-2"/>
     <n v="0.16500000000000001"/>
     <n v="0.21212121212121213"/>
-    <n v="0.19084324749302797"/>
-    <n v="7.4447999999999999"/>
-    <n v="23.349599999999995"/>
-    <n v="46.69919999999999"/>
-    <n v="22.65"/>
-    <n v="45.3"/>
-    <n v="0.17999999999999972"/>
-    <n v="19.9646017699115"/>
-    <n v="0.78959999999999653"/>
-    <n v="-1.2976991150442494"/>
-    <n v="-0.50809911504425287"/>
-    <n v="160.78027318128929"/>
-    <n v="6.2196684967218627E-3"/>
-    <n v="0.91760385392556976"/>
+    <n v="1.4851267294035455E-2"/>
+    <n v="8.2486196100000004"/>
+    <n v="22.542300000000001"/>
+    <n v="51.741341190000007"/>
+    <n v="22.79"/>
+    <n v="52.309887000000003"/>
+    <n v="2.3182529999999986"/>
+    <n v="19.274336283185839"/>
+    <n v="0.76229999999999976"/>
+    <n v="-1.252831858407081"/>
+    <n v="-0.49053185840708124"/>
+    <n v="160.76270592465212"/>
+    <n v="6.2203481475902132E-3"/>
+    <n v="0.78430810484102098"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
+    <s v="Robotics &amp; AI"/>
+    <x v="2"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="2"/>
+    <n v="20.927"/>
+    <n v="41.853999999999999"/>
+    <n v="3.5000000000000003E-2"/>
+    <n v="0.16500000000000001"/>
+    <n v="0.21212121212121213"/>
+    <n v="1.4851267294035455E-2"/>
+    <n v="6.9059100000000004"/>
+    <n v="21.659444999999998"/>
+    <n v="43.318889999999996"/>
+    <n v="22.41"/>
+    <n v="44.82"/>
+    <n v="2.9660000000000011"/>
+    <n v="18.51946902654867"/>
+    <n v="0.73244499999999846"/>
+    <n v="-1.2037654867256649"/>
+    <n v="-0.4713204867256664"/>
+    <n v="160.7434945529707"/>
+    <n v="6.2210915768691616E-3"/>
+    <n v="0.78421437890857792"/>
+  </r>
+  <r>
+    <x v="2"/>
     <s v="Batterey Value-Chain"/>
-    <x v="2"/>
+    <x v="3"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="2"/>
     <n v="16.399000000000001"/>
     <n v="32.798000000000002"/>
-    <n v="3.5000000000000003E-2"/>
-    <n v="0.16500000000000001"/>
-    <n v="0.21212121212121213"/>
-    <n v="0.19084324749302797"/>
-    <n v="5.4116700000000009"/>
-    <n v="16.972964999999999"/>
-    <n v="33.945929999999997"/>
-    <n v="16.874600000000001"/>
-    <n v="33.749200000000002"/>
-    <n v="0.95120000000000005"/>
-    <n v="14.512389380530973"/>
-    <n v="0.57396499999999762"/>
-    <n v="-0.9433053097345141"/>
-    <n v="-0.36934030973451648"/>
-    <n v="160.64151437597957"/>
-    <n v="6.2250409172532562E-3"/>
-    <n v="0.91681193081212453"/>
+    <n v="2.5000000000000001E-2"/>
+    <n v="0.25"/>
+    <n v="0.1"/>
+    <n v="7.0013117243310002E-3"/>
+    <n v="8.1995000000000005"/>
+    <n v="16.808975"/>
+    <n v="33.61795"/>
+    <n v="16.802"/>
+    <n v="33.603999999999999"/>
+    <n v="0.80599999999999739"/>
+    <n v="13.386938775510204"/>
+    <n v="0.40997499999999931"/>
+    <n v="-1.5060306122448983"/>
+    <n v="-1.096055612244899"/>
+    <n v="161.36822967848994"/>
+    <n v="6.1970066969960569E-3"/>
+    <n v="0.78726225509046588"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Albertson Companies"/>
-    <x v="3"/>
+    <x v="4"/>
     <d v="2024-12-04T00:00:00"/>
     <n v="2"/>
     <n v="20.5"/>
@@ -1564,7 +1470,7 @@
     <n v="0.14929999999999999"/>
     <n v="0.31569999999999998"/>
     <n v="0.47291732657586316"/>
-    <n v="0.42547879816887618"/>
+    <n v="3.3110416231948631E-2"/>
     <n v="12.9437"/>
     <n v="23.560649999999999"/>
     <n v="47.121299999999998"/>
@@ -1577,36 +1483,10 @@
     <n v="1.5983729080932765"/>
     <n v="158.67380115815178"/>
     <n v="6.302237626508298E-3"/>
-    <n v="0.90558181410456573"/>
+    <n v="0.77411702893704148"/>
   </r>
   <r>
     <x v="3"/>
-    <s v="ING Group NV"/>
-    <x v="4"/>
-    <d v="2024-11-27T00:00:00"/>
-    <n v="1.9595"/>
-    <n v="15.3"/>
-    <n v="29.980350000000001"/>
-    <n v="7.0499999999999993E-2"/>
-    <n v="0.35260000000000002"/>
-    <n v="0.19994327850255245"/>
-    <n v="0.17988688732377014"/>
-    <n v="10.571071410000002"/>
-    <n v="16.37865"/>
-    <n v="32.093964675000002"/>
-    <n v="17.03"/>
-    <n v="33.370285000000003"/>
-    <n v="3.3899350000000013"/>
-    <n v="11.933546525232041"/>
-    <n v="1.0786499999999997"/>
-    <n v="-1.68322673738398"/>
-    <n v="-0.60457673738398032"/>
-    <n v="160.87675080362902"/>
-    <n v="6.2159385679079878E-3"/>
-    <n v="0.91815447021900465"/>
-  </r>
-  <r>
-    <x v="2"/>
     <s v="Altaria"/>
     <x v="5"/>
     <d v="2024-09-18T00:00:00"/>
@@ -1616,49 +1496,49 @@
     <n v="5.8799999999999998E-2"/>
     <n v="0.22600000000000001"/>
     <n v="0.26017699115044246"/>
-    <n v="0.23407853188082897"/>
+    <n v="1.8215802185427555E-2"/>
     <n v="20.337976848"/>
     <n v="54.930543999999998"/>
     <n v="95.282521622399997"/>
-    <n v="53.34"/>
-    <n v="92.523564000000007"/>
-    <n v="2.5325160000000011"/>
+    <n v="55.05"/>
+    <n v="95.489729999999994"/>
+    <n v="5.4986819999999881"/>
     <n v="44.44825222755312"/>
     <n v="3.050543999999995"/>
     <n v="-3.7158738862234415"/>
     <n v="-0.66532988622344647"/>
     <n v="160.93750395246849"/>
-    <n v="6.21359208040993E-3"/>
-    <n v="0.91850120009083625"/>
+    <n v="6.2135920804099291E-3"/>
+    <n v="0.78516088664223582"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="YPF"/>
     <x v="6"/>
     <d v="2024-12-01T00:00:00"/>
-    <n v="1.2354000000000001"/>
-    <n v="40.49"/>
-    <n v="50.021346000000001"/>
+    <n v="1.5004999999999999"/>
+    <n v="40"/>
+    <n v="60.019999999999996"/>
     <n v="4.19E-2"/>
     <n v="0.53510000000000002"/>
     <n v="7.8303120911979066E-2"/>
-    <n v="7.0448503165926199E-2"/>
-    <n v="26.766422244600001"/>
-    <n v="42.186531000000002"/>
-    <n v="52.117240397400003"/>
-    <n v="37.11"/>
-    <n v="45.845694000000002"/>
-    <n v="-4.1756519999999995"/>
-    <n v="27.116260380391111"/>
-    <n v="1.6965310000000002"/>
-    <n v="-6.6868698098044455"/>
-    <n v="-4.9903388098044452"/>
-    <n v="165.2625128760495"/>
-    <n v="6.0509790308587519E-3"/>
-    <n v="0.94318485547973796"/>
+    <n v="5.4822455849274695E-3"/>
+    <n v="32.116701999999997"/>
+    <n v="41.676000000000002"/>
+    <n v="62.534838000000001"/>
+    <n v="36.6"/>
+    <n v="54.918300000000002"/>
+    <n v="-5.1016999999999939"/>
+    <n v="26.788106080900082"/>
+    <n v="1.6760000000000019"/>
+    <n v="-6.6059469595499589"/>
+    <n v="-4.929946959549957"/>
+    <n v="165.20212102579501"/>
+    <n v="6.0531910473707413E-3"/>
+    <n v="0.80596654374669541"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="Emergin Markets"/>
     <x v="7"/>
     <d v="2025-01-31T00:00:00"/>
@@ -1668,23 +1548,23 @@
     <n v="6.2E-2"/>
     <n v="0.26100000000000001"/>
     <n v="0.23754789272030649"/>
-    <n v="0.21371936747166675"/>
+    <n v="1.6631468463928045E-2"/>
     <n v="11.546640000000002"/>
     <n v="46.982880000000002"/>
     <n v="46.982880000000002"/>
-    <n v="45.97"/>
-    <n v="45.97"/>
-    <n v="1.7299999999999969"/>
+    <n v="46.4"/>
+    <n v="46.4"/>
+    <n v="2.1599999999999966"/>
     <n v="36.897414512093412"/>
     <n v="2.7428799999999995"/>
     <n v="-3.6712927439532947"/>
     <n v="-0.92841274395329521"/>
     <n v="161.20058681019833"/>
-    <n v="6.2034513632225506E-3"/>
-    <n v="0.92000266441464951"/>
+    <n v="6.2034513632225514E-3"/>
+    <n v="0.78644438094755664"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="Bitcoin ETF"/>
     <x v="8"/>
     <d v="2024-07-08T00:00:00"/>
@@ -1694,23 +1574,23 @@
     <n v="3.7999999999999999E-2"/>
     <n v="0.16900000000000001"/>
     <n v="0.22485207100591714"/>
-    <n v="0.20229706877113868"/>
+    <n v="1.5742594409738343E-2"/>
     <n v="8.2269199999999998"/>
     <n v="50.52984"/>
     <n v="50.52984"/>
-    <n v="49.3"/>
-    <n v="49.3"/>
-    <n v="0.61999999999999744"/>
+    <n v="50.3"/>
+    <n v="50.3"/>
+    <n v="1.6199999999999974"/>
     <n v="43.041556145004421"/>
     <n v="1.8498400000000004"/>
     <n v="-2.8192219274977894"/>
     <n v="-0.96938192749778906"/>
     <n v="161.24155599374282"/>
     <n v="6.2018751545588301E-3"/>
-    <n v="0.92023648340231989"/>
+    <n v="0.78664425605240662"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="ETF5"/>
     <x v="9"/>
     <d v="2024-07-08T00:00:00"/>
@@ -1720,7 +1600,7 @@
     <n v="3.7999999999999999E-2"/>
     <n v="0.16900000000000001"/>
     <n v="0.22485207100591714"/>
-    <n v="0.20229706877113868"/>
+    <n v="1.5742594409738343E-2"/>
     <n v="8.6663200000000007"/>
     <n v="53.228640000000006"/>
     <n v="53.228640000000006"/>
@@ -1733,10 +1613,10 @@
     <n v="-1.0211566401414629"/>
     <n v="161.29333070638651"/>
     <n v="6.1998843698030494E-3"/>
-    <n v="0.92053197161687317"/>
+    <n v="0.78689684776214863"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="NextEra Energy"/>
     <x v="10"/>
     <d v="2024-08-07T00:00:00"/>
@@ -1746,23 +1626,23 @@
     <n v="0.1212"/>
     <n v="0.24540000000000001"/>
     <n v="0.49388753056234719"/>
-    <n v="0.44434547250734346"/>
+    <n v="3.4578605582270466E-2"/>
     <n v="13.493949678"/>
     <n v="82.632440000000003"/>
     <n v="61.652063484000003"/>
-    <n v="69.06"/>
-    <n v="51.525666000000001"/>
-    <n v="-3.461903999999997"/>
+    <n v="71.58"/>
+    <n v="53.405837999999996"/>
+    <n v="-1.5817320000000024"/>
     <n v="65.557729941291583"/>
     <n v="8.9324399999999997"/>
     <n v="-4.0711350293542097"/>
     <n v="4.86130497064579"/>
     <n v="155.41086909559925"/>
-    <n v="6.4345563847587857E-3"/>
-    <n v="0.886959635049555"/>
+    <n v="6.4345563847587849E-3"/>
+    <n v="0.7581982619102845"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Excelon"/>
     <x v="11"/>
     <d v="2024-12-01T00:00:00"/>
@@ -1772,23 +1652,23 @@
     <n v="8.6900000000000005E-2"/>
     <n v="0.24529999999999999"/>
     <n v="0.35426008968609868"/>
-    <n v="0.31872411672922735"/>
+    <n v="2.4802853193818343E-2"/>
     <n v="5.1495672008"/>
     <n v="43.845546000000006"/>
     <n v="22.817222138400002"/>
-    <n v="42.65"/>
-    <n v="22.195059999999998"/>
-    <n v="1.2021239999999977"/>
+    <n v="43.39"/>
+    <n v="22.580155999999999"/>
+    <n v="1.5872199999999985"/>
     <n v="34.82389502762431"/>
     <n v="3.5055460000000025"/>
     <n v="-2.7580524861878466"/>
     <n v="0.7474935138121559"/>
     <n v="159.5246805524329"/>
     <n v="6.2686224886143432E-3"/>
-    <n v="0.91043794599170247"/>
+    <n v="0.77826818825809496"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Kimberly Clark"/>
     <x v="12"/>
     <d v="2024-09-09T00:00:00"/>
@@ -1798,23 +1678,23 @@
     <n v="5.0200000000000002E-2"/>
     <n v="0.2001"/>
     <n v="0.25087456271864067"/>
-    <n v="0.22570923380948818"/>
+    <n v="1.7564510172984316E-2"/>
     <n v="14.242460471400001"/>
     <n v="145.484206"/>
     <n v="74.749785042799999"/>
-    <n v="137.93"/>
-    <n v="70.868434000000008"/>
-    <n v="-0.30827999999999633"/>
+    <n v="140.26"/>
+    <n v="72.065588000000005"/>
+    <n v="0.88887400000000127"/>
     <n v="120.47134533437691"/>
     <n v="6.9542059999999992"/>
     <n v="-9.0293273328115475"/>
     <n v="-2.0751213328115483"/>
     <n v="162.34729539905658"/>
-    <n v="6.1596344893948326E-3"/>
-    <n v="0.92654715025016887"/>
+    <n v="6.1596344893948335E-3"/>
+    <n v="0.79203879312766667"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Pepsi"/>
     <x v="13"/>
     <d v="2024-06-17T00:00:00"/>
@@ -1824,20 +1704,20 @@
     <n v="6.59E-2"/>
     <n v="0.1875"/>
     <n v="0.35146666666666665"/>
-    <n v="0.31621090310330507"/>
+    <n v="2.4607276940448689E-2"/>
     <n v="15.178889250000001"/>
     <n v="168.40154100000001"/>
     <n v="86.288949608400003"/>
-    <n v="139.5"/>
-    <n v="71.479799999999997"/>
-    <n v="-9.4742760000000033"/>
+    <n v="153.5"/>
+    <n v="78.653399999999991"/>
+    <n v="-2.3006760000000099"/>
     <n v="140.86126961483598"/>
     <n v="10.411541"/>
     <n v="-8.5643651925820166"/>
     <n v="1.8471758074179832"/>
     <n v="158.42499825882706"/>
     <n v="6.312135149064345E-3"/>
-    <n v="0.90416184824201995"/>
+    <n v="0.77290320182878303"/>
   </r>
   <r>
     <x v="4"/>
@@ -1850,20 +1730,20 @@
     <n v="0.24179999999999999"/>
     <n v="0.32229999999999998"/>
     <n v="0.75023270245113249"/>
-    <n v="0.67497655646729637"/>
+    <n v="5.2526130156476447E-2"/>
     <n v="25.124383398399996"/>
     <n v="235.643968"/>
     <n v="96.802542054400007"/>
-    <n v="200.95"/>
-    <n v="82.550259999999994"/>
-    <n v="4.5968519999999984"/>
+    <n v="198.24"/>
+    <n v="81.436992000000004"/>
+    <n v="3.4835840000000076"/>
     <n v="175.62239703840814"/>
     <n v="45.88396800000001"/>
     <n v="-7.0688014807959263"/>
     <n v="38.815166519204084"/>
     <n v="121.45700754704096"/>
     <n v="8.2333660296438193E-3"/>
-    <n v="0.69317843542762225"/>
+    <n v="0.59254859428360551"/>
   </r>
   <r>
     <x v="5"/>
@@ -1876,20 +1756,20 @@
     <n v="6.9500000000000006E-2"/>
     <n v="0.25430000000000003"/>
     <n v="0.2732992528509634"/>
-    <n v="0.24588449419990988"/>
+    <n v="1.9134532632363525E-2"/>
     <n v="11.693686951800002"/>
     <n v="141.07774500000002"/>
     <n v="49.179701907000009"/>
-    <n v="126.91"/>
-    <n v="44.240825999999998"/>
-    <n v="-1.7430000000000021"/>
+    <n v="128.08000000000001"/>
+    <n v="44.648688000000007"/>
+    <n v="-1.3351379999999935"/>
     <n v="111.3352464550979"/>
     <n v="9.1677450000000249"/>
     <n v="-10.287376772451047"/>
     <n v="-1.1196317724510223"/>
     <n v="161.39180583869606"/>
-    <n v="6.1961014365218489E-3"/>
-    <n v="0.92109398808279364"/>
+    <n v="6.1961014365218498E-3"/>
+    <n v="0.78737727538341462"/>
   </r>
   <r>
     <x v="6"/>
@@ -1902,51 +1782,155 @@
     <n v="-0.1268"/>
     <n v="0.58609999999999995"/>
     <n v="-0.2163453335608258"/>
-    <n v="-0.19464364560163458"/>
+    <n v="-1.5147011203637107E-2"/>
     <n v="5.8605604249999992"/>
     <n v="30.369896000000001"/>
     <n v="8.7313450999999986"/>
-    <n v="34.020000000000003"/>
-    <n v="9.7807499999999994"/>
-    <n v="-0.21850000000000058"/>
+    <n v="35.22"/>
+    <n v="10.125749999999998"/>
+    <n v="0.12649999999999828"/>
     <n v="20.304746336622102"/>
     <n v="-4.4101040000000005"/>
     <n v="-7.2376268316889494"/>
     <n v="-11.64773083168895"/>
     <n v="171.919904897934"/>
     <n v="5.8166621287609683E-3"/>
-    <n v="0.981179868521459"/>
+    <n v="0.83874039081019502"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="First Solar"/>
+    <x v="17"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.34489999999999998"/>
+    <n v="173.73"/>
+    <n v="59.919476999999993"/>
+    <n v="0.123"/>
+    <n v="0.47839999999999999"/>
+    <n v="0.25710702341137126"/>
+    <n v="1.8000864174178784E-2"/>
+    <n v="28.665477796799998"/>
+    <n v="195.09878999999998"/>
+    <n v="67.289572670999988"/>
+    <n v="155.44"/>
+    <n v="53.611255999999997"/>
+    <n v="-6.3082209999999961"/>
+    <n v="128.17618415227977"/>
+    <n v="21.36878999999999"/>
+    <n v="-22.776907923860108"/>
+    <n v="-1.408117923860118"/>
+    <n v="161.68029199010516"/>
+    <n v="6.1850457324829676E-3"/>
+    <n v="0.78878470396197198"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Microsoft"/>
+    <x v="18"/>
+    <d v="2024-10-09T00:00:00"/>
+    <n v="0.16059999999999999"/>
+    <n v="421.18"/>
+    <n v="67.641508000000002"/>
+    <n v="0.2412"/>
+    <n v="0.27010000000000001"/>
+    <n v="0.89300259163272855"/>
+    <n v="6.2521895146561909E-2"/>
+    <n v="18.269971310800003"/>
+    <n v="522.76861600000007"/>
+    <n v="83.956639729600013"/>
+    <n v="408.21"/>
+    <n v="65.558526000000001"/>
+    <n v="-2.0829820000000012"/>
+    <n v="409.34979103897371"/>
+    <n v="101.58861600000006"/>
+    <n v="-5.9151044805131505"/>
+    <n v="95.673511519486908"/>
+    <n v="64.598662546758135"/>
+    <n v="1.5480196656953616E-2"/>
+    <n v="0.31515552258157942"/>
   </r>
   <r>
     <x v="0"/>
-    <s v="First Solar"/>
-    <x v="17"/>
+    <s v="Master Card"/>
+    <x v="19"/>
     <d v="2024-08-07T00:00:00"/>
-    <n v="0.25169999999999998"/>
-    <n v="178.56"/>
-    <n v="44.943551999999997"/>
-    <n v="0.123"/>
-    <n v="0.47839999999999999"/>
-    <n v="0.25710702341137126"/>
-    <n v="0.23131651384800542"/>
-    <n v="21.500995276799998"/>
-    <n v="200.52288000000001"/>
-    <n v="50.471608895999999"/>
-    <n v="162.5"/>
-    <n v="40.901249999999997"/>
-    <n v="-4.0423019999999994"/>
-    <n v="131.73970783532536"/>
-    <n v="21.962880000000013"/>
-    <n v="-23.41014608233732"/>
-    <n v="-1.4472660823373076"/>
-    <n v="161.71944014858235"/>
-    <n v="6.1835484904055682E-3"/>
-    <n v="0.92296385992391761"/>
+    <n v="0.12939999999999999"/>
+    <n v="501.56"/>
+    <n v="64.901863999999989"/>
+    <n v="0.1928"/>
+    <n v="0.26650000000000001"/>
+    <n v="0.72345215759849901"/>
+    <n v="5.0651140729869294E-2"/>
+    <n v="17.296346755999998"/>
+    <n v="598.2607680000001"/>
+    <n v="77.414943379200011"/>
+    <n v="557.51"/>
+    <n v="72.14179399999999"/>
+    <n v="7.2399300000000011"/>
+    <n v="467.13234609294966"/>
+    <n v="96.700768000000096"/>
+    <n v="-17.213826953525171"/>
+    <n v="79.486941046474925"/>
+    <n v="80.785233019770118"/>
+    <n v="1.2378499914152324E-2"/>
+    <n v="0.39412444972512845"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Google"/>
+    <x v="20"/>
+    <d v="2025-01-21T00:00:00"/>
+    <n v="5.3800000000000001E-2"/>
+    <n v="185.82"/>
+    <n v="9.9971160000000001"/>
+    <n v="0.1925"/>
+    <n v="0.28539999999999999"/>
+    <n v="0.6744919411352488"/>
+    <n v="4.722328335436992E-2"/>
+    <n v="2.8531769063999999"/>
+    <n v="221.59034999999997"/>
+    <n v="11.921560829999999"/>
+    <n v="179.66"/>
+    <n v="9.6657080000000004"/>
+    <n v="-0.3314079999999997"/>
+    <n v="170.02470491353276"/>
+    <n v="35.770349999999979"/>
+    <n v="-7.8976475432336173"/>
+    <n v="27.872702456766362"/>
+    <n v="132.39947160947867"/>
+    <n v="7.5529002332393649E-3"/>
+    <n v="0.64593325959972625"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Yum! Brands"/>
+    <x v="21"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="2.9999999999999997E-4"/>
+    <n v="130.51"/>
+    <n v="3.9152999999999993E-2"/>
+    <n v="0.1169"/>
+    <n v="0.23899999999999999"/>
+    <n v="0.48912133891213394"/>
+    <n v="3.4244909647459999E-2"/>
+    <n v="9.3575669999999972E-3"/>
+    <n v="145.76661899999999"/>
+    <n v="4.3729985699999994E-2"/>
+    <n v="148.75"/>
+    <n v="4.4624999999999998E-2"/>
+    <n v="5.4720000000000046E-3"/>
+    <n v="116.3087068888691"/>
+    <n v="15.256619000000001"/>
+    <n v="-7.1006465555654472"/>
+    <n v="8.1559724444345534"/>
+    <n v="152.11620162181049"/>
+    <n v="6.5739217081306582E-3"/>
+    <n v="0.74212466830170387"/>
   </r>
   <r>
     <x v="4"/>
     <s v="Apple2"/>
-    <x v="18"/>
+    <x v="22"/>
     <d v="2024-07-09T00:00:00"/>
     <n v="1E-4"/>
     <n v="227.38"/>
@@ -1954,127 +1938,23 @@
     <n v="0.2092"/>
     <n v="0.28439999999999999"/>
     <n v="0.73558368495077353"/>
-    <n v="0.66179698784050023"/>
+    <n v="5.1500506776724513E-2"/>
     <n v="6.4666871999999997E-3"/>
     <n v="274.94789600000001"/>
     <n v="2.7494789600000003E-2"/>
-    <n v="244.87"/>
-    <n v="2.4487000000000002E-2"/>
-    <n v="1.7490000000000006E-3"/>
+    <n v="245.55"/>
+    <n v="2.4555000000000004E-2"/>
+    <n v="1.8170000000000026E-3"/>
     <n v="211.47693452380955"/>
     <n v="47.567896000000019"/>
     <n v="-7.9515327380952243"/>
     <n v="39.616363261904795"/>
     <n v="120.65581080434025"/>
     <n v="8.2880384569429116E-3"/>
-    <n v="0.68860585196132951"/>
+    <n v="0.58863982019786132"/>
   </r>
   <r>
-    <x v="4"/>
-    <s v="Microsoft"/>
-    <x v="19"/>
-    <d v="2024-10-09T00:00:00"/>
-    <n v="0.16059999999999999"/>
-    <n v="421.18"/>
-    <n v="67.641508000000002"/>
-    <n v="0.2412"/>
-    <n v="0.27010000000000001"/>
-    <n v="0.89300259163272855"/>
-    <n v="0.80342514028957801"/>
-    <n v="18.269971310800003"/>
-    <n v="522.76861600000007"/>
-    <n v="83.956639729600013"/>
-    <n v="414.77"/>
-    <n v="66.612061999999995"/>
-    <n v="-1.0294460000000072"/>
-    <n v="409.34979103897371"/>
-    <n v="101.58861600000006"/>
-    <n v="-5.9151044805131505"/>
-    <n v="95.673511519486908"/>
-    <n v="64.598662546758135"/>
-    <n v="1.5480196656953615E-2"/>
-    <n v="0.36867695606229905"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="Master Card"/>
-    <x v="20"/>
-    <d v="2024-08-07T00:00:00"/>
-    <n v="0.12939999999999999"/>
-    <n v="501.56"/>
-    <n v="64.901863999999989"/>
-    <n v="0.1928"/>
-    <n v="0.26650000000000001"/>
-    <n v="0.72345215759849901"/>
-    <n v="0.65088237890626699"/>
-    <n v="17.296346755999998"/>
-    <n v="598.2607680000001"/>
-    <n v="77.414943379200011"/>
-    <n v="568.5"/>
-    <n v="73.56389999999999"/>
-    <n v="8.6620360000000005"/>
-    <n v="467.13234609294966"/>
-    <n v="96.700768000000096"/>
-    <n v="-17.213826953525171"/>
-    <n v="79.486941046474925"/>
-    <n v="80.785233019770118"/>
-    <n v="1.2378499914152326E-2"/>
-    <n v="0.46105681805647636"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="Google"/>
-    <x v="21"/>
-    <d v="2025-01-21T00:00:00"/>
-    <n v="5.3800000000000001E-2"/>
-    <n v="185.82"/>
-    <n v="9.9971160000000001"/>
-    <n v="0.1925"/>
-    <n v="0.28539999999999999"/>
-    <n v="0.6744919411352488"/>
-    <n v="0.60683338156945643"/>
-    <n v="2.8531769063999999"/>
-    <n v="221.59034999999997"/>
-    <n v="11.921560829999999"/>
-    <n v="185.27"/>
-    <n v="9.9675260000000012"/>
-    <n v="-2.9589999999998895E-2"/>
-    <n v="170.02470491353276"/>
-    <n v="35.770349999999979"/>
-    <n v="-7.8976475432336173"/>
-    <n v="27.872702456766362"/>
-    <n v="132.39947160947867"/>
-    <n v="7.552900233239364E-3"/>
-    <n v="0.75562917640760074"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="Yum! Brands"/>
-    <x v="22"/>
-    <d v="2024-10-15T00:00:00"/>
-    <n v="2.9999999999999997E-4"/>
-    <n v="130.51"/>
-    <n v="3.9152999999999993E-2"/>
-    <n v="0.1169"/>
-    <n v="0.23899999999999999"/>
-    <n v="0.48912133891213394"/>
-    <n v="0.44005737947032519"/>
-    <n v="9.3575669999999972E-3"/>
-    <n v="145.76661899999999"/>
-    <n v="4.3729985699999994E-2"/>
-    <n v="148.29"/>
-    <n v="4.4486999999999992E-2"/>
-    <n v="5.3339999999999985E-3"/>
-    <n v="116.3087068888691"/>
-    <n v="15.256619000000001"/>
-    <n v="-7.1006465555654472"/>
-    <n v="8.1559724444345534"/>
-    <n v="152.11620162181049"/>
-    <n v="6.5739217081306582E-3"/>
-    <n v="0.86815633591631525"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Maxeon Solar"/>
     <x v="23"/>
     <d v="2024-08-07T00:00:00"/>
@@ -2084,23 +1964,23 @@
     <n v="-1.4844999999999999"/>
     <n v="1.3212999999999999"/>
     <n v="-1.1235147203511693"/>
-    <n v="-1.0108145040936092"/>
+    <n v="-7.8660767840531068E-2"/>
     <n v="1.4428596E-18"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="5.64"/>
-    <n v="5.6399999999999995E-19"/>
-    <n v="-5.280000000000001E-19"/>
+    <n v="5.22"/>
+    <n v="5.22E-19"/>
+    <n v="-5.7000000000000005E-19"/>
     <n v="2.8693047453886176"/>
     <n v="-10.92"/>
     <n v="-4.025347627305691"/>
     <n v="-14.94534762730569"/>
     <n v="175.21752169355074"/>
     <n v="5.7071917827314364E-3"/>
-    <n v="1"/>
+    <n v="0.85482837318512639"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="0"/>
     <s v="Visa"/>
     <x v="24"/>
     <d v="2024-08-07T00:00:00"/>
@@ -2110,20 +1990,20 @@
     <n v="0.17100000000000001"/>
     <n v="0.24360000000000001"/>
     <n v="0.70197044334975367"/>
-    <n v="0.6315555041069415"/>
+    <n v="4.9147138951584603E-2"/>
     <n v="6.9043547999999996E-18"/>
     <n v="331.89653000000004"/>
     <n v="3.3189653000000001E-17"/>
-    <n v="355.23"/>
-    <n v="3.5522999999999998E-17"/>
-    <n v="7.1800000000000003E-18"/>
+    <n v="348.53"/>
+    <n v="3.4852999999999998E-17"/>
+    <n v="6.51E-18"/>
     <n v="264.24575797128472"/>
     <n v="48.466530000000034"/>
     <n v="-9.5921210143576445"/>
     <n v="38.87440898564239"/>
     <n v="121.39776508060265"/>
-    <n v="8.2373839364838809E-3"/>
-    <n v="0.6928403273099768"/>
+    <n v="8.2373839364838792E-3"/>
+    <n v="0.59225956987143791"/>
   </r>
   <r>
     <x v="4"/>
@@ -2136,20 +2016,20 @@
     <n v="0.1164"/>
     <n v="0.3664"/>
     <n v="0.31768558951965065"/>
-    <n v="0.28581841947528813"/>
+    <n v="2.2242158425549354E-2"/>
     <n v="6.8927168000000004E-18"/>
     <n v="210.01716800000003"/>
     <n v="2.1001716800000003E-17"/>
-    <n v="175.22"/>
-    <n v="1.7522E-17"/>
-    <n v="-1.2900000000000016E-18"/>
+    <n v="165.43"/>
+    <n v="1.6542999999999999E-17"/>
+    <n v="-2.2690000000000023E-18"/>
     <n v="150.49600000000001"/>
     <n v="21.897168000000022"/>
     <n v="-18.811999999999998"/>
     <n v="3.0851680000000243"/>
     <n v="157.18700606624503"/>
     <n v="6.3618490168236884E-3"/>
-    <n v="0.89709638937343017"/>
+    <n v="0.76686344711833998"/>
   </r>
   <r>
     <x v="5"/>
@@ -2159,23 +2039,23 @@
     <n v="9.9999999999999998E-20"/>
     <n v="668.82"/>
     <n v="6.6881999999999999E-17"/>
-    <n v="0.16070000000000001"/>
-    <n v="0.27700000000000002"/>
-    <n v="0.58014440433212999"/>
-    <n v="0.52194988436321643"/>
-    <n v="1.8526314000000002E-17"/>
-    <n v="776.29937400000006"/>
-    <n v="7.7629937400000001E-17"/>
-    <s v="#VALUE!"/>
-    <n v="6.6881999999999999E-17"/>
-    <n v="0"/>
-    <n v="599.14001612469769"/>
-    <n v="107.47937400000001"/>
-    <n v="-34.839991937651178"/>
-    <n v="72.63938206234883"/>
-    <n v="87.632792003896213"/>
-    <n v="1.1411253449000453E-2"/>
-    <n v="0.50013715042244966"/>
+    <n v="2.5000000000000001E-2"/>
+    <n v="0.25"/>
+    <n v="0.1"/>
+    <n v="7.0013117243310002E-3"/>
+    <n v="1.67205E-17"/>
+    <n v="685.54049999999995"/>
+    <n v="6.8554049999999998E-17"/>
+    <n v="702.4"/>
+    <n v="7.0239999999999996E-17"/>
+    <n v="3.3579999999999971E-18"/>
+    <n v="545.97551020408162"/>
+    <n v="16.720499999999902"/>
+    <n v="-61.422244897959217"/>
+    <n v="-44.701744897959315"/>
+    <n v="204.97391896420436"/>
+    <n v="4.878669467087835E-3"/>
+    <n v="1"/>
   </r>
   <r>
     <x v="4"/>
@@ -2188,20 +2068,20 @@
     <n v="0.2051"/>
     <n v="0.36940000000000001"/>
     <n v="0.55522468868435304"/>
-    <n v="0.49952987547647199"/>
+    <n v="3.8873011225237904E-2"/>
     <n v="2.5869820800000001E-17"/>
     <n v="843.95563200000015"/>
     <n v="8.4395563200000012E-17"/>
-    <n v="717.5"/>
-    <n v="7.1749999999999995E-17"/>
-    <n v="1.7179999999999966E-18"/>
+    <n v="737.21"/>
+    <n v="7.3720999999999998E-17"/>
+    <n v="3.6889999999999994E-18"/>
     <n v="601.49446019067261"/>
     <n v="143.6356320000001"/>
     <n v="-49.412769904663719"/>
     <n v="94.222862095336382"/>
     <n v="66.049311970908661"/>
-    <n v="1.5140203132478486E-2"/>
-    <n v="0.376956090535435"/>
+    <n v="1.5140203132478484E-2"/>
+    <n v="0.32223276163463116"/>
   </r>
   <r>
     <x v="4"/>
@@ -2214,20 +2094,20 @@
     <n v="0.55089999999999995"/>
     <n v="0.48780000000000001"/>
     <n v="1.1293562935629355"/>
-    <n v="1.0160701067325602"/>
+    <n v="7.9069754590691835E-2"/>
     <n v="7.1711477999999992E-18"/>
     <n v="227.99780899999999"/>
     <n v="2.2799780899999998E-17"/>
-    <n v="139.22999999999999"/>
-    <n v="1.3922999999999999E-17"/>
-    <n v="-7.7800000000000002E-19"/>
+    <n v="134.43"/>
+    <n v="1.3443E-17"/>
+    <n v="-1.257999999999999E-18"/>
     <n v="156.91108976411567"/>
     <n v="80.987808999999999"/>
     <n v="4.9505448820578408"/>
     <n v="85.938353882057839"/>
     <n v="74.333820184187203"/>
     <n v="1.3452826688069595E-2"/>
-    <n v="0.42423736773422943"/>
+    <n v="0.36265013890459158"/>
   </r>
   <r>
     <x v="4"/>
@@ -2240,23 +2120,23 @@
     <n v="0.21429999999999999"/>
     <n v="0.40479999999999999"/>
     <n v="0.52939723320158105"/>
-    <n v="0.47629318250492114"/>
+    <n v="3.7064750556426218E-2"/>
     <n v="6.8548831999999995E-18"/>
     <n v="205.62956199999999"/>
     <n v="2.0562956199999998E-17"/>
-    <n v="174.06"/>
-    <n v="1.7406000000000001E-17"/>
-    <n v="4.720000000000018E-19"/>
+    <n v="171.98"/>
+    <n v="1.7197999999999997E-17"/>
+    <n v="2.6399999999999798E-19"/>
     <n v="142.2427551448971"/>
     <n v="36.289561999999989"/>
     <n v="-13.54862242755145"/>
     <n v="22.740939572448539"/>
     <n v="137.53123449379649"/>
     <n v="7.2710755755275806E-3"/>
-    <n v="0.78491713137190566"/>
+    <n v="0.67096943449578217"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Duke Energy"/>
     <x v="30"/>
     <d v="2024-08-07T00:00:00"/>
@@ -2266,20 +2146,20 @@
     <n v="7.6100000000000001E-2"/>
     <n v="0.20619999999999999"/>
     <n v="0.36905916585838994"/>
-    <n v="0.33203869158184923"/>
+    <n v="2.5838982648961645E-2"/>
     <n v="2.3420195999999997E-18"/>
     <n v="122.223438"/>
     <n v="1.2222343799999999E-17"/>
-    <n v="111.79"/>
-    <n v="1.1179E-17"/>
-    <n v="-1.7899999999999882E-19"/>
+    <n v="115.55"/>
+    <n v="1.1554999999999999E-17"/>
+    <n v="1.969999999999998E-19"/>
     <n v="100.50438014335016"/>
     <n v="8.6434380000000033"/>
     <n v="-6.5378099283249185"/>
     <n v="2.1056280716750848"/>
     <n v="158.16654599456996"/>
-    <n v="6.3224495022754764E-3"/>
-    <n v="0.9026868116032235"/>
+    <n v="6.3224495022754755E-3"/>
+    <n v="0.77164229865845224"/>
   </r>
   <r>
     <x v="4"/>
@@ -2292,23 +2172,23 @@
     <n v="0.56589999999999996"/>
     <n v="0.70699999999999996"/>
     <n v="0.80042432814710041"/>
-    <n v="0.7201334398783692"/>
+    <n v="5.6040202330960576E-2"/>
     <n v="4.5495449999999992E-18"/>
     <n v="100.765665"/>
     <n v="1.0076566499999999E-17"/>
-    <n v="112.06"/>
-    <n v="1.1206E-17"/>
-    <n v="4.771000000000001E-18"/>
+    <n v="101.35"/>
+    <n v="1.0134999999999999E-17"/>
+    <n v="3.6999999999999996E-18"/>
     <n v="56.392954167031817"/>
     <n v="36.415665000000004"/>
     <n v="-3.9785229164840885"/>
     <n v="32.437142083515916"/>
     <n v="127.83503198272913"/>
-    <n v="7.822581842316139E-3"/>
-    <n v="0.7295790440770421"/>
+    <n v="7.8225818423161408E-3"/>
+    <n v="0.62366486735833748"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Jinko Solar"/>
     <x v="32"/>
     <d v="2024-08-07T00:00:00"/>
@@ -2318,23 +2198,23 @@
     <n v="1.1900000000000001E-2"/>
     <n v="0.70799999999999996"/>
     <n v="1.6807909604519777E-2"/>
-    <n v="1.5121901390337388E-2"/>
+    <n v="1.1767741457561994E-3"/>
     <n v="1.474056E-18"/>
     <n v="21.067758000000001"/>
     <n v="2.1067757999999999E-18"/>
-    <n v="23.2"/>
-    <n v="2.32E-18"/>
-    <n v="2.3799999999999981E-19"/>
+    <n v="23.06"/>
+    <n v="2.3059999999999999E-18"/>
+    <n v="2.2399999999999973E-19"/>
     <n v="12.275219621484583"/>
     <n v="0.24775800000000103"/>
     <n v="-4.2723901892577087"/>
     <n v="-4.0246321892577077"/>
     <n v="164.29680625550276"/>
-    <n v="6.0865455804714232E-3"/>
-    <n v="0.93767338259042421"/>
+    <n v="6.086545580471424E-3"/>
+    <n v="0.80154981221876698"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="SolarWinds"/>
     <x v="33"/>
     <d v="2024-08-07T00:00:00"/>
@@ -2344,23 +2224,23 @@
     <n v="4.82E-2"/>
     <n v="0.4264"/>
     <n v="0.11303939962476547"/>
-    <n v="0.10170037170410422"/>
+    <n v="7.914240739042077E-3"/>
     <n v="5.5602559999999997E-19"/>
     <n v="13.668528"/>
     <n v="1.3668528E-18"/>
-    <n v="18.309999999999999"/>
-    <n v="1.8309999999999997E-18"/>
-    <n v="5.2699999999999978E-19"/>
+    <n v="18.32"/>
+    <n v="1.832E-18"/>
+    <n v="5.28E-19"/>
     <n v="9.4616166013640974"/>
     <n v="0.62852800000000109"/>
     <n v="-1.7891916993179509"/>
     <n v="-1.1606636993179498"/>
     <n v="161.43283776556299"/>
-    <n v="6.1945265525978448E-3"/>
-    <n v="0.92132816515863825"/>
+    <n v="6.1945265525978439E-3"/>
+    <n v="0.78757745659219613"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Canadian Solar"/>
     <x v="34"/>
     <d v="2024-08-07T00:00:00"/>
@@ -2370,39 +2250,39 @@
     <n v="-0.1055"/>
     <n v="0.57940000000000003"/>
     <n v="-0.18208491542975491"/>
-    <n v="-0.16381990387765097"/>
+    <n v="-1.2748332532221617E-2"/>
     <n v="6.4023700000000011E-19"/>
     <n v="9.8842250000000007"/>
     <n v="9.8842250000000007E-19"/>
-    <n v="11.05"/>
-    <n v="1.1050000000000001E-18"/>
-    <n v="0"/>
+    <n v="11.28"/>
+    <n v="1.1279999999999999E-18"/>
+    <n v="2.2999999999999801E-20"/>
     <n v="6.5582527152946763"/>
     <n v="-1.165775"/>
     <n v="-2.2458736423526622"/>
     <n v="-3.4116486423526622"/>
     <n v="163.68382270859772"/>
-    <n v="6.1093392337266909E-3"/>
-    <n v="0.93417496792857824"/>
+    <n v="6.1093392337266917E-3"/>
+    <n v="0.79855926810465416"/>
   </r>
   <r>
     <x v="7"/>
     <s v="Gold"/>
     <x v="35"/>
-    <d v="2025-01-30T00:00:00"/>
+    <d v="2025-02-03T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="2742.9"/>
     <n v="2.7429000000000002E-16"/>
     <n v="8.6599999999999996E-2"/>
     <n v="0.14630000000000001"/>
     <n v="0.59193438140806554"/>
-    <n v="0.53255720406754736"/>
+    <n v="4.1443171245869069E-2"/>
     <n v="4.0128627000000008E-17"/>
     <n v="2980.43514"/>
     <n v="2.98043514E-16"/>
-    <n v="0.78559999999999997"/>
-    <n v="7.8559999999999989E-20"/>
-    <n v="-2.7421144000000001E-16"/>
+    <n v="0.74750000000000005"/>
+    <n v="7.4750000000000002E-20"/>
+    <n v="-2.7421525000000001E-16"/>
     <n v="2588.3740681324903"/>
     <n v="237.53513999999996"/>
     <n v="-77.262965933754913"/>
@@ -2412,7 +2292,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Walmart"/>
     <x v="36"/>
     <d v="2024-08-01T00:00:00"/>
@@ -2422,20 +2302,20 @@
     <n v="0.1467"/>
     <n v="0.21079999999999999"/>
     <n v="0.6959203036053131"/>
-    <n v="0.62611225632861045"/>
+    <n v="4.8723549808318681E-2"/>
     <n v="1.8255279999999995E-18"/>
     <n v="99.304220000000001"/>
     <n v="9.9304219999999992E-18"/>
-    <n v="104"/>
-    <n v="1.04E-17"/>
-    <n v="1.7400000000000015E-18"/>
+    <n v="94.78"/>
+    <n v="9.4779999999999999E-18"/>
+    <n v="8.1800000000000135E-19"/>
     <n v="81.383328634526833"/>
     <n v="12.704220000000007"/>
     <n v="-2.6083356827365805"/>
     <n v="10.095884317263426"/>
     <n v="150.17628974898162"/>
     <n v="6.6588407642211127E-3"/>
-    <n v="0.8570848868164832"/>
+    <n v="0.73266047947889246"/>
   </r>
   <r>
     <x v="8"/>
@@ -2448,20 +2328,20 @@
     <n v="4.1000000000000003E-3"/>
     <n v="0.4047"/>
     <n v="1.0130961205831481E-2"/>
-    <n v="9.1147203875204513E-3"/>
+    <n v="7.0930017469130477E-4"/>
     <n v="2.2663199999999999E-18"/>
     <n v="56.229599999999998"/>
     <n v="5.6229599999999995E-18"/>
-    <n v="66.66"/>
-    <n v="6.6659999999999998E-18"/>
-    <n v="1.0660000000000003E-18"/>
+    <n v="66.680000000000007"/>
+    <n v="6.6680000000000003E-18"/>
+    <n v="1.0680000000000008E-18"/>
     <n v="39.98286448664858"/>
     <n v="0.22959999999999781"/>
     <n v="-8.0085677566757099"/>
     <n v="-7.7789677566757121"/>
     <n v="168.05114182292075"/>
-    <n v="5.9505695061192881E-3"/>
-    <n v="0.95910009569040855"/>
+    <n v="5.9505695061192873E-3"/>
+    <n v="0.81986597452073107"/>
   </r>
   <r>
     <x v="7"/>
@@ -2474,20 +2354,20 @@
     <n v="3.1099999999999999E-2"/>
     <n v="0.1285"/>
     <n v="0.24202334630350195"/>
-    <n v="0.21774588649482446"/>
+    <n v="1.69448089203653E-2"/>
     <n v="2.1845000000000003E-19"/>
     <n v="17.528699999999997"/>
     <n v="1.7528699999999997E-18"/>
-    <n v="20.431999999999999"/>
-    <n v="2.0431999999999997E-18"/>
-    <n v="3.4319999999999965E-19"/>
+    <n v="20.41"/>
+    <n v="2.0410000000000002E-18"/>
+    <n v="3.4100000000000015E-19"/>
     <n v="15.491160925824675"/>
     <n v="0.52869999999999706"/>
     <n v="-0.75441953708766274"/>
     <n v="-0.22571953708766568"/>
     <n v="160.4978936033327"/>
     <n v="6.2306113653521197E-3"/>
-    <n v="0.91599225951864482"/>
+    <n v="0.78301617305449123"/>
   </r>
   <r>
     <x v="5"/>
@@ -2500,46 +2380,46 @@
     <n v="8.5199999999999998E-2"/>
     <n v="0.36359999999999998"/>
     <n v="0.23432343234323433"/>
-    <n v="0.21081835401987956"/>
+    <n v="1.6405713941501684E-2"/>
     <n v="1.7241911999999999E-18"/>
     <n v="51.460183999999998"/>
     <n v="5.1460184E-18"/>
-    <n v="47.29"/>
-    <n v="4.729E-18"/>
-    <n v="-1.2999999999999854E-20"/>
+    <n v="46.69"/>
+    <n v="4.6689999999999996E-18"/>
+    <n v="-7.3000000000000305E-20"/>
     <n v="37.093241551939926"/>
     <n v="4.0401839999999964"/>
     <n v="-5.163379224030038"/>
     <n v="-1.1231952240300416"/>
     <n v="161.39536929027508"/>
     <n v="6.1959646326745959E-3"/>
-    <n v="0.92111432538436366"/>
+    <n v="0.78739466028583072"/>
   </r>
   <r>
     <x v="5"/>
     <s v="MSG"/>
     <x v="40"/>
     <d v="2024-08-03T00:00:00"/>
-    <n v="9.9999999999999998E-20"/>
-    <n v="41.8"/>
-    <n v="4.1799999999999993E-18"/>
+    <n v="0.52270000000000005"/>
+    <n v="38.229999999999997"/>
+    <n v="19.982821000000001"/>
     <n v="8.3500000000000005E-2"/>
     <n v="0.39029999999999998"/>
     <n v="0.21393799641301564"/>
-    <n v="0.19247778941731217"/>
-    <n v="1.6314539999999997E-18"/>
-    <n v="45.290299999999995"/>
-    <n v="4.5290299999999995E-18"/>
-    <n v="38.39"/>
-    <n v="3.8390000000000001E-18"/>
-    <n v="-3.4099999999999919E-19"/>
-    <n v="31.986531986531986"/>
-    <n v="3.4902999999999977"/>
-    <n v="-4.9067340067340055"/>
-    <n v="-1.4164340067340078"/>
-    <n v="161.68860807297904"/>
-    <n v="6.1847276188353641E-3"/>
-    <n v="0.92278789535538974"/>
+    <n v="1.4978466025663299E-2"/>
+    <n v="7.7992950363000002"/>
+    <n v="41.422204999999991"/>
+    <n v="21.651386553499997"/>
+    <n v="39.22"/>
+    <n v="20.500294"/>
+    <n v="0.51747299999999896"/>
+    <n v="29.254667891031527"/>
+    <n v="3.1922049999999942"/>
+    <n v="-4.4876660544842348"/>
+    <n v="-1.2954610544842406"/>
+    <n v="161.56763512072928"/>
+    <n v="6.1893584024595221E-3"/>
+    <n v="0.78823508833309008"/>
   </r>
   <r>
     <x v="7"/>
@@ -2552,20 +2432,20 @@
     <n v="2.2700000000000001E-2"/>
     <n v="8.8400000000000006E-2"/>
     <n v="0.25678733031674206"/>
-    <n v="0.23102888929707052"/>
+    <n v="1.7978481464062633E-2"/>
     <n v="1.359195968E-18"/>
     <n v="157.24544304"/>
     <n v="1.5724544303999999E-17"/>
-    <n v="151.47"/>
-    <n v="1.5146999999999998E-17"/>
-    <n v="-2.28520000000001E-19"/>
+    <n v="149.29"/>
+    <n v="1.4928999999999998E-17"/>
+    <n v="-4.4652000000000092E-19"/>
     <n v="144.27625035188137"/>
     <n v="3.4902430399999957"/>
     <n v="-4.7394748240593145"/>
     <n v="-1.2492317840593188"/>
     <n v="161.52140585030435"/>
     <n v="6.1911298674974706E-3"/>
-    <n v="0.92183364020408631"/>
+    <n v="0.78800955100298231"/>
   </r>
   <r>
     <x v="9"/>
@@ -2578,23 +2458,23 @@
     <n v="4.0899999999999999E-2"/>
     <n v="0.25"/>
     <n v="0.1636"/>
-    <n v="0.14718921779505134"/>
+    <n v="1.1454145981005515E-2"/>
     <n v="3.3382499999999999E-18"/>
     <n v="138.991377"/>
     <n v="1.38991377E-17"/>
-    <n v="150.19999999999999"/>
-    <n v="1.5019999999999999E-17"/>
-    <n v="1.6669999999999989E-18"/>
+    <n v="144.97999999999999"/>
+    <n v="1.4497999999999998E-17"/>
+    <n v="1.1449999999999981E-18"/>
     <n v="110.4375155074022"/>
     <n v="5.4613769999999988"/>
     <n v="-11.546242246298903"/>
     <n v="-6.0848652462989037"/>
     <n v="166.35703931254395"/>
     <n v="6.0111673310153475E-3"/>
-    <n v="0.94943152776408135"/>
+    <n v="0.81160100832923887"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="PG&amp;E"/>
     <x v="43"/>
     <d v="2024-12-01T00:00:00"/>
@@ -2604,20 +2484,20 @@
     <n v="-0.1193"/>
     <n v="0.60340000000000005"/>
     <n v="-0.19771295989393436"/>
-    <n v="-0.17788029287733836"/>
+    <n v="-1.3842500641575875E-2"/>
     <n v="1.6068542000000001E-18"/>
     <n v="23.453040999999999"/>
     <n v="2.3453040999999998E-18"/>
-    <n v="15.66"/>
-    <n v="1.566E-18"/>
-    <n v="-1.097E-18"/>
+    <n v="15.99"/>
+    <n v="1.5989999999999999E-18"/>
+    <n v="-1.0640000000000001E-18"/>
     <n v="15.458292215707898"/>
     <n v="-3.1769590000000001"/>
     <n v="-5.5858538921460505"/>
     <n v="-8.7628128921460515"/>
     <n v="169.0349869583911"/>
-    <n v="5.9159350261975968E-3"/>
-    <n v="0.96471508856304522"/>
+    <n v="5.9159350261975977E-3"/>
+    <n v="0.82466582974349312"/>
   </r>
   <r>
     <x v="6"/>
@@ -2630,40 +2510,40 @@
     <n v="0.16109999999999999"/>
     <n v="0.32779999999999998"/>
     <n v="0.49145820622330688"/>
-    <n v="0.44215983467584091"/>
+    <n v="3.4408521012499207E-2"/>
     <n v="1.0612525E-17"/>
     <n v="375.90612500000003"/>
     <n v="3.7590612500000005E-17"/>
-    <n v="320.56"/>
-    <n v="3.2055999999999996E-17"/>
-    <n v="-3.1900000000000578E-19"/>
+    <n v="316.42"/>
+    <n v="3.1641999999999998E-17"/>
+    <n v="-7.3300000000000373E-19"/>
     <n v="277.49207165509563"/>
     <n v="52.156125000000031"/>
     <n v="-23.128964172452186"/>
     <n v="29.027160827547846"/>
     <n v="131.2450132386972"/>
     <n v="7.619337110974918E-3"/>
-    <n v="0.74904046108037126"/>
+    <n v="0.64030103879517075"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18AC1D4E-8AFF-4F3A-87D7-1A82850D7D48}" name="PivotTable4" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18AC1D4E-8AFF-4F3A-87D7-1A82850D7D48}" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:H14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="29">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="11">
         <item sd="0" x="5"/>
         <item sd="0" x="8"/>
-        <item sd="0" x="3"/>
         <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
         <item sd="0" x="7"/>
         <item sd="0" x="6"/>
         <item sd="0" x="9"/>
         <item sd="0" x="4"/>
+        <item sd="0" x="3"/>
         <item sd="0" x="2"/>
-        <item sd="0" x="1"/>
         <item t="default" sd="0"/>
       </items>
       <autoSortScope>
@@ -2678,35 +2558,35 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="46">
-        <item x="18"/>
-        <item x="3"/>
+      <items count="47">
+        <item x="22"/>
+        <item x="4"/>
         <item x="16"/>
         <item x="29"/>
-        <item x="0"/>
+        <item x="1"/>
         <item x="37"/>
         <item x="27"/>
+        <item x="3"/>
+        <item x="9"/>
         <item x="2"/>
-        <item x="9"/>
-        <item x="1"/>
         <item x="34"/>
         <item x="40"/>
         <item x="30"/>
         <item x="11"/>
         <item x="17"/>
         <item x="35"/>
-        <item x="21"/>
+        <item x="20"/>
         <item x="44"/>
-        <item x="4"/>
+        <item x="0"/>
         <item x="15"/>
         <item x="32"/>
         <item x="12"/>
-        <item x="20"/>
+        <item x="19"/>
         <item x="23"/>
-        <item x="26"/>
+        <item m="1" x="45"/>
         <item x="42"/>
         <item x="5"/>
-        <item x="19"/>
+        <item x="18"/>
         <item x="10"/>
         <item x="28"/>
         <item x="43"/>
@@ -2721,9 +2601,10 @@
         <item x="8"/>
         <item x="36"/>
         <item x="6"/>
-        <item x="22"/>
+        <item x="21"/>
         <item x="39"/>
         <item x="7"/>
+        <item x="26"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -2772,10 +2653,10 @@
       <x v="8"/>
     </i>
     <i>
-      <x v="9"/>
+      <x v="3"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="9"/>
     </i>
     <i>
       <x v="7"/>
@@ -2844,7 +2725,7 @@
     <dataField name="Actual P&amp;L " fld="26" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="32">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2854,7 +2735,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2864,7 +2745,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="5">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2873,7 +2754,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2882,7 +2763,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="3">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2891,7 +2772,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2904,7 +2785,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2917,7 +2798,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2989,953 +2870,404 @@
 </file>
 
 <file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="42">
-  <a r="1">
-    <v t="i">0</v>
-  </a>
-  <a r="1">
-    <v>200.95</v>
-  </a>
-  <a r="1">
-    <v>162.5</v>
-  </a>
-  <a r="1">
-    <v>148.29</v>
-  </a>
-  <a r="1">
-    <v>45.97</v>
-  </a>
-  <a r="1">
-    <v>151.47</v>
-  </a>
-  <a r="1">
-    <v>137.93</v>
-  </a>
-  <a r="1">
-    <v>175.22</v>
-  </a>
-  <a r="1">
-    <v>5.64</v>
-  </a>
-  <a r="1">
-    <v>0.78559999999999997</v>
-  </a>
-  <a r="1">
-    <v>37.11</v>
-  </a>
-  <a r="1">
-    <v>23.2</v>
-  </a>
-  <a r="1">
-    <v>23.59</v>
-  </a>
-  <a r="1">
-    <v>174.06</v>
-  </a>
-  <a r="1">
-    <v>66.66</v>
-  </a>
-  <a r="1">
-    <v>53.34</v>
-  </a>
-  <a r="1">
-    <v>11.05</v>
-  </a>
-  <a r="1">
-    <v>139.22999999999999</v>
-  </a>
-  <a r="1">
-    <v>414.77</v>
-  </a>
-  <a r="1">
-    <v>69.06</v>
-  </a>
-  <a r="1">
-    <v>355.23</v>
-  </a>
-  <a r="1">
-    <v>42.65</v>
-  </a>
-  <a r="1">
-    <v>568.5</v>
-  </a>
-  <a r="1">
-    <v>20.431999999999999</v>
-  </a>
-  <a r="1">
-    <v>38.39</v>
-  </a>
-  <a r="1">
-    <v>18.309999999999999</v>
-  </a>
-  <a r="1">
-    <v>112.06</v>
-  </a>
-  <a r="1">
-    <v>34.020000000000003</v>
-  </a>
-  <a r="1">
-    <v>49.3</v>
-  </a>
-  <a r="1">
-    <v>150.19999999999999</v>
-  </a>
-  <a r="1">
-    <v>47.29</v>
-  </a>
-  <a r="1">
-    <v>104</v>
-  </a>
-  <a r="1">
-    <v>717.5</v>
-  </a>
-  <a r="1">
-    <v>185.27</v>
-  </a>
-  <a r="1">
-    <v>244.87</v>
-  </a>
-  <a r="1">
-    <v>320.56</v>
-  </a>
-  <a r="1">
-    <v>126.91</v>
-  </a>
-  <a r="1">
-    <v>139.5</v>
-  </a>
-  <a r="1">
-    <v>16.874600000000001</v>
-  </a>
-  <a r="1">
-    <v>111.79</v>
-  </a>
-  <a r="1">
-    <v>15.66</v>
-  </a>
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
   <a r="46">
-    <v t="r">0</v>
     <v t="e">#NULL!</v>
-    <v t="r">1</v>
+    <v t="r">41</v>
     <v t="e">#NULL!</v>
-    <v t="r">2</v>
-    <v t="r">3</v>
-    <v t="r">4</v>
-    <v t="r">5</v>
-    <v t="r">6</v>
+    <v t="r">42</v>
     <v t="e">#NULL!</v>
-    <v t="r">7</v>
-    <v t="r">8</v>
-    <v t="r">9</v>
-    <v t="r">10</v>
-    <v t="r">11</v>
-    <v t="r">12</v>
-    <v t="r">13</v>
-    <v t="r">14</v>
-    <v t="r">15</v>
-    <v t="r">16</v>
-    <v t="r">17</v>
-    <v t="r">18</v>
-    <v t="r">19</v>
-    <v t="r">20</v>
-    <v t="r">21</v>
-    <v t="r">22</v>
-    <v t="r">82</v>
-    <v t="r">24</v>
-    <v t="r">25</v>
-    <v t="r">26</v>
-    <v t="r">27</v>
-    <v t="r">28</v>
-    <v t="r">29</v>
-    <v t="r">30</v>
-    <v t="r">31</v>
-    <v t="r">32</v>
-    <v t="r">33</v>
-    <v t="r">34</v>
-    <v t="r">35</v>
-    <v t="r">36</v>
-    <v t="r">37</v>
-    <v t="r">38</v>
-    <v t="r">39</v>
-    <v t="r">40</v>
-    <v t="r">41</v>
+    <v t="r">43</v>
+    <v t="r">44</v>
+    <v t="r">45</v>
+    <v t="r">46</v>
+    <v t="e">#NULL!</v>
+    <v t="r">47</v>
+    <v t="r">48</v>
+    <v t="r">49</v>
+    <v t="r">50</v>
+    <v t="r">51</v>
+    <v t="r">52</v>
+    <v t="r">53</v>
+    <v t="r">54</v>
+    <v t="r">55</v>
+    <v t="r">56</v>
+    <v t="r">57</v>
+    <v t="r">58</v>
+    <v t="r">59</v>
+    <v t="r">60</v>
+    <v t="r">61</v>
+    <v t="r">62</v>
+    <v t="r">63</v>
+    <v t="r">64</v>
+    <v t="r">65</v>
+    <v t="r">66</v>
+    <v t="r">67</v>
+    <v t="r">68</v>
+    <v t="r">69</v>
+    <v t="r">70</v>
+    <v t="r">71</v>
+    <v t="r">72</v>
+    <v t="r">73</v>
+    <v t="r">74</v>
+    <v t="r">75</v>
+    <v t="r">76</v>
+    <v t="r">77</v>
+    <v t="r">78</v>
+    <v t="r">79</v>
+    <v t="r">80</v>
+    <v t="r">81</v>
     <v t="i">2</v>
   </a>
 </arrayData>
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="85">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="84">
   <rv s="0">
-    <fb>23.59</fb>
+    <fb>22.87</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>16.874600000000001</fb>
+    <fb>16.5548</fb>
     <v>1</v>
   </rv>
   <rv s="0">
-    <fb>17.03</fb>
+    <fb>55.25</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>53.34</fb>
+    <fb>36.380000000000003</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>37.11</fb>
+    <fb>45.69</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>45.97</fb>
+    <fb>47.963999999999999</fb>
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <fb>70.8</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>49.3</fb>
+    <fb>43.35</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>140.04</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>153.85</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>191.65</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>130.30000000000001</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>35.47</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>152.91</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>404</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>559</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>179.25</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>150.22999999999999</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>247.1</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>5.09</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>349.86</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>161.1</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>692.1</fb>
     <v>1</v>
   </rv>
   <rv s="0">
-    <fb>69.06</fb>
+    <fb>735.96</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>42.65</fb>
+    <fb>130.28</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>137.93</fb>
+    <fb>168.57</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>139.5</fb>
+    <fb>115.92</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>90.68</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>22.1</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18.28</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>10.79</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>0.72499999999999998</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>93.67</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>66.790000000000006</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>20.470300000000002</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46.81</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>39.369999999999997</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>149.71</fb>
+    <v>3</v>
+  </rv>
+  <rv s="0">
+    <fb>145.47999999999999</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>16.010000000000002</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>319.57</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>22.79</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>16.802</fb>
     <v>1</v>
   </rv>
   <rv s="0">
-    <fb>200.95</fb>
+    <fb>55.05</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>126.91</fb>
+    <fb>36.6</fb>
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <fb>46.4</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>34.020000000000003</fb>
+    <fb>50.3</fb>
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <fb>71.58</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>162.5</fb>
+    <fb>43.39</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>244.87</fb>
+    <fb>140.26</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>414.77</fb>
+    <fb>153.5</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>568.5</fb>
+    <fb>198.24</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>185.27</fb>
+    <fb>128.08000000000001</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>148.29</fb>
+    <fb>35.22</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>5.64</fb>
+    <fb>155.44</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>355.23</fb>
+    <fb>408.21</fb>
     <v>0</v>
   </rv>
   <rv s="0">
-    <fb>175.22</fb>
+    <fb>557.51</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>179.66</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>148.75</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>245.55</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>5.22</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>348.53</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>165.43</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>702.4</fb>
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <fb>737.21</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>134.43</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>171.98</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>115.55</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>101.35</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>23.06</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18.32</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>11.28</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>0.74750000000000005</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>94.78</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>66.680000000000007</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>20.41</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46.69</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>39.22</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>149.29</fb>
+    <v>3</v>
+  </rv>
+  <rv s="0">
+    <fb>144.97999999999999</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>15.99</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>316.42</fb>
     <v>0</v>
   </rv>
   <rv s="1">
-    <v>2</v>
-    <v>18</v>
-  </rv>
-  <rv s="0">
-    <fb>717.5</fb>
-    <v>1</v>
-  </rv>
-  <rv s="0">
-    <fb>139.22999999999999</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>174.06</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>111.79</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>112.06</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>23.2</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>18.309999999999999</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>11.05</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>0.78559999999999997</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>104</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>66.66</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>20.431999999999999</fb>
-    <v>2</v>
-  </rv>
-  <rv s="0">
-    <fb>47.29</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>38.39</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>151.47</fb>
-    <v>3</v>
-  </rv>
-  <rv s="0">
-    <fb>150.19999999999999</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>15.66</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>320.56</fb>
     <v>0</v>
   </rv>
   <rv s="2">
-    <v>4</v>
-    <v>TSM</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345373213,0</v>
-    <v>0</v>
-    <v>a24kjc</v>
-    <v>XNYS:TSM</v>
-    <v>1</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>FSLR</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195344434400,0</v>
-    <v>0</v>
-    <v>a1tdvh</v>
-    <v>XNAS:FSLR</v>
-    <v>2</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>YUM</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343637206,0</v>
-    <v>0</v>
-    <v>a26em7</v>
-    <v>XNYS:YUM</v>
-    <v>3</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>VWO.US</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195344265467,0</v>
-    <v>0</v>
-    <v>a25nhw</v>
-    <v>ARCX:VWO</v>
-    <v>4</v>
-  </rv>
-  <rv s="2">
-    <v>5</v>
-    <v>USDJPY=X</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195344297942,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>5</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>KMB</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195344463565,0</v>
-    <v>0</v>
-    <v>a1wjz2</v>
-    <v>XNYS:KMB</v>
-    <v>6</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>QCOM</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345514549,0</v>
-    <v>0</v>
-    <v>a21k2w</v>
-    <v>XNAS:QCOM</v>
-    <v>7</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>MAXN</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195344407151,0</v>
-    <v>0</v>
-    <v>bvhkk2</v>
-    <v>XNAS:MAXN</v>
-    <v>8</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>GC=F</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195344336785,0</v>
-    <v>0</v>
-    <v>a2losm</v>
-    <v>OTCM:JETMF</v>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>YPF</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195435611501,0</v>
-    <v>0</v>
-    <v>a26e7w</v>
-    <v>XNYS:YPF</v>
-    <v>10</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>JKS</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195344370947,0</v>
-    <v>0</v>
-    <v>a1w7f2</v>
-    <v>XNYS:JKS</v>
-    <v>11</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>APA</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195344530952,0</v>
-    <v>0</v>
-    <v>a1nkur</v>
-    <v>XNAS:APA</v>
-    <v>12</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>AMAT</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343841890,0</v>
-    <v>0</v>
-    <v>a1nda2</v>
-    <v>XNAS:AMAT</v>
-    <v>13</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>APTV</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343547070,0</v>
-    <v>0</v>
-    <v>awagjc</v>
-    <v>XNYS:APTV</v>
-    <v>14</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>MO</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345407070,0</v>
-    <v>0</v>
-    <v>a1xtpr</v>
-    <v>XNYS:MO</v>
-    <v>15</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>CSIQ</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343580784,0</v>
-    <v>0</v>
-    <v>a1qepr</v>
-    <v>XNAS:CSIQ</v>
-    <v>16</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>NVDA</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343604968,0</v>
-    <v>0</v>
-    <v>a1yv52</v>
-    <v>XNAS:NVDA</v>
-    <v>17</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>MSFT</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343657119,0</v>
-    <v>0</v>
-    <v>a1xzim</v>
-    <v>XNAS:MSFT</v>
-    <v>18</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>NEE</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343682753,0</v>
-    <v>0</v>
-    <v>a1ye2w</v>
-    <v>XNYS:NEE</v>
-    <v>19</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>V</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343744492,0</v>
-    <v>0</v>
-    <v>a256cw</v>
-    <v>XNYS:V</v>
-    <v>20</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>EXC</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343720482,0</v>
-    <v>0</v>
-    <v>a1shjc</v>
-    <v>XNAS:EXC</v>
-    <v>21</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>MA</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345356613,0</v>
-    <v>0</v>
-    <v>a1x8w7</v>
-    <v>XNYS:MA</v>
-    <v>22</v>
-  </rv>
-  <rv s="2">
-    <v>6</v>
-    <v>USDMXN=X</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343813914,0</v>
-    <v>0</v>
-    <v>avyqcw</v>
-    <v>USDMXN</v>
-    <v>23</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>DAR</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345450404,0</v>
-    <v>0</v>
-    <v>a1qqk2</v>
-    <v>XNYS:DAR</v>
-    <v>24</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>SWI</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343680192,0</v>
-    <v>0</v>
-    <v>bn8mkr</v>
-    <v>XNYS:SWI</v>
-    <v>25</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>PLTR</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345479208,0</v>
-    <v>0</v>
-    <v>bvsk7w</v>
-    <v>XNAS:PLTR</v>
-    <v>26</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>AGIO</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345541479,0</v>
-    <v>0</v>
-    <v>a1n2qh</v>
-    <v>XNAS:AGIO</v>
-    <v>27</v>
-  </rv>
-  <rv s="2">
-    <v>7</v>
-    <v>VBTC.DE</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345591773,0</v>
-    <v>0</v>
-    <v>bwxxim</v>
-    <v>XFRA:VBTC</v>
-    <v>28</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>MMM</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345619194,0</v>
-    <v>0</v>
-    <v>a1xroc</v>
-    <v>XNYS:MMM</v>
-    <v>29</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>YUMC</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195345649314,0</v>
-    <v>0</v>
-    <v>a26erw</v>
-    <v>XNYS:YUMC</v>
-    <v>30</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>WMT</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343638409,0</v>
-    <v>0</v>
-    <v>a25ya2</v>
-    <v>XNYS:WMT</v>
-    <v>31</v>
-  </rv>
-  <rv s="2">
-    <v>7</v>
-    <v>ASML</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343716563,0</v>
-    <v>0</v>
-    <v>alnz5r</v>
-    <v>XAMS:ASML</v>
-    <v>32</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>GOOGL</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343767202,0</v>
-    <v>0</v>
-    <v>a1u3rw</v>
-    <v>XNAS:GOOGL</v>
-    <v>33</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>AAPL</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343793213,0</v>
-    <v>0</v>
-    <v>a1mou2</v>
-    <v>XNAS:AAPL</v>
-    <v>34</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>HCA</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343924290,0</v>
-    <v>0</v>
-    <v>a1uhnm</v>
-    <v>XNYS:HCA</v>
-    <v>35</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>INGR</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343830973,0</v>
-    <v>0</v>
-    <v>a1vkp2</v>
-    <v>XNYS:INGR</v>
-    <v>36</v>
-  </rv>
-  <rv s="2">
-    <v>7</v>
-    <v>PEP</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343863163,0</v>
-    <v>0</v>
-    <v>afiar7</v>
-    <v>XFRA:PEP</v>
-    <v>37</v>
-  </rv>
-  <rv s="2">
-    <v>7</v>
-    <v>BATT.NL</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343888223,0</v>
-    <v>0</v>
-    <v>aytcmw</v>
-    <v>XAMS:BATT</v>
-    <v>38</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>DUK</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343286502,0</v>
-    <v>0</v>
-    <v>a1rdzr</v>
-    <v>XNYS:DUK</v>
-    <v>39</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>PCG</v>
-    <v>Daily</v>
-    <v>45707</v>
-    <v>45707</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638755200000000000,638756195343315233,0</v>
-    <v>0</v>
-    <v>a1zkar</v>
-    <v>XNYS:PCG</v>
-    <v>40</v>
-  </rv>
-  <rv s="3">
-    <v>2</v>
-    <v>1</v>
-  </rv>
-  <rv s="4">
-    <v>41</v>
-  </rv>
-  <rv s="5">
     <v>{1E74FF3F-FD41-47C6-9554-6AF9D4A04843}</v>
     <v>0</v>
-    <v>8</v>
-    <v>83</v>
+    <v>4</v>
+    <v>82</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <s t="_formattednumber">
     <k n="_Format" t="spb"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-  <s t="_stockhistorycache">
-    <k n="_Format" t="spb"/>
-    <k n="Symbol" t="s"/>
-    <k n="Interval" t="s"/>
-    <k n="StartDate" t="i"/>
-    <k n="EndDate" t="i"/>
-    <k n="f1904" t="b"/>
-    <k n="fdcompat" t="b"/>
-    <k n="etag" t="s"/>
-    <k n="Date" t="a"/>
-    <k n="EntityId" t="s"/>
-    <k n="Instrument" t="s"/>
-    <k n="Close" t="a"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="propagated" t="b"/>
   </s>
   <s t="_array">
     <k n="array" t="a"/>
@@ -3959,7 +3291,7 @@
       <v t="s">_Display</v>
     </a>
   </spbArrays>
-  <spbData count="9">
+  <spbData count="5">
     <spb s="0">
       <v>1</v>
     </spb>
@@ -3973,22 +3305,6 @@
       <v>4</v>
     </spb>
     <spb s="1">
-      <v>5</v>
-      <v>1</v>
-    </spb>
-    <spb s="1">
-      <v>5</v>
-      <v>4</v>
-    </spb>
-    <spb s="1">
-      <v>5</v>
-      <v>3</v>
-    </spb>
-    <spb s="1">
-      <v>5</v>
-      <v>2</v>
-    </spb>
-    <spb s="2">
       <v>0</v>
     </spb>
   </spbData>
@@ -3996,13 +3312,9 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="3">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="2">
   <s>
     <k n="_Self" t="i"/>
-  </s>
-  <s>
-    <k n="Date" t="i"/>
-    <k n="Close" t="i"/>
   </s>
   <s>
     <k n="^Order" t="spba"/>
@@ -4012,12 +3324,9 @@
 
 <file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
 <richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <dxfs count="2">
+  <dxfs count="1">
     <x:dxf>
       <x:numFmt numFmtId="0" formatCode="General"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </x:dxf>
   </dxfs>
   <richProperties>
@@ -4036,7 +3345,6 @@
     <rSty dxfid="0">
       <rpv i="0">_-[$¥-ja-JP]* #,##0.00_-;-[$¥-ja-JP]* #,##0.00_-;_-[$¥-ja-JP]* "-"??_-;_-@_-</rpv>
     </rSty>
-    <rSty dxfid="1"/>
   </richStyles>
 </richStyleSheet>
 </file>
@@ -4405,119 +3713,117 @@
     </row>
     <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
+        <v>37</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>87</v>
       </c>
       <c r="D2" s="8">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="E2" s="2">
-        <v>2.2953000000000001</v>
+        <v>3.1236000000000002</v>
       </c>
       <c r="F2" s="1">
-        <v>21.78</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1">
         <f t="shared" ref="G2:G46" si="0">E2*F2</f>
-        <v>49.991634000000005</v>
+        <v>49.977600000000002</v>
       </c>
       <c r="H2" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-8.7400000000000005E-2</v>
+        <v>7.0499999999999993E-2</v>
       </c>
       <c r="I2" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.60389999999999999</v>
+        <v>0.35260000000000002</v>
       </c>
       <c r="J2" s="9">
         <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
-        <v>-0.14472594800463653</v>
+        <v>0.19994327850255245</v>
       </c>
       <c r="K2" s="9">
         <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.13020842959321346</v>
+        <v>4.267101492179555E-2</v>
       </c>
       <c r="L2" s="9">
         <f>I2*G2</f>
-        <v>30.189947772600004</v>
+        <v>17.622101760000003</v>
       </c>
       <c r="M2" s="12">
         <f>IF((1+H2)*F2&lt;0,0,(1+H2)*F2)</f>
-        <v>19.876428000000001</v>
+        <v>17.128</v>
       </c>
       <c r="N2" s="12">
         <f t="shared" ref="N2:N46" si="3">M2*E2</f>
-        <v>45.622365188400003</v>
-      </c>
-      <c r="O2" s="12" cm="1" vm="1">
-        <f t="array" aca="1" ref="O2" ca="1">_xlfn.STOCKHISTORY(C2,TODAY(),TODAY(),0,0,1)</f>
-        <v>23.59</v>
+        <v>53.501020800000006</v>
+      </c>
+      <c r="O2" s="12">
+        <v>17.100000000000001</v>
       </c>
       <c r="P2" s="12">
-        <f ca="1">IFERROR(O2*E2,G2)</f>
-        <v>54.146127</v>
+        <f t="shared" ref="P2:P46" si="4">IFERROR(O2*E2,G2)</f>
+        <v>53.413560000000004</v>
       </c>
       <c r="Q2" s="12">
-        <f ca="1">P2-G2</f>
-        <v>4.1544929999999951</v>
+        <f t="shared" ref="Q2:Q46" si="5">P2-G2</f>
+        <v>3.4359600000000015</v>
       </c>
       <c r="R2" s="12">
-        <f t="shared" ref="R2:R41" si="4">F2/(1+I2-H2)</f>
-        <v>12.877668065984748</v>
+        <f t="shared" ref="R2:R41" si="6">F2/(1+I2-H2)</f>
+        <v>12.479525778020435</v>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S41" si="5">M2-F2</f>
-        <v>-1.9035720000000005</v>
+        <f t="shared" ref="S2:S41" si="7">M2-F2</f>
+        <v>1.1280000000000001</v>
       </c>
       <c r="T2" s="12">
-        <f t="shared" ref="T2:T41" si="6">0.5*(R2-F2)</f>
-        <v>-4.4511659670076265</v>
+        <f t="shared" ref="T2:T41" si="8">0.5*(R2-F2)</f>
+        <v>-1.7602371109897827</v>
       </c>
       <c r="U2" s="14">
-        <f t="shared" ref="U2:U41" si="7">S2+T2</f>
-        <v>-6.3547379670076269</v>
+        <f t="shared" ref="U2:U41" si="9">S2+T2</f>
+        <v>-0.63223711098978264</v>
       </c>
       <c r="V2" s="12">
-        <f t="shared" ref="V2:V46" si="8">MAX($U$2:$U$280)-U2</f>
-        <v>166.62691203325267</v>
+        <f t="shared" ref="V2:V46" si="10">MAX($U$2:$U$280)-U2</f>
+        <v>160.90441117723483</v>
       </c>
       <c r="W2" s="9">
-        <f t="shared" ref="W2:W46" si="9">IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V2)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>6.0014315082574203E-3</v>
+        <f t="shared" ref="W2:W46" si="11">IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V2)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
+        <v>6.2148700130943493E-3</v>
       </c>
       <c r="X2" s="9">
-        <f t="shared" ref="X2:X41" si="10">V2/MAX($V$2:$V$28)</f>
-        <v>0.95097174313809352</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+        <f t="shared" ref="X2:X41" si="12">V2/MAX($V$2:$V$28)</f>
+        <v>0.91831233327595496</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="D3" s="8">
-        <v>45481</v>
+        <v>45627</v>
       </c>
       <c r="E3" s="2">
-        <v>2</v>
+        <v>2.2953000000000001</v>
       </c>
       <c r="F3" s="1">
-        <f>45.12/2</f>
-        <v>22.56</v>
+        <v>21.78</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>45.12</v>
+        <v>49.991634000000005</v>
       </c>
       <c r="H3" s="21">
         <v>3.5000000000000003E-2</v>
@@ -4531,69 +3837,69 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>0.19084324749302797</v>
+        <v>4.5269975942392342E-2</v>
       </c>
       <c r="L3" s="9">
-        <f t="shared" ref="L3:L47" si="11">I3*G3</f>
-        <v>7.4447999999999999</v>
+        <f t="shared" ref="L3:L46" si="13">I3*G3</f>
+        <v>8.2486196100000004</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ref="M3:M41" si="12">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
-        <v>23.349599999999995</v>
+        <f t="shared" ref="M3:M41" si="14">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
+        <v>22.542300000000001</v>
       </c>
       <c r="N3" s="12">
         <f t="shared" si="3"/>
-        <v>46.69919999999999</v>
-      </c>
-      <c r="O3" s="12">
-        <v>22.65</v>
+        <v>51.741341190000007</v>
+      </c>
+      <c r="O3" s="12" vm="1">
+        <v>22.87</v>
       </c>
       <c r="P3" s="12">
-        <f>IFERROR(O3*E3,G3)</f>
-        <v>45.3</v>
+        <f t="shared" si="4"/>
+        <v>52.493511000000005</v>
       </c>
       <c r="Q3" s="12">
-        <f>P3-G3</f>
-        <v>0.17999999999999972</v>
+        <f t="shared" si="5"/>
+        <v>2.5018770000000004</v>
       </c>
       <c r="R3" s="12">
-        <f t="shared" si="4"/>
-        <v>19.9646017699115</v>
+        <f t="shared" si="6"/>
+        <v>19.274336283185839</v>
       </c>
       <c r="S3" s="12">
-        <f t="shared" si="5"/>
-        <v>0.78959999999999653</v>
+        <f t="shared" si="7"/>
+        <v>0.76229999999999976</v>
       </c>
       <c r="T3" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.2976991150442494</v>
+        <f t="shared" si="8"/>
+        <v>-1.252831858407081</v>
       </c>
       <c r="U3" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.50809911504425287</v>
+        <f t="shared" si="9"/>
+        <v>-0.49053185840708124</v>
       </c>
       <c r="V3" s="12">
-        <f t="shared" si="8"/>
-        <v>160.78027318128929</v>
+        <f t="shared" si="10"/>
+        <v>160.76270592465212</v>
       </c>
       <c r="W3" s="9">
-        <f t="shared" si="9"/>
-        <v>6.2196684967218627E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.2203481475902132E-3</v>
       </c>
       <c r="X3" s="9">
-        <f t="shared" si="10"/>
-        <v>0.91760385392556976</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0.917503594222845</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>145</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D4" s="8">
         <v>45481</v>
@@ -4602,11 +3908,11 @@
         <v>2</v>
       </c>
       <c r="F4" s="1">
-        <v>16.399000000000001</v>
+        <v>20.927</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>32.798000000000002</v>
+        <v>41.853999999999999</v>
       </c>
       <c r="H4" s="21">
         <v>3.5000000000000003E-2</v>
@@ -4620,244 +3926,243 @@
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>0.19084324749302797</v>
+        <v>4.5269975942392342E-2</v>
       </c>
       <c r="L4" s="9">
-        <f t="shared" si="11"/>
-        <v>5.4116700000000009</v>
+        <f t="shared" si="13"/>
+        <v>6.9059100000000004</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" si="12"/>
-        <v>16.972964999999999</v>
+        <f t="shared" si="14"/>
+        <v>21.659444999999998</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" si="3"/>
-        <v>33.945929999999997</v>
-      </c>
-      <c r="O4" s="26" cm="1" vm="2">
-        <f t="array" aca="1" ref="O4" ca="1">_xlfn.STOCKHISTORY(C4,TODAY(),TODAY(),0,0,1)</f>
-        <v>16.874600000000001</v>
+        <v>43.318889999999996</v>
+      </c>
+      <c r="O4" s="12">
+        <v>22.41</v>
       </c>
       <c r="P4" s="12">
-        <f ca="1">IFERROR(O4*E4,G4)</f>
-        <v>33.749200000000002</v>
+        <f t="shared" si="4"/>
+        <v>44.82</v>
       </c>
       <c r="Q4" s="12">
-        <f ca="1">P4-G4</f>
-        <v>0.95120000000000005</v>
+        <f t="shared" si="5"/>
+        <v>2.9660000000000011</v>
       </c>
       <c r="R4" s="12">
-        <f t="shared" si="4"/>
-        <v>14.512389380530973</v>
+        <f t="shared" si="6"/>
+        <v>18.51946902654867</v>
       </c>
       <c r="S4" s="12">
-        <f t="shared" si="5"/>
-        <v>0.57396499999999762</v>
+        <f t="shared" si="7"/>
+        <v>0.73244499999999846</v>
       </c>
       <c r="T4" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.9433053097345141</v>
+        <f t="shared" si="8"/>
+        <v>-1.2037654867256649</v>
       </c>
       <c r="U4" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.36934030973451648</v>
+        <f t="shared" si="9"/>
+        <v>-0.4713204867256664</v>
       </c>
       <c r="V4" s="12">
-        <f t="shared" si="8"/>
-        <v>160.64151437597957</v>
+        <f t="shared" si="10"/>
+        <v>160.7434945529707</v>
       </c>
       <c r="W4" s="9">
-        <f t="shared" si="9"/>
-        <v>6.2250409172532562E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.2210915768691616E-3</v>
       </c>
       <c r="X4" s="9">
-        <f t="shared" si="10"/>
-        <v>0.91681193081212453</v>
+        <f t="shared" si="12"/>
+        <v>0.91739395124024981</v>
       </c>
     </row>
     <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>100</v>
+        <v>145</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" t="s">
+        <v>147</v>
       </c>
       <c r="D5" s="8">
-        <v>45630</v>
+        <v>45481</v>
       </c>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="1">
-        <v>20.5</v>
+        <v>16.399000000000001</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>32.798000000000002</v>
       </c>
       <c r="H5" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.14929999999999999</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I5" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.31569999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="J5" s="9">
         <f t="shared" si="1"/>
-        <v>0.47291732657586316</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>0.42547879816887618</v>
+        <v>2.1341560087127818E-2</v>
       </c>
       <c r="L5" s="9">
-        <f t="shared" si="11"/>
-        <v>12.9437</v>
+        <f t="shared" si="13"/>
+        <v>8.1995000000000005</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="12"/>
-        <v>23.560649999999999</v>
+        <f t="shared" si="14"/>
+        <v>16.808975</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="3"/>
-        <v>47.121299999999998</v>
-      </c>
-      <c r="O5" s="26">
-        <v>20.52</v>
+        <v>33.61795</v>
+      </c>
+      <c r="O5" s="12" vm="2">
+        <v>16.5548</v>
       </c>
       <c r="P5" s="12">
-        <f>IFERROR(O5*E5,G5)</f>
-        <v>41.04</v>
+        <f t="shared" si="4"/>
+        <v>33.1096</v>
       </c>
       <c r="Q5" s="12">
-        <f>P5-G5</f>
-        <v>3.9999999999999147E-2</v>
+        <f t="shared" si="5"/>
+        <v>0.31159999999999854</v>
       </c>
       <c r="R5" s="12">
-        <f t="shared" si="4"/>
-        <v>17.575445816186555</v>
+        <f t="shared" si="6"/>
+        <v>13.386938775510204</v>
       </c>
       <c r="S5" s="12">
-        <f t="shared" si="5"/>
-        <v>3.060649999999999</v>
+        <f t="shared" si="7"/>
+        <v>0.40997499999999931</v>
       </c>
       <c r="T5" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.4622770919067225</v>
+        <f t="shared" si="8"/>
+        <v>-1.5060306122448983</v>
       </c>
       <c r="U5" s="14">
-        <f t="shared" si="7"/>
-        <v>1.5983729080932765</v>
+        <f t="shared" si="9"/>
+        <v>-1.096055612244899</v>
       </c>
       <c r="V5" s="12">
-        <f t="shared" si="8"/>
-        <v>158.67380115815178</v>
+        <f t="shared" si="10"/>
+        <v>161.36822967848994</v>
       </c>
       <c r="W5" s="9">
-        <f t="shared" si="9"/>
-        <v>6.302237626508298E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.1970066969960569E-3</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" si="10"/>
-        <v>0.90558181410456573</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0.92095943441499695</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>86</v>
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D6" s="8">
-        <v>45623</v>
+        <v>45630</v>
       </c>
       <c r="E6" s="2">
-        <v>1.9595</v>
+        <v>2</v>
       </c>
       <c r="F6" s="1">
-        <v>15.3</v>
+        <v>20.5</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>29.980350000000001</v>
+        <v>41</v>
       </c>
       <c r="H6" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>7.0499999999999993E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1),2.5%)+2.5%</f>
+        <v>0.17429999999999998</v>
       </c>
       <c r="I6" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.35260000000000002</v>
+        <v>0.31569999999999998</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="1"/>
-        <v>0.19994327850255245</v>
+        <v>0.55210643015521066</v>
       </c>
       <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v>0.17988688732377014</v>
+        <v>0.11782812553647067</v>
       </c>
       <c r="L6" s="9">
-        <f t="shared" si="11"/>
-        <v>10.571071410000002</v>
+        <f t="shared" si="13"/>
+        <v>12.9437</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="12"/>
-        <v>16.37865</v>
+        <f t="shared" si="14"/>
+        <v>24.073149999999998</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="3"/>
-        <v>32.093964675000002</v>
-      </c>
-      <c r="O6" s="12" vm="3">
-        <v>17.03</v>
+        <v>48.146299999999997</v>
+      </c>
+      <c r="O6" s="26">
+        <v>20.52</v>
       </c>
       <c r="P6" s="12">
-        <f>IFERROR(O6*E6,G6)</f>
-        <v>33.370285000000003</v>
+        <f t="shared" si="4"/>
+        <v>41.04</v>
       </c>
       <c r="Q6" s="12">
-        <f>P6-G6</f>
-        <v>3.3899350000000013</v>
+        <f t="shared" si="5"/>
+        <v>3.9999999999999147E-2</v>
       </c>
       <c r="R6" s="12">
-        <f t="shared" si="4"/>
-        <v>11.933546525232041</v>
+        <f t="shared" si="6"/>
+        <v>17.960399509374451</v>
       </c>
       <c r="S6" s="12">
-        <f t="shared" si="5"/>
-        <v>1.0786499999999997</v>
+        <f t="shared" si="7"/>
+        <v>3.5731499999999983</v>
       </c>
       <c r="T6" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.68322673738398</v>
+        <f t="shared" si="8"/>
+        <v>-1.2698002453127746</v>
       </c>
       <c r="U6" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.60457673738398032</v>
+        <f t="shared" si="9"/>
+        <v>2.3033497546872237</v>
       </c>
       <c r="V6" s="12">
-        <f t="shared" si="8"/>
-        <v>160.87675080362902</v>
+        <f t="shared" si="10"/>
+        <v>157.96882431155782</v>
       </c>
       <c r="W6" s="9">
-        <f t="shared" si="9"/>
-        <v>6.2159385679079878E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.3303629963575971E-3</v>
       </c>
       <c r="X6" s="9">
-        <f t="shared" si="10"/>
-        <v>0.91815447021900465</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0.90155837603866884</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -4881,8 +4186,8 @@
         <v>89.991048000000006</v>
       </c>
       <c r="H7" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>5.8799999999999998E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1),2.5%)+8.2%</f>
+        <v>0.14079999999999998</v>
       </c>
       <c r="I7" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),2),25%)</f>
@@ -4890,63 +4195,62 @@
       </c>
       <c r="J7" s="9">
         <f t="shared" si="1"/>
-        <v>0.26017699115044246</v>
+        <v>0.623008849557522</v>
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>0.23407853188082897</v>
+        <v>0.1329598079764423</v>
       </c>
       <c r="L7" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>20.337976848</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="12"/>
-        <v>54.930543999999998</v>
+        <f t="shared" si="14"/>
+        <v>59.184704000000004</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="3"/>
-        <v>95.282521622399997</v>
-      </c>
-      <c r="O7" s="12" cm="1" vm="4">
-        <f t="array" aca="1" ref="O7" ca="1">_xlfn.STOCKHISTORY(C7,TODAY(),TODAY(),0,0,1)</f>
-        <v>53.34</v>
+        <v>102.66178755840001</v>
+      </c>
+      <c r="O7" s="12" vm="3">
+        <v>55.25</v>
       </c>
       <c r="P7" s="12">
-        <f ca="1">IFERROR(O7*E7,G7)</f>
-        <v>92.523564000000007</v>
+        <f t="shared" si="4"/>
+        <v>95.836649999999992</v>
       </c>
       <c r="Q7" s="12">
-        <f ca="1">P7-G7</f>
-        <v>2.5325160000000011</v>
+        <f t="shared" si="5"/>
+        <v>5.8456019999999853</v>
       </c>
       <c r="R7" s="12">
-        <f t="shared" si="4"/>
-        <v>44.44825222755312</v>
+        <f t="shared" si="6"/>
+        <v>47.806855879100631</v>
       </c>
       <c r="S7" s="12">
-        <f t="shared" si="5"/>
-        <v>3.050543999999995</v>
+        <f t="shared" si="7"/>
+        <v>7.304704000000001</v>
       </c>
       <c r="T7" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.7158738862234415</v>
+        <f t="shared" si="8"/>
+        <v>-2.0365720604496858</v>
       </c>
       <c r="U7" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.66532988622344647</v>
+        <f t="shared" si="9"/>
+        <v>5.2681319395503152</v>
       </c>
       <c r="V7" s="12">
-        <f t="shared" si="8"/>
-        <v>160.93750395246849</v>
+        <f t="shared" si="10"/>
+        <v>155.00404212669474</v>
       </c>
       <c r="W7" s="9">
-        <f t="shared" si="9"/>
-        <v>6.21359208040993E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.4514446609246221E-3</v>
       </c>
       <c r="X7" s="9">
-        <f t="shared" si="10"/>
-        <v>0.91850120009083625</v>
+        <f t="shared" si="12"/>
+        <v>0.88463779551562971</v>
       </c>
     </row>
     <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -4963,14 +4267,14 @@
         <v>45627</v>
       </c>
       <c r="E8" s="2">
-        <v>1.2354000000000001</v>
+        <v>1.5004999999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>40.49</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>50.021346000000001</v>
+        <v>60.019999999999996</v>
       </c>
       <c r="H8" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),1),2.5%)</f>
@@ -4986,62 +4290,61 @@
       </c>
       <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v>7.0448503165926199E-2</v>
+        <v>1.6711107599526358E-2</v>
       </c>
       <c r="L8" s="9">
-        <f t="shared" si="11"/>
-        <v>26.766422244600001</v>
+        <f t="shared" si="13"/>
+        <v>32.116701999999997</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="12"/>
-        <v>42.186531000000002</v>
+        <f t="shared" si="14"/>
+        <v>41.676000000000002</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="3"/>
-        <v>52.117240397400003</v>
-      </c>
-      <c r="O8" s="12" cm="1" vm="5">
-        <f t="array" aca="1" ref="O8" ca="1">_xlfn.STOCKHISTORY(C8,TODAY(),TODAY(),0,0,1)</f>
-        <v>37.11</v>
+        <v>62.534838000000001</v>
+      </c>
+      <c r="O8" s="12" vm="4">
+        <v>36.380000000000003</v>
       </c>
       <c r="P8" s="12">
-        <f ca="1">IFERROR(O8*E8,G8)</f>
-        <v>45.845694000000002</v>
+        <f t="shared" si="4"/>
+        <v>54.588190000000004</v>
       </c>
       <c r="Q8" s="12">
-        <f ca="1">P8-G8</f>
-        <v>-4.1756519999999995</v>
+        <f t="shared" si="5"/>
+        <v>-5.4318099999999916</v>
       </c>
       <c r="R8" s="12">
-        <f t="shared" si="4"/>
-        <v>27.116260380391111</v>
+        <f t="shared" si="6"/>
+        <v>26.788106080900082</v>
       </c>
       <c r="S8" s="12">
-        <f t="shared" si="5"/>
-        <v>1.6965310000000002</v>
+        <f t="shared" si="7"/>
+        <v>1.6760000000000019</v>
       </c>
       <c r="T8" s="12">
-        <f t="shared" si="6"/>
-        <v>-6.6868698098044455</v>
+        <f t="shared" si="8"/>
+        <v>-6.6059469595499589</v>
       </c>
       <c r="U8" s="14">
-        <f t="shared" si="7"/>
-        <v>-4.9903388098044452</v>
+        <f t="shared" si="9"/>
+        <v>-4.929946959549957</v>
       </c>
       <c r="V8" s="12">
-        <f t="shared" si="8"/>
-        <v>165.2625128760495</v>
+        <f t="shared" si="10"/>
+        <v>165.20212102579501</v>
       </c>
       <c r="W8" s="9">
-        <f t="shared" si="9"/>
-        <v>6.0509790308587519E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.0531910473707404E-3</v>
       </c>
       <c r="X8" s="9">
-        <f t="shared" si="10"/>
-        <v>0.94318485547973796</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0.94284018760822152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>145</v>
       </c>
@@ -5076,62 +4379,61 @@
       </c>
       <c r="K9" s="9">
         <f t="shared" si="2"/>
-        <v>0.21371936747166675</v>
+        <v>5.0696426260610133E-2</v>
       </c>
       <c r="L9" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>11.546640000000002</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>46.982880000000002</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="3"/>
         <v>46.982880000000002</v>
       </c>
-      <c r="O9" s="12" cm="1" vm="6">
-        <f t="array" aca="1" ref="O9" ca="1">_xlfn.STOCKHISTORY(C9,TODAY(),TODAY(),0,0,1)</f>
-        <v>45.97</v>
+      <c r="O9" s="12" vm="5">
+        <v>45.69</v>
       </c>
       <c r="P9" s="12">
-        <f ca="1">IFERROR(O9*E9,G9)</f>
-        <v>45.97</v>
+        <f t="shared" si="4"/>
+        <v>45.69</v>
       </c>
       <c r="Q9" s="12">
-        <f ca="1">P9-G9</f>
-        <v>1.7299999999999969</v>
+        <f t="shared" si="5"/>
+        <v>1.4499999999999957</v>
       </c>
       <c r="R9" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>36.897414512093412</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.7428799999999995</v>
       </c>
       <c r="T9" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-3.6712927439532947</v>
       </c>
       <c r="U9" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-0.92841274395329521</v>
       </c>
       <c r="V9" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>161.20058681019833</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" si="9"/>
-        <v>6.2034513632225506E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.2034513632225514E-3</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.92000266441464951</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>145</v>
       </c>
@@ -5166,62 +4468,61 @@
       </c>
       <c r="K10" s="9">
         <f t="shared" si="2"/>
-        <v>0.20229706877113868</v>
+        <v>4.7986939840879116E-2</v>
       </c>
       <c r="L10" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8.2269199999999998</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>50.52984</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="3"/>
         <v>50.52984</v>
       </c>
-      <c r="O10" s="12" cm="1" vm="7">
-        <f t="array" aca="1" ref="O10" ca="1">_xlfn.STOCKHISTORY(C10,TODAY(),TODAY(),0,0,1)</f>
-        <v>49.3</v>
+      <c r="O10" s="12" vm="6">
+        <v>47.963999999999999</v>
       </c>
       <c r="P10" s="12">
-        <f ca="1">IFERROR(O10*E10,G10)</f>
-        <v>49.3</v>
+        <f t="shared" si="4"/>
+        <v>47.963999999999999</v>
       </c>
       <c r="Q10" s="12">
-        <f ca="1">P10-G10</f>
-        <v>0.61999999999999744</v>
+        <f t="shared" si="5"/>
+        <v>-0.71600000000000108</v>
       </c>
       <c r="R10" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>43.041556145004421</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.8498400000000004</v>
       </c>
       <c r="T10" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-2.8192219274977894</v>
       </c>
       <c r="U10" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-0.96938192749778906</v>
       </c>
       <c r="V10" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>161.24155599374282</v>
       </c>
       <c r="W10" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.2018751545588301E-3</v>
       </c>
       <c r="X10" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.92023648340231989</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>145</v>
       </c>
@@ -5256,14 +4557,14 @@
       </c>
       <c r="K11" s="9">
         <f t="shared" si="2"/>
-        <v>0.20229706877113868</v>
+        <v>4.7986939840879116E-2</v>
       </c>
       <c r="L11" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8.6663200000000007</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>53.228640000000006</v>
       </c>
       <c r="N11" s="12">
@@ -5274,39 +4575,39 @@
         <v>51.28</v>
       </c>
       <c r="P11" s="12">
-        <f>IFERROR(O11*E11,G11)</f>
+        <f t="shared" si="4"/>
         <v>51.28</v>
       </c>
       <c r="Q11" s="12">
-        <f>P11-G11</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R11" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>45.340406719717066</v>
       </c>
       <c r="S11" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.9486400000000046</v>
       </c>
       <c r="T11" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-2.9697966401414675</v>
       </c>
       <c r="U11" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-1.0211566401414629</v>
       </c>
       <c r="V11" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>161.29333070638651</v>
       </c>
       <c r="W11" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1998843698030494E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.1998843698030503E-3</v>
       </c>
       <c r="X11" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.92053197161687317</v>
       </c>
     </row>
@@ -5347,58 +4648,57 @@
       </c>
       <c r="K12" s="9">
         <f t="shared" si="2"/>
-        <v>0.44434547250734346</v>
+        <v>0.10540330409779509</v>
       </c>
       <c r="L12" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>13.493949678</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>82.632440000000003</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="3"/>
         <v>61.652063484000003</v>
       </c>
-      <c r="O12" s="12" cm="1" vm="8">
-        <f t="array" aca="1" ref="O12" ca="1">_xlfn.STOCKHISTORY(C12,TODAY(),TODAY(),0,0,1)</f>
-        <v>69.06</v>
+      <c r="O12" s="12" vm="7">
+        <v>70.8</v>
       </c>
       <c r="P12" s="12">
-        <f ca="1">IFERROR(O12*E12,G12)</f>
-        <v>51.525666000000001</v>
+        <f t="shared" si="4"/>
+        <v>52.823879999999996</v>
       </c>
       <c r="Q12" s="12">
-        <f ca="1">P12-G12</f>
-        <v>-3.461903999999997</v>
+        <f t="shared" si="5"/>
+        <v>-2.1636900000000026</v>
       </c>
       <c r="R12" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>65.557729941291583</v>
       </c>
       <c r="S12" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>8.9324399999999997</v>
       </c>
       <c r="T12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-4.0711350293542097</v>
       </c>
       <c r="U12" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4.86130497064579</v>
       </c>
       <c r="V12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>155.41086909559925</v>
       </c>
       <c r="W12" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.4345563847587857E-3</v>
       </c>
       <c r="X12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.886959635049555</v>
       </c>
     </row>
@@ -5439,62 +4739,61 @@
       </c>
       <c r="K13" s="9">
         <f t="shared" si="2"/>
-        <v>0.31872411672922735</v>
+        <v>7.5604629905071649E-2</v>
       </c>
       <c r="L13" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.1495672008</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>43.845546000000006</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="3"/>
         <v>22.817222138400002</v>
       </c>
-      <c r="O13" s="12" cm="1" vm="9">
-        <f t="array" aca="1" ref="O13" ca="1">_xlfn.STOCKHISTORY(C13,TODAY(),TODAY(),0,0,1)</f>
-        <v>42.65</v>
+      <c r="O13" s="12" vm="8">
+        <v>43.35</v>
       </c>
       <c r="P13" s="12">
-        <f ca="1">IFERROR(O13*E13,G13)</f>
-        <v>22.195059999999998</v>
+        <f t="shared" si="4"/>
+        <v>22.559339999999999</v>
       </c>
       <c r="Q13" s="12">
-        <f ca="1">P13-G13</f>
-        <v>1.2021239999999977</v>
+        <f t="shared" si="5"/>
+        <v>1.5664039999999986</v>
       </c>
       <c r="R13" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>34.82389502762431</v>
       </c>
       <c r="S13" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3.5055460000000025</v>
       </c>
       <c r="T13" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-2.7580524861878466</v>
       </c>
       <c r="U13" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.7474935138121559</v>
       </c>
       <c r="V13" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>159.5246805524329</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.2686224886143432E-3</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.91043794599170247</v>
       </c>
     </row>
-    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -5518,8 +4817,8 @@
         <v>71.176714000000004</v>
       </c>
       <c r="H14" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>5.0200000000000002E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1),2.5%)+3.4%</f>
+        <v>8.4199999999999997E-2</v>
       </c>
       <c r="I14" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),2),25%)</f>
@@ -5527,66 +4826,65 @@
       </c>
       <c r="J14" s="9">
         <f t="shared" si="1"/>
-        <v>0.25087456271864067</v>
+        <v>0.42078960519740127</v>
       </c>
       <c r="K14" s="9">
         <f t="shared" si="2"/>
-        <v>0.22570923380948818</v>
+        <v>8.9803066433591316E-2</v>
       </c>
       <c r="L14" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>14.242460471400001</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="12"/>
-        <v>145.484206</v>
+        <f t="shared" si="14"/>
+        <v>150.19422600000001</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="3"/>
-        <v>74.749785042799999</v>
-      </c>
-      <c r="O14" s="12" cm="1" vm="10">
-        <f t="array" aca="1" ref="O14" ca="1">_xlfn.STOCKHISTORY(C14,TODAY(),TODAY(),0,0,1)</f>
-        <v>137.93</v>
+        <v>77.169793318800018</v>
+      </c>
+      <c r="O14" s="12" vm="9">
+        <v>140.04</v>
       </c>
       <c r="P14" s="12">
-        <f ca="1">IFERROR(O14*E14,G14)</f>
-        <v>70.868434000000008</v>
+        <f t="shared" si="4"/>
+        <v>71.952551999999997</v>
       </c>
       <c r="Q14" s="12">
-        <f ca="1">P14-G14</f>
-        <v>-0.30827999999999633</v>
+        <f t="shared" si="5"/>
+        <v>0.77583799999999314</v>
       </c>
       <c r="R14" s="12">
-        <f t="shared" si="4"/>
-        <v>120.47134533437691</v>
+        <f t="shared" si="6"/>
+        <v>124.14194820324403</v>
       </c>
       <c r="S14" s="12">
-        <f t="shared" si="5"/>
-        <v>6.9542059999999992</v>
+        <f t="shared" si="7"/>
+        <v>11.664226000000014</v>
       </c>
       <c r="T14" s="12">
-        <f t="shared" si="6"/>
-        <v>-9.0293273328115475</v>
+        <f t="shared" si="8"/>
+        <v>-7.194025898377987</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="7"/>
-        <v>-2.0751213328115483</v>
+        <f t="shared" si="9"/>
+        <v>4.4702001016220265</v>
       </c>
       <c r="V14" s="12">
-        <f t="shared" si="8"/>
-        <v>162.34729539905658</v>
+        <f t="shared" si="10"/>
+        <v>155.80197396462302</v>
       </c>
       <c r="W14" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1596344893948326E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.4184039171869779E-3</v>
       </c>
       <c r="X14" s="9">
-        <f t="shared" si="10"/>
-        <v>0.92654715025016887</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0.88919174554423375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -5610,8 +4908,8 @@
         <v>80.954076000000001</v>
       </c>
       <c r="H15" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>6.59E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1),2.5%)+2.8%</f>
+        <v>9.3899999999999997E-2</v>
       </c>
       <c r="I15" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),2),25%)</f>
@@ -5619,63 +4917,62 @@
       </c>
       <c r="J15" s="9">
         <f t="shared" si="1"/>
-        <v>0.35146666666666665</v>
+        <v>0.50080000000000002</v>
       </c>
       <c r="K15" s="9">
         <f t="shared" si="2"/>
-        <v>0.31621090310330507</v>
+        <v>0.10687853291633612</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>15.178889250000001</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="12"/>
-        <v>168.40154100000001</v>
+        <f t="shared" si="14"/>
+        <v>172.82526100000001</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="3"/>
-        <v>86.288949608400003</v>
-      </c>
-      <c r="O15" s="12" cm="1" vm="11">
-        <f t="array" aca="1" ref="O15" ca="1">_xlfn.STOCKHISTORY(C15,TODAY(),TODAY(),0,0,1)</f>
-        <v>139.5</v>
+        <v>88.555663736400007</v>
+      </c>
+      <c r="O15" s="12" vm="10">
+        <v>153.85</v>
       </c>
       <c r="P15" s="12">
-        <f ca="1">IFERROR(O15*E15,G15)</f>
-        <v>71.479799999999997</v>
+        <f t="shared" si="4"/>
+        <v>78.832739999999987</v>
       </c>
       <c r="Q15" s="12">
-        <f ca="1">P15-G15</f>
-        <v>-9.4742760000000033</v>
+        <f t="shared" si="5"/>
+        <v>-2.1213360000000137</v>
       </c>
       <c r="R15" s="12">
-        <f t="shared" si="4"/>
-        <v>140.86126961483598</v>
+        <f t="shared" si="6"/>
+        <v>144.46781272860281</v>
       </c>
       <c r="S15" s="12">
-        <f t="shared" si="5"/>
-        <v>10.411541</v>
+        <f t="shared" si="7"/>
+        <v>14.835261000000003</v>
       </c>
       <c r="T15" s="12">
-        <f t="shared" si="6"/>
-        <v>-8.5643651925820166</v>
+        <f t="shared" si="8"/>
+        <v>-6.7610936356986002</v>
       </c>
       <c r="U15" s="14">
-        <f t="shared" si="7"/>
-        <v>1.8471758074179832</v>
+        <f t="shared" si="9"/>
+        <v>8.0741673643014025</v>
       </c>
       <c r="V15" s="12">
-        <f t="shared" si="8"/>
-        <v>158.42499825882706</v>
+        <f t="shared" si="10"/>
+        <v>152.19800670194365</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="9"/>
-        <v>6.312135149064345E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.5703882834572585E-3</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="10"/>
-        <v>0.90416184824201995</v>
+        <f t="shared" si="12"/>
+        <v>0.86862321319743696</v>
       </c>
     </row>
     <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -5715,62 +5012,61 @@
       </c>
       <c r="K16" s="9">
         <f t="shared" si="2"/>
-        <v>0.67497655646729637</v>
+        <v>0.1601113629868913</v>
       </c>
       <c r="L16" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>25.124383398399996</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>235.643968</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="3"/>
         <v>96.802542054400007</v>
       </c>
-      <c r="O16" s="12" cm="1" vm="12">
-        <f t="array" aca="1" ref="O16" ca="1">_xlfn.STOCKHISTORY(C16,TODAY(),TODAY(),0,0,1)</f>
-        <v>200.95</v>
+      <c r="O16" s="12" vm="11">
+        <v>191.65</v>
       </c>
       <c r="P16" s="12">
-        <f ca="1">IFERROR(O16*E16,G16)</f>
-        <v>82.550259999999994</v>
+        <f t="shared" si="4"/>
+        <v>78.729820000000004</v>
       </c>
       <c r="Q16" s="12">
-        <f ca="1">P16-G16</f>
-        <v>4.5968519999999984</v>
+        <f t="shared" si="5"/>
+        <v>0.77641200000000765</v>
       </c>
       <c r="R16" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>175.62239703840814</v>
       </c>
       <c r="S16" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>45.88396800000001</v>
       </c>
       <c r="T16" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-7.0688014807959263</v>
       </c>
       <c r="U16" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>38.815166519204084</v>
       </c>
       <c r="V16" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>121.45700754704096</v>
       </c>
       <c r="W16" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>8.2333660296438193E-3</v>
       </c>
       <c r="X16" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.69317843542762225</v>
       </c>
     </row>
-    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -5794,8 +5090,8 @@
         <v>45.983826000000001</v>
       </c>
       <c r="H17" s="21">
-        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>6.9500000000000006E-2</v>
+        <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),1),2.5%)+2.6%</f>
+        <v>9.5500000000000002E-2</v>
       </c>
       <c r="I17" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),2),25%)</f>
@@ -5803,63 +5099,62 @@
       </c>
       <c r="J17" s="9">
         <f t="shared" si="1"/>
-        <v>0.2732992528509634</v>
+        <v>0.37554069996067635</v>
       </c>
       <c r="K17" s="9">
         <f t="shared" si="2"/>
-        <v>0.24588449419990988</v>
+        <v>8.0146244133728131E-2</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>11.693686951800002</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="12"/>
-        <v>141.07774500000002</v>
+        <f t="shared" si="14"/>
+        <v>144.50740499999998</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="3"/>
-        <v>49.179701907000009</v>
-      </c>
-      <c r="O17" s="12" cm="1" vm="13">
-        <f t="array" aca="1" ref="O17" ca="1">_xlfn.STOCKHISTORY(C17,TODAY(),TODAY(),0,0,1)</f>
-        <v>126.91</v>
+        <v>50.375281382999994</v>
+      </c>
+      <c r="O17" s="12" vm="12">
+        <v>130.30000000000001</v>
       </c>
       <c r="P17" s="12">
-        <f ca="1">IFERROR(O17*E17,G17)</f>
-        <v>44.240825999999998</v>
+        <f t="shared" si="4"/>
+        <v>45.422580000000004</v>
       </c>
       <c r="Q17" s="12">
-        <f ca="1">P17-G17</f>
-        <v>-1.7430000000000021</v>
+        <f t="shared" si="5"/>
+        <v>-0.56124599999999703</v>
       </c>
       <c r="R17" s="12">
-        <f t="shared" si="4"/>
-        <v>111.3352464550979</v>
+        <f t="shared" si="6"/>
+        <v>113.83327580255435</v>
       </c>
       <c r="S17" s="12">
-        <f t="shared" si="5"/>
-        <v>9.1677450000000249</v>
+        <f t="shared" si="7"/>
+        <v>12.597404999999981</v>
       </c>
       <c r="T17" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.287376772451047</v>
+        <f t="shared" si="8"/>
+        <v>-9.0383620987228213</v>
       </c>
       <c r="U17" s="14">
-        <f t="shared" si="7"/>
-        <v>-1.1196317724510223</v>
+        <f t="shared" si="9"/>
+        <v>3.5590429012771594</v>
       </c>
       <c r="V17" s="12">
-        <f t="shared" si="8"/>
-        <v>161.39180583869606</v>
+        <f t="shared" si="10"/>
+        <v>156.71313116496788</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1961014365218489E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.3810862087065679E-3</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" si="10"/>
-        <v>0.92109398808279364</v>
+        <f t="shared" si="12"/>
+        <v>0.89439189443081846</v>
       </c>
     </row>
     <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -5899,58 +5194,57 @@
       </c>
       <c r="K18" s="9">
         <f t="shared" si="2"/>
-        <v>-0.19464364560163458</v>
+        <v>-4.6171469357580742E-2</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.8605604249999992</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>30.369896000000001</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="3"/>
         <v>8.7313450999999986</v>
       </c>
-      <c r="O18" s="12" cm="1" vm="14">
-        <f t="array" aca="1" ref="O18" ca="1">_xlfn.STOCKHISTORY(C18,TODAY(),TODAY(),0,0,1)</f>
-        <v>34.020000000000003</v>
+      <c r="O18" s="12" vm="13">
+        <v>35.47</v>
       </c>
       <c r="P18" s="12">
-        <f ca="1">IFERROR(O18*E18,G18)</f>
-        <v>9.7807499999999994</v>
+        <f t="shared" si="4"/>
+        <v>10.197624999999999</v>
       </c>
       <c r="Q18" s="12">
-        <f ca="1">P18-G18</f>
-        <v>-0.21850000000000058</v>
+        <f t="shared" si="5"/>
+        <v>0.19837499999999864</v>
       </c>
       <c r="R18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20.304746336622102</v>
       </c>
       <c r="S18" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-4.4101040000000005</v>
       </c>
       <c r="T18" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-7.2376268316889494</v>
       </c>
       <c r="U18" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-11.64773083168895</v>
       </c>
       <c r="V18" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>171.919904897934</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5.8166621287609683E-3</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.981179868521459</v>
       </c>
     </row>
@@ -5968,14 +5262,14 @@
         <v>45511</v>
       </c>
       <c r="E19" s="2">
-        <v>0.25169999999999998</v>
+        <v>0.34489999999999998</v>
       </c>
       <c r="F19" s="1">
-        <v>178.56</v>
+        <v>173.73</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="0"/>
-        <v>44.943551999999997</v>
+        <v>59.919476999999993</v>
       </c>
       <c r="H19" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),1),2.5%)</f>
@@ -5991,59 +5285,58 @@
       </c>
       <c r="K19" s="9">
         <f t="shared" si="2"/>
-        <v>0.23131651384800542</v>
+        <v>5.4870649889563583E-2</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="11"/>
-        <v>21.500995276799998</v>
+        <f t="shared" si="13"/>
+        <v>28.665477796799998</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="12"/>
-        <v>200.52288000000001</v>
+        <f t="shared" si="14"/>
+        <v>195.09878999999998</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="3"/>
-        <v>50.471608895999999</v>
-      </c>
-      <c r="O19" s="12" cm="1" vm="15">
-        <f t="array" aca="1" ref="O19" ca="1">_xlfn.STOCKHISTORY(C19,TODAY(),TODAY(),0,0,1)</f>
-        <v>162.5</v>
+        <v>67.289572670999988</v>
+      </c>
+      <c r="O19" s="12" vm="14">
+        <v>152.91</v>
       </c>
       <c r="P19" s="12">
-        <f ca="1">IFERROR(O19*E19,G19)</f>
-        <v>40.901249999999997</v>
+        <f t="shared" si="4"/>
+        <v>52.738658999999998</v>
       </c>
       <c r="Q19" s="12">
-        <f ca="1">P19-G19</f>
-        <v>-4.0423019999999994</v>
+        <f t="shared" si="5"/>
+        <v>-7.180817999999995</v>
       </c>
       <c r="R19" s="12">
-        <f t="shared" si="4"/>
-        <v>131.73970783532536</v>
+        <f t="shared" si="6"/>
+        <v>128.17618415227977</v>
       </c>
       <c r="S19" s="12">
-        <f t="shared" si="5"/>
-        <v>21.962880000000013</v>
+        <f t="shared" si="7"/>
+        <v>21.36878999999999</v>
       </c>
       <c r="T19" s="12">
-        <f t="shared" si="6"/>
-        <v>-23.41014608233732</v>
+        <f t="shared" si="8"/>
+        <v>-22.776907923860108</v>
       </c>
       <c r="U19" s="14">
-        <f t="shared" si="7"/>
-        <v>-1.4472660823373076</v>
+        <f t="shared" si="9"/>
+        <v>-1.408117923860118</v>
       </c>
       <c r="V19" s="12">
-        <f t="shared" si="8"/>
-        <v>161.71944014858235</v>
+        <f t="shared" si="10"/>
+        <v>161.68029199010516</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1835484904055682E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.1850457324829676E-3</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" si="10"/>
-        <v>0.92296385992391761</v>
+        <f t="shared" si="12"/>
+        <v>0.92274043387554749</v>
       </c>
     </row>
     <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -6051,459 +5344,454 @@
         <v>36</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="8">
-        <v>45482</v>
+        <v>45574</v>
       </c>
       <c r="E20" s="2">
-        <v>1E-4</v>
+        <v>0.16059999999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>227.38</v>
+        <v>421.18</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="0"/>
-        <v>2.2738000000000001E-2</v>
+        <v>67.641508000000002</v>
       </c>
       <c r="H20" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.2092</v>
+        <v>0.2412</v>
       </c>
       <c r="I20" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.28439999999999999</v>
+        <v>0.27010000000000001</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>0.73558368495077353</v>
+        <v>0.89300259163272855</v>
       </c>
       <c r="K20" s="9">
         <f t="shared" si="2"/>
-        <v>0.66179698784050023</v>
+        <v>0.19058068467290742</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="11"/>
-        <v>6.4666871999999997E-3</v>
+        <f t="shared" si="13"/>
+        <v>18.269971310800003</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="12"/>
-        <v>274.94789600000001</v>
+        <f t="shared" si="14"/>
+        <v>522.76861600000007</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="3"/>
-        <v>2.7494789600000003E-2</v>
-      </c>
-      <c r="O20" s="12" cm="1" vm="16">
-        <f t="array" aca="1" ref="O20" ca="1">_xlfn.STOCKHISTORY(C20,TODAY(),TODAY(),0,0,1)</f>
-        <v>244.87</v>
+        <v>83.956639729600013</v>
+      </c>
+      <c r="O20" s="12" vm="15">
+        <v>404</v>
       </c>
       <c r="P20" s="12">
-        <f ca="1">IFERROR(O20*E20,G20)</f>
-        <v>2.4487000000000002E-2</v>
+        <f t="shared" si="4"/>
+        <v>64.882400000000004</v>
       </c>
       <c r="Q20" s="12">
-        <f ca="1">P20-G20</f>
-        <v>1.7490000000000006E-3</v>
+        <f t="shared" si="5"/>
+        <v>-2.7591079999999977</v>
       </c>
       <c r="R20" s="12">
-        <f t="shared" si="4"/>
-        <v>211.47693452380955</v>
+        <f t="shared" si="6"/>
+        <v>409.34979103897371</v>
       </c>
       <c r="S20" s="12">
-        <f t="shared" si="5"/>
-        <v>47.567896000000019</v>
+        <f t="shared" si="7"/>
+        <v>101.58861600000006</v>
       </c>
       <c r="T20" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.9515327380952243</v>
+        <f t="shared" si="8"/>
+        <v>-5.9151044805131505</v>
       </c>
       <c r="U20" s="14">
-        <f t="shared" si="7"/>
-        <v>39.616363261904795</v>
+        <f t="shared" si="9"/>
+        <v>95.673511519486908</v>
       </c>
       <c r="V20" s="12">
-        <f t="shared" si="8"/>
-        <v>120.65581080434025</v>
+        <f t="shared" si="10"/>
+        <v>64.598662546758135</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" si="9"/>
-        <v>8.2880384569429116E-3</v>
+        <f t="shared" si="11"/>
+        <v>1.5480196656953616E-2</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" si="10"/>
-        <v>0.68860585196132951</v>
+        <f t="shared" si="12"/>
+        <v>0.36867695606229905</v>
       </c>
     </row>
     <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
+        <v>37</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D21" s="8">
-        <v>45574</v>
+        <v>45511</v>
       </c>
       <c r="E21" s="2">
-        <v>0.16059999999999999</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F21" s="1">
-        <v>421.18</v>
+        <v>501.56</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="0"/>
-        <v>67.641508000000002</v>
+        <v>64.901863999999989</v>
       </c>
       <c r="H21" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.2412</v>
+        <v>0.1928</v>
       </c>
       <c r="I21" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.27010000000000001</v>
+        <v>0.26650000000000001</v>
       </c>
       <c r="J21" s="9">
         <f t="shared" si="1"/>
-        <v>0.89300259163272855</v>
+        <v>0.72345215759849901</v>
       </c>
       <c r="K21" s="9">
         <f t="shared" si="2"/>
-        <v>0.80342514028957801</v>
+        <v>0.1543959769155063</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="11"/>
-        <v>18.269971310800003</v>
+        <f t="shared" si="13"/>
+        <v>17.296346755999998</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="12"/>
-        <v>522.76861600000007</v>
+        <f t="shared" si="14"/>
+        <v>598.2607680000001</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="3"/>
-        <v>83.956639729600013</v>
-      </c>
-      <c r="O21" s="12" cm="1" vm="17">
-        <f t="array" aca="1" ref="O21" ca="1">_xlfn.STOCKHISTORY(C21,TODAY(),TODAY(),0,0,1)</f>
-        <v>414.77</v>
+        <v>77.414943379200011</v>
+      </c>
+      <c r="O21" s="12" vm="16">
+        <v>559</v>
       </c>
       <c r="P21" s="12">
-        <f ca="1">IFERROR(O21*E21,G21)</f>
-        <v>66.612061999999995</v>
+        <f t="shared" si="4"/>
+        <v>72.334599999999995</v>
       </c>
       <c r="Q21" s="12">
-        <f ca="1">P21-G21</f>
-        <v>-1.0294460000000072</v>
+        <f t="shared" si="5"/>
+        <v>7.4327360000000056</v>
       </c>
       <c r="R21" s="12">
-        <f t="shared" si="4"/>
-        <v>409.34979103897371</v>
+        <f t="shared" si="6"/>
+        <v>467.13234609294966</v>
       </c>
       <c r="S21" s="12">
-        <f t="shared" si="5"/>
-        <v>101.58861600000006</v>
+        <f t="shared" si="7"/>
+        <v>96.700768000000096</v>
       </c>
       <c r="T21" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.9151044805131505</v>
+        <f t="shared" si="8"/>
+        <v>-17.213826953525171</v>
       </c>
       <c r="U21" s="14">
-        <f t="shared" si="7"/>
-        <v>95.673511519486908</v>
+        <f t="shared" si="9"/>
+        <v>79.486941046474925</v>
       </c>
       <c r="V21" s="12">
-        <f t="shared" si="8"/>
-        <v>64.598662546758135</v>
+        <f t="shared" si="10"/>
+        <v>80.785233019770118</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="9"/>
-        <v>1.5480196656953615E-2</v>
+        <f t="shared" si="11"/>
+        <v>1.2378499914152326E-2</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="10"/>
-        <v>0.36867695606229905</v>
+        <f t="shared" si="12"/>
+        <v>0.46105681805647636</v>
       </c>
     </row>
     <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D22" s="8">
-        <v>45511</v>
+        <v>45678</v>
       </c>
       <c r="E22" s="2">
-        <v>0.12939999999999999</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="F22" s="1">
-        <v>501.56</v>
+        <v>185.82</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="0"/>
-        <v>64.901863999999989</v>
+        <v>9.9971160000000001</v>
       </c>
       <c r="H22" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1928</v>
+        <v>0.1925</v>
       </c>
       <c r="I22" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.26650000000000001</v>
+        <v>0.28539999999999999</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>0.72345215759849901</v>
+        <v>0.6744919411352488</v>
       </c>
       <c r="K22" s="9">
         <f t="shared" si="2"/>
-        <v>0.65088237890626699</v>
+        <v>0.14394710290021392</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="11"/>
-        <v>17.296346755999998</v>
+        <f t="shared" si="13"/>
+        <v>2.8531769063999999</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="12"/>
-        <v>598.2607680000001</v>
+        <f t="shared" si="14"/>
+        <v>221.59034999999997</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="3"/>
-        <v>77.414943379200011</v>
-      </c>
-      <c r="O22" s="12" cm="1" vm="18">
-        <f t="array" aca="1" ref="O22" ca="1">_xlfn.STOCKHISTORY(C22,TODAY(),TODAY(),0,0,1)</f>
-        <v>568.5</v>
+        <v>11.921560829999999</v>
+      </c>
+      <c r="O22" s="12" vm="17">
+        <v>179.25</v>
       </c>
       <c r="P22" s="12">
-        <f ca="1">IFERROR(O22*E22,G22)</f>
-        <v>73.56389999999999</v>
+        <f t="shared" si="4"/>
+        <v>9.6436500000000009</v>
       </c>
       <c r="Q22" s="12">
-        <f ca="1">P22-G22</f>
-        <v>8.6620360000000005</v>
+        <f t="shared" si="5"/>
+        <v>-0.35346599999999917</v>
       </c>
       <c r="R22" s="12">
-        <f t="shared" si="4"/>
-        <v>467.13234609294966</v>
+        <f t="shared" si="6"/>
+        <v>170.02470491353276</v>
       </c>
       <c r="S22" s="12">
-        <f t="shared" si="5"/>
-        <v>96.700768000000096</v>
+        <f t="shared" si="7"/>
+        <v>35.770349999999979</v>
       </c>
       <c r="T22" s="12">
-        <f t="shared" si="6"/>
-        <v>-17.213826953525171</v>
+        <f t="shared" si="8"/>
+        <v>-7.8976475432336173</v>
       </c>
       <c r="U22" s="14">
-        <f t="shared" si="7"/>
-        <v>79.486941046474925</v>
+        <f t="shared" si="9"/>
+        <v>27.872702456766362</v>
       </c>
       <c r="V22" s="12">
-        <f t="shared" si="8"/>
-        <v>80.785233019770118</v>
+        <f t="shared" si="10"/>
+        <v>132.39947160947867</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="9"/>
-        <v>1.2378499914152326E-2</v>
+        <f t="shared" si="11"/>
+        <v>7.552900233239364E-3</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="10"/>
-        <v>0.46105681805647636</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0.75562917640760074</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D23" s="8">
-        <v>45678</v>
+        <v>45580</v>
       </c>
       <c r="E23" s="2">
-        <v>5.3800000000000001E-2</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F23" s="1">
-        <v>185.82</v>
+        <v>130.51</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="0"/>
-        <v>9.9971160000000001</v>
+        <v>3.9152999999999993E-2</v>
       </c>
       <c r="H23" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1925</v>
+        <v>0.1169</v>
       </c>
       <c r="I23" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.28539999999999999</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>0.6744919411352488</v>
+        <v>0.48912133891213394</v>
       </c>
       <c r="K23" s="9">
         <f t="shared" si="2"/>
-        <v>0.60683338156945643</v>
+        <v>0.10438612444289716</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="11"/>
-        <v>2.8531769063999999</v>
+        <f t="shared" si="13"/>
+        <v>9.3575669999999972E-3</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="12"/>
-        <v>221.59034999999997</v>
+        <f t="shared" si="14"/>
+        <v>145.76661899999999</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="3"/>
-        <v>11.921560829999999</v>
-      </c>
-      <c r="O23" s="12" cm="1" vm="19">
-        <f t="array" aca="1" ref="O23" ca="1">_xlfn.STOCKHISTORY(C23,TODAY(),TODAY(),0,0,1)</f>
-        <v>185.27</v>
+        <v>4.3729985699999994E-2</v>
+      </c>
+      <c r="O23" s="12" vm="18">
+        <v>150.22999999999999</v>
       </c>
       <c r="P23" s="12">
-        <f ca="1">IFERROR(O23*E23,G23)</f>
-        <v>9.9675260000000012</v>
+        <f t="shared" si="4"/>
+        <v>4.5068999999999991E-2</v>
       </c>
       <c r="Q23" s="12">
-        <f ca="1">P23-G23</f>
-        <v>-2.9589999999998895E-2</v>
+        <f t="shared" si="5"/>
+        <v>5.9159999999999976E-3</v>
       </c>
       <c r="R23" s="12">
-        <f t="shared" si="4"/>
-        <v>170.02470491353276</v>
+        <f t="shared" si="6"/>
+        <v>116.3087068888691</v>
       </c>
       <c r="S23" s="12">
-        <f t="shared" si="5"/>
-        <v>35.770349999999979</v>
+        <f t="shared" si="7"/>
+        <v>15.256619000000001</v>
       </c>
       <c r="T23" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.8976475432336173</v>
+        <f t="shared" si="8"/>
+        <v>-7.1006465555654472</v>
       </c>
       <c r="U23" s="14">
-        <f t="shared" si="7"/>
-        <v>27.872702456766362</v>
+        <f t="shared" si="9"/>
+        <v>8.1559724444345534</v>
       </c>
       <c r="V23" s="12">
-        <f t="shared" si="8"/>
-        <v>132.39947160947867</v>
+        <f t="shared" si="10"/>
+        <v>152.11620162181049</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="9"/>
-        <v>7.552900233239364E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.5739217081306573E-3</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="10"/>
-        <v>0.75562917640760074</v>
+        <f t="shared" si="12"/>
+        <v>0.86815633591631525</v>
       </c>
     </row>
     <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>58</v>
+        <v>36</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="D24" s="8">
-        <v>45580</v>
+        <v>45482</v>
       </c>
       <c r="E24" s="2">
-        <v>2.9999999999999997E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="F24" s="1">
-        <v>130.51</v>
+        <v>227.38</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>3.9152999999999993E-2</v>
+        <v>2.2738000000000001E-2</v>
       </c>
       <c r="H24" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1169</v>
+        <v>0.2092</v>
       </c>
       <c r="I24" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.23899999999999999</v>
+        <v>0.28439999999999999</v>
       </c>
       <c r="J24" s="9">
         <f t="shared" si="1"/>
-        <v>0.48912133891213394</v>
+        <v>0.73558368495077353</v>
       </c>
       <c r="K24" s="9">
         <f t="shared" si="2"/>
-        <v>0.44005737947032519</v>
+        <v>0.15698503411487832</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="11"/>
-        <v>9.3575669999999972E-3</v>
+        <f t="shared" si="13"/>
+        <v>6.4666871999999997E-3</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="12"/>
-        <v>145.76661899999999</v>
+        <f t="shared" si="14"/>
+        <v>274.94789600000001</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="3"/>
-        <v>4.3729985699999994E-2</v>
-      </c>
-      <c r="O24" s="12" cm="1" vm="20">
-        <f t="array" aca="1" ref="O24" ca="1">_xlfn.STOCKHISTORY(C24,TODAY(),TODAY(),0,0,1)</f>
-        <v>148.29</v>
+        <v>2.7494789600000003E-2</v>
+      </c>
+      <c r="O24" s="12" vm="19">
+        <v>247.1</v>
       </c>
       <c r="P24" s="12">
-        <f ca="1">IFERROR(O24*E24,G24)</f>
-        <v>4.4486999999999992E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.4709999999999999E-2</v>
       </c>
       <c r="Q24" s="12">
-        <f ca="1">P24-G24</f>
-        <v>5.3339999999999985E-3</v>
+        <f t="shared" si="5"/>
+        <v>1.9719999999999981E-3</v>
       </c>
       <c r="R24" s="12">
-        <f t="shared" si="4"/>
-        <v>116.3087068888691</v>
+        <f t="shared" si="6"/>
+        <v>211.47693452380955</v>
       </c>
       <c r="S24" s="12">
-        <f t="shared" si="5"/>
-        <v>15.256619000000001</v>
+        <f t="shared" si="7"/>
+        <v>47.567896000000019</v>
       </c>
       <c r="T24" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.1006465555654472</v>
+        <f t="shared" si="8"/>
+        <v>-7.9515327380952243</v>
       </c>
       <c r="U24" s="14">
-        <f t="shared" si="7"/>
-        <v>8.1559724444345534</v>
+        <f t="shared" si="9"/>
+        <v>39.616363261904795</v>
       </c>
       <c r="V24" s="12">
-        <f t="shared" si="8"/>
-        <v>152.11620162181049</v>
+        <f t="shared" si="10"/>
+        <v>120.65581080434025</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="9"/>
-        <v>6.5739217081306582E-3</v>
+        <f t="shared" si="11"/>
+        <v>8.2880384569429116E-3</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="10"/>
-        <v>0.86815633591631525</v>
+        <f t="shared" si="12"/>
+        <v>0.68860585196132951</v>
       </c>
     </row>
     <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -6543,58 +5831,57 @@
       </c>
       <c r="K25" s="9">
         <f t="shared" si="2"/>
-        <v>-1.0108145040936092</v>
+        <v>-0.23977556913147086</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.4428596E-18</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O25" s="12" cm="1" vm="21">
-        <f t="array" aca="1" ref="O25" ca="1">_xlfn.STOCKHISTORY(C25,TODAY(),TODAY(),0,0,1)</f>
-        <v>5.64</v>
+      <c r="O25" s="12" vm="20">
+        <v>5.09</v>
       </c>
       <c r="P25" s="12">
-        <f ca="1">IFERROR(O25*E25,G25)</f>
-        <v>5.6399999999999995E-19</v>
+        <f t="shared" si="4"/>
+        <v>5.0899999999999995E-19</v>
       </c>
       <c r="Q25" s="12">
-        <f ca="1">P25-G25</f>
-        <v>-5.280000000000001E-19</v>
+        <f t="shared" si="5"/>
+        <v>-5.8300000000000009E-19</v>
       </c>
       <c r="R25" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.8693047453886176</v>
       </c>
       <c r="S25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-10.92</v>
       </c>
       <c r="T25" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-4.025347627305691</v>
       </c>
       <c r="U25" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-14.94534762730569</v>
       </c>
       <c r="V25" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>175.21752169355074</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="9"/>
-        <v>5.7071917827314364E-3</v>
+        <f t="shared" si="11"/>
+        <v>5.7071917827314373E-3</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -6635,58 +5922,57 @@
       </c>
       <c r="K26" s="9">
         <f t="shared" si="2"/>
-        <v>0.6315555041069415</v>
+        <v>0.14981144396136523</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6.9043547999999996E-18</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>331.89653000000004</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="3"/>
         <v>3.3189653000000001E-17</v>
       </c>
-      <c r="O26" s="12" cm="1" vm="22">
-        <f t="array" aca="1" ref="O26" ca="1">_xlfn.STOCKHISTORY(C26,TODAY(),TODAY(),0,0,1)</f>
-        <v>355.23</v>
+      <c r="O26" s="12" vm="21">
+        <v>349.86</v>
       </c>
       <c r="P26" s="12">
-        <f ca="1">IFERROR(O26*E26,G26)</f>
-        <v>3.5522999999999998E-17</v>
+        <f t="shared" si="4"/>
+        <v>3.4986000000000002E-17</v>
       </c>
       <c r="Q26" s="12">
-        <f ca="1">P26-G26</f>
-        <v>7.1800000000000003E-18</v>
+        <f t="shared" si="5"/>
+        <v>6.6430000000000039E-18</v>
       </c>
       <c r="R26" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>264.24575797128472</v>
       </c>
       <c r="S26" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>48.466530000000034</v>
       </c>
       <c r="T26" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-9.5921210143576445</v>
       </c>
       <c r="U26" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>38.87440898564239</v>
       </c>
       <c r="V26" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>121.39776508060265</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="9"/>
-        <v>8.2373839364838809E-3</v>
+        <f t="shared" si="11"/>
+        <v>8.2373839364838792E-3</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.6928403273099768</v>
       </c>
     </row>
@@ -6727,62 +6013,61 @@
       </c>
       <c r="K27" s="9">
         <f t="shared" si="2"/>
-        <v>0.28581841947528813</v>
+        <v>6.7799060975482481E-2</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6.8927168000000004E-18</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>210.01716800000003</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="3"/>
         <v>2.1001716800000003E-17</v>
       </c>
-      <c r="O27" s="12" cm="1" vm="23">
-        <f t="array" aca="1" ref="O27" ca="1">_xlfn.STOCKHISTORY(C27,TODAY(),TODAY(),0,0,1)</f>
-        <v>175.22</v>
+      <c r="O27" s="12" vm="22">
+        <v>161.1</v>
       </c>
       <c r="P27" s="12">
-        <f ca="1">IFERROR(O27*E27,G27)</f>
-        <v>1.7522E-17</v>
+        <f t="shared" si="4"/>
+        <v>1.6109999999999998E-17</v>
       </c>
       <c r="Q27" s="12">
-        <f ca="1">P27-G27</f>
-        <v>-1.2900000000000016E-18</v>
+        <f t="shared" si="5"/>
+        <v>-2.702000000000003E-18</v>
       </c>
       <c r="R27" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>150.49600000000001</v>
       </c>
       <c r="S27" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>21.897168000000022</v>
       </c>
       <c r="T27" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-18.811999999999998</v>
       </c>
       <c r="U27" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3.0851680000000243</v>
       </c>
       <c r="V27" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>157.18700606624503</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="9"/>
-        <v>6.3618490168236884E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.3618490168236876E-3</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.89709638937343017</v>
       </c>
     </row>
-    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -6819,58 +6104,57 @@
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
-        <v>0.52194988436321643</v>
+        <v>0.12381186664265129</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.8526314000000002E-17</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>776.29937400000006</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="3"/>
         <v>7.7629937400000001E-17</v>
       </c>
-      <c r="O28" s="12" t="e" cm="1" vm="24">
-        <f t="array" aca="1" ref="O28" ca="1">_xlfn.STOCKHISTORY(C28,TODAY(),TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+      <c r="O28" s="12" vm="23">
+        <v>692.1</v>
       </c>
       <c r="P28" s="12">
-        <f ca="1">IFERROR(O28*E28,G28)</f>
-        <v>6.6881999999999999E-17</v>
+        <f t="shared" si="4"/>
+        <v>6.9209999999999995E-17</v>
       </c>
       <c r="Q28" s="12">
-        <f ca="1">P28-G28</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>2.3279999999999956E-18</v>
       </c>
       <c r="R28" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>599.14001612469769</v>
       </c>
       <c r="S28" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>107.47937400000001</v>
       </c>
       <c r="T28" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-34.839991937651178</v>
       </c>
       <c r="U28" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>72.63938206234883</v>
       </c>
       <c r="V28" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>87.632792003896213</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1411253449000453E-2</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.50013715042244966</v>
       </c>
     </row>
@@ -6911,58 +6195,57 @@
       </c>
       <c r="K29" s="9">
         <f t="shared" si="2"/>
-        <v>0.49952987547647199</v>
+        <v>0.11849361055413957</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2.5869820800000001E-17</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>843.95563200000015</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="3"/>
         <v>8.4395563200000012E-17</v>
       </c>
-      <c r="O29" s="12" cm="1" vm="25">
-        <f t="array" aca="1" ref="O29" ca="1">_xlfn.STOCKHISTORY(C29,TODAY(),TODAY(),0,0,1)</f>
-        <v>717.5</v>
+      <c r="O29" s="12" vm="24">
+        <v>735.96</v>
       </c>
       <c r="P29" s="12">
-        <f ca="1">IFERROR(O29*E29,G29)</f>
-        <v>7.1749999999999995E-17</v>
+        <f t="shared" si="4"/>
+        <v>7.3595999999999996E-17</v>
       </c>
       <c r="Q29" s="12">
-        <f ca="1">P29-G29</f>
-        <v>1.7179999999999966E-18</v>
+        <f t="shared" si="5"/>
+        <v>3.5639999999999974E-18</v>
       </c>
       <c r="R29" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>601.49446019067261</v>
       </c>
       <c r="S29" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>143.6356320000001</v>
       </c>
       <c r="T29" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-49.412769904663719</v>
       </c>
       <c r="U29" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>94.222862095336382</v>
       </c>
       <c r="V29" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>66.049311970908661</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="9"/>
-        <v>1.5140203132478486E-2</v>
+        <f t="shared" si="11"/>
+        <v>1.5140203132478484E-2</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.376956090535435</v>
       </c>
     </row>
@@ -7003,58 +6286,57 @@
       </c>
       <c r="K30" s="9">
         <f t="shared" si="2"/>
-        <v>1.0160701067325602</v>
+        <v>0.24102225198849353</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>7.1711477999999992E-18</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>227.99780899999999</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="3"/>
         <v>2.2799780899999998E-17</v>
       </c>
-      <c r="O30" s="12" cm="1" vm="26">
-        <f t="array" aca="1" ref="O30" ca="1">_xlfn.STOCKHISTORY(C30,TODAY(),TODAY(),0,0,1)</f>
-        <v>139.22999999999999</v>
+      <c r="O30" s="12" vm="25">
+        <v>130.28</v>
       </c>
       <c r="P30" s="12">
-        <f ca="1">IFERROR(O30*E30,G30)</f>
-        <v>1.3922999999999999E-17</v>
+        <f t="shared" si="4"/>
+        <v>1.3028E-17</v>
       </c>
       <c r="Q30" s="12">
-        <f ca="1">P30-G30</f>
-        <v>-7.7800000000000002E-19</v>
+        <f t="shared" si="5"/>
+        <v>-1.6729999999999987E-18</v>
       </c>
       <c r="R30" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>156.91108976411567</v>
       </c>
       <c r="S30" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>80.987808999999999</v>
       </c>
       <c r="T30" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4.9505448820578408</v>
       </c>
       <c r="U30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>85.938353882057839</v>
       </c>
       <c r="V30" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>74.333820184187203</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.3452826688069595E-2</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.42423736773422943</v>
       </c>
     </row>
@@ -7095,58 +6377,57 @@
       </c>
       <c r="K31" s="9">
         <f t="shared" si="2"/>
-        <v>0.47629318250492114</v>
+        <v>0.1129816286233076</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6.8548831999999995E-18</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>205.62956199999999</v>
       </c>
       <c r="N31" s="12">
         <f t="shared" si="3"/>
         <v>2.0562956199999998E-17</v>
       </c>
-      <c r="O31" s="12" cm="1" vm="27">
-        <f t="array" aca="1" ref="O31" ca="1">_xlfn.STOCKHISTORY(C31,TODAY(),TODAY(),0,0,1)</f>
-        <v>174.06</v>
+      <c r="O31" s="12" vm="26">
+        <v>168.57</v>
       </c>
       <c r="P31" s="12">
-        <f ca="1">IFERROR(O31*E31,G31)</f>
-        <v>1.7406000000000001E-17</v>
+        <f t="shared" si="4"/>
+        <v>1.6856999999999999E-17</v>
       </c>
       <c r="Q31" s="12">
-        <f ca="1">P31-G31</f>
-        <v>4.720000000000018E-19</v>
+        <f t="shared" si="5"/>
+        <v>-7.7000000000000438E-20</v>
       </c>
       <c r="R31" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>142.2427551448971</v>
       </c>
       <c r="S31" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>36.289561999999989</v>
       </c>
       <c r="T31" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-13.54862242755145</v>
       </c>
       <c r="U31" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>22.740939572448539</v>
       </c>
       <c r="V31" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>137.53123449379649</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="9"/>
-        <v>7.2710755755275806E-3</v>
+        <f t="shared" si="11"/>
+        <v>7.2710755755275814E-3</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.78491713137190566</v>
       </c>
     </row>
@@ -7187,58 +6468,57 @@
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>0.33203869158184923</v>
+        <v>7.8762983638721001E-2</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2.3420195999999997E-18</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>122.223438</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="3"/>
         <v>1.2222343799999999E-17</v>
       </c>
-      <c r="O32" s="12" cm="1" vm="28">
-        <f t="array" aca="1" ref="O32" ca="1">_xlfn.STOCKHISTORY(C32,TODAY(),TODAY(),0,0,1)</f>
-        <v>111.79</v>
+      <c r="O32" s="12" vm="27">
+        <v>115.92</v>
       </c>
       <c r="P32" s="12">
-        <f ca="1">IFERROR(O32*E32,G32)</f>
-        <v>1.1179E-17</v>
+        <f t="shared" si="4"/>
+        <v>1.1592E-17</v>
       </c>
       <c r="Q32" s="12">
-        <f ca="1">P32-G32</f>
-        <v>-1.7899999999999882E-19</v>
+        <f t="shared" si="5"/>
+        <v>2.3400000000000045E-19</v>
       </c>
       <c r="R32" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>100.50438014335016</v>
       </c>
       <c r="S32" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>8.6434380000000033</v>
       </c>
       <c r="T32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-6.5378099283249185</v>
       </c>
       <c r="U32" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.1056280716750848</v>
       </c>
       <c r="V32" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>158.16654599456996</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.3224495022754764E-3</v>
       </c>
       <c r="X32" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.9026868116032235</v>
       </c>
     </row>
@@ -7279,58 +6559,57 @@
       </c>
       <c r="K33" s="9">
         <f t="shared" si="2"/>
-        <v>0.7201334398783692</v>
+        <v>0.17082303894350256</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4.5495449999999992E-18</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>100.765665</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="3"/>
         <v>1.0076566499999999E-17</v>
       </c>
-      <c r="O33" s="12" cm="1" vm="29">
-        <f t="array" aca="1" ref="O33" ca="1">_xlfn.STOCKHISTORY(C33,TODAY(),TODAY(),0,0,1)</f>
-        <v>112.06</v>
+      <c r="O33" s="12" vm="28">
+        <v>90.68</v>
       </c>
       <c r="P33" s="12">
-        <f ca="1">IFERROR(O33*E33,G33)</f>
-        <v>1.1206E-17</v>
+        <f t="shared" si="4"/>
+        <v>9.0679999999999998E-18</v>
       </c>
       <c r="Q33" s="12">
-        <f ca="1">P33-G33</f>
-        <v>4.771000000000001E-18</v>
+        <f t="shared" si="5"/>
+        <v>2.6330000000000005E-18</v>
       </c>
       <c r="R33" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>56.392954167031817</v>
       </c>
       <c r="S33" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>36.415665000000004</v>
       </c>
       <c r="T33" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-3.9785229164840885</v>
       </c>
       <c r="U33" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>32.437142083515916</v>
       </c>
       <c r="V33" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>127.83503198272913</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="9"/>
-        <v>7.822581842316139E-3</v>
+        <f t="shared" si="11"/>
+        <v>7.8225818423161408E-3</v>
       </c>
       <c r="X33" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.7295790440770421</v>
       </c>
     </row>
@@ -7371,58 +6650,57 @@
       </c>
       <c r="K34" s="9">
         <f t="shared" si="2"/>
-        <v>1.5121901390337388E-2</v>
+        <v>3.5870701276387159E-3</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.474056E-18</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>21.067758000000001</v>
       </c>
       <c r="N34" s="12">
         <f t="shared" si="3"/>
         <v>2.1067757999999999E-18</v>
       </c>
-      <c r="O34" s="12" cm="1" vm="30">
-        <f t="array" aca="1" ref="O34" ca="1">_xlfn.STOCKHISTORY(C34,TODAY(),TODAY(),0,0,1)</f>
-        <v>23.2</v>
+      <c r="O34" s="12" vm="29">
+        <v>22.1</v>
       </c>
       <c r="P34" s="12">
-        <f ca="1">IFERROR(O34*E34,G34)</f>
-        <v>2.32E-18</v>
+        <f t="shared" si="4"/>
+        <v>2.2100000000000002E-18</v>
       </c>
       <c r="Q34" s="12">
-        <f ca="1">P34-G34</f>
-        <v>2.3799999999999981E-19</v>
+        <f t="shared" si="5"/>
+        <v>1.2800000000000001E-19</v>
       </c>
       <c r="R34" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>12.275219621484583</v>
       </c>
       <c r="S34" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.24775800000000103</v>
       </c>
       <c r="T34" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-4.2723901892577087</v>
       </c>
       <c r="U34" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-4.0246321892577077</v>
       </c>
       <c r="V34" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>164.29680625550276</v>
       </c>
       <c r="W34" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.0865455804714232E-3</v>
       </c>
       <c r="X34" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.93767338259042421</v>
       </c>
     </row>
@@ -7463,58 +6741,57 @@
       </c>
       <c r="K35" s="9">
         <f t="shared" si="2"/>
-        <v>0.10170037170410422</v>
+        <v>2.412437139304786E-2</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.5602559999999997E-19</v>
       </c>
       <c r="M35" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13.668528</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="3"/>
         <v>1.3668528E-18</v>
       </c>
-      <c r="O35" s="12" cm="1" vm="31">
-        <f t="array" aca="1" ref="O35" ca="1">_xlfn.STOCKHISTORY(C35,TODAY(),TODAY(),0,0,1)</f>
-        <v>18.309999999999999</v>
+      <c r="O35" s="12" vm="30">
+        <v>18.28</v>
       </c>
       <c r="P35" s="12">
-        <f ca="1">IFERROR(O35*E35,G35)</f>
-        <v>1.8309999999999997E-18</v>
+        <f t="shared" si="4"/>
+        <v>1.8280000000000002E-18</v>
       </c>
       <c r="Q35" s="12">
-        <f ca="1">P35-G35</f>
-        <v>5.2699999999999978E-19</v>
+        <f t="shared" si="5"/>
+        <v>5.2400000000000025E-19</v>
       </c>
       <c r="R35" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9.4616166013640974</v>
       </c>
       <c r="S35" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.62852800000000109</v>
       </c>
       <c r="T35" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-1.7891916993179509</v>
       </c>
       <c r="U35" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-1.1606636993179498</v>
       </c>
       <c r="V35" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>161.43283776556299</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1945265525978448E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.1945265525978439E-3</v>
       </c>
       <c r="X35" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.92132816515863825</v>
       </c>
     </row>
@@ -7555,58 +6832,57 @@
       </c>
       <c r="K36" s="9">
         <f t="shared" si="2"/>
-        <v>-0.16381990387765097</v>
+        <v>-3.8859761636037014E-2</v>
       </c>
       <c r="L36" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6.4023700000000011E-19</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>9.8842250000000007</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="3"/>
         <v>9.8842250000000007E-19</v>
       </c>
-      <c r="O36" s="12" cm="1" vm="32">
-        <f t="array" aca="1" ref="O36" ca="1">_xlfn.STOCKHISTORY(C36,TODAY(),TODAY(),0,0,1)</f>
-        <v>11.05</v>
+      <c r="O36" s="12" vm="31">
+        <v>10.79</v>
       </c>
       <c r="P36" s="12">
-        <f ca="1">IFERROR(O36*E36,G36)</f>
-        <v>1.1050000000000001E-18</v>
+        <f t="shared" si="4"/>
+        <v>1.0789999999999998E-18</v>
       </c>
       <c r="Q36" s="12">
-        <f ca="1">P36-G36</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-2.6000000000000285E-20</v>
       </c>
       <c r="R36" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.5582527152946763</v>
       </c>
       <c r="S36" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-1.165775</v>
       </c>
       <c r="T36" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-2.2458736423526622</v>
       </c>
       <c r="U36" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-3.4116486423526622</v>
       </c>
       <c r="V36" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>163.68382270859772</v>
       </c>
       <c r="W36" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1093392337266909E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.1093392337266917E-3</v>
       </c>
       <c r="X36" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.93417496792857824</v>
       </c>
     </row>
@@ -7622,7 +6898,7 @@
       </c>
       <c r="D37" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45687</v>
+        <v>45692</v>
       </c>
       <c r="E37" s="2">
         <v>9.9999999999999998E-20</v>
@@ -7648,62 +6924,61 @@
       </c>
       <c r="K37" s="9">
         <f t="shared" si="2"/>
-        <v>0.53255720406754736</v>
+        <v>0.12632803168457066</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4.0128627000000008E-17</v>
       </c>
       <c r="M37" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2980.43514</v>
       </c>
       <c r="N37" s="12">
         <f t="shared" si="3"/>
         <v>2.98043514E-16</v>
       </c>
-      <c r="O37" s="12" cm="1" vm="33">
-        <f t="array" aca="1" ref="O37" ca="1">_xlfn.STOCKHISTORY(C37,TODAY(),TODAY(),0,0,1)</f>
-        <v>0.78559999999999997</v>
+      <c r="O37" s="12" vm="32">
+        <v>0.72499999999999998</v>
       </c>
       <c r="P37" s="12">
-        <f ca="1">IFERROR(O37*E37,G37)</f>
-        <v>7.8559999999999989E-20</v>
+        <f t="shared" si="4"/>
+        <v>7.2499999999999999E-20</v>
       </c>
       <c r="Q37" s="12">
-        <f ca="1">P37-G37</f>
-        <v>-2.7421144000000001E-16</v>
+        <f t="shared" si="5"/>
+        <v>-2.742175E-16</v>
       </c>
       <c r="R37" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2588.3740681324903</v>
       </c>
       <c r="S37" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>237.53513999999996</v>
       </c>
       <c r="T37" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-77.262965933754913</v>
       </c>
       <c r="U37" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>160.27217406624504</v>
       </c>
       <c r="V37" s="12">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X37" s="9">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="W37" s="9">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="9">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -7740,58 +7015,57 @@
       </c>
       <c r="K38" s="9">
         <f t="shared" si="2"/>
-        <v>0.62611225632861045</v>
+        <v>0.14852024975245023</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.8255279999999995E-18</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>99.304220000000001</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="3"/>
         <v>9.9304219999999992E-18</v>
       </c>
-      <c r="O38" s="12" cm="1" vm="34">
-        <f t="array" aca="1" ref="O38" ca="1">_xlfn.STOCKHISTORY(C38,TODAY(),TODAY(),0,0,1)</f>
-        <v>104</v>
+      <c r="O38" s="12" vm="33">
+        <v>93.67</v>
       </c>
       <c r="P38" s="12">
-        <f ca="1">IFERROR(O38*E38,G38)</f>
-        <v>1.04E-17</v>
+        <f t="shared" si="4"/>
+        <v>9.3669999999999995E-18</v>
       </c>
       <c r="Q38" s="12">
-        <f ca="1">P38-G38</f>
-        <v>1.7400000000000015E-18</v>
+        <f t="shared" si="5"/>
+        <v>7.0700000000000094E-19</v>
       </c>
       <c r="R38" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>81.383328634526833</v>
       </c>
       <c r="S38" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>12.704220000000007</v>
       </c>
       <c r="T38" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-2.6083356827365805</v>
       </c>
       <c r="U38" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10.095884317263426</v>
       </c>
       <c r="V38" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>150.17628974898162</v>
       </c>
       <c r="W38" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.6588407642211127E-3</v>
       </c>
       <c r="X38" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.8570848868164832</v>
       </c>
     </row>
@@ -7832,58 +7106,57 @@
       </c>
       <c r="K39" s="9">
         <f t="shared" si="2"/>
-        <v>9.1147203875204513E-3</v>
+        <v>2.1621051731461343E-3</v>
       </c>
       <c r="L39" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2.2663199999999999E-18</v>
       </c>
       <c r="M39" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>56.229599999999998</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="3"/>
         <v>5.6229599999999995E-18</v>
       </c>
-      <c r="O39" s="12" cm="1" vm="35">
-        <f t="array" aca="1" ref="O39" ca="1">_xlfn.STOCKHISTORY(C39,TODAY(),TODAY(),0,0,1)</f>
-        <v>66.66</v>
+      <c r="O39" s="12" vm="34">
+        <v>66.790000000000006</v>
       </c>
       <c r="P39" s="12">
-        <f ca="1">IFERROR(O39*E39,G39)</f>
-        <v>6.6659999999999998E-18</v>
+        <f t="shared" si="4"/>
+        <v>6.6790000000000004E-18</v>
       </c>
       <c r="Q39" s="12">
-        <f ca="1">P39-G39</f>
-        <v>1.0660000000000003E-18</v>
+        <f t="shared" si="5"/>
+        <v>1.079000000000001E-18</v>
       </c>
       <c r="R39" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>39.98286448664858</v>
       </c>
       <c r="S39" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.22959999999999781</v>
       </c>
       <c r="T39" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-8.0085677566757099</v>
       </c>
       <c r="U39" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-7.7789677566757121</v>
       </c>
       <c r="V39" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>168.05114182292075</v>
       </c>
       <c r="W39" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5.9505695061192881E-3</v>
       </c>
       <c r="X39" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.95910009569040855</v>
       </c>
     </row>
@@ -7924,62 +7197,61 @@
       </c>
       <c r="K40" s="9">
         <f t="shared" si="2"/>
-        <v>0.21774588649482446</v>
+        <v>5.1651557876239311E-2</v>
       </c>
       <c r="L40" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2.1845000000000003E-19</v>
       </c>
       <c r="M40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>17.528699999999997</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="3"/>
         <v>1.7528699999999997E-18</v>
       </c>
-      <c r="O40" s="12" cm="1" vm="36">
-        <f t="array" aca="1" ref="O40" ca="1">_xlfn.STOCKHISTORY(C40,TODAY(),TODAY(),0,0,1)</f>
-        <v>20.431999999999999</v>
+      <c r="O40" s="12" vm="35">
+        <v>20.470300000000002</v>
       </c>
       <c r="P40" s="12">
-        <f ca="1">IFERROR(O40*E40,G40)</f>
-        <v>2.0431999999999997E-18</v>
+        <f t="shared" si="4"/>
+        <v>2.04703E-18</v>
       </c>
       <c r="Q40" s="12">
-        <f ca="1">P40-G40</f>
-        <v>3.4319999999999965E-19</v>
+        <f t="shared" si="5"/>
+        <v>3.4702999999999996E-19</v>
       </c>
       <c r="R40" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>15.491160925824675</v>
       </c>
       <c r="S40" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.52869999999999706</v>
       </c>
       <c r="T40" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-0.75441953708766274</v>
       </c>
       <c r="U40" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-0.22571953708766568</v>
       </c>
       <c r="V40" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>160.4978936033327</v>
       </c>
       <c r="W40" s="9">
-        <f t="shared" si="9"/>
-        <v>6.2306113653521197E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.2306113653521206E-3</v>
       </c>
       <c r="X40" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.91599225951864482</v>
       </c>
     </row>
-    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -8016,62 +7288,61 @@
       </c>
       <c r="K41" s="9">
         <f t="shared" si="2"/>
-        <v>0.21081835401987956</v>
+        <v>5.0008276111751654E-2</v>
       </c>
       <c r="L41" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.7241911999999999E-18</v>
       </c>
       <c r="M41" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>51.460183999999998</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="3"/>
         <v>5.1460184E-18</v>
       </c>
-      <c r="O41" s="12" cm="1" vm="37">
-        <f t="array" aca="1" ref="O41" ca="1">_xlfn.STOCKHISTORY(C41,TODAY(),TODAY(),0,0,1)</f>
-        <v>47.29</v>
+      <c r="O41" s="12" vm="36">
+        <v>46.81</v>
       </c>
       <c r="P41" s="12">
-        <f ca="1">IFERROR(O41*E41,G41)</f>
-        <v>4.729E-18</v>
+        <f t="shared" si="4"/>
+        <v>4.681E-18</v>
       </c>
       <c r="Q41" s="12">
-        <f ca="1">P41-G41</f>
-        <v>-1.2999999999999854E-20</v>
+        <f t="shared" si="5"/>
+        <v>-6.0999999999999907E-20</v>
       </c>
       <c r="R41" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>37.093241551939926</v>
       </c>
       <c r="S41" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4.0401839999999964</v>
       </c>
       <c r="T41" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-5.163379224030038</v>
       </c>
       <c r="U41" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-1.1231952240300416</v>
       </c>
       <c r="V41" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>161.39536929027508</v>
       </c>
       <c r="W41" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1959646326745959E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.195964632674595E-3</v>
       </c>
       <c r="X41" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.92111432538436366</v>
       </c>
     </row>
-    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -8085,14 +7356,14 @@
         <v>45507</v>
       </c>
       <c r="E42" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.52270000000000005</v>
       </c>
       <c r="F42" s="1">
-        <v>41.8</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="G42" s="1">
         <f t="shared" si="0"/>
-        <v>4.1799999999999993E-18</v>
+        <v>19.982821000000001</v>
       </c>
       <c r="H42" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C42,Sheet1!$G:$G,0),1),2.5%)</f>
@@ -8103,64 +7374,63 @@
         <v>0.39029999999999998</v>
       </c>
       <c r="J42" s="9">
-        <f t="shared" ref="J42:J46" si="13">IFERROR(H42/I42,"")</f>
+        <f t="shared" ref="J42:J46" si="15">IFERROR(H42/I42,"")</f>
         <v>0.21393799641301564</v>
       </c>
       <c r="K42" s="9">
         <f t="shared" si="2"/>
-        <v>0.19247778941731217</v>
+        <v>4.5657706053681087E-2</v>
       </c>
       <c r="L42" s="9">
-        <f t="shared" si="11"/>
-        <v>1.6314539999999997E-18</v>
+        <f t="shared" si="13"/>
+        <v>7.7992950363000002</v>
       </c>
       <c r="M42" s="12">
-        <f t="shared" ref="M42:M46" si="14">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
-        <v>45.290299999999995</v>
+        <f t="shared" ref="M42:M46" si="16">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
+        <v>41.422204999999991</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="3"/>
-        <v>4.5290299999999995E-18</v>
-      </c>
-      <c r="O42" s="12" cm="1" vm="38">
-        <f t="array" aca="1" ref="O42" ca="1">_xlfn.STOCKHISTORY(C42,TODAY(),TODAY(),0,0,1)</f>
-        <v>38.39</v>
+        <v>21.651386553499997</v>
+      </c>
+      <c r="O42" s="12" vm="37">
+        <v>39.369999999999997</v>
       </c>
       <c r="P42" s="12">
-        <f ca="1">IFERROR(O42*E42,G42)</f>
-        <v>3.8390000000000001E-18</v>
+        <f t="shared" si="4"/>
+        <v>20.578699</v>
       </c>
       <c r="Q42" s="12">
-        <f ca="1">P42-G42</f>
-        <v>-3.4099999999999919E-19</v>
+        <f t="shared" si="5"/>
+        <v>0.59587799999999902</v>
       </c>
       <c r="R42" s="12">
-        <f t="shared" ref="R42:R46" si="15">F42/(1+I42-H42)</f>
-        <v>31.986531986531986</v>
+        <f t="shared" ref="R42:R46" si="17">F42/(1+I42-H42)</f>
+        <v>29.254667891031527</v>
       </c>
       <c r="S42" s="12">
-        <f t="shared" ref="S42:S46" si="16">M42-F42</f>
-        <v>3.4902999999999977</v>
+        <f t="shared" ref="S42:S46" si="18">M42-F42</f>
+        <v>3.1922049999999942</v>
       </c>
       <c r="T42" s="12">
-        <f t="shared" ref="T42:T46" si="17">0.5*(R42-F42)</f>
-        <v>-4.9067340067340055</v>
+        <f t="shared" ref="T42:T46" si="19">0.5*(R42-F42)</f>
+        <v>-4.4876660544842348</v>
       </c>
       <c r="U42" s="14">
-        <f t="shared" ref="U42:U46" si="18">S42+T42</f>
-        <v>-1.4164340067340078</v>
+        <f t="shared" ref="U42:U46" si="20">S42+T42</f>
+        <v>-1.2954610544842406</v>
       </c>
       <c r="V42" s="12">
-        <f t="shared" si="8"/>
-        <v>161.68860807297904</v>
+        <f t="shared" si="10"/>
+        <v>161.56763512072928</v>
       </c>
       <c r="W42" s="9">
-        <f t="shared" si="9"/>
-        <v>6.1847276188353641E-3</v>
+        <f t="shared" si="11"/>
+        <v>6.189358402459523E-3</v>
       </c>
       <c r="X42" s="9">
-        <f t="shared" ref="X42:X46" si="19">V42/MAX($V$2:$V$28)</f>
-        <v>0.92278789535538974</v>
+        <f t="shared" ref="X42:X46" si="21">V42/MAX($V$2:$V$28)</f>
+        <v>0.92209747951637722</v>
       </c>
     </row>
     <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -8195,63 +7465,62 @@
         <v>8.8400000000000006E-2</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.25678733031674206</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="2"/>
-        <v>0.23102888929707052</v>
+        <v>5.4802422395678896E-2</v>
       </c>
       <c r="L43" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.359195968E-18</v>
       </c>
       <c r="M43" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>157.24544304</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="3"/>
         <v>1.5724544303999999E-17</v>
       </c>
-      <c r="O43" s="12" cm="1" vm="39">
-        <f t="array" aca="1" ref="O43" ca="1">_xlfn.STOCKHISTORY(C43,TODAY(),TODAY(),0,0,1)</f>
-        <v>151.47</v>
+      <c r="O43" s="12" vm="38">
+        <v>149.71</v>
       </c>
       <c r="P43" s="12">
-        <f ca="1">IFERROR(O43*E43,G43)</f>
-        <v>1.5146999999999998E-17</v>
+        <f t="shared" si="4"/>
+        <v>1.4971000000000001E-17</v>
       </c>
       <c r="Q43" s="12">
-        <f ca="1">P43-G43</f>
-        <v>-2.28520000000001E-19</v>
+        <f t="shared" si="5"/>
+        <v>-4.045199999999976E-19</v>
       </c>
       <c r="R43" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>144.27625035188137</v>
       </c>
       <c r="S43" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3.4902430399999957</v>
       </c>
       <c r="T43" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-4.7394748240593145</v>
       </c>
       <c r="U43" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-1.2492317840593188</v>
       </c>
       <c r="V43" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>161.52140585030435</v>
       </c>
       <c r="W43" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.1911298674974706E-3</v>
       </c>
       <c r="X43" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.92183364020408631</v>
       </c>
     </row>
@@ -8287,63 +7556,62 @@
         <v>0.25</v>
       </c>
       <c r="J44" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.1636</v>
       </c>
       <c r="K44" s="9">
         <f t="shared" si="2"/>
-        <v>0.14718921779505134</v>
+        <v>3.491479230254111E-2</v>
       </c>
       <c r="L44" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3.3382499999999999E-18</v>
       </c>
       <c r="M44" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>138.991377</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="3"/>
         <v>1.38991377E-17</v>
       </c>
-      <c r="O44" s="12" cm="1" vm="40">
-        <f t="array" aca="1" ref="O44" ca="1">_xlfn.STOCKHISTORY(C44,TODAY(),TODAY(),0,0,1)</f>
-        <v>150.19999999999999</v>
+      <c r="O44" s="12" vm="39">
+        <v>145.47999999999999</v>
       </c>
       <c r="P44" s="12">
-        <f ca="1">IFERROR(O44*E44,G44)</f>
-        <v>1.5019999999999999E-17</v>
+        <f t="shared" si="4"/>
+        <v>1.4548E-17</v>
       </c>
       <c r="Q44" s="12">
-        <f ca="1">P44-G44</f>
-        <v>1.6669999999999989E-18</v>
+        <f t="shared" si="5"/>
+        <v>1.1950000000000002E-18</v>
       </c>
       <c r="R44" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>110.4375155074022</v>
       </c>
       <c r="S44" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>5.4613769999999988</v>
       </c>
       <c r="T44" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-11.546242246298903</v>
       </c>
       <c r="U44" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-6.0848652462989037</v>
       </c>
       <c r="V44" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>166.35703931254395</v>
       </c>
       <c r="W44" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.0111673310153475E-3</v>
       </c>
       <c r="X44" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.94943152776408135</v>
       </c>
     </row>
@@ -8379,63 +7647,62 @@
         <v>0.60340000000000005</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-0.19771295989393436</v>
       </c>
       <c r="K45" s="9">
         <f t="shared" si="2"/>
-        <v>-0.17788029287733836</v>
+        <v>-4.2195030135802926E-2</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.6068542000000001E-18</v>
       </c>
       <c r="M45" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>23.453040999999999</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="3"/>
         <v>2.3453040999999998E-18</v>
       </c>
-      <c r="O45" s="12" cm="1" vm="41">
-        <f t="array" aca="1" ref="O45" ca="1">_xlfn.STOCKHISTORY(C45,TODAY(),TODAY(),0,0,1)</f>
-        <v>15.66</v>
+      <c r="O45" s="12" vm="40">
+        <v>16.010000000000002</v>
       </c>
       <c r="P45" s="12">
-        <f ca="1">IFERROR(O45*E45,G45)</f>
-        <v>1.566E-18</v>
+        <f t="shared" si="4"/>
+        <v>1.6010000000000002E-18</v>
       </c>
       <c r="Q45" s="12">
-        <f ca="1">P45-G45</f>
-        <v>-1.097E-18</v>
+        <f t="shared" si="5"/>
+        <v>-1.0619999999999998E-18</v>
       </c>
       <c r="R45" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>15.458292215707898</v>
       </c>
       <c r="S45" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-3.1769590000000001</v>
       </c>
       <c r="T45" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-5.5858538921460505</v>
       </c>
       <c r="U45" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-8.7628128921460515</v>
       </c>
       <c r="V45" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>169.0349869583911</v>
       </c>
       <c r="W45" s="9">
-        <f t="shared" si="9"/>
-        <v>5.9159350261975968E-3</v>
+        <f t="shared" si="11"/>
+        <v>5.9159350261975977E-3</v>
       </c>
       <c r="X45" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.96471508856304522</v>
       </c>
     </row>
@@ -8471,63 +7738,62 @@
         <v>0.32779999999999998</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.49145820622330688</v>
       </c>
       <c r="K46" s="9">
         <f t="shared" si="2"/>
-        <v>0.44215983467584091</v>
+        <v>0.10488484838426758</v>
       </c>
       <c r="L46" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.0612525E-17</v>
       </c>
       <c r="M46" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>375.90612500000003</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="3"/>
         <v>3.7590612500000005E-17</v>
       </c>
-      <c r="O46" s="12" cm="1" vm="42">
-        <f t="array" aca="1" ref="O46" ca="1">_xlfn.STOCKHISTORY(C46,TODAY(),TODAY(),0,0,1)</f>
-        <v>320.56</v>
+      <c r="O46" s="12" vm="41">
+        <v>319.57</v>
       </c>
       <c r="P46" s="12">
-        <f ca="1">IFERROR(O46*E46,G46)</f>
-        <v>3.2055999999999996E-17</v>
+        <f t="shared" si="4"/>
+        <v>3.1956999999999997E-17</v>
       </c>
       <c r="Q46" s="12">
-        <f ca="1">P46-G46</f>
-        <v>-3.1900000000000578E-19</v>
+        <f t="shared" si="5"/>
+        <v>-4.1800000000000502E-19</v>
       </c>
       <c r="R46" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>277.49207165509563</v>
       </c>
       <c r="S46" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>52.156125000000031</v>
       </c>
       <c r="T46" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-23.128964172452186</v>
       </c>
       <c r="U46" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>29.027160827547846</v>
       </c>
       <c r="V46" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>131.2450132386972</v>
       </c>
       <c r="W46" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>7.619337110974918E-3</v>
       </c>
       <c r="X46" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.74904046108037126</v>
       </c>
     </row>
@@ -8538,7 +7804,8 @@
   <autoFilter ref="A1:X46" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="ETF"/>
+        <filter val="Asia Consumer"/>
+        <filter val="US Consumer"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8597,9 +7864,7 @@
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8637,7 +7902,7 @@
         <v>283.12183800000003</v>
       </c>
       <c r="C4" s="24">
-        <v>0.27415794541660166</v>
+        <v>0.2587041174008915</v>
       </c>
       <c r="D4" s="19">
         <v>0.22147011693742963</v>
@@ -8649,62 +7914,62 @@
         <v>20.320718273599937</v>
       </c>
       <c r="G4" s="19">
-        <v>-2.5466209356835242E-2</v>
+        <v>1.4576339392088756E-2</v>
       </c>
       <c r="H4" s="12">
-        <v>-7.2100399999999922</v>
+        <v>4.1268799999999715</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="B5" s="12">
-        <v>222.11800000000002</v>
+        <v>245.91161700000001</v>
       </c>
       <c r="C5" s="24">
-        <v>0.21508554391358795</v>
+        <v>0.22470307583483215</v>
       </c>
       <c r="D5" s="19">
-        <v>0.1859207718419939</v>
+        <v>0.35652775316263313</v>
       </c>
       <c r="E5" s="19">
-        <v>4.172777532662808E-2</v>
+        <v>8.183192290342256E-2</v>
       </c>
       <c r="F5" s="12">
-        <v>9.2684899999999857</v>
+        <v>20.123420483399997</v>
       </c>
       <c r="G5" s="19">
-        <v>1.5672750519993752E-2</v>
+        <v>-3.6948966099474727E-2</v>
       </c>
       <c r="H5" s="12">
-        <v>3.4811999999999728</v>
+        <v>-9.086180000000013</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="B6" s="12">
-        <v>220.93703800000003</v>
+        <v>218.852</v>
       </c>
       <c r="C6" s="24">
-        <v>0.21394197223496991</v>
+        <v>0.19997720381223261</v>
       </c>
       <c r="D6" s="19">
-        <v>0.43949571810951849</v>
+        <v>0.19897140533328458</v>
       </c>
       <c r="E6" s="19">
-        <v>5.3152980643290659E-2</v>
+        <v>4.0329537769816959E-2</v>
       </c>
       <c r="F6" s="12">
-        <v>11.743462104199978</v>
+        <v>8.8262</v>
       </c>
       <c r="G6" s="19">
-        <v>-2.8620103977314997E-2</v>
+        <v>3.4507338292544827E-2</v>
       </c>
       <c r="H6" s="12">
-        <v>-6.3232409999999959</v>
+        <v>7.5520000000000209</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -8715,22 +7980,22 @@
         <v>155.61477000000002</v>
       </c>
       <c r="C7" s="24">
-        <v>0.15068786611817991</v>
+        <v>0.14219384139273894</v>
       </c>
       <c r="D7" s="19">
-        <v>0.29723398558375913</v>
+        <v>0.29723398558375919</v>
       </c>
       <c r="E7" s="19">
-        <v>0.23836726683206222</v>
+        <v>0.23836726683206244</v>
       </c>
       <c r="F7" s="12">
-        <v>37.093467403599988</v>
+        <v>37.093467403600016</v>
       </c>
       <c r="G7" s="19">
-        <v>2.2745687957511699E-2</v>
+        <v>6.8824508110635644E-3</v>
       </c>
       <c r="H7" s="12">
-        <v>3.5395649999999534</v>
+        <v>1.0710109999999702</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -8738,25 +8003,25 @@
         <v>37</v>
       </c>
       <c r="B8" s="12">
-        <v>94.882213999999991</v>
+        <v>114.87946399999998</v>
       </c>
       <c r="C8" s="24">
-        <v>9.1878157582525696E-2</v>
+        <v>0.10497173425953628</v>
       </c>
       <c r="D8" s="19">
-        <v>0.29370539525985345</v>
+        <v>0.30395727225886082</v>
       </c>
       <c r="E8" s="19">
-        <v>0.1541563317040644</v>
+        <v>0.1395941417275417</v>
       </c>
       <c r="F8" s="12">
-        <v>14.62669405420003</v>
+        <v>16.036500179200033</v>
       </c>
       <c r="G8" s="19">
-        <v>0.12702033913331739</v>
+        <v>9.2931230946551174E-2</v>
       </c>
       <c r="H8" s="12">
-        <v>12.051970999999995</v>
+        <v>10.67589000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -8764,25 +8029,25 @@
         <v>39</v>
       </c>
       <c r="B9" s="12">
-        <v>46.022978999999999</v>
+        <v>66.005799999999994</v>
       </c>
       <c r="C9" s="24">
-        <v>4.4565850001974779E-2</v>
+        <v>6.0313158295969248E-2</v>
       </c>
       <c r="D9" s="19">
-        <v>0.25428698387386012</v>
+        <v>0.29546402823842755</v>
       </c>
       <c r="E9" s="19">
-        <v>6.9540324469218096E-2</v>
+        <v>7.3766524247869336E-2</v>
       </c>
       <c r="F9" s="12">
-        <v>3.2004528927000067</v>
+        <v>4.8690184462000161</v>
       </c>
       <c r="G9" s="19">
-        <v>-3.7756486819334412E-2</v>
+        <v>-1.2304873208111702E-2</v>
       </c>
       <c r="H9" s="12">
-        <v>-1.7376660000000044</v>
+        <v>-0.81219299999997929</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -8793,7 +8058,7 @@
         <v>9.99925</v>
       </c>
       <c r="C10" s="24">
-        <v>9.6826647321601317E-3</v>
+        <v>9.1368690037992202E-3</v>
       </c>
       <c r="D10" s="19">
         <v>0.58609999999999995</v>
@@ -8805,10 +8070,10 @@
         <v>-1.2679049000000013</v>
       </c>
       <c r="G10" s="19">
-        <v>-2.1851638872915528E-2</v>
+        <v>1.2650948821161415E-2</v>
       </c>
       <c r="H10" s="12">
-        <v>-0.21850000000000058</v>
+        <v>0.12649999999999828</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -8819,7 +8084,7 @@
         <v>2.9136552000000001E-16</v>
       </c>
       <c r="C11" s="24">
-        <v>2.8214062501402581E-19</v>
+        <v>2.6623682660837979E-19</v>
       </c>
       <c r="D11" s="19">
         <v>0.14314072910205713</v>
@@ -8831,10 +8096,10 @@
         <v>2.4155408304000005E-17</v>
       </c>
       <c r="G11" s="19">
-        <v>-0.9407316280938115</v>
+        <v>-0.94150045619673872</v>
       </c>
       <c r="H11" s="12">
-        <v>-2.7409676E-16</v>
+        <v>-2.7432077E-16</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -8845,7 +8110,7 @@
         <v>1.3353E-17</v>
       </c>
       <c r="C12" s="24">
-        <v>1.2930231984252241E-20</v>
+        <v>1.2201376283994398E-20</v>
       </c>
       <c r="D12" s="19">
         <v>0.25</v>
@@ -8857,10 +8122,10 @@
         <v>5.4613770000000075E-19</v>
       </c>
       <c r="G12" s="19">
-        <v>0.12484085973189538</v>
+        <v>8.5748520931625716E-2</v>
       </c>
       <c r="H12" s="12">
-        <v>1.6669999999999989E-18</v>
+        <v>1.1449999999999981E-18</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -8871,7 +8136,7 @@
         <v>5.5999999999999995E-18</v>
       </c>
       <c r="C13" s="24">
-        <v>5.4226989524311053E-21</v>
+        <v>5.1170304194090184E-21</v>
       </c>
       <c r="D13" s="19">
         <v>0.4047</v>
@@ -8883,10 +8148,10 @@
         <v>2.2960000000000069E-20</v>
       </c>
       <c r="G13" s="19">
-        <v>0.19035714285714295</v>
+        <v>0.19071428571428586</v>
       </c>
       <c r="H13" s="12">
-        <v>1.0660000000000003E-18</v>
+        <v>1.0680000000000008E-18</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -8894,25 +8159,25 @@
         <v>165</v>
       </c>
       <c r="B14" s="12">
-        <v>1032.696089</v>
+        <v>1094.3847390000001</v>
       </c>
       <c r="C14" s="24">
         <v>1</v>
       </c>
       <c r="D14" s="19">
-        <v>0.28351543428262177</v>
+        <v>0.27454511100771112</v>
       </c>
       <c r="E14" s="19">
-        <v>9.1978057087713339E-2</v>
+        <v>9.6859373224501999E-2</v>
       </c>
       <c r="F14" s="12">
-        <v>94.985379828300211</v>
+        <v>106.00141988600012</v>
       </c>
       <c r="G14" s="19">
-        <v>3.4698388404566937E-3</v>
+        <v>1.2476332603537886E-2</v>
       </c>
       <c r="H14" s="12">
-        <v>3.5832889999999225</v>
+        <v>13.653908000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C63D74-45BB-4E2C-BE9B-F70462B19001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553B1C43-8D78-4619-8FF9-9CBB7F72A71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2529,7 +2529,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18AC1D4E-8AFF-4F3A-87D7-1A82850D7D48}" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18AC1D4E-8AFF-4F3A-87D7-1A82850D7D48}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:H14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="29">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -3612,7 +3612,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:X47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3711,119 +3710,119 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>87</v>
+        <v>40</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" t="s">
+        <v>136</v>
       </c>
       <c r="D2" s="8">
-        <v>45623</v>
+        <v>45627</v>
       </c>
       <c r="E2" s="2">
-        <v>3.1236000000000002</v>
+        <v>1.5004999999999999</v>
       </c>
       <c r="F2" s="1">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1">
         <f t="shared" ref="G2:G46" si="0">E2*F2</f>
-        <v>49.977600000000002</v>
+        <v>60.019999999999996</v>
       </c>
       <c r="H2" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>7.0499999999999993E-2</v>
+        <v>4.19E-2</v>
       </c>
       <c r="I2" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.35260000000000002</v>
+        <v>0.53510000000000002</v>
       </c>
       <c r="J2" s="9">
         <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
-        <v>0.19994327850255245</v>
+        <v>7.8303120911979066E-2</v>
       </c>
       <c r="K2" s="9">
         <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.267101492179555E-2</v>
+        <v>5.7776977267865372E-3</v>
       </c>
       <c r="L2" s="9">
         <f>I2*G2</f>
-        <v>17.622101760000003</v>
+        <v>32.116701999999997</v>
       </c>
       <c r="M2" s="12">
         <f>IF((1+H2)*F2&lt;0,0,(1+H2)*F2)</f>
-        <v>17.128</v>
+        <v>41.676000000000002</v>
       </c>
       <c r="N2" s="12">
         <f t="shared" ref="N2:N46" si="3">M2*E2</f>
-        <v>53.501020800000006</v>
+        <v>62.534838000000001</v>
       </c>
       <c r="O2" s="12">
         <v>17.100000000000001</v>
       </c>
       <c r="P2" s="12">
         <f t="shared" ref="P2:P46" si="4">IFERROR(O2*E2,G2)</f>
-        <v>53.413560000000004</v>
+        <v>25.658550000000002</v>
       </c>
       <c r="Q2" s="12">
         <f t="shared" ref="Q2:Q46" si="5">P2-G2</f>
-        <v>3.4359600000000015</v>
+        <v>-34.361449999999991</v>
       </c>
       <c r="R2" s="12">
         <f t="shared" ref="R2:R41" si="6">F2/(1+I2-H2)</f>
-        <v>12.479525778020435</v>
+        <v>26.788106080900082</v>
       </c>
       <c r="S2" s="12">
         <f t="shared" ref="S2:S41" si="7">M2-F2</f>
-        <v>1.1280000000000001</v>
+        <v>1.6760000000000019</v>
       </c>
       <c r="T2" s="12">
         <f t="shared" ref="T2:T41" si="8">0.5*(R2-F2)</f>
-        <v>-1.7602371109897827</v>
+        <v>-6.6059469595499589</v>
       </c>
       <c r="U2" s="14">
         <f t="shared" ref="U2:U41" si="9">S2+T2</f>
-        <v>-0.63223711098978264</v>
+        <v>-4.929946959549957</v>
       </c>
       <c r="V2" s="12">
         <f t="shared" ref="V2:V46" si="10">MAX($U$2:$U$280)-U2</f>
-        <v>160.90441117723483</v>
+        <v>277.12713313576421</v>
       </c>
       <c r="W2" s="9">
         <f t="shared" ref="W2:W46" si="11">IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V2)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>6.2148700130943493E-3</v>
+        <v>3.6084521522116758E-3</v>
       </c>
       <c r="X2" s="9">
         <f t="shared" ref="X2:X41" si="12">V2/MAX($V$2:$V$28)</f>
-        <v>0.91831233327595496</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.96512045591055184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="D3" s="8">
-        <v>45627</v>
+        <v>45481</v>
       </c>
       <c r="E3" s="2">
-        <v>2.2953000000000001</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1">
-        <v>21.78</v>
+        <v>48.68</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>49.991634000000005</v>
+        <v>48.68</v>
       </c>
       <c r="H3" s="21">
         <v>3.5000000000000003E-2</v>
@@ -3837,82 +3836,82 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>4.5269975942392342E-2</v>
+        <v>1.5651639817186903E-2</v>
       </c>
       <c r="L3" s="9">
         <f t="shared" ref="L3:L46" si="13">I3*G3</f>
-        <v>8.2486196100000004</v>
+        <v>8.0321999999999996</v>
       </c>
       <c r="M3" s="12">
         <f t="shared" ref="M3:M41" si="14">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
-        <v>22.542300000000001</v>
+        <v>50.383799999999994</v>
       </c>
       <c r="N3" s="12">
         <f t="shared" si="3"/>
-        <v>51.741341190000007</v>
+        <v>50.383799999999994</v>
       </c>
       <c r="O3" s="12" vm="1">
         <v>22.87</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="4"/>
-        <v>52.493511000000005</v>
+        <v>22.87</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" si="5"/>
-        <v>2.5018770000000004</v>
+        <v>-25.81</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="6"/>
-        <v>19.274336283185839</v>
+        <v>43.079646017699112</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" si="7"/>
-        <v>0.76229999999999976</v>
+        <v>1.703799999999994</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" si="8"/>
-        <v>-1.252831858407081</v>
+        <v>-2.8001769911504439</v>
       </c>
       <c r="U3" s="14">
         <f t="shared" si="9"/>
-        <v>-0.49053185840708124</v>
+        <v>-1.09637699115045</v>
       </c>
       <c r="V3" s="12">
         <f t="shared" si="10"/>
-        <v>160.76270592465212</v>
+        <v>273.29356316736471</v>
       </c>
       <c r="W3" s="9">
         <f t="shared" si="11"/>
-        <v>6.2203481475902132E-3</v>
+        <v>3.6590689821245481E-3</v>
       </c>
       <c r="X3" s="9">
         <f t="shared" si="12"/>
-        <v>0.917503594222845</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95176969969335323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>152</v>
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="D4" s="8">
-        <v>45481</v>
+        <v>45574</v>
       </c>
       <c r="E4" s="2">
-        <v>2</v>
+        <v>0.16059999999999999</v>
       </c>
       <c r="F4" s="1">
-        <v>20.927</v>
+        <v>421.18</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>41.853999999999999</v>
+        <v>67.641508000000002</v>
       </c>
       <c r="H4" s="21">
         <v>3.5000000000000003E-2</v>
@@ -3926,446 +3925,446 @@
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>4.5269975942392342E-2</v>
+        <v>1.5651639817186903E-2</v>
       </c>
       <c r="L4" s="9">
         <f t="shared" si="13"/>
-        <v>6.9059100000000004</v>
+        <v>11.16084882</v>
       </c>
       <c r="M4" s="12">
         <f t="shared" si="14"/>
-        <v>21.659444999999998</v>
+        <v>435.92129999999997</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" si="3"/>
-        <v>43.318889999999996</v>
+        <v>70.008960779999995</v>
       </c>
       <c r="O4" s="12">
         <v>22.41</v>
       </c>
       <c r="P4" s="12">
         <f t="shared" si="4"/>
-        <v>44.82</v>
+        <v>3.599046</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="5"/>
-        <v>2.9660000000000011</v>
+        <v>-64.042462</v>
       </c>
       <c r="R4" s="12">
         <f t="shared" si="6"/>
-        <v>18.51946902654867</v>
+        <v>372.72566371681415</v>
       </c>
       <c r="S4" s="12">
         <f t="shared" si="7"/>
-        <v>0.73244499999999846</v>
+        <v>14.741299999999967</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="8"/>
-        <v>-1.2037654867256649</v>
+        <v>-24.227168141592927</v>
       </c>
       <c r="U4" s="14">
         <f t="shared" si="9"/>
-        <v>-0.4713204867256664</v>
+        <v>-9.4858681415929595</v>
       </c>
       <c r="V4" s="12">
         <f t="shared" si="10"/>
-        <v>160.7434945529707</v>
+        <v>281.6830543178072</v>
       </c>
       <c r="W4" s="9">
         <f t="shared" si="11"/>
-        <v>6.2210915768691616E-3</v>
+        <v>3.5500893102066266E-3</v>
       </c>
       <c r="X4" s="9">
         <f t="shared" si="12"/>
-        <v>0.91739395124024981</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.98098686595330931</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>153</v>
+        <v>36</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>22</v>
       </c>
       <c r="D5" s="8">
-        <v>45481</v>
+        <v>45484</v>
       </c>
       <c r="E5" s="2">
-        <v>2</v>
+        <v>0.60660000000000003</v>
       </c>
       <c r="F5" s="1">
-        <v>16.399000000000001</v>
+        <v>186.18</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>32.798000000000002</v>
+        <v>112.93678800000001</v>
       </c>
       <c r="H5" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.24179999999999999</v>
       </c>
       <c r="I5" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
+        <v>0.32229999999999998</v>
       </c>
       <c r="J5" s="9">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.75023270245113249</v>
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>2.1341560087127818E-2</v>
+        <v>5.535689674981658E-2</v>
       </c>
       <c r="L5" s="9">
         <f t="shared" si="13"/>
-        <v>8.1995000000000005</v>
+        <v>36.399526772400002</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="14"/>
-        <v>16.808975</v>
+        <v>231.19832400000001</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="3"/>
-        <v>33.61795</v>
+        <v>140.24490333840001</v>
       </c>
       <c r="O5" s="12" vm="2">
         <v>16.5548</v>
       </c>
       <c r="P5" s="12">
         <f t="shared" si="4"/>
-        <v>33.1096</v>
+        <v>10.04214168</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="5"/>
-        <v>0.31159999999999854</v>
+        <v>-102.89464632000001</v>
       </c>
       <c r="R5" s="12">
         <f t="shared" si="6"/>
-        <v>13.386938775510204</v>
+        <v>172.30911614993059</v>
       </c>
       <c r="S5" s="12">
         <f t="shared" si="7"/>
-        <v>0.40997499999999931</v>
+        <v>45.018324000000007</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="8"/>
-        <v>-1.5060306122448983</v>
+        <v>-6.9354419250347092</v>
       </c>
       <c r="U5" s="14">
         <f t="shared" si="9"/>
-        <v>-1.096055612244899</v>
+        <v>38.082882074965298</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" si="10"/>
-        <v>161.36822967848994</v>
+        <v>234.11430410124893</v>
       </c>
       <c r="W5" s="9">
         <f t="shared" si="11"/>
-        <v>6.1970066969960569E-3</v>
+        <v>4.2714177753424391E-3</v>
       </c>
       <c r="X5" s="9">
         <f t="shared" si="12"/>
-        <v>0.92095943441499695</v>
+        <v>0.81532436522080676</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
       </c>
       <c r="D6" s="8">
-        <v>45630</v>
+        <v>45511</v>
       </c>
       <c r="E6" s="2">
-        <v>2</v>
+        <v>0.34489999999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>20.5</v>
+        <v>173.73</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>59.919476999999993</v>
       </c>
       <c r="H6" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1),2.5%)+2.5%</f>
-        <v>0.17429999999999998</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="I6" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.31569999999999998</v>
+        <v>0.47839999999999999</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="1"/>
-        <v>0.55210643015521066</v>
+        <v>0.30936454849498329</v>
       </c>
       <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v>0.11782812553647067</v>
+        <v>2.2826866001893469E-2</v>
       </c>
       <c r="L6" s="9">
         <f t="shared" si="13"/>
-        <v>12.9437</v>
+        <v>28.665477796799998</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="14"/>
-        <v>24.073149999999998</v>
+        <v>199.44203999999996</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="3"/>
-        <v>48.146299999999997</v>
+        <v>68.78755959599998</v>
       </c>
       <c r="O6" s="26">
         <v>20.52</v>
       </c>
       <c r="P6" s="12">
         <f t="shared" si="4"/>
-        <v>41.04</v>
+        <v>7.0773479999999998</v>
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="5"/>
-        <v>3.9999999999999147E-2</v>
+        <v>-52.842128999999993</v>
       </c>
       <c r="R6" s="12">
         <f t="shared" si="6"/>
-        <v>17.960399509374451</v>
+        <v>130.58478653036678</v>
       </c>
       <c r="S6" s="12">
         <f t="shared" si="7"/>
-        <v>3.5731499999999983</v>
+        <v>25.712039999999973</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="8"/>
-        <v>-1.2698002453127746</v>
+        <v>-21.572606734816603</v>
       </c>
       <c r="U6" s="14">
         <f t="shared" si="9"/>
-        <v>2.3033497546872237</v>
+        <v>4.1394332651833707</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="10"/>
-        <v>157.96882431155782</v>
+        <v>268.05775291103089</v>
       </c>
       <c r="W6" s="9">
         <f t="shared" si="11"/>
-        <v>6.3303629963575971E-3</v>
+        <v>3.7305393675067583E-3</v>
       </c>
       <c r="X6" s="9">
         <f t="shared" si="12"/>
-        <v>0.90155837603866884</v>
+        <v>0.93353551408880442</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D7" s="8">
-        <v>45553</v>
+        <v>45511</v>
       </c>
       <c r="E7" s="2">
-        <v>1.7345999999999999</v>
+        <v>0.74609999999999999</v>
       </c>
       <c r="F7" s="1">
-        <v>51.88</v>
+        <v>73.7</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>89.991048000000006</v>
+        <v>54.987569999999998</v>
       </c>
       <c r="H7" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1),2.5%)+8.2%</f>
-        <v>0.14079999999999998</v>
+        <v>0.20319999999999999</v>
       </c>
       <c r="I7" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.22600000000000001</v>
+        <v>0.24540000000000001</v>
       </c>
       <c r="J7" s="9">
         <f t="shared" si="1"/>
-        <v>0.623008849557522</v>
+        <v>0.82803585982070083</v>
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>0.1329598079764423</v>
+        <v>6.1097704015676157E-2</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" si="13"/>
-        <v>20.337976848</v>
+        <v>13.493949678</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" si="14"/>
-        <v>59.184704000000004</v>
+        <v>88.675840000000008</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="3"/>
-        <v>102.66178755840001</v>
+        <v>66.161044224000008</v>
       </c>
       <c r="O7" s="12" vm="3">
         <v>55.25</v>
       </c>
       <c r="P7" s="12">
         <f t="shared" si="4"/>
-        <v>95.836649999999992</v>
+        <v>41.222025000000002</v>
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="5"/>
-        <v>5.8456019999999853</v>
+        <v>-13.765544999999996</v>
       </c>
       <c r="R7" s="12">
         <f t="shared" si="6"/>
-        <v>47.806855879100631</v>
+        <v>70.715793513720982</v>
       </c>
       <c r="S7" s="12">
         <f t="shared" si="7"/>
-        <v>7.304704000000001</v>
+        <v>14.975840000000005</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="8"/>
-        <v>-2.0365720604496858</v>
+        <v>-1.4921032431395105</v>
       </c>
       <c r="U7" s="14">
         <f t="shared" si="9"/>
-        <v>5.2681319395503152</v>
+        <v>13.483736756860495</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="10"/>
-        <v>155.00404212669474</v>
+        <v>258.71344941935376</v>
       </c>
       <c r="W7" s="9">
         <f t="shared" si="11"/>
-        <v>6.4514446609246221E-3</v>
+        <v>3.8652803023745404E-3</v>
       </c>
       <c r="X7" s="9">
         <f t="shared" si="12"/>
-        <v>0.88463779551562971</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.90099312697568157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="D8" s="8">
         <v>45627</v>
       </c>
       <c r="E8" s="2">
-        <v>1.5004999999999999</v>
+        <v>3.0230999999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>40</v>
+        <v>21.49</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>60.019999999999996</v>
+        <v>64.966418999999988</v>
       </c>
       <c r="H8" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>4.19E-2</v>
+        <v>-8.7400000000000005E-2</v>
       </c>
       <c r="I8" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.53510000000000002</v>
+        <v>0.60389999999999999</v>
       </c>
       <c r="J8" s="9">
         <f t="shared" si="1"/>
-        <v>7.8303120911979066E-2</v>
+        <v>-0.14472594800463653</v>
       </c>
       <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v>1.6711107599526358E-2</v>
+        <v>-1.0678792506027599E-2</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="13"/>
-        <v>32.116701999999997</v>
+        <v>39.233220434099991</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="14"/>
-        <v>41.676000000000002</v>
+        <v>19.611773999999997</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="3"/>
-        <v>62.534838000000001</v>
+        <v>59.288353979399986</v>
       </c>
       <c r="O8" s="12" vm="4">
         <v>36.380000000000003</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="4"/>
-        <v>54.588190000000004</v>
+        <v>109.980378</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="5"/>
-        <v>-5.4318099999999916</v>
+        <v>45.013959000000014</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="6"/>
-        <v>26.788106080900082</v>
+        <v>12.706202329568971</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" si="7"/>
-        <v>1.6760000000000019</v>
+        <v>-1.8782260000000015</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="8"/>
-        <v>-6.6059469595499589</v>
+        <v>-4.3918988352155139</v>
       </c>
       <c r="U8" s="14">
         <f t="shared" si="9"/>
-        <v>-4.929946959549957</v>
+        <v>-6.2701248352155154</v>
       </c>
       <c r="V8" s="12">
         <f t="shared" si="10"/>
-        <v>165.20212102579501</v>
+        <v>278.46731101142979</v>
       </c>
       <c r="W8" s="9">
         <f t="shared" si="11"/>
-        <v>6.0531910473707404E-3</v>
+        <v>3.5910857772421074E-3</v>
       </c>
       <c r="X8" s="9">
         <f t="shared" si="12"/>
-        <v>0.94284018760822152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.96978774730034856</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>145</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>154</v>
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="D9" s="8">
-        <v>45688</v>
+        <v>45460</v>
       </c>
       <c r="E9" s="2">
-        <v>1</v>
+        <v>0.51239999999999997</v>
       </c>
       <c r="F9" s="1">
-        <v>44.24</v>
+        <v>157.99</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>44.24</v>
+        <v>80.954076000000001</v>
       </c>
       <c r="H9" s="21">
         <v>6.2E-2</v>
@@ -4379,82 +4378,82 @@
       </c>
       <c r="K9" s="9">
         <f t="shared" si="2"/>
-        <v>5.0696426260610133E-2</v>
+        <v>1.7527780550609964E-2</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="13"/>
-        <v>11.546640000000002</v>
+        <v>21.129013836000002</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="14"/>
-        <v>46.982880000000002</v>
+        <v>167.78538000000003</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="3"/>
-        <v>46.982880000000002</v>
+        <v>85.973228712000008</v>
       </c>
       <c r="O9" s="12" vm="5">
         <v>45.69</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="4"/>
-        <v>45.69</v>
+        <v>23.411555999999997</v>
       </c>
       <c r="Q9" s="12">
         <f t="shared" si="5"/>
-        <v>1.4499999999999957</v>
+        <v>-57.542520000000003</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="6"/>
-        <v>36.897414512093412</v>
+        <v>131.76814011676396</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" si="7"/>
-        <v>2.7428799999999995</v>
+        <v>9.7953800000000228</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="8"/>
-        <v>-3.6712927439532947</v>
+        <v>-13.110929941618025</v>
       </c>
       <c r="U9" s="14">
         <f t="shared" si="9"/>
-        <v>-0.92841274395329521</v>
+        <v>-3.3155499416180021</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="10"/>
-        <v>161.20058681019833</v>
+        <v>275.51273611783222</v>
       </c>
       <c r="W9" s="9">
         <f t="shared" si="11"/>
-        <v>6.2034513632225514E-3</v>
+        <v>3.6295962723564136E-3</v>
       </c>
       <c r="X9" s="9">
         <f t="shared" si="12"/>
-        <v>0.92000266441464951</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95949817140763438</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>155</v>
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="D10" s="8">
-        <v>45481</v>
+        <v>45507</v>
       </c>
       <c r="E10" s="2">
-        <v>1</v>
+        <v>0.52270000000000005</v>
       </c>
       <c r="F10" s="1">
-        <v>48.68</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>48.68</v>
+        <v>19.982821000000001</v>
       </c>
       <c r="H10" s="21">
         <v>3.7999999999999999E-2</v>
@@ -4468,82 +4467,82 @@
       </c>
       <c r="K10" s="9">
         <f t="shared" si="2"/>
-        <v>4.7986939840879116E-2</v>
+        <v>1.6591002815513421E-2</v>
       </c>
       <c r="L10" s="9">
         <f t="shared" si="13"/>
-        <v>8.2269199999999998</v>
+        <v>3.3770967490000006</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="14"/>
-        <v>50.52984</v>
+        <v>39.682739999999995</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="3"/>
-        <v>50.52984</v>
+        <v>20.742168197999998</v>
       </c>
       <c r="O10" s="12" vm="6">
         <v>47.963999999999999</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="4"/>
-        <v>47.963999999999999</v>
+        <v>25.070782800000003</v>
       </c>
       <c r="Q10" s="12">
         <f t="shared" si="5"/>
-        <v>-0.71600000000000108</v>
+        <v>5.0879618000000022</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="6"/>
-        <v>43.041556145004421</v>
+        <v>33.801945181255526</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" si="7"/>
-        <v>1.8498400000000004</v>
+        <v>1.4527399999999986</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="8"/>
-        <v>-2.8192219274977894</v>
+        <v>-2.2140274093722354</v>
       </c>
       <c r="U10" s="14">
         <f t="shared" si="9"/>
-        <v>-0.96938192749778906</v>
+        <v>-0.76128740937223682</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="10"/>
-        <v>161.24155599374282</v>
+        <v>272.95847358558649</v>
       </c>
       <c r="W10" s="9">
         <f t="shared" si="11"/>
-        <v>6.2018751545588301E-3</v>
+        <v>3.6635609324157828E-3</v>
       </c>
       <c r="X10" s="9">
         <f t="shared" si="12"/>
-        <v>0.92023648340231989</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95060271973625809</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>149</v>
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D11" s="8">
-        <v>45481</v>
+        <v>45678</v>
       </c>
       <c r="E11" s="2">
-        <v>1</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="F11" s="1">
-        <v>51.28</v>
+        <v>185.82</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>51.28</v>
+        <v>9.9971160000000001</v>
       </c>
       <c r="H11" s="21">
         <v>3.7999999999999999E-2</v>
@@ -4557,1252 +4556,1253 @@
       </c>
       <c r="K11" s="9">
         <f t="shared" si="2"/>
-        <v>4.7986939840879116E-2</v>
+        <v>1.6591002815513421E-2</v>
       </c>
       <c r="L11" s="9">
         <f t="shared" si="13"/>
-        <v>8.6663200000000007</v>
+        <v>1.6895126040000001</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="14"/>
-        <v>53.228640000000006</v>
+        <v>192.88115999999999</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="3"/>
-        <v>53.228640000000006</v>
+        <v>10.377006408</v>
       </c>
       <c r="O11" s="12">
         <v>51.28</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="4"/>
-        <v>51.28</v>
+        <v>2.758864</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-7.2382520000000001</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="6"/>
-        <v>45.340406719717066</v>
+        <v>164.29708222811669</v>
       </c>
       <c r="S11" s="12">
         <f t="shared" si="7"/>
-        <v>1.9486400000000046</v>
+        <v>7.061160000000001</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="8"/>
-        <v>-2.9697966401414675</v>
+        <v>-10.76145888594165</v>
       </c>
       <c r="U11" s="14">
         <f t="shared" si="9"/>
-        <v>-1.0211566401414629</v>
+        <v>-3.700298885941649</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" si="10"/>
-        <v>161.29333070638651</v>
+        <v>275.89748506215591</v>
       </c>
       <c r="W11" s="9">
         <f t="shared" si="11"/>
-        <v>6.1998843698030503E-3</v>
+        <v>3.6245346700957198E-3</v>
       </c>
       <c r="X11" s="9">
         <f t="shared" si="12"/>
-        <v>0.92053197161687317</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.96083809461311442</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="D12" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E12" s="2">
-        <v>0.74609999999999999</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1">
-        <v>73.7</v>
+        <v>16.399000000000001</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
-        <v>54.987569999999998</v>
+        <v>32.798000000000002</v>
       </c>
       <c r="H12" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1212</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I12" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24540000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" si="1"/>
-        <v>0.49388753056234719</v>
+        <v>0.1</v>
       </c>
       <c r="K12" s="9">
         <f t="shared" si="2"/>
-        <v>0.10540330409779509</v>
+        <v>7.3786301995309696E-3</v>
       </c>
       <c r="L12" s="9">
         <f t="shared" si="13"/>
-        <v>13.493949678</v>
+        <v>8.1995000000000005</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="14"/>
-        <v>82.632440000000003</v>
+        <v>16.808975</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="3"/>
-        <v>61.652063484000003</v>
+        <v>33.61795</v>
       </c>
       <c r="O12" s="12" vm="7">
         <v>70.8</v>
       </c>
       <c r="P12" s="12">
         <f t="shared" si="4"/>
-        <v>52.823879999999996</v>
+        <v>141.6</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="5"/>
-        <v>-2.1636900000000026</v>
+        <v>108.80199999999999</v>
       </c>
       <c r="R12" s="12">
         <f t="shared" si="6"/>
-        <v>65.557729941291583</v>
+        <v>13.386938775510204</v>
       </c>
       <c r="S12" s="12">
         <f t="shared" si="7"/>
-        <v>8.9324399999999997</v>
+        <v>0.40997499999999931</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="8"/>
-        <v>-4.0711350293542097</v>
+        <v>-1.5060306122448983</v>
       </c>
       <c r="U12" s="14">
         <f t="shared" si="9"/>
-        <v>4.86130497064579</v>
+        <v>-1.096055612244899</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="10"/>
-        <v>155.41086909559925</v>
+        <v>273.29324178845917</v>
       </c>
       <c r="W12" s="9">
         <f t="shared" si="11"/>
-        <v>6.4345563847587857E-3</v>
+        <v>3.6590732850029398E-3</v>
       </c>
       <c r="X12" s="9">
         <f t="shared" si="12"/>
-        <v>0.886959635049555</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95176858046207369</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>92</v>
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
       </c>
       <c r="D13" s="8">
-        <v>45627</v>
+        <v>45580</v>
       </c>
       <c r="E13" s="2">
-        <v>0.52039999999999997</v>
+        <v>0.34860000000000002</v>
       </c>
       <c r="F13" s="1">
-        <v>40.340000000000003</v>
+        <v>131.91</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="0"/>
-        <v>20.992936</v>
+        <v>45.983826000000001</v>
       </c>
       <c r="H13" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>8.6900000000000005E-2</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="I13" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24529999999999999</v>
+        <v>0.25430000000000003</v>
       </c>
       <c r="J13" s="9">
         <f t="shared" si="1"/>
-        <v>0.35426008968609868</v>
+        <v>0.2732992528509634</v>
       </c>
       <c r="K13" s="9">
         <f t="shared" si="2"/>
-        <v>7.5604629905071649E-2</v>
+        <v>2.0165741205953689E-2</v>
       </c>
       <c r="L13" s="9">
         <f t="shared" si="13"/>
-        <v>5.1495672008</v>
+        <v>11.693686951800002</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="14"/>
-        <v>43.845546000000006</v>
+        <v>141.07774500000002</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="3"/>
-        <v>22.817222138400002</v>
+        <v>49.179701907000009</v>
       </c>
       <c r="O13" s="12" vm="8">
         <v>43.35</v>
       </c>
       <c r="P13" s="12">
         <f t="shared" si="4"/>
-        <v>22.559339999999999</v>
+        <v>15.111810000000002</v>
       </c>
       <c r="Q13" s="12">
         <f t="shared" si="5"/>
-        <v>1.5664039999999986</v>
+        <v>-30.872015999999999</v>
       </c>
       <c r="R13" s="12">
         <f t="shared" si="6"/>
-        <v>34.82389502762431</v>
+        <v>111.3352464550979</v>
       </c>
       <c r="S13" s="12">
         <f t="shared" si="7"/>
-        <v>3.5055460000000025</v>
+        <v>9.1677450000000249</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="8"/>
-        <v>-2.7580524861878466</v>
+        <v>-10.287376772451047</v>
       </c>
       <c r="U13" s="14">
         <f t="shared" si="9"/>
-        <v>0.7474935138121559</v>
+        <v>-1.1196317724510223</v>
       </c>
       <c r="V13" s="12">
         <f t="shared" si="10"/>
-        <v>159.5246805524329</v>
+        <v>273.31681794866529</v>
       </c>
       <c r="W13" s="9">
         <f t="shared" si="11"/>
-        <v>6.2686224886143432E-3</v>
+        <v>3.6587576553295791E-3</v>
       </c>
       <c r="X13" s="9">
         <f t="shared" si="12"/>
-        <v>0.91043794599170247</v>
+        <v>0.95185068658509842</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>19</v>
+        <v>145</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="D14" s="8">
-        <v>45544</v>
+        <v>45481</v>
       </c>
       <c r="E14" s="2">
-        <v>0.51380000000000003</v>
+        <v>2</v>
       </c>
       <c r="F14" s="1">
-        <v>138.53</v>
+        <v>20.927</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="0"/>
-        <v>71.176714000000004</v>
+        <v>41.853999999999999</v>
       </c>
       <c r="H14" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1),2.5%)+3.4%</f>
-        <v>8.4199999999999997E-2</v>
+        <v>5.9000000000000004E-2</v>
       </c>
       <c r="I14" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.2001</v>
+        <v>0.25</v>
       </c>
       <c r="J14" s="9">
         <f t="shared" si="1"/>
-        <v>0.42078960519740127</v>
+        <v>0.23600000000000002</v>
       </c>
       <c r="K14" s="9">
         <f t="shared" si="2"/>
-        <v>8.9803066433591316E-2</v>
+        <v>1.7413567270893087E-2</v>
       </c>
       <c r="L14" s="9">
         <f t="shared" si="13"/>
-        <v>14.242460471400001</v>
+        <v>10.4635</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" si="14"/>
-        <v>150.19422600000001</v>
+        <v>22.161693</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="3"/>
-        <v>77.169793318800018</v>
+        <v>44.323385999999999</v>
       </c>
       <c r="O14" s="12" vm="9">
         <v>140.04</v>
       </c>
       <c r="P14" s="12">
         <f t="shared" si="4"/>
-        <v>71.952551999999997</v>
+        <v>280.08</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="5"/>
-        <v>0.77583799999999314</v>
+        <v>238.226</v>
       </c>
       <c r="R14" s="12">
         <f t="shared" si="6"/>
-        <v>124.14194820324403</v>
+        <v>17.570948782535684</v>
       </c>
       <c r="S14" s="12">
         <f t="shared" si="7"/>
-        <v>11.664226000000014</v>
+        <v>1.234693</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="8"/>
-        <v>-7.194025898377987</v>
+        <v>-1.6780256087321579</v>
       </c>
       <c r="U14" s="14">
         <f t="shared" si="9"/>
-        <v>4.4702001016220265</v>
+        <v>-0.44333260873215785</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="10"/>
-        <v>155.80197396462302</v>
+        <v>272.64051878494638</v>
       </c>
       <c r="W14" s="9">
         <f t="shared" si="11"/>
-        <v>6.4184039171869779E-3</v>
+        <v>3.6678333963587446E-3</v>
       </c>
       <c r="X14" s="9">
         <f t="shared" si="12"/>
-        <v>0.88919174554423375</v>
+        <v>0.94949541321350639</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
+        <v>75</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="D15" s="8">
-        <v>45460</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45697</v>
       </c>
       <c r="E15" s="2">
-        <v>0.51239999999999997</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F15" s="1">
-        <v>157.99</v>
+        <v>2742.9</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="0"/>
-        <v>80.954076000000001</v>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="H15" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1),2.5%)+2.8%</f>
-        <v>9.3899999999999997E-2</v>
+        <v>0.11459999999999999</v>
       </c>
       <c r="I15" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.1875</v>
+        <v>0.14630000000000001</v>
       </c>
       <c r="J15" s="9">
         <f t="shared" si="1"/>
-        <v>0.50080000000000002</v>
+        <v>0.78332194121667797</v>
       </c>
       <c r="K15" s="9">
         <f t="shared" si="2"/>
-        <v>0.10687853291633612</v>
+        <v>5.7798429314166025E-2</v>
       </c>
       <c r="L15" s="9">
         <f t="shared" si="13"/>
-        <v>15.178889250000001</v>
+        <v>4.0128627000000008E-17</v>
       </c>
       <c r="M15" s="12">
         <f t="shared" si="14"/>
-        <v>172.82526100000001</v>
+        <v>3057.2363400000004</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="3"/>
-        <v>88.555663736400007</v>
+        <v>3.0572363400000003E-16</v>
       </c>
       <c r="O15" s="12" vm="10">
         <v>153.85</v>
       </c>
       <c r="P15" s="12">
         <f t="shared" si="4"/>
-        <v>78.832739999999987</v>
+        <v>1.5384999999999999E-17</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="5"/>
-        <v>-2.1213360000000137</v>
+        <v>-2.5890500000000001E-16</v>
       </c>
       <c r="R15" s="12">
         <f t="shared" si="6"/>
-        <v>144.46781272860281</v>
+        <v>2658.621692352428</v>
       </c>
       <c r="S15" s="12">
         <f t="shared" si="7"/>
-        <v>14.835261000000003</v>
+        <v>314.33634000000029</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="8"/>
-        <v>-6.7610936356986002</v>
+        <v>-42.139153823786046</v>
       </c>
       <c r="U15" s="14">
         <f t="shared" si="9"/>
-        <v>8.0741673643014025</v>
+        <v>272.19718617621425</v>
       </c>
       <c r="V15" s="12">
         <f t="shared" si="10"/>
-        <v>152.19800670194365</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9">
         <f t="shared" si="11"/>
-        <v>6.5703882834572585E-3</v>
+        <v>0</v>
       </c>
       <c r="X15" s="9">
         <f t="shared" si="12"/>
-        <v>0.86862321319743696</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D16" s="8">
-        <v>45484</v>
+        <v>45544</v>
       </c>
       <c r="E16" s="2">
-        <v>0.4108</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F16" s="1">
-        <v>189.76</v>
+        <v>188.12</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="0"/>
-        <v>77.953407999999996</v>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="H16" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.24179999999999999</v>
+        <v>0.1164</v>
       </c>
       <c r="I16" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.32229999999999998</v>
+        <v>0.3664</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>0.75023270245113249</v>
+        <v>0.31768558951965065</v>
       </c>
       <c r="K16" s="9">
         <f t="shared" si="2"/>
-        <v>0.1601113629868913</v>
+        <v>2.3440844847854934E-2</v>
       </c>
       <c r="L16" s="9">
         <f t="shared" si="13"/>
-        <v>25.124383398399996</v>
+        <v>6.8927168000000004E-18</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" si="14"/>
-        <v>235.643968</v>
+        <v>210.01716800000003</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="3"/>
-        <v>96.802542054400007</v>
+        <v>2.1001716800000003E-17</v>
       </c>
       <c r="O16" s="12" vm="11">
         <v>191.65</v>
       </c>
       <c r="P16" s="12">
         <f t="shared" si="4"/>
-        <v>78.729820000000004</v>
+        <v>1.9164999999999999E-17</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="5"/>
-        <v>0.77641200000000765</v>
+        <v>3.5299999999999804E-19</v>
       </c>
       <c r="R16" s="12">
         <f t="shared" si="6"/>
-        <v>175.62239703840814</v>
+        <v>150.49600000000001</v>
       </c>
       <c r="S16" s="12">
         <f t="shared" si="7"/>
-        <v>45.88396800000001</v>
+        <v>21.897168000000022</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="8"/>
-        <v>-7.0688014807959263</v>
+        <v>-18.811999999999998</v>
       </c>
       <c r="U16" s="14">
         <f t="shared" si="9"/>
-        <v>38.815166519204084</v>
+        <v>3.0851680000000243</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="10"/>
-        <v>121.45700754704096</v>
+        <v>269.11201817621424</v>
       </c>
       <c r="W16" s="9">
         <f t="shared" si="11"/>
-        <v>8.2333660296438193E-3</v>
+        <v>3.715924717064108E-3</v>
       </c>
       <c r="X16" s="9">
         <f t="shared" si="12"/>
-        <v>0.69317843542762225</v>
+        <v>0.9372070887984737</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>156</v>
+        <v>36</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D17" s="8">
-        <v>45580</v>
+        <v>45482</v>
       </c>
       <c r="E17" s="2">
-        <v>0.34860000000000002</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F17" s="1">
-        <v>131.91</v>
+        <v>147.01</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="0"/>
-        <v>45.983826000000001</v>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H17" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),1),2.5%)+2.6%</f>
-        <v>9.5500000000000002E-2</v>
+        <v>0.57689999999999997</v>
       </c>
       <c r="I17" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25430000000000003</v>
+        <v>0.48780000000000001</v>
       </c>
       <c r="J17" s="9">
         <f t="shared" si="1"/>
-        <v>0.37554069996067635</v>
+        <v>1.1826568265682655</v>
       </c>
       <c r="K17" s="9">
         <f t="shared" si="2"/>
-        <v>8.0146244133728131E-2</v>
+        <v>8.7263873761980637E-2</v>
       </c>
       <c r="L17" s="9">
         <f t="shared" si="13"/>
-        <v>11.693686951800002</v>
+        <v>7.1711477999999992E-18</v>
       </c>
       <c r="M17" s="12">
         <f t="shared" si="14"/>
-        <v>144.50740499999998</v>
+        <v>231.82006899999999</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="3"/>
-        <v>50.375281382999994</v>
+        <v>2.3182006899999998E-17</v>
       </c>
       <c r="O17" s="12" vm="12">
         <v>130.30000000000001</v>
       </c>
       <c r="P17" s="12">
         <f t="shared" si="4"/>
-        <v>45.422580000000004</v>
+        <v>1.3030000000000001E-17</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="5"/>
-        <v>-0.56124599999999703</v>
+        <v>-1.6709999999999983E-18</v>
       </c>
       <c r="R17" s="12">
         <f t="shared" si="6"/>
-        <v>113.83327580255435</v>
+        <v>161.38983422988252</v>
       </c>
       <c r="S17" s="12">
         <f t="shared" si="7"/>
-        <v>12.597404999999981</v>
+        <v>84.810068999999999</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="8"/>
-        <v>-9.0383620987228213</v>
+        <v>7.1899171149412666</v>
       </c>
       <c r="U17" s="14">
         <f t="shared" si="9"/>
-        <v>3.5590429012771594</v>
+        <v>91.999986114941265</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="10"/>
-        <v>156.71313116496788</v>
+        <v>180.19720006127298</v>
       </c>
       <c r="W17" s="9">
         <f t="shared" si="11"/>
-        <v>6.3810862087065679E-3</v>
+        <v>5.5494757946292564E-3</v>
       </c>
       <c r="X17" s="9">
         <f t="shared" si="12"/>
-        <v>0.89439189443081846</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.62755314468519197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D18" s="8">
         <v>45630</v>
       </c>
       <c r="E18" s="2">
-        <v>0.28749999999999998</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F18" s="1">
-        <v>34.78</v>
+        <v>323.75</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="0"/>
-        <v>9.99925</v>
+        <v>3.2375000000000002E-17</v>
       </c>
       <c r="H18" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-0.1268</v>
+        <v>0.16109999999999999</v>
       </c>
       <c r="I18" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.58609999999999995</v>
+        <v>0.32779999999999998</v>
       </c>
       <c r="J18" s="9">
         <f t="shared" si="1"/>
-        <v>-0.2163453335608258</v>
+        <v>0.49145820622330688</v>
       </c>
       <c r="K18" s="9">
         <f t="shared" si="2"/>
-        <v>-4.6171469357580742E-2</v>
+        <v>3.6262883622466109E-2</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="13"/>
-        <v>5.8605604249999992</v>
+        <v>1.0612525E-17</v>
       </c>
       <c r="M18" s="12">
         <f t="shared" si="14"/>
-        <v>30.369896000000001</v>
+        <v>375.90612500000003</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="3"/>
-        <v>8.7313450999999986</v>
+        <v>3.7590612500000005E-17</v>
       </c>
       <c r="O18" s="12" vm="13">
         <v>35.47</v>
       </c>
       <c r="P18" s="12">
         <f t="shared" si="4"/>
-        <v>10.197624999999999</v>
+        <v>3.5469999999999997E-18</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>0.19837499999999864</v>
+        <v>-2.8828000000000001E-17</v>
       </c>
       <c r="R18" s="12">
         <f t="shared" si="6"/>
-        <v>20.304746336622102</v>
+        <v>277.49207165509563</v>
       </c>
       <c r="S18" s="12">
         <f t="shared" si="7"/>
-        <v>-4.4101040000000005</v>
+        <v>52.156125000000031</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="8"/>
-        <v>-7.2376268316889494</v>
+        <v>-23.128964172452186</v>
       </c>
       <c r="U18" s="14">
         <f t="shared" si="9"/>
-        <v>-11.64773083168895</v>
+        <v>29.027160827547846</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="10"/>
-        <v>171.919904897934</v>
+        <v>243.1700253486664</v>
       </c>
       <c r="W18" s="9">
         <f t="shared" si="11"/>
-        <v>5.8166621287609683E-3</v>
+        <v>4.112348956521932E-3</v>
       </c>
       <c r="X18" s="9">
         <f t="shared" si="12"/>
-        <v>0.981179868521459</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.84686173841127221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>47</v>
+        <v>36</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D19" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E19" s="2">
-        <v>0.34489999999999998</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F19" s="1">
-        <v>173.73</v>
+        <v>169.34</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="0"/>
-        <v>59.919476999999993</v>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="H19" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.123</v>
+        <v>0.21429999999999999</v>
       </c>
       <c r="I19" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.47839999999999999</v>
+        <v>0.40479999999999999</v>
       </c>
       <c r="J19" s="9">
         <f t="shared" si="1"/>
-        <v>0.25710702341137126</v>
+        <v>0.52939723320158105</v>
       </c>
       <c r="K19" s="9">
         <f t="shared" si="2"/>
-        <v>5.4870649889563583E-2</v>
+        <v>3.9062264124493248E-2</v>
       </c>
       <c r="L19" s="9">
         <f t="shared" si="13"/>
-        <v>28.665477796799998</v>
+        <v>6.8548831999999995E-18</v>
       </c>
       <c r="M19" s="12">
         <f t="shared" si="14"/>
-        <v>195.09878999999998</v>
+        <v>205.62956199999999</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="3"/>
-        <v>67.289572670999988</v>
+        <v>2.0562956199999998E-17</v>
       </c>
       <c r="O19" s="12" vm="14">
         <v>152.91</v>
       </c>
       <c r="P19" s="12">
         <f t="shared" si="4"/>
-        <v>52.738658999999998</v>
+        <v>1.5291E-17</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="5"/>
-        <v>-7.180817999999995</v>
+        <v>-1.6429999999999997E-18</v>
       </c>
       <c r="R19" s="12">
         <f t="shared" si="6"/>
-        <v>128.17618415227977</v>
+        <v>142.2427551448971</v>
       </c>
       <c r="S19" s="12">
         <f t="shared" si="7"/>
-        <v>21.36878999999999</v>
+        <v>36.289561999999989</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="8"/>
-        <v>-22.776907923860108</v>
+        <v>-13.54862242755145</v>
       </c>
       <c r="U19" s="14">
         <f t="shared" si="9"/>
-        <v>-1.408117923860118</v>
+        <v>22.740939572448539</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="10"/>
-        <v>161.68029199010516</v>
+        <v>249.45624660376569</v>
       </c>
       <c r="W19" s="9">
         <f t="shared" si="11"/>
-        <v>6.1850457324829676E-3</v>
+        <v>4.0087190183230488E-3</v>
       </c>
       <c r="X19" s="9">
         <f t="shared" si="12"/>
-        <v>0.92274043387554749</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.86875407589200471</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
+        <v>40</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="D20" s="8">
-        <v>45574</v>
+        <v>45627</v>
       </c>
       <c r="E20" s="2">
-        <v>0.16059999999999999</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F20" s="1">
-        <v>421.18</v>
+        <v>26.63</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="0"/>
-        <v>67.641508000000002</v>
+        <v>2.663E-18</v>
       </c>
       <c r="H20" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.2412</v>
+        <v>-0.1193</v>
       </c>
       <c r="I20" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.27010000000000001</v>
+        <v>0.60340000000000005</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>0.89300259163272855</v>
+        <v>-0.19771295989393436</v>
       </c>
       <c r="K20" s="9">
         <f t="shared" si="2"/>
-        <v>0.19058068467290742</v>
+        <v>-1.4588508167120394E-2</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" si="13"/>
-        <v>18.269971310800003</v>
+        <v>1.6068542000000001E-18</v>
       </c>
       <c r="M20" s="12">
         <f t="shared" si="14"/>
-        <v>522.76861600000007</v>
+        <v>23.453040999999999</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="3"/>
-        <v>83.956639729600013</v>
+        <v>2.3453040999999998E-18</v>
       </c>
       <c r="O20" s="12" vm="15">
         <v>404</v>
       </c>
       <c r="P20" s="12">
         <f t="shared" si="4"/>
-        <v>64.882400000000004</v>
+        <v>4.0400000000000001E-17</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="5"/>
-        <v>-2.7591079999999977</v>
+        <v>3.7737000000000002E-17</v>
       </c>
       <c r="R20" s="12">
         <f t="shared" si="6"/>
-        <v>409.34979103897371</v>
+        <v>15.458292215707898</v>
       </c>
       <c r="S20" s="12">
         <f t="shared" si="7"/>
-        <v>101.58861600000006</v>
+        <v>-3.1769590000000001</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="8"/>
-        <v>-5.9151044805131505</v>
+        <v>-5.5858538921460505</v>
       </c>
       <c r="U20" s="14">
         <f t="shared" si="9"/>
-        <v>95.673511519486908</v>
+        <v>-8.7628128921460515</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="10"/>
-        <v>64.598662546758135</v>
+        <v>280.95999906836028</v>
       </c>
       <c r="W20" s="9">
         <f t="shared" si="11"/>
-        <v>1.5480196656953616E-2</v>
+        <v>3.5592255243305664E-3</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="12"/>
-        <v>0.36867695606229905</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.97846876025900742</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D21" s="8">
         <v>45511</v>
       </c>
       <c r="E21" s="2">
-        <v>0.12939999999999999</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F21" s="1">
-        <v>501.56</v>
+        <v>10.92</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="0"/>
-        <v>64.901863999999989</v>
+        <v>1.092E-18</v>
       </c>
       <c r="H21" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1928</v>
+        <v>-1.4844999999999999</v>
       </c>
       <c r="I21" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.26650000000000001</v>
+        <v>1.3212999999999999</v>
       </c>
       <c r="J21" s="9">
         <f t="shared" si="1"/>
-        <v>0.72345215759849901</v>
+        <v>-1.1235147203511693</v>
       </c>
       <c r="K21" s="9">
         <f t="shared" si="2"/>
-        <v>0.1543959769155063</v>
+        <v>-8.2899996452007296E-2</v>
       </c>
       <c r="L21" s="9">
         <f t="shared" si="13"/>
-        <v>17.296346755999998</v>
+        <v>1.4428596E-18</v>
       </c>
       <c r="M21" s="12">
         <f t="shared" si="14"/>
-        <v>598.2607680000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="3"/>
-        <v>77.414943379200011</v>
+        <v>0</v>
       </c>
       <c r="O21" s="12" vm="16">
         <v>559</v>
       </c>
       <c r="P21" s="12">
         <f t="shared" si="4"/>
-        <v>72.334599999999995</v>
+        <v>5.5899999999999994E-17</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="5"/>
-        <v>7.4327360000000056</v>
+        <v>5.4807999999999994E-17</v>
       </c>
       <c r="R21" s="12">
         <f t="shared" si="6"/>
-        <v>467.13234609294966</v>
+        <v>2.8693047453886176</v>
       </c>
       <c r="S21" s="12">
         <f t="shared" si="7"/>
-        <v>96.700768000000096</v>
+        <v>-10.92</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="8"/>
-        <v>-17.213826953525171</v>
+        <v>-4.025347627305691</v>
       </c>
       <c r="U21" s="14">
         <f t="shared" si="9"/>
-        <v>79.486941046474925</v>
+        <v>-14.94534762730569</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="10"/>
-        <v>80.785233019770118</v>
+        <v>287.14253380351994</v>
       </c>
       <c r="W21" s="9">
         <f t="shared" si="11"/>
-        <v>1.2378499914152326E-2</v>
+        <v>3.4825909862739443E-3</v>
       </c>
       <c r="X21" s="9">
         <f t="shared" si="12"/>
-        <v>0.46105681805647636</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>18</v>
+        <v>75</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="D22" s="8">
-        <v>45678</v>
+        <v>45574</v>
       </c>
       <c r="E22" s="2">
-        <v>5.3800000000000001E-2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F22" s="1">
-        <v>185.82</v>
+        <v>153.7552</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="0"/>
-        <v>9.9971160000000001</v>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="H22" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1925</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="I22" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.28539999999999999</v>
+        <v>8.8400000000000006E-2</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>0.6744919411352488</v>
+        <v>0.25678733031674206</v>
       </c>
       <c r="K22" s="9">
         <f t="shared" si="2"/>
-        <v>0.14394710290021392</v>
+        <v>1.8947387503320475E-2</v>
       </c>
       <c r="L22" s="9">
         <f t="shared" si="13"/>
-        <v>2.8531769063999999</v>
+        <v>1.359195968E-18</v>
       </c>
       <c r="M22" s="12">
         <f t="shared" si="14"/>
-        <v>221.59034999999997</v>
+        <v>157.24544304</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="3"/>
-        <v>11.921560829999999</v>
+        <v>1.5724544303999999E-17</v>
       </c>
       <c r="O22" s="12" vm="17">
         <v>179.25</v>
       </c>
       <c r="P22" s="12">
         <f t="shared" si="4"/>
-        <v>9.6436500000000009</v>
+        <v>1.7925E-17</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="5"/>
-        <v>-0.35346599999999917</v>
+        <v>2.5494800000000007E-18</v>
       </c>
       <c r="R22" s="12">
         <f t="shared" si="6"/>
-        <v>170.02470491353276</v>
+        <v>144.27625035188137</v>
       </c>
       <c r="S22" s="12">
         <f t="shared" si="7"/>
-        <v>35.770349999999979</v>
+        <v>3.4902430399999957</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="8"/>
-        <v>-7.8976475432336173</v>
+        <v>-4.7394748240593145</v>
       </c>
       <c r="U22" s="14">
         <f t="shared" si="9"/>
-        <v>27.872702456766362</v>
+        <v>-1.2492317840593188</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="10"/>
-        <v>132.39947160947867</v>
+        <v>273.44641796027355</v>
       </c>
       <c r="W22" s="9">
         <f t="shared" si="11"/>
-        <v>7.552900233239364E-3</v>
+        <v>3.6570235860441244E-3</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" si="12"/>
-        <v>0.75562917640760074</v>
+        <v>0.9523020304173464</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D23" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E23" s="2">
-        <v>2.9999999999999997E-4</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F23" s="1">
-        <v>130.51</v>
+        <v>11.05</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="0"/>
-        <v>3.9152999999999993E-2</v>
+        <v>1.1050000000000001E-18</v>
       </c>
       <c r="H23" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1169</v>
+        <v>-0.1055</v>
       </c>
       <c r="I23" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.23899999999999999</v>
+        <v>0.57940000000000003</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>0.48912133891213394</v>
+        <v>-0.18208491542975491</v>
       </c>
       <c r="K23" s="9">
         <f t="shared" si="2"/>
-        <v>0.10438612444289716</v>
+        <v>-1.3435372558690322E-2</v>
       </c>
       <c r="L23" s="9">
         <f t="shared" si="13"/>
-        <v>9.3575669999999972E-3</v>
+        <v>6.4023700000000011E-19</v>
       </c>
       <c r="M23" s="12">
         <f t="shared" si="14"/>
-        <v>145.76661899999999</v>
+        <v>9.8842250000000007</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="3"/>
-        <v>4.3729985699999994E-2</v>
+        <v>9.8842250000000007E-19</v>
       </c>
       <c r="O23" s="12" vm="18">
         <v>150.22999999999999</v>
       </c>
       <c r="P23" s="12">
         <f t="shared" si="4"/>
-        <v>4.5068999999999991E-2</v>
+        <v>1.5022999999999998E-17</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="5"/>
-        <v>5.9159999999999976E-3</v>
+        <v>1.3917999999999996E-17</v>
       </c>
       <c r="R23" s="12">
         <f t="shared" si="6"/>
-        <v>116.3087068888691</v>
+        <v>6.5582527152946763</v>
       </c>
       <c r="S23" s="12">
         <f t="shared" si="7"/>
-        <v>15.256619000000001</v>
+        <v>-1.165775</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="8"/>
-        <v>-7.1006465555654472</v>
+        <v>-2.2458736423526622</v>
       </c>
       <c r="U23" s="14">
         <f t="shared" si="9"/>
-        <v>8.1559724444345534</v>
+        <v>-3.4116486423526622</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="10"/>
-        <v>152.11620162181049</v>
+        <v>275.60883481856689</v>
       </c>
       <c r="W23" s="9">
         <f t="shared" si="11"/>
-        <v>6.5739217081306573E-3</v>
+        <v>3.6283307124689939E-3</v>
       </c>
       <c r="X23" s="9">
         <f t="shared" si="12"/>
-        <v>0.86815633591631525</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95983284387660561</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>14</v>
+        <v>145</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="D24" s="8">
-        <v>45482</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="2">
-        <v>1E-4</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>227.38</v>
+        <v>51.28</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>2.2738000000000001E-2</v>
+        <v>51.28</v>
       </c>
       <c r="H24" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.2092</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I24" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.28439999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="J24" s="9">
         <f t="shared" si="1"/>
-        <v>0.73558368495077353</v>
+        <v>0.1</v>
       </c>
       <c r="K24" s="9">
         <f t="shared" si="2"/>
-        <v>0.15698503411487832</v>
+        <v>7.3786301995309696E-3</v>
       </c>
       <c r="L24" s="9">
         <f t="shared" si="13"/>
-        <v>6.4666871999999997E-3</v>
+        <v>12.82</v>
       </c>
       <c r="M24" s="12">
         <f t="shared" si="14"/>
-        <v>274.94789600000001</v>
+        <v>52.561999999999998</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="3"/>
-        <v>2.7494789600000003E-2</v>
+        <v>52.561999999999998</v>
       </c>
       <c r="O24" s="12" vm="19">
         <v>247.1</v>
       </c>
       <c r="P24" s="12">
         <f t="shared" si="4"/>
-        <v>2.4709999999999999E-2</v>
+        <v>247.1</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="5"/>
-        <v>1.9719999999999981E-3</v>
+        <v>195.82</v>
       </c>
       <c r="R24" s="12">
         <f t="shared" si="6"/>
-        <v>211.47693452380955</v>
+        <v>41.861224489795916</v>
       </c>
       <c r="S24" s="12">
         <f t="shared" si="7"/>
-        <v>47.567896000000019</v>
+        <v>1.2819999999999965</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="8"/>
-        <v>-7.9515327380952243</v>
+        <v>-4.7093877551020427</v>
       </c>
       <c r="U24" s="14">
         <f t="shared" si="9"/>
-        <v>39.616363261904795</v>
+        <v>-3.4273877551020462</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="10"/>
-        <v>120.65581080434025</v>
+        <v>275.62457393131626</v>
       </c>
       <c r="W24" s="9">
         <f t="shared" si="11"/>
-        <v>8.2880384569429116E-3</v>
+        <v>3.6281235222850382E-3</v>
       </c>
       <c r="X24" s="9">
         <f t="shared" si="12"/>
-        <v>0.68860585196132951</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.9598876567687985</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D25" s="8">
         <v>45511</v>
@@ -5811,39 +5811,39 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>10.92</v>
+        <v>20.82</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="0"/>
-        <v>1.092E-18</v>
+        <v>2.0820000000000002E-18</v>
       </c>
       <c r="H25" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-1.4844999999999999</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="I25" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),2),25%)</f>
-        <v>1.3212999999999999</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>-1.1235147203511693</v>
+        <v>1.6807909604519777E-2</v>
       </c>
       <c r="K25" s="9">
         <f t="shared" si="2"/>
-        <v>-0.23977556913147086</v>
+        <v>1.2401934939889627E-3</v>
       </c>
       <c r="L25" s="9">
         <f t="shared" si="13"/>
-        <v>1.4428596E-18</v>
+        <v>1.474056E-18</v>
       </c>
       <c r="M25" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>21.067758000000001</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.1067757999999999E-18</v>
       </c>
       <c r="O25" s="12" vm="20">
         <v>5.09</v>
@@ -5854,87 +5854,87 @@
       </c>
       <c r="Q25" s="12">
         <f t="shared" si="5"/>
-        <v>-5.8300000000000009E-19</v>
+        <v>-1.5730000000000002E-18</v>
       </c>
       <c r="R25" s="12">
         <f t="shared" si="6"/>
-        <v>2.8693047453886176</v>
+        <v>12.275219621484583</v>
       </c>
       <c r="S25" s="12">
         <f t="shared" si="7"/>
-        <v>-10.92</v>
+        <v>0.24775800000000103</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="8"/>
-        <v>-4.025347627305691</v>
+        <v>-4.2723901892577087</v>
       </c>
       <c r="U25" s="14">
         <f t="shared" si="9"/>
-        <v>-14.94534762730569</v>
+        <v>-4.0246321892577077</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="10"/>
-        <v>175.21752169355074</v>
+        <v>276.22181836547196</v>
       </c>
       <c r="W25" s="9">
         <f t="shared" si="11"/>
-        <v>5.7071917827314373E-3</v>
+        <v>3.6202788248859094E-3</v>
       </c>
       <c r="X25" s="9">
         <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.96196761485179139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>7</v>
+        <v>39</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D26" s="8">
-        <v>45511</v>
+        <v>45574</v>
       </c>
       <c r="E26" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>283.43</v>
+        <v>47.42</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="0"/>
-        <v>2.8342999999999998E-17</v>
+        <v>4.7419999999999999E-18</v>
       </c>
       <c r="H26" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.17100000000000001</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="I26" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24360000000000001</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>0.70197044334975367</v>
+        <v>0.23432343234323433</v>
       </c>
       <c r="K26" s="9">
         <f t="shared" si="2"/>
-        <v>0.14981144396136523</v>
+        <v>1.7289859543455407E-2</v>
       </c>
       <c r="L26" s="9">
         <f t="shared" si="13"/>
-        <v>6.9043547999999996E-18</v>
+        <v>1.7241911999999999E-18</v>
       </c>
       <c r="M26" s="12">
         <f t="shared" si="14"/>
-        <v>331.89653000000004</v>
+        <v>51.460183999999998</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="3"/>
-        <v>3.3189653000000001E-17</v>
+        <v>5.1460184E-18</v>
       </c>
       <c r="O26" s="12" vm="21">
         <v>349.86</v>
@@ -5945,87 +5945,87 @@
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="5"/>
-        <v>6.6430000000000039E-18</v>
+        <v>3.0244E-17</v>
       </c>
       <c r="R26" s="12">
         <f t="shared" si="6"/>
-        <v>264.24575797128472</v>
+        <v>37.093241551939926</v>
       </c>
       <c r="S26" s="12">
         <f t="shared" si="7"/>
-        <v>48.466530000000034</v>
+        <v>4.0401839999999964</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="8"/>
-        <v>-9.5921210143576445</v>
+        <v>-5.163379224030038</v>
       </c>
       <c r="U26" s="14">
         <f t="shared" si="9"/>
-        <v>38.87440898564239</v>
+        <v>-1.1231952240300416</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="10"/>
-        <v>121.39776508060265</v>
+        <v>273.32038140024429</v>
       </c>
       <c r="W26" s="9">
         <f t="shared" si="11"/>
-        <v>8.2373839364838792E-3</v>
+        <v>3.6587099537799279E-3</v>
       </c>
       <c r="X26" s="9">
         <f t="shared" si="12"/>
-        <v>0.6928403273099768</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95186309662944746</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
+        <v>75</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="D27" s="8">
-        <v>45544</v>
+        <v>45580</v>
       </c>
       <c r="E27" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F27" s="1">
-        <v>188.12</v>
+        <v>17</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="0"/>
-        <v>1.8812000000000001E-17</v>
+        <v>1.7E-18</v>
       </c>
       <c r="H27" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1164</v>
+        <v>3.1099999999999999E-2</v>
       </c>
       <c r="I27" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.3664</v>
+        <v>0.1285</v>
       </c>
       <c r="J27" s="9">
         <f t="shared" si="1"/>
-        <v>0.31768558951965065</v>
+        <v>0.24202334630350195</v>
       </c>
       <c r="K27" s="9">
         <f t="shared" si="2"/>
-        <v>6.7799060975482481E-2</v>
+        <v>1.7858007720265613E-2</v>
       </c>
       <c r="L27" s="9">
         <f t="shared" si="13"/>
-        <v>6.8927168000000004E-18</v>
+        <v>2.1845000000000003E-19</v>
       </c>
       <c r="M27" s="12">
         <f t="shared" si="14"/>
-        <v>210.01716800000003</v>
+        <v>17.528699999999997</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="3"/>
-        <v>2.1001716800000003E-17</v>
+        <v>1.7528699999999997E-18</v>
       </c>
       <c r="O27" s="12" vm="22">
         <v>161.1</v>
@@ -6036,87 +6036,87 @@
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="5"/>
-        <v>-2.702000000000003E-18</v>
+        <v>1.441E-17</v>
       </c>
       <c r="R27" s="12">
         <f t="shared" si="6"/>
-        <v>150.49600000000001</v>
+        <v>15.491160925824675</v>
       </c>
       <c r="S27" s="12">
         <f t="shared" si="7"/>
-        <v>21.897168000000022</v>
+        <v>0.52869999999999706</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="8"/>
-        <v>-18.811999999999998</v>
+        <v>-0.75441953708766274</v>
       </c>
       <c r="U27" s="14">
         <f t="shared" si="9"/>
-        <v>3.0851680000000243</v>
+        <v>-0.22571953708766568</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="10"/>
-        <v>157.18700606624503</v>
+        <v>272.42290571330193</v>
       </c>
       <c r="W27" s="9">
         <f t="shared" si="11"/>
-        <v>6.3618490168236876E-3</v>
+        <v>3.6707632839523439E-3</v>
       </c>
       <c r="X27" s="9">
         <f t="shared" si="12"/>
-        <v>0.89709638937343017</v>
+        <v>0.94873755589170206</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="D28" s="8">
-        <v>45562</v>
+        <v>45511</v>
       </c>
       <c r="E28" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F28" s="1">
-        <v>668.82</v>
+        <v>113.58</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="0"/>
-        <v>6.6881999999999999E-17</v>
+        <v>1.1357999999999999E-17</v>
       </c>
       <c r="H28" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.16070000000000001</v>
+        <v>7.6100000000000001E-2</v>
       </c>
       <c r="I28" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.27700000000000002</v>
+        <v>0.20619999999999999</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>0.58014440433212999</v>
+        <v>0.36905916585838994</v>
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
-        <v>0.12381186664265129</v>
+        <v>2.7231511066164248E-2</v>
       </c>
       <c r="L28" s="9">
         <f t="shared" si="13"/>
-        <v>1.8526314000000002E-17</v>
+        <v>2.3420195999999997E-18</v>
       </c>
       <c r="M28" s="12">
         <f t="shared" si="14"/>
-        <v>776.29937400000006</v>
+        <v>122.223438</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="3"/>
-        <v>7.7629937400000001E-17</v>
+        <v>1.2222343799999999E-17</v>
       </c>
       <c r="O28" s="12" vm="23">
         <v>692.1</v>
@@ -6127,87 +6127,87 @@
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="5"/>
-        <v>2.3279999999999956E-18</v>
+        <v>5.7851999999999991E-17</v>
       </c>
       <c r="R28" s="12">
         <f t="shared" si="6"/>
-        <v>599.14001612469769</v>
+        <v>100.50438014335016</v>
       </c>
       <c r="S28" s="12">
         <f t="shared" si="7"/>
-        <v>107.47937400000001</v>
+        <v>8.6434380000000033</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="8"/>
-        <v>-34.839991937651178</v>
+        <v>-6.5378099283249185</v>
       </c>
       <c r="U28" s="14">
         <f t="shared" si="9"/>
-        <v>72.63938206234883</v>
+        <v>2.1056280716750848</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="10"/>
-        <v>87.632792003896213</v>
+        <v>270.09155810453916</v>
       </c>
       <c r="W28" s="9">
         <f t="shared" si="11"/>
-        <v>1.1411253449000453E-2</v>
+        <v>3.7024481883767327E-3</v>
       </c>
       <c r="X28" s="9">
         <f t="shared" si="12"/>
-        <v>0.50013715042244966</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.94061842572355348</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D29" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E29" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F29" s="1">
-        <v>700.32</v>
+        <v>13.04</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" si="0"/>
-        <v>7.0031999999999998E-17</v>
+        <v>1.304E-18</v>
       </c>
       <c r="H29" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C29,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.2051</v>
+        <v>4.82E-2</v>
       </c>
       <c r="I29" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C29,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.36940000000000001</v>
+        <v>0.4264</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>0.55522468868435304</v>
+        <v>0.11303939962476547</v>
       </c>
       <c r="K29" s="9">
         <f t="shared" si="2"/>
-        <v>0.11849361055413957</v>
+        <v>8.340759278081443E-3</v>
       </c>
       <c r="L29" s="9">
         <f t="shared" si="13"/>
-        <v>2.5869820800000001E-17</v>
+        <v>5.5602559999999997E-19</v>
       </c>
       <c r="M29" s="12">
         <f t="shared" si="14"/>
-        <v>843.95563200000015</v>
+        <v>13.668528</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="3"/>
-        <v>8.4395563200000012E-17</v>
+        <v>1.3668528E-18</v>
       </c>
       <c r="O29" s="12" vm="24">
         <v>735.96</v>
@@ -6218,87 +6218,87 @@
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="5"/>
-        <v>3.5639999999999974E-18</v>
+        <v>7.2291999999999997E-17</v>
       </c>
       <c r="R29" s="12">
         <f t="shared" si="6"/>
-        <v>601.49446019067261</v>
+        <v>9.4616166013640974</v>
       </c>
       <c r="S29" s="12">
         <f t="shared" si="7"/>
-        <v>143.6356320000001</v>
+        <v>0.62852800000000109</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="8"/>
-        <v>-49.412769904663719</v>
+        <v>-1.7891916993179509</v>
       </c>
       <c r="U29" s="14">
         <f t="shared" si="9"/>
-        <v>94.222862095336382</v>
+        <v>-1.1606636993179498</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="10"/>
-        <v>66.049311970908661</v>
+        <v>273.35784987553217</v>
       </c>
       <c r="W29" s="9">
         <f t="shared" si="11"/>
-        <v>1.5140203132478484E-2</v>
+        <v>3.6582084635774286E-3</v>
       </c>
       <c r="X29" s="9">
         <f t="shared" si="12"/>
-        <v>0.376956090535435</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95199358400375444</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D30" s="8">
-        <v>45482</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F30" s="1">
-        <v>147.01</v>
+        <v>700.32</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" si="0"/>
-        <v>1.4700999999999999E-17</v>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="H30" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.55089999999999995</v>
+        <v>0.2051</v>
       </c>
       <c r="I30" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.48780000000000001</v>
+        <v>0.36940000000000001</v>
       </c>
       <c r="J30" s="9">
         <f t="shared" si="1"/>
-        <v>1.1293562935629355</v>
+        <v>0.55522468868435304</v>
       </c>
       <c r="K30" s="9">
         <f t="shared" si="2"/>
-        <v>0.24102225198849353</v>
+        <v>4.0967976554515485E-2</v>
       </c>
       <c r="L30" s="9">
         <f t="shared" si="13"/>
-        <v>7.1711477999999992E-18</v>
+        <v>2.5869820800000001E-17</v>
       </c>
       <c r="M30" s="12">
         <f t="shared" si="14"/>
-        <v>227.99780899999999</v>
+        <v>843.95563200000015</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="3"/>
-        <v>2.2799780899999998E-17</v>
+        <v>8.4395563200000012E-17</v>
       </c>
       <c r="O30" s="12" vm="25">
         <v>130.28</v>
@@ -6309,87 +6309,87 @@
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="5"/>
-        <v>-1.6729999999999987E-18</v>
+        <v>-5.7003999999999997E-17</v>
       </c>
       <c r="R30" s="12">
         <f t="shared" si="6"/>
-        <v>156.91108976411567</v>
+        <v>601.49446019067261</v>
       </c>
       <c r="S30" s="12">
         <f t="shared" si="7"/>
-        <v>80.987808999999999</v>
+        <v>143.6356320000001</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="8"/>
-        <v>4.9505448820578408</v>
+        <v>-49.412769904663719</v>
       </c>
       <c r="U30" s="14">
         <f t="shared" si="9"/>
-        <v>85.938353882057839</v>
+        <v>94.222862095336382</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="10"/>
-        <v>74.333820184187203</v>
+        <v>177.97432408087786</v>
       </c>
       <c r="W30" s="9">
         <f t="shared" si="11"/>
-        <v>1.3452826688069595E-2</v>
+        <v>5.6187880199256406E-3</v>
       </c>
       <c r="X30" s="9">
         <f t="shared" si="12"/>
-        <v>0.42423736773422943</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.61981177683226307</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>72</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D31" s="8">
-        <v>45481</v>
+        <v>45562</v>
       </c>
       <c r="E31" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F31" s="1">
-        <v>169.34</v>
+        <v>56</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="0"/>
-        <v>1.6933999999999999E-17</v>
+        <v>5.5999999999999995E-18</v>
       </c>
       <c r="H31" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.21429999999999999</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="I31" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.40479999999999999</v>
+        <v>0.4047</v>
       </c>
       <c r="J31" s="9">
         <f t="shared" si="1"/>
-        <v>0.52939723320158105</v>
+        <v>1.0130961205831481E-2</v>
       </c>
       <c r="K31" s="9">
         <f t="shared" si="2"/>
-        <v>0.1129816286233076</v>
+        <v>7.4752616303624855E-4</v>
       </c>
       <c r="L31" s="9">
         <f t="shared" si="13"/>
-        <v>6.8548831999999995E-18</v>
+        <v>2.2663199999999999E-18</v>
       </c>
       <c r="M31" s="12">
         <f t="shared" si="14"/>
-        <v>205.62956199999999</v>
+        <v>56.229599999999998</v>
       </c>
       <c r="N31" s="12">
         <f t="shared" si="3"/>
-        <v>2.0562956199999998E-17</v>
+        <v>5.6229599999999995E-18</v>
       </c>
       <c r="O31" s="12" vm="26">
         <v>168.57</v>
@@ -6400,87 +6400,87 @@
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="5"/>
-        <v>-7.7000000000000438E-20</v>
+        <v>1.1256999999999999E-17</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="6"/>
-        <v>142.2427551448971</v>
+        <v>39.98286448664858</v>
       </c>
       <c r="S31" s="12">
         <f t="shared" si="7"/>
-        <v>36.289561999999989</v>
+        <v>0.22959999999999781</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="8"/>
-        <v>-13.54862242755145</v>
+        <v>-8.0085677566757099</v>
       </c>
       <c r="U31" s="14">
         <f t="shared" si="9"/>
-        <v>22.740939572448539</v>
+        <v>-7.7789677566757121</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="10"/>
-        <v>137.53123449379649</v>
+        <v>279.97615393288993</v>
       </c>
       <c r="W31" s="9">
         <f t="shared" si="11"/>
-        <v>7.2710755755275814E-3</v>
+        <v>3.5717327563535976E-3</v>
       </c>
       <c r="X31" s="9">
         <f t="shared" si="12"/>
-        <v>0.78491713137190566</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.97504243005832891</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" t="s">
+        <v>55</v>
       </c>
       <c r="D32" s="8">
-        <v>45511</v>
+        <v>45505</v>
       </c>
       <c r="E32" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F32" s="1">
-        <v>113.58</v>
+        <v>86.6</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" si="0"/>
-        <v>1.1357999999999999E-17</v>
+        <v>8.6599999999999986E-18</v>
       </c>
       <c r="H32" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C32,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>7.6100000000000001E-2</v>
+        <v>0.1467</v>
       </c>
       <c r="I32" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C32,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.20619999999999999</v>
+        <v>0.21079999999999999</v>
       </c>
       <c r="J32" s="9">
         <f t="shared" si="1"/>
-        <v>0.36905916585838994</v>
+        <v>0.6959203036053131</v>
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>7.8762983638721001E-2</v>
+        <v>5.1349385686489238E-2</v>
       </c>
       <c r="L32" s="9">
         <f t="shared" si="13"/>
-        <v>2.3420195999999997E-18</v>
+        <v>1.8255279999999995E-18</v>
       </c>
       <c r="M32" s="12">
         <f t="shared" si="14"/>
-        <v>122.223438</v>
+        <v>99.304220000000001</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="3"/>
-        <v>1.2222343799999999E-17</v>
+        <v>9.9304219999999992E-18</v>
       </c>
       <c r="O32" s="12" vm="27">
         <v>115.92</v>
@@ -6491,38 +6491,38 @@
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="5"/>
-        <v>2.3400000000000045E-19</v>
+        <v>2.932000000000001E-18</v>
       </c>
       <c r="R32" s="12">
         <f t="shared" si="6"/>
-        <v>100.50438014335016</v>
+        <v>81.383328634526833</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="7"/>
-        <v>8.6434380000000033</v>
+        <v>12.704220000000007</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="8"/>
-        <v>-6.5378099283249185</v>
+        <v>-2.6083356827365805</v>
       </c>
       <c r="U32" s="14">
         <f t="shared" si="9"/>
-        <v>2.1056280716750848</v>
+        <v>10.095884317263426</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="10"/>
-        <v>158.16654599456996</v>
+        <v>262.10130185895082</v>
       </c>
       <c r="W32" s="9">
         <f t="shared" si="11"/>
-        <v>6.3224495022754764E-3</v>
+        <v>3.8153187065745582E-3</v>
       </c>
       <c r="X32" s="9">
         <f t="shared" si="12"/>
-        <v>0.9026868116032235</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.91279163134464847</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="K33" s="9">
         <f t="shared" si="2"/>
-        <v>0.17082303894350256</v>
+        <v>5.9060351201054816E-2</v>
       </c>
       <c r="L33" s="9">
         <f t="shared" si="13"/>
@@ -6602,67 +6602,67 @@
       </c>
       <c r="V33" s="12">
         <f t="shared" si="10"/>
-        <v>127.83503198272913</v>
+        <v>239.76004409269834</v>
       </c>
       <c r="W33" s="9">
         <f t="shared" si="11"/>
-        <v>7.8225818423161408E-3</v>
+        <v>4.1708367371394474E-3</v>
       </c>
       <c r="X33" s="9">
         <f t="shared" si="12"/>
-        <v>0.7295790440770421</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.83498616842587481</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>48</v>
+        <v>88</v>
+      </c>
+      <c r="B34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>90</v>
       </c>
       <c r="D34" s="8">
-        <v>45511</v>
+        <v>45627</v>
       </c>
       <c r="E34" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F34" s="1">
-        <v>20.82</v>
+        <v>133.53</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" si="0"/>
-        <v>2.0820000000000002E-18</v>
+        <v>1.3353E-17</v>
       </c>
       <c r="H34" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C34,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>1.1900000000000001E-2</v>
+        <v>4.0899999999999999E-2</v>
       </c>
       <c r="I34" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C34,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.70799999999999996</v>
+        <v>0.25</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>1.6807909604519777E-2</v>
+        <v>0.1636</v>
       </c>
       <c r="K34" s="9">
         <f t="shared" si="2"/>
-        <v>3.5870701276387159E-3</v>
+        <v>1.2071439006432665E-2</v>
       </c>
       <c r="L34" s="9">
         <f t="shared" si="13"/>
-        <v>1.474056E-18</v>
+        <v>3.3382499999999999E-18</v>
       </c>
       <c r="M34" s="12">
         <f t="shared" si="14"/>
-        <v>21.067758000000001</v>
+        <v>138.991377</v>
       </c>
       <c r="N34" s="12">
         <f t="shared" si="3"/>
-        <v>2.1067757999999999E-18</v>
+        <v>1.38991377E-17</v>
       </c>
       <c r="O34" s="12" vm="29">
         <v>22.1</v>
@@ -6673,87 +6673,87 @@
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="5"/>
-        <v>1.2800000000000001E-19</v>
+        <v>-1.1143E-17</v>
       </c>
       <c r="R34" s="12">
         <f t="shared" si="6"/>
-        <v>12.275219621484583</v>
+        <v>110.4375155074022</v>
       </c>
       <c r="S34" s="12">
         <f t="shared" si="7"/>
-        <v>0.24775800000000103</v>
+        <v>5.4613769999999988</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="8"/>
-        <v>-4.2723901892577087</v>
+        <v>-11.546242246298903</v>
       </c>
       <c r="U34" s="14">
         <f t="shared" si="9"/>
-        <v>-4.0246321892577077</v>
+        <v>-6.0848652462989037</v>
       </c>
       <c r="V34" s="12">
         <f t="shared" si="10"/>
-        <v>164.29680625550276</v>
+        <v>278.28205142251318</v>
       </c>
       <c r="W34" s="9">
         <f t="shared" si="11"/>
-        <v>6.0865455804714232E-3</v>
+        <v>3.5934764563083838E-3</v>
       </c>
       <c r="X34" s="9">
         <f t="shared" si="12"/>
-        <v>0.93767338259042421</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.96914256392586673</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D35" s="8">
-        <v>45511</v>
+        <v>45685</v>
       </c>
       <c r="E35" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F35" s="1">
-        <v>13.04</v>
+        <v>336.69</v>
       </c>
       <c r="G35" s="1">
         <f t="shared" si="0"/>
-        <v>1.304E-18</v>
+        <v>3.3669000000000002E-17</v>
       </c>
       <c r="H35" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C35,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>4.82E-2</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="I35" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C35,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.4264</v>
+        <v>0.24360000000000001</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="1"/>
-        <v>0.11303939962476547</v>
+        <v>0.70197044334975367</v>
       </c>
       <c r="K35" s="9">
         <f t="shared" si="2"/>
-        <v>2.412437139304786E-2</v>
+        <v>5.1795803124786356E-2</v>
       </c>
       <c r="L35" s="9">
         <f t="shared" si="13"/>
-        <v>5.5602559999999997E-19</v>
+        <v>8.2017684000000009E-18</v>
       </c>
       <c r="M35" s="12">
         <f t="shared" si="14"/>
-        <v>13.668528</v>
+        <v>394.26399000000004</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="3"/>
-        <v>1.3668528E-18</v>
+        <v>3.9426399E-17</v>
       </c>
       <c r="O35" s="12" vm="30">
         <v>18.28</v>
@@ -6764,87 +6764,87 @@
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="5"/>
-        <v>5.2400000000000025E-19</v>
+        <v>-3.1841000000000002E-17</v>
       </c>
       <c r="R35" s="12">
         <f t="shared" si="6"/>
-        <v>9.4616166013640974</v>
+        <v>313.90080179004286</v>
       </c>
       <c r="S35" s="12">
         <f t="shared" si="7"/>
-        <v>0.62852800000000109</v>
+        <v>57.573990000000038</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="8"/>
-        <v>-1.7891916993179509</v>
+        <v>-11.394599104978568</v>
       </c>
       <c r="U35" s="14">
         <f t="shared" si="9"/>
-        <v>-1.1606636993179498</v>
+        <v>46.17939089502147</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="10"/>
-        <v>161.43283776556299</v>
+        <v>226.01779528119278</v>
       </c>
       <c r="W35" s="9">
         <f t="shared" si="11"/>
-        <v>6.1945265525978439E-3</v>
+        <v>4.4244303806073417E-3</v>
       </c>
       <c r="X35" s="9">
         <f t="shared" si="12"/>
-        <v>0.92132816515863825</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.78712753658379164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D36" s="8">
-        <v>45511</v>
+        <v>45562</v>
       </c>
       <c r="E36" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F36" s="1">
-        <v>11.05</v>
+        <v>668.82</v>
       </c>
       <c r="G36" s="1">
         <f t="shared" si="0"/>
-        <v>1.1050000000000001E-18</v>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="H36" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-0.1055</v>
+        <v>0.16070000000000001</v>
       </c>
       <c r="I36" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.57940000000000003</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="1"/>
-        <v>-0.18208491542975491</v>
+        <v>0.58014440433212999</v>
       </c>
       <c r="K36" s="9">
         <f t="shared" si="2"/>
-        <v>-3.8859761636037014E-2</v>
+        <v>4.2806710218939593E-2</v>
       </c>
       <c r="L36" s="9">
         <f t="shared" si="13"/>
-        <v>6.4023700000000011E-19</v>
+        <v>1.8526314000000002E-17</v>
       </c>
       <c r="M36" s="12">
         <f t="shared" si="14"/>
-        <v>9.8842250000000007</v>
+        <v>776.29937400000006</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="3"/>
-        <v>9.8842250000000007E-19</v>
+        <v>7.7629937400000001E-17</v>
       </c>
       <c r="O36" s="12" vm="31">
         <v>10.79</v>
@@ -6855,960 +6855,952 @@
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>-2.6000000000000285E-20</v>
+        <v>-6.5802999999999994E-17</v>
       </c>
       <c r="R36" s="12">
         <f t="shared" si="6"/>
-        <v>6.5582527152946763</v>
+        <v>599.14001612469769</v>
       </c>
       <c r="S36" s="12">
         <f t="shared" si="7"/>
-        <v>-1.165775</v>
+        <v>107.47937400000001</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="8"/>
-        <v>-2.2458736423526622</v>
+        <v>-34.839991937651178</v>
       </c>
       <c r="U36" s="14">
         <f t="shared" si="9"/>
-        <v>-3.4116486423526622</v>
+        <v>72.63938206234883</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="10"/>
-        <v>163.68382270859772</v>
+        <v>199.55780411386542</v>
       </c>
       <c r="W36" s="9">
         <f t="shared" si="11"/>
-        <v>6.1093392337266917E-3</v>
+        <v>5.0110793934644189E-3</v>
       </c>
       <c r="X36" s="9">
         <f t="shared" si="12"/>
-        <v>0.93417496792857824</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.69497820984756919</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>81</v>
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
       </c>
       <c r="D37" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45692</v>
+        <v>45482</v>
       </c>
       <c r="E37" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>1E-4</v>
       </c>
       <c r="F37" s="1">
-        <v>2742.9</v>
+        <v>227.38</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" si="0"/>
-        <v>2.7429000000000002E-16</v>
+        <v>2.2738000000000001E-2</v>
       </c>
       <c r="H37" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>8.6599999999999996E-2</v>
+        <v>0.2092</v>
       </c>
       <c r="I37" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.14630000000000001</v>
+        <v>0.28439999999999999</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="1"/>
-        <v>0.59193438140806554</v>
+        <v>0.73558368495077353</v>
       </c>
       <c r="K37" s="9">
         <f t="shared" si="2"/>
-        <v>0.12632803168457066</v>
+        <v>5.4275999920600518E-2</v>
       </c>
       <c r="L37" s="9">
         <f t="shared" si="13"/>
-        <v>4.0128627000000008E-17</v>
+        <v>6.4666871999999997E-3</v>
       </c>
       <c r="M37" s="12">
         <f t="shared" si="14"/>
-        <v>2980.43514</v>
+        <v>274.94789600000001</v>
       </c>
       <c r="N37" s="12">
         <f t="shared" si="3"/>
-        <v>2.98043514E-16</v>
+        <v>2.7494789600000003E-2</v>
       </c>
       <c r="O37" s="12" vm="32">
         <v>0.72499999999999998</v>
       </c>
       <c r="P37" s="12">
         <f t="shared" si="4"/>
-        <v>7.2499999999999999E-20</v>
+        <v>7.25E-5</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>-2.742175E-16</v>
+        <v>-2.2665500000000002E-2</v>
       </c>
       <c r="R37" s="12">
         <f t="shared" si="6"/>
-        <v>2588.3740681324903</v>
+        <v>211.47693452380955</v>
       </c>
       <c r="S37" s="12">
         <f t="shared" si="7"/>
-        <v>237.53513999999996</v>
+        <v>47.567896000000019</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="8"/>
-        <v>-77.262965933754913</v>
+        <v>-7.9515327380952243</v>
       </c>
       <c r="U37" s="14">
         <f t="shared" si="9"/>
-        <v>160.27217406624504</v>
+        <v>39.616363261904795</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>232.58082291430946</v>
       </c>
       <c r="W37" s="9">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4.2995806252196182E-3</v>
       </c>
       <c r="X37" s="9">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.80998387746155065</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>54</v>
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D38" s="8">
-        <v>45505</v>
+        <v>45695</v>
       </c>
       <c r="E38" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F38" s="1">
-        <v>86.6</v>
+        <v>143.18</v>
       </c>
       <c r="G38" s="1">
         <f t="shared" si="0"/>
-        <v>8.6599999999999986E-18</v>
+        <v>4.2953999999999999E-2</v>
       </c>
       <c r="H38" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1467</v>
+        <v>0.1169</v>
       </c>
       <c r="I38" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.21079999999999999</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="J38" s="9">
         <f t="shared" si="1"/>
-        <v>0.6959203036053131</v>
+        <v>0.48912133891213394</v>
       </c>
       <c r="K38" s="9">
         <f t="shared" si="2"/>
-        <v>0.14852024975245023</v>
+        <v>3.6090454825320938E-2</v>
       </c>
       <c r="L38" s="9">
         <f t="shared" si="13"/>
-        <v>1.8255279999999995E-18</v>
+        <v>1.0266005999999999E-2</v>
       </c>
       <c r="M38" s="12">
         <f t="shared" si="14"/>
-        <v>99.304220000000001</v>
+        <v>159.917742</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="3"/>
-        <v>9.9304219999999992E-18</v>
+        <v>4.7975322599999995E-2</v>
       </c>
       <c r="O38" s="12" vm="33">
         <v>93.67</v>
       </c>
       <c r="P38" s="12">
         <f t="shared" si="4"/>
-        <v>9.3669999999999995E-18</v>
+        <v>2.8100999999999998E-2</v>
       </c>
       <c r="Q38" s="12">
         <f t="shared" si="5"/>
-        <v>7.0700000000000094E-19</v>
+        <v>-1.4853000000000002E-2</v>
       </c>
       <c r="R38" s="12">
         <f t="shared" si="6"/>
-        <v>81.383328634526833</v>
+        <v>127.60003564744677</v>
       </c>
       <c r="S38" s="12">
         <f t="shared" si="7"/>
-        <v>12.704220000000007</v>
+        <v>16.737741999999997</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="8"/>
-        <v>-2.6083356827365805</v>
+        <v>-7.7899821762766166</v>
       </c>
       <c r="U38" s="14">
         <f t="shared" si="9"/>
-        <v>10.095884317263426</v>
+        <v>8.9477598237233806</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="10"/>
-        <v>150.17628974898162</v>
+        <v>263.24942635249084</v>
       </c>
       <c r="W38" s="9">
         <f t="shared" si="11"/>
-        <v>6.6588407642211127E-3</v>
+        <v>3.7986787430298154E-3</v>
       </c>
       <c r="X38" s="9">
         <f t="shared" si="12"/>
-        <v>0.8570848868164832</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.91679007935697121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>74</v>
+        <v>96</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>98</v>
       </c>
       <c r="D39" s="8">
-        <v>45562</v>
+        <v>45630</v>
       </c>
       <c r="E39" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="F39" s="1">
-        <v>56</v>
+        <v>34.78</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="0"/>
-        <v>5.5999999999999995E-18</v>
+        <v>9.99925</v>
       </c>
       <c r="H39" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>4.1000000000000003E-3</v>
+        <v>-0.1268</v>
       </c>
       <c r="I39" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.4047</v>
+        <v>0.58609999999999995</v>
       </c>
       <c r="J39" s="9">
         <f t="shared" si="1"/>
-        <v>1.0130961205831481E-2</v>
+        <v>-0.2163453335608258</v>
       </c>
       <c r="K39" s="9">
         <f t="shared" si="2"/>
-        <v>2.1621051731461343E-3</v>
+        <v>-1.5963322117395103E-2</v>
       </c>
       <c r="L39" s="9">
         <f t="shared" si="13"/>
-        <v>2.2663199999999999E-18</v>
+        <v>5.8605604249999992</v>
       </c>
       <c r="M39" s="12">
         <f t="shared" si="14"/>
-        <v>56.229599999999998</v>
+        <v>30.369896000000001</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="3"/>
-        <v>5.6229599999999995E-18</v>
+        <v>8.7313450999999986</v>
       </c>
       <c r="O39" s="12" vm="34">
         <v>66.790000000000006</v>
       </c>
       <c r="P39" s="12">
         <f t="shared" si="4"/>
-        <v>6.6790000000000004E-18</v>
+        <v>19.202124999999999</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="5"/>
-        <v>1.079000000000001E-18</v>
+        <v>9.2028749999999988</v>
       </c>
       <c r="R39" s="12">
         <f t="shared" si="6"/>
-        <v>39.98286448664858</v>
+        <v>20.304746336622102</v>
       </c>
       <c r="S39" s="12">
         <f t="shared" si="7"/>
-        <v>0.22959999999999781</v>
+        <v>-4.4101040000000005</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="8"/>
-        <v>-8.0085677566757099</v>
+        <v>-7.2376268316889494</v>
       </c>
       <c r="U39" s="14">
         <f t="shared" si="9"/>
-        <v>-7.7789677566757121</v>
+        <v>-11.64773083168895</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="10"/>
-        <v>168.05114182292075</v>
+        <v>283.84491700790318</v>
       </c>
       <c r="W39" s="9">
         <f t="shared" si="11"/>
-        <v>5.9505695061192881E-3</v>
+        <v>3.5230505817800389E-3</v>
       </c>
       <c r="X39" s="9">
         <f t="shared" si="12"/>
-        <v>0.95910009569040855</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.98851574947139953</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>76</v>
+        <v>145</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="D40" s="8">
-        <v>45580</v>
+        <v>45688</v>
       </c>
       <c r="E40" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2</v>
       </c>
       <c r="F40" s="1">
-        <v>17</v>
+        <v>44.37</v>
       </c>
       <c r="G40" s="1">
         <f t="shared" si="0"/>
-        <v>1.7E-18</v>
+        <v>88.74</v>
       </c>
       <c r="H40" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>3.1099999999999999E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I40" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.1285</v>
+        <v>0.25</v>
       </c>
       <c r="J40" s="9">
         <f t="shared" si="1"/>
-        <v>0.24202334630350195</v>
+        <v>0.1</v>
       </c>
       <c r="K40" s="9">
         <f t="shared" si="2"/>
-        <v>5.1651557876239311E-2</v>
+        <v>7.3786301995309696E-3</v>
       </c>
       <c r="L40" s="9">
         <f t="shared" si="13"/>
-        <v>2.1845000000000003E-19</v>
+        <v>22.184999999999999</v>
       </c>
       <c r="M40" s="12">
         <f t="shared" si="14"/>
-        <v>17.528699999999997</v>
+        <v>45.479249999999993</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="3"/>
-        <v>1.7528699999999997E-18</v>
+        <v>90.958499999999987</v>
       </c>
       <c r="O40" s="12" vm="35">
         <v>20.470300000000002</v>
       </c>
       <c r="P40" s="12">
         <f t="shared" si="4"/>
-        <v>2.04703E-18</v>
+        <v>40.940600000000003</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>3.4702999999999996E-19</v>
+        <v>-47.799399999999991</v>
       </c>
       <c r="R40" s="12">
         <f t="shared" si="6"/>
-        <v>15.491160925824675</v>
+        <v>36.220408163265304</v>
       </c>
       <c r="S40" s="12">
         <f t="shared" si="7"/>
-        <v>0.52869999999999706</v>
+        <v>1.1092499999999959</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="8"/>
-        <v>-0.75441953708766274</v>
+        <v>-4.0747959183673466</v>
       </c>
       <c r="U40" s="14">
         <f t="shared" si="9"/>
-        <v>-0.22571953708766568</v>
+        <v>-2.9655459183673507</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="10"/>
-        <v>160.4978936033327</v>
+        <v>275.1627320945816</v>
       </c>
       <c r="W40" s="9">
         <f t="shared" si="11"/>
-        <v>6.2306113653521206E-3</v>
+        <v>3.6342130796123591E-3</v>
       </c>
       <c r="X40" s="9">
         <f t="shared" si="12"/>
-        <v>0.91599225951864482</v>
+        <v>0.95827925055110219</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" t="s">
-        <v>56</v>
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="D41" s="8">
-        <v>45574</v>
+        <v>45630</v>
       </c>
       <c r="E41" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2</v>
       </c>
       <c r="F41" s="1">
-        <v>47.42</v>
+        <v>20.5</v>
       </c>
       <c r="G41" s="1">
         <f t="shared" si="0"/>
-        <v>4.7419999999999999E-18</v>
+        <v>41</v>
       </c>
       <c r="H41" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>8.5199999999999998E-2</v>
+        <v>0.14929999999999999</v>
       </c>
       <c r="I41" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.36359999999999998</v>
+        <v>0.31569999999999998</v>
       </c>
       <c r="J41" s="9">
         <f t="shared" si="1"/>
-        <v>0.23432343234323433</v>
+        <v>0.47291732657586316</v>
       </c>
       <c r="K41" s="9">
         <f t="shared" si="2"/>
-        <v>5.0008276111751654E-2</v>
+        <v>3.4894820677541134E-2</v>
       </c>
       <c r="L41" s="9">
         <f t="shared" si="13"/>
-        <v>1.7241911999999999E-18</v>
+        <v>12.9437</v>
       </c>
       <c r="M41" s="12">
         <f t="shared" si="14"/>
-        <v>51.460183999999998</v>
+        <v>23.560649999999999</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="3"/>
-        <v>5.1460184E-18</v>
+        <v>47.121299999999998</v>
       </c>
       <c r="O41" s="12" vm="36">
         <v>46.81</v>
       </c>
       <c r="P41" s="12">
         <f t="shared" si="4"/>
-        <v>4.681E-18</v>
+        <v>93.62</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>-6.0999999999999907E-20</v>
+        <v>52.620000000000005</v>
       </c>
       <c r="R41" s="12">
         <f t="shared" si="6"/>
-        <v>37.093241551939926</v>
+        <v>17.575445816186555</v>
       </c>
       <c r="S41" s="12">
         <f t="shared" si="7"/>
-        <v>4.0401839999999964</v>
+        <v>3.060649999999999</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="8"/>
-        <v>-5.163379224030038</v>
+        <v>-1.4622770919067225</v>
       </c>
       <c r="U41" s="14">
         <f t="shared" si="9"/>
-        <v>-1.1231952240300416</v>
+        <v>1.5983729080932765</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="10"/>
-        <v>161.39536929027508</v>
+        <v>270.59881326812098</v>
       </c>
       <c r="W41" s="9">
         <f t="shared" si="11"/>
-        <v>6.195964632674595E-3</v>
+        <v>3.6955077072313575E-3</v>
       </c>
       <c r="X41" s="9">
         <f t="shared" si="12"/>
-        <v>0.92111432538436366</v>
+        <v>0.9423849879839844</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D42" s="8">
-        <v>45507</v>
+        <v>45544</v>
       </c>
       <c r="E42" s="2">
-        <v>0.52270000000000005</v>
+        <v>0.51380000000000003</v>
       </c>
       <c r="F42" s="1">
-        <v>38.229999999999997</v>
+        <v>138.53</v>
       </c>
       <c r="G42" s="1">
         <f t="shared" si="0"/>
-        <v>19.982821000000001</v>
+        <v>71.176714000000004</v>
       </c>
       <c r="H42" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C42,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>8.3500000000000005E-2</v>
+        <v>5.0200000000000002E-2</v>
       </c>
       <c r="I42" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C42,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.39029999999999998</v>
+        <v>0.2001</v>
       </c>
       <c r="J42" s="9">
         <f t="shared" ref="J42:J46" si="15">IFERROR(H42/I42,"")</f>
-        <v>0.21393799641301564</v>
+        <v>0.25087456271864067</v>
       </c>
       <c r="K42" s="9">
         <f t="shared" si="2"/>
-        <v>4.5657706053681087E-2</v>
+        <v>1.8511106247698882E-2</v>
       </c>
       <c r="L42" s="9">
         <f t="shared" si="13"/>
-        <v>7.7992950363000002</v>
+        <v>14.242460471400001</v>
       </c>
       <c r="M42" s="12">
         <f t="shared" ref="M42:M46" si="16">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
-        <v>41.422204999999991</v>
+        <v>145.484206</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="3"/>
-        <v>21.651386553499997</v>
+        <v>74.749785042799999</v>
       </c>
       <c r="O42" s="12" vm="37">
         <v>39.369999999999997</v>
       </c>
       <c r="P42" s="12">
         <f t="shared" si="4"/>
-        <v>20.578699</v>
+        <v>20.228306</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="5"/>
-        <v>0.59587799999999902</v>
+        <v>-50.948408000000001</v>
       </c>
       <c r="R42" s="12">
         <f t="shared" ref="R42:R46" si="17">F42/(1+I42-H42)</f>
-        <v>29.254667891031527</v>
+        <v>120.47134533437691</v>
       </c>
       <c r="S42" s="12">
         <f t="shared" ref="S42:S46" si="18">M42-F42</f>
-        <v>3.1922049999999942</v>
+        <v>6.9542059999999992</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" ref="T42:T46" si="19">0.5*(R42-F42)</f>
-        <v>-4.4876660544842348</v>
+        <v>-9.0293273328115475</v>
       </c>
       <c r="U42" s="14">
         <f t="shared" ref="U42:U46" si="20">S42+T42</f>
-        <v>-1.2954610544842406</v>
+        <v>-2.0751213328115483</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="10"/>
-        <v>161.56763512072928</v>
+        <v>274.27230750902578</v>
       </c>
       <c r="W42" s="9">
         <f t="shared" si="11"/>
-        <v>6.189358402459523E-3</v>
+        <v>3.6460115462699123E-3</v>
       </c>
       <c r="X42" s="9">
         <f t="shared" ref="X42:X46" si="21">V42/MAX($V$2:$V$28)</f>
-        <v>0.92209747951637722</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95517826591548871</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" t="s">
-        <v>79</v>
+        <v>91</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="D43" s="8">
-        <v>45574</v>
+        <v>45627</v>
       </c>
       <c r="E43" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.75290000000000001</v>
       </c>
       <c r="F43" s="1">
-        <v>153.7552</v>
+        <v>41.16</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" si="0"/>
-        <v>1.5375519999999999E-17</v>
+        <v>30.989363999999998</v>
       </c>
       <c r="H43" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C43,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.2700000000000001E-2</v>
+        <v>8.6900000000000005E-2</v>
       </c>
       <c r="I43" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C43,Sheet1!$G:$G,0),2),25%)</f>
-        <v>8.8400000000000006E-2</v>
+        <v>0.24529999999999999</v>
       </c>
       <c r="J43" s="9">
         <f t="shared" si="15"/>
-        <v>0.25678733031674206</v>
+        <v>0.35426008968609868</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="2"/>
-        <v>5.4802422395678896E-2</v>
+        <v>2.6139541962463975E-2</v>
       </c>
       <c r="L43" s="9">
         <f t="shared" si="13"/>
-        <v>1.359195968E-18</v>
+        <v>7.6016909891999989</v>
       </c>
       <c r="M43" s="12">
         <f t="shared" si="16"/>
-        <v>157.24544304</v>
+        <v>44.736803999999992</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="3"/>
-        <v>1.5724544303999999E-17</v>
+        <v>33.682339731599996</v>
       </c>
       <c r="O43" s="12" vm="38">
         <v>149.71</v>
       </c>
       <c r="P43" s="12">
         <f t="shared" si="4"/>
-        <v>1.4971000000000001E-17</v>
+        <v>112.71665900000001</v>
       </c>
       <c r="Q43" s="12">
         <f t="shared" si="5"/>
-        <v>-4.045199999999976E-19</v>
+        <v>81.727295000000012</v>
       </c>
       <c r="R43" s="12">
         <f t="shared" si="17"/>
-        <v>144.27625035188137</v>
+        <v>35.531767955801101</v>
       </c>
       <c r="S43" s="12">
         <f t="shared" si="18"/>
-        <v>3.4902430399999957</v>
+        <v>3.5768039999999957</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="19"/>
-        <v>-4.7394748240593145</v>
+        <v>-2.8141160220994479</v>
       </c>
       <c r="U43" s="14">
         <f t="shared" si="20"/>
-        <v>-1.2492317840593188</v>
+        <v>0.76268797790054776</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="10"/>
-        <v>161.52140585030435</v>
+        <v>271.43449819831369</v>
       </c>
       <c r="W43" s="9">
         <f t="shared" si="11"/>
-        <v>6.1911298674974706E-3</v>
+        <v>3.6841300816132317E-3</v>
       </c>
       <c r="X43" s="9">
         <f t="shared" si="21"/>
-        <v>0.92183364020408631</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.94529533678923849</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" t="s">
-        <v>89</v>
+        <v>37</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D44" s="8">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="E44" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>3.1236000000000002</v>
       </c>
       <c r="F44" s="1">
-        <v>133.53</v>
+        <v>16</v>
       </c>
       <c r="G44" s="1">
         <f t="shared" si="0"/>
-        <v>1.3353E-17</v>
+        <v>49.977600000000002</v>
       </c>
       <c r="H44" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C44,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>4.0899999999999999E-2</v>
+        <v>7.0499999999999993E-2</v>
       </c>
       <c r="I44" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C44,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
+        <v>0.35260000000000002</v>
       </c>
       <c r="J44" s="9">
         <f t="shared" si="15"/>
-        <v>0.1636</v>
+        <v>0.19994327850255245</v>
       </c>
       <c r="K44" s="9">
         <f t="shared" si="2"/>
-        <v>3.491479230254111E-2</v>
+        <v>1.4753075129521648E-2</v>
       </c>
       <c r="L44" s="9">
         <f t="shared" si="13"/>
-        <v>3.3382499999999999E-18</v>
+        <v>17.622101760000003</v>
       </c>
       <c r="M44" s="12">
         <f t="shared" si="16"/>
-        <v>138.991377</v>
+        <v>17.128</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="3"/>
-        <v>1.38991377E-17</v>
+        <v>53.501020800000006</v>
       </c>
       <c r="O44" s="12" vm="39">
         <v>145.47999999999999</v>
       </c>
       <c r="P44" s="12">
         <f t="shared" si="4"/>
-        <v>1.4548E-17</v>
+        <v>454.42132800000002</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="5"/>
-        <v>1.1950000000000002E-18</v>
+        <v>404.44372800000002</v>
       </c>
       <c r="R44" s="12">
         <f t="shared" si="17"/>
-        <v>110.4375155074022</v>
+        <v>12.479525778020435</v>
       </c>
       <c r="S44" s="12">
         <f t="shared" si="18"/>
-        <v>5.4613769999999988</v>
+        <v>1.1280000000000001</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="19"/>
-        <v>-11.546242246298903</v>
+        <v>-1.7602371109897827</v>
       </c>
       <c r="U44" s="14">
         <f t="shared" si="20"/>
-        <v>-6.0848652462989037</v>
+        <v>-0.63223711098978264</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="10"/>
-        <v>166.35703931254395</v>
+        <v>272.82942328720401</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" si="11"/>
-        <v>6.0111673310153475E-3</v>
+        <v>3.6652938233399882E-3</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" si="21"/>
-        <v>0.94943152776408135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95015329033033535</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>94</v>
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
       </c>
       <c r="D45" s="8">
-        <v>45627</v>
+        <v>45553</v>
       </c>
       <c r="E45" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>1.7345999999999999</v>
       </c>
       <c r="F45" s="1">
-        <v>26.63</v>
+        <v>51.88</v>
       </c>
       <c r="G45" s="1">
         <f t="shared" si="0"/>
-        <v>2.663E-18</v>
+        <v>89.991048000000006</v>
       </c>
       <c r="H45" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C45,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-0.1193</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="I45" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C45,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.60340000000000005</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="J45" s="9">
         <f t="shared" si="15"/>
-        <v>-0.19771295989393436</v>
+        <v>0.26017699115044246</v>
       </c>
       <c r="K45" s="9">
         <f t="shared" si="2"/>
-        <v>-4.2195030135802926E-2</v>
+        <v>1.9197498041257564E-2</v>
       </c>
       <c r="L45" s="9">
         <f t="shared" si="13"/>
-        <v>1.6068542000000001E-18</v>
+        <v>20.337976848</v>
       </c>
       <c r="M45" s="12">
         <f t="shared" si="16"/>
-        <v>23.453040999999999</v>
+        <v>54.930543999999998</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="3"/>
-        <v>2.3453040999999998E-18</v>
+        <v>95.282521622399997</v>
       </c>
       <c r="O45" s="12" vm="40">
         <v>16.010000000000002</v>
       </c>
       <c r="P45" s="12">
         <f t="shared" si="4"/>
-        <v>1.6010000000000002E-18</v>
+        <v>27.770946000000002</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>-1.0619999999999998E-18</v>
+        <v>-62.220102000000004</v>
       </c>
       <c r="R45" s="12">
         <f t="shared" si="17"/>
-        <v>15.458292215707898</v>
+        <v>44.44825222755312</v>
       </c>
       <c r="S45" s="12">
         <f t="shared" si="18"/>
-        <v>-3.1769590000000001</v>
+        <v>3.050543999999995</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="19"/>
-        <v>-5.5858538921460505</v>
+        <v>-3.7158738862234415</v>
       </c>
       <c r="U45" s="14">
         <f t="shared" si="20"/>
-        <v>-8.7628128921460515</v>
+        <v>-0.66532988622344647</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="10"/>
-        <v>169.0349869583911</v>
+        <v>272.86251606243769</v>
       </c>
       <c r="W45" s="9">
         <f t="shared" si="11"/>
-        <v>5.9159350261975977E-3</v>
+        <v>3.6648492963803621E-3</v>
       </c>
       <c r="X45" s="9">
         <f t="shared" si="21"/>
-        <v>0.96471508856304522</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.95026853893107499</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>102</v>
+        <v>37</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>28</v>
       </c>
       <c r="D46" s="8">
-        <v>45630</v>
+        <v>45511</v>
       </c>
       <c r="E46" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F46" s="1">
-        <v>323.75</v>
+        <v>501.56</v>
       </c>
       <c r="G46" s="1">
         <f t="shared" si="0"/>
-        <v>3.2375000000000002E-17</v>
+        <v>64.901863999999989</v>
       </c>
       <c r="H46" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C46,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.16109999999999999</v>
+        <v>0.1928</v>
       </c>
       <c r="I46" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C46,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.32779999999999998</v>
+        <v>0.26650000000000001</v>
       </c>
       <c r="J46" s="9">
         <f t="shared" si="15"/>
-        <v>0.49145820622330688</v>
+        <v>0.72345215759849901</v>
       </c>
       <c r="K46" s="9">
         <f t="shared" si="2"/>
-        <v>0.10488484838426758</v>
+        <v>5.3380859379721229E-2</v>
       </c>
       <c r="L46" s="9">
         <f t="shared" si="13"/>
-        <v>1.0612525E-17</v>
+        <v>17.296346755999998</v>
       </c>
       <c r="M46" s="12">
         <f t="shared" si="16"/>
-        <v>375.90612500000003</v>
+        <v>598.2607680000001</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="3"/>
-        <v>3.7590612500000005E-17</v>
+        <v>77.414943379200011</v>
       </c>
       <c r="O46" s="12" vm="41">
         <v>319.57</v>
       </c>
       <c r="P46" s="12">
         <f t="shared" si="4"/>
-        <v>3.1956999999999997E-17</v>
+        <v>41.352357999999995</v>
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="5"/>
-        <v>-4.1800000000000502E-19</v>
+        <v>-23.549505999999994</v>
       </c>
       <c r="R46" s="12">
         <f t="shared" si="17"/>
-        <v>277.49207165509563</v>
+        <v>467.13234609294966</v>
       </c>
       <c r="S46" s="12">
         <f t="shared" si="18"/>
-        <v>52.156125000000031</v>
+        <v>96.700768000000096</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="19"/>
-        <v>-23.128964172452186</v>
+        <v>-17.213826953525171</v>
       </c>
       <c r="U46" s="14">
         <f t="shared" si="20"/>
-        <v>29.027160827547846</v>
+        <v>79.486941046474925</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="10"/>
-        <v>131.2450132386972</v>
+        <v>192.71024512973932</v>
       </c>
       <c r="W46" s="9">
         <f t="shared" si="11"/>
-        <v>7.619337110974918E-3</v>
+        <v>5.1891377094495667E-3</v>
       </c>
       <c r="X46" s="9">
         <f t="shared" si="21"/>
-        <v>0.74904046108037126</v>
+        <v>0.67113096265147254</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="L47" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X46" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Asia Consumer"/>
-        <filter val="US Consumer"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:X46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="W2:W46">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Symbols">

--- a/Portfolio Expected Returns.xlsx
+++ b/Portfolio Expected Returns.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553B1C43-8D78-4619-8FF9-9CBB7F72A71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A48F86-DB0B-46C0-AC53-DF3792E6FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3712,117 +3712,117 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>136</v>
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="D2" s="8">
-        <v>45627</v>
+        <v>45484</v>
       </c>
       <c r="E2" s="2">
-        <v>1.5004999999999999</v>
+        <v>0.69389999999999996</v>
       </c>
       <c r="F2" s="1">
-        <v>40</v>
+        <v>184.36</v>
       </c>
       <c r="G2" s="1">
         <f t="shared" ref="G2:G46" si="0">E2*F2</f>
-        <v>60.019999999999996</v>
+        <v>127.927404</v>
       </c>
       <c r="H2" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>4.19E-2</v>
+        <v>0.24179999999999999</v>
       </c>
       <c r="I2" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C2,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.53510000000000002</v>
+        <v>0.32229999999999998</v>
       </c>
       <c r="J2" s="9">
         <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
-        <v>7.8303120911979066E-2</v>
+        <v>0.75023270245113249</v>
       </c>
       <c r="K2" s="9">
         <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.7776977267865372E-3</v>
+        <v>5.597082988843096E-2</v>
       </c>
       <c r="L2" s="9">
         <f>I2*G2</f>
-        <v>32.116701999999997</v>
+        <v>41.231002309199994</v>
       </c>
       <c r="M2" s="12">
         <f>IF((1+H2)*F2&lt;0,0,(1+H2)*F2)</f>
-        <v>41.676000000000002</v>
+        <v>228.93824800000002</v>
       </c>
       <c r="N2" s="12">
         <f t="shared" ref="N2:N46" si="3">M2*E2</f>
-        <v>62.534838000000001</v>
+        <v>158.86025028719999</v>
       </c>
       <c r="O2" s="12">
         <v>17.100000000000001</v>
       </c>
       <c r="P2" s="12">
         <f t="shared" ref="P2:P46" si="4">IFERROR(O2*E2,G2)</f>
-        <v>25.658550000000002</v>
+        <v>11.865690000000001</v>
       </c>
       <c r="Q2" s="12">
         <f t="shared" ref="Q2:Q46" si="5">P2-G2</f>
-        <v>-34.361449999999991</v>
+        <v>-116.06171399999999</v>
       </c>
       <c r="R2" s="12">
         <f t="shared" ref="R2:R41" si="6">F2/(1+I2-H2)</f>
-        <v>26.788106080900082</v>
+        <v>170.62471078204536</v>
       </c>
       <c r="S2" s="12">
         <f t="shared" ref="S2:S41" si="7">M2-F2</f>
-        <v>1.6760000000000019</v>
+        <v>44.578248000000002</v>
       </c>
       <c r="T2" s="12">
         <f t="shared" ref="T2:T41" si="8">0.5*(R2-F2)</f>
-        <v>-6.6059469595499589</v>
+        <v>-6.8676446089773293</v>
       </c>
       <c r="U2" s="14">
         <f t="shared" ref="U2:U41" si="9">S2+T2</f>
-        <v>-4.929946959549957</v>
+        <v>37.710603391022673</v>
       </c>
       <c r="V2" s="12">
         <f t="shared" ref="V2:V46" si="10">MAX($U$2:$U$280)-U2</f>
-        <v>277.12713313576421</v>
+        <v>122.56157067522237</v>
       </c>
       <c r="W2" s="9">
         <f t="shared" ref="W2:W46" si="11">IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V2)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>3.6084521522116758E-3</v>
+        <v>8.1591643652308768E-3</v>
       </c>
       <c r="X2" s="9">
         <f t="shared" ref="X2:X41" si="12">V2/MAX($V$2:$V$28)</f>
-        <v>0.96512045591055184</v>
+        <v>0.71289924658802684</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="D3" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E3" s="2">
-        <v>1</v>
+        <v>0.57440000000000002</v>
       </c>
       <c r="F3" s="1">
-        <v>48.68</v>
+        <v>158.26</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>48.68</v>
+        <v>90.904544000000001</v>
       </c>
       <c r="H3" s="21">
         <v>3.5000000000000003E-2</v>
@@ -3836,82 +3836,82 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>1.5651639817186903E-2</v>
+        <v>1.5825223614719039E-2</v>
       </c>
       <c r="L3" s="9">
         <f t="shared" ref="L3:L46" si="13">I3*G3</f>
-        <v>8.0321999999999996</v>
+        <v>14.999249760000001</v>
       </c>
       <c r="M3" s="12">
         <f t="shared" ref="M3:M41" si="14">IF((1+H3)*F3&lt;0,0,(1+H3)*F3)</f>
-        <v>50.383799999999994</v>
+        <v>163.79909999999998</v>
       </c>
       <c r="N3" s="12">
         <f t="shared" si="3"/>
-        <v>50.383799999999994</v>
+        <v>94.086203039999987</v>
       </c>
       <c r="O3" s="12" vm="1">
         <v>22.87</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="4"/>
-        <v>22.87</v>
+        <v>13.136528</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" si="5"/>
-        <v>-25.81</v>
+        <v>-77.768016000000003</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="6"/>
-        <v>43.079646017699112</v>
+        <v>140.05309734513273</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" si="7"/>
-        <v>1.703799999999994</v>
+        <v>5.5390999999999906</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" si="8"/>
-        <v>-2.8001769911504439</v>
+        <v>-9.1034513274336319</v>
       </c>
       <c r="U3" s="14">
         <f t="shared" si="9"/>
-        <v>-1.09637699115045</v>
+        <v>-3.5643513274336414</v>
       </c>
       <c r="V3" s="12">
         <f t="shared" si="10"/>
-        <v>273.29356316736471</v>
+        <v>163.8365253936787</v>
       </c>
       <c r="W3" s="9">
         <f t="shared" si="11"/>
-        <v>3.6590689821245481E-3</v>
+        <v>6.1036450669173124E-3</v>
       </c>
       <c r="X3" s="9">
         <f t="shared" si="12"/>
-        <v>0.95176969969335323</v>
+        <v>0.95298171256519559</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D4" s="8">
-        <v>45574</v>
+        <v>45553</v>
       </c>
       <c r="E4" s="2">
-        <v>0.16059999999999999</v>
+        <v>1.7345999999999999</v>
       </c>
       <c r="F4" s="1">
-        <v>421.18</v>
+        <v>51.88</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>67.641508000000002</v>
+        <v>89.991048000000006</v>
       </c>
       <c r="H4" s="21">
         <v>3.5000000000000003E-2</v>
@@ -3925,240 +3925,240 @@
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>1.5651639817186903E-2</v>
+        <v>1.5825223614719039E-2</v>
       </c>
       <c r="L4" s="9">
         <f t="shared" si="13"/>
-        <v>11.16084882</v>
+        <v>14.848522920000002</v>
       </c>
       <c r="M4" s="12">
         <f t="shared" si="14"/>
-        <v>435.92129999999997</v>
+        <v>53.695799999999998</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" si="3"/>
-        <v>70.008960779999995</v>
+        <v>93.140734679999994</v>
       </c>
       <c r="O4" s="12">
         <v>22.41</v>
       </c>
       <c r="P4" s="12">
         <f t="shared" si="4"/>
-        <v>3.599046</v>
+        <v>38.872385999999999</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="5"/>
-        <v>-64.042462</v>
+        <v>-51.118662000000008</v>
       </c>
       <c r="R4" s="12">
         <f t="shared" si="6"/>
-        <v>372.72566371681415</v>
+        <v>45.911504424778755</v>
       </c>
       <c r="S4" s="12">
         <f t="shared" si="7"/>
-        <v>14.741299999999967</v>
+        <v>1.8157999999999959</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="8"/>
-        <v>-24.227168141592927</v>
+        <v>-2.9842477876106237</v>
       </c>
       <c r="U4" s="14">
         <f t="shared" si="9"/>
-        <v>-9.4858681415929595</v>
+        <v>-1.1684477876106278</v>
       </c>
       <c r="V4" s="12">
         <f t="shared" si="10"/>
-        <v>281.6830543178072</v>
+        <v>161.44062185385567</v>
       </c>
       <c r="W4" s="9">
         <f t="shared" si="11"/>
-        <v>3.5500893102066266E-3</v>
+        <v>6.194227874724437E-3</v>
       </c>
       <c r="X4" s="9">
         <f t="shared" si="12"/>
-        <v>0.98098686595330931</v>
+        <v>0.93904555118094257</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>145</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
       <c r="D5" s="8">
-        <v>45484</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="2">
-        <v>0.60660000000000003</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
-        <v>186.18</v>
+        <v>44.37</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>112.93678800000001</v>
+        <v>88.74</v>
       </c>
       <c r="H5" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.24179999999999999</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I5" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C5,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.32229999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="J5" s="9">
         <f t="shared" si="1"/>
-        <v>0.75023270245113249</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>5.535689674981658E-2</v>
+        <v>7.4604625612246902E-3</v>
       </c>
       <c r="L5" s="9">
         <f t="shared" si="13"/>
-        <v>36.399526772400002</v>
+        <v>22.184999999999999</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="14"/>
-        <v>231.19832400000001</v>
+        <v>45.479249999999993</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="3"/>
-        <v>140.24490333840001</v>
+        <v>90.958499999999987</v>
       </c>
       <c r="O5" s="12" vm="2">
         <v>16.5548</v>
       </c>
       <c r="P5" s="12">
         <f t="shared" si="4"/>
-        <v>10.04214168</v>
+        <v>33.1096</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="5"/>
-        <v>-102.89464632000001</v>
+        <v>-55.630399999999995</v>
       </c>
       <c r="R5" s="12">
         <f t="shared" si="6"/>
-        <v>172.30911614993059</v>
+        <v>36.220408163265304</v>
       </c>
       <c r="S5" s="12">
         <f t="shared" si="7"/>
-        <v>45.018324000000007</v>
+        <v>1.1092499999999959</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="8"/>
-        <v>-6.9354419250347092</v>
+        <v>-4.0747959183673466</v>
       </c>
       <c r="U5" s="14">
         <f t="shared" si="9"/>
-        <v>38.082882074965298</v>
+        <v>-2.9655459183673507</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" si="10"/>
-        <v>234.11430410124893</v>
+        <v>163.2377199846124</v>
       </c>
       <c r="W5" s="9">
         <f t="shared" si="11"/>
-        <v>4.2714177753424391E-3</v>
+        <v>6.1260350860956958E-3</v>
       </c>
       <c r="X5" s="9">
         <f t="shared" si="12"/>
-        <v>0.81532436522080676</v>
+        <v>0.94949866381978243</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="D6" s="8">
-        <v>45511</v>
+        <v>45460</v>
       </c>
       <c r="E6" s="2">
-        <v>0.34489999999999998</v>
+        <v>0.51239999999999997</v>
       </c>
       <c r="F6" s="1">
-        <v>173.73</v>
+        <v>157.99</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>59.919476999999993</v>
+        <v>80.954076000000001</v>
       </c>
       <c r="H6" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),1),2.5%)+2.5%</f>
-        <v>0.14799999999999999</v>
+        <v>9.0900000000000009E-2</v>
       </c>
       <c r="I6" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C6,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.47839999999999999</v>
+        <v>0.1875</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="1"/>
-        <v>0.30936454849498329</v>
+        <v>0.48480000000000006</v>
       </c>
       <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v>2.2826866001893469E-2</v>
+        <v>3.6168322496817298E-2</v>
       </c>
       <c r="L6" s="9">
         <f t="shared" si="13"/>
-        <v>28.665477796799998</v>
+        <v>15.178889250000001</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="14"/>
-        <v>199.44203999999996</v>
+        <v>172.351291</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="3"/>
-        <v>68.78755959599998</v>
+        <v>88.3128015084</v>
       </c>
       <c r="O6" s="26">
         <v>20.52</v>
       </c>
       <c r="P6" s="12">
         <f t="shared" si="4"/>
-        <v>7.0773479999999998</v>
+        <v>10.514448</v>
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="5"/>
-        <v>-52.842128999999993</v>
+        <v>-70.439627999999999</v>
       </c>
       <c r="R6" s="12">
         <f t="shared" si="6"/>
-        <v>130.58478653036678</v>
+        <v>144.07258799927047</v>
       </c>
       <c r="S6" s="12">
         <f t="shared" si="7"/>
-        <v>25.712039999999973</v>
+        <v>14.361290999999994</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="8"/>
-        <v>-21.572606734816603</v>
+        <v>-6.9587060003647707</v>
       </c>
       <c r="U6" s="14">
         <f t="shared" si="9"/>
-        <v>4.1394332651833707</v>
+        <v>7.4025849996352235</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="10"/>
-        <v>268.05775291103089</v>
+        <v>152.86958906660982</v>
       </c>
       <c r="W6" s="9">
         <f t="shared" si="11"/>
-        <v>3.7305393675067583E-3</v>
+        <v>6.5415234390685147E-3</v>
       </c>
       <c r="X6" s="9">
         <f t="shared" si="12"/>
-        <v>0.93353551408880442</v>
+        <v>0.88919074936300113</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -4166,205 +4166,205 @@
         <v>40</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="D7" s="8">
-        <v>45511</v>
+        <v>45627</v>
       </c>
       <c r="E7" s="2">
-        <v>0.74609999999999999</v>
+        <v>3.8043</v>
       </c>
       <c r="F7" s="1">
-        <v>73.7</v>
+        <v>21.02</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>54.987569999999998</v>
+        <v>79.966386</v>
       </c>
       <c r="H7" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),1),2.5%)+8.2%</f>
-        <v>0.20319999999999999</v>
+        <v>-5.4000000000000159E-3</v>
       </c>
       <c r="I7" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C7,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24540000000000001</v>
+        <v>0.60389999999999999</v>
       </c>
       <c r="J7" s="9">
         <f t="shared" si="1"/>
-        <v>0.82803585982070083</v>
+        <v>-8.9418777943368367E-3</v>
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>6.1097704015676157E-2</v>
+        <v>-6.6710544511696377E-4</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" si="13"/>
-        <v>13.493949678</v>
+        <v>48.291700505400001</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" si="14"/>
-        <v>88.675840000000008</v>
+        <v>20.906491999999997</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="3"/>
-        <v>66.161044224000008</v>
+        <v>79.534567515599988</v>
       </c>
       <c r="O7" s="12" vm="3">
         <v>55.25</v>
       </c>
       <c r="P7" s="12">
         <f t="shared" si="4"/>
-        <v>41.222025000000002</v>
+        <v>210.18757500000001</v>
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="5"/>
-        <v>-13.765544999999996</v>
+        <v>130.22118900000001</v>
       </c>
       <c r="R7" s="12">
         <f t="shared" si="6"/>
-        <v>70.715793513720982</v>
+        <v>13.061579568756603</v>
       </c>
       <c r="S7" s="12">
         <f t="shared" si="7"/>
-        <v>14.975840000000005</v>
+        <v>-0.11350800000000305</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="8"/>
-        <v>-1.4921032431395105</v>
+        <v>-3.9792102156216984</v>
       </c>
       <c r="U7" s="14">
         <f t="shared" si="9"/>
-        <v>13.483736756860495</v>
+        <v>-4.0927182156217015</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="10"/>
-        <v>258.71344941935376</v>
+        <v>164.36489228186673</v>
       </c>
       <c r="W7" s="9">
         <f t="shared" si="11"/>
-        <v>3.8652803023745404E-3</v>
+        <v>6.0840243078498536E-3</v>
       </c>
       <c r="X7" s="9">
         <f t="shared" si="12"/>
-        <v>0.90099312697568157</v>
+        <v>0.95605504423381016</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="D8" s="8">
-        <v>45627</v>
+        <v>45544</v>
       </c>
       <c r="E8" s="2">
-        <v>3.0230999999999999</v>
+        <v>0.51380000000000003</v>
       </c>
       <c r="F8" s="1">
-        <v>21.49</v>
+        <v>138.53</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>64.966418999999988</v>
+        <v>71.176714000000004</v>
       </c>
       <c r="H8" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-8.7400000000000005E-2</v>
+        <v>5.0200000000000002E-2</v>
       </c>
       <c r="I8" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C8,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.60389999999999999</v>
+        <v>0.2001</v>
       </c>
       <c r="J8" s="9">
         <f t="shared" si="1"/>
-        <v>-0.14472594800463653</v>
+        <v>0.25087456271864067</v>
       </c>
       <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v>-1.0678792506027599E-2</v>
+        <v>1.871640282726034E-2</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="13"/>
-        <v>39.233220434099991</v>
+        <v>14.242460471400001</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="14"/>
-        <v>19.611773999999997</v>
+        <v>145.484206</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="3"/>
-        <v>59.288353979399986</v>
+        <v>74.749785042799999</v>
       </c>
       <c r="O8" s="12" vm="4">
         <v>36.380000000000003</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="4"/>
-        <v>109.980378</v>
+        <v>18.692044000000003</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="5"/>
-        <v>45.013959000000014</v>
+        <v>-52.484670000000001</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="6"/>
-        <v>12.706202329568971</v>
+        <v>120.47134533437691</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" si="7"/>
-        <v>-1.8782260000000015</v>
+        <v>6.9542059999999992</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="8"/>
-        <v>-4.3918988352155139</v>
+        <v>-9.0293273328115475</v>
       </c>
       <c r="U8" s="14">
         <f t="shared" si="9"/>
-        <v>-6.2701248352155154</v>
+        <v>-2.0751213328115483</v>
       </c>
       <c r="V8" s="12">
         <f t="shared" si="10"/>
-        <v>278.46731101142979</v>
+        <v>162.34729539905658</v>
       </c>
       <c r="W8" s="9">
         <f t="shared" si="11"/>
-        <v>3.5910857772421074E-3</v>
+        <v>6.1596344893948326E-3</v>
       </c>
       <c r="X8" s="9">
         <f t="shared" si="12"/>
-        <v>0.96978774730034856</v>
+        <v>0.94431936485446222</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D9" s="8">
-        <v>45460</v>
+        <v>45574</v>
       </c>
       <c r="E9" s="2">
-        <v>0.51239999999999997</v>
+        <v>0.16059999999999999</v>
       </c>
       <c r="F9" s="1">
-        <v>157.99</v>
+        <v>421.18</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>80.954076000000001</v>
+        <v>67.641508000000002</v>
       </c>
       <c r="H9" s="21">
         <v>6.2E-2</v>
@@ -4378,82 +4378,82 @@
       </c>
       <c r="K9" s="9">
         <f t="shared" si="2"/>
-        <v>1.7527780550609964E-2</v>
+        <v>1.7722171601376655E-2</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="13"/>
-        <v>21.129013836000002</v>
+        <v>17.654433588</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="14"/>
-        <v>167.78538000000003</v>
+        <v>447.29316000000006</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="3"/>
-        <v>85.973228712000008</v>
+        <v>71.835281496000007</v>
       </c>
       <c r="O9" s="12" vm="5">
         <v>45.69</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="4"/>
-        <v>23.411555999999997</v>
+        <v>7.3378139999999989</v>
       </c>
       <c r="Q9" s="12">
         <f t="shared" si="5"/>
-        <v>-57.542520000000003</v>
+        <v>-60.303694</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="6"/>
-        <v>131.76814011676396</v>
+        <v>351.2760633861551</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" si="7"/>
-        <v>9.7953800000000228</v>
+        <v>26.11316000000005</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="8"/>
-        <v>-13.110929941618025</v>
+        <v>-34.951968306922453</v>
       </c>
       <c r="U9" s="14">
         <f t="shared" si="9"/>
-        <v>-3.3155499416180021</v>
+        <v>-8.8388083069224024</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="10"/>
-        <v>275.51273611783222</v>
+        <v>169.11098237316745</v>
       </c>
       <c r="W9" s="9">
         <f t="shared" si="11"/>
-        <v>3.6295962723564136E-3</v>
+        <v>5.9132765120680202E-3</v>
       </c>
       <c r="X9" s="9">
         <f t="shared" si="12"/>
-        <v>0.95949817140763438</v>
+        <v>0.98366144672756672</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D10" s="8">
-        <v>45507</v>
+        <v>45511</v>
       </c>
       <c r="E10" s="2">
-        <v>0.52270000000000005</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>38.229999999999997</v>
+        <v>501.56</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>19.982821000000001</v>
+        <v>64.901863999999989</v>
       </c>
       <c r="H10" s="21">
         <v>3.7999999999999999E-2</v>
@@ -4467,82 +4467,82 @@
       </c>
       <c r="K10" s="9">
         <f t="shared" si="2"/>
-        <v>1.6591002815513421E-2</v>
+        <v>1.6775004575534803E-2</v>
       </c>
       <c r="L10" s="9">
         <f t="shared" si="13"/>
-        <v>3.3770967490000006</v>
+        <v>10.968415015999998</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="14"/>
-        <v>39.682739999999995</v>
+        <v>520.61928</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="3"/>
-        <v>20.742168197999998</v>
+        <v>67.368134831999996</v>
       </c>
       <c r="O10" s="12" vm="6">
         <v>47.963999999999999</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="4"/>
-        <v>25.070782800000003</v>
+        <v>6.2065415999999995</v>
       </c>
       <c r="Q10" s="12">
         <f t="shared" si="5"/>
-        <v>5.0879618000000022</v>
+        <v>-58.695322399999988</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="6"/>
-        <v>33.801945181255526</v>
+        <v>443.4659593280283</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" si="7"/>
-        <v>1.4527399999999986</v>
+        <v>19.059280000000001</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="8"/>
-        <v>-2.2140274093722354</v>
+        <v>-29.047020335985849</v>
       </c>
       <c r="U10" s="14">
         <f t="shared" si="9"/>
-        <v>-0.76128740937223682</v>
+        <v>-9.9877403359858477</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="10"/>
-        <v>272.95847358558649</v>
+        <v>170.25991440223089</v>
       </c>
       <c r="W10" s="9">
         <f t="shared" si="11"/>
-        <v>3.6635609324157828E-3</v>
+        <v>5.8733730926091507E-3</v>
       </c>
       <c r="X10" s="9">
         <f t="shared" si="12"/>
-        <v>0.95060271973625809</v>
+        <v>0.99034439614954051</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="D11" s="8">
-        <v>45678</v>
+        <v>45627</v>
       </c>
       <c r="E11" s="2">
-        <v>5.3800000000000001E-2</v>
+        <v>1.5004999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>185.82</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>9.9971160000000001</v>
+        <v>60.019999999999996</v>
       </c>
       <c r="H11" s="21">
         <v>3.7999999999999999E-2</v>
@@ -4556,240 +4556,240 @@
       </c>
       <c r="K11" s="9">
         <f t="shared" si="2"/>
-        <v>1.6591002815513421E-2</v>
+        <v>1.6775004575534803E-2</v>
       </c>
       <c r="L11" s="9">
         <f t="shared" si="13"/>
-        <v>1.6895126040000001</v>
+        <v>10.143380000000001</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="14"/>
-        <v>192.88115999999999</v>
+        <v>41.52</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="3"/>
-        <v>10.377006408</v>
+        <v>62.300760000000004</v>
       </c>
       <c r="O11" s="12">
         <v>51.28</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="4"/>
-        <v>2.758864</v>
+        <v>76.945639999999997</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="5"/>
-        <v>-7.2382520000000001</v>
+        <v>16.925640000000001</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="6"/>
-        <v>164.29708222811669</v>
+        <v>35.366931918656057</v>
       </c>
       <c r="S11" s="12">
         <f t="shared" si="7"/>
-        <v>7.061160000000001</v>
+        <v>1.5200000000000031</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="8"/>
-        <v>-10.76145888594165</v>
+        <v>-2.3165340406719714</v>
       </c>
       <c r="U11" s="14">
         <f t="shared" si="9"/>
-        <v>-3.700298885941649</v>
+        <v>-0.79653404067196831</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" si="10"/>
-        <v>275.89748506215591</v>
+        <v>161.068708106917</v>
       </c>
       <c r="W11" s="9">
         <f t="shared" si="11"/>
-        <v>3.6245346700957198E-3</v>
+        <v>6.2085305814721164E-3</v>
       </c>
       <c r="X11" s="9">
         <f t="shared" si="12"/>
-        <v>0.96083809461311442</v>
+        <v>0.93688225457395891</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="D12" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E12" s="2">
-        <v>2</v>
+        <v>0.74609999999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>16.399000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
-        <v>32.798000000000002</v>
+        <v>54.987569999999998</v>
       </c>
       <c r="H12" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.1212</v>
       </c>
       <c r="I12" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C12,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
+        <v>0.24540000000000001</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.49388753056234719</v>
       </c>
       <c r="K12" s="9">
         <f t="shared" si="2"/>
-        <v>7.3786301995309696E-3</v>
+        <v>3.6846294312161056E-2</v>
       </c>
       <c r="L12" s="9">
         <f t="shared" si="13"/>
-        <v>8.1995000000000005</v>
+        <v>13.493949678</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="14"/>
-        <v>16.808975</v>
+        <v>82.632440000000003</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="3"/>
-        <v>33.61795</v>
+        <v>61.652063484000003</v>
       </c>
       <c r="O12" s="12" vm="7">
         <v>70.8</v>
       </c>
       <c r="P12" s="12">
         <f t="shared" si="4"/>
-        <v>141.6</v>
+        <v>52.823879999999996</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="5"/>
-        <v>108.80199999999999</v>
+        <v>-2.1636900000000026</v>
       </c>
       <c r="R12" s="12">
         <f t="shared" si="6"/>
-        <v>13.386938775510204</v>
+        <v>65.557729941291583</v>
       </c>
       <c r="S12" s="12">
         <f t="shared" si="7"/>
-        <v>0.40997499999999931</v>
+        <v>8.9324399999999997</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="8"/>
-        <v>-1.5060306122448983</v>
+        <v>-4.0711350293542097</v>
       </c>
       <c r="U12" s="14">
         <f t="shared" si="9"/>
-        <v>-1.096055612244899</v>
+        <v>4.86130497064579</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="10"/>
-        <v>273.29324178845917</v>
+        <v>155.41086909559925</v>
       </c>
       <c r="W12" s="9">
         <f t="shared" si="11"/>
-        <v>3.6590732850029398E-3</v>
+        <v>6.4345563847587857E-3</v>
       </c>
       <c r="X12" s="9">
         <f t="shared" si="12"/>
-        <v>0.95176858046207369</v>
+        <v>0.90397251666620049</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>87</v>
       </c>
       <c r="D13" s="8">
-        <v>45580</v>
+        <v>45623</v>
       </c>
       <c r="E13" s="2">
-        <v>0.34860000000000002</v>
+        <v>3.1236000000000002</v>
       </c>
       <c r="F13" s="1">
-        <v>131.91</v>
+        <v>16</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="0"/>
-        <v>45.983826000000001</v>
+        <v>49.977600000000002</v>
       </c>
       <c r="H13" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>6.9500000000000006E-2</v>
+        <v>7.0499999999999993E-2</v>
       </c>
       <c r="I13" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C13,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25430000000000003</v>
+        <v>0.35260000000000002</v>
       </c>
       <c r="J13" s="9">
         <f t="shared" si="1"/>
-        <v>0.2732992528509634</v>
+        <v>0.19994327850255245</v>
       </c>
       <c r="K13" s="9">
         <f t="shared" si="2"/>
-        <v>2.0165741205953689E-2</v>
+        <v>1.4916693436368138E-2</v>
       </c>
       <c r="L13" s="9">
         <f t="shared" si="13"/>
-        <v>11.693686951800002</v>
+        <v>17.622101760000003</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="14"/>
-        <v>141.07774500000002</v>
+        <v>17.128</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="3"/>
-        <v>49.179701907000009</v>
+        <v>53.501020800000006</v>
       </c>
       <c r="O13" s="12" vm="8">
         <v>43.35</v>
       </c>
       <c r="P13" s="12">
         <f t="shared" si="4"/>
-        <v>15.111810000000002</v>
+        <v>135.40806000000001</v>
       </c>
       <c r="Q13" s="12">
         <f t="shared" si="5"/>
-        <v>-30.872015999999999</v>
+        <v>85.430460000000011</v>
       </c>
       <c r="R13" s="12">
         <f t="shared" si="6"/>
-        <v>111.3352464550979</v>
+        <v>12.479525778020435</v>
       </c>
       <c r="S13" s="12">
         <f t="shared" si="7"/>
-        <v>9.1677450000000249</v>
+        <v>1.1280000000000001</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="8"/>
-        <v>-10.287376772451047</v>
+        <v>-1.7602371109897827</v>
       </c>
       <c r="U13" s="14">
         <f t="shared" si="9"/>
-        <v>-1.1196317724510223</v>
+        <v>-0.63223711098978264</v>
       </c>
       <c r="V13" s="12">
         <f t="shared" si="10"/>
-        <v>273.31681794866529</v>
+        <v>160.90441117723483</v>
       </c>
       <c r="W13" s="9">
         <f t="shared" si="11"/>
-        <v>3.6587576553295791E-3</v>
+        <v>6.2148700130943493E-3</v>
       </c>
       <c r="X13" s="9">
         <f t="shared" si="12"/>
-        <v>0.95185068658509842</v>
+        <v>0.93592659484520491</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -4797,23 +4797,23 @@
         <v>145</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D14" s="8">
         <v>45481</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1">
-        <v>20.927</v>
+        <v>48.68</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="0"/>
-        <v>41.853999999999999</v>
+        <v>48.68</v>
       </c>
       <c r="H14" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C14,Sheet1!$G:$G,0),1),2.5%)+3.4%</f>
@@ -4829,1021 +4829,1021 @@
       </c>
       <c r="K14" s="9">
         <f t="shared" si="2"/>
-        <v>1.7413567270893087E-2</v>
+        <v>1.7606691644490267E-2</v>
       </c>
       <c r="L14" s="9">
         <f t="shared" si="13"/>
-        <v>10.4635</v>
+        <v>12.17</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" si="14"/>
-        <v>22.161693</v>
+        <v>51.552119999999995</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="3"/>
-        <v>44.323385999999999</v>
+        <v>51.552119999999995</v>
       </c>
       <c r="O14" s="12" vm="9">
         <v>140.04</v>
       </c>
       <c r="P14" s="12">
         <f t="shared" si="4"/>
-        <v>280.08</v>
+        <v>140.04</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="5"/>
-        <v>238.226</v>
+        <v>91.359999999999985</v>
       </c>
       <c r="R14" s="12">
         <f t="shared" si="6"/>
-        <v>17.570948782535684</v>
+        <v>40.873215785054576</v>
       </c>
       <c r="S14" s="12">
         <f t="shared" si="7"/>
-        <v>1.234693</v>
+        <v>2.8721199999999953</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="8"/>
-        <v>-1.6780256087321579</v>
+        <v>-3.9033921074727118</v>
       </c>
       <c r="U14" s="14">
         <f t="shared" si="9"/>
-        <v>-0.44333260873215785</v>
+        <v>-1.0312721074727165</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="10"/>
-        <v>272.64051878494638</v>
+        <v>161.30344617371776</v>
       </c>
       <c r="W14" s="9">
         <f t="shared" si="11"/>
-        <v>3.6678333963587446E-3</v>
+        <v>6.1994955701258694E-3</v>
       </c>
       <c r="X14" s="9">
         <f t="shared" si="12"/>
-        <v>0.94949541321350639</v>
+        <v>0.93824764659729742</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>81</v>
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
       </c>
       <c r="D15" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45697</v>
+        <v>45580</v>
       </c>
       <c r="E15" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.34860000000000002</v>
       </c>
       <c r="F15" s="1">
-        <v>2742.9</v>
+        <v>131.91</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="0"/>
-        <v>2.7429000000000002E-16</v>
+        <v>45.983826000000001</v>
       </c>
       <c r="H15" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),1),2.5%)+2.8%</f>
-        <v>0.11459999999999999</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="I15" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C15,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.14630000000000001</v>
+        <v>0.25430000000000003</v>
       </c>
       <c r="J15" s="9">
         <f t="shared" si="1"/>
-        <v>0.78332194121667797</v>
+        <v>0.38340542666142347</v>
       </c>
       <c r="K15" s="9">
         <f t="shared" si="2"/>
-        <v>5.7798429314166025E-2</v>
+        <v>2.860381831377928E-2</v>
       </c>
       <c r="L15" s="9">
         <f t="shared" si="13"/>
-        <v>4.0128627000000008E-17</v>
+        <v>11.693686951800002</v>
       </c>
       <c r="M15" s="12">
         <f t="shared" si="14"/>
-        <v>3057.2363400000004</v>
+        <v>144.77122499999999</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="3"/>
-        <v>3.0572363400000003E-16</v>
+        <v>50.467249035000002</v>
       </c>
       <c r="O15" s="12" vm="10">
         <v>153.85</v>
       </c>
       <c r="P15" s="12">
         <f t="shared" si="4"/>
-        <v>1.5384999999999999E-17</v>
+        <v>53.632110000000004</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="5"/>
-        <v>-2.5890500000000001E-16</v>
+        <v>7.6482840000000039</v>
       </c>
       <c r="R15" s="12">
         <f t="shared" si="6"/>
-        <v>2658.621692352428</v>
+        <v>114.03008298755186</v>
       </c>
       <c r="S15" s="12">
         <f t="shared" si="7"/>
-        <v>314.33634000000029</v>
+        <v>12.86122499999999</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="8"/>
-        <v>-42.139153823786046</v>
+        <v>-8.9399585062240661</v>
       </c>
       <c r="U15" s="14">
         <f t="shared" si="9"/>
-        <v>272.19718617621425</v>
+        <v>3.9212664937759243</v>
       </c>
       <c r="V15" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>156.35090757246911</v>
       </c>
       <c r="W15" s="9">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>6.3958694933478211E-3</v>
       </c>
       <c r="X15" s="9">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.90944040287418759</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
+        <v>145</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="D16" s="8">
-        <v>45544</v>
+        <v>45481</v>
       </c>
       <c r="E16" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1">
-        <v>188.12</v>
+        <v>20.927</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="0"/>
-        <v>1.8812000000000001E-17</v>
+        <v>41.853999999999999</v>
       </c>
       <c r="H16" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1164</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I16" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C16,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.3664</v>
+        <v>0.25</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>0.31768558951965065</v>
+        <v>0.1</v>
       </c>
       <c r="K16" s="9">
         <f t="shared" si="2"/>
-        <v>2.3440844847854934E-2</v>
+        <v>7.4604625612246902E-3</v>
       </c>
       <c r="L16" s="9">
         <f t="shared" si="13"/>
-        <v>6.8927168000000004E-18</v>
+        <v>10.4635</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" si="14"/>
-        <v>210.01716800000003</v>
+        <v>21.450174999999998</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="3"/>
-        <v>2.1001716800000003E-17</v>
+        <v>42.900349999999996</v>
       </c>
       <c r="O16" s="12" vm="11">
         <v>191.65</v>
       </c>
       <c r="P16" s="12">
         <f t="shared" si="4"/>
-        <v>1.9164999999999999E-17</v>
+        <v>383.3</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="5"/>
-        <v>3.5299999999999804E-19</v>
+        <v>341.44600000000003</v>
       </c>
       <c r="R16" s="12">
         <f t="shared" si="6"/>
-        <v>150.49600000000001</v>
+        <v>17.083265306122449</v>
       </c>
       <c r="S16" s="12">
         <f t="shared" si="7"/>
-        <v>21.897168000000022</v>
+        <v>0.52317499999999839</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="8"/>
-        <v>-18.811999999999998</v>
+        <v>-1.9218673469387753</v>
       </c>
       <c r="U16" s="14">
         <f t="shared" si="9"/>
-        <v>3.0851680000000243</v>
+        <v>-1.3986923469387769</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="10"/>
-        <v>269.11201817621424</v>
+        <v>161.67086641318383</v>
       </c>
       <c r="W16" s="9">
         <f t="shared" si="11"/>
-        <v>3.715924717064108E-3</v>
+        <v>6.185406326977244E-3</v>
       </c>
       <c r="X16" s="9">
         <f t="shared" si="12"/>
-        <v>0.9372070887984737</v>
+        <v>0.94038480598954</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="D17" s="8">
-        <v>45482</v>
+        <v>45630</v>
       </c>
       <c r="E17" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1">
-        <v>147.01</v>
+        <v>20.5</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="0"/>
-        <v>1.4700999999999999E-17</v>
+        <v>41</v>
       </c>
       <c r="H17" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),1),2.5%)+2.6%</f>
-        <v>0.57689999999999997</v>
+        <v>0.17529999999999998</v>
       </c>
       <c r="I17" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C17,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.48780000000000001</v>
+        <v>0.31569999999999998</v>
       </c>
       <c r="J17" s="9">
         <f t="shared" si="1"/>
-        <v>1.1826568265682655</v>
+        <v>0.55527399429838453</v>
       </c>
       <c r="K17" s="9">
         <f t="shared" si="2"/>
-        <v>8.7263873761980637E-2</v>
+        <v>4.1426008456847893E-2</v>
       </c>
       <c r="L17" s="9">
         <f t="shared" si="13"/>
-        <v>7.1711477999999992E-18</v>
+        <v>12.9437</v>
       </c>
       <c r="M17" s="12">
         <f t="shared" si="14"/>
-        <v>231.82006899999999</v>
+        <v>24.09365</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="3"/>
-        <v>2.3182006899999998E-17</v>
+        <v>48.1873</v>
       </c>
       <c r="O17" s="12" vm="12">
         <v>130.30000000000001</v>
       </c>
       <c r="P17" s="12">
         <f t="shared" si="4"/>
-        <v>1.3030000000000001E-17</v>
+        <v>260.60000000000002</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="5"/>
-        <v>-1.6709999999999983E-18</v>
+        <v>219.60000000000002</v>
       </c>
       <c r="R17" s="12">
         <f t="shared" si="6"/>
-        <v>161.38983422988252</v>
+        <v>17.976148719747457</v>
       </c>
       <c r="S17" s="12">
         <f t="shared" si="7"/>
-        <v>84.810068999999999</v>
+        <v>3.5936500000000002</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="8"/>
-        <v>7.1899171149412666</v>
+        <v>-1.2619256401262717</v>
       </c>
       <c r="U17" s="14">
         <f t="shared" si="9"/>
-        <v>91.999986114941265</v>
+        <v>2.3317243598737285</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="10"/>
-        <v>180.19720006127298</v>
+        <v>157.94044970637131</v>
       </c>
       <c r="W17" s="9">
         <f t="shared" si="11"/>
-        <v>5.5494757946292564E-3</v>
+        <v>6.3315002702544546E-3</v>
       </c>
       <c r="X17" s="9">
         <f t="shared" si="12"/>
-        <v>0.62755314468519197</v>
+        <v>0.91868623240652636</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>102</v>
+        <v>153</v>
+      </c>
+      <c r="C18" t="s">
+        <v>147</v>
       </c>
       <c r="D18" s="8">
-        <v>45630</v>
+        <v>45481</v>
       </c>
       <c r="E18" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2</v>
       </c>
       <c r="F18" s="1">
-        <v>323.75</v>
+        <v>16.399000000000001</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="0"/>
-        <v>3.2375000000000002E-17</v>
+        <v>32.798000000000002</v>
       </c>
       <c r="H18" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.16109999999999999</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I18" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C18,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.32779999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="J18" s="9">
         <f t="shared" si="1"/>
-        <v>0.49145820622330688</v>
+        <v>0.1</v>
       </c>
       <c r="K18" s="9">
         <f t="shared" si="2"/>
-        <v>3.6262883622466109E-2</v>
+        <v>7.4604625612246902E-3</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="13"/>
-        <v>1.0612525E-17</v>
+        <v>8.1995000000000005</v>
       </c>
       <c r="M18" s="12">
         <f t="shared" si="14"/>
-        <v>375.90612500000003</v>
+        <v>16.808975</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="3"/>
-        <v>3.7590612500000005E-17</v>
+        <v>33.61795</v>
       </c>
       <c r="O18" s="12" vm="13">
         <v>35.47</v>
       </c>
       <c r="P18" s="12">
         <f t="shared" si="4"/>
-        <v>3.5469999999999997E-18</v>
+        <v>70.94</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>-2.8828000000000001E-17</v>
+        <v>38.141999999999996</v>
       </c>
       <c r="R18" s="12">
         <f t="shared" si="6"/>
-        <v>277.49207165509563</v>
+        <v>13.386938775510204</v>
       </c>
       <c r="S18" s="12">
         <f t="shared" si="7"/>
-        <v>52.156125000000031</v>
+        <v>0.40997499999999931</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="8"/>
-        <v>-23.128964172452186</v>
+        <v>-1.5060306122448983</v>
       </c>
       <c r="U18" s="14">
         <f t="shared" si="9"/>
-        <v>29.027160827547846</v>
+        <v>-1.096055612244899</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="10"/>
-        <v>243.1700253486664</v>
+        <v>161.36822967848994</v>
       </c>
       <c r="W18" s="9">
         <f t="shared" si="11"/>
-        <v>4.112348956521932E-3</v>
+        <v>6.1970066969960569E-3</v>
       </c>
       <c r="X18" s="9">
         <f t="shared" si="12"/>
-        <v>0.84686173841127221</v>
+        <v>0.9386244703560741</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="D19" s="8">
-        <v>45481</v>
+        <v>45627</v>
       </c>
       <c r="E19" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.75290000000000001</v>
       </c>
       <c r="F19" s="1">
-        <v>169.34</v>
+        <v>41.16</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="0"/>
-        <v>1.6933999999999999E-17</v>
+        <v>30.989363999999998</v>
       </c>
       <c r="H19" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.21429999999999999</v>
+        <v>8.6900000000000005E-2</v>
       </c>
       <c r="I19" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C19,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.40479999999999999</v>
+        <v>0.24529999999999999</v>
       </c>
       <c r="J19" s="9">
         <f t="shared" si="1"/>
-        <v>0.52939723320158105</v>
+        <v>0.35426008968609868</v>
       </c>
       <c r="K19" s="9">
         <f t="shared" si="2"/>
-        <v>3.9062264124493248E-2</v>
+        <v>2.6429441360392398E-2</v>
       </c>
       <c r="L19" s="9">
         <f t="shared" si="13"/>
-        <v>6.8548831999999995E-18</v>
+        <v>7.6016909891999989</v>
       </c>
       <c r="M19" s="12">
         <f t="shared" si="14"/>
-        <v>205.62956199999999</v>
+        <v>44.736803999999992</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="3"/>
-        <v>2.0562956199999998E-17</v>
+        <v>33.682339731599996</v>
       </c>
       <c r="O19" s="12" vm="14">
         <v>152.91</v>
       </c>
       <c r="P19" s="12">
         <f t="shared" si="4"/>
-        <v>1.5291E-17</v>
+        <v>115.125939</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="5"/>
-        <v>-1.6429999999999997E-18</v>
+        <v>84.136575000000008</v>
       </c>
       <c r="R19" s="12">
         <f t="shared" si="6"/>
-        <v>142.2427551448971</v>
+        <v>35.531767955801101</v>
       </c>
       <c r="S19" s="12">
         <f t="shared" si="7"/>
-        <v>36.289561999999989</v>
+        <v>3.5768039999999957</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="8"/>
-        <v>-13.54862242755145</v>
+        <v>-2.8141160220994479</v>
       </c>
       <c r="U19" s="14">
         <f t="shared" si="9"/>
-        <v>22.740939572448539</v>
+        <v>0.76268797790054776</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="10"/>
-        <v>249.45624660376569</v>
+        <v>159.50948608834449</v>
       </c>
       <c r="W19" s="9">
         <f t="shared" si="11"/>
-        <v>4.0087190183230488E-3</v>
+        <v>6.269219621497301E-3</v>
       </c>
       <c r="X19" s="9">
         <f t="shared" si="12"/>
-        <v>0.86875407589200471</v>
+        <v>0.92781278690819791</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>94</v>
+        <v>36</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
       </c>
       <c r="D20" s="8">
-        <v>45627</v>
+        <v>45678</v>
       </c>
       <c r="E20" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.1782</v>
       </c>
       <c r="F20" s="1">
-        <v>26.63</v>
+        <v>168.24</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="0"/>
-        <v>2.663E-18</v>
+        <v>29.980368000000002</v>
       </c>
       <c r="H20" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-0.1193</v>
+        <v>0.1925</v>
       </c>
       <c r="I20" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C20,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.60340000000000005</v>
+        <v>0.28539999999999999</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>-0.19771295989393436</v>
+        <v>0.6744919411352488</v>
       </c>
       <c r="K20" s="9">
         <f t="shared" si="2"/>
-        <v>-1.4588508167120394E-2</v>
+        <v>5.0320218746872904E-2</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" si="13"/>
-        <v>1.6068542000000001E-18</v>
+        <v>8.5563970272000009</v>
       </c>
       <c r="M20" s="12">
         <f t="shared" si="14"/>
-        <v>23.453040999999999</v>
+        <v>200.62619999999998</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="3"/>
-        <v>2.3453040999999998E-18</v>
+        <v>35.751588839999997</v>
       </c>
       <c r="O20" s="12" vm="15">
         <v>404</v>
       </c>
       <c r="P20" s="12">
         <f t="shared" si="4"/>
-        <v>4.0400000000000001E-17</v>
+        <v>71.992800000000003</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="5"/>
-        <v>3.7737000000000002E-17</v>
+        <v>42.012432000000004</v>
       </c>
       <c r="R20" s="12">
         <f t="shared" si="6"/>
-        <v>15.458292215707898</v>
+        <v>153.93906121328573</v>
       </c>
       <c r="S20" s="12">
         <f t="shared" si="7"/>
-        <v>-3.1769590000000001</v>
+        <v>32.386199999999974</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="8"/>
-        <v>-5.5858538921460505</v>
+        <v>-7.1504693933571417</v>
       </c>
       <c r="U20" s="14">
         <f t="shared" si="9"/>
-        <v>-8.7628128921460515</v>
+        <v>25.235730606642832</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="10"/>
-        <v>280.95999906836028</v>
+        <v>135.0364434596022</v>
       </c>
       <c r="W20" s="9">
         <f t="shared" si="11"/>
-        <v>3.5592255243305664E-3</v>
+        <v>7.4054083059375171E-3</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="12"/>
-        <v>0.97846876025900742</v>
+        <v>0.78546136667403987</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
       </c>
       <c r="D21" s="8">
-        <v>45511</v>
+        <v>45507</v>
       </c>
       <c r="E21" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.52270000000000005</v>
       </c>
       <c r="F21" s="1">
-        <v>10.92</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="0"/>
-        <v>1.092E-18</v>
+        <v>19.982821000000001</v>
       </c>
       <c r="H21" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-1.4844999999999999</v>
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="I21" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C21,Sheet1!$G:$G,0),2),25%)</f>
-        <v>1.3212999999999999</v>
+        <v>0.39029999999999998</v>
       </c>
       <c r="J21" s="9">
         <f t="shared" si="1"/>
-        <v>-1.1235147203511693</v>
+        <v>0.21393799641301564</v>
       </c>
       <c r="K21" s="9">
         <f t="shared" si="2"/>
-        <v>-8.2899996452007296E-2</v>
+        <v>1.5960764126627249E-2</v>
       </c>
       <c r="L21" s="9">
         <f t="shared" si="13"/>
-        <v>1.4428596E-18</v>
+        <v>7.7992950363000002</v>
       </c>
       <c r="M21" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>41.422204999999991</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>21.651386553499997</v>
       </c>
       <c r="O21" s="12" vm="16">
         <v>559</v>
       </c>
       <c r="P21" s="12">
         <f t="shared" si="4"/>
-        <v>5.5899999999999994E-17</v>
+        <v>292.1893</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="5"/>
-        <v>5.4807999999999994E-17</v>
+        <v>272.206479</v>
       </c>
       <c r="R21" s="12">
         <f t="shared" si="6"/>
-        <v>2.8693047453886176</v>
+        <v>29.254667891031527</v>
       </c>
       <c r="S21" s="12">
         <f t="shared" si="7"/>
-        <v>-10.92</v>
+        <v>3.1922049999999942</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="8"/>
-        <v>-4.025347627305691</v>
+        <v>-4.4876660544842348</v>
       </c>
       <c r="U21" s="14">
         <f t="shared" si="9"/>
-        <v>-14.94534762730569</v>
+        <v>-1.2954610544842406</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="10"/>
-        <v>287.14253380351994</v>
+        <v>161.56763512072928</v>
       </c>
       <c r="W21" s="9">
         <f t="shared" si="11"/>
-        <v>3.4825909862739443E-3</v>
+        <v>6.1893584024595221E-3</v>
       </c>
       <c r="X21" s="9">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.93978434444021652</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
+        <v>97</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>98</v>
       </c>
       <c r="D22" s="8">
-        <v>45574</v>
+        <v>45630</v>
       </c>
       <c r="E22" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="F22" s="1">
-        <v>153.7552</v>
+        <v>34.78</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="0"/>
-        <v>1.5375519999999999E-17</v>
+        <v>9.99925</v>
       </c>
       <c r="H22" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.2700000000000001E-2</v>
+        <v>-0.1268</v>
       </c>
       <c r="I22" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C22,Sheet1!$G:$G,0),2),25%)</f>
-        <v>8.8400000000000006E-2</v>
+        <v>0.58609999999999995</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>0.25678733031674206</v>
+        <v>-0.2163453335608258</v>
       </c>
       <c r="K22" s="9">
         <f t="shared" si="2"/>
-        <v>1.8947387503320475E-2</v>
+        <v>-1.6140362613262082E-2</v>
       </c>
       <c r="L22" s="9">
         <f t="shared" si="13"/>
-        <v>1.359195968E-18</v>
+        <v>5.8605604249999992</v>
       </c>
       <c r="M22" s="12">
         <f t="shared" si="14"/>
-        <v>157.24544304</v>
+        <v>30.369896000000001</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="3"/>
-        <v>1.5724544303999999E-17</v>
+        <v>8.7313450999999986</v>
       </c>
       <c r="O22" s="12" vm="17">
         <v>179.25</v>
       </c>
       <c r="P22" s="12">
         <f t="shared" si="4"/>
-        <v>1.7925E-17</v>
+        <v>51.534374999999997</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="5"/>
-        <v>2.5494800000000007E-18</v>
+        <v>41.535124999999994</v>
       </c>
       <c r="R22" s="12">
         <f t="shared" si="6"/>
-        <v>144.27625035188137</v>
+        <v>20.304746336622102</v>
       </c>
       <c r="S22" s="12">
         <f t="shared" si="7"/>
-        <v>3.4902430399999957</v>
+        <v>-4.4101040000000005</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="8"/>
-        <v>-4.7394748240593145</v>
+        <v>-7.2376268316889494</v>
       </c>
       <c r="U22" s="14">
         <f t="shared" si="9"/>
-        <v>-1.2492317840593188</v>
+        <v>-11.64773083168895</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="10"/>
-        <v>273.44641796027355</v>
+        <v>171.919904897934</v>
       </c>
       <c r="W22" s="9">
         <f t="shared" si="11"/>
-        <v>3.6570235860441244E-3</v>
+        <v>5.8166621287609683E-3</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" si="12"/>
-        <v>0.9523020304173464</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D23" s="8">
-        <v>45511</v>
+        <v>45695</v>
       </c>
       <c r="E23" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F23" s="1">
-        <v>11.05</v>
+        <v>143.18</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="0"/>
-        <v>1.1050000000000001E-18</v>
+        <v>4.2953999999999999E-2</v>
       </c>
       <c r="H23" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-0.1055</v>
+        <v>0.1169</v>
       </c>
       <c r="I23" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C23,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.57940000000000003</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>-0.18208491542975491</v>
+        <v>0.48912133891213394</v>
       </c>
       <c r="K23" s="9">
         <f t="shared" si="2"/>
-        <v>-1.3435372558690322E-2</v>
+        <v>3.6490714368500682E-2</v>
       </c>
       <c r="L23" s="9">
         <f t="shared" si="13"/>
-        <v>6.4023700000000011E-19</v>
+        <v>1.0266005999999999E-2</v>
       </c>
       <c r="M23" s="12">
         <f t="shared" si="14"/>
-        <v>9.8842250000000007</v>
+        <v>159.917742</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="3"/>
-        <v>9.8842250000000007E-19</v>
+        <v>4.7975322599999995E-2</v>
       </c>
       <c r="O23" s="12" vm="18">
         <v>150.22999999999999</v>
       </c>
       <c r="P23" s="12">
         <f t="shared" si="4"/>
-        <v>1.5022999999999998E-17</v>
+        <v>4.5068999999999991E-2</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="5"/>
-        <v>1.3917999999999996E-17</v>
+        <v>2.1149999999999919E-3</v>
       </c>
       <c r="R23" s="12">
         <f t="shared" si="6"/>
-        <v>6.5582527152946763</v>
+        <v>127.60003564744677</v>
       </c>
       <c r="S23" s="12">
         <f t="shared" si="7"/>
-        <v>-1.165775</v>
+        <v>16.737741999999997</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="8"/>
-        <v>-2.2458736423526622</v>
+        <v>-7.7899821762766166</v>
       </c>
       <c r="U23" s="14">
         <f t="shared" si="9"/>
-        <v>-3.4116486423526622</v>
+        <v>8.9477598237233806</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="10"/>
-        <v>275.60883481856689</v>
+        <v>151.32441424252167</v>
       </c>
       <c r="W23" s="9">
         <f t="shared" si="11"/>
-        <v>3.6283307124689939E-3</v>
+        <v>6.6083189880870082E-3</v>
       </c>
       <c r="X23" s="9">
         <f t="shared" si="12"/>
-        <v>0.95983284387660561</v>
+        <v>0.88020298948141262</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>149</v>
+        <v>36</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="D24" s="8">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="E24" s="2">
-        <v>1</v>
+        <v>1E-4</v>
       </c>
       <c r="F24" s="1">
-        <v>51.28</v>
+        <v>227.38</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>51.28</v>
+        <v>2.2738000000000001E-2</v>
       </c>
       <c r="H24" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.2092</v>
       </c>
       <c r="I24" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C24,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
+        <v>0.28439999999999999</v>
       </c>
       <c r="J24" s="9">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.73558368495077353</v>
       </c>
       <c r="K24" s="9">
         <f t="shared" si="2"/>
-        <v>7.3786301995309696E-3</v>
+        <v>5.4877945422229429E-2</v>
       </c>
       <c r="L24" s="9">
         <f t="shared" si="13"/>
-        <v>12.82</v>
+        <v>6.4666871999999997E-3</v>
       </c>
       <c r="M24" s="12">
         <f t="shared" si="14"/>
-        <v>52.561999999999998</v>
+        <v>274.94789600000001</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="3"/>
-        <v>52.561999999999998</v>
+        <v>2.7494789600000003E-2</v>
       </c>
       <c r="O24" s="12" vm="19">
         <v>247.1</v>
       </c>
       <c r="P24" s="12">
         <f t="shared" si="4"/>
-        <v>247.1</v>
+        <v>2.4709999999999999E-2</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="5"/>
-        <v>195.82</v>
+        <v>1.9719999999999981E-3</v>
       </c>
       <c r="R24" s="12">
         <f t="shared" si="6"/>
-        <v>41.861224489795916</v>
+        <v>211.47693452380955</v>
       </c>
       <c r="S24" s="12">
         <f t="shared" si="7"/>
-        <v>1.2819999999999965</v>
+        <v>47.567896000000019</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="8"/>
-        <v>-4.7093877551020427</v>
+        <v>-7.9515327380952243</v>
       </c>
       <c r="U24" s="14">
         <f t="shared" si="9"/>
-        <v>-3.4273877551020462</v>
+        <v>39.616363261904795</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="10"/>
-        <v>275.62457393131626</v>
+        <v>120.65581080434025</v>
       </c>
       <c r="W24" s="9">
         <f t="shared" si="11"/>
-        <v>3.6281235222850382E-3</v>
+        <v>8.2880384569429116E-3</v>
       </c>
       <c r="X24" s="9">
         <f t="shared" si="12"/>
-        <v>0.9598876567687985</v>
+        <v>0.70181408532055434</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D25" s="8">
-        <v>45511</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45718</v>
       </c>
       <c r="E25" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>20.82</v>
+        <v>2742.9</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="0"/>
-        <v>2.0820000000000002E-18</v>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="H25" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>1.1900000000000001E-2</v>
+        <v>8.6599999999999996E-2</v>
       </c>
       <c r="I25" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C25,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.70799999999999996</v>
+        <v>0.14630000000000001</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>1.6807909604519777E-2</v>
+        <v>0.59193438140806554</v>
       </c>
       <c r="K25" s="9">
         <f t="shared" si="2"/>
-        <v>1.2401934939889627E-3</v>
+        <v>4.4161042911965688E-2</v>
       </c>
       <c r="L25" s="9">
         <f t="shared" si="13"/>
-        <v>1.474056E-18</v>
+        <v>4.0128627000000008E-17</v>
       </c>
       <c r="M25" s="12">
         <f t="shared" si="14"/>
-        <v>21.067758000000001</v>
+        <v>2980.43514</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="3"/>
-        <v>2.1067757999999999E-18</v>
+        <v>2.98043514E-16</v>
       </c>
       <c r="O25" s="12" vm="20">
         <v>5.09</v>
@@ -5854,87 +5854,87 @@
       </c>
       <c r="Q25" s="12">
         <f t="shared" si="5"/>
-        <v>-1.5730000000000002E-18</v>
+        <v>-2.73781E-16</v>
       </c>
       <c r="R25" s="12">
         <f t="shared" si="6"/>
-        <v>12.275219621484583</v>
+        <v>2588.3740681324903</v>
       </c>
       <c r="S25" s="12">
         <f t="shared" si="7"/>
-        <v>0.24775800000000103</v>
+        <v>237.53513999999996</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="8"/>
-        <v>-4.2723901892577087</v>
+        <v>-77.262965933754913</v>
       </c>
       <c r="U25" s="14">
         <f t="shared" si="9"/>
-        <v>-4.0246321892577077</v>
+        <v>160.27217406624504</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="10"/>
-        <v>276.22181836547196</v>
+        <v>0</v>
       </c>
       <c r="W25" s="9">
         <f t="shared" si="11"/>
-        <v>3.6202788248859094E-3</v>
+        <v>0</v>
       </c>
       <c r="X25" s="9">
         <f t="shared" si="12"/>
-        <v>0.96196761485179139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>57</v>
+        <v>36</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D26" s="8">
-        <v>45574</v>
+        <v>45481</v>
       </c>
       <c r="E26" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>47.42</v>
+        <v>700.32</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="0"/>
-        <v>4.7419999999999999E-18</v>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="H26" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>8.5199999999999998E-2</v>
+        <v>0.2051</v>
       </c>
       <c r="I26" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C26,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.36359999999999998</v>
+        <v>0.36940000000000001</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>0.23432343234323433</v>
+        <v>0.55522468868435304</v>
       </c>
       <c r="K26" s="9">
         <f t="shared" si="2"/>
-        <v>1.7289859543455407E-2</v>
+        <v>4.142233002997249E-2</v>
       </c>
       <c r="L26" s="9">
         <f t="shared" si="13"/>
-        <v>1.7241911999999999E-18</v>
+        <v>2.5869820800000001E-17</v>
       </c>
       <c r="M26" s="12">
         <f t="shared" si="14"/>
-        <v>51.460183999999998</v>
+        <v>843.95563200000015</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="3"/>
-        <v>5.1460184E-18</v>
+        <v>8.4395563200000012E-17</v>
       </c>
       <c r="O26" s="12" vm="21">
         <v>349.86</v>
@@ -5945,87 +5945,87 @@
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="5"/>
-        <v>3.0244E-17</v>
+        <v>-3.5045999999999997E-17</v>
       </c>
       <c r="R26" s="12">
         <f t="shared" si="6"/>
-        <v>37.093241551939926</v>
+        <v>601.49446019067261</v>
       </c>
       <c r="S26" s="12">
         <f t="shared" si="7"/>
-        <v>4.0401839999999964</v>
+        <v>143.6356320000001</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="8"/>
-        <v>-5.163379224030038</v>
+        <v>-49.412769904663719</v>
       </c>
       <c r="U26" s="14">
         <f t="shared" si="9"/>
-        <v>-1.1231952240300416</v>
+        <v>94.222862095336382</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="10"/>
-        <v>273.32038140024429</v>
+        <v>66.049311970908661</v>
       </c>
       <c r="W26" s="9">
         <f t="shared" si="11"/>
-        <v>3.6587099537799279E-3</v>
+        <v>1.5140203132478484E-2</v>
       </c>
       <c r="X26" s="9">
         <f t="shared" si="12"/>
-        <v>0.95186309662944746</v>
+        <v>0.38418653157190286</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>76</v>
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="D27" s="8">
-        <v>45580</v>
+        <v>45562</v>
       </c>
       <c r="E27" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F27" s="1">
-        <v>17</v>
+        <v>668.82</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="0"/>
-        <v>1.7E-18</v>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="H27" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>3.1099999999999999E-2</v>
+        <v>0.16070000000000001</v>
       </c>
       <c r="I27" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C27,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.1285</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="J27" s="9">
         <f t="shared" si="1"/>
-        <v>0.24202334630350195</v>
+        <v>0.58014440433212999</v>
       </c>
       <c r="K27" s="9">
         <f t="shared" si="2"/>
-        <v>1.7858007720265613E-2</v>
+        <v>4.328145608623854E-2</v>
       </c>
       <c r="L27" s="9">
         <f t="shared" si="13"/>
-        <v>2.1845000000000003E-19</v>
+        <v>1.8526314000000002E-17</v>
       </c>
       <c r="M27" s="12">
         <f t="shared" si="14"/>
-        <v>17.528699999999997</v>
+        <v>776.29937400000006</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="3"/>
-        <v>1.7528699999999997E-18</v>
+        <v>7.7629937400000001E-17</v>
       </c>
       <c r="O27" s="12" vm="22">
         <v>161.1</v>
@@ -6036,87 +6036,87 @@
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="5"/>
-        <v>1.441E-17</v>
+        <v>-5.0772000000000001E-17</v>
       </c>
       <c r="R27" s="12">
         <f t="shared" si="6"/>
-        <v>15.491160925824675</v>
+        <v>599.14001612469769</v>
       </c>
       <c r="S27" s="12">
         <f t="shared" si="7"/>
-        <v>0.52869999999999706</v>
+        <v>107.47937400000001</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="8"/>
-        <v>-0.75441953708766274</v>
+        <v>-34.839991937651178</v>
       </c>
       <c r="U27" s="14">
         <f t="shared" si="9"/>
-        <v>-0.22571953708766568</v>
+        <v>72.63938206234883</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="10"/>
-        <v>272.42290571330193</v>
+        <v>87.632792003896213</v>
       </c>
       <c r="W27" s="9">
         <f t="shared" si="11"/>
-        <v>3.6707632839523439E-3</v>
+        <v>1.1411253449000453E-2</v>
       </c>
       <c r="X27" s="9">
         <f t="shared" si="12"/>
-        <v>0.94873755589170206</v>
+        <v>0.50973034248665006</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
       </c>
       <c r="D28" s="8">
-        <v>45511</v>
+        <v>45685</v>
       </c>
       <c r="E28" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F28" s="1">
-        <v>113.58</v>
+        <v>336.69</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="0"/>
-        <v>1.1357999999999999E-17</v>
+        <v>3.3669000000000002E-17</v>
       </c>
       <c r="H28" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>7.6100000000000001E-2</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="I28" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C28,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.20619999999999999</v>
+        <v>0.24360000000000001</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>0.36905916585838994</v>
+        <v>0.70197044334975367</v>
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
-        <v>2.7231511066164248E-2</v>
+        <v>5.237024211697134E-2</v>
       </c>
       <c r="L28" s="9">
         <f t="shared" si="13"/>
-        <v>2.3420195999999997E-18</v>
+        <v>8.2017684000000009E-18</v>
       </c>
       <c r="M28" s="12">
         <f t="shared" si="14"/>
-        <v>122.223438</v>
+        <v>394.26399000000004</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="3"/>
-        <v>1.2222343799999999E-17</v>
+        <v>3.9426399E-17</v>
       </c>
       <c r="O28" s="12" vm="23">
         <v>692.1</v>
@@ -6127,87 +6127,87 @@
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="5"/>
-        <v>5.7851999999999991E-17</v>
+        <v>3.5540999999999993E-17</v>
       </c>
       <c r="R28" s="12">
         <f t="shared" si="6"/>
-        <v>100.50438014335016</v>
+        <v>313.90080179004286</v>
       </c>
       <c r="S28" s="12">
         <f t="shared" si="7"/>
-        <v>8.6434380000000033</v>
+        <v>57.573990000000038</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="8"/>
-        <v>-6.5378099283249185</v>
+        <v>-11.394599104978568</v>
       </c>
       <c r="U28" s="14">
         <f t="shared" si="9"/>
-        <v>2.1056280716750848</v>
+        <v>46.17939089502147</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="10"/>
-        <v>270.09155810453916</v>
+        <v>114.09278317122357</v>
       </c>
       <c r="W28" s="9">
         <f t="shared" si="11"/>
-        <v>3.7024481883767327E-3</v>
+        <v>8.7647962667302126E-3</v>
       </c>
       <c r="X28" s="9">
         <f t="shared" si="12"/>
-        <v>0.94061842572355348</v>
+        <v>0.66363917103699288</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" t="s">
-        <v>53</v>
+        <v>101</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>102</v>
       </c>
       <c r="D29" s="8">
-        <v>45511</v>
+        <v>45630</v>
       </c>
       <c r="E29" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F29" s="1">
-        <v>13.04</v>
+        <v>323.75</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" si="0"/>
-        <v>1.304E-18</v>
+        <v>3.2375000000000002E-17</v>
       </c>
       <c r="H29" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C29,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>4.82E-2</v>
+        <v>0.16109999999999999</v>
       </c>
       <c r="I29" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C29,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.4264</v>
+        <v>0.32779999999999998</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>0.11303939962476547</v>
+        <v>0.49145820622330688</v>
       </c>
       <c r="K29" s="9">
         <f t="shared" si="2"/>
-        <v>8.340759278081443E-3</v>
+        <v>3.6665055479356237E-2</v>
       </c>
       <c r="L29" s="9">
         <f t="shared" si="13"/>
-        <v>5.5602559999999997E-19</v>
+        <v>1.0612525E-17</v>
       </c>
       <c r="M29" s="12">
         <f t="shared" si="14"/>
-        <v>13.668528</v>
+        <v>375.90612500000003</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="3"/>
-        <v>1.3668528E-18</v>
+        <v>3.7590612500000005E-17</v>
       </c>
       <c r="O29" s="12" vm="24">
         <v>735.96</v>
@@ -6218,35 +6218,35 @@
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="5"/>
-        <v>7.2291999999999997E-17</v>
+        <v>4.1220999999999994E-17</v>
       </c>
       <c r="R29" s="12">
         <f t="shared" si="6"/>
-        <v>9.4616166013640974</v>
+        <v>277.49207165509563</v>
       </c>
       <c r="S29" s="12">
         <f t="shared" si="7"/>
-        <v>0.62852800000000109</v>
+        <v>52.156125000000031</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="8"/>
-        <v>-1.7891916993179509</v>
+        <v>-23.128964172452186</v>
       </c>
       <c r="U29" s="14">
         <f t="shared" si="9"/>
-        <v>-1.1606636993179498</v>
+        <v>29.027160827547846</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="10"/>
-        <v>273.35784987553217</v>
+        <v>131.2450132386972</v>
       </c>
       <c r="W29" s="9">
         <f t="shared" si="11"/>
-        <v>3.6582084635774286E-3</v>
+        <v>7.619337110974918E-3</v>
       </c>
       <c r="X29" s="9">
         <f t="shared" si="12"/>
-        <v>0.95199358400375444</v>
+        <v>0.76340789809426191</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -6254,51 +6254,51 @@
         <v>36</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="D30" s="8">
-        <v>45481</v>
+        <v>45544</v>
       </c>
       <c r="E30" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F30" s="1">
-        <v>700.32</v>
+        <v>188.12</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" si="0"/>
-        <v>7.0031999999999998E-17</v>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="H30" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.2051</v>
+        <v>0.1164</v>
       </c>
       <c r="I30" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C30,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.36940000000000001</v>
+        <v>0.3664</v>
       </c>
       <c r="J30" s="9">
         <f t="shared" si="1"/>
-        <v>0.55522468868435304</v>
+        <v>0.31768558951965065</v>
       </c>
       <c r="K30" s="9">
         <f t="shared" si="2"/>
-        <v>4.0967976554515485E-2</v>
+        <v>2.3700814468519481E-2</v>
       </c>
       <c r="L30" s="9">
         <f t="shared" si="13"/>
-        <v>2.5869820800000001E-17</v>
+        <v>6.8927168000000004E-18</v>
       </c>
       <c r="M30" s="12">
         <f t="shared" si="14"/>
-        <v>843.95563200000015</v>
+        <v>210.01716800000003</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="3"/>
-        <v>8.4395563200000012E-17</v>
+        <v>2.1001716800000003E-17</v>
       </c>
       <c r="O30" s="12" vm="25">
         <v>130.28</v>
@@ -6309,87 +6309,87 @@
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="5"/>
-        <v>-5.7003999999999997E-17</v>
+        <v>-5.784000000000001E-18</v>
       </c>
       <c r="R30" s="12">
         <f t="shared" si="6"/>
-        <v>601.49446019067261</v>
+        <v>150.49600000000001</v>
       </c>
       <c r="S30" s="12">
         <f t="shared" si="7"/>
-        <v>143.6356320000001</v>
+        <v>21.897168000000022</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="8"/>
-        <v>-49.412769904663719</v>
+        <v>-18.811999999999998</v>
       </c>
       <c r="U30" s="14">
         <f t="shared" si="9"/>
-        <v>94.222862095336382</v>
+        <v>3.0851680000000243</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="10"/>
-        <v>177.97432408087786</v>
+        <v>157.18700606624503</v>
       </c>
       <c r="W30" s="9">
         <f t="shared" si="11"/>
-        <v>5.6187880199256406E-3</v>
+        <v>6.3618490168236876E-3</v>
       </c>
       <c r="X30" s="9">
         <f t="shared" si="12"/>
-        <v>0.61981177683226307</v>
+        <v>0.91430370531884808</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>73</v>
+        <v>36</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="D31" s="8">
-        <v>45562</v>
+        <v>45481</v>
       </c>
       <c r="E31" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F31" s="1">
-        <v>56</v>
+        <v>169.34</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="0"/>
-        <v>5.5999999999999995E-18</v>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="H31" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>4.1000000000000003E-3</v>
+        <v>0.21429999999999999</v>
       </c>
       <c r="I31" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C31,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.4047</v>
+        <v>0.40479999999999999</v>
       </c>
       <c r="J31" s="9">
         <f t="shared" si="1"/>
-        <v>1.0130961205831481E-2</v>
+        <v>0.52939723320158105</v>
       </c>
       <c r="K31" s="9">
         <f t="shared" si="2"/>
-        <v>7.4752616303624855E-4</v>
+        <v>3.9495482383163312E-2</v>
       </c>
       <c r="L31" s="9">
         <f t="shared" si="13"/>
-        <v>2.2663199999999999E-18</v>
+        <v>6.8548831999999995E-18</v>
       </c>
       <c r="M31" s="12">
         <f t="shared" si="14"/>
-        <v>56.229599999999998</v>
+        <v>205.62956199999999</v>
       </c>
       <c r="N31" s="12">
         <f t="shared" si="3"/>
-        <v>5.6229599999999995E-18</v>
+        <v>2.0562956199999998E-17</v>
       </c>
       <c r="O31" s="12" vm="26">
         <v>168.57</v>
@@ -6400,87 +6400,87 @@
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="5"/>
-        <v>1.1256999999999999E-17</v>
+        <v>-7.7000000000000438E-20</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="6"/>
-        <v>39.98286448664858</v>
+        <v>142.2427551448971</v>
       </c>
       <c r="S31" s="12">
         <f t="shared" si="7"/>
-        <v>0.22959999999999781</v>
+        <v>36.289561999999989</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="8"/>
-        <v>-8.0085677566757099</v>
+        <v>-13.54862242755145</v>
       </c>
       <c r="U31" s="14">
         <f t="shared" si="9"/>
-        <v>-7.7789677566757121</v>
+        <v>22.740939572448539</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="10"/>
-        <v>279.97615393288993</v>
+        <v>137.53123449379649</v>
       </c>
       <c r="W31" s="9">
         <f t="shared" si="11"/>
-        <v>3.5717327563535976E-3</v>
+        <v>7.2710755755275806E-3</v>
       </c>
       <c r="X31" s="9">
         <f t="shared" si="12"/>
-        <v>0.97504243005832891</v>
+        <v>0.79997272320181023</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>54</v>
+        <v>75</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="D32" s="8">
-        <v>45505</v>
+        <v>45574</v>
       </c>
       <c r="E32" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F32" s="1">
-        <v>86.6</v>
+        <v>153.7552</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" si="0"/>
-        <v>8.6599999999999986E-18</v>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="H32" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C32,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1467</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="I32" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C32,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.21079999999999999</v>
+        <v>8.8400000000000006E-2</v>
       </c>
       <c r="J32" s="9">
         <f t="shared" si="1"/>
-        <v>0.6959203036053131</v>
+        <v>0.25678733031674206</v>
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>5.1349385686489238E-2</v>
+        <v>1.9157522640248916E-2</v>
       </c>
       <c r="L32" s="9">
         <f t="shared" si="13"/>
-        <v>1.8255279999999995E-18</v>
+        <v>1.359195968E-18</v>
       </c>
       <c r="M32" s="12">
         <f t="shared" si="14"/>
-        <v>99.304220000000001</v>
+        <v>157.24544304</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="3"/>
-        <v>9.9304219999999992E-18</v>
+        <v>1.5724544303999999E-17</v>
       </c>
       <c r="O32" s="12" vm="27">
         <v>115.92</v>
@@ -6491,35 +6491,35 @@
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="5"/>
-        <v>2.932000000000001E-18</v>
+        <v>-3.7835199999999994E-18</v>
       </c>
       <c r="R32" s="12">
         <f t="shared" si="6"/>
-        <v>81.383328634526833</v>
+        <v>144.27625035188137</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="7"/>
-        <v>12.704220000000007</v>
+        <v>3.4902430399999957</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="8"/>
-        <v>-2.6083356827365805</v>
+        <v>-4.7394748240593145</v>
       </c>
       <c r="U32" s="14">
         <f t="shared" si="9"/>
-        <v>10.095884317263426</v>
+        <v>-1.2492317840593188</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="10"/>
-        <v>262.10130185895082</v>
+        <v>161.52140585030435</v>
       </c>
       <c r="W32" s="9">
         <f t="shared" si="11"/>
-        <v>3.8153187065745582E-3</v>
+        <v>6.1911298674974715E-3</v>
       </c>
       <c r="X32" s="9">
         <f t="shared" si="12"/>
-        <v>0.91279163134464847</v>
+        <v>0.93951544439369561</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -6527,51 +6527,51 @@
         <v>36</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="D33" s="8">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="E33" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F33" s="1">
-        <v>64.349999999999994</v>
+        <v>147.01</v>
       </c>
       <c r="G33" s="1">
         <f t="shared" si="0"/>
-        <v>6.4349999999999993E-18</v>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H33" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C33,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.56589999999999996</v>
+        <v>0.55089999999999995</v>
       </c>
       <c r="I33" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C33,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.70699999999999996</v>
+        <v>0.48780000000000001</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="1"/>
-        <v>0.80042432814710041</v>
+        <v>1.1293562935629355</v>
       </c>
       <c r="K33" s="9">
         <f t="shared" si="2"/>
-        <v>5.9060351201054816E-2</v>
+        <v>8.4255203464097608E-2</v>
       </c>
       <c r="L33" s="9">
         <f t="shared" si="13"/>
-        <v>4.5495449999999992E-18</v>
+        <v>7.1711477999999992E-18</v>
       </c>
       <c r="M33" s="12">
         <f t="shared" si="14"/>
-        <v>100.765665</v>
+        <v>227.99780899999999</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="3"/>
-        <v>1.0076566499999999E-17</v>
+        <v>2.2799780899999998E-17</v>
       </c>
       <c r="O33" s="12" vm="28">
         <v>90.68</v>
@@ -6582,35 +6582,35 @@
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="5"/>
-        <v>2.6330000000000005E-18</v>
+        <v>-5.6329999999999992E-18</v>
       </c>
       <c r="R33" s="12">
         <f t="shared" si="6"/>
-        <v>56.392954167031817</v>
+        <v>156.91108976411567</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="7"/>
-        <v>36.415665000000004</v>
+        <v>80.987808999999999</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
-        <v>-3.9785229164840885</v>
+        <v>4.9505448820578408</v>
       </c>
       <c r="U33" s="14">
         <f t="shared" si="9"/>
-        <v>32.437142083515916</v>
+        <v>85.938353882057839</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="10"/>
-        <v>239.76004409269834</v>
+        <v>74.333820184187203</v>
       </c>
       <c r="W33" s="9">
         <f t="shared" si="11"/>
-        <v>4.1708367371394474E-3</v>
+        <v>1.3452826688069597E-2</v>
       </c>
       <c r="X33" s="9">
         <f t="shared" si="12"/>
-        <v>0.83498616842587481</v>
+        <v>0.43237471675148936</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="K34" s="9">
         <f t="shared" si="2"/>
-        <v>1.2071439006432665E-2</v>
+        <v>1.2205316750163592E-2</v>
       </c>
       <c r="L34" s="9">
         <f t="shared" si="13"/>
@@ -6693,67 +6693,67 @@
       </c>
       <c r="V34" s="12">
         <f t="shared" si="10"/>
-        <v>278.28205142251318</v>
+        <v>166.35703931254395</v>
       </c>
       <c r="W34" s="9">
         <f t="shared" si="11"/>
-        <v>3.5934764563083838E-3</v>
+        <v>6.0111673310153475E-3</v>
       </c>
       <c r="X34" s="9">
         <f t="shared" si="12"/>
-        <v>0.96914256392586673</v>
+        <v>0.96764269042207396</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>25</v>
+        <v>40</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="D35" s="8">
-        <v>45685</v>
+        <v>45511</v>
       </c>
       <c r="E35" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F35" s="1">
-        <v>336.69</v>
+        <v>113.58</v>
       </c>
       <c r="G35" s="1">
         <f t="shared" si="0"/>
-        <v>3.3669000000000002E-17</v>
+        <v>1.1357999999999999E-17</v>
       </c>
       <c r="H35" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C35,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.17100000000000001</v>
+        <v>7.6100000000000001E-2</v>
       </c>
       <c r="I35" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C35,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24360000000000001</v>
+        <v>0.20619999999999999</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="1"/>
-        <v>0.70197044334975367</v>
+        <v>0.36905916585838994</v>
       </c>
       <c r="K35" s="9">
         <f t="shared" si="2"/>
-        <v>5.1795803124786356E-2</v>
+        <v>2.7533520897633314E-2</v>
       </c>
       <c r="L35" s="9">
         <f t="shared" si="13"/>
-        <v>8.2017684000000009E-18</v>
+        <v>2.3420195999999997E-18</v>
       </c>
       <c r="M35" s="12">
         <f t="shared" si="14"/>
-        <v>394.26399000000004</v>
+        <v>122.223438</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="3"/>
-        <v>3.9426399E-17</v>
+        <v>1.2222343799999999E-17</v>
       </c>
       <c r="O35" s="12" vm="30">
         <v>18.28</v>
@@ -6764,87 +6764,87 @@
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="5"/>
-        <v>-3.1841000000000002E-17</v>
+        <v>-9.5299999999999994E-18</v>
       </c>
       <c r="R35" s="12">
         <f t="shared" si="6"/>
-        <v>313.90080179004286</v>
+        <v>100.50438014335016</v>
       </c>
       <c r="S35" s="12">
         <f t="shared" si="7"/>
-        <v>57.573990000000038</v>
+        <v>8.6434380000000033</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="8"/>
-        <v>-11.394599104978568</v>
+        <v>-6.5378099283249185</v>
       </c>
       <c r="U35" s="14">
         <f t="shared" si="9"/>
-        <v>46.17939089502147</v>
+        <v>2.1056280716750848</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="10"/>
-        <v>226.01779528119278</v>
+        <v>158.16654599456996</v>
       </c>
       <c r="W35" s="9">
         <f t="shared" si="11"/>
-        <v>4.4244303806073417E-3</v>
+        <v>6.3224495022754755E-3</v>
       </c>
       <c r="X35" s="9">
         <f t="shared" si="12"/>
-        <v>0.78712753658379164</v>
+        <v>0.92000135812354489</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D36" s="8">
-        <v>45562</v>
+        <v>45505</v>
       </c>
       <c r="E36" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F36" s="1">
-        <v>668.82</v>
+        <v>86.6</v>
       </c>
       <c r="G36" s="1">
         <f t="shared" si="0"/>
-        <v>6.6881999999999999E-17</v>
+        <v>8.6599999999999986E-18</v>
       </c>
       <c r="H36" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.16070000000000001</v>
+        <v>0.1467</v>
       </c>
       <c r="I36" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C36,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.27700000000000002</v>
+        <v>0.21079999999999999</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="1"/>
-        <v>0.58014440433212999</v>
+        <v>0.6959203036053131</v>
       </c>
       <c r="K36" s="9">
         <f t="shared" si="2"/>
-        <v>4.2806710218939593E-2</v>
+        <v>5.1918873706435574E-2</v>
       </c>
       <c r="L36" s="9">
         <f t="shared" si="13"/>
-        <v>1.8526314000000002E-17</v>
+        <v>1.8255279999999995E-18</v>
       </c>
       <c r="M36" s="12">
         <f t="shared" si="14"/>
-        <v>776.29937400000006</v>
+        <v>99.304220000000001</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="3"/>
-        <v>7.7629937400000001E-17</v>
+        <v>9.9304219999999992E-18</v>
       </c>
       <c r="O36" s="12" vm="31">
         <v>10.79</v>
@@ -6855,35 +6855,35 @@
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>-6.5802999999999994E-17</v>
+        <v>-7.5809999999999984E-18</v>
       </c>
       <c r="R36" s="12">
         <f t="shared" si="6"/>
-        <v>599.14001612469769</v>
+        <v>81.383328634526833</v>
       </c>
       <c r="S36" s="12">
         <f t="shared" si="7"/>
-        <v>107.47937400000001</v>
+        <v>12.704220000000007</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="8"/>
-        <v>-34.839991937651178</v>
+        <v>-2.6083356827365805</v>
       </c>
       <c r="U36" s="14">
         <f t="shared" si="9"/>
-        <v>72.63938206234883</v>
+        <v>10.095884317263426</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="10"/>
-        <v>199.55780411386542</v>
+        <v>150.17628974898162</v>
       </c>
       <c r="W36" s="9">
         <f t="shared" si="11"/>
-        <v>5.0110793934644189E-3</v>
+        <v>6.6588407642211127E-3</v>
       </c>
       <c r="X36" s="9">
         <f t="shared" si="12"/>
-        <v>0.69497820984756919</v>
+        <v>0.87352473722073543</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -6891,909 +6891,909 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="D37" s="8">
-        <v>45482</v>
+        <v>45481</v>
       </c>
       <c r="E37" s="2">
-        <v>1E-4</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F37" s="1">
-        <v>227.38</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" si="0"/>
-        <v>2.2738000000000001E-2</v>
+        <v>6.4349999999999993E-18</v>
       </c>
       <c r="H37" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.2092</v>
+        <v>0.56589999999999996</v>
       </c>
       <c r="I37" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C37,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.28439999999999999</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="1"/>
-        <v>0.73558368495077353</v>
+        <v>0.80042432814710041</v>
       </c>
       <c r="K37" s="9">
         <f t="shared" si="2"/>
-        <v>5.4275999920600518E-2</v>
+        <v>5.971535733234868E-2</v>
       </c>
       <c r="L37" s="9">
         <f t="shared" si="13"/>
-        <v>6.4666871999999997E-3</v>
+        <v>4.5495449999999992E-18</v>
       </c>
       <c r="M37" s="12">
         <f t="shared" si="14"/>
-        <v>274.94789600000001</v>
+        <v>100.765665</v>
       </c>
       <c r="N37" s="12">
         <f t="shared" si="3"/>
-        <v>2.7494789600000003E-2</v>
+        <v>1.0076566499999999E-17</v>
       </c>
       <c r="O37" s="12" vm="32">
         <v>0.72499999999999998</v>
       </c>
       <c r="P37" s="12">
         <f t="shared" si="4"/>
-        <v>7.25E-5</v>
+        <v>7.2499999999999999E-20</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>-2.2665500000000002E-2</v>
+        <v>-6.3624999999999991E-18</v>
       </c>
       <c r="R37" s="12">
         <f t="shared" si="6"/>
-        <v>211.47693452380955</v>
+        <v>56.392954167031817</v>
       </c>
       <c r="S37" s="12">
         <f t="shared" si="7"/>
-        <v>47.567896000000019</v>
+        <v>36.415665000000004</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="8"/>
-        <v>-7.9515327380952243</v>
+        <v>-3.9785229164840885</v>
       </c>
       <c r="U37" s="14">
         <f t="shared" si="9"/>
-        <v>39.616363261904795</v>
+        <v>32.437142083515916</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="10"/>
-        <v>232.58082291430946</v>
+        <v>127.83503198272913</v>
       </c>
       <c r="W37" s="9">
         <f t="shared" si="11"/>
-        <v>4.2995806252196182E-3</v>
+        <v>7.8225818423161408E-3</v>
       </c>
       <c r="X37" s="9">
         <f t="shared" si="12"/>
-        <v>0.80998387746155065</v>
+        <v>0.74357318926288773</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>58</v>
+        <v>72</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D38" s="8">
-        <v>45695</v>
+        <v>45562</v>
       </c>
       <c r="E38" s="2">
-        <v>2.9999999999999997E-4</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F38" s="1">
-        <v>143.18</v>
+        <v>56</v>
       </c>
       <c r="G38" s="1">
         <f t="shared" si="0"/>
-        <v>4.2953999999999999E-2</v>
+        <v>5.5999999999999995E-18</v>
       </c>
       <c r="H38" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1169</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="I38" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C38,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.23899999999999999</v>
+        <v>0.4047</v>
       </c>
       <c r="J38" s="9">
         <f t="shared" si="1"/>
-        <v>0.48912133891213394</v>
+        <v>1.0130961205831481E-2</v>
       </c>
       <c r="K38" s="9">
         <f t="shared" si="2"/>
-        <v>3.6090454825320938E-2</v>
+        <v>7.5581656785325495E-4</v>
       </c>
       <c r="L38" s="9">
         <f t="shared" si="13"/>
-        <v>1.0266005999999999E-2</v>
+        <v>2.2663199999999999E-18</v>
       </c>
       <c r="M38" s="12">
         <f t="shared" si="14"/>
-        <v>159.917742</v>
+        <v>56.229599999999998</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="3"/>
-        <v>4.7975322599999995E-2</v>
+        <v>5.6229599999999995E-18</v>
       </c>
       <c r="O38" s="12" vm="33">
         <v>93.67</v>
       </c>
       <c r="P38" s="12">
         <f t="shared" si="4"/>
-        <v>2.8100999999999998E-2</v>
+        <v>9.3669999999999995E-18</v>
       </c>
       <c r="Q38" s="12">
         <f t="shared" si="5"/>
-        <v>-1.4853000000000002E-2</v>
+        <v>3.7670000000000001E-18</v>
       </c>
       <c r="R38" s="12">
         <f t="shared" si="6"/>
-        <v>127.60003564744677</v>
+        <v>39.98286448664858</v>
       </c>
       <c r="S38" s="12">
         <f t="shared" si="7"/>
-        <v>16.737741999999997</v>
+        <v>0.22959999999999781</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="8"/>
-        <v>-7.7899821762766166</v>
+        <v>-8.0085677566757099</v>
       </c>
       <c r="U38" s="14">
         <f t="shared" si="9"/>
-        <v>8.9477598237233806</v>
+        <v>-7.7789677566757121</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="10"/>
-        <v>263.24942635249084</v>
+        <v>168.05114182292075</v>
       </c>
       <c r="W38" s="9">
         <f t="shared" si="11"/>
-        <v>3.7986787430298154E-3</v>
+        <v>5.9505695061192881E-3</v>
       </c>
       <c r="X38" s="9">
         <f t="shared" si="12"/>
-        <v>0.91679007935697121</v>
+        <v>0.97749671233642166</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>98</v>
+        <v>149</v>
+      </c>
+      <c r="C39" t="s">
+        <v>150</v>
       </c>
       <c r="D39" s="8">
-        <v>45630</v>
+        <v>45481</v>
       </c>
       <c r="E39" s="2">
-        <v>0.28749999999999998</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F39" s="1">
-        <v>34.78</v>
+        <v>51.28</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="0"/>
-        <v>9.99925</v>
+        <v>5.128E-18</v>
       </c>
       <c r="H39" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>-0.1268</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I39" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C39,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.58609999999999995</v>
+        <v>0.25</v>
       </c>
       <c r="J39" s="9">
         <f t="shared" si="1"/>
-        <v>-0.2163453335608258</v>
+        <v>0.1</v>
       </c>
       <c r="K39" s="9">
         <f t="shared" si="2"/>
-        <v>-1.5963322117395103E-2</v>
+        <v>7.4604625612246902E-3</v>
       </c>
       <c r="L39" s="9">
         <f t="shared" si="13"/>
-        <v>5.8605604249999992</v>
+        <v>1.282E-18</v>
       </c>
       <c r="M39" s="12">
         <f t="shared" si="14"/>
-        <v>30.369896000000001</v>
+        <v>52.561999999999998</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="3"/>
-        <v>8.7313450999999986</v>
+        <v>5.2561999999999998E-18</v>
       </c>
       <c r="O39" s="12" vm="34">
         <v>66.790000000000006</v>
       </c>
       <c r="P39" s="12">
         <f t="shared" si="4"/>
-        <v>19.202124999999999</v>
+        <v>6.6790000000000004E-18</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="5"/>
-        <v>9.2028749999999988</v>
+        <v>1.5510000000000005E-18</v>
       </c>
       <c r="R39" s="12">
         <f t="shared" si="6"/>
-        <v>20.304746336622102</v>
+        <v>41.861224489795916</v>
       </c>
       <c r="S39" s="12">
         <f t="shared" si="7"/>
-        <v>-4.4101040000000005</v>
+        <v>1.2819999999999965</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="8"/>
-        <v>-7.2376268316889494</v>
+        <v>-4.7093877551020427</v>
       </c>
       <c r="U39" s="14">
         <f t="shared" si="9"/>
-        <v>-11.64773083168895</v>
+        <v>-3.4273877551020462</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="10"/>
-        <v>283.84491700790318</v>
+        <v>163.69956182134709</v>
       </c>
       <c r="W39" s="9">
         <f t="shared" si="11"/>
-        <v>3.5230505817800389E-3</v>
+        <v>6.1087518431561004E-3</v>
       </c>
       <c r="X39" s="9">
         <f t="shared" si="12"/>
-        <v>0.98851574947139953</v>
+        <v>0.9521850417409945</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>145</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>154</v>
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="D40" s="8">
-        <v>45688</v>
+        <v>45574</v>
       </c>
       <c r="E40" s="2">
-        <v>2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F40" s="1">
-        <v>44.37</v>
+        <v>47.42</v>
       </c>
       <c r="G40" s="1">
         <f t="shared" si="0"/>
-        <v>88.74</v>
+        <v>4.7419999999999999E-18</v>
       </c>
       <c r="H40" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="I40" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C40,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.25</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="J40" s="9">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.23432343234323433</v>
       </c>
       <c r="K40" s="9">
         <f t="shared" si="2"/>
-        <v>7.3786301995309696E-3</v>
+        <v>1.7481611942143663E-2</v>
       </c>
       <c r="L40" s="9">
         <f t="shared" si="13"/>
-        <v>22.184999999999999</v>
+        <v>1.7241911999999999E-18</v>
       </c>
       <c r="M40" s="12">
         <f t="shared" si="14"/>
-        <v>45.479249999999993</v>
+        <v>51.460183999999998</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="3"/>
-        <v>90.958499999999987</v>
+        <v>5.1460184E-18</v>
       </c>
       <c r="O40" s="12" vm="35">
         <v>20.470300000000002</v>
       </c>
       <c r="P40" s="12">
         <f t="shared" si="4"/>
-        <v>40.940600000000003</v>
+        <v>2.04703E-18</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>-47.799399999999991</v>
+        <v>-2.6949699999999999E-18</v>
       </c>
       <c r="R40" s="12">
         <f t="shared" si="6"/>
-        <v>36.220408163265304</v>
+        <v>37.093241551939926</v>
       </c>
       <c r="S40" s="12">
         <f t="shared" si="7"/>
-        <v>1.1092499999999959</v>
+        <v>4.0401839999999964</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="8"/>
-        <v>-4.0747959183673466</v>
+        <v>-5.163379224030038</v>
       </c>
       <c r="U40" s="14">
         <f t="shared" si="9"/>
-        <v>-2.9655459183673507</v>
+        <v>-1.1231952240300416</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="10"/>
-        <v>275.1627320945816</v>
+        <v>161.39536929027508</v>
       </c>
       <c r="W40" s="9">
         <f t="shared" si="11"/>
-        <v>3.6342130796123591E-3</v>
+        <v>6.1959646326745959E-3</v>
       </c>
       <c r="X40" s="9">
         <f t="shared" si="12"/>
-        <v>0.95827925055110219</v>
+        <v>0.93878233230813402</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>99</v>
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D41" s="8">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="E41" s="2">
-        <v>2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F41" s="1">
-        <v>20.5</v>
+        <v>26.63</v>
       </c>
       <c r="G41" s="1">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>2.663E-18</v>
       </c>
       <c r="H41" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.14929999999999999</v>
+        <v>-0.1193</v>
       </c>
       <c r="I41" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C41,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.31569999999999998</v>
+        <v>0.60340000000000005</v>
       </c>
       <c r="J41" s="9">
         <f t="shared" si="1"/>
-        <v>0.47291732657586316</v>
+        <v>-0.19771295989393436</v>
       </c>
       <c r="K41" s="9">
         <f t="shared" si="2"/>
-        <v>3.4894820677541134E-2</v>
+        <v>-1.4750301351576159E-2</v>
       </c>
       <c r="L41" s="9">
         <f t="shared" si="13"/>
-        <v>12.9437</v>
+        <v>1.6068542000000001E-18</v>
       </c>
       <c r="M41" s="12">
         <f t="shared" si="14"/>
-        <v>23.560649999999999</v>
+        <v>23.453040999999999</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="3"/>
-        <v>47.121299999999998</v>
+        <v>2.3453040999999998E-18</v>
       </c>
       <c r="O41" s="12" vm="36">
         <v>46.81</v>
       </c>
       <c r="P41" s="12">
         <f t="shared" si="4"/>
-        <v>93.62</v>
+        <v>4.681E-18</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>52.620000000000005</v>
+        <v>2.018E-18</v>
       </c>
       <c r="R41" s="12">
         <f t="shared" si="6"/>
-        <v>17.575445816186555</v>
+        <v>15.458292215707898</v>
       </c>
       <c r="S41" s="12">
         <f t="shared" si="7"/>
-        <v>3.060649999999999</v>
+        <v>-3.1769590000000001</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="8"/>
-        <v>-1.4622770919067225</v>
+        <v>-5.5858538921460505</v>
       </c>
       <c r="U41" s="14">
         <f t="shared" si="9"/>
-        <v>1.5983729080932765</v>
+        <v>-8.7628128921460515</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="10"/>
-        <v>270.59881326812098</v>
+        <v>169.0349869583911</v>
       </c>
       <c r="W41" s="9">
         <f t="shared" si="11"/>
-        <v>3.6955077072313575E-3</v>
+        <v>5.9159350261975968E-3</v>
       </c>
       <c r="X41" s="9">
         <f t="shared" si="12"/>
-        <v>0.9423849879839844</v>
+        <v>0.9832194070764777</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" t="s">
-        <v>20</v>
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="D42" s="8">
-        <v>45544</v>
+        <v>45511</v>
       </c>
       <c r="E42" s="2">
-        <v>0.51380000000000003</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F42" s="1">
-        <v>138.53</v>
+        <v>20.82</v>
       </c>
       <c r="G42" s="1">
         <f t="shared" si="0"/>
-        <v>71.176714000000004</v>
+        <v>2.0820000000000002E-18</v>
       </c>
       <c r="H42" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C42,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>5.0200000000000002E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="I42" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C42,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.2001</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="J42" s="9">
         <f t="shared" ref="J42:J46" si="15">IFERROR(H42/I42,"")</f>
-        <v>0.25087456271864067</v>
+        <v>1.6807909604519777E-2</v>
       </c>
       <c r="K42" s="9">
         <f t="shared" si="2"/>
-        <v>1.8511106247698882E-2</v>
+        <v>1.2539478033696868E-3</v>
       </c>
       <c r="L42" s="9">
         <f t="shared" si="13"/>
-        <v>14.242460471400001</v>
+        <v>1.474056E-18</v>
       </c>
       <c r="M42" s="12">
         <f t="shared" ref="M42:M46" si="16">IF((1+H42)*F42&lt;0,0,(1+H42)*F42)</f>
-        <v>145.484206</v>
+        <v>21.067758000000001</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="3"/>
-        <v>74.749785042799999</v>
+        <v>2.1067757999999999E-18</v>
       </c>
       <c r="O42" s="12" vm="37">
         <v>39.369999999999997</v>
       </c>
       <c r="P42" s="12">
         <f t="shared" si="4"/>
-        <v>20.228306</v>
+        <v>3.9369999999999999E-18</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="5"/>
-        <v>-50.948408000000001</v>
+        <v>1.8549999999999998E-18</v>
       </c>
       <c r="R42" s="12">
         <f t="shared" ref="R42:R46" si="17">F42/(1+I42-H42)</f>
-        <v>120.47134533437691</v>
+        <v>12.275219621484583</v>
       </c>
       <c r="S42" s="12">
         <f t="shared" ref="S42:S46" si="18">M42-F42</f>
-        <v>6.9542059999999992</v>
+        <v>0.24775800000000103</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" ref="T42:T46" si="19">0.5*(R42-F42)</f>
-        <v>-9.0293273328115475</v>
+        <v>-4.2723901892577087</v>
       </c>
       <c r="U42" s="14">
         <f t="shared" ref="U42:U46" si="20">S42+T42</f>
-        <v>-2.0751213328115483</v>
+        <v>-4.0246321892577077</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="10"/>
-        <v>274.27230750902578</v>
+        <v>164.29680625550276</v>
       </c>
       <c r="W42" s="9">
         <f t="shared" si="11"/>
-        <v>3.6460115462699123E-3</v>
+        <v>6.0865455804714232E-3</v>
       </c>
       <c r="X42" s="9">
         <f t="shared" ref="X42:X46" si="21">V42/MAX($V$2:$V$28)</f>
-        <v>0.95517826591548871</v>
+        <v>0.95565901082276106</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" t="s">
+        <v>77</v>
       </c>
       <c r="D43" s="8">
-        <v>45627</v>
+        <v>45580</v>
       </c>
       <c r="E43" s="2">
-        <v>0.75290000000000001</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F43" s="1">
-        <v>41.16</v>
+        <v>17</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" si="0"/>
-        <v>30.989363999999998</v>
+        <v>1.7E-18</v>
       </c>
       <c r="H43" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C43,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>8.6900000000000005E-2</v>
+        <v>3.1099999999999999E-2</v>
       </c>
       <c r="I43" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C43,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.24529999999999999</v>
+        <v>0.1285</v>
       </c>
       <c r="J43" s="9">
         <f t="shared" si="15"/>
-        <v>0.35426008968609868</v>
+        <v>0.24202334630350195</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="2"/>
-        <v>2.6139541962463975E-2</v>
+        <v>1.805606114039594E-2</v>
       </c>
       <c r="L43" s="9">
         <f t="shared" si="13"/>
-        <v>7.6016909891999989</v>
+        <v>2.1845000000000003E-19</v>
       </c>
       <c r="M43" s="12">
         <f t="shared" si="16"/>
-        <v>44.736803999999992</v>
+        <v>17.528699999999997</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="3"/>
-        <v>33.682339731599996</v>
+        <v>1.7528699999999997E-18</v>
       </c>
       <c r="O43" s="12" vm="38">
         <v>149.71</v>
       </c>
       <c r="P43" s="12">
         <f t="shared" si="4"/>
-        <v>112.71665900000001</v>
+        <v>1.4971000000000001E-17</v>
       </c>
       <c r="Q43" s="12">
         <f t="shared" si="5"/>
-        <v>81.727295000000012</v>
+        <v>1.3271000000000001E-17</v>
       </c>
       <c r="R43" s="12">
         <f t="shared" si="17"/>
-        <v>35.531767955801101</v>
+        <v>15.491160925824675</v>
       </c>
       <c r="S43" s="12">
         <f t="shared" si="18"/>
-        <v>3.5768039999999957</v>
+        <v>0.52869999999999706</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="19"/>
-        <v>-2.8141160220994479</v>
+        <v>-0.75441953708766274</v>
       </c>
       <c r="U43" s="14">
         <f t="shared" si="20"/>
-        <v>0.76268797790054776</v>
+        <v>-0.22571953708766568</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="10"/>
-        <v>271.43449819831369</v>
+        <v>160.4978936033327</v>
       </c>
       <c r="W43" s="9">
         <f t="shared" si="11"/>
-        <v>3.6841300816132317E-3</v>
+        <v>6.2306113653521197E-3</v>
       </c>
       <c r="X43" s="9">
         <f t="shared" si="21"/>
-        <v>0.94529533678923849</v>
+        <v>0.93356201946841255</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>87</v>
+        <v>40</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" t="s">
+        <v>53</v>
       </c>
       <c r="D44" s="8">
-        <v>45623</v>
+        <v>45511</v>
       </c>
       <c r="E44" s="2">
-        <v>3.1236000000000002</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F44" s="1">
-        <v>16</v>
+        <v>13.04</v>
       </c>
       <c r="G44" s="1">
         <f t="shared" si="0"/>
-        <v>49.977600000000002</v>
+        <v>1.304E-18</v>
       </c>
       <c r="H44" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C44,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>7.0499999999999993E-2</v>
+        <v>4.82E-2</v>
       </c>
       <c r="I44" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C44,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.35260000000000002</v>
+        <v>0.4264</v>
       </c>
       <c r="J44" s="9">
         <f t="shared" si="15"/>
-        <v>0.19994327850255245</v>
+        <v>0.11303939962476547</v>
       </c>
       <c r="K44" s="9">
         <f t="shared" si="2"/>
-        <v>1.4753075129521648E-2</v>
+        <v>8.4332620884387897E-3</v>
       </c>
       <c r="L44" s="9">
         <f t="shared" si="13"/>
-        <v>17.622101760000003</v>
+        <v>5.5602559999999997E-19</v>
       </c>
       <c r="M44" s="12">
         <f t="shared" si="16"/>
-        <v>17.128</v>
+        <v>13.668528</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="3"/>
-        <v>53.501020800000006</v>
+        <v>1.3668528E-18</v>
       </c>
       <c r="O44" s="12" vm="39">
         <v>145.47999999999999</v>
       </c>
       <c r="P44" s="12">
         <f t="shared" si="4"/>
-        <v>454.42132800000002</v>
+        <v>1.4548E-17</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="5"/>
-        <v>404.44372800000002</v>
+        <v>1.3244E-17</v>
       </c>
       <c r="R44" s="12">
         <f t="shared" si="17"/>
-        <v>12.479525778020435</v>
+        <v>9.4616166013640974</v>
       </c>
       <c r="S44" s="12">
         <f t="shared" si="18"/>
-        <v>1.1280000000000001</v>
+        <v>0.62852800000000109</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="19"/>
-        <v>-1.7602371109897827</v>
+        <v>-1.7891916993179509</v>
       </c>
       <c r="U44" s="14">
         <f t="shared" si="20"/>
-        <v>-0.63223711098978264</v>
+        <v>-1.1606636993179498</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="10"/>
-        <v>272.82942328720401</v>
+        <v>161.43283776556299</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" si="11"/>
-        <v>3.6652938233399882E-3</v>
+        <v>6.1945265525978439E-3</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" si="21"/>
-        <v>0.95015329033033535</v>
+        <v>0.93900027376936368</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D45" s="8">
-        <v>45553</v>
+        <v>45511</v>
       </c>
       <c r="E45" s="2">
-        <v>1.7345999999999999</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F45" s="1">
-        <v>51.88</v>
+        <v>11.05</v>
       </c>
       <c r="G45" s="1">
         <f t="shared" si="0"/>
-        <v>89.991048000000006</v>
+        <v>1.1050000000000001E-18</v>
       </c>
       <c r="H45" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C45,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>5.8799999999999998E-2</v>
+        <v>-0.1055</v>
       </c>
       <c r="I45" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C45,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.22600000000000001</v>
+        <v>0.57940000000000003</v>
       </c>
       <c r="J45" s="9">
         <f t="shared" si="15"/>
-        <v>0.26017699115044246</v>
+        <v>-0.18208491542975491</v>
       </c>
       <c r="K45" s="9">
         <f t="shared" si="2"/>
-        <v>1.9197498041257564E-2</v>
+        <v>-1.3584376945274503E-2</v>
       </c>
       <c r="L45" s="9">
         <f t="shared" si="13"/>
-        <v>20.337976848</v>
+        <v>6.4023700000000011E-19</v>
       </c>
       <c r="M45" s="12">
         <f t="shared" si="16"/>
-        <v>54.930543999999998</v>
+        <v>9.8842250000000007</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="3"/>
-        <v>95.282521622399997</v>
+        <v>9.8842250000000007E-19</v>
       </c>
       <c r="O45" s="12" vm="40">
         <v>16.010000000000002</v>
       </c>
       <c r="P45" s="12">
         <f t="shared" si="4"/>
-        <v>27.770946000000002</v>
+        <v>1.6010000000000002E-18</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>-62.220102000000004</v>
+        <v>4.960000000000001E-19</v>
       </c>
       <c r="R45" s="12">
         <f t="shared" si="17"/>
-        <v>44.44825222755312</v>
+        <v>6.5582527152946763</v>
       </c>
       <c r="S45" s="12">
         <f t="shared" si="18"/>
-        <v>3.050543999999995</v>
+        <v>-1.165775</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="19"/>
-        <v>-3.7158738862234415</v>
+        <v>-2.2458736423526622</v>
       </c>
       <c r="U45" s="14">
         <f t="shared" si="20"/>
-        <v>-0.66532988622344647</v>
+        <v>-3.4116486423526622</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="10"/>
-        <v>272.86251606243769</v>
+        <v>163.68382270859772</v>
       </c>
       <c r="W45" s="9">
         <f t="shared" si="11"/>
-        <v>3.6648492963803621E-3</v>
+        <v>6.1093392337266917E-3</v>
       </c>
       <c r="X45" s="9">
         <f t="shared" si="21"/>
-        <v>0.95026853893107499</v>
+        <v>0.95209349263992493</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" t="s">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D46" s="8">
         <v>45511</v>
       </c>
       <c r="E46" s="2">
-        <v>0.12939999999999999</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F46" s="1">
-        <v>501.56</v>
+        <v>10.92</v>
       </c>
       <c r="G46" s="1">
         <f t="shared" si="0"/>
-        <v>64.901863999999989</v>
+        <v>1.092E-18</v>
       </c>
       <c r="H46" s="21">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C46,Sheet1!$G:$G,0),1),2.5%)</f>
-        <v>0.1928</v>
+        <v>-1.4844999999999999</v>
       </c>
       <c r="I46" s="11">
         <f>IFERROR(INDEX(Sheet1!$B:$C,MATCH(Positions!$C46,Sheet1!$G:$G,0),2),25%)</f>
-        <v>0.26650000000000001</v>
+        <v>1.3212999999999999</v>
       </c>
       <c r="J46" s="9">
         <f t="shared" si="15"/>
-        <v>0.72345215759849901</v>
+        <v>-1.1235147203511693</v>
       </c>
       <c r="K46" s="9">
         <f t="shared" si="2"/>
-        <v>5.3380859379721229E-2</v>
+        <v>-8.3819395081647249E-2</v>
       </c>
       <c r="L46" s="9">
         <f t="shared" si="13"/>
-        <v>17.296346755999998</v>
+        <v>1.4428596E-18</v>
       </c>
       <c r="M46" s="12">
         <f t="shared" si="16"/>
-        <v>598.2607680000001</v>
+        <v>0</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="3"/>
-        <v>77.414943379200011</v>
+        <v>0</v>
       </c>
       <c r="O46" s="12" vm="41">
         <v>319.57</v>
       </c>
       <c r="P46" s="12">
         <f t="shared" si="4"/>
-        <v>41.352357999999995</v>
+        <v>3.1956999999999997E-17</v>
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="5"/>
-        <v>-23.549505999999994</v>
+        <v>3.0864999999999997E-17</v>
       </c>
       <c r="R46" s="12">
         <f t="shared" si="17"/>
-        <v>467.13234609294966</v>
+        <v>2.8693047453886176</v>
       </c>
       <c r="S46" s="12">
         <f t="shared" si="18"/>
-        <v>96.700768000000096</v>
+        <v>-10.92</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="19"/>
-        <v>-17.213826953525171</v>
+        <v>-4.025347627305691</v>
       </c>
       <c r="U46" s="14">
         <f t="shared" si="20"/>
-        <v>79.486941046474925</v>
+        <v>-14.94534762730569</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="10"/>
-        <v>192.71024512973932</v>
+        <v>175.21752169355074</v>
       </c>
       <c r="W46" s="9">
         <f t="shared" si="11"/>
-        <v>5.1891377094495667E-3</v>
+        <v>5.7071917827314373E-3</v>
       </c>
       <c r="X46" s="9">
         <f t="shared" si="21"/>
-        <v>0.67113096265147254</v>
+        <v>1.0191811227302299</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
